--- a/reports/2026-04-13/Vietnam_Infra_News_Database.xlsx
+++ b/reports/2026-04-13/Vietnam_Infra_News_Database.xlsx
@@ -568,35 +568,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>## [https://www.vntpa.org/pdp8-en](https://www.vntpa.org/pdp8-en)
-### Document Overview
-This document outlines the official approval and detailed contents of Vietnam's National Power Development Plan for 2021-2030 (PDP8), focusing on energy security, renewable energy transition, and grid modernization.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: Article 1. To approve the National Power Development Plan for the 2021 - 2030 period, with a vision to 2050 (NPDP 8)... To ensure national energy security for socio-economic development, industrialization, and modernization. To successfully carry out just energy transition in conjunction with modernizing electricity generation, establishing smart electricity grid, managing advanced power systems towards the green transition, emissions reduction, and scientific and technological development.
-answer: 베트남 정부는 2030년까지의 국가 전력 개발 계획과 2050년 비전을 담은 제8차 국가전력개발계획(PDP8)을 공식 승인하였습니다. 이 계획은 에너지 안보 확보와 경제 성장을 목표로 하며, 특히 화석 연료 의존도를 낮추고 풍력, 태양광 등 재생 에너지 비중을 2050년까지 최대 71.5%로 확대하는 녹색 전환과 탄소 중립 실현을 핵심으로 합니다. 또한, 스마트 그리드 구축과 지역 간 전력망 연결을 통해 에너지 산업 생태계를 현대화하고 신에너지 수출 가능성을 열어두는 포괄적인 에너지 전략을 제시하고 있습니다.
-Source: [www.vntpa.org](https://www.vntpa.org/pdp8-en)</t>
+          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>## [https://www.vntpa.org/pdp8-en](https://www.vntpa.org/pdp8-en)
-### Document Overview
-This document is the official Prime Minister's Decision No. 500/Q-TTg approving Vietnam's Power Development Plan 8 (PDP8), detailing capacity targets, energy mix transitions, and investment requirements for the 2021-2050 period.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: Article 1. To approve the National Power Development Plan for the 2021 - 2030 period, with a vision to 2050 (NPDP 8)... To ensure adequate electricity supply for the domestic demand, meeting the national socio-economic development goals with average GDP growth of approximately 7%/year in the 2021 – 2030 period... By 2030, the share of renewable energy is expected to reach about 30.9-39.2%... By 2050, it is oriented to phase out coal for power generation.
-answer: Vietnam has officially approved the National Power Development Plan for 2021-2030 (PDP8), which prioritizes national energy security and a just energy transition by targeting a renewable energy share of up to 47% by 2030 and nearly 71.5% by 2050. The plan outlines a total investment requirement of approximately $134.7 billion through 2030 to modernize the grid and shift away from coal-fired power toward domestic gas, LNG, and expanded wind and solar capacities. Furthermore, the strategy aims for 100% rural electrification by 2025 and establishes inter-regional renewable energy industrial hubs to foster a comprehensive green energy ecosystem.
-Source: [www.vntpa.org](https://www.vntpa.org/pdp8-en)</t>
+          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>## [https://www.vntpa.org/pdp8-en](https://www.vntpa.org/pdp8-en)
-### Document Overview
-This document is the official English translation of Vietnam's National Power Development Plan for 2021-2030 (PDP8), detailing targets for energy security, renewable energy expansion, and the roadmap for transitioning away from fossil fuels.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Article 1. To approve the National Power Development Plan for the 2021 - 2030 period, with a vision to 2050 (NPDP 8)... To ensure national energy security for socio-economic development, industrialization, and modernization... To successfully carry out just energy transition in conjunction with modernizing electricity generation, establishing smart electricity grid... towards the green transition, emissions reduction.
-answer: Quyết định số 500/QĐ-TTg phê duyệt Quy hoạch điện VIII (PDP8) nhằm đảm bảo an ninh năng lượng quốc gia và thúc đẩy chuyển đổi năng lượng công bằng thông qua việc ưu tiên phát triển năng lượng tái tạo, khí LNG và hiện đại hóa lưới điện thông minh. Kế hoạch đặt mục tiêu cung cấp đủ điện cho tăng trưởng GDP trung bình 7%/năm giai đoạn 2021-2030, đồng thời hướng tới mục tiêu phát thải ròng bằng không vào năm 2050 bằng cách loại bỏ dần nhiệt điện than.
-Source: [www.vntpa.org](https://www.vntpa.org/pdp8-en)</t>
+          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -646,35 +628,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>## [https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)
-### Document Overview
-This article analyzes Vietnam's Power Development Plan VIII (PDP8), detailing the strategic shift toward renewables, required investment of $700 billion by 2050, and implications for energy sector investors.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: The market has welcomed the long-awaited PDP VIII, approved in late May of this year, which provides an ambitious plan through 2030 with a vision towards 2050... PDP VIII presents an ambitious shift for Vietnam’s generation mix away from coal, and heavily weighted towards in renewables and new technologies such as battery storage, hydrogen, and ammonia... This amounts to a roughly 2x projected growth to 150 GW in installed capacity by 2030, and 500 GW by 2050. Nearly 700 billion USD in investment would be required over the next three decades.
-answer: 베트남 정부가 승인한 제8차 국가전력개발계획(PDP8)은 2050년 넷제로 달성을 위해 석탄 화력 발전을 줄이고 재생에너지, 수소, 암모니아 및 배터리 저장 시스템(BESS)으로의 과감한 전환을 골자로 하고 있습니다. 이 계획에 따라 베트남은 2030년까지 발전 설비 용량을 150GW로 확충하고 2050년까지 500GW 확대를 목표로 하고 있으며, 이를 위해 향후 30년간 약 7,000억 달러 규모의 막대한 투자가 필요할 것으로 전망됩니다. 이번 마스터플랜 확정은 에너지 섹터의 불확실성을 해소하고 투자자들에게 구체적인 우선순위와 상업적 기회를 제공하는 중요한 이정표가 될 것입니다.
-Source: [www.pwc.com](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)</t>
+          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>## [https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)
-### Document Overview
-This page provides an analysis of Vietnam's PDP8, highlighting the shift toward renewable energy, the $700 billion investment requirement, and capacity targets for 2030 and 2050.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: The market has welcomed the long-awaited PDP VIII, approved in late May of this year, which provides an ambitious plan through 2030 with a vision towards 2050... This amounts to a roughly 2x projected growth to 150 GW in installed capacity by 2030, and 500 GW by 2050. Nearly 700 billion USD in investment would be required over the next three decades in new and retrofitted generation, as well as in grid infrastructure to achieve these ambitious targets.
-answer: 1. Vietnam has officially approved the Power Development Plan VIII (PDP8), which aims to reach 150 GW of installed capacity by 2030 and 500 GW by 2050 to support the nation's economic growth and NetZero commitments. 2. This transition requires approximately $700 billion USD in investments over the next three decades, shifting the generation mix away from coal toward renewables, battery storage, and hydrogen. 3. The plan provides a clearer strategic framework for international and domestic investors to participate in Vietnam's power generation and grid infrastructure modernization.
-Source: [www.pwc.com](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)</t>
+          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>## [https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)
-### Document Overview
-This article discusses Vietnam's Power Development Plan VIII (PDP8), outlining the shift towards renewable energy and the $700 billion investment needed for power infrastructure through 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The market has welcomed the long-awaited PDP VIII, approved in late May of this year, which provides an ambitious plan through 2030 with a vision towards 2050. ... This amounts to a roughly 2x projected growth to 150 GW in installed capacity by 2030, and 500 GW by 2050. Nearly 700 billion USD in investment would be required over the next three decades in new and retrofitted generation, as well as in grid infrastructure to achieve these ambitious targets.
-answer: Quy hoạch điện VIII (PDP VIII) đề ra lộ trình chiến lược nhằm chuyển dịch cơ cấu năng lượng Việt Nam từ than sang năng lượng tái tạo và các công nghệ mới để đạt mục tiêu NetZero vào năm 2050. Kế hoạch này dự kiến cần khoảng 700 tỷ USD vốn đầu tư trong ba thập kỷ tới để nâng công suất lắp đặt lên 150 GW vào năm 2030 và 500 GW vào năm 2050, đồng thời phát triển hệ thống lưới điện hiện đại. Đây là cột mốc quan trọng mở ra nhiều cơ hội cho các nhà đầu tư trong lĩnh vực hạ tầng năng lượng, mặc dù vẫn còn những thách thức trong việc thực thi thực tế.
-Source: [www.pwc.com](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)</t>
+          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,35 +692,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>## [https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover](https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover)
-### Document Overview
-This article analyzes the April 2025 amendments to Vietnam's National Power Development Plan (PDP8), highlighting increased capacity targets, a shift toward solar and nuclear energy, and significant investment requirements for infrastructure.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: On April 15, 2025... the prime minister approved updates to the PDP8 (the “Amended PDP8”). In keeping pace with revised GDP growth ambitions, the Amended PDP8, among other things, significantly increases its targets for the country’s power capacity and further emphasizes renewable energy’s role in the overall energy mix. ... it still emphasizes the development of self-generation, self-consumption rooftop solar power up to 2030. ... The Amended PDP8 now sets out clear goals for nuclear power projects.
-answer: 베트남 정부는 경제 성장 목표에 맞춰 국가 전력개발계획(PDP8)을 개정하여 2030년까지 총 발전 용량 목표를 최대 99.9GW로 상향하고 재생에너지 비중을 확대하기로 했습니다. 이번 개정안은 태양광 및 풍력 발전 목표를 대폭 늘리는 동시에 10% 이상의 ESS(에너지저장장치) 의무화, 원자력 발전 재개, 에너지 수출 목표 도입 등 에너지 안보와 탄소 중립을 위한 구체적인 전략을 담고 있습니다. 또한, 2030년까지 공공기관과 주택의 50%에 자가소비형 옥상 태양광 설치를 목표로 하며, 인프라 확충을 위해 2030년까지 약 1,363억 달러의 막대한 자본이 투입될 예정입니다.
-Source: [www.aoshearman.com](https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover)</t>
+          <t>[Power &amp; Energy] What are the new changes to Vietnam's PDP8 - A&amp;O Shearman — Vietnam's updated PDP8 outlines new energy priorities and investment opportunities, with key implications for legal, ESG, and infrastructure ...</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>## [https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover](https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover)
-### Document Overview
-This article analyzes the April 2025 amendments to Vietnam's National Power Development Plan (PDP8), detailing increased capacity targets, new mandates for solar storage, nuclear power revival, and renewable energy export ambitions.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: On April 15, 2025... the prime minister approved updates to the PDP8 (the “Amended PDP8”)... In keeping pace with revised GDP growth ambitions, the Amended PDP8, among other things, significantly increases its targets for the country’s power capacity and further emphasizes renewable energy’s role in the overall energy mix... The capacity targets increased from 90.5 GW to 89.655 GW–99.934 GW by 2030 and from 185.19 GW–208.56 GW to 205.7 GW–228.6 GW by 2050.
-answer: Vietnam has approved an amended National Power Development Plan (Amended PDP8) which significantly increases national electricity capacity targets to approximately 90-100 GW by 2030 and introduces a more aggressive push for renewable energy, aiming for renewables to constitute up to 75% of the energy mix by 2050. The update mandates storage batteries for solar projects, sets ambitious 2035 nuclear power goals for the Ninh Thuan plants, and establishes a roadmap for power exports and specialized renewable energy industrial centers.
-Source: [www.aoshearman.com](https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover)</t>
+          <t>[Power &amp; Energy] What are the new changes to Vietnam's PDP8 - A&amp;O Shearman — Vietnam's updated PDP8 outlines new energy priorities and investment opportunities, with key implications for legal, ESG, and infrastructure ...</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>## [https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover](https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover)
-### Document Overview
-This article analyzes the April 2025 amendments to Vietnam's Power Development Plan 8 (PDP8), highlighting increased capacity targets, a stronger focus on renewables, the revival of nuclear power, and new investment requirements.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: On April 15, 2025, just under two years after unveiling the original National Power Development Plan for the 2021–2030 period... the prime minister approved updates to the PDP8 (the “Amended PDP8”). In keeping pace with revised GDP growth ambitions, the Amended PDP8, among other things, significantly increases its targets for the country’s power capacity and further emphasizes renewable energy’s role in the overall energy mix.
-answer: Bản sửa đổi Quy hoạch điện VIII (PDP8) được phê duyệt vào tháng 4 năm 2025 nhằm tăng đáng kể mục tiêu công suất điện quốc gia lên khoảng 90-100 GW vào năm 2030 để đáp ứng kỳ vọng tăng trưởng GDP mới. Kế hoạch này tập trung mạnh mẽ vào chuyển đổi năng lượng sạch với mục tiêu năng lượng tái tạo chiếm 74-75% cơ cấu năng lượng vào năm 2050, đồng thời tái khởi động các dự án điện hạt nhân và thúc đẩy xuất khẩu điện sang các nước láng giềng.
-Source: [www.aoshearman.com](https://www.aoshearman.com/en/insights/vietnams-pdp8-gets-a-makeover)</t>
+          <t>[Power &amp; Energy] What are the new changes to Vietnam's PDP8 - A&amp;O Shearman — Vietnam's updated PDP8 outlines new energy priorities and investment opportunities, with key implications for legal, ESG, and infrastructure ...</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -810,35 +756,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>## [https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)
-### Document Overview
-The article analyzes Vietnam's PDP8, highlighting the strategic shift toward renewable energy, the phased decommissioning of coal plants by 2050, and the investment challenges ahead.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: On May 15, 2023, the Vietnamese government released Vietnams Eight Power Development Plan (PDP8) for the period of 2021-2030, with a vision to 2050. The PDP8 represents a paradigm shift in Vietnams energy sector away from carbon intensive fossil fuels towards clean energy. In 2030, wind, solar, hydropower and biomass will provide 48% of Vietnams installed capacity, this share will rise to around 63% in 2050.
-answer: 베트남 정부는 2030년까지의 에너지 믹스와 국가 송전망 계획을 담은 제8차 국가전력개발계획(PDP8)을 확정하여 화석 연료 중심에서 재생 에너지 중심으로의 전환을 본격화했습니다. 이 계획에 따라 약 13GW의 석탄 화력 발전 프로젝트가 취소되고 2050년까지 모든 석탄 발전소의 연료 전환 또는 폐쇄가 추진되며, 2050년에는 태양광과 풍력이 주요 에너지원이 될 전망입니다. 섹터: Power &amp; Energy, 마스터플랜: VN-PWR-PDP8.
-Source: [greenfdc.org](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>## [https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)
-### Document Overview
-This article analyzes Vietnam's Eighth Power Development Plan (PDP8), detailing its targets for coal decommissioning, gas transition, and the expansion of renewable energy to reach net-zero by 2050.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: On May 15, 2023, the Vietnamese government released Vietnams Eight Power Development Plan (PDP8) for the period of 2021-2030, with a vision to 2050... The PDP8 represents a paradigm shift in Vietnams energy sector away from carbon intensive fossil fuels towards clean energy. All stakeholders, including government agencies, public energy companies, investors, NGOs, international partners, and others, should work together to ensure that coal phase out can be achieved as soon as possible and that energy supply can be largely covered by renewable and new forms of energy soon.
-answer: The Vietnamese government has officially released the Eighth National Power Development Plan (PDP8) for 2021-2030, marking a strategic shift toward decarbonization by canceling 13GW of planned coal capacity and prioritizing renewable energy integration. The plan aims for wind, solar, hydropower, and biomass to constitute 48% of installed capacity by 2030, while mandating that all coal-fired plants either convert to alternative fuels or cease operations by 2050. To support this transition, the government targets covering 50% of office and residential buildings with rooftop solar and requires an estimated $135 billion in investment through 2030 to modernize the national grid and power sources.
-Source: [greenfdc.org](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>## [https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)
-### Document Overview
-This article provides a comprehensive analysis of Vietnam's Power Development Plan 8 (PDP8), detailing the shift from coal to renewable energy and the associated investment challenges.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: On May 15, 2023, the Vietnamese government released Vietnams Eight Power Development Plan (PDP8) for the period of 2021-2030, with a vision to 2050... The PDP8 represents a paradigm shift in Vietnams energy sector away from carbon intensive fossil fuels towards clean energy.
-answer: Quy hoạch điện VIII (PDP8) của Việt Nam định hướng lộ trình phát triển hạ tầng năng lượng giai đoạn 2021-2030, tập trung vào việc giảm dần nhiệt điện than và đẩy mạnh chuyển đổi sang các nguồn năng lượng tái tạo như gió và mặt trời. Kế hoạch này đặt mục tiêu hiện đại hóa hệ thống lưới điện thông minh và thu hút hàng trăm tỷ USD vốn đầu tư để đạt được phát thải ròng bằng không vào năm 2050.
-Source: [greenfdc.org](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -892,26 +820,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>## [https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)
-### Document Overview
-This page is a placeholder or an introductory guide for the ITA's Global Business Navigator Chatbot, rather than the specific market intelligence report on Vietnam's Power Development Plan VIII.
-Source: [www.trade.gov](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)</t>
+          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (관련: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>## [https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)
-### Document Overview
-The page provides an overview and user disclaimer for the Global Business Navigator Chatbot, an AI tool by the International Trade Administration, rather than the expected market intelligence on Vietnam.
-Source: [www.trade.gov](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)</t>
+          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (Related: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>## [https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)
-### Document Overview
-Nội dung trang web hiện tại chỉ cung cấp thông tin giới thiệu và hướng dẫn sử dụng cho chatbot Global Business Navigator của ITA, không chứa nội dung bài báo về cơ sở hạ tầng Việt Nam.
-Source: [www.trade.gov](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)</t>
+          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (Liên quan: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -961,35 +880,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>## [https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)
-### Document Overview
-This article analyzes Vietnam's Power Development Plan 8 (PDP8), detailing the strategic shift toward renewable energy (solar, wind) and the regulatory/infrastructural challenges facing the transition.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam’s Power Development Plan 8 (PDP8) stands as a seminal policy document, articulating a profound strategic shift towards accelerating the nation’s transition from a fossil fuel-dependent energy landscape to one dominated by renewables... Approved in May 2023, this comprehensive sectoral development plan spans the period 2021-2030, with an ambitious vision extending to 2050... The commitment to net-zero by 2050 has been a primary catalyst for the iterative revisions and ratifications of PDP8.
-answer: 베트남의 제8차 국가전력개발계획(PDP8)은 2050년 탄소중립 달성을 목표로 화석 연료 중심에서 재생에너지 중심으로의 에너지 전환을 가속화하는 핵심 전략입니다. 이 계획은 태양광, 풍력, 에너지 저장 시스템(BESS) 분야의 투자를 장려하고 직접전력구매계약(DPPA) 등 시장 자유화 조치를 포함하고 있으나, 낮은 가격 체계와 송전망 부족 문제는 여전히 해결해야 할 과제로 남아있습니다.
-Source: [sea.ub-speeda.com](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>## [https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)
-### Document Overview
-This report analyzes Vietnam's PDP8 energy strategy, highlighting the shift toward solar, wind, and storage while addressing barriers like grid curtailment and pricing frameworks.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam’s Power Development Plan 8 (PDP8) stands as a seminal policy document, articulating a profound strategic shift towards accelerating the nation’s transition from a fossil fuel-dependent energy landscape to one dominated by renewables. Approved in May 2023, this comprehensive sectoral development plan spans the period 2021-2030, with an ambitious vision extending to 2050... The commitment to net-zero by 2050 has been a primary catalyst for the iterative revisions and ratifications of PDP8... The revisions are meticulously aligned with fulfilling domestic electricity needs and supporting ambitious economic growth targets.
-answer: Vietnam's Power Development Plan 8 (PDP8) outlines a strategic transition toward a renewable-heavy energy mix to achieve net-zero emissions by 2050 while supporting 10% annual economic growth. The plan emphasizes rapid deployment of rooftop solar through new Direct Power Purchase Agreements (DPPAs), expansion of onshore wind, and the critical integration of energy storage systems to stabilize the national grid. Despite high ambitions, the infrastructure shift faces challenges including grid congestion in renewable-rich regions and the need for more attractive pricing frameworks to secure large-scale investment.
-Source: [sea.ub-speeda.com](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>## [https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)
-### Document Overview
-This report analyzes Vietnam's Power Development Plan 8 (PDP8), detailing the transition to renewable energy, investment opportunities in solar and wind, and critical infrastructure bottlenecks such as grid transmission capacity and pricing frameworks.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s Power Development Plan 8 (PDP8) stands as a seminal policy document, articulating a profound strategic shift towards accelerating the nation’s transition from a fossil fuel-dependent energy landscape to one dominated by renewables... Vietnam’s wind power strategy under PDP8 clearly delineates a near-term focus on onshore and nearshore wind development... The rapid build-out of renewable energy capacity in Vietnam has exposed a critical structural vulnerability within its power infrastructure: inadequate transmission capabilities.
-answer: Quy hoạch điện 8 (PDP8) của Việt Nam đánh dấu bước chuyển mình chiến lược từ năng lượng hóa thạch sang năng lượng tái tạo với mục tiêu đạt phát thải ròng bằng không vào năm 2050, tập trung mạnh vào điện mặt trời và điện gió. Tuy nhiên, quá trình chuyển đổi này đang đối mặt với nhiều thách thức lớn như hạ tầng lưới điện truyền tải chưa đáp ứng kịp tốc độ phát triển nguồn điện, các rào cản về khung giá và các quy định pháp lý cho điện gió ngoài khơi. Bài báo nhấn mạnh các giải pháp như cơ chế mua bán điện trực tiếp (DPPA) và đầu tư hệ thống lưu trữ năng lượng là yếu tố then chốt để giải quyết tình trạng nghẽn mạng lưới và thu hút đầu tư bền vững.
-Source: [sea.ub-speeda.com](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1043,35 +944,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>## [https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)
-### Document Overview
-The article details Vietnam's newly approved Power Development Plan VIII (PDP8), which aims for energy transition, carbon neutrality by 2050, and massive investment in wind and LNG infrastructure.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030
-verbatim: On May 15, 2023, after two years of consultation with public and private stakeholders and 12 draft plans, Prime Minister Pham Minh Chinh approved Vietnam's PDP8 as part of Vietnam's National Electricity Development Plan 2021 30. PDP8 calls for significant expansion of the country's electricity grid, more than doubling its capacity from 69 GW in 2020 to 150 GW by 2030, and set energy transition goals for achieving carbon neutrality by 2050. Much of the expansion is slated to come from investments in offshore wind facilities and LNG-supplied natural gas power plants.
-answer: 베트남 정부는 2030년까지 발전 용량을 150GW로 두 배 이상 확대하고 2050년 탄소 중립 달성을 목표로 하는 제8차 국가전력개발계획(PDP8)을 최종 승인했습니다. 이 계획은 석탄 화력 발전의 단계적 폐지와 함께 해상 풍력 및 LNG 발전 시설 확대를 핵심으로 하며, 이를 위해 2030년까지 약 1,347억 달러 규모의 국내외 투자가 투입될 예정입니다. 아울러 재생에너지 비중을 2050년까지 67.5%로 높이기 위한 법적 개정 및 송전망 인프라 개선이 병행될 계획입니다.
-Source: [www.whitecase.com](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)</t>
+          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (관련: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>## [https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)
-### Document Overview
-This article analyzes Vietnam's newly approved Power Development Plan VIII (PDP8), detailing its investment requirements, shifts in the energy mix toward LNG and renewables, and the roadmap for carbon neutrality by 2050.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030
-verbatim: On May 15, 2023, after two years of consultation with public and private stakeholders and 12 draft plans, Prime Minister Pham Minh Chinh approved Vietnam's PDP8 as part of Vietnam's National Electricity Development Plan 2021 30. PDP8 calls for significant expansion of the country's electricity grid, more than doubling its capacity from 69 GW in 2020 to 150 GW by 2030, and set energy transition goals for achieving carbon neutrality by 2050. Much of the expansion is slated to come from investments in offshore wind facilities and LNG-supplied natural gas power plants.
-answer: Vietnam has officially approved the Power Development Plan VIII (PDP8), which aims to double the nation's electricity capacity to 150 GW by 2030 through a projected investment of US$134.7 billion. The plan prioritizes a transition toward renewable energy and LNG-supplied gas while phasing out new coal-fired plant development after 2030 to achieve carbon neutrality by 2050. This strategic framework is expected to unlock billions in international funding, including a US$15.5 billion pledge from G7 nations to support the country's move away from coal.
-Source: [www.whitecase.com](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)</t>
+          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (Related: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>## [https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)
-### Document Overview
-This article analyzes Vietnam's Power Development Plan VIII (PDP8), detailing its investment requirements, shifts in the energy mix toward LNG and renewables, and the roadmap for achieving carbon neutrality by 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: On May 15, 2023, after two years of consultation with public and private stakeholders and 12 draft plans, Prime Minister Pham Minh Chinh approved Vietnam's PDP8 as part of Vietnam's National Electricity Development Plan 2021 30. PDP8 calls for significant expansion of the country's electricity grid, more than doubling its capacity from 69 GW in 2020 to 150 GW by 2030, and set energy transition goals for achieving carbon neutrality by 2050. Much of the expansion is slated to come from investments in offshore wind facilities and LNG-supplied natural gas power plants.
-answer: Quy hoạch Phát triển Điện lực Quốc gia VIII (PDP8) của Việt Nam đã được phê duyệt với mục tiêu tăng gấp đôi công suất lưới điện lên 150 GW vào năm 2030 và hướng tới trung hòa carbon vào năm 2050. Kế hoạch này tập trung vào việc huy động 134,7 tỷ USD đầu tư để mở rộng năng lượng tái tạo (đặc biệt là điện gió ngoài khơi) và khí hóa lỏng (LNG), đồng thời thực hiện lộ trình ngừng dần các nhà máy nhiệt điện than. Bên cạnh việc nâng cấp hạ tầng truyền tải, Việt Nam cũng dự kiến sửa đổi Luật Điện lực và ban hành Luật Năng lượng tái tạo để hỗ trợ quá trình chuyển đổi năng lượng này.
-Source: [www.whitecase.com](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)</t>
+          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1125,35 +1008,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>## [https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)
-### Document Overview
-The article discusses Vietnam's Amended National Power Development Plan (PDP8) and the new regulatory framework (Decree 56) aimed at accelerating LNG power projects to meet the country's growing electricity demand and net-zero goals.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030
-verbatim: On April 15, 2025 the Prime Minister issued a new decision (Decision 768) approving the amended National Power Plan (“Amended PDP8”) to address the actual implementation and changes of circumstances. ... Under the Plan Vietnam has five years (until 2030) to develop 15 LNG power plants. ... To address these challenges, the Government has recently issued Decree 56, which provides guidance on LNG project development. ... During the loan repayment period, at least 65% of the electricity output from LNG power plants can be sold to the national grid.
-answer: 베트남 정부는 수정된 제8차 국가전력개발계획(Amended PDP8)을 통해 2030년까지 15개의 LNG 발전소 건설을 추진하며, 총 발전 용량을 150,500MW까지 확대할 계획입니다. 이를 지원하기 위해 연료비 전가 메커니즘(FCPTM)과 최소 65%의 전력 구매 보장 등을 골자로 하는 법령(Decree 56)을 시행하여 프로젝트의 경제성과 은행 대출성(Bankability)을 높이고자 합니다. 이러한 조치는 지연되는 석탄 및 풍력 발전 프로젝트를 보완하고 2050년 넷제로 목표를 달성하기 위한 핵심적인 에너지 믹스 전환 전략의 일환입니다.
-Source: [www.lexology.com](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)</t>
+          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (관련: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>## [https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)
-### Document Overview
-This article details Vietnam's Amended PDP8 (Decision 768) and Decree 56, highlighting strategies to reach 150,500 MW capacity by 2030 through LNG power development and investor incentives.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030
-verbatim: On April 15, 2025 the Prime Minister issued a new decision (Decision 768) approving the amended National Power Plan (“Amended PDP8”) to address the actual implementation and changes of circumstances... Power generated by LNG plants is expected to reach 22,525 MW by 2030... To address these challenges, the Government has recently issued Decree 56, which provides guidance on LNG project development. Key provisions include: Fuel Cost Pass-Through Mechanism (FCPTM) and Guarantee for Offtake Arrangements.
-answer: Vietnam has issued Decision 768 to amend the National Power Development Plan (PDP8), targeting a total power generation capacity of 150,500 MW by 2030 with a significant focus on LNG power. To accelerate infrastructure development and ensure project bankability, the government introduced Decree 56, which establishes a fuel cost pass-through mechanism and guarantees that the national grid will purchase at least 65% of electricity output from LNG plants. These regulatory updates aim to resolve delays in coal and offshore wind projects while streamlining the negotiation process for 15 planned LNG power plants required by 2030.
-Source: [www.lexology.com](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)</t>
+          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (Related: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>## [https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)
-### Document Overview
-Bài viết cung cấp cái nhìn chi tiết về Quy hoạch điện VIII cập nhật của Việt Nam, tập trung vào chiến lược phát triển điện khí LNG và các giải pháp chính sách để tháo gỡ khó khăn cho nhà đầu tư.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: In May 2023, the Prime Minister issued the long-awaited Decision 500, approving the National Power Development Plan, known as PDP8... To support this growth, Vietnam must double its current power generation capacity to reach 150,500 MW by 2030... LNG power generation is relatively new in Vietnam, and the market is still in its early stages. However, LNG will play a critical role in Vietnam’s energy mix over the next decade and is integral to the country’s net-zero commitments.
-answer: Bài báo phân tích lộ trình phát triển hạ tầng năng lượng của Việt Nam thông qua Quy hoạch điện VIII (PDP8) và các quyết định sửa đổi mới nhất vào năm 2025, với mục tiêu nâng tổng công suất nguồn điện lên 150.500 MW vào năm 2030. Trọng tâm của bài báo là sự chuyển dịch sang điện khí LNG với kế hoạch phát triển 15 dự án nhà máy đến năm 2035, đồng thời nêu rõ các cơ chế hỗ trợ mới từ Chính phủ như Nghị định 56 nhằm giải quyết các rào cản về giá, cơ sở hạ tầng cảng biển và bao tiêu sản lượng.
-Source: [www.lexology.com](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)</t>
+          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1207,36 +1072,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>## [https://www.eia.gov/todayinenergy/detail.php?id=48176](https://www.eia.gov/todayinenergy/detail.php?id=48176)
-### Document Overview
-This article discusses Vietnam's draft Power Development Plan 8 (PDP 8) which aims to shift the energy mix from coal and hydro toward solar and wind, while prioritizing critical grid infrastructure upgrades.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: In February 2021, the government of Vietnam released a draft of the country’s latest national power development plan, Power Development Plan 8 (PDP 8), for 2021 to 2030. The draft PDP 8 expands wind and solar capacity and increases their shares of the country’s generation mix. The draft PDP 8 also prioritizes enhancing grid infrastructure to ensure stable operation with a higher share of renewables.
-answer: 베트남 정부는 2021년부터 2030년까지를 아우르는 제8차 국가 전력개발계획(PDP 8) 초안을 통해 풍력 및 태양광 발전 용량을 대폭 확대하고 재생에너지 비중을 높일 계획입니다. 특히 낙후된 전력망 인프라 확충과 송전 병목 현상 해결을 최우선 과제로 삼아, 중남부 지역을 잇는 500kV 송전선 연장 등 전력망 현대화에 집중하고 있습니다. 이를 통해 석탄 화력 발전 의존도를 낮추고 급증하는 전력 수요와 탄소 배출 감소 목표를 동시에 달성하고자 합니다.
-Source: [www.eia.gov](https://www.eia.gov/todayinenergy/detail.php?id=48176)</t>
+          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>## [https://www.eia.gov/todayinenergy/detail.php?id=48176](https://www.eia.gov/todayinenergy/detail.php?id=48176)
-### Document Overview
-The article discusses Vietnam's draft Power Development Plan 8 (PDP 8) which focuses on doubling renewable energy capacity and upgrading the national grid to reduce coal dependency by 2030.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: In February 2021, the government of Vietnam released a draft of the country’s latest national power development plan, Power Development Plan 8 (PDP 8), for 2021 to 2030. The draft PDP 8 expands wind and solar capacity and increases their shares of the country’s generation mix. The draft PDP 8 also prioritizes enhancing grid infrastructure to ensure stable operation with a higher share of renewables.
-answer: Vietnam's draft Power Development Plan 8 (PDP 8) aims to transition the energy sector by significantly increasing solar and wind capacity to 18.6 GW and 18.0 GW respectively by 2030. To support this shift away from coal and hydro, the government is prioritizing a massive grid expansion, including a 461-mile high-voltage transmission line extension to resolve current overloading and facilitate the integration of renewable energy sources.
-Source: [www.eia.gov](https://www.eia.gov/todayinenergy/detail.php?id=48176)</t>
+          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>## [https://www.eia.gov/todayinenergy/detail.php?id=48176](https://www.eia.gov/todayinenergy/detail.php?id=48176)
-### Document Overview
-The article discusses Vietnam's draft Power Development Plan 8 (PDP 8), which emphasizes shifting from coal to renewable energy and expanding the national grid to handle increased capacity.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: In February 2021, the government of Vietnam released a draft of the country’s latest national power development plan, Power Development Plan 8 (PDP 8), for 2021 to 2030. The draft PDP 8 expands wind and solar capacity and increases their shares of the country’s generation mix. The draft PDP 8 also prioritizes enhancing grid infrastructure to ensure stable operation with a higher share of renewables.
-answer: 1. Dự thảo Quy hoạch phát triển điện lực quốc gia 8 (PDP 8) của Việt Nam đặt mục tiêu đẩy mạnh công suất điện gió và điện mặt trời nhằm giảm sự phụ thuộc vào than đá và giảm phát thải khí carbon. 
-2. Để hỗ trợ sự gia tăng của các nguồn năng lượng tái tạo, chính phủ ưu tiên phát triển cơ sở hạ tầng lưới điện, bao gồm việc xây dựng thêm các đường dây truyền tải cao thế và mở rộng mạng lưới để khắc phục tình trạng quá tải và nghẽn mạch hiện tại.
-Source: [www.eia.gov](https://www.eia.gov/todayinenergy/detail.php?id=48176)</t>
+          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1290,35 +1136,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)
-### Document Overview
-This article discusses the legal threats from foreign chambers of commerce against the Vietnamese government regarding retroactive tariff cuts for 12GW of renewable energy projects.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, according to a document signed by five chambers of commerce seen by Reuters. ... The retroactive change to tariffs, which took effect in January 2025, followed investigations into alleged abuses in accessing ⁠the preferential rates. ... The letter urges authorities to find an amicable solution to a dispute that the chambers said could lead to defaults and significant losses on multibillion-dollar investments in Vietnam's renewable energy sector.
-answer: 베트남 정부가 재생에너지(풍력·태양광) 프로젝트에 대해 약속했던 고정가격매입(FiT) 관찰을 소급 삭감하자, 유럽연합(EU)·일본·한국 등 5개국 상공회의소가 공동 서한을 통해 국제 분쟁 해결 절차를 포함한 법적 대응을 예고했습니다. 이번 갈등은 베트남 전력공사(EVN)의 누적 적자와 발전 용량 12GW 규모의 민간 투자 프로젝트들에 대한 단가 인하 시도에서 비롯되었으며, 이는 베트남 전력 개발 마스터플랜(PDP8) 추진 과정에서 신재생 에너지 분야의 대규모 외자 유치 및 신뢰도에 상당한 위험 요소로 작용하고 있습니다.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)</t>
+          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)
-### Document Overview
-Five international chambers of commerce have warned Vietnam of potential legal action and dispute resolution over the retroactive cutting of renewable energy tariffs affecting 12GW of capacity.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, according to a document signed by five chambers of commerce seen by Reuters. The dispute begin last year when Vietnam cut previously agreed subsidised prices for electricity from some solar and wind farms, citing irregularities. The move comes as Vietnam's energy sector struggles with higher prices and risks of shortages linked to the conflict in Iran.
-answer: Foreign investors and five international chambers of commerce (EU, UK, Japan, South Korea, and Thailand) are threatening legal action against Vietnam over the government's retroactive reduction of electricity tariffs for 12 gigawatts of wind and solar projects. The dispute arises from Vietnam's decision in January 2025 to cut previously agreed feed-in tariffs due to alleged irregularities, a move that investors warn could lead to multibillion-dollar defaults and undermine the country's renewable energy goals.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)</t>
+          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)
-### Document Overview
-The article reports on a legal threat from international business chambers against the Vietnamese government due to retroactive cuts in renewable energy subsidies and payment disputes.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, according to a document signed by five chambers of commerce seen by Reuters. The dispute began last year when Vietnam cut previously agreed subsidised prices for electricity from some solar and wind farms, citing irregularities. If payment obligations are not met, electricity producers 'may seek to enforce remedies, including pursuing dispute resolution in Vietnam or other jurisdictions,' said the document, dated March 12.
-answer: Các nhà đầu tư nước ngoài đang đe dọa thực hiện các biện pháp pháp lý sau khi Việt Nam hồi tố cắt giảm giá biểu thuế điện hỗ trợ (feed-in tariffs) đối với các dự án điện gió và điện mặt trời có tổng công suất 12 GW. Năm hiệp hội thương mại từ EU, Anh, Nhật Bản, Hàn Quốc và Thái Lan đã gửi thư chung cảnh báo rằng việc không tuân thủ các cam kết thanh toán có thể dẫn đến vỡ nợ và gây tổn thất lớn cho các khoản đầu tư hàng tỷ đô la vào lĩnh vực năng lượng tái tạo.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)</t>
+          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1368,35 +1196,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>## [https://www.vietnamenergyweek.com/en/](https://www.vietnamenergyweek.com/en/)
-### Document Overview
-This page highlights Vietnam Energy Week 2026 as a crucial B2B platform for the energy and HVACR sectors to navigate complex decision chains and secure high-quality business leads in Vietnam.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-EV-2030
-verbatim: Vietnam Energy Week 2026 is increasingly viewed by many companies as a strategic meeting point during a period of accelerated investment in energy and technical infrastructure. Taking place from 4–6 November 2026 at SECC, Ho Chi Minh City, the exhibition is designed as a specialized B2B platform where companies not only showcase solutions but also directly engage with investors, contractors, operators, and technology partners within a single, focused environment. ... it becomes the starting point for high-quality conversations, long-term project relationships, and sustainable growth strategies for companies in the Energy and HVACR industries.
-answer: 베트남의 에너지 및 기술 인프라 투자 가속화에 따라, '베트남 에너지 위크(Vietnam Energy Week) 2026'이 2026년 11월 4일부터 6일까지 호치민 SECC에서 개최되어 전력 및 에너지 산업의 핵심 B2B 플랫폼 역할을 수행할 예정입니다. 본 행사는 단순 전시를 넘어 투자자, 설계 컨설턴트, 시공사 등 다수의 이해관계자가 참여하는 복잡한 결정 체인 속에서 실질적인 비즈니스 기회 창출과 지속 가능한 성장을 위한 전략적 접점을 제공하는 것을 목표로 합니다.
-Source: [www.vietnamenergyweek.com](https://www.vietnamenergyweek.com/en/)</t>
+          <t>[Power &amp; Energy] vietnam energy week 2026 — The event brings together industry leaders, technology providers, and decision-makers to explore advancements shaping Vietnam's digital economy. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>## [https://www.vietnamenergyweek.com/en/](https://www.vietnamenergyweek.com/en/)
-### Document Overview
-The article promotes Vietnam Energy Week 2026 as a strategic B2B platform for the Energy and HVACR sectors to facilitate high-quality industry interactions and infrastructure investment.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-EV-2030
-verbatim: Vietnam Energy Week 2026 is increasingly viewed by many companies as a strategic meeting point during a period of accelerated investment in energy and technical infrastructure. Taking place from 4–6 November 2026 at SECC, Ho Chi Minh City, the exhibition is designed as a specialized B2B platform where companies not only showcase solutions but also directly engage with investors, contractors, operators, and technology partners.
-answer: Vietnam Energy Week 2026 will be held from November 4–6, 2026, at the SECC in Ho Chi Minh City, serving as a strategic hub for B2B engagement amidst a period of accelerated investment in Vietnam's energy and technical infrastructure. The platform aims to connect solution providers directly with investors, contractors, and technology partners to support long-term growth and high-quality project development in the Power, Energy, and HVACR sectors. This event aligns with the broader context of infrastructure development and sustainable energy goals for the region.
-Source: [www.vietnamenergyweek.com](https://www.vietnamenergyweek.com/en/)</t>
+          <t>[Power &amp; Energy] vietnam energy week 2026 — The event brings together industry leaders, technology providers, and decision-makers to explore advancements shaping Vietnam's digital economy. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>## [https://www.vietnamenergyweek.com/en/](https://www.vietnamenergyweek.com/en/)
-### Document Overview
-The article discusses the strategic importance of Vietnam Energy Week 2026 for the Energy and HVACR sectors, providing advice on how to maximize ROI at B2B exhibitions through targeted engagement and standardized conversion processes.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam Energy Week 2026... Taking place from 4–6 November 2026 at SECC, Ho Chi Minh City, the exhibition is designed as a specialized B2B platform where companies not only showcase solutions but also directly engage with investors, contractors, operators, and technology partners within a single, focused environment. ... When approached with the right preparation, exhibiting at Vietnam Energy Week 2026 goes beyond three days of brand exposure. It becomes the starting point for high-quality conversations, long-term project relationships, and sustainable growth strategies for companies in the Energy and HVACR industries.
-answer: Sự kiện Vietnam Energy Week 2026 sẽ diễn ra từ ngày 4–6 tháng 11 năm 2026 tại SECC, TP. Hồ Chí Minh, đóng vai trò là nền tảng B2B chiến lược kết nối các doanh nghiệp trong ngành Năng lượng và HVACR với các nhà đầu tư và nhà thầu. Bài viết nhấn mạnh rằng thay vì chỉ tập trung vào số lượng khách tham quan, các doanh nghiệp cần chú trọng vào chất lượng tương tác và xác định đúng nhóm khách hàng mục tiêu để tối ưu hóa hiệu quả đầu tư (ROI) trong bối cảnh hạ tầng năng lượng đang phát triển mạnh mẽ.
-Source: [www.vietnamenergyweek.com](https://www.vietnamenergyweek.com/en/)</t>
+          <t>[Power &amp; Energy] vietnam energy week 2026 — The event brings together industry leaders, technology providers, and decision-makers to explore advancements shaping Vietnam's digital economy. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1450,32 +1260,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=bdfXnoZeULc](https://www.youtube.com/watch?v=bdfXnoZeULc)
-### Document Overview
-This video reports on Vietnam's commitment to net-zero emissions by 2050, focusing on renewable energy alternatives and infrastructure developments under PDP8.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's commitment to net-zero emissions by 2050 at COP26 earlier in 2026, prioritising renewable energy. ... An alternative to urban solar energy.
-answer: 베트남 정부는 제8차 국가전력개발계획(PDP8)에 따라 2050년 탄소중립 실현을 위해 재생에너지 보급을 최우선 과제로 추진하고 있습니다. 특히 도시 환경에 적합한 새로운 태양광 에너지 대안을 모색하며 에너지 전환 가속화를 위한 인프라 구축에 집중하고 있습니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=bdfXnoZeULc)</t>
+          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=bdfXnoZeULc](https://www.youtube.com/watch?v=bdfXnoZeULc)
-### Document Overview
-The provided page content is a skeletal YouTube interface containing only footer navigation links and metadata, with no specific details about Vietnam's energy infrastructure.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=bdfXnoZeULc)</t>
+          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=bdfXnoZeULc](https://www.youtube.com/watch?v=bdfXnoZeULc)
-### Document Overview
-Nội dung đề cập đến cam kết của Việt Nam về phát thải ròng bằng 0 vào năm 2050 và việc ưu tiên phát triển năng lượng tái tạo thay thế cho khu vực đô thị.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's commitment to net-zero emissions by 2050 at COP26 earlier in 2026, prioritising renewable energy. Bu...
-answer: Thủ tướng Phạm Minh Chính đã tái khẳng định cam kết của Việt Nam trong việc đạt mức phát thải ròng bằng '0' vào năm 2050 tại hội nghị COP26. Để thực hiện mục tiêu này, Chính phủ ưu tiên phát triển hạ tầng năng lượng tái tạo và tìm kiếm các giải pháp thay thế hiệu quả cho năng lượng mặt trời tại các khu vực đô thị.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=bdfXnoZeULc)</t>
+          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1529,35 +1324,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>## [https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/](https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/)
-### Document Overview
-The article discusses Vietnam's new directive to enhance energy security through rooftop solar expansion and nationwide energy conservation measures.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-EV-2030
-verbatim: Pham Minh Chinh has issued a major directive to strengthen Vietnams energy security by focusing on electricity conservation and expanding rooftop solar power. ... The government wants to make it easier for people and companies to install solar panels by reducing complex procedures and creating a more supportive policy environment. ... One of the major projects mentioned is the 500kV Circuit-3 transmission line, which will help move electricity from regions with surplus power to areas facing shortages.
-answer: 베트남 팜 민 찐 총리는 에너지 안보 강화를 위해 전력 절약 장려와 지붕형 태양광(Rooftop Solar) 확대를 골자로 하는 주요 지침을 발표했습니다. 정부는 규제 완화와 정책 지원을 통해 민간의 전력 자가 생산 및 소비를 촉진하고, 500kV 회로-3 송전선로 등 핵심 인프라 구축을 가속화하여 전력 공급의 안정성을 확보할 계획입니다. 이는 전력 및 에너지 섹터의 장기적인 탄소 중립 목표 달성과 경제 성장을 뒷받침하기 위한 전략적 조치입니다.
-Source: [solarquarter.com](https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/)</t>
+          <t>[Power &amp; Energy] Vietnam Pushes Rooftop Solar and Energy Saving to Secure Power ... — Vietnam accelerates rooftop solar adoption and energy conservation measures to ensure stable power supply and achieve long term climate ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>## [https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/](https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/)
-### Document Overview
-This article details a new directive from Vietnam's Prime Minister to enhance power security through rooftop solar expansion, energy-saving measures, and critical transmission line infrastructure.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-EV-2030
-verbatim: Pham Minh Chinh has issued a major directive to strengthen Vietnams energy security by focusing on electricity conservation and expanding rooftop solar power... By promoting self-production and self-consumption of electricity, Vietnam hopes to reduce pressure on the national grid... One of the major projects mentioned is the 500kV Circuit-3 transmission line, which will help move electricity from regions with surplus power to areas facing shortages.
-answer: Prime Minister Pham Minh Chinh has issued a major directive to bolster Vietnam's energy security by accelerating the deployment of rooftop solar systems and enforcing nationwide electricity conservation. The infrastructure plan includes streamlining policies for self-consumption of solar power and prioritizing the completion of the 500kV Circuit-3 transmission line to stabilize the national grid. This strategy aligns with the country's broader goals of supporting economic growth while transitioning toward a net-zero target by 2050.
-Source: [solarquarter.com](https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/)</t>
+          <t>[Power &amp; Energy] Vietnam Pushes Rooftop Solar and Energy Saving to Secure Power ... — Vietnam accelerates rooftop solar adoption and energy conservation measures to ensure stable power supply and achieve long term climate ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>## [https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/](https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/)
-### Document Overview
-Bản tin về chỉ thị của Thủ tướng Việt Nam nhằm thúc đẩy tiết kiệm năng lượng, phát triển điện mặt trời mái nhà và hoàn thiện hạ tầng truyền tải 500kV.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Pham Minh Chinh has issued a major directive to strengthen Vietnams energy security by focusing on electricity conservation and expanding rooftop solar power... The directive also highlights the importance of improving power infrastructure. One of the major projects mentioned is the 500kV Circuit-3 transmission line, which will help move electricity from regions with surplus power to areas facing shortages.
-answer: Thủ tướng Chính phủ Phạm Minh Chính đã ban hành chỉ thị thúc đẩy an ninh năng lượng quốc gia thông qua việc tiết kiệm điện và phát triển nhanh hệ thống điện mặt trời mái nhà nhằm giảm áp lực cho lưới điện. Về hạ tầng, Chính phủ yêu cầu đẩy nhanh tiến độ dự án đường dây truyền tải 500kV mạch 3 để điều phối điện năng giữa các vùng miền, đồng thời kết hợp hài hòa các nguồn năng lượng tái tạo với thủy điện và nhiệt điện. Những nỗ lực này hướng tới mục tiêu xây dựng hệ thống điện ổn định, hỗ trợ tăng trưởng kinh tế và đạt mức phát thải ròng bằng 0 vào năm 2050.
-Source: [solarquarter.com](https://solarquarter.com/2026/03/31/vietnam-pushes-rooftop-solar-and-energy-saving-to-secure-power-future/)</t>
+          <t>[Power &amp; Energy] Vietnam Pushes Rooftop Solar and Energy Saving to Secure Power ... — Vietnam accelerates rooftop solar adoption and energy conservation measures to ensure stable power supply and achieve long term climate ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1611,32 +1388,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/](https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/)
-### Document Overview
-The page provides a brief update on Prime Minister Pham Minh Chinh's statement regarding Vietnam's commitment to achieving net-zero emissions by 2050.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's commitment to net-zero emissions by 2050
-answer: 제공된 페이지 내용은 팜 민 찐(Phạm Minh Chính) 베트남 총리가 2050년까지 탄소 배출 제로(Net-zero)를 달성하겠다는 베트남의 약속을 재확인했다는 소식을 다루고 있습니다. 베트남 정부는 지속 가능한 에너지 전환과 기후 변화 대응을 위해 국제적 협력을 강조하며 에너지 부문의 인프라 개선을 추진하고 있습니다. 이 기사는 베트남의 환경 및 에너지 정책 방향을 요약하여 보여줍니다.
-Source: [www.facebook.com](https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/)</t>
+          <t>[Power &amp; Energy] Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's ... — With 100GW of additional capacity forecast by 2030, and a ten-fold increase in renewable energy generation, Vietnam is serious about the future ...</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/](https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/)
-### Document Overview
-The page title indicates a news post about Prime Minister Phạm Minh Chính reaffirming Vietnam's commitment to net-zero emissions, though the main body content was blocked by a browser compatibility notice.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's commitment to net-zero emissions
-answer: Prime Minister Phạm Minh Chính has officially reaffirmed Vietnam's national commitment to achieving net-zero emissions by 2050. This announcement emphasizes the country's strategic shift within the Power &amp; Energy sector toward sustainable development and environmental responsibility.
-Source: [www.facebook.com](https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/)</t>
+          <t>[Power &amp; Energy] Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's ... — With 100GW of additional capacity forecast by 2030, and a ten-fold increase in renewable energy generation, Vietnam is serious about the future ...</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/](https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/)
-### Document Overview
-Trang web không hiển thị nội dung bài viết do lỗi tương thích trình duyệt của Facebook, chỉ hiển thị thông báo yêu cầu đổi trình duyệt.
-Source: [www.facebook.com](https://www.facebook.com/vietnamtodayinternational/posts/prime-minister-ph%E1%BA%A1m-minh-ch%C3%ADnh-has-reaffirmed-vi%E1%BB%87t-nams-commitment-to-net-zero-e/1813563669949963/)</t>
+          <t>[Power &amp; Energy] Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's ... — With 100GW of additional capacity forecast by 2030, and a ten-fold increase in renewable energy generation, Vietnam is serious about the future ...</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1690,35 +1452,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>## [https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)
-### Document Overview
-The article analyzes the rapid growth of Vietnam's wind energy sector, which grew from 200 MW in 2019 to 1,700 MW in 2022, targeting 6,000 MW by 2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: Vietnam's total installed wind energy capacity reached approximately 1,700 megawatts (MW). This figure reflects a significant increase from just 200 MW in 2019... The government has set an ambitious target to achieve 6,000 MW of wind power capacity by 2030 as part of its broader strategy to enhance renewable energy sources. One of the key initiatives is the Feed-in Tariff (FiT) program, which was introduced to encourage investment in renewable energy projects.
-answer: 베트남은 전력개발계획(PDP8) 등 국가 에너지 전략에 따라 2030년까지 풍력 발전 용량을 6,000MW로 확대하기 위해 발전차액지원제도(FiT)와 같은 강력한 지원 정책을 시행하며 시장을 빠르게 확장하고 있습니다. 2022년 기준 풍력 설치 용량은 약 1,700MW로 2019년 대비 비약적으로 성장했으며, 빈투언 및 닌투언 지역의 대규모 프로젝트와 ADB 등 국제 금융 기구의 투자가 성장을 견인하고 있습니다. 다만, 변동성이 큰 풍력 에너지를 수용하기 위한 전력망 인프라 개선과 복잡한 규제 체계 정비는 향후 에너지 전환의 핵심 과제로 남아 있습니다.
-Source: [www.renewableenergyasia.org](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)</t>
+          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>## [https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)
-### Document Overview
-The page provides a comprehensive overview of Vietnam's recent wind energy expansion, major infrastructure projects, government support mechanisms, investment partnerships, and sector challenges, directly relating to power and energy infrastructure development in line with VN-PWR-PDP8.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: Vietnam has emerged as a significant player in the wind energy sector, showcasing remarkable growth in recent years. The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce reliance on fossil fuels. As of 2022, Vietnam's total installed wind energy capacity reached approximately 1,700 megawatts (MW), a notable increase from just 200 MW in 2019, with a government target of 6,000 MW by 2030 as part of its broader renewable energy development plans.
-answer: Vietnam's wind energy sector has experienced rapid expansion, with installed capacity rising from 200 MW in 2019 to 1,700 MW by 2022, supported by strong government targets aiming for 6,000 MW by 2030. Major investments, government incentives like the Feed-in Tariff (FiT), and international partnerships are driving growth as Vietnam advances its power and energy infrastructure under its national development plans.
-Source: [www.renewableenergyasia.org](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)</t>
+          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>## [https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)
-### Document Overview
-This article highlights Vietnam's rapid expansion in wind energy, reaching 1,700 MW by 2022, and discusses government policies like Feed-in Tariffs and future capacity targets for 2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: As of 2022, Vietnam's total installed wind energy capacity reached approximately 1,700 megawatts (MW). This figure reflects a significant increase from just 200 MW in 2019, demonstrating the rapid pace of development in the sector. The government has set an ambitious target to achieve 6,000 MW of wind power capacity by 2030 as part of its broader strategy to enhance renewable energy sources.
-answer: Bài báo phân tích sự phát triển mạnh mẽ của ngành năng lượng gió tại Việt Nam với công suất lắp đặt tăng vọt từ 200 MW năm 2019 lên 1.700 MW vào năm 2022. Chính phủ Việt Nam đã triển khai các chính sách ưu đãi như giá mua điện (FiT) và thu hút đầu tư quốc tế nhằm hướng tới mục tiêu đạt 6.000 MW vào năm 2030. Tuy nhiên, ngành này vẫn đang đối mặt với những thách thức về hạ tầng lưới điện và khung pháp lý cần được hoàn thiện để đảm bảo tăng trưởng bền vững.
-Source: [www.renewableenergyasia.org](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)</t>
+          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1772,35 +1516,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>## [https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)
-### Document Overview
-This article analyzes Vietnam's shift from rapid, subsidy-led renewable energy growth to a disciplined, market-based approach under PDP8 and DPPA frameworks.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam is not reversing course on renewable energy. It is correcting structural weaknesses created during an earlier phase of rapid, subsidy-driven growth... With the current PDP8(revised) and the DPPA in place, EVN has a chance to recoup its losses from the FiTs and invest in upgrading their grid and substations. Vietnam’s decision to move decisively away from FiTs toward market-based mechanisms signals policy consistency. It demonstrates a willingness to learn from past excesses and to prioritize long-term system stability over short-term volume.
-answer: 베트남은 과거 급격한 보조금(FiT) 중심의 성장에서 벗어나 제8차 국가전력개발계획(PDP8) 및 직접전력구매계약(DPPA)을 통해 시장 기반의 체계적인 에너지 전환을 추진하고 있습니다. 현재 진행 중인 재생에너지 프로젝트 검토는 정책 후퇴가 아닌 규정 준수를 위한 시장 기강 확립 과정이며, 이를 통해 전력망 안정성과 장기적인 투자 신뢰성을 확보하려 합니다. 결론적으로 베트남은 단순한 개발 속도보다 전력망 수용 능력과 시장 원리를 우선시하는 지속 가능한 재생에너지 생태계 구축에 집중하고 있습니다.
-Source: [indochina-ep.com](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)</t>
+          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>## [https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)
-### Document Overview
-The article analyzes Vietnam's shift from rapid, subsidy-based renewable energy growth to a disciplined, market-driven phase under PDP8 and DPPA, emphasizing structural stability over speed.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam is not reversing course on renewable energy. It is correcting structural weaknesses created during an earlier phase of rapid, subsidy-driven growth... With the current PDP8(revised) and the DPPA in place, EVN has a chance to recoup its losses from the FiTs and invest in upgrading their grid and substations. This is not a retreat from clean energy. It is a transition from subsidies to structure.
-answer: Vietnam is pivoting its Power &amp; Energy sector away from rapid, subsidy-driven Feed-in Tariffs (FiTs) toward a more disciplined, market-based framework under the Power Development Plan 8 (PDP8) and Direct Power Purchase Agreements (DPPA). This strategic shift aims to rectify previous grid congestion and financial strain on Vietnam Electricity (EVN) by prioritizing legal clarity, transmission infrastructure upgrades, and predictable risk allocation over sheer development speed. The transition signals a move toward a mature, sustainable renewable energy market that rewards operational discipline rather than speculation.
-Source: [indochina-ep.com](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)</t>
+          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>## [https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)
-### Document Overview
-Bài viết phân tích sự chuyển đổi chiến lược năng lượng của Việt Nam từ cơ chế giá FiT sang DPPA, nhấn mạnh tầm quan trọng của kỷ luật quản lý và tính bền vững của hệ thống lưới điện hơn là tốc độ phát triển ồ ạt.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is not reversing course on renewable energy. It is correcting structural weaknesses created during an earlier phase of rapid, subsidy-driven growth... The current phase is about doing so sustainably—financially, legally, and operationally. This is not a retreat from clean energy. It is a transition from subsidies to structure.
-answer: Bài báo nhận định Việt Nam không hề thoái lui khỏi năng lượng tái tạo mà đang chuyển dịch từ giai đoạn phát triển nóng dựa trên trợ giá (FiT) sang một thị trường có kỷ luật và cấu trúc bền vững thông qua cơ chế mua bán điện trực tiếp (DPPA). Việc thực thi các quy định nghiêm ngặt và kiểm soát tốc độ tăng trưởng giúp khắc phục các yếu kém về hạ tầng lưới điện, đảm bảo tính ổn định lâu dài và thu hút các nhà đầu tư có năng lực thực sự thay vì đầu cơ.
-Source: [indochina-ep.com](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)</t>
+          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1854,35 +1580,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>## [https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)
-### Document Overview
-The article discusses Vietnam's transition from high-subsidy feed-in tariffs to more mature, cost-efficient energy policies like competitive auctions and DPPAs under the revised PDP8 framework to ensure financial sustainability.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam’s clean energy transformation was one of the fastest in Southeast Asia... The rapid, subsidy-driven expansion has exposed gaps in planning and financial sustainability – laying the groundwork that is now reshaping the sector’s trajectory. According to the revised Power Development Plan 8 (PDP8), the country aims to reach 73 gigawatts (GW) of installed solar power capacity and 38GW of onshore wind power by 2030... The targets for 2030 were significantly raised from the original 2023 plan – solar capacity was increased to between 46GW and 73GW, onshore wind to 26GW-38GW, and energy storage to 10GW-16GW.
-answer: 베트남은 급격한 재생에너지 확대에 따른 전력공사(EVN)의 재정적 부담을 해결하기 위해 고정가격매입제도(FiT)에서 경쟁 입찰 방식으로의 정책 전환을 추진하고 있습니다. 수정된 제8차 국가전력개발계획(PDP8)에 따라 2030년까지 태양광 73GW, 육상 풍력 38GW, 에너지 저장 장치 16GW로 목표를 상향 조정하였으며, 민간 직접전력구매계약(DPPA) 도입과 그리드 인프라 확충을 통해 에너지 전환의 지속 가능성을 확보할 계획입니다.
-Source: [ieefa.org](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)</t>
+          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>## [https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)
-### Document Overview
-The article analyzes Vietnam's shift from a subsidy-driven renewable energy boom to a more sustainable, auction-based model under the revised PDP8 to address utility losses and grid stability.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: According to the revised Power Development Plan 8 (PDP8), the country aims to reach 73 gigawatts (GW) of installed solar power capacity and 38GW of onshore wind power by 2030. ... The targets for 2030 were significantly raised from the original 2023 plan – solar capacity was increased to between 46GW and 73GW, onshore wind to 26GW-38GW, and energy storage to 10GW-16GW. ... This need is recognized in PDP8, which calls for more than USD18 billion in transmission investment and installing 10,000MW to 16,300MW of battery storage by 2030.
-answer: Vietnam is recalibrating its power sector strategy by transitioning from high-cost fixed feed-in tariffs to competitive green auctions and Direct Power Purchase Agreements (DPPAs) to manage the financial strain on state utility EVN. Under the revised Power Development Plan 8 (PDP8), the country has significantly raised its 2030 targets to reach up to 73GW of solar and 38GW of wind capacity, supported by an 18 billion USD investment in grid infrastructure and up to 16.3GW of battery storage. These measures aim to sustain investor confidence while reducing reliance on volatile fossil fuels like LNG to ensure long-term energy security and economic resilience.
-Source: [ieefa.org](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)</t>
+          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>## [https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)
-### Document Overview
-Phân tích sự chuyển dịch năng lượng của Việt Nam từ cơ chế giá FiT sang đấu thầu cạnh tranh và DPPA nhằm đảm bảo bền vững tài chính và hạ tầng.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s clean energy transformation was one of the fastest in Southeast Asia. Between 2018 and 2023, the country scaled up its solar and wind capacity from virtually zero to over 21,000 megawatts (MW), fueled by generous feed-in tariffs (FiTs). ... Vietnam is now well-positioned to transition to the next phase of its clean energy journey – adopting cost-effective models such as competitive green auctions for renewables, advancing direct power purchase agreements (DPPAs), and accelerating grid infrastructure and energy storage investments.
-answer: Bài báo phân tích quá trình chuyển đổi năng lượng sạch của Việt Nam, từ giai đoạn bùng nổ công suất điện mặt trời và gió nhờ cơ chế giá hỗ trợ (FiT) sang giai đoạn điều chỉnh để giải quyết các áp lực tài chính cho tập đoàn EVN. Để duy trì đà tăng trưởng bền vững theo quy hoạch PDP8, Việt Nam cần chuyển đổi sang các mô hình hiệu quả hơn như đấu thầu cạnh tranh, triển khai cơ chế mua bán điện trực tiếp (DPPA) và đẩy mạnh đầu tư vào hạ tầng lưới điện cùng hệ thống lưu trữ năng lượng.
-Source: [ieefa.org](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)</t>
+          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1936,35 +1644,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc](https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc)
-### Document Overview
-This article analyzes the growth projections for Vietnam's solar energy market from 2026 to 2035, identifying key drivers like government support and challenges like grid integration.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual growth rate (CAGR) of 3.10% from 2026 to 2035. By 2035, the market is expected to reach a volume of around 35.58 TWh. The markets growth is driven by favorable government policies, falling solar panel costs, and an increasing focus on clean energy. However, challenges such as grid integration and the need for further technological advancements persist.
-answer: 베트남 태양광 에너지 시장은 2025년 약 26.22 TWh 규모에서 연평균 3.10% 성장하여 2035년에는 약 35.58 TWh에 도달할 것으로 전망됩니다. 정부의 정책적 지원과 태양광 패널 가격 하락, 청정 에너지 수요 증가가 성장을 견인하고 있으나, 전력망 통합 문제와 규제 불확실성 등의 과제도 여전히 남아있습니다. 결과적으로 베트남은 탄소 배출 감소와 에너지 믹스 다변화를 위해 태양광 설비 확대를 지속적으로 추진하고 있습니다.
-Source: [www.linkedin.com](https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc)</t>
+          <t>[Power &amp; Energy] Vietnam Solar Energy Market Growth and Forecast (2026-2035) — The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual ...</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc](https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc)
-### Document Overview
-This article analyzes the growth trajectory of Vietnam's solar energy market through 2035, highlighting drivers like policy support and challenges like grid stability.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual growth rate (CAGR) of 3.10% from 2026 to 2035. By 2035, the market is expected to reach a volume of around 35.58 TWh... The markets growth is driven by favorable government policies, falling solar panel costs, and an increasing focus on clean energy.
-answer: Vietnam's solar energy market is projected to expand from 26.22 TWh in 2025 to approximately 35.58 TWh by 2035, maintaining a compound annual growth rate of 3.10%. This growth in the power sector is being driven by government initiatives like feed-in tariffs, declining equipment costs, and increased foreign investment, although challenges regarding grid integration and energy storage persist.
-Source: [www.linkedin.com](https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc)</t>
+          <t>[Power &amp; Energy] Vietnam Solar Energy Market Growth and Forecast (2026-2035) — The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual ...</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc](https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc)
-### Document Overview
-This article analyzes the growth drivers and challenges of the Vietnam solar energy market, forecasting a volume of 35.58 TWh by 2035.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual growth rate (CAGR) of 3.10% from 2026 to 2035... The market's growth is driven by favorable government policies, falling solar panel costs, and an increasing focus on clean energy. However, challenges such as grid integration and the need for further technological advancements persist.
-answer: Thị trường năng lượng mặt trời Việt Nam dự kiến đạt quy mô 35,58 TWh vào năm 2035 với tốc độ tăng trưởng hàng năm 3,10% nhờ các chính sách hỗ trợ của chính phủ và chi phí lắp đặt ngày càng giảm. Mặc dù tiềm năng phát triển hạ tầng năng lượng tái tạo là rất lớn, ngành này vẫn đang đối mặt với những thách thức đáng kể về tích hợp lưới điện và nhu cầu cải tiến công nghệ lưu trữ.
-Source: [www.linkedin.com](https://www.linkedin.com/pulse/vietnam-solar-energy-market-growth-forecast-2026-2035-sophia-grace-1r5gc)</t>
+          <t>[Power &amp; Energy] Vietnam Solar Energy Market Growth and Forecast (2026-2035) — The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual ...</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2014,37 +1704,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>## [https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260](https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260)
-### Document Overview
-This document provides a strategic and legal guide for investing in Vietnam's wind energy sector as of 2026, highlighting the shift toward domestic 'National Champions' and the transition from FiT to a competitive price framework under PDP8.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Vietnam, one of the worlds fastest growing and energy-intensive economies, has recently been identified by the World Bank as having world class wind energy resources... PDP8 sets a target of approximately 21 23GW of onshore and nearshore wind capacity and approximately 6GW of offshore wind capacity by 2030... Foreign investors must now operate with the understanding that they are competing against favored local players. Building strong, strategic alliances with capable Vietnamese partners is now a critical success factor.
-answer: 베트남은 제8차 국가전력개발계획(PDP8)에 따라 2030년까지 육·해상 풍력 발전 용량을 대폭 확대할 계획이며, 최근 PNE AG의 입찰 탈락 사례에서 보듯 '국가 챔피언' 육성 정책에 따라 현지 기업의 영향력이 강화되고 있습니다. 외국인 투자자는 100% 지분 소유가 가능함에도 불구하고, 불확실한 규제 환경과 금융 요건 강화에 대응하기 위해 역량 있는 현지 파트너와의 전략적 제휴 및 자본 준비성을 필수적으로 갖추어야 합니다. 특히 고정가격매수제(FiT) 종료 후 전환된 가격 프레임워크 모델 하에서의 수익성 확보와 전력망 접속 및 차단 리스크 관리가 향후 투자의 핵심 과제가 될 전망입니다.
-Source: [www.slideshare.net](https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260)</t>
+          <t>[Power &amp; Energy] VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - Slideshare — VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - WHAT YOU MUST KNOW - Download as a PDF or view online for free.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>## [https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260](https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260)
-### Document Overview
-This document provides a strategic 2026 investment guide for Vietnam's wind energy sector, detailing the shift toward domestic 'National Champions,' the implementation of PDP8, and the legal challenges facing foreign developers post-Feed-in-Tariff era.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: In early February 2026, authorities announced that VinEnergo, a newly established energy subsidiary of Vingroup, had been awarded the rights to develop Phase 1 of the Hon Trau wind power project off the coast of Binh Dinh province... This indicates that Vietnamese authorities are adopting much stricter, and at times unpredictable, measures to ensure financial security and project delivery... Vietnam is no longer a frontier market seeking foreign leadership. It is an emerging power shaping its own industrial destiny.
-answer: 1. Vietnam has shifted toward a 'National Champions' policy in its energy sector, evidenced by the 2026 decision to award the $1.9 billion Hon Trau offshore wind project to domestic conglomerate Vingroup's subsidiary, VinEnergo, over the experienced German firm PNE AG. 
-2. The investment landscape for wind energy is transitioning from fixed feed-in-tariffs to a competitive price-framework model under Power Development Plan VIII (PDP8), which targets 6GW of offshore wind capacity by 2030 and up to 70GW by 2050. 
-3. Foreign investors are now encouraged to adopt 'Vietnam-integrated' strategies, involving mandatory domestic partnerships and significant upfront financial deposits, to navigate the evolving regulatory and maritime zoning requirements.
-Source: [www.slideshare.net](https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260)</t>
+          <t>[Power &amp; Energy] VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - Slideshare — VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - WHAT YOU MUST KNOW - Download as a PDF or view online for free.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>## [https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260](https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260)
-### Document Overview
-Hướng dẫn đầu tư năng lượng gió Việt Nam năm 2026 phân tích các cơ hội từ Quy hoạch điện VIII và các bài học kinh nghiệm từ thực tế thị trường như vụ việc PNE AG.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam, one of the worlds fastest growing and energy-intensive economies, has recently been identified by the World Bank as having world class wind energy resources... PDP8 sets a target of approximately 21 23GW of onshore and nearshore wind capacity and approximately 6GW of offshore wind capacity by 2030... The PNE AG experience highlights several critical realities of the current Vietnamese market: The Rise of 'National Champions' Policy... Domestic Partnership is No Longer Optional.
-answer: Tài liệu này cung cấp hướng dẫn đầu tư toàn diện vào lĩnh vực năng lượng gió tại Việt Nam năm 2026, nhấn mạnh các mục tiêu đầy tham vọng của Quy hoạch điện VIII (PDP8) với 6GW điện gió ngoài khơi vào năm 2030. Bài viết phân tích sự chuyển dịch sang ưu tiên các doanh nghiệp nội địa thông qua chính sách "Nhà vô địch quốc gia", đồng thời cảnh báo các nhà đầu tư nước ngoài về những thách thức pháp lý, rủi ro cắt giảm công suất và yêu cầu khắt khe về ký quỹ tài chính. Để thành công, các nhà đầu tư quốc tế cần xây dựng chiến lược hợp tác chặt chẽ với đối tác trong nước, đảm bảo nguồn vốn sẵn sàng và thích ứng với khung giá mới thay thế cho cơ chế giá FIT đã hết hạn.
-Source: [www.slideshare.net](https://www.slideshare.net/slideshow/vietnam-wind-energy-investment-guide-2026-what-you-must-know/286201260)</t>
+          <t>[Power &amp; Energy] VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - Slideshare — VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - WHAT YOU MUST KNOW - Download as a PDF or view online for free.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2098,29 +1768,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>## [https://www.bloomberg.com/news/articles/2026-03-31/vietnam-lng-power-project-eyes-green-pivot-on-soaring-gas-prices](https://www.bloomberg.com/news/articles/2026-03-31/vietnam-lng-power-project-eyes-green-pivot-on-soaring-gas-prices)
-### Document Overview
-This article discusses Vingroup's request to pivot its Haiphong LNG power project toward renewable energy due to soaring global gas prices and supply chain risks.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-GAS-PDP8
-verbatim: Vingroup JSC has asked the Vietnamese government to allow it to replace a large liquefied natural gas power project with renewable energy, citing surging fuel prices linked to the Middle East conflict. The rapid increase in LNG prices — due to war-driven supply disruptions in key exporter Qatar and intensifying competition among Asian buyers for limited supplies — has underscored significant risks for import-dependent projects like Vingroup’s proposed Haiphong LNG-to-power facility.
-answer: 빈그룹(Vingroup)은 중동 분쟁에 따른 카타르산 LNG 공급 차질과 가격 폭등으로 인해 하이퐁 LNG 발전 프로젝트를 재생에너지 사업으로 전환해 줄 것을 베트남 정부에 요청했습니다. 이는 제8차 국가전력개발계획(PDP8) 내 LNG 의존도를 낮추고 수입 연료 가격 변동 리스크를 회피하려는 움직임으로 풀이됩니다. 에너지 안보와 비용 효율성을 위해 기존 가스 화력 발전 대신 친환경 에너지로의 피벗을 추진하는 사례입니다.
-Source: [www.bloomberg.com](https://www.bloomberg.com/news/articles/2026-03-31/vietnam-lng-power-project-eyes-green-pivot-on-soaring-gas-prices)</t>
+          <t>[Power &amp; Energy] Vietnam LNG Power Project Eyes Green Pivot on Soaring Gas Prices — Vingroup JSC has asked the Vietnamese government to replace a large liquefied natural gas power project with renewable energy due to surging ... (관련: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>## [https://www.bloomberg.com/news/articles/2026-03-31/vietnam-lng-power-project-eyes-green-pivot-on-soaring-gas-prices](https://www.bloomberg.com/news/articles/2026-03-31/vietnam-lng-power-project-eyes-green-pivot-on-soaring-gas-prices)
-### Document Overview
-Vingroup JSC is seeking government approval to convert its Haiphong LNG-to-power project into a renewable energy site due to rising LNG costs and supply instability.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-GAS-PDP8
-verbatim: Vingroup JSC has asked the Vietnamese government to allow it to replace a large liquefied natural gas power project with renewable energy, citing surging fuel prices linked to the Middle East conflict. The rapid increase in LNG prices — due to war-driven supply disruptions in key exporter Qatar and intensifying competition among Asian buyers for limited supplies — has underscored significant risks for import-dependent projects like Vingroup’s proposed Haiphong LNG-to-power facility.
-answer: Vingroup JSC has formally requested the Vietnamese government to pivot its proposed Haiphong LNG-to-power facility away from natural gas in favor of renewable energy development. This strategic shift is driven by soaring global LNG prices and supply chain vulnerabilities caused by conflicts in the Middle East and disruptions in Qatar, which pose significant financial risks to import-dependent energy projects under the nation's power development framework.
-Source: [www.bloomberg.com](https://www.bloomberg.com/news/articles/2026-03-31/vietnam-lng-power-project-eyes-green-pivot-on-soaring-gas-prices)</t>
+          <t>[Power &amp; Energy] Vietnam LNG Power Project Eyes Green Pivot on Soaring Gas Prices — Vingroup JSC has asked the Vietnamese government to replace a large liquefied natural gas power project with renewable energy due to surging ... (Related: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Content not found or crawler failed</t>
+          <t>[Power &amp; Energy] Vietnam LNG Power Project Eyes Green Pivot on Soaring Gas Prices — Vingroup JSC has asked the Vietnamese government to replace a large liquefied natural gas power project with renewable energy due to surging ... (Liên quan: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2174,35 +1832,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/](https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/)
-### Document Overview
-Vietnam's EVN awarded a $974 million contract to a PowerChina-Lilama consortium for the 1,612 MW Quang Trach II LNG power plant, targeting completion by 2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-GAS-PDP8, VN-EV-2030
-verbatim: Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired power plant... The Quang Trach II plant in the central province of Quang Tri will have a capacity of 1,612 megawatts... The plant will use turbines from General Electric Vernova, EVN said. It said last month the plant would be fully operational by 2030.
-answer: 베트남 전력공사(EVN)는 PowerChina와 Lilama 컨소시엄에 9억 7,400만 달러 규모의 꽝짝(Quang Trach) II LNG 발전소 건설 계약을 체결했습니다. 이 발전소는 1,612MW 용량으로 제8차 국가전력개발계획(PDP8)에 따라 추진되며, GE 베르노바의 터빈을 사용하여 2030년까지 완공될 예정입니다. 이번 프로젝트는 베트남의 2050년 넷제로 목표 달성과 에너지 안보 확보를 위한 핵심 인프라 구축의 일환입니다.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/)</t>
+          <t>[Power &amp; Energy] Vietnam awards $974 million LNG power plant construction contract ... — Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired ... (관련: VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/](https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/)
-### Document Overview
-This article reports on the $974 million contract award by Vietnam's EVN to PowerChina and Lilama for the construction of the Quang Trach II LNG power plant, expected to be operational by 2030.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-GAS-PDP8, VN-EV-2030
-verbatim: Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired power plant... The Quang Trach II plant in the central province of Quang Tri will have a capacity of 1,612 megawatts... The plant will use turbines from General Electric Vernova... it said last month the plant would be fully operational by 2030.
-answer: Vietnam's state utility EVN has awarded a $974 million contract to a consortium of PowerChina and Lilama to construct the 1,612-megawatt Quang Trach II LNG-fired power plant in Quang Tri province. Utilizing turbines from General Electric Vernova, the facility is scheduled to be fully operational by 2030 as part of Vietnam's broader energy transition strategy to enhance energy security and achieve net-zero emissions by 2050.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/)</t>
+          <t>[Power &amp; Energy] Vietnam awards $974 million LNG power plant construction contract ... — Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired ... (Related: VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/](https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/)
-### Document Overview
-This article reports on EVN awarding a $974 million contract to a Chinese-Vietnamese consortium for the construction of the Quang Trach II LNG power plant, scheduled for completion by 2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired power plant... The Quang Trach II plant in the central province of Quang Tri will have a capacity of 1,612 megawatts... The plant will use turbines from General Electric Vernova... it said last month the plant would be fully operational by 2030.
-answer: Tập đoàn Điện lực Việt Nam (EVN) đã trao gói thầu trị giá 974 triệu USD cho liên danh PowerChina và Lilama để xây dựng nhà máy điện khí LNG Quảng Trạch II tại tỉnh Quảng Bình (văn bản gốc ghi Quảng Trị). Dự án có công suất 1.612 MW, sử dụng tuabin từ General Electric Vernova và dự kiến sẽ đi vào hoạt động đầy đủ vào năm 2030 nhằm đảm bảo an ninh năng lượng và hỗ trợ mục tiêu giảm phát thải của Việt Nam.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/climate-energy/vietnam-awards-974-million-lng-power-plant-construction-contract-powerchina-2026-02-09/)</t>
+          <t>[Power &amp; Energy] Vietnam awards $974 million LNG power plant construction contract ... — Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired ... (Liên quan: VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2256,35 +1896,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html](https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html)
-### Document Overview
-Vietnam's PV Gas has signed major agreements with EVN and PV Power to secure LNG supply chains for key power plants, aiming to address rising electricity demand and declining domestic gas reserves.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-GAS-PDP8, VN-EV-2030
-verbatim: PV Gas signed a series of agreements with Vietnam Electricity (EVN) and PV Power to supply fuel for large-scale gas-fired power projects. Under a framework deal with EVN, PV Gas will supply regasified LNG from its planned Vung Ang Terminal (Ha Tinh province) to the Quang Trach power complex (Quang Tri province) in central Vietnam, including Quang Trach 2 and Quang Trach 3. Separately, PV Gas signed an addendum to a long-term LNG sales contract with PV Power - another Petrovietnam subsidiary - to supply fuel for Nhon Trach 3 and 4, Vietnam’s first LNG-to-power project.
-answer: 베트남 국영기업 PV Gas가 EVN 및 PV Power와 대규모 LNG 공급 협약을 체결하며 통합 에너지 생태계 구축에 나섰습니다. 이번 협약에 따라 하띤성 붕앙 터미널에서 광짝 2·3호기 전력 단지로 가스를 공급하며, 베트남 최초의 LNG 발전 프로젝트인 년짝 3·4호기에는 25년 장기 공급을 확정했습니다. 이는 PDP8 및 국가 에너지 계획에 발맞추어 국내 가스 생산 감소와 급증하는 전력 수요에 대응하기 위한 전략적 행보로 평가됩니다.
-Source: [theinvestor.vn](https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html)</t>
+          <t>[Power &amp; Energy] Vietnam moves to cement LNG supply chain as power demand surges — Vietnam is stepping up efforts to build a national LNG supply chain, as PV Gas signed a series of agreements with Vietnam Electricity (EVN) ... (관련: VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html](https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html)
-### Document Overview
-The article reports on key fuel supply agreements signed between PV Gas, EVN, and PV Power to secure LNG for major power projects like Nhon Trach 3 &amp; 4 and Quang Trach, supported by the development of the $1 billion Vung Ang LNG terminal.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-GAS-PDP8, VN-EV-2030
-verbatim: Vietnam is stepping up efforts to build a national LNG supply chain, as PV Gas signed a series of agreements with Vietnam Electricity (EVN) and PV Power to supply fuel for large-scale gas-fired power projects... Under a framework deal with EVN, PV Gas will supply regasified LNG from its planned Vung Ang Terminal (Ha Tinh province) to the Quang Trach power complex (Quang Tri province) in central Vietnam, including Quang Trach 2 and Quang Trach 3... Separately, PV Gas signed an addendum to a long-term LNG sales contract with PV Power... to supply fuel for Nhon Trach 3 and 4, Vietnam’s first LNG-to-power project.
-answer: Vietnam is accelerating its LNG infrastructure development under Power Development Plan 8 (PDP8) objectives through new strategic agreements between PV Gas, EVN, and PV Power to ensure long-term fuel security for the Nhon Trach 3 &amp; 4 and Quang Trach power complexes. These deals establish an integrated supply chain centered around the $1.01 billion North Central LNG Terminal, facilitating the transition from declining domestic gas reserves to imported LNG to meet surging electricity demand by 2030.
-Source: [theinvestor.vn](https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html)</t>
+          <t>[Power &amp; Energy] Vietnam moves to cement LNG supply chain as power demand surges — Vietnam is stepping up efforts to build a national LNG supply chain, as PV Gas signed a series of agreements with Vietnam Electricity (EVN) ... (Related: VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html](https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html)
-### Document Overview
-The article details PV Gas's new agreements with EVN and PV Power to supply LNG to major power plants, emphasizing the development of the $1 billion Vung Ang LNG terminal to secure Vietnam's energy supply chain.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is stepping up efforts to build a national LNG supply chain, as PV Gas signed a series of agreements with Vietnam Electricity (EVN) and PV Power to supply fuel for large-scale gas-fired power projects... Under a framework deal with EVN, PV Gas will supply regasified LNG from its planned Vung Ang Terminal (Ha Tinh province) to the Quang Trach power complex (Quang Tri province)... Separately, PV Gas signed an addendum to a long-term LNG sales contract with PV Power... to supply fuel for Nhon Trach 3 and 4.
-answer: PV Gas đã ký kết các thỏa thuận chiến lược với EVN và PV Power nhằm cung cấp LNG cho các tổ hợp nhiệt điện lớn như Quảng Trạch 2, 3 và Nhơn Trạch 3, 4, đánh dấu bước tiến quan trọng trong việc xây dựng hệ sinh thái LNG tích hợp tại Việt Nam. Dự án kho cảng LNG Bắc Trung Bộ tại Hà Tĩnh với vốn đầu tư hơn 1 tỷ USD sẽ đóng vai trò mắt xích chủ chốt, dự kiến đi vào hoạt động từ năm 2029 để bù đắp sự thiếu hụt khí đốt trong nước và đáp ứng nhu cầu điện năng đang tăng cao.
-Source: [theinvestor.vn](https://theinvestor.vn/vietnam-moves-to-cement-lng-supply-chain-as-power-demand-surges-d18773.html)</t>
+          <t>[Power &amp; Energy] Vietnam moves to cement LNG supply chain as power demand surges — Vietnam is stepping up efforts to build a national LNG supply chain, as PV Gas signed a series of agreements with Vietnam Electricity (EVN) ... (Liên quan: VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2338,35 +1960,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>## [https://en.powerchina.cn/2026-02/27/c_829055.htm](https://en.powerchina.cn/2026-02/27/c_829055.htm)
-### Document Overview
-This article details the EPC contract signing between POWERCHINA-Lilama JV and Vietnam Electricity Corporation for the 1,612.8MW Quang Trach II LNG Thermal Power Plant, a major project under Vietnam's PDP8.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-GAS-PDP8
-verbatim: Vietnam Electricity Corporation signed an engineering, procurement and construction (EPC) turnkey contract for the Quang Trach II LNG Thermal Power Plant Project with a joint venture comprising POWERCHINA and Lilama on Feb 9. A landmark project under Vietnam's Eighth National Power Development Plan, it currently ranks as the largest LNG power generation project in the country and marks POWERCHINA's largest LNG power project to date in Southeast Asia... the project will utilize H-class gas turbine technology with a total installed capacity of 1,612.8MW.
-answer: 베트남 전력공사(EVN)는 POWERCHINA와 Lilama 컨소시엄과 함께 베트남 제8차 국가전력개발계획(PDP8)의 핵심 프로젝트인 '광짝(Quang Trach) II LNG 화력발전소' 건설을 위한 EPC 턴키 계약을 체결했습니다. 이 프로젝트는 총 설비용량 1,612.8MW 규모로 베트남 내 최대 LNG 발전 사업이며, 완공 시 연간 약 100억 kWh의 전력을 공급하여 베트남의 에너지 전환과 경제 발전에 기여할 전망입니다.
-Source: [en.powerchina.cn](https://en.powerchina.cn/2026-02/27/c_829055.htm)</t>
+          <t>[Power &amp; Energy] POWERCHINA signs SE Asia's largest LNG power project in Vietnam — The project will play a pivotal role in advancing Vietnam's energy transition from a coal-dominated mix to one centered on natural gas and ... (관련: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>## [https://en.powerchina.cn/2026-02/27/c_829055.htm](https://en.powerchina.cn/2026-02/27/c_829055.htm)
-### Document Overview
-This article reports on the signing of an EPC contract between Vietnam Electricity Corporation and a POWERCHINA-led joint venture for the Quang Trach II LNG Thermal Power Plant, a major infrastructure project under Vietnam's Eighth National Power Development Plan.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-GAS-PDP8
-verbatim: Vietnam Electricity Corporation signed an engineering, procurement and construction (EPC) turnkey contract for the Quang Trach II LNG Thermal Power Plant Project with a joint venture comprising POWERCHINA and Lilama on Feb 9. A landmark project under Vietnam's Eighth National Power Development Plan, it currently ranks as the largest LNG power generation project in the country and marks POWERCHINA's largest LNG power project to date in Southeast Asia, signifying a historic breakthrough in POWERCHINA's entry into Vietnam's gas power market. The project will utilize H-class gas turbine technology with a total installed capacity of 1,612.8MW.
-answer: Vietnam Electricity Corporation (EVN) has signed an EPC turnkey contract with a joint venture of POWERCHINA and Lilama for the 1,612.8MW Quang Trach II LNG Thermal Power Plant, a landmark project under Vietnam's Eighth National Power Development Plan (PDP8). As Vietnam's largest LNG power generation project, it utilizes H-class gas turbine technology and is expected to deliver 10 billion kWh of electricity annually, playing a critical role in the nation's transition from coal-dominated energy to a mix centered on natural gas and renewables.
-Source: [en.powerchina.cn](https://en.powerchina.cn/2026-02/27/c_829055.htm)</t>
+          <t>[Power &amp; Energy] POWERCHINA signs SE Asia's largest LNG power project in Vietnam — The project will play a pivotal role in advancing Vietnam's energy transition from a coal-dominated mix to one centered on natural gas and ... (Related: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>## [https://en.powerchina.cn/2026-02/27/c_829055.htm](https://en.powerchina.cn/2026-02/27/c_829055.htm)
-### Document Overview
-This article details the signing of an EPC contract between EVN and a POWERCHINA-Lilama joint venture for the 1,612.8MW Quang Trach II LNG power plant in Vietnam.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam Electricity Corporation signed an engineering, procurement and construction (EPC) turnkey contract for the Quang Trach II LNG Thermal Power Plant Project with a joint venture comprising POWERCHINA and Lilama on Feb 9... it currently ranks as the largest LNG power generation project in the country and marks POWERCHINA's largest LNG power project to date in Southeast Asia... total installed capacity of 1,612.8MW. Once operational, it is expected to deliver approximately 10 billion kWh of electricity annually to the national grid.
-answer: Tập đoàn Điện lực Việt Nam đã ký kết hợp đồng EPC với liên danh POWERCHINA và Lilama để thực hiện dự án Nhà máy nhiệt điện LNG Quảng Trạch II với tổng công suất 1.612,8 MW. Đây là dự án điện khí LNG lớn nhất Việt Nam tính đến thời điểm hiện tại, dự kiến cung cấp khoảng 10 tỷ kWh điện mỗi năm cho lưới điện quốc gia sau khi đi vào hoạt động. Dự án này đóng vai trò quan trọng trong việc thúc đẩy chuyển dịch năng lượng của Việt Nam từ than sang khí tự nhiên và năng lượng tái tạo.
-Source: [en.powerchina.cn](https://en.powerchina.cn/2026-02/27/c_829055.htm)</t>
+          <t>[Power &amp; Energy] POWERCHINA signs SE Asia's largest LNG power project in Vietnam — The project will play a pivotal role in advancing Vietnam's energy transition from a coal-dominated mix to one centered on natural gas and ... (Liên quan: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2420,35 +2024,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C](https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C)
-### Document Overview
-This LinkedIn post reports the official commencement of commercial operations for Nhon Trach 3 &amp; 4, Vietnam's first 1.6GW LNG power plants, on January 5, 2026.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-GAS-PDP8
-verbatim: On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power plants in Vietnam, invested by PV Power (a member of Petrovietnam) – officially entered commercial operation... With a total capacity of over 1.6 GW and advanced H-class gas turbine technology, the plants are expected to supply more than 9 billion kWh annually, strengthening power security for Southern Vietnam while enhancing grid flexibility. 🌱 By using LNG, Nhon Trach 3 &amp; 4 can reduce carbon emissions by around 60% compared to coal-fired plants, support large-scale integration of renewable energy, and pave the way toward net-zero emissions
-answer: 베트남 전력 개발 계획 8차(PDP8)의 핵심 프로젝트인 1.6GW 규모의 년짝(Nhon Trach) 3·4호기 LNG 발전소가 2026년 1월 5일 상업 운전을 공식 개시했습니다. PV Power가 투자한 이 시설은 베트남 최초의 LNG 발전소로서 연간 90억 kWh 이상의 전력을 생산하여 남부 지역의 전력 안보를 강화하고 탄소 배출을 기존 석탄 발전 대비 약 60% 감축할 것으로 기대됩니다. 이번 가동은 베트남의 에너지 전환과 넷제로 목표 달성을 위한 중요한 이정표가 될 것입니다.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C)</t>
+          <t>[Power &amp; Energy] Vietnam's 1.6GW LNG Power Plants Enter Commercial Operation — VIETNAM'S FIRST LNG POWER PLANTS OFFICIALLY BEGIN COMMERCIAL OPERATION On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power ... (관련: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C](https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C)
-### Document Overview
-The page reports the official commercial operation of Vietnam's first LNG power plants, Nhon Trach 3 and 4, as of January 2026.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-GAS-PDP8
-verbatim: On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power plants in Vietnam, invested by PV Power (a member of Petrovietnam) – officially entered commercial operation, marking a major milestone in Vietnam’s energy transition. With a total capacity of over 1.6 GW and advanced H-class gas turbine technology, the plants are expected to supply more than 9 billion kWh annually, strengthening power security for Southern Vietnam while enhancing grid flexibility.
-answer: Vietnam has officially inaugurated its first LNG-fired power plants, Nhon Trach 3 &amp; 4, which entered commercial operation on January 5, 2026. Managed by PV Power, the facility utilizes advanced H-class gas turbine technology with a total capacity of 1.6 GW to provide over 9 billion kWh annually to Southern Vietnam. This project represents a critical step in the nation's energy transition, reducing carbon emissions by 60% compared to coal and supporting future net-zero goals through hydrogen co-firing readiness.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C)</t>
+          <t>[Power &amp; Energy] Vietnam's 1.6GW LNG Power Plants Enter Commercial Operation — VIETNAM'S FIRST LNG POWER PLANTS OFFICIALLY BEGIN COMMERCIAL OPERATION On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power ... (Related: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C](https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C)
-### Document Overview
-This article announces the official commercial operation of Nhon Trach 3 &amp; 4, Vietnam's first LNG-fired power plants, as of January 5, 2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power plants in Vietnam, invested by PV Power (a member of Petrovietnam) – officially entered commercial operation, marking a major milestone in Vietnam’s energy transition. With a total capacity of over 1.6 GW and advanced H-class gas turbine technology, the plants are expected to supply more than 9 billion kWh annually, strengthening power security for Southern Vietnam while enhancing grid flexibility.
-answer: Ngày 5/1/2026, hai nhà máy điện khí LNG đầu tiên của Việt Nam là Nhơn Trạch 3 và 4 với tổng công suất 1,6 GW đã chính thức đi vào vận hành thương mại. Dự án do PV Power đầu tư, sử dụng công nghệ tuabin khí thế hệ H hiện đại, dự kiến cung cấp hơn 9 tỷ kWh mỗi năm nhằm đảm bảo an ninh năng lượng cho miền Nam và hỗ trợ mục tiêu phát thải ròng bằng không.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/lngvietnamsummit_lng2power-vietnam-energy-activity-7414535651024351232-FN4C)</t>
+          <t>[Power &amp; Energy] Vietnam's 1.6GW LNG Power Plants Enter Commercial Operation — VIETNAM'S FIRST LNG POWER PLANTS OFFICIALLY BEGIN COMMERCIAL OPERATION On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power ... (Liên quan: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2502,37 +2088,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>## [https://knowledge.energyinst.org/new-energy-world/article?id=140062](https://knowledge.energyinst.org/new-energy-world/article?id=140062)
-### Document Overview
-This article discusses the commercial start of Vietnam's first LNG-to-power project (Nhon Trach 3 &amp; 4) under the PDP8 framework and a significant oil discovery by Murphy Oil at the Hai Su Vang prospect.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-GAS-PDP8
-verbatim: The project aligns closely with Vietnam’s revised National Power Development Plan VIII, which identifies LNG as a key source of flexible generation during a transition away from coal. Under the plan, LNG-fired capacity is projected to reach 22 GW by 2030, accounting for roughly 9.5–12.3% of total installed capacity... GE Vernova has announced that PetroVietnam Power Corporation’s (PV Power) Nhon Trach 3 and 4 power plants have officially entered commercial operation. Located at Ong Keo Industrial Park in Dai Phuoc Commune, around 70 km south-east of Ho Chi Minh City, the twin plants represent Vietnam’s first foray into LNG-fired electricity generation.
-answer: 베트남의 제8차 국가전력개발계획(PDP8)에 따라 최초의 LNG 발전소인 년짝(Nhon Trach) 3·4호기가 상업 운전을 시작하며, 이는 2030년까지 LNG 발전 용량을 22GW로 확대하려는 에너지 전환 전략의 핵심 이정표입니다. 또한, 구룡 분지의 하이수방(HSV) 광구에서 최근 20년 내 동남아시아 최대 규모 중 하나로 평가받는 대규모 원유 발견이 확인되어 베트남의 에너지 안보와 석유 산업 부활에 기여할 것으로 기대됩니다.
-Source: [knowledge.energyinst.org](https://knowledge.energyinst.org/new-energy-world/article?id=140062)</t>
+          <t>[Power &amp; Energy] Vietnam commissions its first LNG-fired power project, and one of ... — Vietnam commissions its first LNG-fired power project, and one of south-east Asia's biggest oil discoveries is confirmed. 14/1/2026. News. (관련: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>## [https://knowledge.energyinst.org/new-energy-world/article?id=140062](https://knowledge.energyinst.org/new-energy-world/article?id=140062)
-### Document Overview
-This article highlights Vietnam's energy sector milestones, specifically the opening of its first 1.6 GW LNG-fired power plant complex and a massive new offshore oil discovery by Murphy Oil.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-GAS-PDP8
-verbatim: Vietnam’s evolving energy landscape is under the spotlight with two major developments: the start of commercial operations at the country’s first LNG-powered combined-cycle gas plant, and confirmation of one of south-east Asia’s largest oil discoveries in two decades. ... The project aligns closely with Vietnam’s revised National Power Development Plan VIII, which identifies LNG as a key source of flexible generation during a transition away from coal.
-answer: Vietnam has officially entered a new energy phase with the commercial launch of its first LNG-fired power plants, Nhon Trach 3 and 4, which utilize high-efficiency GE Vernova turbines to support the country's transition away from coal. Aligned with the National Power Development Plan VIII (PDP8) targeting 22 GW of LNG capacity by 2030, this infrastructure development is complemented by Murphy Oil's major 'Hai Su Vang' offshore discovery, which could be the largest oil find in Southeast Asia in twenty years.
-Source: [knowledge.energyinst.org](https://knowledge.energyinst.org/new-energy-world/article?id=140062)</t>
+          <t>[Power &amp; Energy] Vietnam commissions its first LNG-fired power project, and one of ... — Vietnam commissions its first LNG-fired power project, and one of south-east Asia's biggest oil discoveries is confirmed. 14/1/2026. News. (Related: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>## [https://knowledge.energyinst.org/new-energy-world/article?id=140062](https://knowledge.energyinst.org/new-energy-world/article?id=140062)
-### Document Overview
-Bài báo tổng hợp hai sự kiện năng lượng quan trọng tại Việt Nam: khánh thành nhà máy điện khí LNG Nhơn Trạch 3 &amp; 4 và phát hiện mỏ dầu Hải Sư Vàng với trữ lượng lớn.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s evolving energy landscape is under the spotlight with two major developments: the start of commercial operations at the country’s first LNG-powered combined-cycle gas plant, and confirmation of one of south-east Asia’s largest oil discoveries in two decades. ... PV Power’s Nhon Trach 3 and 4 power plants have officially entered commercial operation. ... Murphy Oil has confirmed a major discovery at the Hai Su Vang (HSV) prospect in the offshore Cuu Long Basin.
-answer: 1. Việt Nam vừa đánh dấu bước ngoặt về hạ tầng năng lượng với việc vận hành thương mại hai nhà máy điện khí LNG đầu tiên là Nhơn Trạch 3 và 4, có tổng công suất 1,6 GW và hiệu suất vượt trội trên 63%.
-2. Song song đó, phát hiện dầu khí lớn tại mỏ Hải Sư Vàng thuộc bể Cửu Long của Murphy Oil được đánh giá là một trong những phát hiện lớn nhất Đông Nam Á trong 20 năm qua, hứa hẹn thúc đẩy lại ngành khai thác dầu khí của quốc gia.
-3. Những phát triển này phù hợp với Quy hoạch điện VIII nhằm chuyển dịch khỏi năng lượng than và đảm bảo an ninh năng lượng cũng như ổn định lưới điện khi tỷ trọng năng lượng tái tạo tăng cao.
-Source: [knowledge.energyinst.org](https://knowledge.energyinst.org/new-energy-world/article?id=140062)</t>
+          <t>[Power &amp; Energy] Vietnam commissions its first LNG-fired power project, and one of ... — Vietnam commissions its first LNG-fired power project, and one of south-east Asia's biggest oil discoveries is confirmed. 14/1/2026. News. (Liên quan: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2586,35 +2152,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>## [https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/](https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/)
-### Document Overview
-Vietnam's EVN has signed a $974 million deal for the 1,612 MW Quang Trach II LNG power plant to support industrial growth and the transition toward net-zero emissions.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-GAS-PDP8
-verbatim: State utility Electricity of Vietnam (EVN) has awarded a construction contract worth $974 million to a consortium led by PowerChina and Lilama to develop the Quang Trach II liquefied natural gas power plant... The project timeline targets full operations by 2030, aligning with Vietnam’s medium term power development roadmap.
-answer: 베트남 전력공사(EVN)가 1,612MW 규모의 꽝짝(Quang Trach) II LNG 발전소 건설을 위해 PowerChina 및 Lilama 컨소시엄과 9억 7,400만 달러 규모의 계약을 체결했습니다. 이 프로젝트는 제8차 국가전력개발계획(PDP8)에 따라 2030년 가동을 목표로 하며, 석탄 의존도를 낮추고 2050년 넷제로 목표를 달성하기 위한 에너지 전환의 핵심 교두보 역할을 할 것으로 기대됩니다. 이번 투자는 베트남의 급격한 경제 성장에 따른 전력 수요 급증에 대응하고 국가 에너지 안보를 강화하기 위한 전략적 조치입니다.
-Source: [esgnews.com](https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/)</t>
+          <t>[Power &amp; Energy] Vietnam Signs $974 Million LNG Deal To Strengthen Energy Security — State utility Electricity of Vietnam has awarded a construction contract worth $974 million to a consortium led by PowerChina and Lilama. (관련: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>## [https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/](https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/)
-### Document Overview
-Vietnam's state utility EVN has awarded a $974 million contract for the 1,612 MW Quang Trach II LNG power plant to strengthen energy security and support its 2050 net-zero goals.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-GAS-PDP8
-verbatim: State utility Electricity of Vietnam (EVN) has awarded a construction contract worth $974 million to a consortium led by PowerChina and Lilama to develop the Quang Trach II liquefied natural gas power plant... The project timeline targets full operations by 2030, aligning with Vietnam’s medium term power development roadmap.
-answer: Vietnam's state utility EVN has awarded a $974 million contract to a PowerChina-Lilama consortium to develop the 1,612 MW Quang Trach II LNG power plant in central Quang Tri province. This project is a critical component of the country's Power Development Plan 8 (PDP8), serving as a transitional energy bridge to reduce coal dependency and support the goal of net-zero emissions by 2050. Targeted for full operation by 2030, the facility aims to stabilize the national grid and ensure energy security amidst rapid industrial growth.
-Source: [esgnews.com](https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/)</t>
+          <t>[Power &amp; Energy] Vietnam Signs $974 Million LNG Deal To Strengthen Energy Security — State utility Electricity of Vietnam has awarded a construction contract worth $974 million to a consortium led by PowerChina and Lilama. (Related: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>## [https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/](https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/)
-### Document Overview
-This article discusses Vietnam's $974 million deal for the Quang Trach II LNG power plant, a 1,612 MW project aimed at balancing energy security with decarbonization goals.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s state utility EVN has awarded a $974 million contract for a 1,612 MW LNG power plant, marking a major shift in regional energy infrastructure investment... Located in central Quang Tri province, the plant will deliver 1,612 megawatts of capacity once completed... Vietnam has committed to achieving net zero emissions by 2050.
-answer: Tập đoàn Điện lực Việt Nam (EVN) đã ký hợp đồng trị giá 974 triệu USD với liên danh PowerChina và Lilama để xây dựng nhà máy điện LNG Quảng Trạch II tại tỉnh Quảng Bình với công suất 1.612 MW. Dự án này là một phần trong chiến lược chuyển dịch năng lượng của Việt Nam, sử dụng khí thiên nhiên hóa lỏng làm cầu nối để giảm sự phụ thuộc vào than đá và đảm bảo an ninh năng lượng trong khi hướng tới mục tiêu phát thải ròng bằng không vào năm 2050. Nhà máy dự kiến đi vào hoạt động đầy đủ vào năm 2030, sử dụng công nghệ tuabin từ GE Vernova để hỗ trợ nhu cầu điện năng đang tăng cao cho phát triển kinh tế.
-Source: [esgnews.com](https://esgnews.com/vietnam-signs-974-million-lng-deal-to-strengthen-energy-security/)</t>
+          <t>[Power &amp; Energy] Vietnam Signs $974 Million LNG Deal To Strengthen Energy Security — State utility Electricity of Vietnam has awarded a construction contract worth $974 million to a consortium led by PowerChina and Lilama. (Liên quan: VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2668,35 +2216,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>## [https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)
-### Document Overview
-This article reports on the inauguration of Vietnam's first $1.4 billion LNG power plants (Nhon Trach 3 &amp; 4) by Petrovietnam, highlighting their role in energy security and the country's net-zero goals.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-GAS-PDP8
-verbatim: Vietnam has opened its first liquefied natural gas power plants, the twin Nhon Trach 3 and Nhon Trach 4 facilities in Dong Nai Province, at a cost of USD1.4 billion. Built by state energy giant Petrovietnam, the plants will generate more than nine billion kilowatt-hours annually with a combined capacity of 1 624 megawatts to support grid stability as renewable energy increases in the southern region. These plants are a crucial piece in strengthening national energy security and meeting the countrys fast and sustainable development requirements... and provide a template for 13 additional LNG projects outlined in the national power development plan.
-answer: 베트남 정부는 동나이성에서 총 1624MW 규모의 첫 액화천연가스(LNG) 발전소인 년짝(Nhon Trach) 3, 4호기를 공식 가동하며 국가 에너지 안보 강화 및 탄소 배출 감축에 나섰습니다. 이 프로젝트는 제8차 국가전력개발계획(PDP8)에 따라 추진되는 13개 추가 LNG 프로젝트의 모델이 될 것이며, 연간 90억 kWh 이상의 전력을 공급하여 남부 지역의 전력망 안정화와 고첨단 산업 수요를 뒷받침할 예정입니다.
-Source: [www.pvn.vn](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)</t>
+          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (관련: VN-PWR-PDP8, VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>## [https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)
-### Document Overview
-This article reports on the inauguration of Vietnam's first LNG power plants (Nhon Trach 3 &amp; 4) by Petrovietnam, highlighting their role in energy security and the transition toward cleaner energy under national development plans.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-GAS-PDP8
-verbatim: Vietnam has opened its first liquefied natural gas power plants, the twin Nhon Trach 3 and Nhon Trach 4 facilities in Dong Nai Province, at a cost of USD1.4 billion. Built by state energy giant Petrovietnam, the plants will generate more than nine billion kilowatt-hours annually with a combined capacity of 1 624 megawatts to support grid stability as renewable energy increases in the southern region. The facilities will primarily serve southern Vietnam... and provide a template for 13 additional LNG projects outlined in the national power development plan.
-answer: Vietnam has officially inaugurated its first liquefied natural gas (LNG) power project, the $1.4 billion Nhon Trach 3 and Nhon Trach 4 twin plants in Dong Nai Province, boasting a combined capacity of 1,624 MW. Developed by Petrovietnam using advanced GE 9HA.02 turbines, these facilities are designed to generate over nine billion kWh annually to support grid stability and high-tech manufacturing growth. This milestone aligns with national energy security goals and serves as a blueprint for 13 additional LNG projects planned under Vietnam's Power Development Plan 8 (PDP8) to reach net-zero by 2050.
-Source: [www.pvn.vn](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)</t>
+          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (Related: VN-PWR-PDP8, VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>## [https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)
-### Document Overview
-The article reports on the inauguration of Vietnam's first LNG power plants (Nhon Trach 3 &amp; 4) by Petrovietnam, highlighting their role in national energy security and carbon reduction.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam has opened its first liquefied natural gas power plants, the twin Nhon Trach 3 and Nhon Trach 4 facilities in Dong Nai Province, at a cost of USD1.4 billion. Built by state energy giant Petrovietnam, the plants will generate more than nine billion kilowatt-hours annually with a combined capacity of 1 624 megawatts to support grid stability as renewable energy increases in the southern region.
-answer: Thủ tướng Chính phủ đã khánh thành hai nhà máy điện khí LNG đầu tiên của Việt Nam là Nhơn Trạch 3 và Nhơn Trạch 4 tại tỉnh Đồng Nai với tổng vốn đầu tư 1,4 tỷ USD. Dự án do Tập đoàn Dầu khí Việt Nam (Petrovietnam) xây dựng, có tổng công suất 1.624 MW, dự kiến cung cấp hơn 9 tỷ kWh mỗi năm nhằm đảm bảo an ninh năng lượng và hỗ trợ mục tiêu phát thải ròng bằng 0 vào năm 2050.
-Source: [www.pvn.vn](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)</t>
+          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2750,35 +2280,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>## [https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390](https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390)
-### Document Overview
-This article outlines Vietnam's official target to reduce total national power consumption by at least 3% in 2026, as published by Vietnam Electricity (EVN).
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Vietnam targets saving at least 3% of total power consumption in 2026... No. Publishing license: 34/GP-SVHTT By Hanoi Department of Culture and Sports on January 19, 2026.
-answer: 베트남은 2026년까지 전체 전력 소비량의 최소 3%를 절감하겠다는 목표를 설정했습니다. 이번 조치는 전력 수요 관리와 에너지 효율성 제고를 통해 국가 에너지 안보를 강화하려는 정책의 일환입니다. (주요 섹터: 전력 및 에너지)
-Source: [en.evn.com.vn](https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390)</t>
+          <t>[Power &amp; Energy] Vietnam targets saving at least 3% of total power consumption in 2026 — Vietnam is striving to save at least three percent of the total national electricity consumption in 2026.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>## [https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390](https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390)
-### Document Overview
-The page provides a headline regarding Vietnam's 2026 energy saving targets and lists the contact/license details for Vietnam Electricity (EVN).
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: Vietnam targets saving at least 3% of total power consumption in 2026... No. Publishing license: 34/GP-SVHTT By Hanoi Department of Culture and Sports on January 19, 2026.
-answer: Vietnam has established a national objective to reduce total electricity consumption by at least 3% in 2026 through enhanced power-saving measures. This initiative, managed under the authority of Vietnam Electricity (EVN), forms part of the country's broader strategy to improve energy efficiency and infrastructure sustainability.
-Source: [en.evn.com.vn](https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390)</t>
+          <t>[Power &amp; Energy] Vietnam targets saving at least 3% of total power consumption in 2026 — Vietnam is striving to save at least three percent of the total national electricity consumption in 2026.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>## [https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390](https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390)
-### Document Overview
-Trang web cung cấp thông tin liên hệ của Tập đoàn Điện lực Việt Nam (EVN) và tiêu đề bài báo về mục tiêu tiết kiệm 3% tổng điện năng tiêu thụ vào năm 2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam targets saving at least 3% of total power consumption in 2026
-answer: Bài báo thông tin về mục tiêu của Việt Nam trong việc tiết kiệm ít nhất 3% tổng điện năng tiêu thụ vào năm 2026. Đây là một phần trong nỗ lực quản lý hạ tầng năng lượng và thúc đẩy sử dụng điện hiệu quả được công bố bởi Tập đoàn Điện lực Việt Nam (EVN).
-Source: [en.evn.com.vn](https://en.evn.com.vn/d/en-US/news/Vietnam-targets-saving-at-least-3-of-total-power-consumption-in-2026-60-219-501390)</t>
+          <t>[Power &amp; Energy] Vietnam targets saving at least 3% of total power consumption in 2026 — Vietnam is striving to save at least three percent of the total national electricity consumption in 2026.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2832,35 +2344,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>## [https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/](https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/)
-### Document Overview
-Vietnam is accelerating negotiations with Russia to finalize an agreement for the Ninh Thuan nuclear power plant project by January 2026 following Japan's withdrawal from the deal.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-REN-NPP-2050, VN-EV-2030
-verbatim: Vietnam’s Prime Minister Phm Minh Chnh has urged all relevant ministries in his nation to work ‘day and night, and even on holidays’ to advance negotiations with Russia to develop the Ninh Thun nuclear power plants... In response to Japan pulling out of a major deal to develop a new nuclear energy facility, Vietnam is now targeting closing the deal with Russia in January.
-answer: 베트남 정부는 청정 에너지 수요 급증에 대응하기 위해 닌투언(Ninh Thuan) 원자력 발전소 건설 프로젝트를 재가동하며, 일본의 사업 철수 이후 러시아와의 협상을 1월 내로 마무리하기 위해 속도를 내고 있습니다. 팜 민 찐 총리는 관련 부처에 휴일 없는 긴급 협상을 지시했으며, 이는 베트남의 국가 원자력 발전 계획(VN-REN-NPP-2050 등) 및 에너지 전환 목표(VN-EV-2030 관련 전력망 확충)를 달성하기 위한 핵심 인프라 사업으로 평가됩니다.
-Source: [energiesmedia.com](https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/)</t>
+          <t>[Power &amp; Energy] Vietnam targets January 2026 agreement with Russia to revive ... — Vietnam targets January 2026 agreement with Russia to revive nuclear power plans after Japan exit · Vietnam's Prime Minister has urged his ... (관련: VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>## [https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/](https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/)
-### Document Overview
-The article details Vietnam's urgent push to finalize a nuclear energy agreement with Russia in early 2026 to replace Japanese investment and meet clean energy targets.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-REN-NPP-2050, VN-EV-2030
-verbatim: Vietnam is now targeting closing the deal with Russia in January. Vietnam’s Prime Minister Phm Minh Chnh has urged all relevant ministries in his nation to work ‘day and night, and even on holidays’ to advance negotiations with Russia to develop the Ninh Thun nuclear power plants... Japan opted to pull its investment from the Ninh Thun 2 nuclear power plant project due to what it says are unrealistic expectations from the Vietnamese government, which was hoping for the Ninh Thun 2 nuclear power plant to be fully operational by 2035.
-answer: Vietnam is fast-tracking a financing and development agreement with Russia to revitalize the Ninh Thuan 1 nuclear power plant project following Japan's exit from the Ninh Thuan 2 project due to timeline disagreements. Prime Minister Pham Minh Chinh has directed ministries to finalize the deal within January 2026 to meet the country's rising demand for clean energy and support national infrastructure goals for the 2030-2050 period.
-Source: [energiesmedia.com](https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/)</t>
+          <t>[Power &amp; Energy] Vietnam targets January 2026 agreement with Russia to revive ... — Vietnam targets January 2026 agreement with Russia to revive nuclear power plans after Japan exit · Vietnam's Prime Minister has urged his ... (Related: VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>## [https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/](https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/)
-### Document Overview
-Bài báo báo cáo về việc Thủ tướng Chính phủ Việt Nam hối thúc các bộ ngành nhanh chóng hoàn tất thỏa thuận hạt nhân với Nga vào tháng 1 năm 2026 sau khi Nhật Bản rút khỏi dự án Ninh Thuận 2.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is now targeting closing the deal with Russia in January. Vietnam’s Prime Minister Phm Minh Chnh has urged all relevant ministries in his nation to work ‘day and night, and even on holidays’ to advance negotiations with Russia to develop the Ninh Thun nuclear power plants... Japan opted to pull its investment from the Ninh Thun 2 nuclear power plant project due to what it says are unrealistic expectations from the Vietnamese government.
-answer: Chính phủ Việt Nam đang nỗ lực đẩy nhanh tiến độ đàm phán với Nga để đạt được thỏa thuận tài trợ cho dự án nhà máy điện hạt nhân Ninh Thuận 1 ngay trong tháng 1 năm 2026. Động thái này diễn ra sau khi Nhật Bản rút khỏi dự án Ninh Thuận 2 do những bất đồng về kỳ vọng tiến độ, thúc đẩy Thủ tướng Phạm Minh Chính chỉ đạo các bộ ngành làm việc khẩn trương để đảm bảo an ninh năng lượng sạch.
-Source: [energiesmedia.com](https://energiesmedia.com/vietnam-targets-january-agreement-with-russia/)</t>
+          <t>[Power &amp; Energy] Vietnam targets January 2026 agreement with Russia to revive ... — Vietnam targets January 2026 agreement with Russia to revive nuclear power plans after Japan exit · Vietnam's Prime Minister has urged his ... (Liên quan: VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2914,35 +2408,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>## [https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)
-### Document Overview
-This page details a technology request from a Vietnamese energy firm seeking smart-grid and advanced power system solutions to enhance grid reliability and renewable energy integration.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: A Vietnam-based renewable energy and engineering company... is seeking international partners that can provide smart-grid and advanced technological solutions for transmission, distribution, and renewable energy systems. The company supports clients in achieving their sustainability goals through technology transfer, renewable energy development, engineering consulting, green energy solutions, reliability improvement, and project management services.
-answer: 2018년에 설립된 베트남의 신재생 에너지 및 엔지니어링 전문 기업이 전력망 효율성과 안정성을 높이기 위해 스마트 그리드 및 송배전 분야의 기술 협력 파트너를 찾고 있습니다. 이 기업은 베트남 제8차 국가 전력개발계획(PDP8)의 방향성에 맞춰 송배전망 자동화, 디지털 모니터링, 자산 관리 최적화 솔루션을 도입하여 현지 신재생 에너지 시스템의 신뢰성을 강화하고자 합니다. 이를 위해 글로벌 기업 및 연구소와 상업적 기술 지원 또는 기술 협력 계약을 희망하고 있습니다.
-Source: [een.ec.europa.eu](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)</t>
+          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>## [https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)
-### Document Overview
-This page details a technology request from a Vietnamese energy company looking for international partners to supply smart-grid, AI, and IoT solutions to modernize Vietnam's power distribution and transmission infrastructure.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: A Vietnam-based renewable energy and engineering company... is seeking international partners that can provide smart-grid and advanced technological solutions for transmission, distribution, and renewable energy systems. The company supports clients in achieving their sustainability goals through technology transfer, renewable energy development, engineering consulting, green energy solutions, reliability improvement, and project management services.
-answer: A Vietnamese renewable energy and engineering firm established in 2018 is seeking international technology partners to provide advanced smart-grid solutions, grid automation, and digital monitoring systems for transmission and distribution networks. This initiative aligns with Vietnam's energy infrastructure goals by focusing on improving operational reliability and integrating sustainable energy solutions into the national power system through commercial and technical cooperation agreements.
-Source: [een.ec.europa.eu](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)</t>
+          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>## [https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)
-### Document Overview
-This page is a technology request from a Vietnamese energy company seeking international partners for smart-grid, transmission, and distribution solutions under commercial or technical agreements.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: A Vietnam-based renewable energy and engineering company provides services in power system design, installation, and project management... The company is seeking international partners that can provide smart-grid and advanced technological solutions for transmission, distribution, and renewable energy systems. The cooperation is expected to focus on improving operational reliability and optimising asset management for energy utilities and industrial clients.
-answer: Một công ty kỹ thuật và năng lượng tái tạo tại Việt Nam đang tìm kiếm các đối tác quốc tế để cung cấp các giải pháp lưới điện thông minh (smart-grid) và công nghệ tiên tiến cho hệ thống truyền tải, phân phối điện. Mục tiêu của sự hợp tác này là nhằm cải thiện độ tin cậy vận hành và tối ưu hóa quản lý tài sản cho các đơn vị điện lực và khách hàng công nghiệp thông qua các thỏa thuận thương mại hoặc hỗ trợ kỹ thuật.
-Source: [een.ec.europa.eu](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)</t>
+          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2992,35 +2468,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>## [https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)
-### Document Overview
-This article analyzes the 2025 revised Power Development Plan 8 (PDP8) in Vietnam, detailing targets for LNG, renewables, BESS, and nuclear power, while addressing regulatory changes like the new Electricity Law and bankability challenges.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: Vietnam’s power sector is expected to experience strong growth in 2026, driven by surging electricity demand, infrastructure expansion, and a major shift toward renewable energy. ... Decision No. 768/QD-TTg was issued on 15 April 2025 by the Prime Minister of Vietnam, which approved the revised National Power Development Plan VIII (PDP 8) for the period 2021–2030, with a vision to 2050.
-answer: 베트남은 급증하는 전력 수요에 대응하기 위해 2025년 4월 개정된 제8차 국가전력개발계획(PDP8)을 승인하고, 2030년까지 재생에너지, LNG 및 천연가스 발전 비중을 대폭 확대할 계획입니다. 특히 해상풍력, 태양광, 배터리 에너지 저장 장치(BESS)뿐만 아니라 중단되었던 원자력 발전 재개를 추진하며, 민간 직접 전력구매계약(DPPA) 도입과 전력망 현대화를 통해 에너지 안보와 2050년 넷제로 목표 달성을 도모하고 있습니다.
-Source: [www.nortonrosefulbright.com](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)</t>
+          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>## [https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)
-### Document Overview
-This article provides a comprehensive overview of Vietnam's power sector evolution under the revised PDP8, detailing new capacity targets, recent legislative decrees for renewables and gas, and the persisting bankability challenges for foreign investors.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: Vietnam’s revised Power Development Plan 8 (PDP8) sets aggressive targets for the power sector for 2030 and beyond, including 22,524 MW of LNG-based power, expanded wind and solar capacities, and the reintroduction of nuclear power. Recent regulatory updates like Decree 58/2025 and the 2024 Electricity Law aim to facilitate direct power purchase agreements (DPPAs) and market-based pricing, although bankability challenges regarding EVN's payment guarantees and curtailment risks remain central concerns for investors.
-answer: Vietnam has updated its National Power Development Plan VIII (PDP8) via Decision No. 768/QD-TTg, setting ambitious 2030 targets that include over 22 GW of LNG capacity, up to 38 GW of onshore wind, and the reintroduction of nuclear power (4-6 GW). To support this transition, the government has implemented new regulations such as Decree 58/2025 and Decree 57/2025 to enable direct power purchase agreements (DPPAs) and market-oriented pricing, while addressing ongoing infrastructure hurdles like grid synchronization and BESS integration.
-Source: [www.nortonrosefulbright.com](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)</t>
+          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>## [https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)
-### Document Overview
-Báo cáo phân tích chi tiết về Quy hoạch điện VIII điều chỉnh của Việt Nam, các chính sách khuyến khích năng lượng sạch và những rào cản pháp lý/tài chính trong việc thu hút đầu tư nước ngoài vào hạ tầng điện lực.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s power sector is expected to experience strong growth in 2026, driven by surging electricity demand, infrastructure expansion, and a major shift toward renewable energy. Vietnam’s revised Power Development Plan 8 (PDP8) sets aggressive targets for the power sector for 2030 and beyond, including 22,524 MW of LNG based power, expanded wind and solar capacity, and the reintroduction of nuclear power.
-answer: Bài viết cung cấp cái nhìn tổng quan về sự phát triển mạnh mẽ của ngành điện Việt Nam năm 2026, với trọng tâm là Quy hoạch điện VIII (PDP8) điều chỉnh nhằm đẩy mạnh năng lượng tái tạo, khí LNG và tái khởi động điện hạt nhân. Đồng thời, báo cáo phân tích các khung pháp lý mới như cơ chế mua bán điện trực tiếp (DPPA), phát triển hệ thống lưu trữ năng lượng (BESS) và những thách thức về tính khả thi tài chính (bankability) mà các nhà đầu tư nước ngoài đang quan tâm.
-Source: [www.nortonrosefulbright.com](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)</t>
+          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3070,35 +2528,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>## [https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)
-### Document Overview
-This report outlines the updated Smart Grid Roadmap for Vietnam to 2030 and 2050, focusing on integrating renewable energy, enhancing grid reliability, and supporting PDP8 objectives.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: The objective of this report is to offer insights and recommendations to the development of a new roadmap that can effectively address the current and anticipated challenges facing the Vietnamese power grid for the period up to 2030, with a vision for 2050... This new roadmap is hence required to ensure the reliability and sustainability of the energy system, aligning with the objectives of Power Development Plan VIII and Viet Nam's commitment to achieving net-zero emissions... Key technologies that the Updated Smart Grid roadmap needs to consider are: Utility scale solar and rooftop solar, Onshore and offshore wind, Energy storage technologies, Electric Vehicle (EV) charging infrastructure.
-answer: 베트남은 제8차 국가전력개발계획(PDP8) 및 2050년 넷제로 목표에 발맞추어, 재생에너지 통합과 전력 계통의 안정성을 강화하기 위한 '2030 스마트 그리드 로드맵 및 2050 비전' 업데이트를 추진하고 있습니다. 본 로드맵은 전기차(EV) 충전 인프라 확충, 에너지 저장 장치(BESS) 도입, 지능형 원격 검침 인프라(AMI) 확대를 핵심 과제로 설정하여 현대적이고 효율적인 에너지 전환 시스템 구축을 목표로 합니다.
-Source: [www.energytransitionpartnership.org](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)</t>
+          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>## [https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)
-### Document Overview
-This report details the updated Vietnam Smart Grid Roadmap to 2030 and 2050, focusing on integrating renewable energy, improving grid reliability, and establishing new technical standards in line with PDP8.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: The objective of this report is to offer insights and recommendations to the development of a new roadmap that can effectively address the current and anticipated challenges facing the Vietnamese power grid for the period up to 2030, with a vision for 2050. This new roadmap is hence required to ensure the reliability and sustainability of the energy system, aligning with the objectives of Power Development Plan VIII and Viet Nam's commitment to achieving net-zero emissions... It will outline a strategic plan for the efficient integration of renewable energy sources into the grid, enabling it to operate in a more robust, secure, and sustainable manner.
-answer: Vietnam has introduced an updated Smart Grid Development Roadmap to 2030 with a vision to 2050, specifically designed to align with Power Development Plan VIII (PDP8) and the national goal of net-zero emissions. The plan prioritizes the integration of massive renewable energy sources, the deployment of energy storage systems (BESS), and the establishment of a regulatory framework for electric vehicle (EV) charging infrastructure and virtual power plants. By 2030, the initiative aims to achieve 100% automation of high-voltage substations and 95% electronic metering to ensure a stable, secure, and flexible power system.
-Source: [www.energytransitionpartnership.org](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)</t>
+          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>## [https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)
-### Document Overview
-Báo cáo trình bày chi tiết lộ trình cập nhật phát triển lưới điện thông minh của Việt Nam giai đoạn 2025-2030 và tầm nhìn 2050, bao gồm các yêu cầu về khung pháp lý, tiêu chuẩn kỹ thuật và các giải pháp hạ tầng ICT phục vụ chuyển dịch năng lượng.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The objective of this report is to oﬀer insights and recommendations to the development of a new roadmap that can eﬀectively address the current and anticipated challenges facing the Vietnamese power grid for the period up to 2030, with a vision for 2050... The Updated Smart Grid objective is to continue the development of an Smart Grid with modern technologies that aim to enhance power quality and supply reliability, contribute toward the eﬃcient management of power demand, encourage eﬃciency in the use of energy resources, enhance labour productivity, reduce demand of investment in power grid and source development.
-answer: Báo cáo này đề xuất lộ trình cập nhật phát triển lưới điện thông minh tại Việt Nam đến năm 2030 và tầm nhìn đến năm 2050 nhằm thay thế các quy định cũ để phù hợp với bối cảnh gia tăng năng lượng tái tạo và cam kết phát thải ròng bằng không. Tài liệu tập trung vào các trụ cột công nghệ như hiện đại hóa hệ thống điều khiển SCADA/EMS/DMS, tự động hóa trạm biến áp, hạ tầng đo đếm tiên tiến (AMI) và tăng cường an ninh mạng để đảm bảo vận hành lưới điện an toàn, tin cậy và hiệu quả.
-Source: [www.energytransitionpartnership.org](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)</t>
+          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3152,35 +2592,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>## [https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid](https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid)
-### Document Overview
-The article discusses Vietnam's updated Atomic Energy Law and the technical/regulatory requirements for integrating advanced nuclear technologies like SMRs into the national grid by 2050.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-REN-NPP-2050
-verbatim: Vietnam’s new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic Energy Agency (IAEA). It also opens the door to advanced technologies such as Generation III+ reactors and small modular reactors (SMRs). Vietnam’s energy roadmap anticipates nuclear capacity reaching 4,000-6,400 megawatts by 2035 and up to 14,000 megawatts by 2050, contributing approximately 1.4-1.7% of total electricity generation.
-answer: 베트남은 2026년 1월 발효되는 개정 원자력법을 통해 3세대+ 원자로 및 소형모듈원자로(SMR) 도입을 위한 법적 근거를 마련하고, 2050년까지 최대 14,000MW의 원전 용량 확보를 목표로 하고 있습니다. RMIT 대학 전문가들은 이 마스터플랜의 성공을 위해 국제원자력기구(IAEA) 기준에 부합하는 안전 문화 정착, 숙련된 인적 자원 양성, 그리고 대규모 전력을 수용할 수 있는 국가 그리드망의 보강이 필수적이라고 강조합니다.
-Source: [www.rmit.edu.vn](https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid)</t>
+          <t>[Power &amp; Energy] Plugging nuclear energy safely into Vietnam's grid - RMIT University — Vietnam's new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic ... (관련: VN-REN-NPP-2050)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>## [https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid](https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid)
-### Document Overview
-The article discusses Vietnam's 2026 Atomic Energy Law and the technical, regulatory, and human resource requirements needed to integrate 14,000 MW of nuclear power into the national grid by 2050.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-REN-NPP-2050
-verbatim: Vietnam’s new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic Energy Agency (IAEA). It also opens the door to advanced technologies such as Generation III+ reactors and small modular reactors (SMRs). ... Vietnam’s energy roadmap anticipates nuclear capacity reaching 4,000-6,400 megawatts by 2035 and up to 14,000 megawatts by 2050, contributing approximately 1.4-1.7% of total electricity generation.
-answer: Vietnam has enacted a new Law on Atomic Energy effective January 1, 2026, which aligns with IAEA standards to facilitate the deployment of Generation III+ and small modular reactors (SMRs). Under the national energy roadmap (VN-REN-NPP-2050 context), the country aims to reach a nuclear capacity of up to 14,000 megawatts by 2050, though experts emphasize that success depends on significant upgrades to the national grid and the development of a specialized workforce.
-Source: [www.rmit.edu.vn](https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid)</t>
+          <t>[Power &amp; Energy] Plugging nuclear energy safely into Vietnam's grid - RMIT University — Vietnam's new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic ... (Related: VN-REN-NPP-2050)</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>## [https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid](https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid)
-### Document Overview
-This article discusses the implementation of Vietnam's new Atomic Energy Law and the technical, infrastructural, and human resource requirements needed to integrate nuclear power into the national grid safely.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic Energy Agency (IAEA). It also opens the door to advanced technologies such as Generation III+ reactors and small modular reactors (SMRs). ...success will hinge on grid readiness, safety culture, and skilled people, say RMIT University Vietnam academics.
-answer: Luật Năng lượng nguyên tử mới của Việt Nam có hiệu lực từ đầu năm 2026 đã tạo khung pháp lý cho các công nghệ hạt nhân tiên tiến như lò phản ứng thế hệ III+ và lò phản ứng mô-đun nhỏ (SMR). Tuy nhiên, các chuyên gia từ RMIT nhấn mạnh rằng sự thành công của chương trình này sẽ phụ thuộc lớn vào việc nâng cấp hệ thống lưới điện quốc gia, phát triển nguồn nhân lực chuyên môn cao và xây dựng văn hóa an toàn nghiêm ngặt theo tiêu chuẩn quốc tế (IAEA).
-Source: [www.rmit.edu.vn](https://www.rmit.edu.vn/news/all-news/2026/jan/plugging-nuclear-energy-safely-into-vietnams-grid)</t>
+          <t>[Power &amp; Energy] Plugging nuclear energy safely into Vietnam's grid - RMIT University — Vietnam's new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic ... (Liên quan: VN-REN-NPP-2050)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3230,35 +2652,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>## [https://www.mdpi.com/2076-3417/15/20/10981](https://www.mdpi.com/2076-3417/15/20/10981)
-### Document Overview
-This article analyzes Vietnam's transition to green hydrogen, highlighting its potential to ensure energy security and meet 2050 net-zero targets through renewable-powered electrolysis.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-REN-NPP-2050
-verbatim: In 2024, the Vietnamese Government published the Hydrogen Energy Development Strategy (HEDS) until 2030, with a vision to 2050. This strategy provides a structured roadmap aligned with the country’s broader energy transition objectives. ... If hydrogen can fully replace these fossil fuels in power generation, Vietnam could achieve a 100% renewable and clean energy power system by 2050, as seen in Figure 8.
-answer: 베트남 정부는 2050년 넷제로 달성과 에너지 안보 강화를 위해 풍부한 재생에너지 잠재력을 활용한 그린 수소 개발 전략(HEDS)을 추진하고 있습니다. 제8차 국가전력개발계획(PDP8) 및 국가 에너지 마스터플랜과 연계하여, 2050년까지 가스 터빈 연료를 수소로 완전 대체함으로써 100% 청정 에너지 전력 시스템 구축을 목표로 하고 있습니다. 다만, 이를 실현하기 위해서는 부족한 수소 운송 인프라 구축과 높은 생산 비용 문제를 해결하기 위한 범부처적 정책 공조와 국제적 협력이 필수적입니다.
-Source: [www.mdpi.com](https://www.mdpi.com/2076-3417/15/20/10981)</t>
+          <t>[Power &amp; Energy] Green Hydrogen: A Pathway to Vietnam's Energy Security - MDPI — The study summarizes the energy landscape of Vietnam in Section 2 and addresses the role of green hydrogen in Vietnam's energy transition in Section 3. The ... (관련: VN-REN-NPP-2050)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>## [https://www.mdpi.com/2076-3417/15/20/10981](https://www.mdpi.com/2076-3417/15/20/10981)
-### Document Overview
-This article analyzes Vietnam's transition to green hydrogen as a core component of its 2050 net-zero goals, evaluating the technical potential of solar/wind resources and the 2024 Hydrogen Energy Development Strategy.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-REN-NPP-2050
-verbatim: In 2024, the Vietnamese Government published the Hydrogen Energy Development Strategy (HEDS) until 2030, with a vision to 2050... This underscores the need for a substantial expansion of RE infrastructure—specifically solar and wind—dedicated to hydrogen production, with a minimum installed capacity of 20 GW by 2030 and 40 GW by 2050... if hydrogen can fully replace these fossil fuels in power generation, Vietnam could achieve a 100% renewable and clean energy power system by 2050.
-answer: Vietnam is accelerating its Power &amp; Energy sector transition through the 2024 Hydrogen Energy Development Strategy (HEDS), which aims to produce up to 20 million tons of hydrogen annually by 2050 to achieve a 100% clean energy power system. To support these targets under national net-zero plans, the country requires a massive infrastructure expansion of renewable energy capacity, specifically targeting 20 GW by 2030 and 40 GW by 2050 dedicated to green hydrogen production.
-Source: [www.mdpi.com](https://www.mdpi.com/2076-3417/15/20/10981)</t>
+          <t>[Power &amp; Energy] Green Hydrogen: A Pathway to Vietnam's Energy Security - MDPI — The study summarizes the energy landscape of Vietnam in Section 2 and addresses the role of green hydrogen in Vietnam's energy transition in Section 3. The ... (Related: VN-REN-NPP-2050)</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>## [https://www.mdpi.com/2076-3417/15/20/10981](https://www.mdpi.com/2076-3417/15/20/10981)
-### Document Overview
-This article evaluates the technical, economic, and policy dimensions of green hydrogen in Vietnam, highlighting its role in energy security and the path to net-zero by 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: In Vietnam, the government is actively pursuing the decarbonization of its industrial and energy sectors... green hydrogen is increasingly recognized as a promising pathway for clean energy development in Vietnam... Vietnam currently lacks the necessary pipeline networks, storage systems, and standardized regulations to support large-scale hydrogen deployment.
-answer: Bài báo phân tích tiềm năng và thách thức của hydro xanh trong việc đảm bảo an ninh năng lượng và thực hiện cam kết phát thải ròng bằng không của Việt Nam vào năm 2050. Mặc dù sở hữu nguồn tài nguyên năng lượng tái tạo dồi dào, Việt Nam vẫn đang đối mặt với những rào cản lớn về cơ sở hạ tầng phân phối hạn chế, chi phí sản xuất cao và sự thiếu hụt các khung pháp lý đồng bộ giữa các ngành.
-Source: [www.mdpi.com](https://www.mdpi.com/2076-3417/15/20/10981)</t>
+          <t>[Power &amp; Energy] Green Hydrogen: A Pathway to Vietnam's Energy Security - MDPI — The study summarizes the energy landscape of Vietnam in Section 2 and addresses the role of green hydrogen in Vietnam's energy transition in Section 3. The ... (Liên quan: VN-REN-NPP-2050)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3312,35 +2716,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>## [http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)
-### Document Overview
-베트남의 새로운 에너지 전략인 결의안 제70-NQ/TW호에 대한 분석으로, 투자 장벽 제거, 재생에너지 확대, 원전 재개 및 인력 양성 계획을 다루고 있습니다.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030
-verbatim: On August 20, 2025, Party General Secretary To Lam signed Resolution 70-NQ-TW of the Politburo, a strategic directive aimed at ensuring Vietnam’s national energy security through 2030, with a forward-looking perspective toward 2045... Key legal and policy highlights of Resolution 70 include: Facilitating Capital Inflows... Renewable Energy Prioritization... Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035.
-answer: 베트남 공산당은 2030년 국가 에너지 안보 확보와 2045년 전망을 담은 결의안 제70-NQ/TW호를 발표하여 에너지 분야의 제도적 장벽을 제거하고 민간 및 외국인 투자를 활성화할 계획입니다. 이 결의안은 재생에너지 비중을 2030년까지 25~30%로 확대하고 닌투안 원자력 발전소 건설을 재개하는 등 에너지 믹스의 다변화와 효율성 향상을 목표로 합니다. 특히 전력구매계약(PPA) 집행 강화와 송전 가격 모델 도입을 통해 민간 자본의 유입을 촉진하고 탄소 중립 및 기후 변화 대응을 위한 지속 가능한 에너지 생태계 구축에 집중하고 있습니다.
-Source: [blogs.duanemorris.com](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)</t>
+          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (관련: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>## [http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)
-### Document Overview
-This article discusses Vietnam's Resolution 70-NQ/TW-2025, a new legal framework designed to attract investment and remove bottlenecks in the energy sector, focusing on renewables, nuclear power, and grid modernization.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030
-verbatim: On August 20, 2025, Party General Secretary To Lam signed Resolution 70-NQ-TW of the Politburo, a strategic directive aimed at ensuring Vietnam’s national energy security through 2030, with a forward-looking perspective toward 2045... The Resolution advocates for reforms in finance, credit, and taxation policies, alongside incentives for green projects, energy storage, R&amp;D, and domestic manufacturing... Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035.
-answer: Vietnam has issued Resolution 70-NQ/TW-2025 to overhaul the energy sector by eliminating institutional barriers and facilitating capital inflows for private and international investors in renewables, smart grids, and nuclear power. This strategic directive mandates the expedited development of the Ninh Thuan nuclear plants by 2035 and aims for renewable energy to reach 25-30% of the primary supply by 2030, aligning with the country's long-term goals for energy security and net-zero emissions. The resolution emphasizes market-driven mechanisms, including new transmission pricing models and renewable energy certificate markets, to modernize infrastructure and ensure sustainable, high-quality power supply.
-Source: [blogs.duanemorris.com](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)</t>
+          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (Related: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>## [http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)
-### Document Overview
-This article discusses Vietnam's Resolution 70-NQ/TW of 2025, which aims to transform the energy sector by facilitating capital access, promoting renewable and nuclear energy, and eliminating institutional bottlenecks to ensure national energy security and sustainable growth.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: On August 20, 2025, Party General Secretary To Lam signed Resolution 70-NQ-TW of the Politburo, a strategic directive aimed at ensuring Vietnam’s national energy security through 2030... The focus shifts from merely ensuring sufficient power supply to providing energy that is high-quality, affordable, sustainable, climate-resilient, and integrated with global markets.
-answer: Nghị quyết 70-NQ/TW năm 2025 của Bộ Chính trị tập trung vào việc đảm bảo an ninh năng lượng quốc gia đến năm 2030 bằng cách loại bỏ các rào cản thể chế và thúc đẩy sự tham gia của tư nhân vào các dự án năng lượng tái tạo, điện hạt nhân và lưới điện thông minh. Văn bản này đề ra mục tiêu cụ thể về tỷ trọng năng lượng tái tạo đạt 25-30% vào năm 2030, đồng thời ưu tiên huy động vốn thông qua các cơ chế tài chính xanh và tăng cường thực thi các hợp đồng mua bán điện (PPA) để thu hút nhà đầu tư trong và ngoài nước.
-Source: [blogs.duanemorris.com](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)</t>
+          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (Liên quan: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3390,35 +2776,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>## [https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)
-### Document Overview
-This page details the SGREEE project in Vietnam, a €5 million initiative funded by Germany to modernize the national power grid for better renewable energy integration and energy efficiency through regulatory support, capacity building, and technology cooperation.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: The ‘Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)’ project is supporting the Government of Viet Nam in the implementation of its Smart Grid Roadmap, which aims to promote the modernization and automation of the national power transmission and distribution system. Funded by BMZ, the project is working closely with ERAV to support experts of the Vietnamese power sector in developing a “Smart Grid”, i.e. the digitalization and flexibilization of the power supply system, which allows integration of an increasing share of renewable energies and supports greater energy efficiency.
-answer: 독일 BMZ의 지원을 받는 SGREEE 프로젝트는 베트남 전력 규제 당국(ERAV)과 협력하여 국가 전력망의 현대화 및 자동화를 추진하고 있습니다. 이 사업은 스마트 그리드 로드맵에 따라 전력 시스템의 디지털화와 유연성을 강화함으로써, 재생 에너지 비중 확대와 에너지 효율 향상을 목표로 법적 프레임워크 구축, 역량 강화 및 기술 협력을 진행했습니다. 이는 베트남 전력 개발 마스터플랜(PDP8)의 에너지 전환 목표를 뒷받침하는 핵심적인 인프라 고도화 활동으로 평가됩니다.
-Source: [www.esp.org.vn](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)</t>
+          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>## [https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)
-### Document Overview
-The page details the SGREEE project, a 5-million-euro initiative to modernize Vietnam's power grid through regulatory advice, capacity building, and technology cooperation.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: The ‘Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)’ project is supporting the Government of Viet Nam in the implementation of its Smart Grid Roadmap, which aims to promote the modernization and automation of the national power transmission and distribution system. Funded by BMZ, the project is working closely with ERAV to support experts of the Vietnamese power sector in developing a “Smart Grid”, i.e. the digitalization and flexibilization of the power supply system, which allows integration of an increasing share of renewable energies and supports greater energy efficiency.
-answer: The Smart Grids for Renewable Energy and Energy Efficiency (SGREEE) project, funded by BMZ and partnered with ERAV, supported the modernization of Vietnam's national power grid through digitalization and automation. This initiative facilitates the integration of higher renewable energy shares and enhanced energy efficiency, aligning with the country's strategic energy objectives and smart grid roadmap to ensure a flexible power supply system.
-Source: [www.esp.org.vn](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)</t>
+          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>## [https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)
-### Document Overview
-This page details the SGREEE project in Vietnam, focusing on modernizing the national power grid through digitalization and policy support to integrate renewable energy.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The ‘Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)’ project is supporting the Government of Viet Nam in the implementation of its Smart Grid Roadmap, which aims to promote the modernization and automation of the national power transmission and distribution system. Funded by BMZ, the project is working closely with ERAV to support experts of the Vietnamese power sector in developing a “Smart Grid”, i.e. the digitalization and flexibilization of the power supply system, which allows integration of an increasing share of renewable energies and supports greater energy efficiency.
-answer: Dự án Lưới điện thông minh cho Năng lượng tái tạo và Hiệu quả năng lượng (SGREEE) hỗ trợ Chính phủ Việt Nam hiện đại hóa và tự động hóa hệ thống truyền tải và phân phối điện quốc gia thông qua Lộ trình Lưới điện thông minh. Với ngân sách 5 triệu Euro do BMZ tài trợ, dự án tập trung vào việc số hóa và linh hoạt hóa hệ thống cung cấp điện nhằm tích hợp hiệu quả các nguồn năng lượng tái tạo và cải thiện hiệu suất năng lượng.
-Source: [www.esp.org.vn](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)</t>
+          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3472,35 +2840,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>## [https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says](https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says)
-### Document Overview
-This article discusses the necessity of an $18 billion investment in Vietnam's power grid by 2030 to resolve transmission bottlenecks and support renewable energy growth.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for converting Vietnam’s planning framework into deliverable energy projects, according to a Watson Farley &amp; Williams report. However, the country continues to face challenges, with transmission bottlenecks remaining a key risk as renewable capacity expands faster than grid reinforcement. Legislative reforms scheduled in 2026 are expected to address these bottlenecks by introducing more flexible planning updates, streamlined investor selection mechanisms and targeted incentives for green-energy projects.
-answer: 베트남은 2026년부터 2030년까지 송전 인프라에 180억 달러를 투자하여 에너지 프로젝트의 실행력을 높일 계획이며, 이는 재생에너지 확대에 따른 송전 병목 현상을 해결하는 데 핵심적인 역할을 할 것입니다. 현재 복잡한 인허가 및 송전망 부족이 제약 요인으로 작용하고 있으나, 2026년 예정된 입법 개혁을 통해 투자자 선택 메커니즘을 간소화하고 녹색 에너지 프로젝트에 대한 인센티브를 강화할 전망입니다.
-Source: [asian-power.com](https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says)</t>
+          <t>[Power &amp; Energy] $18b grid investment crucial to driving Vietnam's energy future ... — A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for Vietnam.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>## [https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says](https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says)
-### Document Overview
-Vietnam requires an $18 billion investment in its power grid by 2030 to overcome transmission bottlenecks and align its infrastructure with growing renewable capacity.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for converting Vietnam’s planning framework into deliverable energy projects, according to a Watson Farley &amp; Williams report. However, the country continues to face challenges, with transmission bottlenecks remaining a key risk as renewable capacity expands faster than grid reinforcement. Legislative reforms scheduled in 2026 are expected to address these bottlenecks by introducing more flexible planning updates, streamlined investor selection mechanisms and targeted incentives for green-energy projects.
-answer: Vietnam is planning a critical $18 billion investment in its transmission infrastructure between 2026 and 2030 to resolve grid bottlenecks and support the rapid expansion of renewable energy projects. To facilitate this, the government intends to implement legislative reforms in 2026 aimed at streamlining investor selection, updating planning frameworks, and providing incentives for green energy initiatives.
-Source: [asian-power.com](https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says)</t>
+          <t>[Power &amp; Energy] $18b grid investment crucial to driving Vietnam's energy future ... — A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for Vietnam.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>## [https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says](https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says)
-### Document Overview
-Báo cáo nhấn mạnh tầm quan trọng của khoản đầu tư 18 tỷ USD vào lưới điện Việt Nam để giải quyết các nút thắt truyền tải và hỗ trợ chuyển dịch năng lượng.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for converting Vietnam’s planning framework into deliverable energy projects, according to a Watson Farley &amp; Williams report. However, the country continues to face challenges, with transmission bottlenecks remaining a key risk as renewable capacity expands faster than grid reinforcement. Legislative reforms scheduled in 2026 are expected to address these bottlenecks by introducing more flexible planning updates, streamlined investor selection mechanisms and targeted incentives for green-energy projects.
-answer: Theo báo cáo từ Watson Farley &amp; Williams, Việt Nam cần đầu tư 18 tỷ USD vào hạ tầng truyền tải điện trong giai đoạn 2026-2030 để hiện thực hóa các dự án năng lượng và giải quyết tình trạng tắc nghẽn lưới điện hiện nay. Mặc dù tốc độ phát triển năng lượng tái tạo đang nhanh hơn khả năng nâng cấp lưới điện, các cải cách luật pháp dự kiến vào năm 2026 sẽ giúp tháo gỡ khó khăn thông qua cơ chế quy hoạch linh hoạt và các ưu đãi cho dự án năng lượng xanh.
-Source: [asian-power.com](https://asian-power.com/regulation/news/18b-grid-investment-crucial-driving-vietnams-energy-future-report-says)</t>
+          <t>[Power &amp; Energy] $18b grid investment crucial to driving Vietnam's energy future ... — A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for Vietnam.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3554,35 +2904,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>## [https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html](https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html)
-### Document Overview
-Vietnam announces a $1.12 billion project to build the Can Tho 2 road-rail bridge, scheduled for a 2026 start to enhance the Mekong Delta's connectivity and the North-South expressway network.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-TRAN-2055
-verbatim: Vietnam is preparing to build Can Tho 2, a major road-and-rail bridge across the Hau River with an investment of more than US$1.1 billion, with construction expected to start in late 2026 and take about five years to finish. Total investment is estimated at VND29.525 trillion ($1.12 billion). Seen as a strategic link in the North–South expressway network, Can Tho 2 will also connect the Chau Doc–Can Tho–Soc Trang and Ha Tien–Rach Gia–Bac Lieu expressway corridors.
-answer: 베트남 정부는 메콩 델타 지역의 핵심 고속도로망을 연결하기 위해 하우강을 가로지르는 약 11억 2천만 달러 규모의 '껀터 2 교량' 건설을 추진하며, 2026년 말 착공하여 5년 내 완공할 계획입니다. [VN-TRAN-2055] 마스터플랜의 일환인 이 프로젝트는 도로와 철도가 결합된 복합 교량으로, 호치민-까마우 고속도로와 호치민-껀터 철도망을 통합하여 지역 물류 및 경제 활성화의 전략적 요충지 역할을 할 것으로 기대됩니다.
-Source: [e.vnexpress.net](https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam to build $1.1B bridge to connect key Mekong Delta ... — The bridge will have six lanes, 100 kph design speed, 300 m navigation clearance, plus approach roads with emergency lanes. Total investment is ... (관련: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>## [https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html](https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html)
-### Document Overview
-Vietnam is planning a $1.12 billion road-and-rail bridge (Can Tho 2) to connect major expressways in the Mekong Delta, with construction starting in late 2026.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-TRAN-2055
-verbatim: Vietnam is preparing to build Can Tho 2, a major road-and-rail bridge across the Hau River with an investment of more than US$1.1 billion, with construction expected to start in late 2026 and take about five years to finish. Seen as a strategic link in the North–South expressway network, Can Tho 2 will also connect the Chau Doc–Can Tho–Soc Trang and Ha Tien–Rach Gia–Bac Lieu expressway corridors.
-answer: Vietnam is set to commence construction of the US$1.12 billion Can Tho 2 bridge in late 2026, a critical 17.5-km combined road-and-rail link across the Hau River that aligns with the VN-TRAN-2055 objectives for the Mekong Delta. This infrastructure project will connect the Ho Chi Minh City–Ca Mau expressway with other regional corridors, featuring a 1-km cable-stayed main span designed to enhance logistics and regional economic security over a five-year development period.
-Source: [e.vnexpress.net](https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam to build $1.1B bridge to connect key Mekong Delta ... — The bridge will have six lanes, 100 kph design speed, 300 m navigation clearance, plus approach roads with emergency lanes. Total investment is ... (Related: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>## [https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html](https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html)
-### Document Overview
-The article reports on the upcoming construction of the $1.1 billion Can Tho 2 road-and-rail bridge, a key infrastructure project in the Mekong Delta starting in late 2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is preparing to build Can Tho 2, a major road-and-rail bridge across the Hau River with an investment of more than US$1.1 billion, with construction expected to start in late 2026 and take about five years to finish... Total investment is estimated at VND29.525 trillion ($1.12 billion)... It starts at the Cha Va interchange in Vinh Long Province and ends at IC2 interchange in Can Tho, connecting directly to the HCMC–Ca Mau expressway.
-answer: Việt Nam đang chuẩn bị xây dựng cầu Cần Thơ 2 bắc qua sông Hậu với tổng mức đầu tư hơn 1,1 tỷ USD (khoảng 29.525 tỷ đồng), dự kiến khởi công vào cuối năm 2026 và hoàn thành sau 5 năm. Đây là công trình cầu kết hợp đường bộ và đường sắt dài 17,5 km, đóng vai trò chiến lược trong việc kết nối các tuyến cao tốc huyết mạch tại Đồng bằng sông Cửu Long và giảm tải cho Quốc lộ 1.
-Source: [e.vnexpress.net](https://e.vnexpress.net/news/news/traffic/vietnam-to-build-1-1b-bridge-to-connect-key-mekong-delta-expressways-5000271.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam to build $1.1B bridge to connect key Mekong Delta ... — The bridge will have six lanes, 100 kph design speed, 300 m navigation clearance, plus approach roads with emergency lanes. Total investment is ... (Liên quan: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3632,35 +2964,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>## [https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue](https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue)
-### Document Overview
-The article details Vietnam's plans to expand its highway network by 830km with an investment of $6.5 billion in the Central Highlands by 2030, alongside the HCMC Beltway No4 project.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-TRAN-2055, VN-EV-2030
-verbatim: Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam’s expressway network. Construction is expected to cost nearly US$6.5 billion... Meanwhile, plans are underway for the Ho Chi Minh City (HCMC) Beltway No4 project. The expressway will run through cost an estimated $776.75 million and should be completed by 2026.
-answer: 베트남은 2030년까지 중부 고원 지대에 약 65억 달러를 투입하여 830km 길이의 8개 신규 고속도로를 건설할 계획입니다. 주요 프로젝트로는 2023년 착공 예정인 탄푸-바오록 구간과 2026년 완공을 목표로 하는 호치민시 제4순환도로(Beltway No4) 등이 포함됩니다. 이번 인프라 확충은 국가 운송망 강화 마스터플랜(VN-TRAN-2055 및 VN-EV-2030)의 일환으로 추진되어 지역 간 연결성을 크게 개선할 전망입니다.
-Source: [www.globalhighways.com](https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam highway developments continue | Global Highways — Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam's expressway ... (관련: VN-TRAN-2055, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>## [https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue](https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue)
-### Document Overview
-This article outlines Vietnam's strategic plan to invest $6.5 billion in building eight expressways in the Central Highlands and completing the HCMC Beltway No4 by 2026.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-TRAN-2055, VN-EV-2030
-verbatim: Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam’s expressway network. Construction is expected to cost nearly US$6.5 billion. Meanwhile, plans are underway for the Ho Chi Minh City (HCMC) Beltway No4 project. The expressway will run through cost an estimated $776.75 million and should be completed by 2026.
-answer: Vietnam is expanding its transport network by planning eight new expressways in the Central Highlands by 2030, a project estimated at $6.5 billion that will add 830km to the national infrastructure. Key developments include the Tan Phu-Bao Loc expressway starting in 2023 and the Ho Chi Minh City Beltway No4 project, which is scheduled for completion by 2026 at a cost of $776.75 million.
-Source: [www.globalhighways.com](https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam highway developments continue | Global Highways — Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam's expressway ... (Related: VN-TRAN-2055, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>## [https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue](https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue)
-### Document Overview
-The article reports on Vietnam's infrastructure plans to expand its expressway network by adding 830km in the Central Highlands and developing the HCMC Beltway No4 by 2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam’s expressway network. Construction is expected to cost nearly US$6.5 billion... Meanwhile, plans are underway for the Ho Chi Minh City (HCMC) Beltway No4 project. The expressway will run through cost an estimated $776.75 million and should be completed by 2026.
-answer: Việt Nam có kế hoạch xây dựng 8 tuyến đường cao tốc mới tại Tây Nguyên vào năm 2030 với tổng chiều dài khoảng 830km và kinh phí dự kiến gần 6,5 tỷ USD. Các dự án trọng điểm bao gồm cao tốc Tân Phú - Bảo Lộc khởi công năm 2023 và dự án đường Vành đai 4 TP.HCM dự kiến hoàn thành vào năm 2026 với chi phí khoảng 776,75 triệu USD.
-Source: [www.globalhighways.com](https://www.globalhighways.com/wh10/news/vietnam-highway-developments-continue)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam highway developments continue | Global Highways — Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam's expressway ... (Liên quan: VN-TRAN-2055, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3714,29 +3028,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/shorts/WDlB13usNMs](https://www.youtube.com/shorts/WDlB13usNMs)
-### Document Overview
-This page is a YouTube Short from Saigon Times News covering Vietnam's infrastructure developments.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Saigon Times News
-answer: 해당 페이지는 'Saigon Times News' 채널의 유튜브 쇼츠 영상으로, 베트남의 교통 및 인프라 관련 소식을 시각적으로 전달하고 있습니다. 구체적인 텍스트 세부 사항은 제한적이나, 사이공 타임즈 뉴스를 통해 베트남 현지 인프라 구축 현황과 최신 프로젝트 소식을 요약하여 제공합니다.
-Source: [www.youtube.com](https://www.youtube.com/shorts/WDlB13usNMs)</t>
+          <t>[Transport &amp; Infrastructure] Binh Goi bridge to open on April 30, 2026 - YouTube — Ho Chi Minh City will open Binh Goi Bridge to technical traffic on April 30, 2026, under the Beltway No. 3 project.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/shorts/WDlB13usNMs](https://www.youtube.com/shorts/WDlB13usNMs)
-### Document Overview
-The page is a YouTube Short from Saigon Times News, but the provided content is insufficient to extract specific infrastructure news details.
-Source: [www.youtube.com](https://www.youtube.com/shorts/WDlB13usNMs)</t>
+          <t>[Transport &amp; Infrastructure] Binh Goi bridge to open on April 30, 2026 - YouTube — Ho Chi Minh City will open Binh Goi Bridge to technical traffic on April 30, 2026, under the Beltway No. 3 project.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/shorts/WDlB13usNMs](https://www.youtube.com/shorts/WDlB13usNMs)
-### Document Overview
-Trang này là một video ngắn (YouTube Shorts) từ nguồn tin Saigon Times News, tuy nhiên dữ liệu văn bản trích xuất được quá ít để phân tích nội dung cụ thể.
-Source: [www.youtube.com](https://www.youtube.com/shorts/WDlB13usNMs)</t>
+          <t>[Transport &amp; Infrastructure] Binh Goi bridge to open on April 30, 2026 - YouTube — Ho Chi Minh City will open Binh Goi Bridge to technical traffic on April 30, 2026, under the Beltway No. 3 project.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3790,35 +3092,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp](https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp)
-### Document Overview
-Vietnam's Ministry of Construction has announced a plan to build 2,000km of expressways by 2030 and upgrade major maritime, railway, and aviation infrastructure to enhance national connectivity.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-TRAN-2055
-verbatim: From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030. . . Priority will be given to the construction of the eastern North–South expressway, several sections of the western North–South expressway, and major east–west routes that connect key economic zones across the country. . . The ministry also aims to develop gateway seaports with international transshipment capacity, major airports, and the North–South high-speed railway.
-answer: 베트남 건설부(MoC)는 VN-TRAN-2055 마스터플랜의 일환으로 2026년부터 2030년까지 약 2,000km의 고속도로를 신설하여 전국 고속도로 총연장을 5,000km까지 확대할 계획입니다. 이번 인프라 확충은 남북 고속도로와 동서 연결 도로망뿐만 아니라 국제 환적 항만, 주요 공항, 남북 고속철도 건설을 포함하여 국가 물류 효율성을 높이는 현대적이고 스마트한 교통 네트워크 구축을 목표로 합니다. 특히 대도시의 메트로 노선 가속화와 공공교통 중심의 도시 개발(TOD)을 통해 기후 회복력이 있는 지속 가능한 성장을 추진할 예정입니다.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam to build 2,000km of new expressways between 2026-2030 — From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030. The coastal route will be completed ... (관련: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp](https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp)
-### Document Overview
-The article details Vietnam's Ministry of Construction's plan to develop 2,000km of expressways and modern transport infrastructure between 2026-2030 to create a national backbone for development.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-TRAN-2055
-verbatim: From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030. The ministry also aims to develop gateway seaports with international transshipment capacity, major airports, and the North–South high-speed railway... In transport management and safety, the ministry is implementing the transport service development strategy to 2035, with a vision to 2050.
-answer: Vietnam's Ministry of Construction has launched a strategic infrastructure campaign for 2025–2030, aiming to build 2,000 km of new expressways to reach a national total of 5,000 km by 2030. The plan focuses on a synchronized transport network including the North-South high-speed railway, international transshipment seaports, and upgraded major airports to boost regional connectivity. Aligned with long-term development strategies through 2050, the initiative prioritizes smart urban growth and public transport-oriented development in major cities like Hanoi and Ho Chi Minh City.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam to build 2,000km of new expressways between 2026-2030 — From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030. The coastal route will be completed ... (Related: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp](https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp)
-### Document Overview
-Bài báo chi tiết kế hoạch của Bộ Xây dựng Việt Nam nhằm xây dựng 2.000 km đường cao tốc mới và nâng cấp hạ tầng đa phương thức (hàng không, cảng biển, đường sắt) trong giai đoạn 2026-2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The Ministry of Construction (MoC) has set an ambitious goal to develop a modern, synchronised, and smart transport network as part of efforts to establish the backbone of the national infrastructure system in the 2025–2030 period... From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030.
-answer: Bộ Xây dựng vừa đề ra mục tiêu phát triển hệ thống hạ tầng giao thông đồng bộ và hiện đại trong giai đoạn 2025–2030, trọng tâm là xây dựng thêm 2.000 km đường bộ cao tốc để nâng tổng chiều dài toàn quốc lên 5.000 km vào năm 2030. Kế hoạch này bao gồm việc ưu tiên hoàn thiện trục cao tốc Bắc-Nam, phát triển các cảng biển quốc tế, nâng cấp hệ thống đường sắt cao tốc và mở rộng các cảng hàng không lớn như Long Thành, Nội Bài. Bên cạnh đó, Chính phủ cũng chú trọng phát triển hạ tầng đô thị gắn liền với giao thông công cộng (TOD) và thúc đẩy các trung tâm logistics thông minh tại hai thành phố lớn là Hà Nội và TP.HCM.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnam-to-build-2000km-of-new-expressways-between-2026-2030-post332185.vnp)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam to build 2,000km of new expressways between 2026-2030 — From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030. The coastal route will be completed ... (Liên quan: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3872,35 +3156,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=woj6Z5-50jQ](https://www.youtube.com/watch?v=woj6Z5-50jQ)
-### Document Overview
-This video content highlights 10 major infrastructure and construction projects in Vietnam scheduled for completion in 2026, reflecting the country's rapid urban development and industrial growth.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: VN-TRAN-2055
-verbatim: Vietnam went from war-torn nation to Apple and Samsung's manufacturing hub in 50 years. Now the infrastructure is racing to catch up. Long Thanh International Airport is part of the projects completing in 2026.
-answer: 베트남은 글로벌 제조 허브로서의 성장에 발맞춰 국가 교통 마스터플랜(VN-TRAN-2055)에 따라 도시 개발 및 인프라 확장을 가속화하고 있으며, 롱탄 국제공항을 포함한 10개의 주요 건설 프로젝트가 2026년 완공을 목표로 진행 중입니다. 이러한 인프라 현대화는 급격한 산업화에 따른 물류 및 주거 수요를 충족시키기 위한 핵심 전략으로, 베트남의 지속 가능한 경제 성장과 도시 경쟁력을 강화하는 데 중점을 두고 있습니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=woj6Z5-50jQ)</t>
+          <t>[Urban Development] 10 Vietnam Construction Projects Completing in 2026 - YouTube — ... expressway connecting north to south for the first time. Metro lines in Hanoi and Ho Chi Minh City that took over a decade to build. And ... (관련: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=woj6Z5-50jQ](https://www.youtube.com/watch?v=woj6Z5-50jQ)
-### Document Overview
-The content highlights Vietnam's transition into a global manufacturing hub and lists ten major infrastructure projects slated for completion by 2026.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: VN-TRAN-2055
-verbatim: Vietnam went from war-torn nation to Apple and Samsung's manufacturing hub in 50 years. Now the infrastructure is racing to catch up. Long Thanh Internationa... 10 Vietnam Construction Projects Completing in 2026
-answer: Vietnam is rapidly modernizing its urban landscape and transport networks to support its status as a global manufacturing hub for companies like Apple and Samsung. Key infrastructure developments, including the Long Thanh International Airport, are part of a surge of ten major construction projects scheduled for completion in 2026 to align with national growth strategies and industrial demand.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=woj6Z5-50jQ)</t>
+          <t>[Urban Development] 10 Vietnam Construction Projects Completing in 2026 - YouTube — ... expressway connecting north to south for the first time. Metro lines in Hanoi and Ho Chi Minh City that took over a decade to build. And ... (Related: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=woj6Z5-50jQ](https://www.youtube.com/watch?v=woj6Z5-50jQ)
-### Document Overview
-Video tổng hợp 10 dự án hạ tầng lớn tại Việt Nam hoàn thành năm 2026 nhằm hỗ trợ vị thế trung tâm sản xuất toàn cầu mới.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam went from war-torn nation to Apple and Samsung's manufacturing hub in 50 years. Now the infrastructure is racing to catch up. Long Thanh Internationa... 10 Vietnam Construction Projects Completing in 2026
-answer: Video này giới thiệu về 10 dự án xây dựng hạ tầng trọng điểm tại Việt Nam dự kiến sẽ hoàn thành vào năm 2026, bao gồm cả các công trình mang tính biểu tượng như Sân bay Quốc tế Long Thành. Nội dung nhấn mạnh quá trình chuyển mình của Việt Nam từ một quốc gia sau chiến tranh trở thành trung tâm sản xuất của Apple và Samsung, đồng thời cho thấy nỗ lực đẩy mạnh hạ tầng để kịp tốc độ phát triển kinh tế.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=woj6Z5-50jQ)</t>
+          <t>[Urban Development] 10 Vietnam Construction Projects Completing in 2026 - YouTube — ... expressway connecting north to south for the first time. Metro lines in Hanoi and Ho Chi Minh City that took over a decade to build. And ... (Liên quan: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3954,35 +3220,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html](https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html)
-### Document Overview
-Ho Chi Minh City plans to initiate 14 major transport projects in 2026, including Ring Road 4 and Metro Line 2, as part of a massive $67.76 billion infrastructure investment program through 2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-TRAN-2055
-verbatim: Projects slated for commencement include Ho Chi Minh City's Ring Road 4; Metro Line No.2 (Ben Thanh–Tham Luong section); a sea-crossing bridge linking Can Gio with Ba Ria–Vung Tau; and major bridges such as Can Gio, Phu My 2, Thu Thiem 4 and Cat Lai... Under the city’s action programme for the 2025–2030 term, Ho Chi Minh City prioritises investment in 77 transport and technical infrastructure projects with a total estimated capital of over 1.78 quadrillion VND (67.76 billion USD).
-answer: 호치민시는 2026년 제4순환도로, 메트로 2호선, 껀저 해상교량 등 14개 주요 교통 인프라 프로젝트를 착공하고 제3순환도로를 포함한 10개 사업을 완공할 계획입니다. 이는 2025-2030 액션 프로그램 및 VN-TRAN-2055 마스터플랜의 일환으로, 총 77개 사업에 약 1.78경 동(677.6억 달러)을 투입하여 현대적인 교통망 구축과 경제 발전을 도모하는 것을 목표로 합니다.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html)</t>
+          <t>[Transport &amp; Infrastructure] HCMC plans to break ground on 14 major transport infrastructure ... — Alongside new ground-breaking projects, the city targets completion of around 10 major works in 2026, including Ring Road 3, An Phu and My Thuy ... (관련: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html](https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html)
-### Document Overview
-This article outlines Ho Chi Minh City's infrastructure roadmap for 2026, highlighting the commencement of 14 major projects and a total investment of $67.76 billion through 2030.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-TRAN-2055
-verbatim: Projects slated for commencement include Ho Chi Minh City's Ring Road 4; Metro Line No.2 (Ben Thanh–Tham Luong section); a sea-crossing bridge linking Can Gio with Ba Ria–Vung Tau; and major bridges such as Can Gio, Phu My 2, Thu Thiem 4 and Cat Lai... Under the city’s action programme for the 2025–2030 term, Ho Chi Minh City prioritises investment in 77 transport and technical infrastructure projects with a total estimated capital of over 1.78 quadrillion VND (67.76 billion USD).
-answer: Ho Chi Minh City plans to initiate 14 major transport infrastructure projects in 2026, including Ring Road 4, Metro Line No. 2, and several strategic bridges such as the Can Gio sea-crossing bridge. These initiatives are part of a broader 2025–2030 action program involving 77 projects with an estimated investment of 1.78 quadrillion VND ($67.76 billion) aimed at modernizing the city's transport network. Additionally, the city aims to complete 10 existing works by 2026, including Ring Road 3 and various key interchanges, to support long-term socio-economic growth.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html)</t>
+          <t>[Transport &amp; Infrastructure] HCMC plans to break ground on 14 major transport infrastructure ... — Alongside new ground-breaking projects, the city targets completion of around 10 major works in 2026, including Ring Road 3, An Phu and My Thuy ... (Related: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html](https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html)
-### Document Overview
-The article details Ho Chi Minh City's infrastructure plans for 2026, including breaking ground on 14 major projects and completing 10 others as part of a long-term investment strategy through 2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Projects slated for commencement include Ho Chi Minh City's Ring Road 4; Metro Line No.2 (Ben Thanh–Tham Luong section); a sea-crossing bridge linking Can Gio with Ba Ria–Vung Tau; and major bridges such as Can Gio, Phu My 2, Thu Thiem 4 and Cat Lai. ... Under the city’s action programme for the 2025–2030 term, Ho Chi Minh City prioritises investment in 77 transport and technical infrastructure projects with a total estimated capital of over 1.78 quadrillion VND (67.76 billion USD).
-answer: TP.HCM dự kiến khởi công 14 dự án hạ tầng giao thông trọng điểm vào năm 2026, bao gồm Đường Vành đai 4, Tuyến Metro số 2 và các cầu lớn như Cần Giờ, Thủ Thiêm 4. Thành phố cũng đặt mục tiêu hoàn thành khoảng 10 công trình quan trọng như Vành đai 3 và cầu đi bộ qua sông Sài Gòn trong cùng năm. Đây là một phần trong kế hoạch đầu tư 77 dự án hạ tầng giai đoạn 2025–2030 với tổng vốn ước tính hơn 1,78 triệu tỷ đồng.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/hcmc-plans-to-break-ground-on-14-major-transport-infrastructure-projects-in-2026-2483539.html)</t>
+          <t>[Transport &amp; Infrastructure] HCMC plans to break ground on 14 major transport infrastructure ... — Alongside new ground-breaking projects, the city targets completion of around 10 major works in 2026, including Ring Road 3, An Phu and My Thuy ... (Liên quan: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4032,35 +3280,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>## [https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade](https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade)
-### Document Overview
-This article outlines the planned construction of the Thu Thiem 4 Bridge in Ho Chi Minh City, a 2.16km, six-lane project connecting District 2 and District 7.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-TRAN-2055
-verbatim: A bridge project is being planned in Vietnam’s Ho Chi Minh City that will span the Saigon River. The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes. The project is being planned jointly by the 970 Vietnamese Ministry of Planning and Investment, the Ho Chi Minh City (HCMC) People's Committee and the Ministry of Transport.
-answer: 베트남 호치민시에서 사이공강을 가로질러 2군과 7군을 연결하는 총 길이 2.16km의 '투티엠 4 교량(Thu Thiem 4 Bridge)' 건설 프로젝트가 추진 중입니다. 왕복 6차로 규모로 계획된 이 사업은 베트남 기획투자부, 호치민 인민위원회, 교통부가 공동으로 협력하여 진행하며, 국가 인프라 마스터플랜(VN-TRAN-2055) 및 교통 섹터 발전의 일환으로 평가됩니다.
-Source: [www.globalhighways.com](https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam plans bridge link upgrade | Global Highways — The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes. The ... (관련: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>## [https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade](https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade)
-### Document Overview
-This article outlines plans for the 2.16km Thu Thiem 4 Bridge in Ho Chi Minh City, a six-lane project spanning the Saigon River to link District 2 and District 7.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-TRAN-2055
-verbatim: A bridge project is being planned in Vietnam’s Ho Chi Minh City that will span the Saigon River. The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes. The project is being planned jointly by the 970 Vietnamese Ministry of Planning and Investment, the Ho Chi Minh City (HCMC) People's Committee and the Ministry of Transport.
-answer: Vietnam is planning the construction of the Thu Thiem 4 Bridge in Ho Chi Minh City, a 2.16km infrastructure project spanning the Saigon River to connect District 2 and District 7. Under the Transport &amp; Infrastructure sector, this six-lane bridge is being jointly developed by the Ministry of Planning and Investment, the HCMC People's Committee, and the Ministry of Transport as part of broader regional connectivity efforts like VN-TRAN-2055.
-Source: [www.globalhighways.com](https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam plans bridge link upgrade | Global Highways — The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes. The ... (Related: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>## [https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade](https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade)
-### Document Overview
-The article reports on the planning of the Thu Thiem 4 Bridge in Ho Chi Minh City, a 2.16km project with six lanes connecting District 2 and District 7.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: A bridge project is being planned in Vietnam’s Ho Chi Minh City that will span the Saigon River. The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes.
-answer: Thành phố Hồ Chí Minh đang lập kế hoạch xây dựng cầu Thủ Thiêm 4 bắc qua sông Sài Gòn nhằm kết nối Quận 2 và Quận 7. Dự án này dự kiến có chiều dài 2,16km với quy mô 6 làn xe, được phối hợp thực hiện bởi Bộ Kế hoạch và Đầu tư, Ủy ban Nhân dân TP.HCM và Bộ Giao thông Vận tải.
-Source: [www.globalhighways.com](https://www.globalhighways.com/wh10/news/vietnam-plans-bridge-link-upgrade)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam plans bridge link upgrade | Global Highways — The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes. The ... (Liên quan: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -4114,35 +3344,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>## [https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm](https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm)
-### Document Overview
-Ho Chi Minh City has proposed a $193 million investment for the Thu Thiem 4 Bridge project, aiming to start construction in 2026 to connect the southern urban area with the Thu Thiem New Urban Area.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: The Ho Chi Minh City Peoples Committee has sent the proposal to the municipal Peoples Council seeking approval of the investment policy for the Thu Thiem 4 Bridge project... The total estimated investment exceeds VND5.063 trillion, funded entirely by the citys budget... Under the proposed timeline, contractor selection and construction are expected to start in the fourth quarter of 2026, with completion targeted for the fourth quarter of 2028.
-answer: 호치민시 인민위원회가 투티엠 신도시와 남부 도심을 잇는 약 1억 9,300만 달러(5조 630억 동) 규모의 '투티엠 4교' 건설 사업에 대한 투자 승인을 요청했습니다. 이 프로젝트는 8차로, 2.16km 길이의 교량을 건설하여 동남부 교통망을 연결하는 핵심 사업으로, 2026년 4분기에 착공하여 2028년 완공을 목표로 하고 있습니다. 완공 시 기존 주요 도로의 교통 혼잡을 완화하고 지역 간 접근성을 획기적으로 개선할 것으로 기대됩니다.
-Source: [news.tuoitre.vn](https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm)</t>
+          <t>[Urban Development] Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project ... — Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project, construction set for 2026 · The Ho Chi Minh City administration has submitted an ...</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>## [https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm](https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm)
-### Document Overview
-Ho Chi Minh City is seeking approval for the $193 million Thu Thiem 4 Bridge project, with construction expected to run from 2026 to 2028 to connect southern districts with the new urban area.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: The Ho Chi Minh City Peoples Committee has sent the proposal to the municipal Peoples Council seeking approval of the investment policy for the Thu Thiem 4 Bridge project... Under the proposed timeline, compensation, support, and resettlement work will be carried out from the third quarter of 2026 through the first quarter of 2027. Contractor selection and construction are expected to start in the fourth quarter of 2026, with completion targeted for the fourth quarter of 2028.
-answer: Ho Chi Minh City has proposed a VND5.063 trillion (approximately US$193 million) investment for the Thu Thiem 4 Bridge, a 2.16-kilometer project designed to connect District 7 with the Thu Thiem New Urban Area via an eight-lane span. The municipal project is slated to begin construction in the fourth quarter of 2026 with an estimated completion date in late 2028, aiming to alleviate traffic congestion and synchronize regional infrastructure with the city's master plan.
-Source: [news.tuoitre.vn](https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm)</t>
+          <t>[Urban Development] Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project ... — Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project, construction set for 2026 · The Ho Chi Minh City administration has submitted an ...</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>## [https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm](https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm)
-### Document Overview
-This article details the proposed Thu Thiem 4 Bridge project in Ho Chi Minh City, covering its budget, technical specifications, strategic importance, and expected construction timeline from 2026 to 2028.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The Ho Chi Minh City Peoples Committee has sent the proposal to the municipal Peoples Council seeking approval of the investment policy for the Thu Thiem 4 Bridge project... The total estimated investment exceeds VND5.063 trillion, funded entirely by the citys budget... Contractor selection and construction are expected to start in the fourth quarter of 2026, with completion targeted for the fourth quarter of 2028.
-answer: UBND TP.HCM vừa đề xuất Hội đồng nhân dân thành phố phê duyệt chủ trương đầu tư dự án cầu Thủ Thiêm 4 với tổng số vốn hơn 5.063 tỷ đồng (khoảng 193 triệu USD) từ ngân sách thành phố. Dự án có chiều dài 2,16 km nối quận 7 với khu đô thị mới Thủ Thiêm, dự kiến sẽ khởi công vào quý 4 năm 2026 và hoàn thành vào quý 4 năm 2028 nhằm giảm tải áp lực giao thông và hoàn thiện mạng lưới hạ tầng khu vực.
-Source: [news.tuoitre.vn](https://news.tuoitre.vn/ho-chi-minh-city-proposes-193mn-thu-thiem-4-bridge-project-construction-set-for-2026-103251226181122185.htm)</t>
+          <t>[Urban Development] Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project ... — Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project, construction set for 2026 · The Ho Chi Minh City administration has submitted an ...</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4196,36 +3408,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>## [https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo](https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo)
-### Document Overview
-This article reports on the nearly completed construction of the Phuoc Khanh Bridge, a record-breaking cable-stayed bridge in Vietnam, scheduled for a May 2026 completion to link the Ben Luc - Long Thanh expressway.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Phuoc Khanh bridge (belonging to Ben Luc - Long Thanh expressway) has reached about 96% of the volume, and is focusing all efforts on construction waiting for completion in May 2026... The technical highlight of the project is the main span 300 m long with a navigation clearance of 55 m - the highest in Vietnam today... Ensuring the closing milestone in May 2026 will create a decisive premise to bring the project to traffic on the entire route in the third quarter of 2026.
-answer: 벤륵-롱탄 고속도로 프로젝트의 핵심 구간이자 베트남에서 가장 높은 55m의 선박 통과 높이를 자랑하는 푸억카잉(Phuoc Khanh) 교량이 현재 공정률 96%를 달성하며 2026년 5월 완공을 목표로 박차를 가하고 있습니다. 약 11년 전 착공 후 지연되었던 이 교량이 완공되면 2026년 3분기 중 고속도로 전 구간 개통이 가능해져, 메콩 델타 지역에서 롱탄 국제공항까지의 이동 시간이 단축되고 남부 경제권의 물류 혁신이 기대됩니다.
-Source: [news.laodong.vn](https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's highest vertical cable-stayed bridge accelerates to wait for ... — Hai Phong - By the end of March 2026, the site clearance progress of the Nguyen Trai - Le Hong Phong intersection will only reach about 60%.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>## [https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo](https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo)
-### Document Overview
-Phuoc Khanh bridge, the bridge with Vietnam's highest navigation clearance (55m), has reached 96% construction volume and aims to close its main span in May 2026 to facilitate the completion of the Ben Luc - Long Thanh expressway.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Phuoc Khanh bridge (belonging to Ben Luc - Long Thanh expressway) has reached about 96% of the volume, and is focusing all efforts on construction waiting for completion in May 2026. ... The technical highlight of the project is the main span 300 m long with a navigation clearance of 55 m - the highest in Vietnam today. ... Ensuring the closing milestone in May 2026 will create a decisive premise to bring the project to traffic on the entire route in the third quarter of 2026.
-answer: The Phuoc Khanh cable-stayed bridge, a critical component of the Ben Luc - Long Thanh expressway, has reached 96% completion and is scheduled for a main span closure in May 2026. Featuring the highest navigation clearance in Vietnam at 55 meters, the bridge will facilitate 30,000-ton vessels and is expected to enable the full opening of the expressway route by the third quarter of 2026.
-Source: [news.laodong.vn](https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's highest vertical cable-stayed bridge accelerates to wait for ... — Hai Phong - By the end of March 2026, the site clearance progress of the Nguyen Trai - Le Hong Phong intersection will only reach about 60%.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>## [https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo](https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo)
-### Document Overview
-Bài báo cập nhật tiến độ thi công cầu Phước Khánh thuộc cao tốc Bến Lức - Long Thành, dự kiến hợp long vào tháng 5/2026 và giúp thông xe toàn tuyến vào quý III/2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Phuoc Khanh bridge (belonging to Ben Luc - Long Thanh expressway) has reached about 96% of the volume, and is focusing all efforts on construction waiting for completion in May 2026... All resources are currently being maximized by units, aiming to officially close the main span of Phuoc Khanh bridge in May 2026... Ensuring the closing milestone in May 2026 will create a decisive premise to bring the project to traffic on the entire route in the third quarter of 2026.
-answer: 1. Dự án cầu Phước Khánh thuộc cao tốc Bến Lức - Long Thành hiện đã đạt khoảng 96% khối lượng thi công và đang tập trung nguồn lực để chính thức hợp long nhịp chính vào tháng 5/2026 sau gần 11 năm triển khai. 
-2. Đây là cây cầu dây văng có tĩnh không thông thuyền cao nhất Việt Nam (55m), đóng vai trò mắt xích quan trọng giúp toàn tuyến cao tốc có thể thông xe vào quý III/2026, kết nối các vùng kinh tế trọng điểm phía Nam.
-Source: [news.laodong.vn](https://news.laodong.vn/xa-hoi/cau-day-vang-tinh-khong-cao-nhat-viet-nam-but-toc-cho-hop-long-sau-gan-11-nam-1680100.ldo)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's highest vertical cable-stayed bridge accelerates to wait for ... — Hai Phong - By the end of March 2026, the site clearance progress of the Nguyen Trai - Le Hong Phong intersection will only reach about 60%.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4279,29 +3472,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=6R31yvR8f7E](https://www.youtube.com/watch?v=6R31yvR8f7E)
-### Document Overview
-제공된 페이지는 YouTube의 일반적인 서비스 약관 및 정책 링크가 포함된 레이아웃 데이터이며, 베트남 인프라 관련 실제 뉴스 정보는 포함되어 있지 않습니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=6R31yvR8f7E)</t>
+          <t>[Other] Vietnam's $67BN Gamble on High-Speed Rail - YouTube — Vietnam is about to build the largest infrastructure project in its history. Rayon is the all-in-one, effortless CAD tool for going from ...</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=6R31yvR8f7E](https://www.youtube.com/watch?v=6R31yvR8f7E)
-### Document Overview
-The page provides a documentary-style overview of Vietnam's proposed $67 billion high-speed rail network, the largest infrastructure undertaking in the country's history.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Other, Related plans: N/A
-verbatim: Vietnam is about to build the largest infrastructure project in its history. Vietnam’s $67BN Gamble on High-Speed Rail
-answer: Vietnam is set to embark on the largest infrastructure project in its national history, a massive high-speed rail development estimated to cost $67 billion. This ambitious initiative represents a significant financial investment aimed at modernizing the country's transportation network and connecting its major urban centers.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=6R31yvR8f7E)</t>
+          <t>[Other] Vietnam's $67BN Gamble on High-Speed Rail - YouTube — Vietnam is about to build the largest infrastructure project in its history. Rayon is the all-in-one, effortless CAD tool for going from ...</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=6R31yvR8f7E](https://www.youtube.com/watch?v=6R31yvR8f7E)
-### Document Overview
-Trang web được cung cấp là một trang xem video trên YouTube nhưng thiếu thông tin chi tiết về nội dung video, tiêu đề và mô tả.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=6R31yvR8f7E)</t>
+          <t>[Other] Vietnam's $67BN Gamble on High-Speed Rail - YouTube — Vietnam is about to build the largest infrastructure project in its history. Rayon is the all-in-one, effortless CAD tool for going from ...</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4355,37 +3536,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html](https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html)
-### Document Overview
-Vietnam is accelerating its North-South high-speed railway project with a goal to break ground by the end of 2026, featuring a 1,541km line designed for speeds up to 350 km/h.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Minister of Construction Tran Hong Minh has asked relevant agencies to ensure Vietnam's flagship North-South high-speed railway project can break ground by the end of 2026. Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) to Thu Thiem Station (Ho Chi Minh City), passing through 15 provinces and cities after recent administrative reorganizations. Designed for speeds of up to 350 km/h, the dual-track railway will use standard gauge (1,435 mm) and accommodate 23 passenger stations and five freight stations.
-answer: 베트남 건설부 장관은 총 연장 1,541km에 달하는 남북 고속철도 프로젝트를 2026년 말까지 착공할 수 있도록 관련 부처에 특별 기구 설립 및 부지 확보 등 속도감 있는 추진을 지시했습니다. 이 프로젝트는 하노이와 호치민을 연결하며 시속 350km급 복선 전철로 건설될 예정으로, 2025년 타당성 조사를 시작해 2035년 완공을 목표로 하고 있습니다. 최근 빈그룹(Vingroup)이 입찰 철회 의사를 밝혔으나, 정부는 공공 투자 자본을 활용해 국방 및 물류 기능을 겸비한 핵심 국가 인프라로 구축할 방침입니다.
-Source: [theinvestor.vn](https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam pushes to break ground on North-South high-speed railway ... — Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) ...</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html](https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html)
-### Document Overview
-Vietnam is accelerating preparations for its flagship North-South high-speed railway, targeting a 2026 groundbreaking for the 1,541 km project that will connect Hanoi and Ho Chi Minh City.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Minister of Construction Tran Hong Minh has asked relevant agencies to ensure Vietnam's flagship North-South high-speed railway project can break ground by the end of 2026... Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) to Thu Thiem Station (Ho Chi Minh City)... Designed for speeds of up to 350 km/h, the dual-track railway will use standard gauge (1,435 mm) and accommodate 23 passenger stations and five freight stations.
-answer: Vietnam’s Ministry of Construction has set a target to break ground on the flagship 1,541-kilometer North-South high-speed railway by late 2026, prioritizing land clearance and special policy frameworks to meet the timeline. The $1,435 mm$ standard-gauge project will connect Hanoi and Ho Chi Minh City with 23 passenger stations, supporting speeds of 350 km/h and utilizing public investment for a targeted completion by 2035. Recent developments include the establishment of steering committees for the project and the withdrawal of Vingroup from the bidding process to refocus on other infrastructure.
-Source: [theinvestor.vn](https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam pushes to break ground on North-South high-speed railway ... — Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) ...</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html](https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html)
-### Document Overview
-Bộ Xây dựng Việt Nam yêu cầu các đơn vị tập trung cao độ để khởi công dự án đường sắt tốc độ cao Bắc-Nam vào cuối năm 2026 với mục tiêu hoàn thành năm 2035.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Minister of Construction Tran Hong Minh has asked relevant agencies to ensure Vietnam's flagship North-South high-speed railway project can break ground by the end of 2026... Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) to Thu Thiem Station (Ho Chi Minh City)... Targeted completion by 2035.
-answer: 1. Bộ Xây dựng Việt Nam đang quyết liệt đẩy nhanh tiến độ để khởi công dự án đường sắt tốc độ cao Bắc-Nam dài 1.541 km vào cuối năm 2026.
-2. Tuyến đường sắt đôi khổ 1.435 mm này có vận tốc thiết kế 350 km/h, đi qua 15 tỉnh thành từ Hà Nội đến TP.HCM với tổng cộng 23 ga hành khách và 5 ga hàng hóa.
-3. Dự án được đầu tư bằng nguồn vốn công, dự kiến bắt đầu lập báo cáo khả thi vào năm 2025 và đặt mục tiêu hoàn thành toàn bộ vào năm 2035.
-Source: [theinvestor.vn](https://theinvestor.vn/vietnam-pushes-to-break-ground-on-north-south-high-speed-railway-by-end-2026-d17996.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam pushes to break ground on North-South high-speed railway ... — Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) ...</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4439,37 +3600,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>## [https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html](https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html)
-### Document Overview
-Prime Minister Pham Minh Chinh has ordered the acceleration of the US$67 billion North-South high-speed railway project to begin construction by late 2026, while also pushing for northern rail links to China and expanded metro systems in major cities.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: VN-EV-2030
-verbatim: Prime Minister Pham Minh Chinh has ordered the Ministry of Construction to expedite procedures to commence construction of the North-South high-speed railway project by the end of next year. The PM wants the bidding mechanism to be completed this month so the National Assembly can review for approval next month... This would push the construction date one year earlier than the original plan. The 1,541-km route will start at in Hanoi and end in Ho Chi Minh City, passing through 20 localities.
-answer: 1. 베트남 정부는 당초 계획보다 1년 앞당긴 2026년 말까지 남북 고속철도 건설 착공을 위해 관련 입찰 및 승인 절차를 가속화하고 있습니다. 
-2. 약 670억 달러(VND 1.7 quadrillion)가 투입되는 이 프로젝트는 하노이와 호치민을 잇는 1,541km 구간에 23개 여객역을 설치하며, 시속 350km로 설계되었습니다. 
-3. Urban Development 섹터 및 VN-EV-2030 마스터플랜의 일환으로, 이번 사업과 더불어 라오카이-하노이-랑선 철도 및 메트로 노선 확충 등 국가 전반의 교통 인프라 현대화가 추진될 예정입니다.
-Source: [e.vnexpress.net](https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html)</t>
+          <t>[Urban Development] Vietnam eyes to begin high-speed rail construction in 2026 — The government plans to complete the north-south high-speed rail within 10 years as it prioritizes breakthroughs in infrastructure development. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>## [https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html](https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html)
-### Document Overview
-Prime Minister Pham Minh Chinh has directed authorities to accelerate the US$67 billion North-South high-speed rail project to start construction in 2026, while also advancing several other key northern rail and metro projects.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: VN-EV-2030
-verbatim: Prime Minister Pham Minh Chinh has ordered the Ministry of Construction to expedite procedures to commence construction of the North-South high-speed railway project by the end of next year... This would push the construction date one year earlier than the original plan. The railway... was approved for investment by the National Assembly in November last year with a preliminary cost of approximately VND1.7 quadrillion (US$67 billion).
-answer: 1. Prime Minister Pham Minh Chinh has ordered the acceleration of the US$67 billion North-South high-speed railway project to begin construction by the end of 2026, which is one year ahead of the original schedule. 2. The 1,541-km high-speed link between Hanoi and Ho Chi Minh City is being prioritized alongside other major rail projects, including lines connecting the capital to China-bordering provinces and expanded metro networks in Vietnam's two largest cities. 3. This massive urban development initiative aims to modernize national transport infrastructure with trains designed for speeds up to 350 km/h, aligning with long-term strategic connectivity goals.
-Source: [e.vnexpress.net](https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html)</t>
+          <t>[Urban Development] Vietnam eyes to begin high-speed rail construction in 2026 — The government plans to complete the north-south high-speed rail within 10 years as it prioritizes breakthroughs in infrastructure development. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>## [https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html](https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html)
-### Document Overview
-Prime Minister Pham Minh Chinh has ordered the start of the $67 billion North-South high-speed railway construction by late 2026, alongside other major rail projects connecting to China.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Prime Minister Pham Minh Chinh has ordered the Ministry of Construction to expedite procedures to commence construction of the North-South high-speed railway project by the end of next year. ... The 1,541-km route will start at in Hanoi and end in Ho Chi Minh City, passing through 20 localities. It will be designed for speeds of up to 350 kilometers per hour. ... The government also eyes to start building the Lao Cai – Hanoi – Lang Son railway in December.
-answer: Thủ tướng Phạm Minh Chính đã chỉ đạo đẩy nhanh tiến độ để khởi công dự án đường sắt cao tốc Bắc-Nam dài 1.541 km vào cuối năm 2026, sớm hơn một năm so với kế hoạch ban đầu. Dự án có tổng vốn đầu tư khoảng 67 tỷ USD, thiết kế với vận tốc 350 km/h và đi qua 20 tỉnh thành từ Hà Nội đến TP.HCM. Bên cạnh đó, Chính phủ cũng đặt mục tiêu khởi công tuyến đường sắt Lào Cai – Hà Nội – Lạng Sơn vào tháng 12/2025 và xúc tiến các dự án đường sắt kết nối với Trung Quốc.
-Source: [e.vnexpress.net](https://e.vnexpress.net/news/news/vietnam-eyes-to-begin-high-speed-rail-construction-in-2026-4870727.html)</t>
+          <t>[Urban Development] Vietnam eyes to begin high-speed rail construction in 2026 — The government plans to complete the north-south high-speed rail within 10 years as it prioritizes breakthroughs in infrastructure development. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4523,35 +3664,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/groups/lapura/posts/2134317037357882/](https://www.facebook.com/groups/lapura/posts/2134317037357882/)
-### Document Overview
-This page is a Facebook group post stating that Ho Chi Minh City plans to begin construction on five major metro lines in 2026.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: Ho Chi Minh City will start construction of 5 key metro lines in 2026
-answer: 호치민시는 2026년부터 5개의 핵심 메트로 노선 건설을 본격적으로 시작할 예정입니다. 도시 개발 섹터의 주요 프로젝트로서 대중교통 인프라 확충을 통해 도시 연결성을 강화하는 것을 목표로 하고 있습니다.
-Source: [www.facebook.com](https://www.facebook.com/groups/lapura/posts/2134317037357882/)</t>
+          <t>[Urban Development] Ho Chi Minh City will start construction of 5 key metro lines in 2026 ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/groups/lapura/posts/2134317037357882/](https://www.facebook.com/groups/lapura/posts/2134317037357882/)
-### Document Overview
-The page reports that Ho Chi Minh City is scheduled to begin the construction of five essential metro lines in 2026 as part of its urban infrastructure expansion.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: Ho Chi Minh City will start construction of 5 key metro lines in 2026
-answer: Ho Chi Minh City has announced plans to commence the construction of five major metro lines starting in 2026. This initiative is a critical component of the city's urban development strategy to enhance public transportation and regional connectivity.
-Source: [www.facebook.com](https://www.facebook.com/groups/lapura/posts/2134317037357882/)</t>
+          <t>[Urban Development] Ho Chi Minh City will start construction of 5 key metro lines in 2026 ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/groups/lapura/posts/2134317037357882/](https://www.facebook.com/groups/lapura/posts/2134317037357882/)
-### Document Overview
-The page is a social media post from a Bình Dương real estate community group discussing Ho Chi Minh City's plan to start 5 metro lines in 2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Ho Chi Minh City will start construction of 5 key metro lines in 2026
-answer: Thành phố Hồ Chí Minh dự kiến sẽ bắt đầu khởi công xây dựng 5 tuyến tàu điện ngầm (metro) trọng điểm vào năm 2026. Đây là một bước tiến quan trọng trong việc phát triển hệ thống giao thông công cộng và hạ tầng đô thị của thành phố.
-Source: [www.facebook.com](https://www.facebook.com/groups/lapura/posts/2134317037357882/)</t>
+          <t>[Urban Development] Ho Chi Minh City will start construction of 5 key metro lines in 2026 ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4605,35 +3728,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html](https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html)
-### Document Overview
-The article highlights the success of Ho Chi Minh City's first metro line and outlines the strategic roadmap to expand the network to nine lines by 2045 to transform urban mobility.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: More than a year after entering commercial service, the Ben Thanh - Suoi Tien metro line has become a decisive boost, driving comprehensive changes in both the transport landscape and the urban development mindset of Ho Chi Minh City... City leaders outlined a clear roadmap: by 2030, urban railway transport is expected to meet 20 to 30 percent of travel demand; by 2035, 35 to 50 percent; and by 2045, 50 to 60 percent... The Ho Chi Minh City People’s Committee has assigned the Urban Railway Management Board to prepare and act as investor for nine urban railway projects.
-answer: 호치민시의 메트로 1호선(벤탄-수오이띠엔)이 개통 1년 만에 2,000만 명 이상의 승객을 유치하며 도시 교통망과 관광 산업에 큰 활력을 불어넣고 있습니다. 이에 힘입어 시 당국은 메트로 2호선 착공과 함께 총 9개의 도시 철도 프로젝트를 추진하고 있으며, 2045년까지 대중교통 분담률을 최대 60%까지 끌어올릴 계획입니다. 이러한 철도 중심의 도시 개발(TOD) 전략은 호치민을 현대적이고 지속 가능한 경제 허브로 변모시키는 핵심 동력이 될 것으로 기대됩니다.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html)</t>
+          <t>[Transport &amp; Infrastructure] The rail dream gains speed in southern Vietnam - VietNamNet — City leaders outlined a clear roadmap: by 2030, urban railway transport is expected to meet 20 to 30 percent of travel demand; by 2035, 35 to 50 ...</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html](https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html)
-### Document Overview
-The article reports on the successful operation of Ho Chi Minh City's first metro line and the expansion of the urban rail network with nine planned projects to transform city transport by 2045.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: More than a year after entering commercial service, the Ben Thanh - Suoi Tien metro line has become a decisive boost, driving comprehensive changes in both the transport landscape and the urban development mindset of Ho Chi Minh City... On January 15, Metro Line 2, Ben Thanh - Tham Luong, officially broke ground, marking the start of simultaneous deployment of the city’s urban railway network... The Ho Chi Minh City People’s Committee has assigned the Urban Railway Management Board to prepare and act as investor for nine urban railway projects.
-answer: Ho Chi Minh City is accelerating its urban railway development following the success of Metro Line 1 (Ben Thanh - Suoi Tien), which served over 20 million passengers in 2025. The city has officially broken ground on Metro Line 2 and is preparing a nine-line master plan aimed at meeting up to 60% of travel demand by 2045 through a synchronized Transit-Oriented Development (TOD) model.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html)</t>
+          <t>[Transport &amp; Infrastructure] The rail dream gains speed in southern Vietnam - VietNamNet — City leaders outlined a clear roadmap: by 2030, urban railway transport is expected to meet 20 to 30 percent of travel demand; by 2035, 35 to 50 ...</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html](https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html)
-### Document Overview
-Bài báo tổng kết thành công sau một năm vận hành của tuyến Metro số 1 tại TP.HCM và chi tiết lộ trình phát triển mạng lưới đường sắt đô thị đến năm 2045.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: More than a year after entering commercial service, the Ben Thanh - Suoi Tien metro line has become a decisive boost, driving comprehensive changes in both the transport landscape and the urban development mindset of Ho Chi Minh City... City leaders outlined a clear roadmap: by 2030, urban railway transport is expected to meet 20 to 30 percent of travel demand; by 2035, 35 to 50 percent; and by 2045, 50 to 60 percent.
-answer: Sau một năm vận hành thương mại với hơn 20 triệu lượt khách, tuyến Metro số 1 (Bến Thành - Suối Tiên) đã tạo động lực mạnh mẽ cho việc thay đổi diện mạo giao thông và phát triển đô thị tại TP.HCM. Thành phố hiện đang tăng tốc triển khai mạng lưới đường sắt đô thị gồm 9 tuyến với mục tiêu đáp ứng 50-60% nhu cầu đi lại vào năm 2045, trong đó tuyến Metro số 2 đã chính thức khởi công vào đầu năm 2026.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/the-rail-dream-gains-speed-in-southern-vietnam-2492174.html)</t>
+          <t>[Transport &amp; Infrastructure] The rail dream gains speed in southern Vietnam - VietNamNet — City leaders outlined a clear roadmap: by 2030, urban railway transport is expected to meet 20 to 30 percent of travel demand; by 2035, 35 to 50 ...</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4687,35 +3792,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>## [https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm](https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm)
-### Document Overview
-This article outlines the Vietnamese government's plan to begin construction of the $58.71 billion North-South high-speed railway by late 2026, detailing technical specifications and administrative priorities.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: Construction of the NorthSouth high-speed railway project - the first high-speed railway in Vietnam - is expected to kick off by the end of 2026... The projected double-track railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City, with a design speed of 350 km/h... It requires an estimated investment capital of some $58.71 billion.
-answer: 베트남 건설부 장관은 하노이와 호치민을 잇는 총 연장 1,541km의 남북 고속철도 건설 사업을 2026년 말까지 착공할 계획이라고 발표했습니다. 이 프로젝트는 시속 350km급 복선 철도로 23개 여객역과 5개 화물역을 포함하며, 약 587억 1,000만 달러의 투자 자금이 투입될 예정입니다. 정부는 적기 착공을 위해 부지 보상과 설계 컨설턴트 선정을 위한 특례 매커니즘 적용 등 실행 계획을 구체화하고 있습니다.
-Source: [en.vneconomy.vn](https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm)</t>
+          <t>[Urban Development] Construction of Vietnam's first high-speed railway expected to start ... — The North-South high-speed railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City with a design speed of 350 km/h.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>## [https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm](https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm)
-### Document Overview
-This article outlines the timeline and technical specifications for Vietnam's first North-South high-speed railway, scheduled for construction to start in late 2026.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: Construction of the NorthSouth high-speed railway project - the first high-speed railway in Vietnam - is expected to kick off by the end of 2026, as instructed by the Minister of Construction... The projected double-track railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City, with a design speed of 350 km/h and an axle load of 22.5 tons... It requires an estimated investment capital of some $58.71 billion.
-answer: Vietnam plans to begin construction of its first high-speed railway, the North-South project, by the end of 2026 following instructions from the Minister of Construction. Spanning 1,541 km from Hanoi to Ho Chi Minh City, the double-track line will feature 23 passenger and 5 freight stations with a design speed of 350 km/h. The project involves an estimated investment of $58.71 billion and prioritizes land clearance and special policy mechanisms for implementation.
-Source: [en.vneconomy.vn](https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm)</t>
+          <t>[Urban Development] Construction of Vietnam's first high-speed railway expected to start ... — The North-South high-speed railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City with a design speed of 350 km/h.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>## [https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm](https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm)
-### Document Overview
-Bản tin về kế hoạch khởi công dự án đường sắt tốc độ cao Bắc-Nam dài 1.541 km tại Việt Nam vào cuối năm 2026 với tổng mức đầu tư 58,71 tỷ USD.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Construction of the NorthSouth high-speed railway project - the first high-speed railway in Vietnam - is expected to kick off by the end of 2026, as instructed by the Minister of Construction... The projected double-track railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City, with a design speed of 350 km/h... It requires an estimated investment capital of some $58.71 billion.
-answer: Dự án đường sắt tốc độ cao Bắc - Nam đầu tiên của Việt Nam với tổng vốn đầu tư ước tính khoảng 58,71 tỷ USD dự kiến sẽ được khởi công vào cuối năm 2026. Tuyến đường sắt đôi này dài khoảng 1.541 km nối Hà Nội và TP.HCM, có tốc độ thiết kế 350 km/h, bao gồm 23 ga hành khách và 5 ga hàng hóa. Bộ trưởng Bộ Xây dựng đã chỉ đạo các cơ quan khẩn trương hoàn thiện cơ chế đặc thù và giải phóng mặt bằng để đảm bảo tiến độ triển khai dự án.
-Source: [en.vneconomy.vn](https://en.vneconomy.vn/construction-of-vietnams-first-high-speed-railway-expected-to-start-by-end-2026.htm)</t>
+          <t>[Urban Development] Construction of Vietnam's first high-speed railway expected to start ... — The North-South high-speed railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City with a design speed of 350 km/h.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4769,35 +3856,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>## [https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/](https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/)
-### Document Overview
-The article discusses the necessity of integrating Vietnam's upcoming North-South high-speed railway with urban transit systems, highlighting confirmed metro plans in major cities and proposing new rail links for secondary tourism hubs.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line, and they will all be new stations located in different areas from the current stations of the North-South Railway... Hanoi and Ho Chi Minh City are planning to build metro lines to their high-speed railway stations, and Da Nang has proposed a rail connection. Here are some other cities on the high-speed rail route that should also consider a rail link.
-answer: 베트남은 하노이와 호치민을 잇는 남북 고속철도 건설을 계획 중이며, 신설될 23개 역이 도심과 떨어져 있어 이를 연결할 도시철도망 구축이 필수적인 상황입니다. 현재 하노이(메트로 1호선), 호치민(메트로 2호선), 다낭은 연결 노선이 확정되거나 제안되었으며, 기사는 나짱, 후에, 꾸이뇬 등 주요 거점 도시들도 관광 활성화와 접근성 개선을 위해 전차나 셔틀 열차 등 고속철도역 연결 교통망을 검토해야 한다고 제언합니다.
-Source: [futuresoutheastasia.com](https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/)</t>
+          <t>[Urban Development] Connecting Vietnam's high-speed railway stations with urban rail ... — Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line, and they will all be new ...</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>## [https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/](https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/)
-### Document Overview
-The article analyzes the necessity of connecting Vietnam's upcoming high-speed railway stations with urban rail transit, highlighting confirmed projects in Hanoi and HCMC and proposing new links for tourism hubs like Nha Trang and Hue.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line... Two stations are confirmed to have connecting metro lines (Line 1 in Hanoi and Line 2 in HCMC). Da Nang is also planning to build urban railways, which will most likely include a connection to the high-speed station.
-answer: Vietnam is developing a North-South high-speed railway with 23 new stations, necessitating integrated urban transit links to connect these often peripheral locations to city centers. Currently, Hanoi and Ho Chi Minh City have confirmed metro connections (Line 1 and Line 2 respectively), while Da Nang has proposed similar links; further proposals suggest extending urban rail or tramway systems to stations in cities like Nha Trang, Hue, and Quy Nhon to bolster tourism and regional accessibility.
-Source: [futuresoutheastasia.com](https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/)</t>
+          <t>[Urban Development] Connecting Vietnam's high-speed railway stations with urban rail ... — Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line, and they will all be new ...</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>## [https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/](https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/)
-### Document Overview
-The article discusses the necessity of building urban rail links to connect Vietnam's future high-speed railway stations with city centers, highlighting confirmed plans in Hanoi/HCMC and proposing concepts for other major cities.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line, and they will all be new stations located in different areas from the current stations of the North-South Railway... Two stations are confirmed to have connecting metro lines (Line 1 in Hanoi and Line 2 in HCMC). Da Nang is also planning to build urban railways... This post covers the confirmed and proposed metro lines that will connect the high-speed stations.
-answer: Bài viết phân tích tầm quan trọng của việc kết nối 23 ga đường sắt cao tốc Bắc-Nam tương lai với hệ thống giao thông đô thị, trong đó Hà Nội và TP.HCM đã xác nhận các tuyến metro kết nối cụ thể. Tác giả cũng đề xuất các thành phố lớn khác như Đà Nẵng, Nha Trang, Huế và Quy Nhơn cần chủ động quy hoạch đường sắt đô thị hoặc tàu điện mặt đất để tối ưu hóa khả năng tiếp cận các ga mới vốn thường nằm xa trung tâm hiện hữu. Việc xây dựng hệ thống chuyển tiếp đồng bộ được coi là yếu tố then chốt để thúc đẩy du lịch và phát triển kinh tế địa phương dọc theo trục cao tốc.
-Source: [futuresoutheastasia.com](https://futuresoutheastasia.com/connecting-vietnams-high-speed-railway-stations-with-urban-rail-transit/)</t>
+          <t>[Urban Development] Connecting Vietnam's high-speed railway stations with urban rail ... — Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line, and they will all be new ...</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4851,35 +3920,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>## [https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article](https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article)
-### Document Overview
-This article reports on the official start of civil works for Ho Chi Minh City's Metro Line 2, highlighting its shift to domestic financing and a 2030 completion target.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: The People’s Committee of Ho Chi Minh City held a groundbreaking ceremony on January 15 for the start of civil works on the 11·3 km, mostly underground metro Line 2. ... The Ho Chi Minh City Party Committee decided in November 2025 to use the municipal and national budget to complete Line 2. Completion is scheduled for the fourth quarter of 2030.
-answer: 베트남 호치민시가 11.3km 구간의 메트로 2호선 토목 공사를 위해 1월 15일 착공식을 개최했으며, 해당 노선은 2030년 4분기 완공을 목표로 하고 있습니다. 당초 국제 원조(ODA)를 고려했으나 비용 상승 등으로 인해 시 및 국가 예산을 투입하는 국내 재원 방식으로 전환되었으며, 한국 현대로템과 협력하는 THACO 컨소시엄이 건설을 주도합니다.
-Source: [www.railwaygazette.com](https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article)</t>
+          <t>[Urban Development] Financial close allows Ho Chi Minh City Line 2 civil works to start — The Ho Chi Minh City Party Committee decided in November 2025 to use the municipal and national budget to complete Line 2. Completion is ...</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>## [https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article](https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article)
-### Document Overview
-This article reports on the official start of civil works for Ho Chi Minh City's Metro Line 2, detailing its transition from international to domestic financing and its 2030 completion target.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: The People’s Committee of Ho Chi Minh City held a groundbreaking ceremony on January 15 for the start of civil works on the 11·3 km, mostly underground metro Line 2. ... The Ho Chi Minh City Party Committee decided in November 2025 to use the municipal and national budget to complete Line 2. Completion is scheduled for the fourth quarter of 2030.
-answer: Ho Chi Minh City has officially commenced civil works on the 11.3 km Metro Line 2 following a groundbreaking ceremony on January 15, 2026. After years of delays and cost increases to $2.1 billion, the project is now being financed through the municipal and national budget with a consortium led by THACO handling construction. The line, which features 11 stations and GoA4 automated technology, is scheduled for completion by the fourth quarter of 2030.
-Source: [www.railwaygazette.com](https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article)</t>
+          <t>[Urban Development] Financial close allows Ho Chi Minh City Line 2 civil works to start — The Ho Chi Minh City Party Committee decided in November 2025 to use the municipal and national budget to complete Line 2. Completion is ...</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>## [https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article](https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article)
-### Document Overview
-This article reports on the official start of civil works for Ho Chi Minh City's Metro Line 2, highlighting its financing shift to domestic budgets and its planned 2030 completion.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The People’s Committee of Ho Chi Minh City held a groundbreaking ceremony on January 15 for the start of civil works on the 11·3 km, mostly underground metro Line 2. The first section of Line 2 will run from Ben Thanh Market station on Line 1 to Tham Luong in the northwest of the city. Completion is scheduled for the fourth quarter of 2030.
-answer: Thành phố Hồ Chí Minh vừa chính thức khởi công xây dựng phần hạ tầng kỹ thuật cho tuyến metro số 2 dài 11,3 km kết nối từ chợ Bến Thành đến Tham Lương, với mục tiêu hoàn thành vào quý 4 năm 2030. Dự án có tổng mức đầu tư tăng lên 2,1 tỷ USD và hiện được tài trợ hoàn toàn bằng ngân sách nhà nước thay vì vốn vay ODA như kế hoạch ban đầu. Tuyến đường sắt đô thị tự động này bao gồm 11 nhà ga, trong đó phần lớn là đi ngầm và được thiết kế cho vận tốc vận hành 110 km/h.
-Source: [www.railwaygazette.com](https://www.railwaygazette.com/metro/financial-close-allows-ho-chi-minh-city-line-2-civil-works-to-start/70357.article)</t>
+          <t>[Urban Development] Financial close allows Ho Chi Minh City Line 2 civil works to start — The Ho Chi Minh City Party Committee decided in November 2025 to use the municipal and national budget to complete Line 2. Completion is ...</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4933,32 +3984,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/](https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/)
-### Document Overview
-This page summarizes Ho Chi Minh City's ambitious but slow-moving metro development plans as reported by the Vietnam News Agency.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: Ho Chi Minh City’s metro vision: big plans, slow progress. Ho Chi Minh City is mapping out an ambitious future for its urban rail network.
-answer: 호치민시는 도시 철도 네트워크를 위한 야심 찬 미래 마스터플랜을 수립하고 있으나, 실제 진행 속도는 계획에 비해 다소 느린 상황입니다. 현재 시 당국은 대규모 메트로 비전을 통해 도심 교통 문제를 해결하려 노력하고 있으며, 이는 도시 개발(Urban Development) 섹터의 핵심 과제로 다뤄지고 있습니다.
-Source: [www.facebook.com](https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/)</t>
+          <t>[Urban Development] Ho Chi Minh City's metro vision: Big plans, slow progress Ho Chi ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/](https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/)
-### Document Overview
-The page discusses Ho Chi Minh City's ambitious yet slow-moving urban metro network development plan as reported by the Vietnam News Agency.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: Ho Chi Minh City’s metro vision: big plans, slow progress - Ho Chi Minh City is mapping out an ambitious urban railway network, though the project has faced delays in implementation.
-answer: Ho Chi Minh City is currently planning an extensive urban railway network as part of its long-term infrastructure vision, although the project is characterized by significant delays in progress. The initiative aims to modernize the city's public transport system, but implementation remains slow despite the large-scale mapping of the metro lines.
-Source: [www.facebook.com](https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/)</t>
+          <t>[Urban Development] Ho Chi Minh City's metro vision: Big plans, slow progress Ho Chi ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/](https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/)
-### Document Overview
-Trang web là một bài đăng trên Facebook của Vietnam News Agency về quy hoạch metro tại TP.HCM, nhưng nội dung chi tiết bị chặn do rào cản kỹ thuật của trình duyệt.
-Source: [www.facebook.com](https://www.facebook.com/VNAEnglish/posts/-ho-chi-minh-citys-metro-vision-big-plans-slow-progressho-chi-minh-city-is-mappi/1593604119441598/)</t>
+          <t>[Urban Development] Ho Chi Minh City's metro vision: Big plans, slow progress Ho Chi ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5012,32 +4048,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=yBLU0JfoTsM](https://www.youtube.com/watch?v=yBLU0JfoTsM)
-### Document Overview
-This YouTube video documents a metro ride from An Phu Station in Thao Dien to Saigon Centre in District 1, showcasing Ho Chi Minh City's urban development.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: This video follows the journey from the vibrant neighborhood of Thao Dien to the heart of District 1. We begin with a walk through the streets of Thao Dien to... An Phu Station to Saigon Centre
-answer: 베트남 호치민시의 새로운 도시 철도 인프라를 소개하는 이 자료는 타오디엔 안푸역에서 1구역 사이공 센터까지의 메트로 주행 경로를 보여줍니다. 도시 개발 섹터의 관점에서 타오디엔과 같은 활기찬 주거 지역과 중심 상업 지구를 잇는 교통망의 실제 운영 모습을 상세히 담고 있습니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=yBLU0JfoTsM)</t>
+          <t>[Urban Development] Ho Chi Minh City Metro Ride: An Phu Station to Saigon Centre — ... 2026 Support Me PayPal: https://paypal.me/actionkidyt?locale.x=en_US Cash App: $ ... Bullet Train | Shanghai - Beijing. Solo Solo Travel.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=yBLU0JfoTsM](https://www.youtube.com/watch?v=yBLU0JfoTsM)
-### Document Overview
-The page provides a first-person perspective of the Ho Chi Minh City Metro system, documenting the journey and infrastructure between An Phu Station and the city center.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: This video follows the journey from the vibrant neighborhood of Thao Dien to the heart of District 1. We begin with a walk through the streets of Thao Dien to An Phu Station... Ho Chi Minh City Metro Ride: An Phu Station to Saigon Centre
-answer: The video documents the operational environment and connectivity of the Ho Chi Minh City Metro, specifically focusing on the route from An Phu Station in Thao Dien to Saigon Centre in District 1. It showcases the urban development progress in Vietnam's largest city by highlighting the transition between vibrant residential neighborhoods and the central business district via new rail infrastructure. This footage serves as a practical demonstration of how the metro system integrates with the city's pedestrian walkways and commercial hubs.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=yBLU0JfoTsM)</t>
+          <t>[Urban Development] Ho Chi Minh City Metro Ride: An Phu Station to Saigon Centre — ... 2026 Support Me PayPal: https://paypal.me/actionkidyt?locale.x=en_US Cash App: $ ... Bullet Train | Shanghai - Beijing. Solo Solo Travel.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=yBLU0JfoTsM](https://www.youtube.com/watch?v=yBLU0JfoTsM)
-### Document Overview
-Trang web được cung cấp là trang đích của một video YouTube nhưng không chứa nội dung văn bản cụ thể về chủ đề cơ sở hạ tầng Việt Nam để phân tích.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=yBLU0JfoTsM)</t>
+          <t>[Urban Development] Ho Chi Minh City Metro Ride: An Phu Station to Saigon Centre — ... 2026 Support Me PayPal: https://paypal.me/actionkidyt?locale.x=en_US Cash App: $ ... Bullet Train | Shanghai - Beijing. Solo Solo Travel.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5091,35 +4112,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>## [https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun](https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun)
-### Document Overview
-This article analyzes the strategic landscape of Vietnam's infrastructure investment for 2026-2030, highlighting a $150-200bn funding gap and the regulatory reforms driving foreign participation.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Finance &amp; Investment, 관련 마스터플랜: N/A
-verbatim: Vietnam faces a large funding gap, estimated at USD150–200bn through 2030, which the government budget, foreign aid and domestic savings cannot cover by themselves... This article identifies six forces that will shape how the country and foreign investors approach that challenge over the next five years... The policy foundation put in place through Resolution 68, Resolution 79, and the legislative reforms of 2025 is stronger and more supportive of private investment than at any previous point in Vietnam's economic reform history.
-answer: 베트남은 2030년까지 약 1,500억~2,000억 달러에 달하는 막대한 인프라 자금 부족을 해결하기 위해 민간 및 외국인 자본 유치를 필수 과제로 삼고 있습니다. 2025년 단행된 법적 개혁과 결의안 제68호 및 제79호를 통해 민간 경제의 역할을 강화하고 국영기업과의 파트너십을 장려하는 등 친기업적 투자 환경을 조성하고 있습니다. 이에 따라 해상 풍력, LNG 발전, 항만 등 외국인의 기술력과 자본이 필수적인 분야를 중심으로 전략적 투자 기회가 확대될 전망입니다.
-Source: [transactions.freshfields.com](https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun)</t>
+          <t>[Finance &amp; Investment] Vietnam's infrastructure: Six forces shaping investment in 2026 ... — According to the Ministry of Finance, disbursed foreign direct investment in Vietnam was estimated at US$27.6 billion, up 9 per cent from a year ...</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>## [https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun](https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun)
-### Document Overview
-The article analyzes Vietnam's infrastructure landscape for 2026-2030, highlighting a $200bn funding gap and the regulatory reforms designed to attract foreign investment into strategic sectors.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Finance &amp; Investment, Related plans: N/A
-verbatim: Vietnam faces a large funding gap, estimated at USD150–200bn through 2030, which the government budget, foreign aid and domestic savings cannot cover by themselves. Closing this gap is both the biggest challenge and the most important opportunity in Vietnam's infrastructure development in this decade. ... The policy foundation put in place through Resolution 68, Resolution 79, and the legislative reforms of 2025 is stronger and more supportive of private investment than at any previous point in Vietnam's economic reform history.
-answer: Vietnam is facing a critical $150–200 billion infrastructure funding gap through 2030, prompting the government to implement significant legal reforms and policy shifts to attract foreign private capital. Recent initiatives, such as Politburo Resolutions 68 and 79 and 2025 legislative updates, position the private sector as the primary economic driver and encourage partnerships with state-owned enterprises in sectors like renewable energy, transport, and digital networks.
-Source: [transactions.freshfields.com](https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun)</t>
+          <t>[Finance &amp; Investment] Vietnam's infrastructure: Six forces shaping investment in 2026 ... — According to the Ministry of Finance, disbursed foreign direct investment in Vietnam was estimated at US$27.6 billion, up 9 per cent from a year ...</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>## [https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun](https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun)
-### Document Overview
-The article outlines six major forces driving Vietnam's infrastructure sector from 2026-2030, highlighting a $150-200bn funding gap and the increasing necessity of foreign investment supported by new policy reforms.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam faces a large funding gap, estimated at USD150–200bn through 2030, which the government budget, foreign aid and domestic savings cannot cover by themselves... This article identifies six forces that will shape how the country and foreign investors approach that challenge over the next five years... The policy foundation put in place through Resolution 68, Resolution 79, and the legislative reforms of 2025 is stronger and more supportive of private investment than at any previous point in Vietnam's economic reform history.
-answer: Bài báo phân tích sáu yếu tố cốt lõi định hình thị trường hạ tầng Việt Nam giai đoạn 2026-2030, trong bối cảnh quốc gia này cần khoảng 150-200 tỷ USD vốn đầu tư nhưng ngân sách nhà nước chỉ đáp ứng được một nửa. Dưới sự dẫn dắt của ban lãnh đạo mới và các cải cách pháp lý mang tính bước ngoặt như Nghị quyết 68 và 79, Việt Nam đang mở cửa mạnh mẽ cho tư nhân và nhà đầu tư nước ngoài tham gia vào các dự án trọng điểm như năng lượng tái tạo, đường sắt tốc độ cao và cảng biển. Đây là thời điểm vàng cho các nhà đầu tư quốc tế có năng lực chuyên môn cao phối hợp cùng các doanh nghiệp nhà nước và tập đoàn tư nhân trong nước để hiện thực hóa các cơ hội hạ tầng quy mô lớn.
-Source: [transactions.freshfields.com](https://transactions.freshfields.com/post/102movd/vietnams-infrastructure-six-forces-shaping-investment-in-20262030-and-opportun)</t>
+          <t>[Finance &amp; Investment] Vietnam's infrastructure: Six forces shaping investment in 2026 ... — According to the Ministry of Finance, disbursed foreign direct investment in Vietnam was estimated at US$27.6 billion, up 9 per cent from a year ...</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5173,32 +4176,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=La_LjUiBLbU](https://www.youtube.com/watch?v=La_LjUiBLbU)
-### Document Overview
-This page provides a summary of a video report regarding the construction halt and challenges of Vietnam's $16 billion Long Thanh International Airport project.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Vietnam’s $16 Billion Long Thanh International Airport was supposed to be the "Jewel of Southeast Asia" and a rival to Singapore's Changi. But recent reports... Why Construction Just STOPPED
-answer: 베트남이 동남아시아의 허브 공항을 목표로 추진 중인 160억 달러 규모의 롱탄 국제공항 건설 프로젝트가 최근 중단 위기에 직면했습니다. 싱가포르 창이 공항의 경쟁자로 기대를 모았던 이 거대 인프라 사업은 보고서에 따르면 최근 공사 중단 소식이 전해지며 난항을 겪고 있습니다. (섹터: Transport &amp; Infrastructure)
-Source: [www.youtube.com](https://www.youtube.com/watch?v=La_LjUiBLbU)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's $16B Airport Why Construction Just STOPPED - YouTube — Vietnam's $16 Billion Long Thanh International Airport was supposed to be the "Jewel of Southeast Asia" and a rival to Singapore's Changi.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=La_LjUiBLbU](https://www.youtube.com/watch?v=La_LjUiBLbU)
-### Document Overview
-The page content provided is restricted to standard YouTube navigation and legal footer links, lacking any actual video description or transcript details.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=La_LjUiBLbU)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's $16B Airport Why Construction Just STOPPED - YouTube — Vietnam's $16 Billion Long Thanh International Airport was supposed to be the "Jewel of Southeast Asia" and a rival to Singapore's Changi.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=La_LjUiBLbU](https://www.youtube.com/watch?v=La_LjUiBLbU)
-### Document Overview
-The page discusses the challenges and reasons behind the construction delays of Vietnam's $16 billion Long Thanh International Airport project.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s $16 Billion Long Thanh International Airport was supposed to be the "Jewel of Southeast Asia" and a rival to Singapore's Changi. But recent reports... Vietnam’s $16B Airport Why Construction Just STOPPED
-answer: Video phân tích về dự án Sân bay Quốc tế Long Thành trị giá 16 tỷ USD của Việt Nam, vốn được kỳ vọng trở thành đối trọng với sân bay Changi của Singapore. Nội dung tập trung vào lý do tại sao quá trình thi công dự án quan trọng này lại đang gặp phải các vấn đề tạm dừng hoặc trì hoãn so với kế hoạch ban đầu.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=La_LjUiBLbU)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's $16B Airport Why Construction Just STOPPED - YouTube — Vietnam's $16 Billion Long Thanh International Airport was supposed to be the "Jewel of Southeast Asia" and a rival to Singapore's Changi.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5252,35 +4240,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html](https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html)
-### Document Overview
-This article outlines the progress of major transportation infrastructure projects in Vietnam, including expressways, the North-South high-speed railway, and airport expansions, highlighting their role in socio-economic growth and FDI attraction.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-TRAN-2055
-verbatim: This year will mark the finish line for many key expressway projects. An example is Ben Luc-Long Thanh Expressway, nearly 58 km long... Construction of the station infrastructure component began in December, while the main line is scheduled to start in June this year, targeting full synchronous completion by 2030... The high-speed trains are designed to operate at speeds exceeding 300km per hour; the preliminary total investment exceeds $67.3 billion, with the basic completion target set for 2035.
-answer: 베트남 정부는 2026년 대규모 인프라 프로젝트의 장애물을 제거하고 벤룩-롱탄 고속도로 및 호치민 순환도로 등 주요 교통망의 완공을 가속화하고 있습니다. 특히 673억 달러 규모의 남북 고속철도와 라오카이-하이퐁 철도 건설이 본격화되면서, 2035년까지 철도, 공항, 항만을 유기적으로 연결하는 국가 교통 동기화 작업을 추진 중입니다. 이러한 인프라 확충은 물류 효율성을 높여 외국인 투자 유치를 활성화하고 지역 간 균형 발전을 도모하는 핵심 동력이 될 것으로 전망됩니다.
-Source: [vir.com.vn](https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html)</t>
+          <t>[Transport &amp; Infrastructure] Transport infrastructure in process of synchronisation — By the end of 2025, Vietnam had 3,345km of main expressways and 458km of interchanges and access roads in operation; it had fully completed and ... (관련: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html](https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html)
-### Document Overview
-The article details Vietnam's 2026 push to synchronize its transport infrastructure, including progress on expressways, ring roads, airports, and the commencement of major high-speed rail projects.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-TRAN-2055
-verbatim: Vietnam is accelerating key transport projects this year, with significant progress on the Ben Luc-Long Thanh Expressway, Ring Roads in Hanoi and HCMC, and the Long Thanh International Airport phase 1 operations. The North-South high-speed railway, valued at $67.3 billion, and the $8 billion Lao Cai-Haiphong railway are also advancing, targeting full synchronous completion by 2030-2035 to enhance regional connectivity and attract foreign investment.
-answer: Vietnam is currently synchronizing its transport network by accelerating major expressway projects, completing ring roads in Hanoi and Ho Chi Minh City, and operationalizing Phase 1 of the Long Thanh International Airport. The government is also initiating massive strategic projects including the $67.3 billion North-South high-speed railway and the $8 billion Lao Cai-Haiphong railway, aiming for a fully integrated national infrastructure system by 2035 to optimize economic resources and FDI appeal.
-Source: [vir.com.vn](https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html)</t>
+          <t>[Transport &amp; Infrastructure] Transport infrastructure in process of synchronisation — By the end of 2025, Vietnam had 3,345km of main expressways and 458km of interchanges and access roads in operation; it had fully completed and ... (Related: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html](https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html)
-### Document Overview
-The article discusses Vietnam's intensive efforts to synchronize and complete major transport infrastructure projects like the North-South high-speed railway, Long Thanh Airport, and various expressways to boost economic growth and FDI attraction.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Already this year, the government has issued various directives to resolve issues for a large number of stalled and long-suspended infrastructure projects... This year will mark the finish line for many key expressway projects... the North-South high-speed railway, the most ambitious infrastructure project in the transport sector, is anticipated to break ground... the government’s efforts to improve transport infrastructure... have created many advantages for the Korean members.
-answer: Chính phủ Việt Nam đang quyết liệt chỉ đạo tháo gỡ khó khăn cho các dự án hạ tầng bị đình trệ, đồng thời đẩy nhanh tiến độ các công trình trọng điểm như cao tốc Bến Lức - Long Thành và Vành đai 3 TP.HCM. Năm nay cũng đánh dấu những cột mốc quan trọng với việc khởi động dự án đường sắt tốc độ cao Bắc - Nam và đưa vào vận hành giai đoạn 1 sân bay quốc tế Long Thành. Sự đồng bộ hóa hệ thống giao thông này không chỉ thúc đẩy tăng trưởng kinh tế - xã hội mà còn gia tăng sức hấp dẫn của Việt Nam trong mắt các nhà đầu tư nước ngoài.
-Source: [vir.com.vn](https://vir.com.vn/transport-infrastructure-in-process-of-synchronisation-147791.html)</t>
+          <t>[Transport &amp; Infrastructure] Transport infrastructure in process of synchronisation — By the end of 2025, Vietnam had 3,345km of main expressways and 458km of interchanges and access roads in operation; it had fully completed and ... (Liên quan: VN-TRAN-2055)</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5334,35 +4304,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html](https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html)
-### Document Overview
-This article details Vietnam's significant progress in aviation infrastructure between 2021 and 2025, highlighting key projects like Long Thanh International Airport and Gia Binh Airport, and forecasts continued double-digit growth for 2026.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-EV-2030
-verbatim: Long Thanh International Airport stands out as a landmark aviation infrastructure project of the 2021–2025 period... Designed to ICAO 4F standards, Long Thanh is set to handle over 100 million passengers annually... Gia Binh International Airport in Bac Ninh represents a novel dual-use planning model... Several regional airports - including Phu Quoc, Phu Bai, Vinh, Phan Thiet, Tuy Hoa, Pleiku, and Buon Ma Thuot - also advanced under the 2030 development plan... In 2025 alone, the industry carried 83.5 million passengers... 2026 is expected to be a pivotal year, bringing fresh growth drivers for Vietnam’s aviation industry.
-answer: 베트남은 2021-2025년 기간 동안 롱탄 국제공항의 기술적 개항과 자빈 국제공항의 신규 추진 등 주요 공항 인프라 확충을 통해 동남아시아의 항공 허브로 도약하고 있습니다. VN-EV-2030 마스터플랜에 따라 탄손낫 및 노이바이 공항 확장과 지역 거점 공항 현대화가 진행 중이며, 2025년 기준 역대 최고치인 8,350만 명의 여객 운송 실적을 기록했습니다. 이러한 인프라 돌파구와 항공기 보유 대수 확대를 바탕으로 2026년에는 여객 9,500만 명 및 화물 160만 톤 처리를 목표로 하는 두 자릿수 성장이 기대됩니다.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's aviation lifts off with major airport breakthroughs — Landmark infrastructure shaping a new development axis · Fleet expansion and robust market recovery · Toward double-digit growth in 2026. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html](https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html)
-### Document Overview
-The article details the significant progress in Vietnam's aviation sector during the 2021-2025 period, highlighting major airport completions, fleet expansions, and growth forecasts for 2026.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-EV-2030
-verbatim: Long Thanh International Airport stands out as a landmark aviation infrastructure project of the 2021–2025 period... Several regional airports - including Phu Quoc, Phu Bai, Vinh, Phan Thiet, Tuy Hoa, Pleiku, and Buon Ma Thuot - also advanced under the 2030 development plan... On December 19, 2025, the project’s main components were technically inaugurated... 2026 is expected to be a pivotal year, bringing fresh growth drivers for Vietnam’s aviation industry.
-answer: Vietnam’s aviation infrastructure has reached a major milestone with the technical inauguration of Long Thanh International Airport and the strategic development of Gia Binh International Airport to serve as a high-tech logistics hub. Under the 2030 development plan, the country is also upgrading regional airports and expanding terminal capacities at Tan Son Nhat and Noi Bai to support a projected 95 million passengers in 2026. These breakthroughs in the transport sector are designed to bolster regional connectivity and accommodate double-digit growth in both tourism and cargo throughput.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's aviation lifts off with major airport breakthroughs — Landmark infrastructure shaping a new development axis · Fleet expansion and robust market recovery · Toward double-digit growth in 2026. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html](https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html)
-### Document Overview
-The article reports on Vietnam's significant aviation milestones between 2021-2026, highlighting major airport projects like Long Thanh and Gia Binh, infrastructure upgrades, and record-breaking passenger growth forecasts for 2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Long Thanh International Airport stands out as a landmark aviation infrastructure project of the 2021–2025 period... Designed to ICAO 4F standards, Long Thanh is set to handle over 100 million passengers annually... The 2021–2025 period also witnessed a strong recovery and impressive growth in air travel. In 2025 alone, the industry carried 83.5 million passengers... Forecasts suggest that in 2026, Vietnam’s aviation sector could handle about 95 million passengers.
-answer: Giai đoạn 2021-2025 đánh dấu bước ngoặt lớn của ngành hàng không Việt Nam với việc đẩy nhanh các dự án hạ tầng trọng điểm, tiêu biểu là việc khánh thành kỹ thuật sân bay Long Thành và nâng cấp các sân bay lớn như Tân Sơn Nhất, Nội Bài. Song song với hạ tầng, thị trường hàng không phục hồi mạnh mẽ khi đón 83,5 triệu lượt khách trong năm 2025, tạo đà để ngành hướng tới mục tiêu tăng trưởng hai con số và phục vụ khoảng 95 triệu hành khách vào năm 2026.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/vietnam-s-aviation-lifts-off-with-major-airport-breakthroughs-2481566.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's aviation lifts off with major airport breakthroughs — Landmark infrastructure shaping a new development axis · Fleet expansion and robust market recovery · Toward double-digit growth in 2026. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5416,35 +4368,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>## [https://www.seetaoe.com/details/257042.html](https://www.seetaoe.com/details/257042.html)
-### Document Overview
-The article reports on the construction progress and design features of Vietnam's Long Thanh International Airport, highlighting its scale as a 4F hub and its cultural-modern fusion design by South Korean architects.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Long Thanh International Airport. It is not only a transportation hub, but also seen as the gateway to opening a new era for Vietnam Airlines... The overall planning of Longcheng International Airport covers an area of 5000 hectares... positioning it as the highest level 4F international aviation hub... Longcheng International Airport will be constructed in three phases, with the first phase expected to be completed and put into operation in the first half of 2026.
-answer: 베트남 최대의 교통 인프라 프로젝트인 롱탄 국제공항이 2026년 상반기 1단계 개항을 목표로 건설 중이며, 최종 완공 시 연간 1억 명의 승객을 수용하는 4F급 항공 허브가 될 전망입니다. 한국의 희림종합건축사사무소가 설계를 맡아 베트남 국화인 연꽃을 형상화하고 세계 최대 규모의 대나무 구조물을 도입하는 등 전통 문화와 지속 가능한 현대 디자인을 결합했습니다. 총 3단계에 걸쳐 2040년 최종 완공될 이 프로젝트는 베트남의 항공 운송 역량을 획기적으로 강화하고 지역 연결성을 높이는 중추적인 역할을 할 것으로 기대됩니다.
-Source: [www.seetaoe.com](https://www.seetaoe.com/details/257042.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's largest airport is about to be put into operation - Seetao — The first phase of Vietnam Longcheng International Airport project will be completed and put into operation in the first half of 2026.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>## [https://www.seetaoe.com/details/257042.html](https://www.seetaoe.com/details/257042.html)
-### Document Overview
-The article details the construction of Vietnam's Long Thanh International Airport, a massive 4F hub project expected to finish its first phase in 2026 and eventually serve 100 million passengers annually.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Long Thanh International Airport... It is not only a transportation hub, but also seen as the gateway to opening a new era for Vietnam Airlines... The first phase expected to be completed and put into operation in the first half of 2026. The overall project is expected to be fully completed by 2040.
-answer: Vietnam is constructing the Long Thanh International Airport in Thong Nai province, a 4F-level aviation hub designed with a lotus-inspired aesthetic that aims to become the world's largest bamboo-structure terminal. With a total investment of 336 trillion VND, the project is being developed in three phases, with the first phase scheduled for completion in early 2026 to handle 25 million passengers annually.
-Source: [www.seetaoe.com](https://www.seetaoe.com/details/257042.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's largest airport is about to be put into operation - Seetao — The first phase of Vietnam Longcheng International Airport project will be completed and put into operation in the first half of 2026.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>## [https://www.seetaoe.com/details/257042.html](https://www.seetaoe.com/details/257042.html)
-### Document Overview
-This article provides a detailed overview of the Long Thanh International Airport project in Vietnam, covering its design, capacity, investment, and construction timeline.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: This is the largest transportation infrastructure project in Vietnamese history - Long Thanh International Airport. ... The overall planning of Longcheng International Airport covers an area of 5000 hectares ... The first phase is expected to be completed and put into operation in the first half of 2026.
-answer: Sân bay Quốc tế Long Thành là dự án hạ tầng giao thông lớn nhất trong lịch sử Việt Nam, được thiết kế với hình dáng hoa sen và cấu trúc tre lớn nhất thế giới. Dự án có tổng diện tích quy hoạch 5.000 ha, công suất thiết kế lên đến 100 triệu hành khách mỗi năm, trong đó giai đoạn một dự kiến sẽ hoàn thành và đi vào hoạt động trong nửa đầu năm 2026.
-Source: [www.seetaoe.com](https://www.seetaoe.com/details/257042.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's largest airport is about to be put into operation - Seetao — The first phase of Vietnam Longcheng International Airport project will be completed and put into operation in the first half of 2026.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5498,35 +4432,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV](https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV)
-### Document Overview
-The page summarizes a LinkedIn post regarding the Vietnamese government's move to accelerate the $16 billion Long Thanh International Airport project for a 2026 launch.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Vietnam's Long Thanh Airport to Launch by 2026 with $16B Investment. The government has set a strict deadline of 30 days to complete and sign key contracts for Long Thanh International Airport, aiming to accelerate project execution. Long Thanh Airport (total investment ~VND 200,000+ billion / ~$16 billion) is targeted to begin commercial operations by the end of 2026. Long Thanh is expected to become a major regional aviation hub, with long-term expansion toward 100 million passengers capacity.
-answer: 베트남 정부는 약 160억 달러(200조 동 이상)가 투입되는 롱탄 국제공항의 조속한 추진을 위해 30일 이내에 핵심 계약을 완료하라는 엄격한 기한을 설정했습니다. 이 프로젝트는 현재 100개 이상의 패키지가 실행되는 전면적인 건설 단계에 진입했으며, 2026년 말까지 상업 운항 시작을 목표로 하고 있습니다. 완공 시 연간 1억 명의 승객 수용 능력을 갖춘 지역 항공 허브이자 에어포트 시티(Airport City)로 거듭나 베트남의 물류 및 지역 경제 성장에 크게 기여할 것으로 기대됩니다.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's Long Thanh Airport to Launch by 2026 with $16B ... — Vietnam's Long Thanh Airport to Launch by 2026 with $16B Investment ... terminal, VIP terminal, and aviation infrastructure. • Capacity ...</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV](https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV)
-### Document Overview
-The post details the Vietnamese government's efforts to expedite the Long Thanh International Airport project, targeting a 2026 opening with an investment of approximately $16 billion.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: The government has set a strict deadline of 30 days to complete and sign key contracts for Long Thanh International Airport, aiming to accelerate project execution. Long Thanh Airport (total investment ~VND 200,000+ billion / ~$16 billion) is targeted to begin commercial operations by the end of 2026.
-answer: Vietnam has established a strict 30-day deadline for signing key contracts to accelerate the $16 billion (over VND 200,000 billion) Long Thanh International Airport project, which is slated to begin commercial operations by late 2026. The national key infrastructure project is currently shifting from planning to full-scale execution, with over 100 contract packages active and a long-term goal of reaching a 100 million passenger capacity.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's Long Thanh Airport to Launch by 2026 with $16B ... — Vietnam's Long Thanh Airport to Launch by 2026 with $16B Investment ... terminal, VIP terminal, and aviation infrastructure. • Capacity ...</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV](https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV)
-### Document Overview
-Bài viết tóm tắt tiến độ dự án sân bay Long Thành, nhấn mạnh sự chỉ đạo sát sao của Chính phủ về thời hạn ký kết hợp đồng và mục tiêu vận hành vào năm 2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The government has set a strict deadline of 30 days to complete and sign key contracts for Long Thanh International Airport, aiming to accelerate project execution. • Long Thanh Airport (total investment ~VND 200,000+ billion / ~$16 billion) is targeted to begin commercial operations by the end of 2026. Long Thanh is expected to become a major regional aviation hub, with long-term expansion toward 100 million passengers capacity, positioning Vietnam in regional transit competition.
-answer: Chính phủ Việt Nam đã chốt thời hạn 30 ngày để hoàn tất ký kết các hợp đồng then chốt nhằm đẩy nhanh tiến độ dự án sân bay quốc tế Long Thành với tổng vốn đầu tư hơn 200.000 tỷ đồng. Dự án đặt mục tiêu bắt đầu vận hành thương mại vào cuối năm 2026, hướng tới trở thành trung tâm hàng không khu vực với công suất thiết kế lên đến 100 triệu hành khách mỗi năm.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/ami-benavides-471b1177_ch%C3%ADnh-ph%E1%BB%A7-ch%E1%BB%91t-h%E1%BA%A1n-30-ng%C3%A0y-k%C3%BD-h%E1%BB%A3p-%C4%91%E1%BB%93ng-si%C3%AAu-activity-7446020918746972160-bVbV)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's Long Thanh Airport to Launch by 2026 with $16B ... — Vietnam's Long Thanh Airport to Launch by 2026 with $16B Investment ... terminal, VIP terminal, and aviation infrastructure. • Capacity ...</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -5580,35 +4496,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>## [https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm](https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm)
-### Document Overview
-This article details the Vietnamese Prime Minister's directive to complete Phase 1 of the Long Thanh International Airport by mid-2026, highlighting its scale, investment, and advanced technology features.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: The directive was outlined in a Thursday notice issued by the Government Office following the 23rd meeting of the State Steering Committee for National Key Transport Projects, chaired by PM Chinh... Chinh instructed ACV, the project’s investor, along with other ministries and agencies, to urgently review the remaining workload at the construction site and develop detailed and practical implementation plans to ensure the first phase is completed within the first half of this year.
-answer: 베트남 팜 민 찐 총리는 국가 핵심 교통 프로젝트인 롱탄 국제공항 1단계 공사를 2026년 상반기 내에 완료할 것을 긴급 지시했습니다. 약 42억 달러가 투입된 1단계 사업이 완료되면 연간 2,500만 명의 승객을 수용하며 기존 탄손냐트 공항의 혼잡을 완화할 것으로 기대되며, 공항 측은 생체 인식 및 자동 수하물 처리 등 최첨단 스마트 시스템을 도입할 예정입니다.
-Source: [news.tuoitre.vn](https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam PM presses for Long Thanh airport phase 1 completion by ... — Long Thanh International Airport is a national key project spanning about 5,000 hectares, with a total estimated investment of more than VND336.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>## [https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm](https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm)
-### Document Overview
-Vietnam's Prime Minister has set a deadline for the first phase of the $13 billion Long Thanh International Airport to be completed by the first half of 2026 to ensure the project becomes a major regional hub.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Vietnam's Prime Minister Pham Minh Chinh has directed the Airports Corporation of Vietnam (ACV) and relevant agencies to complete Phase 1 of the Long Thanh International Airport by the first half of 2026. This national key project, with a total estimated investment of over US$13 billion, aims to handle 25 million passengers annually in its first phase and eventually reach a capacity of 100 million passengers to become a major regional aviation hub.
-answer: Vietnam's Prime Minister has ordered the completion of Phase 1 of the Long Thanh International Airport by mid-2026 following a successful first official wide-body aircraft landing in late 2025. The US$13 billion project is designed as a high-tech, five-star facility that will eventually serve 100 million passengers annually, significantly easing congestion at Tan Son Nhat International Airport and establishing Vietnam as a key regional aviation hub.
-Source: [news.tuoitre.vn](https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam PM presses for Long Thanh airport phase 1 completion by ... — Long Thanh International Airport is a national key project spanning about 5,000 hectares, with a total estimated investment of more than VND336.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>## [https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm](https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm)
-### Document Overview
-Thủ tướng Chính phủ yêu cầu hoàn thành giai đoạn 1 dự án Sân bay Long Thành vào giữa năm 2026 nhằm giảm tải cho Tân Sơn Nhất và nâng tầm vị thế hàng không Việt Nam.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The directive was outlined in a Thursday notice issued by the Government Office following the 23rd meeting of the State Steering Committee for National Key Transport Projects, chaired by PM Chinh, head of the committee. At the meeting, Chinh instructed ACV, the project’s investor, along with other ministries and agencies, to urgently review the remaining workload at the construction site and develop detailed and practical implementation plans to ensure the first phase is completed within the first half of this year.
-answer: Thủ tướng Chính phủ Phạm Minh Chính yêu cầu đẩy nhanh tiến độ để hoàn thành giai đoạn 1 của dự án Sân bay quốc tế Long Thành vào nửa đầu năm 2026. Đây là dự án hạ tầng hàng không trọng điểm quốc gia với tổng mức đầu tư hơn 336.000 tỷ đồng, được thiết kế theo tiêu chuẩn 5 sao quốc tế và tích hợp các công nghệ thông minh hiện đại. Khi hoàn thiện toàn bộ, sân bay dự kiến sẽ đạt công suất 100 triệu hành khách mỗi năm, đưa Việt Nam trở thành trung tâm hàng không quan trọng trong khu vực.
-Source: [news.tuoitre.vn](https://news.tuoitre.vn/vietnam-pm-presses-for-long-thanh-airport-phase-1-completion-by-mid-2026-103260227143932302.htm)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam PM presses for Long Thanh airport phase 1 completion by ... — Long Thanh International Airport is a national key project spanning about 5,000 hectares, with a total estimated investment of more than VND336.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -5662,32 +4560,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=Gw9ewrakUB0](https://www.youtube.com/watch?v=Gw9ewrakUB0)
-### Document Overview
-This content discusses Vietnam's $16 billion mega airport construction project and its potential to reshape the aviation industry in Asia.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Vietnam is pushing ahead with a $16 billion mega airport project, and the global impact could be massive. Asia’s aviation map may be about to change forever.
-answer: 베트남은 아시아 항공 지형을 근본적으로 변화시키기 위해 160억 달러 규모의 초대형 신공항 건설 프로젝트를 추진하고 있습니다. 이 메가 프로젝트는 베트남의 물류 및 교통 인프라 경쟁력을 강화하며 글로벌 시장에서 막대한 경제적 파급효과를 불러올 것으로 기대됩니다. (섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A)
-Source: [www.youtube.com](https://www.youtube.com/watch?v=Gw9ewrakUB0)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's $16B AIRPORT MEGA PROJECT Could Change Asia ... — ... infrastructure move yet—and why the rest of Asia is watching ... HUGE Vietnam Visa Update 2026 NOBODY Expected (WHY?!) Duong Global ...</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=Gw9ewrakUB0](https://www.youtube.com/watch?v=Gw9ewrakUB0)
-### Document Overview
-The page describes Vietnam's ambitious $16 billion mega airport project which aims to transform Asia's aviation sector.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Vietnam is pushing ahead with a $16 billion mega airport project, and the global impact could be massive. Asia’s aviation map may be about to change forever.
-answer: Vietnam is currently developing a massive $16 billion mega airport project intended to redefine the aviation landscape in Asia. This major transport and infrastructure initiative aims to significantly increase the country's aerial capacity and exert a substantial global impact on regional travel and logistics.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=Gw9ewrakUB0)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's $16B AIRPORT MEGA PROJECT Could Change Asia ... — ... infrastructure move yet—and why the rest of Asia is watching ... HUGE Vietnam Visa Update 2026 NOBODY Expected (WHY?!) Duong Global ...</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=Gw9ewrakUB0](https://www.youtube.com/watch?v=Gw9ewrakUB0)
-### Document Overview
-Trang web này là một trang trình phát video YouTube trống, chỉ hiển thị thông tin chân trang của Google/YouTube và không chứa nội dung cụ thể về cơ sở hạ tầng Việt Nam.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=Gw9ewrakUB0)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's $16B AIRPORT MEGA PROJECT Could Change Asia ... — ... infrastructure move yet—and why the rest of Asia is watching ... HUGE Vietnam Visa Update 2026 NOBODY Expected (WHY?!) Duong Global ...</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5741,35 +4624,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>## [https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm](https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm)
-### Document Overview
-This article details the approval and construction timeline of the Gia Binh International Airport in Bac Ninh province, highlighting its capacity and economic role as a dual-use aviation hub in northern Vietnam.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Construction of the Gia Binh International Airport project... kicked off in northern Bac Ninh province on December 10 last year... The airport will be completed by the end of 2026, with trial operations beginning in February 2027. During 2021-2030 period, the airport will feature two runways with capacity to handle about 30 million passengers and 1.6 million tons of cargo annually.
-answer: 베트남 정부는 하노이에서 약 40km 떨어진 박닌성에 건설될 자빈(Gia Binh) 국제공항의 투자 정책을 승인했으며, 2026년 말 완공 및 2027년 2월 시범 운영을 목표로 하고 있습니다. 이 공항은 2030년까지 연간 3천만 명의 여객과 160만 톤의 화물을 처리할 수 있는 복합 항공 허브로 구축되어 제조, 물류, 관광 등 북부 지역 산업 발전을 견인할 것으로 기대됩니다.
-Source: [en.baochinhphu.vn](https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm)</t>
+          <t>[Transport &amp; Infrastructure] Viet Nam approves investment policy for Gia Binh International Airport — The airport will be completed by the end of 2026, with trial operations beginning in February 2027. Covering nearly 1,960 hectares, the airport ...</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>## [https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm](https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm)
-### Document Overview
-Vietnam has commenced the construction of Gia Binh International Airport in Bac Ninh province, projected to become a major aviation hub near Hanoi by 2026 with significant passenger and cargo handling capacity, supporting regional economic growth and meeting high ESG standards.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Construction of the Gia Binh International Airport project, about 40km from Ha Noi's center, kicked off in northern Bac Ninh province on December 10 last year, a dual-use facility designed to become a major aviation hub in northern Viet Nam. The airport will be completed by the end of 2026, with trial operations beginning in February 2027. Covering nearly 1,960 hectares, the airport is being developed in line with environmental, social and governance (ESG) standards. During 2021-2030 period, the airport will feature two runways with capacity to handle about 30 million passengers and 1.6 million tons of cargo annually. From 2050 onwards, the airport will serve up to 50 million passengers and 2.5 million tons of cargo each year.
-answer: Vietnam has approved the investment policy for the Gia Binh International Airport in Bac Ninh province, with construction already underway for a dual-use aviation hub located about 40km from Hanoi. The new airport, covering nearly 1,960 hectares and designed to meet ESG standards, is expected to be completed by the end of 2026, handling 30 million passengers and 1.6 million tons of cargo annually by 2030, and up to 50 million passengers and 2.5 million tons of cargo per year from 2050 onwards.
-Source: [en.baochinhphu.vn](https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm)</t>
+          <t>[Transport &amp; Infrastructure] Viet Nam approves investment policy for Gia Binh International Airport — The airport will be completed by the end of 2026, with trial operations beginning in February 2027. Covering nearly 1,960 hectares, the airport ...</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>## [https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm](https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm)
-### Document Overview
-This article reports on the commencement and investment policy of Gia Binh International Airport in Bac Ninh, a dual-use facility expected to handle 30-50 million passengers annually.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Construction of the Gia Binh International Airport project... kicked off in northern Bac Ninh province on December 10 last year, a dual-use facility designed to become a major aviation hub in northern Viet Nam. The airport will be completed by the end of 2026, with trial operations beginning in February 2027. During 2021-2030 period, the airport will feature two runways with capacity to handle about 30 million passengers and 1.6 million tons of cargo annually.
-answer: 1. Dự án sân bay quốc tế Gia Bình tại tỉnh Bắc Ninh đã chính thức khởi công và được quy hoạch trở thành trung tâm hàng không lưỡng dụng trọng điểm tại miền Bắc Việt Nam với diện tích gần 1.960 ha. 2. Dự án dự kiến hoàn thành vào cuối năm 2026, bắt đầu vận hành thử nghiệm từ tháng 2/2027, với công suất thiết kế giai đoạn 2021-2030 đạt 30 triệu hành khách và 1,6 triệu tấn hàng hóa mỗi năm. 3. Công trình này được kỳ vọng sẽ tạo động lực phát triển cho các ngành công nghiệp, logistics và du lịch, đồng thời kết nối chặt chẽ với sân bay quốc tế Nội Bài.
-Source: [en.baochinhphu.vn](https://en.baochinhphu.vn/viet-nam-approves-investment-policy-for-gia-binh-international-airport-111251211145037895.htm)</t>
+          <t>[Transport &amp; Infrastructure] Viet Nam approves investment policy for Gia Binh International Airport — The airport will be completed by the end of 2026, with trial operations beginning in February 2027. Covering nearly 1,960 hectares, the airport ...</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5819,35 +4684,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>## [https://nghien-cuu.github.io/public-investment_airports/](https://nghien-cuu.github.io/public-investment_airports/)
-### Document Overview
-This page provides a summary of major airport infrastructure projects in Vietnam for 2025, based on Ministry of Transport data analyzed by Mirae Asset Securities.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025. Source: Mirae Asset Securities Vietnam Analysis - Compiled from Ministry of Transport and National Airport Network Master Plan.
-answer: 2025년 기준 베트남의 주요 공항 건설 프로젝트, 입찰 진행 현황 및 신규 전략 제안에 관한 통합 데이터를 담고 있습니다. 미래에셋증권 베트남(Mirae Asset Securities Vietnam)이 베트남 교통부와 국가 공항망 마스터플랜을 바탕으로 분석 및 정리한 자료입니다.
-Source: [nghien-cuu.github.io](https://nghien-cuu.github.io/public-investment_airports/)</t>
+          <t>[Transport &amp; Infrastructure] Planning &amp; Bidding Vietnam Aviation Infrastructure — Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>## [https://nghien-cuu.github.io/public-investment_airports/](https://nghien-cuu.github.io/public-investment_airports/)
-### Document Overview
-This page provides a high-level summary of airport infrastructure projects in Vietnam for 2025, based on Ministry of Transport and Master Plan data analyzed by Mirae Asset Securities.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025. Source: Mirae Asset Securities Vietnam Analysis - Compiled from Ministry of Transport and National Airport Network Master Plan.
-answer: As of 2025, Mirae Asset Securities Vietnam has compiled consolidated data regarding major airport projects within the country, including those currently under construction and in active bidding stages. The report further details new strategic proposals for the aviation sector based on the National Airport Network Master Plan and Ministry of Transport data. This information serves as a key resource for tracking public investment and infrastructure development in Vietnam's transport sector.
-Source: [nghien-cuu.github.io](https://nghien-cuu.github.io/public-investment_airports/)</t>
+          <t>[Transport &amp; Infrastructure] Planning &amp; Bidding Vietnam Aviation Infrastructure — Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>## [https://nghien-cuu.github.io/public-investment_airports/](https://nghien-cuu.github.io/public-investment_airports/)
-### Document Overview
-Trang web cung cấp dữ liệu tổng hợp về các dự án hạ tầng hàng không Việt Nam năm 2025 từ nguồn phân tích của Mirae Asset Securities.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025. Source: Mirae Asset Securities Vietnam Analysis - Compiled from Ministry of Transport and National Airport Network Master Plan.
-answer: Tài liệu này tổng hợp dữ liệu về các dự án sân bay trọng điểm tại Việt Nam tính đến năm 2025, bao gồm các công trình đang xây dựng, các quy trình đấu thầu đang diễn ra và các đề xuất chiến lược mới. Thông tin được phân tích bởi Mirae Asset Securities Vietnam dựa trên số liệu từ Bộ Giao thông Vận tải và Quy hoạch tổng thể mạng lưới cảng hàng không toàn quốc.
-Source: [nghien-cuu.github.io](https://nghien-cuu.github.io/public-investment_airports/)</t>
+          <t>[Transport &amp; Infrastructure] Planning &amp; Bidding Vietnam Aviation Infrastructure — Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5901,35 +4748,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/](https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/)
-### Document Overview
-Vietnam has operationalized its first domestic carbon trading market via Decree 29/2026, establishing a pilot GHG quota system for heavy industries like power and cement to meet its 2030 and 2050 climate goals.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-EV-2030
-verbatim: Vietnam has launched its first carbon trading exchange, quickly establishing an operational framework and piloting a greenhouse gas (GHG) quota allocation for 2025–2026. Decree No. 29/2026/ND-CP (Decree 29) establishes the country’s first operational domestic carbon trading exchange framework, integrating emission quota trading into Vietnam’s securities market infrastructure. The government has authorized pilot GHG emission quotas for 2025–2026, covering 34 thermal power plants, 25 iron and steel facilities, and 51 cement plants.
-answer: 베트남 정부는 법령 제29/2026/ND-CP호를 통해 국가 최초의 공식 탄소 거래소 운영 체계를 구축하고, 이를 증권 거래 인프라와 통합하여 본격적인 탄소 시장 가동을 시작했습니다. 이번 조치에 따라 2025~2026년 시범 기간 동안 화력발전소, 철강, 시멘트 등 주요 배출 산업군을 대상으로 온실가스 배출 할당량이 공식 부여됩니다. 이는 2030년 메탄 감축 및 2050년 넷제로 목표 달성을 위한 국가 마스터플랜 VN-EV-2030의 핵심적인 환경·기후 인프라 구축 단계로 평가됩니다.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/)</t>
+          <t>[Environment &amp; Climate] Decree 29/2026: Vietnam Operationalizes Its First Carbon Trading ... — At COP26, the country pledged to reach net-zero emissions by 2050 and reduce methane emissions by 30 percent by 2030 compared to 2020 levels. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/](https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/)
-### Document Overview
-The article details Vietnam's new regulatory framework (Decree 29) for its first carbon trading exchange, including pilot emission quotas for heavy industries for 2025-2026 and the institutional roles of various financial and environmental agencies.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-EV-2030
-verbatim: Vietnam has launched its first carbon trading exchange, quickly establishing an operational framework and piloting a greenhouse gas (GHG) quota allocation for 2025–2026. Decree No. 29/2026/ND-CP (Decree 29) establishes the country’s first operational domestic carbon trading exchange framework, integrating emission quota trading into Vietnam’s securities market infrastructure... the government has authorized pilot GHG emission quotas for 2025–2026, covering 34 thermal power plants, 25 iron and steel facilities, and 51 cement plants.
-answer: Vietnam has officially operationalized its first domestic carbon trading market through Decree No. 29/2026/ND-CP, integrating emission quota trading into the national securities infrastructure. This climate infrastructure initiative establishes a pilot greenhouse gas quota for 2025-2026 targeting 110 facilities across the power, steel, and cement sectors to support the country's goal of reducing emissions by up to 43.5 percent by 2030. The framework assigns specific oversight roles to the Hanoi Stock Exchange for trading and the Vietnam Securities Depository and Clearing Corporation for settlement, marking a shift from policy commitment to regulated market practice.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/)</t>
+          <t>[Environment &amp; Climate] Decree 29/2026: Vietnam Operationalizes Its First Carbon Trading ... — At COP26, the country pledged to reach net-zero emissions by 2050 and reduce methane emissions by 30 percent by 2030 compared to 2020 levels. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/](https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/)
-### Document Overview
-Bài báo phân tích Nghị định 29/2026/NĐ-CP về việc vận hành sàn giao dịch carbon tại Việt Nam, bao gồm cơ cấu thị trường, cơ chế giao dịch và kế hoạch thí điểm phân bổ hạn ngạch khí nhà kính cho các ngành công nghiệp trọng điểm.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam has launched its first carbon trading exchange, quickly establishing an operational framework and piloting a greenhouse gas (GHG) quota allocation for 2025–2026. Decree No. 29/2026/ND-CP (Decree 29) establishes the country’s first operational domestic carbon trading exchange framework, integrating emission quota trading into Vietnam’s securities market infrastructure.
-answer: Việt Nam đã chính thức vận hành sàn giao dịch tín chỉ carbon đầu tiên thông qua Nghị định 29/2026/NĐ-CP, tích hợp việc giao dịch hạn ngạch phát thải vào hạ tầng thị trường chứng khoán quốc gia. Trong giai đoạn thí điểm 2025-2026, Chính phủ đã phân bổ hạn ngạch cho 110 cơ sở thuộc các ngành phát thải cao như nhiệt điện, sắt thép và xi măng nhằm hiện thực hóa cam kết phát thải ròng bằng không vào năm 2050.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/decree-29-2026-vietnam-operationalizes-its-first-carbon-trading-market.html/)</t>
+          <t>[Environment &amp; Climate] Decree 29/2026: Vietnam Operationalizes Its First Carbon Trading ... — At COP26, the country pledged to reach net-zero emissions by 2050 and reduce methane emissions by 30 percent by 2030 compared to 2020 levels. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5983,35 +4812,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>## [https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm](https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm)
-### Document Overview
-The article details Vietnam's comprehensive strategies to achieve its COP26 net-zero commitment by 2050, highlighting specific actions in energy, agriculture, and forestry, as well as the involvement of the private sector and legal frameworks.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-EV-2030
-verbatim: At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050. The Vietnamese Government acted swiftly after COP26. A series of strategic documents and policies were issued, notably the National Climate Change Strategy to 2050, the Implementation Plan for COP26 Outcomes, and new decrees on greenhouse gas reduction and carbon market development. In the energy sector - at the heart of the transition, Vietnam has set forth Power Development Plan VIII, charting a course to gradually reduce coal dependence while scaling up renewable energy, including wind, solar, and biomass.
-answer: 베트남 정부는 COP26에서 선언한 2050년 넷제로(Net-Zero) 목표 달성을 위해 '국가 기후변화 전략 2050'과 '전력개발계획 8(PDP8)' 등 법적 프레임워크를 구축하며 에너지, 농업, 폐기물 등 전 분야에서 녹색 전환을 가속화하고 있습니다. 특히 석탄 의존도를 낮추고 재생 에너지 비중을 확대하는 에너지 전환과 더불어 메탄 배출을 줄이는 저탄소 쌀 재배 모델 도입 및 민간 부문의 참여를 독려하여 기후 위기 대응 역량을 강화하고 있습니다.
-Source: [en.mae.gov.vn](https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm)</t>
+          <t>[Environment &amp; Climate] Fulfilling climate commitments at COP26: Vietnam's comprehensive ... — At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050 - a historic milestone underscoring its ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>## [https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm](https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm)
-### Document Overview
-The article details Vietnam's progress in fulfilling its COP26 climate pledges, specifically its target for net-zero emissions by 2050 through sectoral reforms in energy, agriculture, and forestry.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-EV-2030
-verbatim: At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050... The Vietnamese Government acted swiftly after COP26. A series of strategic documents and policies were issued, notably the National Climate Change Strategy to 2050, the Implementation Plan for COP26 Outcomes, and new decrees on greenhouse gas reduction and carbon market development.
-answer: Vietnam is actively implementing a multi-sectoral strategy to achieve its COP26 commitment of net-zero emissions by 2050 through the National Climate Change Strategy and Power Development Plan VIII. This comprehensive approach includes transitioning to renewable energy, scaling up sustainable low-emission agriculture in the Mekong Delta, and enhancing forestry management through mechanisms like Payment for Forest Environmental Services. The government is also fostering a green economy by integrating circular practices in industry and encouraging private sector investment in rooftop solar and green supply chains.
-Source: [en.mae.gov.vn](https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm)</t>
+          <t>[Environment &amp; Climate] Fulfilling climate commitments at COP26: Vietnam's comprehensive ... — At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050 - a historic milestone underscoring its ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>## [https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm](https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm)
-### Document Overview
-Bài báo phân tích lộ trình của Việt Nam nhằm đạt mục tiêu Net-zero vào năm 2050, nhấn mạnh sự phối hợp liên ngành trong năng lượng, nông nghiệp và lâm nghiệp cùng với sự tham gia của khối doanh nghiệp.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050... In the energy sector - at the heart of the transition, Vietnam has set forth Power Development Plan VIII, charting a course to gradually reduce coal dependence while scaling up renewable energy... The Vietnamese Government acted swiftly after COP26. A series of strategic documents and policies were issued, notably the National Climate Change Strategy to 2050.
-answer: Bài báo tổng kết nỗ lực của Việt Nam trong việc thực hiện cam kết phát thải ròng bằng không (Net-zero) vào năm 2050 thông qua các chiến lược toàn diện như Quy hoạch điện VIII và Chiến lược quốc gia về biến đổi khí hậu. Việt Nam đang đẩy mạnh chuyển đổi năng lượng từ than sang năng lượng tái tạo, áp dụng nông nghiệp phát thải thấp và huy động sự tham gia của cả khối tư nhân lẫn cộng đồng để hiện thực hóa các mục tiêu khí hậu quốc tế.
-Source: [en.mae.gov.vn](https://en.mae.gov.vn/fulfilling-climate-commitments-at-cop26-vietnams-comprehensive-crosssector-and-wholeofsociety-action-9035.htm)</t>
+          <t>[Environment &amp; Climate] Fulfilling climate commitments at COP26: Vietnam's comprehensive ... — At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050 - a historic milestone underscoring its ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -6065,35 +4876,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp](https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp)
-### Document Overview
-This article details Prime Minister Pham Minh Chinh's directive to prioritize the 2050 net-zero emissions goal as a core national mission, focusing on green transition, carbon markets, and renewable energy integration.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-EV-2030
-verbatim: Achieving the net-zero emissions target is both a challenge and an opportunity to develop the country sustainably... affirmed the correctness of Vietnams strong commitments made at COP26 to jointly acting for net-zero emissions by 2050... The Prime Minister required the Steering Committee to thoroughly grasp the viewpoint that climate change adaptation and achieving net-zero emissions are challenges but also opportunities for sustainable national development and building an independent, self-reliant, and integrated economy.
-answer: 베트남 팜 민 찐(Pham Minh Chinh) 총리는 2050년 넷제로(Net-Zero) 목표 달성을 국가의 정치적 임무이자 지속 가능한 발전을 위한 기회로 규정하며, 전 부처에 탄소 배출권 시장 구축과 신재생 에너지 전환 가속화를 지시했습니다. 특히 'VN-EV-2030' 마스터플랜과 연계된 전기차 등 녹색 교통 인프라 확대 및 철강·시멘트 등 주요 산업의 온실가스 배출 할당량 시범 배정 등을 통해 기후 위기 대응을 국가 경제의 신성장 동력으로 활용할 방침입니다.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp)</t>
+          <t>[Environment &amp; Climate] Achieving net-zero emissions by 2050 is a political mission of Vietnam — Bringing Vietnam to net-zero emissions by 2050 is not merely a promise but a commitment to action - a political mission of the nation and a ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp](https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp)
-### Document Overview
-Prime Minister Pham Minh Chinh chaired the 6th meeting of the National Steering Committee for COP26, outlining Vietnam's strategic roadmap for achieving net-zero emissions by 2050 through green energy transition, transport electrification, and carbon market development.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-EV-2030
-verbatim: Bringing Vietnam to net-zero emissions by 2050 is not merely a promise but a commitment to action - a political mission of the nation... Provincial and municipal Peoples Committees shall take the lead in developing public transport systems powered by electricity and green energy, and in formulating and implementing policies to support the transition of vehicles to clean and green energy sources... He also requested accelerating tasks related to transport electrification and the development of green transport and green infrastructure.
-answer: Vietnam's Prime Minister has declared achieving net-zero emissions by 2050 as a critical national political mission, emphasizing the urgent transition from policy commitments to concrete action through green development and institutional reform. As part of broader environmental and climate infrastructure goals, the government is accelerating transport electrification and green infrastructure development, including the expansion of electric public transport and support for the vehicle transition to clean energy. This initiative aligns with sector-specific mandates for emission quota piloting in heavy industries and the mobilization of international finance through frameworks like the Just Energy Transition Partnership (JETP).
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp)</t>
+          <t>[Environment &amp; Climate] Achieving net-zero emissions by 2050 is a political mission of Vietnam — Bringing Vietnam to net-zero emissions by 2050 is not merely a promise but a commitment to action - a political mission of the nation and a ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp](https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp)
-### Document Overview
-The article reports on PM Pham Minh Chinh's direction during the 6th meeting of the National Steering Committee for COP26, emphasizing the goal of reaching net-zero emissions by 2050 through green energy transition, carbon credit markets, and international cooperation.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Concluding the sixth meeting of the National Steering Committee for implementing Vietnams commitments at the UN Climate Change Conference in Glasgow (COP26), Chinh, who is also head of the Steering Committee, affirmed the correctness of Vietnams strong commitments made at COP26 to jointly acting for net-zero emissions by 2050... The Prime Minister directed efforts to accelerate preparation for the operation of the domestic carbon market and the exchange of emission reduction results and carbon credits... Provincial and municipal Peoples Committees shall take the lead in developing public transport systems powered by electricity and green energy, and in formulating and implementing policies to support the transition of vehicles to clean and green energy sources.
-answer: Thủ tướng Phạm Minh Chính khẳng định mục tiêu phát thải ròng bằng 0 vào năm 2050 là nhiệm vụ chính trị trọng tâm, đòi hỏi Việt Nam phải chuyển đổi mạnh mẽ sang nền kinh tế xanh và tuần hoàn. Chính phủ yêu cầu đẩy nhanh việc phát triển hạ tầng giao thông xanh, hệ thống năng lượng tái tạo, đồng thời sớm vận hành thị trường carbon trong nước để thu hút nguồn vốn đầu tư quốc tế. Đây được xem là vừa là thách thức vừa là cơ hội để xây dựng một nền kinh tế độc lập, tự chủ và hội nhập sâu rộng.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/achieving-net-zero-emissions-by-2050-is-a-political-mission-of-vietnam-pm-post335977.vnp)</t>
+          <t>[Environment &amp; Climate] Achieving net-zero emissions by 2050 is a political mission of Vietnam — Bringing Vietnam to net-zero emissions by 2050 is not merely a promise but a commitment to action - a political mission of the nation and a ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -6143,35 +4936,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>## [https://climateactiontracker.org/countries/vietnam/policies-action/](https://climateactiontracker.org/countries/vietnam/policies-action/)
-### Document Overview
-This page provides a comprehensive analysis of Vietnam's climate policies, highlighting its 2050 net-zero target, the 2025 update to the Power Development Plan 8 (PDP8), and the upcoming emissions trading scheme. It evaluates Vietnam's current actions as 'Critically Insufficient' against a 1.5C warming limit due to continued reliance on fossil fuels despite rapid renewable growth.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-CARBON-2050
-verbatim: The architecture of Viet Nams climate action framework to 2050 is articulated in the National Climate Change Strategy to 2050, setting the goal of reaching net zero by 2050. ... In May 2025, Viet Nam adopted the updated version of PDP8 (2025 PDP8), which is more ambitious and diversified than its predecessor. ... Viet Nam is undertaking a significant step in its climate policy with the launch of a pilot emissions trading scheme (ETS) in August 2025.
-answer: 베트남은 2050년 탄소중립 달성을 목표로 하는 '2050 국가 기후변화 전략(VN-CARBON-2050)'을 수립하고, 이를 실행하기 위해 2025년 개정된 제8차 전력개발계획(PDP8)과 탄소배출권 거래제(ETS) 시범 운영 등 강력한 환경·에너지 인프라 정책을 추진하고 있습니다. 특히 석탄 화력 발전의 단계적 폐지와 재생에너지 비중 확대, 전력망 현대화에 집중하고 있으나, 급격한 전력 수요 증가와 투자 재원 확보는 여전히 해결해야 할 과제로 분석됩니다.
-Source: [climateactiontracker.org](https://climateactiontracker.org/countries/vietnam/policies-action/)</t>
+          <t>[Environment &amp; Climate] Viet Nam - Policies &amp; action | Climate Action Tracker — Viet Nam's emissions under current policies will reach around 686–722 MtCO2e in 2030 (excl. LULUCF) whereas a 1.5˚C fair share pathway is 344 MtCO2e in 2030. (관련: VN-CARBON-2050)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>## [https://climateactiontracker.org/countries/vietnam/policies-action/](https://climateactiontracker.org/countries/vietnam/policies-action/)
-### Document Overview
-The page analyzes Vietnam's climate policies, highlighting the 2025 update to Power Development Plan 8 (PDP8) and the commitment to reach net-zero emissions by 2050 through a transition from coal to renewable energy.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-CARBON-2050
-verbatim: The architecture of Viet Nams climate action framework to 2050 is articulated in the National Climate Change Strategy to 2050, setting the goal of reaching net zero by 2050. Since COP27, important policy documents covering the energy sector have emerged, including the long-awaited Power Development Plan 8 (PDP8) and the Master Plan for National Energy, building on the foundations of the Climate Change Strategy. In May 2025, Viet Nam adopted the updated version of PDP8 (2025 PDP8), which is more ambitious and diversified than its predecessor. The strengthened coal phase-out and sharp scaling up of solar and offshore wind are welcome steps toward aligning with Viet Nams net-zero by 2050 pledge.
-answer: Vietnam is accelerating its 'VN-CARBON-2050' goals through the National Climate Change Strategy to 2050 and the newly updated 2025 Power Development Plan 8 (PDP8), which mandates a full coal phase-out by 2050. This infrastructure shift involves a massive scaling of renewable capacity, targeting up to 300 GW of solar and 139 GW of offshore wind by mid-century, alongside the launch of a pilot domestic emissions trading scheme in August 2025. To support this transition, the government is prioritizing grid modernization and has mobilized approximately USD 7 billion via the Just Energy Transition Partnership (JETP) for transmission and hydropower projects.
-Source: [climateactiontracker.org](https://climateactiontracker.org/countries/vietnam/policies-action/)</t>
+          <t>[Environment &amp; Climate] Viet Nam - Policies &amp; action | Climate Action Tracker — Viet Nam's emissions under current policies will reach around 686–722 MtCO2e in 2030 (excl. LULUCF) whereas a 1.5˚C fair share pathway is 344 MtCO2e in 2030. (Related: VN-CARBON-2050)</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>## [https://climateactiontracker.org/countries/vietnam/policies-action/](https://climateactiontracker.org/countries/vietnam/policies-action/)
-### Document Overview
-This report analyzes Vietnam's climate and energy policies, specifically the 2025 update to Power Development Plan 8 (PDP8), infrastructure investments in the power grid, and the transition toward net-zero emissions by 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Viet Nam's power sector is undergoing a transition, balancing rapid renewable growth with continued reliance on fossil fuels. ... The 2025 amendment [to PDP8] increases the near-term ambition, with the 2030 target to 40–47% (excluding large hydro). ... The amendment places strong emphasis on addressing grid bottlenecks that have hindered renewable deployment in recent years. The government is prioritising investment in transmission and distribution, including new 500 kV and 220 kV lines, HVDC converter stations, and expanded energy storage.
-answer: Việt Nam đang thực hiện quá trình chuyển đổi năng lượng mạnh mẽ thông qua Quy hoạch điện VIII (PDP8) cập nhật năm 2025, tập trung vào việc mở rộng quy mô năng lượng tái tạo và hiện đại hóa hệ thống lưới điện truyền tải (như đường dây 500kV, 220kV và trạm biến áp HVDC). Mặc dù có những bước tiến lớn trong lĩnh vực điện mặt trời và điện gió, hạ tầng năng lượng vẫn đối mặt với thách thức từ việc phụ thuộc vào than và khí đốt trong ngắn hạn cũng như nhu cầu vốn đầu tư khổng lồ để đạt mục tiêu phát thải ròng bằng không vào năm 2050.
-Source: [climateactiontracker.org](https://climateactiontracker.org/countries/vietnam/policies-action/)</t>
+          <t>[Environment &amp; Climate] Viet Nam - Policies &amp; action | Climate Action Tracker — Viet Nam's emissions under current policies will reach around 686–722 MtCO2e in 2030 (excl. LULUCF) whereas a 1.5˚C fair share pathway is 344 MtCO2e in 2030. (Liên quan: VN-CARBON-2050)</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6225,37 +5000,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>## [https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/](https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/)
-### Document Overview
-The article details the legal framework and roadmap for Vietnam's domestic carbon exchange market, established under Decree No. 29/2026/ND-CP to support the country's Net-Zero 2050 goal.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: N/A
-verbatim: The government issued Decree No. 29/2026/ND-CP on January 19 on the domestic carbon exchange, in the context of the Prime Minister approving the Scheme on the “Establishment and Development of the Carbon Market in Vietnam” under Decision No. 232/QD-TTg issued in January 2025. The Scheme clearly defines the viewpoints, objectives, roadmap, and tasks and solutions for forming and developing Vietnam’s carbon market. It aims to promote low-emission technologies, contribute to building a low-carbon economy, and achieve the target of net-zero emissions by 2050.
-answer: 베트남 정부는 2050년 탄소중립 목표 달성을 위해 국내 탄소 거래소 설립에 관한 시행령 제29/2026/ND-CP호를 공표하고, 2028년까지 시범 운영을 거쳐 탄소 시장을 본격적으로 개발할 계획입니다. 이번 시행령은 탄소 배출권 거래를 위한 법적 근거를 마련하여 저탄소 경제 전환을 촉진하고, 기업들이 청정 기술에 투자하도록 유도하여 약 4억 달러에서 8억 달러의 준수 비용 절감 효과를 가져올 것으로 기대됩니다.
-Source: [netzero.vn](https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/)</t>
+          <t>[Environment &amp; Climate] Roadmap for Vietnam's carbon exchange | NetZero.VN — To realize its net-zero by 2050 target, Vietnam is currently promoting a wide range of emission reduction projects across industrial production, ...</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>## [https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/](https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/)
-### Document Overview
-This article details the legal framework and roadmap for Vietnam's domestic carbon exchange, established via Decree No. 29/2026/ND-CP, to support the nation's 2050 net-zero goals.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: N/A
-verbatim: The government issued Decree No. 29/2026/ND-CP on January 19 on the domestic carbon exchange... The Scheme clearly defines the viewpoints, objectives, roadmap, and tasks and solutions for forming and developing Vietnam’s carbon market... It aims to promote low-emission technologies, contribute to building a low-carbon economy, and achieve the target of net-zero emissions by 2050.
-answer: The Vietnamese government has issued Decree No. 29/2026/ND-CP and Decision No. 232/QD-TTg to establish and develop a domestic carbon exchange, which will undergo pilot operations through 2028 and official operation starting in 2029. This environmental infrastructure initiative aims to promote a low-carbon economy and mobilize green financial resources to help the country achieve its net-zero emissions target by 2050. The exchange will provide a centralized platform for trading greenhouse gas emission allowances and carbon credits, incentivizing businesses to invest in clean technologies and nature-based solutions.
-Source: [netzero.vn](https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/)</t>
+          <t>[Environment &amp; Climate] Roadmap for Vietnam's carbon exchange | NetZero.VN — To realize its net-zero by 2050 target, Vietnam is currently promoting a wide range of emission reduction projects across industrial production, ...</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>## [https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/](https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/)
-### Document Overview
-The article details Vietnam's roadmap for establishing a domestic carbon exchange under Decree No. 29/2026/ND-CP, highlighting its role in achieving net-zero by 2050 and supporting corporate green transitions.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The government issued Decree No. 29/2026/ND-CP on January 19 on the domestic carbon exchange, in the context of the Prime Minister approving the Scheme on the “Establishment and Development of the Carbon Market in Vietnam” under Decision No. 232/QD-TTg issued in January 2025. ... The Scheme clearly defines the viewpoints, objectives, roadmap, and tasks and solutions for forming and developing Vietnam’s carbon market. ... The Decision specifies that during the pilot operation of the domestic carbon exchange through December 31, 2028...
-answer: 1. Chính phủ Việt Nam đã ban hành Nghị định số 29/2026/NĐ-CP và Quyết định số 232/QĐ-TTg nhằm thiết lập và phát triển thị trường tín chỉ carbon trong nước, hướng tới mục tiêu phát thải ròng bằng 0 vào năm 2050.
-2. Lộ trình triển khai bao gồm giai đoạn vận hành thí điểm sàn giao dịch tín chỉ carbon đến hết ngày 31/12/2028 và bắt đầu thu phí dịch vụ từ ngày 01/01/2029 thông qua các cơ quan như Sở Giao dịch Chứng khoán Hà Nội và Tổng công ty Lưu ký và Bù trừ Chứng khoán Việt Nam.
-3. Việc hình thành sàn giao dịch này không chỉ giúp hoàn thiện hạ tầng pháp lý về môi trường mà còn tạo ra nguồn tài chính xanh, giúp doanh nghiệp tiết kiệm chi phí tuân thủ từ 400 đến 800 triệu USD và thu hút vốn đầu tư quốc tế.
-Source: [netzero.vn](https://netzero.vn/en/roadmap-for-vietnams-carbon-exchange/)</t>
+          <t>[Environment &amp; Climate] Roadmap for Vietnam's carbon exchange | NetZero.VN — To realize its net-zero by 2050 target, Vietnam is currently promoting a wide range of emission reduction projects across industrial production, ...</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -6305,35 +5060,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>## [https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero](https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero)
-### Document Overview
-This article details Internews’ Earth Journalism Network (EJN) project aimed at improving Vietnam's media coverage of its 2050 Net Zero goals and renewable energy transition.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-CARBON-2050
-verbatim: the government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. ... EJN has now implemented a follow-up phase of the project from August 2024 to June 2025, to continue strengthening the Renewable Energy (RE) knowledge and reporting capacity of journalists in Vietnam. ... The goals of this project are to: Identify the challenges and needs of journalists in Vietnam when reporting on energy transition and renewable energy; Strengthen the knowledge and skills of journalists covering these topics in Vietnam; Improve the quality and quantity of energy reporting in Vietnam.
-answer: 베트남 정부의 2050년 탄소중립 목표(VN-CARBON-2050) 달성을 지원하기 위해, '지구 저널리즘 네트워크(EJN)'는 현지 언론인들의 에너지 전환 및 재생 에너지 보도 역량을 강화하는 프로젝트를 추진하고 있습니다. 2024년부터 2025년까지 진행되는 이번 2단계 사업은 미디어 트레이닝과 취재 지원금을 통해 저널리스트들의 기술적 이해도를 높이고, 대중의 기후 변화 인식을 확산시키는 데 중점을 둡니다. 이를 통해 베트남의 환경 및 기후 섹터에서 보다 정확하고 심도 있는 에너지 정책 보도가 이루어질 것으로 기대됩니다.
-Source: [earthjournalism.net](https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero)</t>
+          <t>[Environment &amp; Climate] Reporting on Vietnam's Pathways to Net Zero — The government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. (관련: VN-CARBON-2050)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>## [https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero](https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero)
-### Document Overview
-The page details Internews' Earth Journalism Network project aimed at training Vietnamese journalists to better report on the country's 2050 net-zero goals and renewable energy transition.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-CARBON-2050
-verbatim: In accordance with the Paris Agreement, the government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. The strategy commits Vietnam to cut total emissions from forestry and land use by 70%, and to increase carbon sequestration from forest and land use by 20% by 2030. Vietnam has also set targets to ensure 6.9% of its electricity produced or imported comes from renewable sources by 2025, and 10.7% by 2030. ... Internews’ Earth Journalism Network (EJN) launched Reporting on Vietnam’s Pathways to Net Zero in 2024.
-answer: Vietnam is advancing its VN-CARBON-2050 goals through a National Climate Change Strategy that targets net-zero emissions by 2050, including a 70% reduction in land-use emissions and increasing renewable electricity to 10.7% by 2030. To support this environmental infrastructure transition, Internews’ Earth Journalism Network (EJN) has launched a project (2024–2025) to enhance the capacity of local journalists to report on energy transition and renewable energy technologies. This initiative aims to improve public awareness and media coverage of Vietnam's complex pathways toward decarbonization and sustainable energy development.
-Source: [earthjournalism.net](https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero)</t>
+          <t>[Environment &amp; Climate] Reporting on Vietnam's Pathways to Net Zero — The government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. (Related: VN-CARBON-2050)</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>## [https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero](https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero)
-### Document Overview
-Bài báo giới thiệu về dự án của EJN nhằm hỗ trợ báo chí Việt Nam truyền thông hiệu quả về chuyển dịch năng lượng và lộ trình Net Zero vào năm 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: In accordance with the Paris Agreement, the government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. ... To meet this need, Internews’ Earth Journalism Network (EJN) launched Reporting on Vietnam’s Pathways to Net Zero in 2024. The goals of this project are to: Identify the challenges and needs of journalists in Vietnam when reporting on energy transition and renewable energy; Strengthen the knowledge and skills of journalists covering these topics in Vietnam; Improve the quality and quantity of energy reporting in Vietnam.
-answer: Dự án "Reporting on Vietnam’s Pathways to Net Zero" của EJN được triển khai nhằm nâng cao năng lực và kỹ năng cho các phóng viên Việt Nam trong việc đưa tin về chuyển dịch năng lượng và hạ tầng năng lượng tái tạo. Dự án hỗ trợ mục tiêu của Chính phủ Việt Nam đạt phát thải ròng bằng 0 vào năm 2050 thông qua các hoạt động đào tạo, cấp ngân sách sản xuất tin bài và xây dựng mạng lưới chuyên gia. Thông qua đó, chương trình kỳ vọng sẽ cải thiện chất lượng truyền thông, giúp cộng đồng hiểu rõ hơn về lộ trình năng lượng sạch và các chính sách khí hậu của quốc gia.
-Source: [earthjournalism.net](https://earthjournalism.net/what-we-do/projects/reporting-on-vietnams-pathways-to-net-zero)</t>
+          <t>[Environment &amp; Climate] Reporting on Vietnam's Pathways to Net Zero — The government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. (Liên quan: VN-CARBON-2050)</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -6387,35 +5124,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>## [https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/](https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/)
-### Document Overview
-This article outlines a BloombergNEF report stating that Vietnam's path to net-zero by 2050 requires $2.4 trillion in investment, primarily driven by rapid solar, wind, and EV adoption.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: N/A
-verbatim: Vietnam can still fulfill its goal of reaching net-zero emissions by 2050 and help limit global warming to well below 2C. But doing so rests on a rapid scale-up of clean power, electric vehicles and, to a lesser extent, carbon capture and storage technology, according to a new report published today by BloombergNEF, Net-Zero Transition: Opportunities for Vietnam. ... Reaching net-zero emissions by mid-century requires a rapid ramp-up in investment in both energy demand and supply. Totaling $2.4 trillion across 2024 to 2050 in the Net Zero Scenario.
-answer: 베트남이 2050년 넷제로(Net-Zero) 목표를 달성하기 위해서는 2050년까지 약 2조 4천억 달러의 투자가 필요하며, 이는 주로 청정 전력 확충과 전기차 보급, 탄소 포집 기술에 집중되어야 합니다. 특히 블룸버그NEF 보고서는 태양광과 풍력 발전이 이번 10년 내 탄소 배출 감축의 57%를 담당할 것으로 분석하며, 이는 베트남의 제8차 국가 전력개발계획(PDP VIII)보다 훨씬 공격적인 재생에너지 확대를 제안하고 있습니다. 이러한 전환은 글로벌 기업들의 녹색 전력 수요를 충족시키고 베트남을 지속 가능한 제조 기지로 자리매김하게 할 다조 달러 규모의 경제적 기회로 평가됩니다.
-Source: [about.bnef.com](https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/)</t>
+          <t>[Environment &amp; Climate] Vietnam's 2050 Net-Zero Target Represents a $2.4 Trillion Opportunity — In this net-zero pathway, three drivers account for 78% of Vietnam's emissions abatement through to mid-century: clean power, carbon capture and ...</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>## [https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/](https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/)
-### Document Overview
-The article details a BloombergNEF report highlighting that Vietnam requires $2.4 trillion in investment to reach its 2050 net-zero target through rapid deployment of clean energy and electrification.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: N/A
-verbatim: Vietnam can still fulfill its goal of reaching net-zero emissions by 2050 and help limit global warming to well below 2C. But doing so rests on a rapid scale-up of clean power, electric vehicles and, to a lesser extent, carbon capture and storage technology, according to a new report published today by BloombergNEF... Reaching net-zero emissions by mid-century requires a rapid ramp-up in investment in both energy demand and supply. Totaling $2.4 trillion across 2024 to 2050 in the Net Zero Scenario.
-answer: Vietnam's pursuit of its 2050 net-zero emissions target presents a $2.4 trillion investment opportunity, primarily driven by a massive scale-up in solar and wind power, electric vehicles, and carbon capture technology. This transition requires decarbonizing the power sector to peak emissions by 2026, necessitating an infrastructure shift that favors renewables and energy storage over traditional gas-fired generation.
-Source: [about.bnef.com](https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/)</t>
+          <t>[Environment &amp; Climate] Vietnam's 2050 Net-Zero Target Represents a $2.4 Trillion Opportunity — In this net-zero pathway, three drivers account for 78% of Vietnam's emissions abatement through to mid-century: clean power, carbon capture and ...</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>## [https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/](https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/)
-### Document Overview
-The article details a $2.4 trillion investment roadmap for Vietnam to reach net-zero emissions by 2050, highlighting the necessity of clean power, electrification, and CCS technology.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam can still fulfill its goal of reaching net-zero emissions by 2050 and help limit global warming to well below 2C. But doing so rests on a rapid scale-up of clean power, electric vehicles and, to a lesser extent, carbon capture and storage technology... More than $2.4 trillion in investment and spending is required by 2050 in a net-zero pathway, 54% more than in an economics-led transition.
-answer: Báo cáo của BloombergNEF cho biết Việt Nam cần huy động khoảng 2,4 nghìn tỷ USD đầu tư từ nay đến năm 2050 để đạt mục tiêu phát thải ròng bằng không (net-zero), tập trung trọng điểm vào việc mở rộng quy mô năng lượng tái tạo, xe điện và công nghệ thu giữ carbon. Lộ trình này đòi hỏi công suất điện mặt trời và điện gió phải tăng trưởng đột phá, đóng góp tới 57% lượng khí thải cắt giảm được trong thập kỷ này để thay thế dần năng lượng hóa thạch.
-Source: [about.bnef.com](https://about.bnef.com/insights/clean-energy/vietnams-2050-net-zero-target-represents-a-2-4-trillion-opportunity-bloombergnef/)</t>
+          <t>[Environment &amp; Climate] Vietnam's 2050 Net-Zero Target Represents a $2.4 Trillion Opportunity — In this net-zero pathway, three drivers account for 78% of Vietnam's emissions abatement through to mid-century: clean power, carbon capture and ...</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -6469,35 +5188,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=mEq68PU4JbM](https://www.youtube.com/watch?v=mEq68PU4JbM)
-### Document Overview
-This video report covers Vietnam's fundamental economic shift toward green growth following its COP26 commitment to achieve net-zero emissions by 2050.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-EV-2030
-verbatim: Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic trajectory, moving from ...
-answer: 베트남은 COP26에서 발표한 2050년 넷제로(탄소중립) 달성 목표를 위해 경제 구조를 녹색 성장으로 전면 전환하고 있습니다. 특히 환경 및 기후 섹터의 VN-EV-2030 마스터플랜과 연계하여 지속 가능한 경제 궤도로의 근본적인 변화를 추진 중입니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=mEq68PU4JbM)</t>
+          <t>[Environment &amp; Climate] Việt Nam's shift to green growth | Vietnam Today - YouTube — Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=mEq68PU4JbM](https://www.youtube.com/watch?v=mEq68PU4JbM)
-### Document Overview
-The page discusses Vietnam's economic shift towards green growth and net-zero emissions by 2050 following COP26 commitments.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-EV-2030
-verbatim: Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic trajectory, moving from ...
-answer: Vietnam is undergoing a fundamental economic transformation driven by its COP26 commitment to reach net-zero emissions by 2050. This shift focuses on green growth and sustainable infrastructure development to align with environmental goals such as the VN-EV-2030 plan. The transition marks a move away from traditional economic models toward a climate-resilient and low-carbon trajectory.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=mEq68PU4JbM)</t>
+          <t>[Environment &amp; Climate] Việt Nam's shift to green growth | Vietnam Today - YouTube — Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=mEq68PU4JbM](https://www.youtube.com/watch?v=mEq68PU4JbM)
-### Document Overview
-Nội dung đề cập đến quá trình chuyển dịch kinh tế của Việt Nam sang hướng tăng trưởng xanh sau cam kết Net Zero tại COP26.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic trajectory, moving from ...
-answer: Video thảo luận về cam kết của Việt Nam tại COP26 trong việc đạt mức phát thải ròng bằng '0' vào năm 2050, dẫn đến sự thay đổi căn bản trong quỹ đạo phát triển kinh tế. Trọng tâm của quá trình này là chuyển đổi từ mô hình kinh tế truyền thống sang tăng trưởng xanh và phát triển hạ tầng bền vững.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=mEq68PU4JbM)</t>
+          <t>[Environment &amp; Climate] Việt Nam's shift to green growth | Vietnam Today - YouTube — Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -6551,36 +5252,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>## [https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html](https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html)
-### Document Overview
-This article outlines Vietnam's strategic commitment to achieving net-zero emissions by 2050, highlighting Prime Minister Pham Minh Chinh's call for institutional improvements, green finance, and technology transfer.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: N/A
-verbatim: Vietnam has defined its target of achieving net-zero emissions by 2050 not as a diplomatic pledge but as an action-driven commitment and a political mission tied to fast, green and sustainable development amid escalating climate risks. ... Prime Minister Pham Minh Chinh reaffirmed that contributing to global climate action is a core mission for Vietnam. ... He outlined five key priorities: improving institutions, mobilizing green finance, accelerating technology transfer and innovation, building smart national governance models and developing human resources for green growth.
-answer: 베트남 정부는 2050년 탄소중립(Net-Zero) 달성을 단순한 외교적 약속이 아닌 국가적 정치 미션으로 규정하고, 녹색 금융 동원 및 에너지 전환을 포함한 5대 핵심 우선순위를 발표했습니다. 이를 위해 국내 탄소 시장 시범 운영, 교통 전기화 가속화, 재생 에너지 확대 등 실질적인 행동 중심의 기후 대응 전략을 강화하고 있습니다.
-Source: [hanoitimes.vn](https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html)</t>
+          <t>[Environment &amp; Climate] Net-zero emissions by 2050: Vietnam's action-driven commitment — The ministry is also preparing Vietnam's updated Nationally Determined Contribution for 2026-2035, known as NDC 3.0, with flexible emissions ...</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>## [https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html](https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html)
-### Document Overview
-This article details Vietnam's updated commitments and multi-sectoral progress toward achieving net-zero emissions by 2050, highlighting specific advancements in renewable energy, electric transportation, and green finance.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: N/A
-verbatim: Vietnam has defined its target of achieving net-zero emissions by 2050 not as a diplomatic pledge but as an action-driven commitment and a political mission tied to fast, green and sustainable development... PM Chinh reaffirmed that contributing to global climate action is a core mission for Vietnam. Green growth is both a development goal and a driving force for fast and sustainable growth.
-answer: Vietnam has reaffirmed its commitment to achieving net-zero emissions by 2050, viewing the target as a mandatory political mission integrated into its national development strategy rather than a mere diplomatic pledge. The government is accelerating infrastructure and policy reforms, including the expansion of green credit to over VND750 trillion ($28.5 billion), the deployment of 270,000 electric vehicles, and the development of renewable energy projects to ensure sustainable economic growth.
-Source: [hanoitimes.vn](https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html)</t>
+          <t>[Environment &amp; Climate] Net-zero emissions by 2050: Vietnam's action-driven commitment — The ministry is also preparing Vietnam's updated Nationally Determined Contribution for 2026-2035, known as NDC 3.0, with flexible emissions ...</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>## [https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html](https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html)
-### Document Overview
-Bài báo phân tích nỗ lực của Việt Nam trong việc thực hiện cam kết Net-Zero vào năm 2050 thông qua cải cách thể chế, phát triển hạ tầng năng lượng xanh và chuyển đổi giao thông điện.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam's Prime Minister Pham Minh Chinh speaks at the meeting on January 14... Vietnam has established a legal framework for direct power purchase agreements... By the end of 2025, outstanding green credit exceeded VND750 trillion... State-owned groups are taking the lead in sustainable energy development... the Vietnam Electricity (EVN) is focusing on expanding transmission infrastructure to unlock capacity for wind and solar power projects, while private corporations such as Vingroup, Vinamilk and TH True Milk are stepping up emissions reduction efforts.
-answer: 1. Bài báo khẳng định cam kết của Việt Nam trong việc đạt phát thải ròng bằng 0 vào năm 2050 thông qua các hành động cụ thể như phát triển hạ tầng năng lượng tái tạo, mở rộng hệ thống truyền tải điện của EVN và thúc đẩy chuyển đổi phương tiện giao thông điện.
-2. Chính phủ đang tập trung tháo gỡ các nút thắt chế định để thu hút đầu tư tư nhân vào đường sắt, đường sắt đô thị, hạ tầng trạm sạc và các công trình xanh nhằm đảm bảo an ninh năng lượng và tăng trưởng bền vững.
-Source: [hanoitimes.vn](https://hanoitimes.vn/net-zero-emissions-by-2050-vietnam-s-action-driven-commitment.961634.html)</t>
+          <t>[Environment &amp; Climate] Net-zero emissions by 2050: Vietnam's action-driven commitment — The ministry is also preparing Vietnam's updated Nationally Determined Contribution for 2026-2035, known as NDC 3.0, with flexible emissions ...</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -6634,26 +5316,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/](https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/)
-### Document Overview
-The provided link leads to a Facebook login wall, preventing the extraction of specific textual details about Mekong River flood and drought forecasts.
-Source: [www.facebook.com](https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/)</t>
+          <t>[Water Resources] ℹ The Mekong Flood and Drought Forecast ... — #Laos is currently experiencing significant flooding due to rising water levels in the #MekongRiver and its tributaries, exacerbated by ... (관련: VN-WAT-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/](https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/)
-### Document Overview
-The provided URL leads to a Facebook login page, preventing access to the specific content regarding the Mekong Flood and Drought Forecast.
-Source: [www.facebook.com](https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/)</t>
+          <t>[Water Resources] ℹ The Mekong Flood and Drought Forecast ... — #Laos is currently experiencing significant flooding due to rising water levels in the #MekongRiver and its tributaries, exacerbated by ... (Related: VN-WAT-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/](https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/)
-### Document Overview
-Trang web là một bài đăng trên Facebook của MRC Mekong nhưng không thể truy cập nội dung do rào cản đăng nhập.
-Source: [www.facebook.com](https://www.facebook.com/mrcmekong/posts/%E2%84%B9-%F0%9D%90%93%F0%9D%90%A1%F0%9D%90%9E-%F0%9D%90%8C%F0%9D%90%9E%F0%9D%90%A4%F0%9D%90%A8%F0%9D%90%A7%F0%9D%90%A0-%F0%9D%90%85%F0%9D%90%A5%F0%9D%90%A8%F0%9D%90%A8%F0%9D%90%9D-%F0%9D%90%9A%F0%9D%90%A7%F0%9D%90%9D-%F0%9D%90%83%F0%9D%90%AB%F0%9D%90%A8%F0%9D%90%AE%F0%9D%90%A0%F0%9D%90%A1%F0%9D%90%AD-%F0%9D%90%85%F0%9D%90%A8%F0%9D%90%AB%F0%9D%90%9E%F0%9D%90%9C%F0%9D%90%9A%F0%9D%90%AC%F0%9D%90%AD-%F0%9D%97%A7%F0%9D%97%A9-%F0%9D%97%BC%F0%9D%97%BB-%F0%9D%9F%AD%F0%9D%9F%AC-%F0%9D%97%A0%F0%9D%97%AE%F0%9D%97%BF%F0%9D%97%B0%F0%9D%97%B5-%F0%9D%9F%AE%F0%9D%9F%AC%F0%9D%9F%AE%F0%9D%9F%B2-please-click-on-the-/1373279351510102/)</t>
+          <t>[Water Resources] ℹ The Mekong Flood and Drought Forecast ... — #Laos is currently experiencing significant flooding due to rising water levels in the #MekongRiver and its tributaries, exacerbated by ... (Liên quan: VN-WAT-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -6707,35 +5380,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>## [https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon](https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon)
-### Document Overview
-This article analyzes how Vietnam's rapid economic development and climate change, exacerbated by hydropower dams and land-use changes, are increasing catastrophic flood risks. It advocates for better risk awareness and actuarial solutions to protect Vietnam's growth and infrastructure.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Another major risk factor exists in the form of hydropower, which influences flood risk through sediment trapping and flow changes. To counteract natural subsidence and erosion, delta land elevation and riverbanks require sediment delivery for replenishment, but dams prevent this process from happening. The Hoa Binh Dam (built in 1988) is a prime example of this blocking effect, preventing sediment from flowing down the Da River, which is a major tributary that feeds the Red River Delta. In addition to its role in slowly building up flood risk downstream, during the October 2017 tropical depression event, the emergency release of water from Hoa Binh Dam further contributed to exacerbated downstream flooding.
-answer: 베트남의 급격한 경제 성장과 기후 변화가 맞물리며 홍수 위험이 심화되는 가운데, 특히 조밀한 수력 발전 네트워크가 하류의 홍수 리스크를 높이는 주요 요인으로 지목되었습니다. 화빈 댐(Hoa Binh Dam)과 같은 수력 발전 시설들은 퇴적물 이동을 차단해 지반 침하를 가속화할 뿐만 아니라, 비상 방류 시 하류 지역에 심각한 침수 피해를 야기하고 있습니다. 이에 따라 에너지 인프라 운영 및 건설 시 기후 변화에 대응하는 엄격한 거버넌스와 위험 기반의 설계 및 보험 솔루션 도입이 시급한 상황입니다.
-Source: [www.actuaries.asn.au](https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon)</t>
+          <t>[Power &amp; Energy] Floods in Vietnam: Will rising waters tame the Rising Dragon? — Vietnam faces mounting flood risk as climate change, land subsidence, and hydropower infrastructure combine with record typhoon activity.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>## [https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon](https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon)
-### Document Overview
-The article analyzes the escalating flood risks in Vietnam driven by climate change and rapid urbanization, highlighting the 2024 Typhoon Yagi losses and the role of hydropower dams in exacerbating downstream flooding. It advocates for actuarial risk-based pricing and improved government coordination to protect Vietnam's economic progress and manufacturing hubs.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: Another major risk factor exists in the form of hydropower, which influences flood risk through sediment trapping and flow changes. To counteract natural subsidence and erosion, delta land elevation and riverbanks require sediment delivery for replenishment, but dams prevent this process from happening. The Hoa Binh Dam (built in 1988) is a prime example of this blocking effect, preventing sediment from flowing down the Da River, which is a major tributary that feeds the Red River Delta. In addition to its role in slowly building up flood risk downstream, during the October 2017 tropical depression event, the emergency release of water from Hoa Binh Dam further contributed to exacerbated downstream flooding.
-answer: Vietnam's extensive hydropower network, including major infrastructure like the Hoa Binh Dam, is increasingly scrutinized for its role in exacerbating flood risks through sediment trapping and emergency water releases. While these energy projects are central to development, they contribute to land subsidence and riverbank erosion in the Red River and Mekong Deltas by blocking essential sediment flow. Experts emphasize that future energy infrastructure must be integrated with more rigorous flood risk governance to mitigate the 'threat multiplier' effect of climate change.
-Source: [www.actuaries.asn.au](https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon)</t>
+          <t>[Power &amp; Energy] Floods in Vietnam: Will rising waters tame the Rising Dragon? — Vietnam faces mounting flood risk as climate change, land subsidence, and hydropower infrastructure combine with record typhoon activity.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>## [https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon](https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon)
-### Document Overview
-This article evaluates how Vietnam's rapid urbanization and infrastructure development, coupled with climate change factors like La Niña, are exacerbating flood risks and threatening economic progress.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Doi Moi reforms since the 1980s have contributed to rapid economic growth lifting millions out of poverty, but also leading to environmental degradation that makes Vietnam particularly vulnerable to floods, mainly through land use change, subsidence issues and hydropower development... Climate change serves as a threat multiplier in Vietnam through increased rainfall to the region. Sea level rise, together with subsidence, increases inundation risk and other knock-on environmental issues.
-answer: Bài báo phân tích rủi ro lũ lụt ngày càng tăng tại Việt Nam do sự kết hợp giữa biến đổi khí hậu và quá trình phát triển kinh tế nhanh chóng, đặc biệt là hệ quả từ thay đổi mục đích sử dụng đất, sụt lún nền và hệ thống thủy điện dày đặc. Tác giả cảnh báo rằng cơ sở hạ tầng và các trung tâm kinh tế đang đối mặt với hiểm họa thiên tai nghiêm trọng (như bão Yagi và chuỗi lũ lụt năm 2025), đồng thời kêu gọi ngành bảo hiểm và chính phủ cần nâng cao nhận thức về rủi ro để bảo vệ thành quả phát triển bền vững.
-Source: [www.actuaries.asn.au](https://www.actuaries.asn.au/research-analysis/floods-in-vietnam-will-rising-waters-tame-the-rising-dragon)</t>
+          <t>[Power &amp; Energy] Floods in Vietnam: Will rising waters tame the Rising Dragon? — Vietnam faces mounting flood risk as climate change, land subsidence, and hydropower infrastructure combine with record typhoon activity.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6785,17 +5440,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Content not found or crawler failed</t>
+          <t>[Water Resources] [PDF] Cumulative impact dams and climate change on the hydrology of the ... — More than 1,000 hydropower and irrigation reservoirs/ponds have been built in the. Mekong basin, and another 350 hydropower and irrigation dams are proposed. (관련: VN-WAT-2050)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Content not found or crawler failed</t>
+          <t>[Water Resources] [PDF] Cumulative impact dams and climate change on the hydrology of the ... — More than 1,000 hydropower and irrigation reservoirs/ponds have been built in the. Mekong basin, and another 350 hydropower and irrigation dams are proposed. (Related: VN-WAT-2050)</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Content not found or crawler failed</t>
+          <t>[Water Resources] [PDF] Cumulative impact dams and climate change on the hydrology of the ... — More than 1,000 hydropower and irrigation reservoirs/ponds have been built in the. Mekong basin, and another 350 hydropower and irrigation dams are proposed. (Liên quan: VN-WAT-2050)</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6849,17 +5504,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Drought and salinity expected near average levels this dry season</t>
+          <t>[Water Resources] Drought and salinity expected near average levels this dry season — Drought and water shortages during the 2025-2026 dry season are expected to occur mainly in localized areas, while saltwater intrusion in ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Drought and salinity expected near average levels this dry season</t>
+          <t>[Water Resources] Drought and salinity expected near average levels this dry season — Drought and water shortages during the 2025-2026 dry season are expected to occur mainly in localized areas, while saltwater intrusion in ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Drought and salinity expected near average levels this dry season</t>
+          <t>[Water Resources] Drought and salinity expected near average levels this dry season — Drought and water shortages during the 2025-2026 dry season are expected to occur mainly in localized areas, while saltwater intrusion in ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6913,34 +5568,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=l1kgnoGFYRY](https://www.youtube.com/watch?v=l1kgnoGFYRY)
-### Document Overview
-This page is a video broadcast by the Mekong River Commission regarding flood and drought forecasts for January 13, 2026, relevant to regional water resource management.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Water Resources, 관련 마스터플랜: VN-WAT-2050, VN-EV-2030
-verbatim: Mekong Flood and Drought Forecast Channel on 13 January 2026
-Mekong River Commission
-ℹ 𝐓𝐡𝐞 𝐌𝐞𝐤𝐨𝐧𝐠 𝐅𝐥𝐨𝐨𝐝 𝐚𝐧𝐝 𝐃𝐫𝐨𝐮𝐠𝐡𝐭 𝐅𝐨𝐫𝐞𝐜𝐚𝐬𝐭 𝗧𝗩 𝗼𝗻 𝟭𝟯 𝗝𝗮𝗻𝘂𝗮𝗿𝘆 𝟮𝟬𝟮𝟲
-answer: 메콩강 위원회(MRC)는 2026년 1월 13일 기준 메콩강 유역의 홍수 및 가뭄 예보를 발표하며 수자원 관리 현황을 공유했습니다. 본 정보는 베트남 수자원 마스터플랜(VN-WAT-2050) 및 환경 마스터플랜(VN-EV-2030)의 핵심 과제인 기후 변화 대응과 유역 안보 강화를 뒷받침하는 데이터로 활용됩니다. 해당 예보는 베트남을 포함한 하류 국가들의 농업 생산성 보호와 인프라 안정을 위한 통합 수자원 관리 전략의 일환입니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=l1kgnoGFYRY)</t>
+          <t>[Water Resources] Mekong Flood and Drought Forecast Channel on 13 January 2026 — ... Vietnamese) ☀️Drought forecast: Mild drought ... Water levels updates: ⬆️Water levels from Chiang ... (관련: VN-WAT-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=l1kgnoGFYRY](https://www.youtube.com/watch?v=l1kgnoGFYRY)
-### Document Overview
-The provided page content is a generic YouTube footer and metadata skeleton, lacking any substantive information about Vietnam's infrastructure or water resource plans.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=l1kgnoGFYRY)</t>
+          <t>[Water Resources] Mekong Flood and Drought Forecast Channel on 13 January 2026 — ... Vietnamese) ☀️Drought forecast: Mild drought ... Water levels updates: ⬆️Water levels from Chiang ... (Related: VN-WAT-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=l1kgnoGFYRY](https://www.youtube.com/watch?v=l1kgnoGFYRY)
-### Document Overview
-Bản tin video ngày 13/01/2026 của Ủy hội sông Mê Kông về dự báo lũ và hạn hán, cung cấp dữ liệu thủy văn quan trọng cho khu vực hạ lưu sông Mê Kông.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Mekong Flood and Drought Forecast Channel on 13 January 2026. Mekong River Commission. ℹ 𝐓𝐡𝐞 𝐌𝐞𝐤𝐨𝐧𝐠 𝐅𝐥𝐨𝐨𝐝 𝐚𝐧𝐝 𝐃𝐫𝐨𝐮𝐠𝐡𝐭 𝐅𝐨𝐫𝐞𝐜𝐚𝐬𝐭 𝗧𝗩 𝗼𝗻 𝟭𝟯 𝗝𝗮𝗻𝘂𝗮𝗿𝘆 𝟮𝟬𝟮𝟲
-answer: Video cung cấp bản tin dự báo tình hình lũ lụt và hạn hán tại khu vực sông Mê Kông vào ngày 13 tháng 1 năm 2026 từ Ủy hội sông Mê Kông (MRC). Nội dung tập trung vào việc giám sát mực nước và các điều kiện thủy văn, hỗ trợ quản lý tài nguyên nước và giảm nhẹ thiên tai cho các quốc gia trong lưu vực, bao gồm cả Việt Nam.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=l1kgnoGFYRY)</t>
+          <t>[Water Resources] Mekong Flood and Drought Forecast Channel on 13 January 2026 — ... Vietnamese) ☀️Drought forecast: Mild drought ... Water levels updates: ⬆️Water levels from Chiang ... (Liên quan: VN-WAT-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6994,35 +5632,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>## [https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html](https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html)
-### Document Overview
-The article reports on urgent flood mitigation efforts in Vietnam's Mekong Delta due to rising water levels expected to peak between October 8-10, 2025, affecting infrastructure like dikes and roads.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Water Resources, 관련 마스터플랜: VN-EV-2030
-verbatim: Water levels on the Mekong River are rising rapidly and expected to peak in the coming days... In response to the threat of severe flooding, downstream localities are urgently implementing a range of measures to mitigate the impact... Local authorities are currently implementing flood hazard warnings to alert residents and vehicles about deeply inundated areas... Authorities are also tasked with inspecting and ensuring the safety of irrigation works, dikes, disaster prevention infrastructure, and drainage systems.
-answer: 베트남 메콩 델타 지역이 폭풍 '부알로이'와 조수 상승의 영향으로 2025년 10월 중순 정점에 달할 것으로 예상되는 대홍수에 대비해 비상 대응에 나섰습니다. 껀터시와 빈롱성 등 하류 지역은 제방 보수, 홍수 경보 시스템 가동, 배수 인프라 점검 등 수자원 관리 및 재난 방지 인프라(VN-EV-2030 관련 분야)를 강화하며 피해 최소화에 총력을 기울이고 있습니다.
-Source: [en.sggp.org.vn](https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html)</t>
+          <t>[Water Resources] Mekong Delta races to respond to peak flood levels — Water levels on the Mekong River are rising rapidly and expected to peak in the coming days, according to meteorological agencies. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>## [https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html](https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html)
-### Document Overview
-The article reports on urgent flood mitigation efforts in the Mekong Delta as water levels rise due to storm Bualoi and high tides, focusing on dike reinforcement and infrastructure safety.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Water Resources, Related plans: VN-EV-2030
-verbatim: In response to the situation, many localities across the Mekong Delta are actively implementing measures to mitigate damage. In An Thanh Commune, Can Tho City, over the past two days, local forces... have been working together to reinforce and shore up vulnerable sections of river dikes at risk of erosion. ... Authorities are also tasked with inspecting and ensuring the safety of irrigation works, dikes, disaster prevention infrastructure, and drainage systems.
-answer: Vietnam's Mekong Delta region is urgently reinforcing critical water resource infrastructure, including river dikes, irrigation works, and drainage systems, as floodwaters are projected to peak between October 8 and 10, 2025. Local authorities in Can Tho, Dong Thap, and Vinh Long are prioritizing the maintenance of disaster prevention infrastructure and implementing hazard warning systems to align with safety and environmental resilience objectives similar to those found in the VN-EV-2030 framework.
-Source: [en.sggp.org.vn](https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html)</t>
+          <t>[Water Resources] Mekong Delta races to respond to peak flood levels — Water levels on the Mekong River are rising rapidly and expected to peak in the coming days, according to meteorological agencies. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>## [https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html](https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html)
-### Document Overview
-The article reports on the Mekong Delta's urgent responses to rising peak flood levels in October 2025, detailing infrastructure reinforcement and local mitigation efforts.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: In response to the threat of severe flooding, downstream localities are urgently implementing a range of measures to mitigate the impact. Local authorities are currently implementing flood hazard warnings to alert residents and vehicles about deeply inundated areas. Authorities are also tasked with inspecting and ensuring the safety of irrigation works, dikes, disaster prevention infrastructure, and drainage systems.
-answer: Các tỉnh miền Tây đang khẩn trương ứng phó với đợt đỉnh lũ và triều cường dự kiến đạt đỉnh từ ngày 8 đến 10 tháng 10 năm 2025, gây ngập lụt cục bộ tại Cần Thơ và một số tuyến giao thông huyết mạch. Chính quyền các địa phương như Đồng Tháp, Vĩnh Long và Cần Thơ đã triển khai gia cố hệ thống đê bao, kiểm tra các công trình thủy lợi, hạ tầng phòng chống thiên tai và tổ chức di dời dân cư tại các khu vực sạt lở nguy hiểm để bảo vệ an toàn tính mạng và tài sản.
-Source: [en.sggp.org.vn](https://en.sggp.org.vn/mekong-delta-races-to-respond-to-peak-flood-levels-post120837.html)</t>
+          <t>[Water Resources] Mekong Delta races to respond to peak flood levels — Water levels on the Mekong River are rising rapidly and expected to peak in the coming days, according to meteorological agencies. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -7076,35 +5696,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era](https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era)
-### Document Overview
-The article details Ho Chi Minh City's strategic urban development plans for 2050, focusing on digital/green transformation, financial center goals, and a broader 2025 economic performance review of Vietnam.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: Ho Chi Minh City (HCMC) is redefining what it means to be an international metropolis... implementing a multi-polar growth model anchored in five strategic development pillars. These include: Promoting high-tech industries and innovation (such as AI, semiconductors, and big data)... A defining feature of HCMCs development strategy is dual transformation - the integration of digital and green transitions. Positioned as a national case study, the city is aiming to become a mega-city by 2050 and a low-carbon regional hub.
-answer: 호치민시는 2050년까지 메가시티 및 저탄소 지역 허브 도약을 목표로 디지털 전환과 녹색 성장을 통합한 이중 전환(Dual Transformation) 개발 전략을 추진하고 있습니다. 이를 위해 AI·반도체 등 하이테크 산업 육성, 국제금융센터(IFC) 조성, 물류 및 자유무역지대 강화 등 5대 전략적 축을 기반으로 하는 다극형 성장 모델을 구축하여 글로벌 경쟁력을 확보할 계획입니다.
-Source: [vietcetera.com](https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era)</t>
+          <t>[Urban Development] Ho Chi Minh City Charts A New Path For Urban ... — The city is piloting a new approach: integrating digital transformation, green growth, and modern finance to restructure urban space, ...</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era](https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era)
-### Document Overview
-The article details Ho Chi Minh City's strategic shift toward a dual digital and green transformation, alongside broader 2025 economic highlights such as GSM's IPO plans and Vietnam's 8% GDP growth.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: Ho Chi Minh City (HCMC) is redefining what it means to be an international metropolis. ... the city is shifting its focus from mere scale to the quality of growth, emphasizing governance, innovation, connectivity, and livability. To support this shift, HCMC is implementing a multi-polar growth model anchored in five strategic development pillars. ... A defining feature of HCMCs development strategy is dual transformation - the integration of digital and green transitions.
-answer: Ho Chi Minh City is piloting a multi-polar urban development model that integrates digital transformation and green growth to transition into a low-carbon regional hub by 2050. The city's strategy focuses on five pillars, including high-tech innovation, an International Financial Center, and improved logistics, prioritizing quality of growth and institutional governance over physical expansion.
-Source: [vietcetera.com](https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era)</t>
+          <t>[Urban Development] Ho Chi Minh City Charts A New Path For Urban ... — The city is piloting a new approach: integrating digital transformation, green growth, and modern finance to restructure urban space, ...</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era](https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era)
-### Document Overview
-The article details Ho Chi Minh City's strategic shift towards high-tech urban development and a regional financial center, while also covering major 2025 economic milestones including GSM's IPO plans and Vietnam's record GDP growth.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Ho Chi Minh City (HCMC) is redefining what it means to be an international metropolis... implementing a multi-polar growth model anchored in five strategic development pillars... The city is piloting a new approach: integrating digital transformation, green growth, and modern finance to restructure urban space. ... GSM is preparing for an international IPO... Decree No. 306/2025/ND-CP, amending sanctioning regulations in the securities and derivatives markets... The government set a massive public investment target of $34.2 billion.
-answer: Thành phố Hồ Chí Minh đang tiên phong mô hình phát triển đô thị đa cực dựa trên chuyển đổi số và tăng trưởng xanh, đồng thời hướng tới mục tiêu trở thành trung tâm tài chính quốc tế vào năm 2050. Song song đó, hạ tầng kinh tế Việt Nam ghi nhận những bước tiến lớn trong năm 2025 với mức đầu tư công kỷ lục 34,2 tỷ USD, sự bùng nổ của hạ tầng xe điện (GSM) và các cải cách thể chế quan trọng trong lĩnh vực tài chính, chứng khoán.
-Source: [vietcetera.com](https://vietcetera.com/en/ho-chi-minh-city-charts-a-new-path-for-urban-development-in-the-digital-era)</t>
+          <t>[Urban Development] Ho Chi Minh City Charts A New Path For Urban ... — The city is piloting a new approach: integrating digital transformation, green growth, and modern finance to restructure urban space, ...</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -7158,35 +5760,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>## [https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/](https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/)
-### Document Overview
-This article outlines Ho Chi Minh City's 2026-2030 strategic roadmap, focusing on major infrastructure like Metro Line 2, a financial center, and an expanded urban governance model to achieve double-digit growth.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-EV-2030
-verbatim: Ho Chi Minh City has identified three new strategic pillars, comprising the Vietnam International Financial Center in Ho Chi Minh City (VIFC-HCM), urban railways and a Free Trade Zone (FTZ). ... Among the series of key infrastructure projects launched on the morning of January 15, 2026, to celebrate the 14th National Congress of the Communist Party of Vietnam (CPV), the construction of Metro Line No.2 (Ben Thanh – Tham Luong) attracted public attention. ... The city is focusing on key sectors such as finance, high technology, artificial intelligence, smart logistics, renewable energy, and river, coastal, and cultural tourism.
-answer: 호치민시는 두 자릿수 경제 성장을 목표로 도시 철도(메트로 2호선), 국제금융센터(VIFC-HCM), 자유무역지대(FTZ)를 3대 신전략 기둥으로 설정하고 2026년부터 본격적인 인프라 구축에 나섭니다. 특히 VN-EV-2030 마스터플랜의 일환으로 행정 구역 통합을 통해 도시 규모를 3배 확장하고, 링로드·고속도로·메트로를 연계한 대중교통 지향형 개발(TOD) 모델을 통해 동남아시아의 주요 메가시티이자 물류·금융 허브로 도약할 계획입니다.
-Source: [avpi.org.au](https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/)</t>
+          <t>[Transport &amp; Infrastructure] Ho Chi Minh City outlines roadmap of new urban development — To reach double-digit growth, Ho Chi Minh City is adding three new pillars, including VIFC-HCM, urban railways and a Free Trade Zone. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>## [https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/](https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/)
-### Document Overview
-The article details Ho Chi Minh City's strategic roadmap for becoming a regional megacity, highlighting key infrastructure projects like Metro Line No. 2 and the transition toward a growth model driven by technology, finance, and integrated transport networks.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-EV-2030
-verbatim: Ho Chi Minh City has identified three new strategic pillars, comprising the Vietnam International Financial Center in Ho Chi Minh City (VIFC-HCM), urban railways and a Free Trade Zone (FTZ)... the construction of Metro Line No.2 (Ben Thanh – Tham Luong) attracted public attention... The city’s transformation has extended far beyond administrative restructuring, marking a strategic turning point that redefines it as one of Southeast Asia’s largest metropolises and a regional hub for finance, logistics and innovation. An integrated network of ring roads, expressways, railways and inland waterways, linked with international gateway airports such as Tan Son Nhat and Long Thanh, will position the city as a regional infrastructure platform.
-answer: Ho Chi Minh City has launched a major urban development roadmap centered on three strategic pillars: urban railways (including Metro Line No. 2), the Vietnam International Financial Center, and a Free Trade Zone to drive double-digit economic growth. The plan integrates massive transport infrastructure projects such as ring roads, expressways, and connectivity to Long Thanh International Airport to transform the expanded city into a regional megacity hub for logistics and innovation by 2030. This shift emphasizes transit-oriented development (TOD) and maritime economic expansion, aiming to balance high-tech industrial growth with sustainable green urban governance.
-Source: [avpi.org.au](https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/)</t>
+          <t>[Transport &amp; Infrastructure] Ho Chi Minh City outlines roadmap of new urban development — To reach double-digit growth, Ho Chi Minh City is adding three new pillars, including VIFC-HCM, urban railways and a Free Trade Zone. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>## [https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/](https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/)
-### Document Overview
-The article details Ho Chi Minh City's strategic roadmap for economic and urban growth, highlighting new pillars like the International Financial Center and key transport projects like Metro Line No.2.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Ho Chi Minh City has identified three new strategic pillars, comprising the Vietnam International Financial Center in Ho Chi Minh City (VIFC-HCM), urban railways and a Free Trade Zone (FTZ)... The project served as a vivid demonstration that once institutional bottlenecks rooted in outdated mechanisms are removed, the project implementation can be significantly accelerated... Ho Chi Minh City’s transformation has extended far beyond administrative restructuring, marking a strategic turning point that redefines it as one of Southeast Asia’s largest metropolises and a regional hub for finance, logistics and innovation.
-answer: Bài báo phác thảo lộ trình phát triển đô thị mới của TP. Hồ Chí Minh với ba trụ cột chiến lược cốt lõi gồm Trung tâm Tài chính Quốc tế (VIFC-HCM), hệ thống đường sắt đô thị (điển hình là Metro số 2) và Khu thương mại tự do (FTZ). Thành phố đang chuyển đổi sang mô hình tăng trưởng dựa trên sáng tạo và công nghệ, đồng thời đẩy mạnh kết nối hạ tầng vùng thông qua các dự án như đường vành đai, cao tốc và cầu vượt biển Cần Giờ nhằm hướng tới mục tiêu trở thành siêu đô thị thông minh, bền vững và là trung tâm tài chính - logistics hàng đầu Đông Nam Á vào năm 2050.
-Source: [avpi.org.au](https://avpi.org.au/resources/ho-chi-minh-city-outlines-roadmap-of-new-urban-development/)</t>
+          <t>[Transport &amp; Infrastructure] Ho Chi Minh City outlines roadmap of new urban development — To reach double-digit growth, Ho Chi Minh City is adding three new pillars, including VIFC-HCM, urban railways and a Free Trade Zone. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -7240,35 +5824,17 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html](https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html)
-### Document Overview
-Savills Việt Nam report highlights that $49 billion in infrastructure investment will drive Vietnam's urban development and real estate growth over the next decade, focusing on satellite cities and high-tech industrial shifts.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: VN-EV-2030
-verbatim: Infrastructure will be the most critical growth driver for the next decade, according to Savills Việt Nam. Infrastructure investment totalling US$49 billion is being deployed nationwide, including the North-South Expressway, Long Thành International Airport, Ring Road systems, and LNG projects. Once completed, these networks will redefine Việt Nam’s urban landscape, connecting emerging growth hubs and expanding development corridors across secondary cities such as Bình Dương, Đồng Nai, Hải Phòng, and Quảng Ninh. By 2035, Savills forecasts Việt Nam’s GDP to triple its current size, with an average growth rate of 7-8 per cent a year. The urbanisation rate is projected at 50 per cent, equivalent to 51 million urban residents, while the middle class could expand to 75 per cent of the population, driving strong demand across residential, commercial, hospitality, and healthcare sectors.
-answer: 베트남은 VN-EV-2030 등 국가 발전 계획과 맞물려 약 490억 달러 규모의 대규모 인프라 투자를 진행 중이며, 이는 향후 10년 동안 부동산 및 도시 개발의 핵심 동력이 될 전망입니다. 남북 고속도로와 롱타 Thành 국제공항 등 교통망 확충을 통해 빈증, 동나이, 하이퐁 등 위성 도시들이 새로운 성장 거점으로 부상하며 2035년까지 도시화율이 50%에 달할 것으로 예상됩니다. 이러한 인프라 기반의 도시 확장은 중산층 확대와 결합하여 주거, 상업, 의료 및 친환경 부동산 분야에서 강력한 수요를 창출할 것으로 보입니다.
-Source: [vietnamnews.vn](https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html)</t>
+          <t>[Urban Development] Satellite cities to be centres of real estate development for ... — The urbanisation rate is projected at 50 per cent, equivalent to 51 million urban residents, while the middle class could expand to 75 per cent ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html](https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html)
-### Document Overview
-This article discusses Savills Vietnam's forecast for 2025-2035, highlighting how a US$49 billion infrastructure push will transform satellite cities into major real estate hubs.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: VN-EV-2030
-verbatim: Infrastructure investment totalling US$49 billion is being deployed nationwide, including the North-South Expressway, Long Thành International Airport, Ring Road systems, and LNG projects. Together with rapid urbanisation, satellite cities will become the next centres of real estate development, according to Troy Griffiths, Deputy Managing Director of Savills Việt Nam. The 2025-2035 period will mark a new phase of transformation for the Vietnamese economy.
-answer: Vietnam is deploying a massive US$49 billion infrastructure investment program, including the North-South Expressway and Ring Road systems, to drive urban development and connect emerging growth hubs in satellite cities through 2035. This initiative, aligned with broad economic goals like the VN-EV-2030 context, aims to support an urbanization rate of 50% and a tripling of GDP by fostering sustainable, high-tech, and green real estate sectors.
-Source: [vietnamnews.vn](https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html)</t>
+          <t>[Urban Development] Satellite cities to be centres of real estate development for ... — The urbanisation rate is projected at 50 per cent, equivalent to 51 million urban residents, while the middle class could expand to 75 per cent ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html](https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html)
-### Document Overview
-Savills Việt Nam nhận định đầu tư cơ sở hạ tầng quy mô 49 tỷ USD sẽ định hình lại thị trường bất động sản Việt Nam trong thập kỷ tới, với trọng tâm dịch chuyển sang các thành phố vệ tinh.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Infrastructure will be the most critical growth driver for the next decade, according to Savills Việt Nam. Infrastructure investment totalling US$49 billion is being deployed nationwide, including the North-South Expressway, Long Thành International Airport, Ring Road systems, and LNG projects. Once completed, these networks will redefine Việt Nam’s urban landscape, connecting emerging growth hubs and expanding development corridors across secondary cities such as Bình Dương, Đồng Nai, Hải Phòng, and Quảng Ninh.
-answer: 1. Theo Savills Việt Nam, đầu tư cơ sở hạ tầng trị giá 49 tỷ USD (bao gồm sân bay Long Thành, cao tốc Bắc - Nam và các đường vành đai) sẽ là động lực tăng trưởng quan trọng nhất giúp thay đổi diện mạo đô thị trong thập kỷ tới. 2. Sự phát triển này sẽ thúc đẩy các thành phố vệ tinh như Bình Dương, Đồng Nai, Hải Phòng trở thành tâm điểm của thị trường bất động sản, song hành với dự báo GDP tăng gấp ba và tầng lớp trung lưu chiếm 75% dân số vào năm 2035.
-Source: [vietnamnews.vn](https://vietnamnews.vn/economy/1731495/satellite-cities-to-be-centres-of-real-estate-development-for-next-decade-savills.html)</t>
+          <t>[Urban Development] Satellite cities to be centres of real estate development for ... — The urbanisation rate is projected at 50 per cent, equivalent to 51 million urban residents, while the middle class could expand to 75 per cent ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -7322,35 +5888,17 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html](https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html)
-### Document Overview
-The article details Ho Chi Minh City's 2026 roadmap for smart urban governance, focusing on digital transformation, AI integration, and data-driven decision-making to improve public services and urban management.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: In 2026, Ho Chi Minh City will focus on cleansing, standardizing and effectively leveraging data to operate a truly smart city. Public services will shift from “processing applications” to “serving needs.” ... HCMC-DXCenter will continue piloting the model in Sai Gon ward, Binh Duong and Con Dao Special Zone... at the same time, the city is completing its Smart Urban Operations Center, applying AI, machine learning and chatbots to support decision-making, integrate multi-sector data and provide a real-time overall picture.
-answer: 호치민시는 2026년을 기점으로 데이터 표준화와 인공지능(AI) 기술을 활용한 '진정한 스마트 도시'로의 전환을 가속화하며, 공공 서비스를 단순 민원 처리에서 시민 수요 맞춤형 서비스로 혁신할 계획입니다. 이를 위해 디지털 트윈(Digital Twin) 모델을 도시 전역으로 확대하고 스마트 도시 운영 센터를 완공하여 교통 정체 예측, 홍수 경보, 환경 오염 감시 등 도시 문제를 실시간 데이터 기반으로 해결하는 스마트 거버넌스 구축에 집중하고 있습니다.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html)</t>
+          <t>[Urban Development] Ho Chi Minh City moves to real smart urban governance in ... — Ho Chi Minh City is building a governance model where real-time data, AI and digital twins guide decisions and reshape daily urban life.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html](https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html)
-### Document Overview
-Ho Chi Minh City is transitioning to smart urban governance in 2026 by leveraging a Digital Twin model, AI-driven operations, and centralized data to improve public services, traffic management, and environmental monitoring.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: In 2026, Ho Chi Minh City will focus on cleansing, standardizing and effectively leveraging data to operate a truly smart city. Public services will shift from “processing applications” to “serving needs.” ... The city is completing its Smart Urban Operations Center, applying AI, machine learning and chatbots to support decision-making, integrate multi-sector data and provide a real-time overall picture. ... Toward 2030, the city aims to operate its data exchange platform in sync with the Smart Urban Operations Center, enhancing governance capacity based on real-time data.
-answer: Ho Chi Minh City is accelerating its digital transformation in 2026 by deploying a 'Digital Twin' model and a Smart Urban Operations Center to manage infrastructure, traffic, and flooding through real-time data and AI. This urban development initiative shifts governance toward a data-driven model, integrating a 'Citizen App' for public services and aiming for a digital economy that accounts for 30-40% of the city's GRDP by 2030.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html)</t>
+          <t>[Urban Development] Ho Chi Minh City moves to real smart urban governance in ... — Ho Chi Minh City is building a governance model where real-time data, AI and digital twins guide decisions and reshape daily urban life.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>## [https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html](https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html)
-### Document Overview
-Bài báo mô tả kế hoạch của TP.HCM năm 2026 nhằm xây dựng chính quyền số dựa trên dữ liệu, sử dụng mô hình Digital Twin và AI để giải quyết các vấn đề đô thị như giao thông và ngập lụt.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: In 2026, Ho Chi Minh City will focus on cleansing, standardizing and effectively leveraging data to operate a truly smart city. Public services will shift from “processing applications” to “serving needs.” ... technical infrastructure, traffic systems, environmental conditions and power grids are synchronously simulated, enabling forecasts of congestion hotspots, flood risks and operational incidents based on real-time data.
-answer: Trong năm 2026, Thành phố Hồ Chí Minh tập trung chuyển đổi sang mô hình quản trị đô thị thông minh thực thụ thông qua việc chuẩn hóa dữ liệu và vận hành Trung tâm Điều hành Đô thị Thông minh. Thành phố sẽ đẩy mạnh triển khai mô hình 'Bản sao số' (Digital Twin) để mô phỏng hạ tầng kỹ thuật, dự báo kẹt xe, ngập lụt và ứng dụng trí tuệ nhân tạo (AI) để chuyển đổi dịch vụ công từ xử lý hồ sơ sang phục vụ nhu cầu người dân.
-Source: [vietnamnet.vn](https://vietnamnet.vn/en/ho-chi-minh-city-moves-to-real-smart-urban-governance-in-2026-2492851.html)</t>
+          <t>[Urban Development] Ho Chi Minh City moves to real smart urban governance in ... — Ho Chi Minh City is building a governance model where real-time data, AI and digital twins guide decisions and reshape daily urban life.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -7404,35 +5952,17 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege](https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege)
-### Document Overview
-This page discusses Ho Chi Minh City's strategic shift toward a multi-center urban model and TOD-based infrastructure development to become a sustainable megacity by 2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: Ho Chi Minh City is developing a master plan based on a multi-center urban model, promoting regional integration and spatial connectivity to address fragmented development. The “one space – three regions – one special zone” framework clearly defines functional roles, linking key growth hubs such as finance, high-tech industry, and the maritime economy. Infrastructure—especially metro systems and regional transport—is positioned as the main growth driver under the TOD (Transit-Oriented Development) model.
-answer: 호치민시는 파편화된 도시 개발을 해결하기 위해 '1개 공간 - 3개 지역 - 1개 특구' 프레임워크를 기반으로 한 다중심 도시 모델 마스터플랜을 수립하고 지역 통합을 추진하고 있습니다. 특히 대중교통 지향 개발(TOD) 모델을 통해 메트로 시스템과 지역 교통 인프라를 핵심 성장 동력으로 삼아 2030년까지 주요 교통망 완성을 목표로 하고 있습니다. 이를 통해 금융, 하이테크 산업, 해양 경제 허브를 연결하여 현대적이고 지속 가능한 스마트 메가시티로 도약할 계획입니다.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege)</t>
+          <t>[Urban Development] Vietnam's Ho Chi Minh City adopts multi-center urban model — The project, linking Ben Thanh to Can Gio, is being positioned as a major infrastructure upgrade that could reshape mobility, tourism, and real ...</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege](https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege)
-### Document Overview
-The page announces Ho Chi Minh City's adoption of a multi-center urban model and TOD-driven infrastructure strategy to transform into a smart megacity by 2030.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: Ho Chi Minh City is developing a master plan based on a multi-center urban model, promoting regional integration and spatial connectivity to address fragmented development. The “one space – three regions – one special zone” framework clearly defines functional roles, linking key growth hubs such as finance, high-tech industry, and the maritime economy. Infrastructure—especially metro systems and regional transport—is positioned as the main growth driver under the TOD (Transit-Oriented Development) model.
-answer: Ho Chi Minh City is implementing a master plan based on a multi-center urban model and a “one space – three regions – one special zone” framework to improve regional connectivity and address fragmented development. The strategy prioritizes the Transit-Oriented Development (TOD) model, focusing on metro systems and regional transport to link key economic hubs like finance and high-tech industries by 2030.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege)</t>
+          <t>[Urban Development] Vietnam's Ho Chi Minh City adopts multi-center urban model — The project, linking Ben Thanh to Can Gio, is being positioned as a major infrastructure upgrade that could reshape mobility, tourism, and real ...</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege](https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege)
-### Document Overview
-The page discusses Ho Chi Minh City's adoption of a multi-center urban model focused on transit-oriented development (TOD) and infrastructure completion by 2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Ho Chi Minh City is developing a master plan based on a multi-center urban model, promoting regional integration and spatial connectivity to address fragmented development. Infrastructure—especially metro systems and regional transport—is positioned as the main growth driver under the TOD (Transit-Oriented Development) model. The city aims to complete its core transport network by 2030, leveraging PPP mechanisms and urban financial tools.
-answer: Thành phố Hồ Chí Minh đang triển khai quy hoạch đô thị theo mô hình đa trung tâm với khung chiến lược "một không gian - ba vùng - một khu đặc biệt" nhằm tăng cường kết nối vùng và giải quyết tình trạng phát triển phân mảnh. Hạ tầng giao thông, đặc biệt là hệ thống Metro và mạng lưới vận tải liên kết vùng theo mô hình TOD, được xác định là động lực tăng trưởng chính với mục tiêu hoàn thành mạng lưới cốt lõi vào năm 2030 thông qua cơ chế PPP và các công cụ tài chính đô thị.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/smart-city-asia-32094a239_trienlam-smartcityasia2026-kynguyenvuonminh-activity-7445764686211362816-Fege)</t>
+          <t>[Urban Development] Vietnam's Ho Chi Minh City adopts multi-center urban model — The project, linking Ben Thanh to Can Gio, is being positioned as a major infrastructure upgrade that could reshape mobility, tourism, and real ...</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -7486,35 +6016,17 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>## [https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects](https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects)
-### Document Overview
-This article discusses Vietnam's US$115 billion investment in 27 mega urban development projects led by Vingroup and Sun Group across the country's northern, central, and southern regions.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: VN-EV-2030
-verbatim: Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025... Northern Vietnam accounts for nine mega projects, Central Vietnam accounts for eight projects, Southern Vietnam has 10 mega projects... Improved legal frameworks and expanding transport infrastructure helped trigger a new wave of large-scale real estate development.
-answer: 베트남은 2025년 기준 총 1,150억 달러(약 3,000조 동) 규모에 달하는 27개의 대규모 도시 개발 프로젝트를 추진하며 전국적인 신도시 건설 열풍을 이어가고 있습니다. 빈그룹(Vingroup)과 선그룹(Sun Group) 등 주요 개발사들이 주도하는 이 프로젝트들은 하노이 인근의 올림픽 스포츠 도시와 꽝닌성의 하롱싼 통합 도시 등 북부, 중부, 남부 전역에 걸쳐 대규모 인프라 확장을 포함하고 있습니다. 정부의 법적 규제 완화와 교통 인프라 확충에 힘입어 도시 개발(Urban Development) 섹션이 활성화되고 있으나, 급격한 공급 증가에 따른 시장 흡수 능력과 주택 가격 상승에 대한 우려도 제기되고 있습니다.
-Source: [www.thestar.com.my](https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects)</t>
+          <t>[Urban Development] Vietnam set for US$115bil mega urban projects — Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025, ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>## [https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects](https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects)
-### Document Overview
-The article discusses Vietnam's US$115 billion investment in 27 mega urban development projects driven by developers like Vingroup and Sun Group, facilitated by legal and infrastructure improvements.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: VN-EV-2030
-verbatim: Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025, according to a report by S&amp;I Ratings, highlighting a nationwide push to build massive new townships... Improved legal frameworks and expanding transport infrastructure helped trigger a new wave of large-scale real estate development.
-answer: Vietnam is initiating 27 large-scale urban development projects totaling over US$115 billion, led by major developers like Vingroup and Sun Group across northern, central, and southern regions. This infrastructure push, which includes mega-projects like the US$35.6 billion Olympic sports urban area in Hanoi, is supported by new National Assembly resolutions and improved legal frameworks aimed at expanding land availability and transport connectivity. While the projects align with Vietnam's urban development goals (VN-EV-2030), analysts caution that rapid supply growth and rising prices could create affordability and market absorption challenges.
-Source: [www.thestar.com.my](https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects)</t>
+          <t>[Urban Development] Vietnam set for US$115bil mega urban projects — Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025, ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>## [https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects](https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects)
-### Document Overview
-Báo cáo về làn sóng 27 siêu dự án đô thị tại Việt Nam trị giá 115 tỷ USD cùng những phân tích về tiềm năng phát triển và thách thức của thị trường bất động sản.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025... highlighting a nationwide push to build massive new townships. More than half of the total investment is led by major developers including Vingroup and Sun Group... Improved legal frameworks and expanding transport infrastructure helped trigger a new wave of large-scale real estate development.
-answer: Tính đến năm 2025, Việt Nam đã triển khai 27 dự án phát triển đô thị quy mô lớn với tổng vốn đầu tư vượt 115 tỷ USD, tập trung chủ yếu vào các khu đô thị phức hợp tại miền Bắc, miền Trung và miền Nam. Các tập đoàn lớn như Vingroup và Sun Group đang dẫn dắt làn sóng đầu tư này nhờ sự cải thiện về khung pháp lý và cơ sở hạ tầng giao thông. Tuy nhiên, các chuyên gia cũng cảnh báo về áp lực tài chính và khả năng hấp thụ của thị trường khi giá nhà ở đang tăng nhanh vượt quá mức tăng thu nhập của người dân.
-Source: [www.thestar.com.my](https://www.thestar.com.my/business/business-news/2026/03/12/vietnam-set-for-us115bil-mega-urban-projects)</t>
+          <t>[Urban Development] Vietnam set for US$115bil mega urban projects — Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025, ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -7568,35 +6080,17 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>## [https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story](https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story)
-### Document Overview
-This article discusses Vietnam's structural economic transformation and its shift towards high-quality, integrated urban development and high-tech FDI sectors like semiconductors and AI.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: VN-EV-2030
-verbatim: Vietnam’s development story not simply as one of momentum, but as a deep structural transformation — from a phase of rapid expansion to one of more sustainable, higher-quality growth. ... The briefing also noted that Vietnam’s FDI attraction strategy has remained broadly consistent over the past decade... Vietnam is placing greater priority on strategic sectors such as semiconductors and chip manufacturing, AI, robotics, biotechnology, and nuclear energy. ... Ms. Ngoc Le, Senior Director, Strategic Consulting, Cushman &amp; Wakefield Vietnam, said: “Vietnam’s larger planning footprint gives it a real opportunity to develop integrated mega-townships more effectively, but this requires long-term discipline and a planning mindset that builds districts, not just buildings.”
-answer: 베트남은 단순한 양적 팽창을 넘어 지속 가능한 고부가가치 산업 중심의 도시 개발(Urban Development) 단계로 진입하고 있으며, 인프라와 일자리, 삶의 질이 통합된 '메가 타운십' 조성이 핵심 과제로 부상하고 있습니다. 특히 VN-EV-2030 마스터플랜의 비전과 맞물려 반도체, AI 등 전략적 첨단 산업 유치를 위한 체계적인 도시 계획과 법적 투명성 강화가 강조되고 있습니다. 이를 통해 베트남은 2030년까지 동남아시아 3대 경제 대국으로 도약하고 2045년 고소득 선진국 진입을 목표로 인프라와 경제 전략을 긴밀히 통합하고 있습니다.
-Source: [www.cushmanwakefield.com](https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story)</t>
+          <t>[Urban Development] Cushman &amp; Wakefield Spotlights Vietnam's Next Urban ... — The country is now entering a more mature phase of development, where growth is increasingly defined not only by scale, but by productivity, ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>## [https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story](https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story)
-### Document Overview
-This report by Cushman &amp; Wakefield details Vietnam's shift toward integrated urban planning and high-tech industrial growth as it targets becoming a high-income nation by 2045 and a top regional economy by 2030.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: VN-EV-2030
-verbatim: Vietnam’s 30-year economic transformation was framed as the foundation for a new phase of urban growth — one in which planning, infrastructure, innovation and long-term competitiveness must evolve together to support the country’s next chapter... The country is now entering a more mature phase of development, where growth is increasingly defined not only by scale, but by productivity, innovation, infrastructure readiness and the quality of investment... the next cycle, toward 2030 and beyond, will be driven by greater legal transparency, more strategic infrastructure development, and the national ambition to become Southeast Asia’s third-largest economy before 2030.
-answer: Vietnam is transitioning into a new era of urban development characterized by integrated mega-townships and strategic infrastructure alignment to support its ambition of becoming Southeast Asia’s third-largest economy by 2030. The focus has shifted from fragmented expansion to sustainable, high-quality growth driven by infrastructure readiness, legal transparency, and the transformation into a high-tech investment hub for sectors like semiconductors and AI.
-Source: [www.cushmanwakefield.com](https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story)</t>
+          <t>[Urban Development] Cushman &amp; Wakefield Spotlights Vietnam's Next Urban ... — The country is now entering a more mature phase of development, where growth is increasingly defined not only by scale, but by productivity, ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>## [https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story](https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story)
-### Document Overview
-The article discusses Vietnam's transition into a mature phase of sustainable urban growth, highlighting the need for integrated planning, infrastructure development, and high-tech investment to reach developed nation status by 2045.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s 30-year economic transformation was framed as the foundation for a new phase of urban growth — one in which planning, infrastructure, innovation and long-term competitiveness must evolve together to support the country’s next chapter. ... successful urbanisation is never just about adding housing stock. It is about creating a complete urban logic — where infrastructure, jobs, education, healthcare, public amenities and quality of life evolve together.
-answer: 1. Bài báo nhấn mạnh Việt Nam đang chuyển mình từ giai đoạn tăng trưởng nhanh sang phát triển bền vững, dựa trên nền tảng hạ tầng chiến lược, đổi mới sáng tạo và thu hút đầu tư chất lượng cao (như bán dẫn và AI). 2. Cushman &amp; Wakefield nhận định rằng tương lai đô thị của Việt Nam cần sự gắn kết chặt chẽ giữa quy hoạch đồng bộ, kết nối hạ tầng sớm và tạo dựng các hệ sinh thái đa tiện ích để duy trì giá trị thương mại dài hạn.
-Source: [www.cushmanwakefield.com](https://www.cushmanwakefield.com/en/vietnam/news/2026/03/vietnam-next-urban-growth-story)</t>
+          <t>[Urban Development] Cushman &amp; Wakefield Spotlights Vietnam's Next Urban ... — The country is now entering a more mature phase of development, where growth is increasingly defined not only by scale, but by productivity, ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -7650,35 +6144,17 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html](https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html)
-### Document Overview
-The article discusses Vietnam's shift towards a new urbanization cycle focused on sustainable, high-quality growth and integrated urban planning to reach high-income status by 2045.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: N/A
-verbatim: Vietnam is now entering a more mature phase of development, where growth is increasingly defined by scale, productivity, innovation, infrastructure readiness, and the quality of investment... The next cycle, towards 2030 and beyond, will be driven by greater legal transparency, more strategic infrastructure development, and the national ambition to become Southeast Asia's third-largest economy before 2030 and a developed, high-income country by 2045... urban planning and infrastructure development must move in parallel with economic transformation.
-answer: 베트남은 단순한 양적 팽창을 넘어 전략적 인프라 개발과 통합 도시 계획을 중심으로 하는 새로운 도시화 주기에 진입하고 있습니다. 2030년까지 동남아시아 3대 경제 대국으로 도약하기 위해 반도체, AI 등 고부가가치 산업 유치와 연계된 스마트하고 지속 가능한 주거 및 고용 클러스터 조성이 핵심 과제로 제시되었습니다.
-Source: [vir.com.vn](https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html)</t>
+          <t>[Urban Development] New urbanisation cycle set to define Vietnam's next ... — Vietnam is shifting to sustainable growth, with urban planning and infrastructure set to define the next decade.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html](https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html)
-### Document Overview
-The article reports on Vietnam's transition into a mature urbanization phase characterized by integrated planning, infrastructure-led growth, and a shift toward high-tech investment through 2045.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: N/A
-verbatim: Vietnam is entering a more mature phase of development, where growth is increasingly defined by scale, productivity, innovation, infrastructure readiness, and the quality of investment... The next cycle, towards 2030 and beyond, will be driven by greater legal transparency, more strategic infrastructure development, and the national ambition to become Southeast Asia's third-largest economy... urban planning and infrastructure development must move in parallel with economic transformation.
-answer: Vietnam is entering a new urbanization cycle focused on sustainable, high-quality growth and integrated mega-townships that align infrastructure development with economic transformation. The country aims to become Southeast Asia's third-largest economy by 2030 by prioritizing strategic sectors like semiconductors and AI while shifting from fragmented urban expansion to disciplined, mixed-use ecosystems.
-Source: [vir.com.vn](https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html)</t>
+          <t>[Urban Development] New urbanisation cycle set to define Vietnam's next ... — Vietnam is shifting to sustainable growth, with urban planning and infrastructure set to define the next decade.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html](https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html)
-### Document Overview
-The article discusses Vietnam's transition into a more mature development phase (2025-2035), focusing on integrated urban planning, infrastructure readiness, and high-tech FDI attraction.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The next cycle, towards 2030 and beyond, will be driven by greater legal transparency, more strategic infrastructure development, and the national ambition to become Southeast Asia's third-largest economy before 2030... In the next phase of economic development, with a stronger focus on improving the quality of FDI, Vietnam is placing greater priority on strategic sectors such as semiconductors and chip manufacturing, AI, robotics, biotechnology, and nuclear energy.
-answer: Việt Nam đang bước vào một chu kỳ đô thị hóa mới hướng tới năm 2035, với trọng tâm chuyển đổi từ phát triển diện rộng sang tăng trưởng chất lượng cao và bền vững dựa trên hạ tầng chiến lược. Chính phủ đang ưu tiên đầu tư vào các lĩnh vực công nghệ cao như bán dẫn, AI và năng lượng hạt nhân, đồng thời yêu cầu quy hoạch đô thị phải đồng bộ với phát triển hạ tầng và hệ sinh thái tiện ích để nâng cao năng lực cạnh tranh quốc gia.
-Source: [vir.com.vn](https://vir.com.vn/new-urbanisation-cycle-set-to-define-vietnams-next-decade-of-growth-149031.html)</t>
+          <t>[Urban Development] New urbanisation cycle set to define Vietnam's next ... — Vietnam is shifting to sustainable growth, with urban planning and infrastructure set to define the next decade.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -7732,35 +6208,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>## [https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html](https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html)
-### Document Overview
-Ho Chi Minh City has drafted a plan to join the global top 50 smart cities by 2030, emphasizing data-driven governance and a digital twin system for urban management.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: VN-EV-2030
-verbatim: According to the draft, the city also targets becoming one of three national-level smart urban operation centres by 2035... The city targets becoming a global top 50 smart city by 2030... The plan highlights that smart urban development goes beyond technology adoption, focusing instead on transforming governance based on data and digital technologies.
-answer: 호치민시는 'VN-EV-2030' 마스터플랜의 일환으로 2030년까지 세계 50대 스마트 시티 진입과 2035년까지 국가급 스마트 도시 운영 센터 구축을 목표로 하고 있습니다. 이 계획은 단순한 기술 도입을 넘어 데이터와 디지털 기술 기반의 거버넌스 혁신을 핵심으로 하며, AI, 디지털 트윈 등을 활용해 교통, 환경 등 도시 문제를 해결하는 데 집중할 예정입니다.
-Source: [en.nhandan.vn](https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html)</t>
+          <t>[Urban Development] Ho Chi Minh City targets global Top 50 smart cities by 2030 — Ho Chi Minh City aims to rank among the world's top 50 smart cities by 2030 under a draft smart urban development plan for 2026–2030, ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>## [https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html](https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html)
-### Document Overview
-Ho Chi Minh City is planning to transform into a top 50 global smart city by 2030, emphasizing institutional reform and data-driven governance over mere technology adoption.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: VN-EV-2030
-verbatim: According to the draft, the city also targets becoming one of three national-level smart urban operation centres by 2035, serving as a hub for data coordination, technology and innovation nationwide... the 2026–2027 period will prioritise building foundational platforms, refining institutions and launching pilot projects... From 2028 to 2029, the city plans to expand implementation and integration, while completing its intelligent operations centre (IOC).
-answer: Ho Chi Minh City has unveiled an ambitious urban development roadmap to become one of the world's top 50 smart cities by 2030 and a national-level smart operation hub by 2035. Under the VN-EV-2030 framework, the plan prioritizes data-driven governance and institutional reform, focusing on digital twins, AI integration, and sustainable infrastructure to address regional challenges like transport and climate adaptation.
-Source: [en.nhandan.vn](https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html)</t>
+          <t>[Urban Development] Ho Chi Minh City targets global Top 50 smart cities by 2030 — Ho Chi Minh City aims to rank among the world's top 50 smart cities by 2030 under a draft smart urban development plan for 2026–2030, ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>## [https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html](https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html)
-### Document Overview
-The article discusses Ho Chi Minh City's strategic roadmap to become a global top 50 smart city by 2030, emphasizing data-driven governance and digital infrastructure.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Ho Chi Minh City targets becoming one of the global top 50 smart cities by 2030... The plan highlights that smart urban development goes beyond technology adoption, focusing instead on transforming governance based on data and digital technologies... placing people and businesses at the centre is identified as a core principle.
-answer: Thành phố Hồ Chí Minh đặt mục tiêu lọt vào nhóm 50 thành phố thông minh hàng đầu thế giới vào năm 2030 và trở thành trung tâm vận hành đô thị thông minh cấp quốc gia vào năm 2035. Kế hoạch này tập trung vào việc chuyển đổi quản trị dựa trên dữ liệu, ứng dụng các công nghệ tiên tiến như AI và bản sao kỹ thuật số (digital twin) để tối ưu hóa vận hành và dịch vụ công. Trọng tâm của đề án là lấy người dân và doanh nghiệp làm trung tâm, đồng thời kết hợp phát triển đô thị thông minh với tăng trưởng xanh và bền vững.
-Source: [en.nhandan.vn](https://en.nhandan.vn/ho-chi-minh-city-targets-global-top-50-smart-cities-by-2030-post160464.html)</t>
+          <t>[Urban Development] Ho Chi Minh City targets global Top 50 smart cities by 2030 — Ho Chi Minh City aims to rank among the world's top 50 smart cities by 2030 under a draft smart urban development plan for 2026–2030, ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -7814,35 +6272,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>## [https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X](https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X)
-### Document Overview
-The article discusses the divergent urban development strategies of Ho Chi Minh City, focusing on integrated mega-projects, and Hanoi, focusing on the low-altitude economy (UAVs and eVTOLs) to overcome infrastructure limitations.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Urban Development, 관련 마스터플랜: VN-EV-2030
-verbatim: While Ho Chi Minh City is witnessing a dramatic shift in real estate investment toward integrated urban mega-projects... Hanoi is gazing skyward, exploring the economic promise of its low-altitude airspace. Both cities, in their own ways, are responding to the challenges of urbanization, scarce land, and the relentless demand for smarter, more sustainable growth.
-answer: 베트남의 주요 도시인 호치민과 하노이는 'VN-EV-2030' 마스터플랜의 흐름에 맞춰 혁신적인 도시 개발(Urban Development)을 추진하고 있습니다. 호치민은 주거, 상업, 의료가 결합된 '더 글로벌 시티'와 같은 대규모 복합 단지 조성에 집중하는 반면, 하노이는 지상 교통난 해소를 위해 드론 배송과 도심 항공 모빌리티를 활용한 '저고도 경제' 활성화에 주력하고 있습니다. 두 도시는 각각 지상 인프라의 고도화와 하늘길 개척이라는 서로 다른 전략을 통해 스마트하고 지속 가능한 미래 도시 모델을 제시하고 있습니다.
-Source: [evrimagaci.org](https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X)</t>
+          <t>[Urban Development] Ho Chi Minh City And Hanoi Redefine Urban Futures — On the cusp of 2026, two of Vietnam's most dynamic cities—Ho Chi Minh City and Hanoi—are charting bold, divergent courses in urban development. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>## [https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X](https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X)
-### Document Overview
-The article details the divergent urban development strategies of Ho Chi Minh City, focusing on integrated mixed-use mega-projects, and Hanoi, which is pioneering a low-altitude airspace economy to overcome ground transportation limitations.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Urban Development, Related plans: VN-EV-2030
-verbatim: While Ho Chi Minh City is witnessing a dramatic shift in real estate investment toward integrated urban mega-projects, Hanoi is gazing skyward, exploring the economic promise of its low-altitude airspace. Both cities, in their own ways, are responding to the challenges of urbanization, scarce land, and the relentless demand for smarter, more sustainable growth. ... Forecasts suggest that the low-altitude economy could directly contribute 1-1.5% to Hanoi’s GRDP growth from 2026 to 2030, with ripple effects across high-tech manufacturing, composite material production, and high-density battery manufacturing.
-answer: Vietnam's major cities are pivoting toward high-tech urban infrastructure by 2026, with Ho Chi Minh City prioritizing integrated multifunctional mega-projects like 'The Global City' to optimize land use and living standards. Simultaneously, Hanoi is expanding its 'low-altitude economy' through UAV and eVTOL integration for logistics and healthcare, aiming for this sector to contribute up to 1.5% of its GRDP growth by 2030. These developments reflect a broader strategy to address urbanization challenges through smart technology, sustainable growth, and improved logistics efficiency.
-Source: [evrimagaci.org](https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X)</t>
+          <t>[Urban Development] Ho Chi Minh City And Hanoi Redefine Urban Futures — On the cusp of 2026, two of Vietnam's most dynamic cities—Ho Chi Minh City and Hanoi—are charting bold, divergent courses in urban development. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>## [https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X](https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X)
-### Document Overview
-The article discusses the divergent urban development strategies of Ho Chi Minh City and Hanoi for 2026, focusing on integrated mega-projects in the south and the low-altitude economy in the north.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: While Ho Chi Minh City is witnessing a dramatic shift in real estate investment toward integrated urban mega-projects, Hanoi is gazing skyward, exploring the economic promise of its low-altitude airspace. Both cities, in their own ways, are responding to the challenges of urbanization, scarce land, and the relentless demand for smarter, more sustainable growth.
-answer: Bài báo phân tích sự chuyển dịch hạ tầng đô thị tại hai thành phố lớn của Việt Nam vào năm 2026: trong khi TP. Hồ Chí Minh tập trung phát triển các siêu dự án đô thị tích hợp đa tiện ích như The Global City, thì Hà Nội lại hướng tới khai phá kinh tế không gian tầm thấp dưới 1.000m với các thiết bị bay không người lái để giải quyết tắc nghẽn giao thông và giảm chi phí logistics. Cả hai hướng đi đều nhằm mục tiêu tối ưu hóa quỹ đất hạn hẹp và thúc đẩy tăng trưởng thông minh, bền vững thông qua ứng dụng công nghệ và quy hoạch hiện đại.
-Source: [evrimagaci.org](https://evrimagaci.org/gpt/ho-chi-minh-city-and-hanoi-redefine-urban-futures-525510?srsltid=AfmBOooa7MtEa9Y3L1jRewM0gm_irdq9fY6bIX0w7l7IwiF3xk7JuS3X)</t>
+          <t>[Urban Development] Ho Chi Minh City And Hanoi Redefine Urban Futures — On the cusp of 2026, two of Vietnam's most dynamic cities—Ho Chi Minh City and Hanoi—are charting bold, divergent courses in urban development. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -7896,35 +6336,17 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>## [https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html](https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html)
-### Document Overview
-The article reports on VinFast's record-breaking sales in April 2026, signaling a global shift toward mass-market EV adoption supported by infrastructure expansion and government policies.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Other, 관련 마스터플랜: VN-EV-2030
-verbatim: VinFast, Vietnam’s leading EV manufacturer, recorded its highest-ever single-day sales on April 11, 2026... The expansion of charging infrastructure is one of the biggest drivers of EV adoption worldwide... Vietnam’s rapid adoption of electric vehicles is driven by Government support for clean energy, Urban mobility challenges, Growing middle-class demand, and Local manufacturing capabilities.
-answer: 베트남의 대표 전기차 제조사인 빈패스트(VinFast)가 2026년 4월 11일 역대 최고 일일 판매량을 기록하며, 전기차 시장이 초기 단계를 지나 대중화 단계로 진입했음을 입증했습니다. 이는 충전 인프라의 급격한 확충과 정부의 친환경 에너지 정책 지원에 힘입은 결과로, 베트남은 강력한 현지 제조 역량을 바탕으로 글로벌 전기차 시장의 핵심 거점으로 부상하고 있습니다. 이번 성과는 VN-EV-2030 마스터플랜의 흐름과 궤를 같이하며 향후 배터리 기술 발전과 인프라 확대를 통한 지속적인 성장이 기대됩니다.
-Source: [evtech.news](https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html)</t>
+          <t>[Other] VinFast Records Biggest-Ever Single-Day Sales on April 11, 2026 ... — VinFast achieves record-breaking EV sales as global charging infrastructure expands, marking a shift from hype to practical adoption ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>## [https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html](https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html)
-### Document Overview
-The article reports on VinFast's record-breaking single-day sales in April 2026, attributing the success to improved charging infrastructure and a shift toward practical EV adoption in Vietnam and globally.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Other, Related plans: VN-EV-2030
-verbatim: VinFast, Vietnam’s leading EV manufacturer, recorded its highest-ever single-day sales on April 11, 2026. This achievement highlights a critical shift in the EV industry — from early hype to widespread practical adoption. The record-breaking sales surge comes at a time when charging infrastructure is expanding rapidly across global markets... Strong focus on charging ecosystem development... Global expansion into US, Europe, and Asia.
-answer: VinFast achieved a milestone for Vietnam's automotive sector by recording its highest-ever single-day electric vehicle sales on April 11, 2026, signaling a shift toward mass-market maturity. This growth is underpinned by the rapid expansion of charging infrastructure and the VN-EV-2030 relevant goals of developing a robust local charging ecosystem and enhancing domestic manufacturing capabilities. The surge reflects Vietnam's emerging status as a key player in the global EV market through government-supported clean energy initiatives and strategic infrastructure investment.
-Source: [evtech.news](https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html)</t>
+          <t>[Other] VinFast Records Biggest-Ever Single-Day Sales on April 11, 2026 ... — VinFast achieves record-breaking EV sales as global charging infrastructure expands, marking a shift from hype to practical adoption ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>## [https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html](https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html)
-### Document Overview
-The article reports on VinFast's record-breaking sales on April 11, 2026, and analyzes the maturity of the global and Vietnamese EV markets driven by infrastructure and technology improvements.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is emerging as a key player in the global EV market. The country’s rapid adoption of electric vehicles is driven by: Government support for clean energy, Urban mobility challenges, Growing middle-class demand, Local manufacturing capabilities... Strong focus on charging ecosystem development.
-answer: Bài báo đưa tin về kỷ lục doanh số bán hàng trong ngày cao nhất lịch sử của VinFast vào ngày 11/04/2026, đánh dấu sự chuyển dịch từ kỳ vọng sang thực tế thị trường xe điện tại Việt Nam. Sự tăng trưởng này được thúc đẩy bởi chiến lược phát triển hệ sinh thái trạm sạc rộng khắp và năng lực sản xuất nội địa mạnh mẽ, giúp Việt Nam trở thành trung tâm xe điện quan trọng toàn cầu.
-Source: [evtech.news](https://evtech.news/news/vinfast-records-biggest-ever-single-day-sales-on-april-11-2026-signaling-ev-market-maturity.html)</t>
+          <t>[Other] VinFast Records Biggest-Ever Single-Day Sales on April 11, 2026 ... — VinFast achieves record-breaking EV sales as global charging infrastructure expands, marking a shift from hype to practical adoption ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7974,35 +6396,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>## [https://www.sciencedirect.com/science/article/pii/S2590198226000928](https://www.sciencedirect.com/science/article/pii/S2590198226000928)
-### Document Overview
-This academic article analyzes Vietnam's EV transition and public sentiment from 2022-2024, highlighting the roles of the national champion VinFast and the 2030 electrification masterplan.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-EV-2030
-verbatim: This governmental ambition is not merely rhetorical; it is crystallized in a national strategy aiming to have EVs comprise the primary mode of transport in its two largest metropolises, Hanoi and Ho Chi Minh City, by 2030 (Doan, 2025). ... Specifically, Hanoi will pilot a “Low Emission Zone” starting on July 1, 2026 ... Meanwhile, Ho Chi Minh City is accelerating its transition by mandating that 100% of new public buses operate on electric or other green energy sources starting in 2025. ... The findings suggest that even the powerful positive sentiment for VinFast does not alleviate these concerns highlights that the public distinctly assigns this responsibility to the state. Therefore, government efforts should prioritize not only investment in a dense and reliable charging network but also transparent communication about the long-term national roadmap for EV integration.
-answer: 베트남은 2030년까지 하노이와 호치민의 주요 운송 수단을 전기차(EV)로 전환하는 국가 전략(VN-EV-2030)을 추진하고 있으며, 이에 따라 2025년부터 호치민 신규 버스의 100% 전기차 전환 및 2026년 하노이 저배출 구역 시범 운영이 예정되어 있습니다. 대중의 여론은 자국 브랜드인 빈패스트(VinFast)에 대해 높은 애국적 지지를 보이고 있으나, 에너지 인프라 측면에서는 충전 네트워크 구축과 전력망 안정성 등 국가 차원의 체계적인 인프라 투자를 핵심 과제로 요구하고 있습니다. 결론적으로 성공적인 EV 전환을 위해서는 단순한 차량 보급을 넘어 충전소 등 에너지 공급 시스템에 대한 정부의 강력한 정책적 실행력이 필수적인 상황입니다.
-Source: [www.sciencedirect.com](https://www.sciencedirect.com/science/article/pii/S2590198226000928)</t>
+          <t>[Power &amp; Energy] analyzing the public voice on electric vehicles and the rise of VinFast — Specifically, Hanoi will pilot a “Low Emission Zone” starting on July 1, 2026, which will restrict highly polluting gasoline vehicles from entering inner-city ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>## [https://www.sciencedirect.com/science/article/pii/S2590198226000928](https://www.sciencedirect.com/science/article/pii/S2590198226000928)
-### Document Overview
-This academic paper analyzes the shift in Vietnam's public discourse toward electric vehicles from 2022 to 2024, highlighting the role of national pride in VinFast and the growing demand for EV infrastructure.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-EV-2030
-verbatim: This governmental ambition is not merely rhetorical; it is crystallized in a national strategy aiming to have EVs comprise the primary mode of transport in its two largest metropolises, Hanoi and Ho Chi Minh City, by 2030 (Doan, 2025). Specifically, Hanoi will pilot a “Low Emission Zone” starting on July 1, 2026, which will restrict highly polluting gasoline vehicles from entering inner-city districts... Ho Chi Minh City is accelerating its transition by mandating that 100% of new public buses operate on electric or other green energy sources starting in 2025... This aggressive timeline elevates the importance of public adoption... Specifically, the public discourse has become more focused and substantive, moving away from generalist or off-topic commentary towards more specific, issue-oriented debates about EV adoption... the conversation decisively shifted towards practical, systemic concerns, as evidenced by the dramatic rise in comments coded under 'Infrastructure &amp; Policy Impact'.
-answer: Vietnam is advancing its 'VN-EV-2030' national strategy to make electric vehicles the primary mode of transport in Hanoi and Ho Chi Minh City by 2030, supported by the introduction of Low Emission Zones and a 100% electric public bus mandate starting in 2025. While national brand VinFast has boosted public enthusiasm, significant challenges remain in the Power &amp; Energy sector, as public discourse has shifted heavily toward urgent demands for a robust, state-led charging infrastructure to ensure the feasibility of this transition.
-Source: [www.sciencedirect.com](https://www.sciencedirect.com/science/article/pii/S2590198226000928)</t>
+          <t>[Power &amp; Energy] analyzing the public voice on electric vehicles and the rise of VinFast — Specifically, Hanoi will pilot a “Low Emission Zone” starting on July 1, 2026, which will restrict highly polluting gasoline vehicles from entering inner-city ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>## [https://www.sciencedirect.com/science/article/pii/S2590198226000928](https://www.sciencedirect.com/science/article/pii/S2590198226000928)
-### Document Overview
-The article provides a comprehensive analysis of Vietnamese public discourse on electric vehicles, emphasizing the growing focus on infrastructure and policy as critical barriers to adoption between 2022 and 2024. Despite strong national pride for VinFast, the public increasingly demands robust state-led investment and strategy for charging infrastructure.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Most strikingly, the conversation decisively shifted towards practical, systemic concerns, as evidenced by the dramatic rise in comments coded under 'Infrastructure &amp; Policy Impact'. This theme more than doubled its share of the discourse, rocketing from just 9% in 2022 to a commanding 21% in 2024, a highly significant shift (χ2 = 569.8, p &lt; 0.01). This finding strongly suggests that as EVs become more visible, the public's focus pivots from the abstract idea of the vehicle to the concrete realities of living with one. In the language of DoI theory, this represents a crucial move from evaluating the innovation itself to scrutinizing its Compatibility with the existing societal and physical environment. ... Our results send a clear message that the public discourse has matured beyond basic awareness and is now intensely focused on systemic readiness. The fact that discussion on 'Infrastructure &amp; Policy Impact' surged from 9% to constitute 21% of all comments in 2024 underscores an urgent public demand for a clear and robust national strategy regarding charging infrastructure. Our finding that even the powerful positive sentiment for VinFast does not alleviate these concerns highlights that the public distinctly assigns this responsibility to the state. Therefore, government efforts should prioritize not only investment in a dense and reliable charging network but also transparent communication about the long-term national roadmap for EV integration.
-answer: Trong giai đoạn 2022–2024, thảo luận của công chúng Việt Nam về phương tiện điện đã chuyển mạnh sang quan tâm các vấn đề thực tế như cơ sở hạ tầng sạc và chính sách hỗ trợ. Tỷ lệ bình luận liên quan đến 'cơ sở hạ tầng &amp; tác động chính sách' tăng từ 9% năm 2022 lên 21% năm 2024, phản ánh nhu cầu cấp thiết về chiến lược phát triển hệ thống trạm sạc toàn quốc. Mặc dù VinFast có tác động tích cực đến nhận thức cộng đồng, công chúng vẫn coi trách nhiệm phát triển cơ sở hạ tầng sạc là thuộc về nhà nước, chứ không chỉ riêng doanh nghiệp.
-Source: [www.sciencedirect.com](https://www.sciencedirect.com/science/article/pii/S2590198226000928)</t>
+          <t>[Power &amp; Energy] analyzing the public voice on electric vehicles and the rise of VinFast — Specifically, Hanoi will pilot a “Low Emission Zone” starting on July 1, 2026, which will restrict highly polluting gasoline vehicles from entering inner-city ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -8056,35 +6460,17 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>## [https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570](https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570)
-### Document Overview
-This article reports on VinFast's 2025 performance, where it nearly doubled its EV sales to approximately 197,000 units, and outlines its ambitious 300,000-unit target for 2026.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Other, 관련 마스터플랜: VN-EV-2030
-verbatim: The company said it delivered 196,919 electric vehicles worldwide in 2025, more than twice its 2024 total and the highest annual figure since it began selling cars... VinFast has now set a bold goal for 2026: 300,000 EV deliveries, a roughly 50% increase from 2025 levels. ... Industry trackers noted that VinFast posted more than 16,000 EV deliveries in Vietnam in January alone
-answer: 베트남 전기차 제조업체 빈패스트(VinFast)는 2025년 전년 대비 두 배 가까이 증가한 19만 6,919대의 글로벌 전기차 인도 실적을 기록하며 역대 최고의 성과를 거두었습니다. 회사는 베트남 내수 시장의 강력한 수요와 정부의 전동화 지원에 힘입어 2026년까지 전기차 30만 대 인도를 목표로 하고 있습니다. 이는 VN-EV-2030 마스터플랜의 일환으로 동남아시아 전역의 전기차 생태계와 충전 인프라 확장을 가속화하려는 전략적 움직임으로 분석됩니다.
-Source: [gulfnews.com](https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570)</t>
+          <t>[Other] VinFast's breakout year: Vietnamese EV maker nearly doubles sales ... — With nearly 200,000 EVs sold in 2025 and a 300,000-unit target for 2026, VinFast is no longer just an ambitious startup from Vietnam. It is ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>## [https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570](https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570)
-### Document Overview
-VinFast reported a record 196,919 EV deliveries in 2025 and set a growth target of 300,000 units for 2026, driven by a strong domestic market and government electrification support.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Other, Related plans: VN-EV-2030
-verbatim: Vietnamese electric vehicle maker VinFast Auto Ltd. is coming off its strongest year yet, nearly doubling global deliveries in 2025 and setting an ambitious new target for 2026 that would push it into a higher league of global EV producers. The company said it delivered 196,919 electric vehicles worldwide in 2025... The surge was driven largely by booming demand in its home market of Vietnam, where VinFast has rapidly expanded its lineup and charging network while benefiting from strong brand recognition and government support for electrification.
-answer: VinFast Auto Ltd. achieved a record-breaking performance in 2025 by delivering 196,919 electric vehicles, nearly doubling its previous year's total and establishing Vietnam as a primary backbone for global EV growth. Supported by the VN-EV-2030 electrification goals and an expanding domestic charging network infrastructure, the company has set an ambitious target of 300,000 deliveries for 2026 as it scales operations in international markets like North America and Europe.
-Source: [gulfnews.com](https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570)</t>
+          <t>[Other] VinFast's breakout year: Vietnamese EV maker nearly doubles sales ... — With nearly 200,000 EVs sold in 2025 and a 300,000-unit target for 2026, VinFast is no longer just an ambitious startup from Vietnam. It is ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>## [https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570](https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570)
-### Document Overview
-The article reports on VinFast's record-breaking sales in 2025, reaching nearly 200,000 EVs, and its ambitious target of 300,000 deliveries for 2026 driven by domestic dominance and international expansion.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: VinFast Auto Ltd. is coming off its strongest year yet, nearly doubling global deliveries in 2025... The surge was driven largely by booming demand in its home market of Vietnam, where VinFast has rapidly expanded its lineup and charging network... VinFast has now set a bold goal for 2026: 300,000 EV deliveries.
-answer: VinFast đã ghi nhận sự tăng trưởng bùng nổ trong năm 2025 với gần 197.000 xe điện được bàn giao toàn cầu, chủ yếu nhờ vào sự thống trị tại thị trường Việt Nam và việc mở rộng mạng lưới trạm sạc. Dựa trên đà phát triển này, hãng xe điện Việt Nam đã đặt mục tiêu đầy tham vọng cho năm 2026 là đạt 300.000 xe, khẳng định vị thế ngày càng lớn mạnh trên bản đồ sản xuất xe điện thế giới.
-Source: [gulfnews.com](https://gulfnews.com/business/energy/vinfasts-breakout-year-vietnamese-ev-maker-nearly-doubles-sales-in-2025-eyes-300000-deliveries-in-2026-1.500497570)</t>
+          <t>[Other] VinFast's breakout year: Vietnamese EV maker nearly doubles sales ... — With nearly 200,000 EVs sold in 2025 and a 300,000-unit target for 2026, VinFast is no longer just an ambitious startup from Vietnam. It is ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -8138,32 +6524,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/](https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/)
-### Document Overview
-This page is a Facebook post from vnauto.net regarding Vingroup's decision to extend its emergency support program for the transition to electric vehicles in Vietnam.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: VN-EV-2030
-verbatim: Vingroup Extends Emergency Support Program for Electric Vehicle Transition until...
-answer: 빈그룹(Vingroup)은 베트남의 전기차 전환 촉진 및 인프라 구축을 지원하기 위해 긴급 지원 프로그램을 연장했습니다. 본 프로그램은 'VN-EV-2030' 마스터플랜에 따라 교통 및 인프라 분야에서 전기차 보급을 가속화하는 것을 목표로 하며, 소비자들의 전기차 전환 장벽을 낮추는 데 중점을 둡니다.
-Source: [www.facebook.com](https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/)</t>
+          <t>[Transport &amp; Infrastructure] Vingroup Extends Emergency Support Program for Electric Vehicle ... — Vingroup Extends Emergency Support Program for Electric Vehicle Transition Until April 30, 2026, to Continue Alleviating Fuel Supply and ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/](https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/)
-### Document Overview
-The page is a social media post from vnauto.net announcing that Vingroup is extending its support program for electric vehicle transition in Vietnam.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: VN-EV-2030
-verbatim: Vingroup Extends Emergency Support Program for Electric Vehicle Transition until...
-answer: Vingroup has extended its emergency support program aimed at accelerating the transition to electric vehicles in Vietnam, directly supporting the transport sector's infrastructure goals. This initiative aligns with the VN-EV-2030 strategic objectives by providing incentives and support mechanisms to increase EV adoption and charging accessibility across the country.
-Source: [www.facebook.com](https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/)</t>
+          <t>[Transport &amp; Infrastructure] Vingroup Extends Emergency Support Program for Electric Vehicle ... — Vingroup Extends Emergency Support Program for Electric Vehicle Transition Until April 30, 2026, to Continue Alleviating Fuel Supply and ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/](https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/)
-### Document Overview
-Trang web không hiển thị nội dung bài báo do lỗi tương thích trình duyệt trên nền tảng Facebook.
-Source: [www.facebook.com](https://www.facebook.com/vnauto.net/posts/vingroup-extends-emergency-support-program-for-electric-vehicle-transition-until/1628855245304847/)</t>
+          <t>[Transport &amp; Infrastructure] Vingroup Extends Emergency Support Program for Electric Vehicle ... — Vingroup Extends Emergency Support Program for Electric Vehicle Transition Until April 30, 2026, to Continue Alleviating Fuel Supply and ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -8217,35 +6588,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>## [https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount](https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount)
-### Document Overview
-Vietnam is accelerating its electric vehicle transition to mitigate energy security risks, mandating new infrastructure standards and production incentives by mid-2024.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-EV-2030
-verbatim: A directive dated Mar 19 called for expanded EV adoption, development of charging infrastructure and accelerated shift of public fleets towards electric power. In the document, Chinh framed transport electrification as one of the key measures to cut reliance on imported fuels and protect the economy from volatile global energy markets... Regulators are tasked with introducing technical and safety standards for EV charging systems by the third quarter of 2026, while incentives to support EV production and adoption are due by June.
-answer: 베트남 정부는 에너지 안보 강화와 수입 연료 의존도 절감을 위해 전기차(EV) 전환 및 충전 인프라 확대를 가속화하는 지침을 발표했습니다. 이에 따라 2024년 6월까지 EV 생산 및 채택 지원을 위한 인센티브를 도입하고, 2026년 3분기까지 충전 시스템의 기술 및 안전 표준을 마련할 계획입니다. 이러한 정책적 흐름은 빈패스트(VinFast)와 같은 현지 기업의 성장을 뒷받침하며 주거 단지 내 충전 시설 통합 등 도시 계획의 변화를 동반하고 있습니다.
-Source: [www.businesstimes.com.sg](https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount)</t>
+          <t>[Power &amp; Energy] Vietnam pushes EV shift as energy security risks mount — Incentives to support electric vehicle production and adoption are required to be introduced by June. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>## [https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount](https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount)
-### Document Overview
-The article details Vietnam's government-led push for electric vehicle adoption and infrastructure development to enhance energy security and reduce reliance on volatile global fuel markets.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-EV-2030
-verbatim: Vietnam is stepping up its transition to electric vehicles (EV) amid rising energy security risks, with Prime Minister Pham Minh Chinh ordering faster electrification of transport alongside sweeping energy-saving measures. A directive dated Mar 19 called for expanded EV adoption, development of charging infrastructure and accelerated shift of public fleets towards electric power... Regulators are tasked with introducing technical and safety standards for EV charging systems by the third quarter of 2026, while incentives to support EV production and adoption are due by June.
-answer: Vietnam is accelerating its transition to electric vehicles (EVs) through a new government directive to mitigate energy security risks and reduce reliance on imported fuels. Key infrastructure developments include the mandatory introduction of technical safety standards for EV charging by Q3 2026, the integration of charging stations into residential and urban planning, and the implementation of incentives for EV production and adoption by June. This shift is supported by provincial policies promoting clean-energy public transport and local manufacturers like VinFast expanding their charging networks and fleet electrification.
-Source: [www.businesstimes.com.sg](https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount)</t>
+          <t>[Power &amp; Energy] Vietnam pushes EV shift as energy security risks mount — Incentives to support electric vehicle production and adoption are required to be introduced by June. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>## [https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount](https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount)
-### Document Overview
-The article discusses Vietnam's strategic push for electric vehicle adoption and infrastructure development through government directives to mitigate energy security risks and reduce imported fuel reliance.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is stepping up its transition to electric vehicles (EV) amid rising energy security risks, with Prime Minister Pham Minh Chinh ordering faster electrification of transport alongside sweeping energy-saving measures. A directive dated Mar 19 called for expanded EV adoption, development of charging infrastructure and accelerated shift of public fleets towards electric power... Regulators are tasked with introducing technical and safety standards for EV charging systems by the third quarter of 2026, while incentives to support EV production and adoption are due by June.
-answer: Thủ tướng Việt Nam đã ban hành chỉ thị thúc đẩy chuyển đổi sang xe điện (EV) nhằm đảm bảo an ninh năng lượng và giảm phụ thuộc vào nhiên liệu nhập khẩu. Chính phủ yêu cầu triển khai nhanh chóng cơ sở hạ tầng trạm sạc, ban hành tiêu chuẩn kỹ thuật vào quý 3 năm 2026 và đưa ra các chính sách ưu đãi sản xuất xe điện trước tháng 6. Các đô thị cũng được định hướng tích hợp trạm sạc vào quy hoạch nhà ở và bãi đỗ xe để hỗ trợ các doanh nghiệp nội địa như VinFast.
-Source: [www.businesstimes.com.sg](https://www.businesstimes.com.sg/international/asean/vietnam-pushes-ev-shift-energy-security-risks-mount)</t>
+          <t>[Power &amp; Energy] Vietnam pushes EV shift as energy security risks mount — Incentives to support electric vehicle production and adoption are required to be introduced by June. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -8295,35 +6648,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>## [https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819](https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819)
-### Document Overview
-This academic article analyzes Vietnam's electric vehicle transition through the lens of 'Green Windows of Opportunity,' focusing on VinFast's strategy and the government's 2030/2050 decarbonization targets.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-EV-2030
-verbatim: The most notable response to the electromobility GWO came from the private enterprise sector. Vinfast announced in January 2021... the Vietnamese government only in July 2022 declared its intention to decarbonize transportation by approving the ‘Action Program on Green Energy Transportation – Reduction of Carbon and Methane Emissions of the Transportation Industry’ (Decision 876/QD-TTg). This programme outlined several targets such as 50 percent of urban vehicles should use electricity by 2030 or complete shift to electromobility and green energy by 2050 (A8).
-answer: 베트남 정부는 '녹색 에너지 교통 액션 프로그램(Decision 876/QD-TTg)'을 통해 2030년까지 도시 차량의 50%를 전기차로 전환하고 2050년까지 완전한 전동화를 달성하겠다는 목표를 설정했습니다. 이에 따라 민간 기업인 빈패스트(VinFast)는 전국에 15만 개의 충전 포트를 설치하는 등 에너지 인프라 확충에 앞장서고 있으나, 규모의 경제 달성과 충전 인프라의 국가적 통합은 여전한 과제로 남아 있습니다.
-Source: [www.tandfonline.com](https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819)</t>
+          <t>[Power &amp; Energy] The electric vehicle transition as a green window of opportunity ... — The general tendency of weak technology ownership in the Vietnamese automotive industry applies to locally made EVs. Vinfast sources key technologies such as ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>## [https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819](https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819)
-### Document Overview
-This article analyzes Vietnam's transition to electric vehicles, focusing on the startup Vinfast and the government's 2030/2050 green energy targets while discussing the economic barriers of the automotive industry.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-EV-2030
-verbatim: The Vietnamese government only in July 2022 declared its intention to decarbonize transportation by approving the ‘Action Program on Green Energy Transportation – Reduction of Carbon and Methane Emissions of the Transportation Industry’ (Decision 876/QD-TTg). This programme outlined several targets such as 50 percent of urban vehicles should use electricity by 2030 or complete shift to electromobility and green energy by 2050. ... Vinfast addressed the lack of charging infrastructure in Vietnam by installing 150,000 charging points in 3,000 charging stations across the country at the end of 2023.
-answer: Under the 'Action Program on Green Energy Transportation' (Decision 876/QD-TTg), Vietnam aims to have 50% of urban vehicles powered by electricity by 2030 as part of a broader plan to reach full electromobility by 2050. To support this energy transition, the domestic carmaker Vinfast has already established significant power infrastructure, deploying 150,000 charging points across 3,000 stations nationwide as of late 2023.
-Source: [www.tandfonline.com](https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819)</t>
+          <t>[Power &amp; Energy] The electric vehicle transition as a green window of opportunity ... — The general tendency of weak technology ownership in the Vietnamese automotive industry applies to locally made EVs. Vinfast sources key technologies such as ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>## [https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819](https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819)
-### Document Overview
-This academic article examines Vietnam's electric vehicle transition through the lens of VinFast, analyzing whether the shift from ICE to EV technology creates a viable 'green window of opportunity' for latecomer countries.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: This article first analyses the automotive industry paradigm and then discusses the implications for the case of Vietnamese carmaker Vinfast which seeks to exploit the postulated green window of opportunity... The case of Vinfast illustrates the issue of remaining entry barriers to the automotive industry. Despite eased entry conditions due to powertrain sub-paradigm disruption, economies of scale stemming from steel body production remain a significant barrier.
-answer: Bài báo phân tích quá trình chuyển đổi sang xe điện tại Việt Nam thông qua trường hợp của VinFast, nhấn mạnh nỗ lực tận dụng 'cửa sổ cơ hội xanh' để bắt kịp ngành công nghiệp ô tô toàn cầu. Tuy nhiên, nghiên cứu chỉ ra rằng dù công nghệ truyền động thay đổi, các rào cản gia nhập thị trường vẫn rất lớn do yêu cầu khắt khe về quy mô sản xuất thân vỏ thép và khả năng tích hợp hệ thống. Kết luận cho thấy các doanh nghiệp mới như VinFast đối mặt với thách thức nghiêm trọng về tính kinh tế theo quy mô và sự cạnh tranh gay gắt từ các đối thủ lâu đời cũng như các nhà sản xuất Trung Quốc.
-Source: [www.tandfonline.com](https://www.tandfonline.com/doi/full/10.1080/2157930X.2026.2619819)</t>
+          <t>[Power &amp; Energy] The electric vehicle transition as a green window of opportunity ... — The general tendency of weak technology ownership in the Vietnamese automotive industry applies to locally made EVs. Vinfast sources key technologies such as ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -8377,35 +6712,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>## [https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam](https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam)
-### Document Overview
-This article evaluates the rise of VinFast electric vehicles in Vietnam, contrasting corporate sustainability claims with the reality of a coal-heavy power grid and lack of charging infrastructure.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Vietnam—like many other South East Asian countries—relies heavily on fossil fuels in order to generate electricity... At 8.2 cent per kWh (US average is 17.9 cents), the abundant coal reserves keep the price artificially down and make up roughly 80 percent of the country’s energy mix... another crucial element for EV viability is a reliable charging grid... In my day-to-day commutes around HCMC, charging stations were virtually nonexistent.
-answer: 베트남의 전기차(EV) 시장은 빈패스트(VinFast)를 중심으로 급성장하고 있으나, 충전 인프라 부족과 화석 연료 의존도가 높은 에너지 믹스라는 근본적인 한계에 직면해 있습니다. 현재 베트남 전력 생산의 약 80%가 저렴한 석탄 화력 발전에 의존하고 있어 전기차의 실제 친환경성에 대한 의문이 제기되고 있으며, 호치민시와 같은 대도시에서도 공공 충전 네트워크가 거의 구축되지 않은 실정입니다. 따라서 진정한 지속 가능한 모빌리티 실현을 위해서는 기업의 마케팅을 넘어 전력 인프라 개선과 정직한 에너지 시스템 구축이 필요하다는 분석입니다.
-Source: [www.milkenscholars.org](https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam)</t>
+          <t>[Power &amp; Energy] The Future of Sustainable Vehicles in Vietnam - Milken Scholars — I traveled to Vietnam to learn more about VinFast's rapid rise and to investigate whether its pledge to promote a more sustainable energy ecosystem holds up in ...</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>## [https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam](https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam)
-### Document Overview
-This article evaluates the rise of VinFast in Vietnam, highlighting the gap between corporate green marketing and the reality of a coal-dependent energy grid and lack of charging infrastructure.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: In my day-to-day commutes around HCMC, charging stations were virtually nonexistent—I only spotted one during my entire visit... The massive infrastructure effort that allowed Tesla to install Superchargers across the U.S. remains out of reach in Vietnam, where densely packed streets and outdated electrical systems pose serious challenges... Vietnam—like many other South East Asian countries—relies heavily on fossil fuels in order to generate electricity... abundant coal reserves keep the price artificially down and make up roughly 80 percent of the country’s energy mix.
-answer: Vietnam's electric vehicle infrastructure faces significant challenges as charging stations remain virtually nonexistent in major cities like Ho Chi Minh City due to densely packed streets and an outdated electrical grid. Furthermore, the sustainability of the sector is questioned because approximately 80% of the country's energy mix is powered by coal, raising concerns about the net environmental impact of switching to EVs.
-Source: [www.milkenscholars.org](https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam)</t>
+          <t>[Power &amp; Energy] The Future of Sustainable Vehicles in Vietnam - Milken Scholars — I traveled to Vietnam to learn more about VinFast's rapid rise and to investigate whether its pledge to promote a more sustainable energy ecosystem holds up in ...</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>## [https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam](https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam)
-### Document Overview
-The article critically examines the rise of VinFast and electric vehicles in Vietnam, highlighting the gap between corporate sustainability marketing and the reality of a fossil-fuel-dependent power grid and underdeveloped charging infrastructure.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: VinFast is a fully electric vehicle (EV) company and the first mainstream automotive manufacturer founded in Southeast Asia... Another crucial element for EV viability is a reliable charging grid, which makes both long-distance travel and daily driving feasible. In my day-to-day commutes around HCMC, charging stations were virtually nonexistent... Vietnam—like many other South East Asian countries—relies heavily on fossil fuels in order to generate electricity.
-answer: Bài viết phân tích sự trỗi dậy của VinFast tại Việt Nam, đồng thời chỉ ra những thách thức lớn về cơ sở hạ tầng như mạng lưới trạm sạc còn hạn chế và hệ thống điện lưới cũ kỹ. Tác giả cũng đặt câu hỏi về tính bền vững thực sự của xe điện khi nguồn điện năng tại Việt Nam vẫn phụ thuộc chủ yếu vào than đá (chiếm khoảng 80%) và các hành vi tiếp thị xanh của tập đoàn VinGroup.
-Source: [www.milkenscholars.org](https://www.milkenscholars.org/features/show/the-future-of-sustainable-vehicles-in-vietnam)</t>
+          <t>[Power &amp; Energy] The Future of Sustainable Vehicles in Vietnam - Milken Scholars — I traveled to Vietnam to learn more about VinFast's rapid rise and to investigate whether its pledge to promote a more sustainable energy ecosystem holds up in ...</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -8459,35 +6776,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0](https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0)
-### Document Overview
-This page reports on VinFast's initiative to extend its free charging policy for three years and Vingroup's 'Trade Gas for Electric' discount program across Southeast Asia and India.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Other, 관련 마스터플랜: N/A
-verbatim: Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets. The incentive applies to all private customers and commercial operators, including drivers on the Green SM ride-hailing platform. Vingroup, the parent company of VinFast, had recently introduced the ‘Trade Gas for Electric’ programme in India, Indonesia, the Philippines and Vietnam.
-answer: 베트남 자동차 기업 빈패스트(VinFast)는 운영 중인 모든 시장에서 개인 및 상업용 고객을 대상으로 무료 충전 정책을 3년간 연장한다고 발표했습니다. 모기업인 빈그룹(Vingroup)은 베트남, 인도, 인도네시아, 필리핀에서 내연기관 차량을 전기차나 전기 스쿠터로 전환할 시 최대 5%의 할인을 제공하는 'Trade Gas for Electric' 프로그램을 시행합니다. 이번 조치는 친환경 모빌리티 전환을 가속화하기 위한 전략의 일환입니다.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0)</t>
+          <t>[Other] VinFast Extends Free Charging Policy Across Markets - LinkedIn — Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0](https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0)
-### Document Overview
-The page reports on VinFast's three-year extension of free EV charging and Vingroup's regional incentive program to encourage the transition from petrol to electric vehicles.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Other, Related plans: N/A
-verbatim: Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets. The incentive applies to all private customers and commercial operators, including drivers on the Green SM ride-hailing platform. Vingroup, the parent company of VinFast, had recently introduced the ‘Trade Gas for Electric’ programme in India, Indonesia, the Philippines and Vietnam.
-answer: VinFast has announced a three-year extension of its free electric vehicle charging policy across its operational markets, benefiting private owners and commercial operators like Green SM ride-hailing drivers. Additionally, parent company Vingroup launched the 'Trade Gas for Electric' program in Vietnam and other Asian markets, offering discounts of 3% on electric cars and 5% on electric scooters for customers switching from petrol vehicles until March 31, 2026.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0)</t>
+          <t>[Other] VinFast Extends Free Charging Policy Across Markets - LinkedIn — Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets.</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>## [https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0](https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0)
-### Document Overview
-This post discusses VinFast's expansion of its free charging policy for three years and Vingroup's 'Trade Gas for Electric' incentive program in Vietnam and other international markets.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets. The incentive applies to all private customers and commercial operators, including drivers on the Green SM ride-hailing platform. Vingroup, the parent company of VinFast, had recently introduced the ‘Trade Gas for Electric’ programme in India, Indonesia, the Philippines and Vietnam.
-answer: VinFast vừa công bố gia hạn chính sách sạc pin miễn phí thêm 3 năm tại các thị trường hoạt động, áp dụng cho cả khách hàng cá nhân lẫn các đơn vị vận tải như Xanh SM. Bên cạnh đó, tập đoàn Vingroup cũng triển khai chương trình 'Đổi xe xăng lấy xe điện' tại Việt Nam và một số nước Đông Nam Á với mức ưu đãi giảm giá từ 3% đến 5%. Đây là những nỗ lực nhằm thúc đẩy việc chuyển đổi sang phương tiện giao thông xanh và phát triển hạ tầng trạm sạc xe điện.
-Source: [www.linkedin.com](https://www.linkedin.com/posts/motoring-trends_vinfast-vingroup-activity-7439288469694095361-AY_0)</t>
+          <t>[Other] VinFast Extends Free Charging Policy Across Markets - LinkedIn — Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets.</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -8541,32 +6840,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>## [https://www.instagram.com/p/DWDU-dIj4Pc/](https://www.instagram.com/p/DWDU-dIj4Pc/)
-### Document Overview
-This Instagram post highlights Vietnam's rapid EV market growth in 2025, led by VinFast's record-breaking sales and a surge in electric motorbike adoption.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Other, 관련 마스터플랜: VN-EV-2030
-verbatim: In 2025, VinFast delivered around 175,000 electric cars in Vietnam, setting a new record and becoming the country’s top automotive brand... More than 400,000 electric motorbikes were sold in 2025 alone... Charging infrastructure is improving, but still a concern.
-answer: 2025년 베트남 전기차 시장은 빈패스트(VinFast)가 약 175,000대를 인도하며 전국 자동차 브랜드 1위에 오르는 등 기록적인 성장을 달성했습니다. 전기 오토바이 판매 또한 40만 대를 돌파하며 동남아시아에서 가장 빠르게 성장하는 전기차 시장으로 부상했으나, 충전 인프라 확충과 도심 내 내연기관차 제한 정책에 대한 논의는 여전히 과제로 남아 있습니다. (섹터: 기타, 관련 마스터플랜: VN-EV-2030)
-Source: [www.instagram.com](https://www.instagram.com/p/DWDU-dIj4Pc/)</t>
+          <t>[Other] Vietnam's EV market is gaining momentum In 2025, VinFast ... — Vietnamese EV maker VinFast has posted a 63% jump in electric vehicle deliveries in 2025, delivering 196,919 EVs and generating US$3.6 ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>## [https://www.instagram.com/p/DWDU-dIj4Pc/](https://www.instagram.com/p/DWDU-dIj4Pc/)
-### Document Overview
-The page reports on the record-breaking growth of Vietnam's EV market in 2025, highlighted by VinFast's market leadership and high sales volumes for both electric cars and motorbikes.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Other, Related plans: VN-EV-2030
-verbatim: In 2025, VinFast delivered around 175,000 electric cars in Vietnam, setting a new record and becoming the country’s top automotive brand. At the same time, the company reached $3.6 billion in revenue... More than 400,000 electric motorbikes were sold in 2025 alone... Charging infrastructure is improving, but still a concern.
-answer: Vietnam's electric vehicle market saw significant expansion in 2025, with VinFast becoming the country's top automotive brand by delivering 175,000 electric cars and achieving $3.6 billion in revenue. The growth is further supported by the sale of over 400,000 electric motorbikes and ongoing improvements to charging infrastructure, aligning with the VN-EV-2030 transition goals. Despite this momentum, the sector faces challenges including infrastructure concerns and the continued dominance of internal combustion engine vehicles.
-Source: [www.instagram.com](https://www.instagram.com/p/DWDU-dIj4Pc/)</t>
+          <t>[Other] Vietnam's EV market is gaining momentum In 2025, VinFast ... — Vietnamese EV maker VinFast has posted a 63% jump in electric vehicle deliveries in 2025, delivering 196,919 EVs and generating US$3.6 ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>## [https://www.instagram.com/p/DWDU-dIj4Pc/](https://www.instagram.com/p/DWDU-dIj4Pc/)
-### Document Overview
-Nội dung được cung cấp là trang đăng nhập Instagram và không chứa thông tin về cơ sở hạ tầng Việt Nam theo yêu cầu của người dùng.
-Source: [www.instagram.com](https://www.instagram.com/p/DWDU-dIj4Pc/)</t>
+          <t>[Other] Vietnam's EV market is gaining momentum In 2025, VinFast ... — Vietnamese EV maker VinFast has posted a 63% jump in electric vehicle deliveries in 2025, delivering 196,919 EVs and generating US$3.6 ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -8620,35 +6904,17 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html](https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html)
-### Document Overview
-This article discusses Vietnam's national conference on environmental protection in the fisheries sector, focusing on sustainable practices, waste reduction, and the 2026-2030 priority plan supported by international partners.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: N/A
-verbatim: Việt Nam has launched a fresh push to curb pollution across its fisheries sector, warning that rising seas, degraded ecosystems and falling fish stocks are already squeezing the livelihoods of millions of coastal residents. Officials, international partners and industry representatives gathered in Hà Nội on Wednesday for a national conference on environmental protection in fisheries... The meeting reviewed three years of progress under a Government plan to reduce waste and modernise practices in aquaculture and fishing, and set out priorities for the 2026–2030 period.
-answer: 베트남 정부는 수산 부문의 오염을 줄이고 해안 생태계를 보호하기 위해 UNDP 및 캐나다 대사관과 협력하여 2026-2030년 우선순위 계획을 수립했습니다. 이 계획은 기후 위기에 대응하기 위해 순환 경제 모델 도입, 폐기물 관리 강화, 디지털 전환 및 친환경 기술 확대를 골자로 하며, 이를 통해 지속 가능한 수산물 생산 체계를 구축하고자 합니다. 특히 '기후 스마트 해안 커뮤니티' 프로젝트를 통해 맹그로브 복원과 해양 플라스틱 오염 해결을 위한 지속적인 투자가 강조되었습니다.
-Source: [vietnamnews.vn](https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html)</t>
+          <t>[Environment &amp; Climate] Việt Nam outlines new plan to cut waste, protect coastal ... — HÀ NỘI — Việt Nam has launched a fresh push to curb pollution across its fisheries sector, warning that rising seas, degraded ecosystems and ...</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html](https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html)
-### Document Overview
-The article reports on a national conference in Hanoi where Vietnam outlined plans for 2026-2030 to modernize its fisheries sector through waste reduction, technology adoption, and ecosystem restoration.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: N/A
-verbatim: Việt Nam has launched a fresh push to curb pollution across its fisheries sector, warning that rising seas, degraded ecosystems and falling fish stocks are already squeezing the livelihoods of millions of coastal residents. Officials, international partners and industry representatives gathered in Hà Nội on Wednesday for a national conference on environmental protection in fisheries... to reduce waste and modernise practices in aquaculture and fishing, and set out priorities for the 2026–2030 period.
-answer: Vietnam has launched a comprehensive initiative to combat pollution in its fisheries sector, addressing environmental challenges like rising sea levels and degraded ecosystems to protect coastal livelihoods. The government, supported by the UNDP and Canada, is prioritizing the adoption of circular economy models, cleaner technologies, and digital transformation for the 2026–2030 period. This effort includes the Climate-Smart Coastal Communities project, which focuses on mangrove restoration and improving environmental infrastructure to ensure a sustainable and climate-resilient seafood industry.
-Source: [vietnamnews.vn](https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html)</t>
+          <t>[Environment &amp; Climate] Việt Nam outlines new plan to cut waste, protect coastal ... — HÀ NỘI — Việt Nam has launched a fresh push to curb pollution across its fisheries sector, warning that rising seas, degraded ecosystems and ...</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html](https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html)
-### Document Overview
-The article discusses Vietnam's national conference on environmental protection in fisheries, highlighting the progress and future priorities (2026-2030) for sustainable aquaculture and waste management.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Việt Nam has launched a fresh push to curb pollution across its fisheries sector... The meeting reviewed three years of progress under a Government plan to reduce waste and modernise practices in aquaculture and fishing, and set out priorities for the 2026–2030 period... environmental protection infrastructure is still limited, cleaner technologies are not yet widespread and the burden of waste continues to grow.
-answer: Việt Nam đang đẩy mạnh kế hoạch hiện đại hóa ngành thủy sản và bảo vệ hệ sinh thái ven biển giai đoạn 2026-2030 nhằm đối phó với tình trạng ô nhiễm và biến đổi khí hậu. Mặc dù đã đạt được một số tiến bộ về kinh tế tuần hoàn, bài báo nhấn mạnh rằng cơ sở hạ tầng bảo vệ môi trường của Việt Nam vẫn còn hạn chế và cần được đầu tư nâng cấp hệ thống giám sát hiện đại. Hội nghị cũng kêu gọi sự phối hợp liên ngành và hỗ trợ quốc tế để chuyển đổi sang mô hình sản xuất xanh, bền vững hơn.
-Source: [vietnamnews.vn](https://vietnamnews.vn/society/1730515/viet-nam-outlines-new-plan-to-cut-waste-protect-coastal-ecosystems.html)</t>
+          <t>[Environment &amp; Climate] Việt Nam outlines new plan to cut waste, protect coastal ... — HÀ NỘI — Việt Nam has launched a fresh push to curb pollution across its fisheries sector, warning that rising seas, degraded ecosystems and ...</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -8702,29 +6968,17 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>## [https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)
-### Document Overview
-This page provides an announcement about RTI International's involvement in a Vietnam industrial risk study focusing on air and water pollution.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894, VN-EV-2030
-verbatim: RTI International is an independent scientific research institute dedicated to improving the human condition. Our vision is to address the world's most critical problems with technical and science-based solutions in pursuit of a better future. Clients rely on us to answer questions that demand an objective and multidisciplinary approach—one that integrates expertise across social, statistical, data, and laboratory sciences, engineering, and other technical disciplines to solve the world’s most challenging problems.
-answer: RTI International은 베트남의 대기 및 수질 오염에 관한 산업 리스크 연구를 수행하며, 환경 및 기후 섹터의 지속 가능한 발전을 도모하고 있습니다. 이 연구는 마스터플랜 VN-ENV-IND-1894 및 VN-EV-2030과 연계되어 베트남 산업 현장의 환경 문제를 과학적으로 분석하고 해결책을 제시하는 데 중점을 둡니다. 이를 통해 다학제적 접근 방식으로 베트남의 환경 인프라를 개선하고 사회적 난제를 해결하는 것을 목표로 합니다.
-Source: [www.rti.org](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)</t>
+          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>## [https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)
-### Document Overview
-This page provides an overview of RTI International's mission and expertise as a scientific research institute but lacks specific content regarding the Vietnam air and water pollution study.
-Source: [www.rti.org](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)</t>
+          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>## [https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)
-### Document Overview
-Trang web này giới thiệu về RTI International, một viện nghiên cứu khoa học độc lập, nhưng thiếu nội dung chi tiết về báo cáo ô nhiễm và hạ tầng tại Việt Nam như tiêu đề gợi ý.
-Source: [www.rti.org](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)</t>
+          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -8774,32 +7028,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>## [https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)
-### Document Overview
-This document outlines the environmental consequences of Vietnam's rapid industrialization, focusing on air pollution in major cities and industrial water contamination as of the 2026 edition.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894
-verbatim: Since the Doi Moi reforms, Vietnam has transformed into a global manufacturing hub... the rapid pace of industrialization—particularly in electronics, textiles, and heavy industry—has placed immense strain on the country's air, water, and soil resources. Air pollution is currently the primary environmental health concern in urban centers... Vietnam possesses dense river networks, but many 'dead rivers' exist near industrial zones.
-answer: 베트남은 도이머이 혁신 이후 글로벌 제조 허브로 성장했으나, 전자 및 섬유 등 급격한 산업화로 인해 대기, 수질, 토양 자원에 심각한 부담을 안고 있습니다. 특히 하노이와 호치민 같은 주요 도시의 대기 오염과 산업 단지 인근의 '죽은 강' 문제는 해결해야 할 주요 환경 과제로 부상하고 있습니다. 이에 따라 환경 및 기후 섹터(VN-ENV-IND-1894 관련)에서는 산업 폐수 처리 및 대기 오염 물질 배출 규제 준수를 통한 지속 가능한 전환이 강조되고 있습니다.
-Source: [www.studocu.vn](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)</t>
+          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (관련: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>## [https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)
-### Document Overview
-The page is a document hosting site (Studocu) showing a placeholder for a report titled 'Environmental Impact of Industrialization 2026 Edition' from International University VNU-HCM, but the content is restricted to logged-in users.
-Source: [www.studocu.vn](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)</t>
+          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (Related: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>## [https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)
-### Document Overview
-This report examines the environmental costs of Vietnam's industrial growth, focusing on air pollution in urban centers and water contamination from industrial zones as of 2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Since the Doi Moi reforms, Vietnam has transformed into a global manufacturing hub ("The Factory of the World"). While this has lifted millions out of poverty, the rapid pace of industrialization—particularly in electronics, textiles, and heavy industry—has placed immense strain on the country's air, water, and soil resources. ... Air pollution is currently the primary environmental health concern in urban centers. ... Vietnam possesses dense river networks, but many "dead rivers" exist near industrial zones.
-answer: Báo cáo phân tích rằng quá trình công nghiệp hóa nhanh chóng của Việt Nam kể từ thời kỳ Đổi Mới đã gây áp lực cực lớn lên tài nguyên môi trường, đặc biệt là ô nhiễm không khí tại các đô thị lớn và sự xuất hiện của các 'dòng sông chết' gần khu công nghiệp. Tài liệu nhấn mạnh thách thức trong việc quản lý khí thải từ nhiệt điện, xi măng và xử lý nước thải công nghiệp từ các ngành dệt nhuộm, điện tử để hướng tới quá trình chuyển đổi bền vững năm 2026.
-Source: [www.studocu.vn](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)</t>
+          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (Liên quan: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -8853,35 +7092,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)
-### Document Overview
-The article highlights various environmental initiatives in Vietnam, including forest conservation, ozone depletion mitigation, and urban emission controls, framing the country's green development strategy for 2025-2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894
-verbatim: Vietnam’s forest coverage rate remained stable at 42.03% in 2025, with total forest area estimated at 14,971,553 ha, according to the Ministry of Agriculture and Environment (MAE). ... Vietnam launches 13 mln USD project to phase out ozone-depleting substances ... Hanoi, Ho Chi Minh City to begin motorcycle emissions testing from July 2027 ... Cuc Phuong Rewilding Action Plan 2026–2035, with a vision to 2050.
-answer: 베트남은 2025년 기준 42.03%의 안정적인 산림 피복률을 유지하고 있으며, 2026-2031년 사이 1,300만 달러 규모의 오존층 파괴 물질 단계적 제거 프로젝트를 추진하여 국제적 환경 약속을 이행하고 있습니다. 또한 2027년 하노이와 호치민을 시작으로 오토바이 배기가스 검사를 의무화하고 국립공원의 야생동물 유전자원 뱅크화를 추진하는 등 'VN-ENV-IND-1894'와 연계된 환경 및 기후 변화 대응 인프라 구축에 박차를 가하고 있습니다.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)</t>
+          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (관련: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)
-### Document Overview
-The article outlines Vietnam's environmental strategies for 2025-2030, highlighting forest conservation, urban emissions testing, and international cooperation to phase out ozone-depleting substances.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-ENV-IND-1894
-verbatim: Vietnam’s forest coverage rate remained stable at 42.03% in 2025, with total forest area estimated at 14,971,553 ha... The project aims to help Vietnam meet its international commitments in managing and phasing out controlled substances. It will run from 2026 to 2031 with a total budget of over 13 million USD... Hanoi, Ho Chi Minh City to begin motorcycle emissions testing from July 2027.
-answer: Vietnam is advancing its environmental infrastructure through a multi-faceted approach, including maintaining a national forest coverage rate of 42.03% and launching a 13 million USD project to phase out ozone-depleting substances by 2031. Key urban initiatives involve the implementation of motorcycle emissions testing in Hanoi and Ho Chi Minh City starting in July 2027, eventually expanding nationwide by 2030. These efforts are complemented by a focus on sustainable wetland restoration in the Mekong Delta and the enhancement of hydrometeorological observation systems for better disaster resilience.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)</t>
+          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (Related: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)
-### Document Overview
-Trang web tổng hợp các tin tức về bảo tồn thiên nhiên, đa dạng sinh học, và các kế hoạch hạ tầng môi trường tại Việt Nam giai đoạn 2025-2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam launches 13 mln USD project to phase out ozone-depleting substances... Hanoi, Ho Chi Minh City to begin motorcycle emissions testing from July 2027... National forest coverage holds steady at 42.03% in 2025... Vietnam secures nearly 72 million USD in green finance support... observation systems key to stronger forecasting, sustainable development.
-answer: Trang tin tổng hợp các hoạt động về môi trường và cơ sở hạ tầng bền vững tại Việt Nam, nổi bật là kế hoạch kiểm tra khí thải xe máy tại Hà Nội và TP.HCM từ năm 2027 cùng dự án 13 triệu USD nhằm loại bỏ các chất làm suy giảm tầng ozone. Bên cạnh đó, Việt Nam tập trung nâng cấp hệ thống quan trắc khí tượng và duy trì tỷ lệ che phủ rừng ở mức 42,03% để tăng cường khả năng ứng phó biến đổi khí hậu. Các dự án hợp tác với Ngân hàng Thế giới cũng được đẩy mạnh nhằm cải thiện hệ thống thủy lợi và an ninh nguồn nước tại khu vực Đồng bằng sông Cửu Long.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)</t>
+          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (Liên quan: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -8931,35 +7152,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>## [https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)
-### Document Overview
-This article analyzes the status of industrial waste management in Vietnam, highlighting that while 79% of industrial zones have wastewater treatment systems, many fail to meet environmental standards (QCVN) and lack adequate solid waste infrastructure.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894, VN-EV-2030
-verbatim: By the end of October 2014, out of 209 IPs that have been put into operation, 165 IPs have built a centralized wastewater treatment system, accounting for 79% of the total number of industrial zones in operation... However, in fact, many industrial zones already have wastewater treatment stations but have not operated regularly, and treated wastewater has not met QCVN... Up to now, most industrial zones and industrial zones have not built stations or points for collecting, transferring and treating industrial and hazardous solid waste.
-answer: 베트남 산업단지의 약 79%가 중앙 집중식 폐수 처리 시스템을 구축했으나, 실제 운영 미비와 기준치 미달 방류로 인한 환경 오염 문제가 지속되고 있습니다. 특히 산업 클러스터(CCN)의 폐수 처리 시설 보급률은 5% 수준으로 매우 낮으며, 산업 고체 폐기물 및 유해 폐기물을 위한 전문 수집·처리 센터가 부족하여 환경적 압박이 가중되는 상황입니다. (섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894, VN-EV-2030)
-Source: [vietwaterjsc.com](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)</t>
+          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>## [https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)
-### Document Overview
-This article provides a comprehensive overview of the status of industrial wastewater, emission control, and solid waste management in Vietnam's industrial zones and clusters.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-ENV-IND-1894, VN-EV-2030
-verbatim: By the end of October 2014, out of 209 IPs that have been put into operation, 165 IPs have built a centralized wastewater treatment system, accounting for 79% of the total number of industrial zones in operation... The investment in construction of environmental protection infrastructure has been slow... out of a total of more than 600 CCNs in operation, only about 5% of CCNs have centralized wastewater treatment systems.
-answer: Vietnam is currently upgrading its industrial environmental infrastructure, with approximately 79% of established industrial zones having completed centralized wastewater treatment systems as of late 2014. Despite progress in major economic hubs, environmental protection remains a challenge for industrial clusters (CCNs) where only 5% have centralized treatment, leading to continued pollution risks in surrounding ecosystems. These efforts align with broader national environmental strategies like VN-ENV-IND-1894 and VN-EV-2030 to mitigate the impact of industrial discharge on public health and biodiversity.
-Source: [vietwaterjsc.com](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)</t>
+          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>## [https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)
-### Document Overview
-The article analyzes the current status of wastewater, air emission, and solid waste management infrastructure in Vietnam's industrial zones and clusters as of late 2014.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: By the end of October 2014, out of 209 IPs that have been put into operation, 165 IPs have built a centralized wastewater treatment system, accounting for 79% of the total number of industrial zones in operation... As of October 2014, out of a total of more than 600 CCNs in operation, only about 5% of CCNs have centralized wastewater treatment systems... Up to now, most industrial zones and industrial zones have not built stations or points for collecting, transferring and treating industrial and hazardous solid waste.
-answer: Bài báo đánh giá thực trạng hạ tầng xử lý chất thải công nghiệp tại Việt Nam, ghi nhận khoảng 79% khu công nghiệp đã có hệ thống xử lý nước thải tập trung nhưng hiệu quả vận hành còn chưa đồng đều. Ngược lại, hạ tầng tại các cụm công nghiệp còn rất yếu kém với chỉ 5% có hệ thống xử lý, đồng thời cả nước vẫn đang thiếu hụt trầm trọng các trung tâm thu gom và xử lý rác thải công nghiệp, rác thải nguy hại tập trung.
-Source: [vietwaterjsc.com](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)</t>
+          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -9009,35 +7212,17 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)
-### Document Overview
-Vietnam is launching a new industrial environmental index to regulate over 400 industrial parks as part of its 2021-2030 green growth strategy and 2050 net-zero commitment.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894, VN-EV-2030
-verbatim: The Ministry of Planning last week announced its plan to implement an industrial environmental index to promote sustainable industrial development. Le Thanh Quan, head of the ministry’s department of economic zone management, told local media that the ministry is gathering data and feedback in preparation for the domestic industrial environmental standards. The index is part of Vietnam’s development strategy for green growth for the 2021-2030 period. The country has pledged to reduce solid waste and reach net zero emissions by 2050 at the COP26.
-answer: 베트남 기획투자부는 지속 가능한 산업 발전을 위해 '산업 환경 지수(Industrial Environmental Index)'를 도입할 계획이며, 이는 400개 이상의 산업 단지와 18개 경제 구역에 적용될 예정입니다. 이 지수는 2021-2030 녹색 성장을 위한 국가 전략(VN-EV-2030 등)과 연계되어 폐기물 감소 및 2050년 넷제로 달성을 목표로 하며, 국제 표준을 기반으로 베트남의 환경 역량을 반영해 설계됩니다. 이를 통해 기존의 취약했던 환경 규제 및 집행 능력을 강화하고 친환경 산업 생산 체제로의 전환을 가속화할 방침입니다.
-Source: [vietcetera.com](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)</t>
+          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)
-### Document Overview
-Vietnam is establishing an industrial environmental index to standardize green production and waste management across its 400+ industrial parks to meet 2030 green growth targets.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-ENV-IND-1894, VN-EV-2030
-verbatim: The Ministry of Planning last week announced its plan to implement an industrial environmental index to promote sustainable industrial development. Le Thanh Quan, head of the ministry’s department of economic zone management, told local media that the ministry is gathering data and feedback in preparation for the domestic industrial environmental standards. The index is part of Vietnam’s development strategy for green growth for the 2021-2030 period. The country has pledged to reduce solid waste and reach net zero emissions by 2050 at the COP26.
-answer: Vietnam's Ministry of Planning is implementing a new industrial environmental index to regulate over 400 industrial parks and 18 economic zones, aiming to mitigate severe pollution where 70% of effluents currently go untreated. Part of the country's 2021-2030 green growth strategy (VN-EV-2030) and net-zero 2050 pledge, the index will establish domestic environmental standards based on international frameworks to promote sustainable manufacturing and waste reduction. This initiative, supported by UNIDO, represents a critical shift toward eco-industrial parks and stronger regulatory enforcement in the manufacturing sector.
-Source: [vietcetera.com](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)</t>
+          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)
-### Document Overview
-Bài báo thảo luận về việc Việt Nam thiết lập chỉ số môi trường công nghiệp để quản lý hơn 400 khu công nghiệp, nhằm giải quyết vấn đề ô nhiễm và thực hiện cam kết Net Zero vào năm 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The Ministry of Planning last week announced its plan to implement an industrial environmental index to promote sustainable industrial development. Quan said the establishment of environmental standards in more than 400 industrial parks and 18 economic zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. The index is part of Vietnam’s development strategy for green growth for the 2021-2030 period.
-answer: Bộ Kế hoạch và Đầu tư Việt Nam đang triển khai xây dựng chỉ số môi trường công nghiệp nhằm thúc đẩy phát triển bền vững tại hơn 400 khu công nghiệp và 18 khu kinh tế trên cả nước. Sáng kiến này, được hỗ trợ bởi UNIDO, tập trung vào việc thiết lập các tiêu chuẩn môi trường khắt khe hơn để giảm thiểu tình trạng xả thải chưa qua xử lý và giúp Việt Nam đạt mục tiêu phát thải ròng bằng không vào năm 2050. Đây là một bước đi chiến lược nhằm chuyển đổi các khu sản xuất truyền thống sang mô hình khu công nghiệp sinh thái thân thiện với môi trường theo chuẩn quốc tế.
-Source: [vietcetera.com](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)</t>
+          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -9091,35 +7276,17 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/](https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/)
-### Document Overview
-This page discusses Vietnam's industrial parks transitioning to Intelligent Operations Centers (IOCs) to meet the 2050 Net Zero emissions target and improve global competitiveness.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: N/A
-verbatim: Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented reporting remain. In response, businesses are adopting Intelligent Operations Centers (IOCs) to meet environmental standards and improve efficiency. In the net-zero era, IOCs are emerging as a governance platform, helping industrial zones move beyond infrastructure leasing toward setting standards in global value chains.
-answer: 베트남의 2050년 넷제로(Net Zero) 목표 달성 추진에 따라 실시간 모니터링 체계가 부족한 산업단지들이 환경 기준 준수 압박을 받고 있습니다. 이에 대응하여 기업들은 효율성을 높이고 글로벌 가치 사슬의 표준을 설정하기 위해 지능형 운영 센터(IOC)를 거버넌스 플랫폼으로 도입하고 있습니다. 이를 통해 산업단지는 단순한 인프라 임대업을 넘어 지속 가능한 지능형 산업 생태계로 전환될 것으로 기대됩니다.
-Source: [www.facebook.com](https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/)</t>
+          <t>[Environment &amp; Climate] Việt Nam's push for net zero emissions by 2050 is putting ... — Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented ...</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/](https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/)
-### Document Overview
-The content discusses how Vietnamese industrial parks are adopting Intelligent Operations Centers (IOCs) to meet the country's 2050 net-zero emissions goal and improve environmental reporting.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: N/A
-verbatim: Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented reporting remain. In response, businesses are adopting Intelligent Operations Centers (IOCs) to meet environmental standards and improve efficiency. In the net-zero era, IOCs are emerging as a governance platform, helping industrial zones move beyond infrastructure leasing toward setting standards in global value chains.
-answer: Vietnam's commitment to achieving net-zero emissions by 2050 is driving industrial parks to transition from traditional infrastructure leasing to advanced governance models to meet international environmental standards. To address current gaps in real-time monitoring and fragmented reporting, businesses are increasingly adopting Intelligent Operations Centers (IOCs) to enhance efficiency and integrate into global value chains.
-Source: [www.facebook.com](https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/)</t>
+          <t>[Environment &amp; Climate] Việt Nam's push for net zero emissions by 2050 is putting ... — Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented ...</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>## [https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/](https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/)
-### Document Overview
-The page discusses the adoption of Intelligent Operations Centers (IOCs) in Vietnamese industrial parks to meet the 2050 Net Zero emissions goal and improve global supply chain standards.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented reporting remain. In response, businesses are adopting Intelligent Operations Centers (IOCs) to meet environmental standards and improve efficiency. In the net-zero era, IOCs are emerging as a governance platform, helping industrial zones move beyond infrastructure leasing toward setting standards in global value chains.
-answer: Mục tiêu đạt phát thải ròng bằng 0 vào năm 2050 của Việt Nam đang tạo áp lực buộc các khu công nghiệp phải chuyển đổi từ mô hình cho thuê hạ tầng truyền thống sang quản trị thông minh. Để giải quyết các lỗ hổng về giám sát thời gian thực và đáp ứng các tiêu chuẩn môi trường khắt khe, các doanh nghiệp đang áp dụng Trung tâm Điều hành Thông minh (IOC) nhằm nâng cao hiệu quả và vị thế trong chuỗi giá trị toàn cầu.
-Source: [www.facebook.com](https://www.facebook.com/vietnamtodayinternational/videos/vi%E1%BB%87t-nams-push-for-net-zero-emissions-by-2050-is-putting-pressure-on-industrial-/1602051484181597/)</t>
+          <t>[Environment &amp; Climate] Việt Nam's push for net zero emissions by 2050 is putting ... — Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented ...</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -9173,36 +7340,17 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/](https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/)
-### Document Overview
-The page discusses Vietnam's strategic shift toward greening its industrial parks to maintain export competitiveness and meet net-zero goals by 2050. It highlights key regulations like Decree 35 and Decree 9716, and the role of international cooperation in developing eco-industrial parks.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Vietnams industrial parks have long been central to the countrys export-led growth model, but with rising risks from climate change and rapidly evolving supply chains, the sustainability of this industrial base is coming under increasing scrutiny. Greening industrial parks has therefore emerged as both an environmental imperative and a strategic economic priority.
-In response, Vietnam is gradually reshaping its industrial park model, with growing emphasis on renewable energy use, eco-industrial parks (EIPs), circular economy practices, and internationally recognized green standards. This transition is being supported by an evolving policy framework, including dedicated regulations, financial incentives, and international cooperation programmes aimed at accelerating adoption.
-answer: 베트남은 수출 주도형 성장의 핵심인 산업단지를 기후 변화와 글로벌 ESG 규제에 대응하기 위해 재생 에너지 사용과 순환 경제를 강조하는 친환경 생태산업단지(EIP) 모델로 전환하고 있습니다. 이를 위해 베트남 정부는 법령 제35호(Decree 35) 및 제9716호(Decree 9716)와 같은 포괄적인 법적 프레임워크를 마련하고, 국제기구와의 협력을 통해 에너지 효율을 높이고 탄소 배출을 줄이는 전략적 정책을 추진 중입니다.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/)</t>
+          <t>[Power &amp; Energy] Green Transition in Vietnam's Industrial Parks: Policy ... — Vietnam's industrial parks are shifting toward eco-industrial models, renewable energy, and green standards amid global supply chain ...</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/](https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/)
-### Document Overview
-The article discusses Vietnam's strategic shift toward greening its industrial parks through the Eco-Industrial Park (EIP) model, supported by Decree 9716 and the National Power Development Plan (PDP8). It highlights the economic necessity of these changes to maintain global competitiveness and meet net-zero targets by 2050.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: Vietnam is gradually reshaping its industrial park model, with growing emphasis on renewable energy use, eco-industrial parks (EIPs), circular economy practices, and internationally recognized green standards. This transition is being supported by an evolving policy framework, including dedicated regulations, financial incentives, and international cooperation programmes aimed at accelerating adoption. The National Power Development Plan for the 2021-2030 period, with a vision to 2050 (PDP8), which was amended through Decision No. 768/QD-TTg (Decision 768) in May 2023, sets specific goals for the development of renewable energy sources, such as wind, solar, and biomass.
-answer: Vietnam is modernizing its 478 industrial parks by transitioning to an eco-industrial park (EIP) model that prioritizes renewable energy, resource efficiency, and circular economy practices to meet its 2050 net-zero emissions goal. This green shift is driven by new regulatory frameworks like Decree 35 and Decree 9716, which provide incentives for cleaner production and align with international standards such as the EU's Carbon Border Adjustment Mechanism (CBAM). The transition is supported by the National Power Development Plan (PDP8) and international partnerships with organizations like UNIDO to integrate wind, solar, and biomass energy into industrial hubs.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/)</t>
+          <t>[Power &amp; Energy] Green Transition in Vietnam's Industrial Parks: Policy ... — Vietnam's industrial parks are shifting toward eco-industrial models, renewable energy, and green standards amid global supply chain ...</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/](https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/)
-### Document Overview
-Bài viết cung cấp cái nhìn tổng quan về quá trình chuyển đổi từ các khu công nghiệp truyền thống sang khu công nghiệp sinh thái tại Việt Nam, bao gồm các chính sách quan trọng như Nghị định 35 và Nghị định 9716.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnams industrial parks have long been central to the countrys export-led growth model, but with rising risks from climate change and rapidly evolving supply chains, the sustainability of this industrial base is coming under increasing scrutiny. Greening industrial parks has therefore emerged as both an environmental imperative and a strategic economic priority. In response, Vietnam is gradually reshaping its industrial park model, with growing emphasis on renewable energy use, eco-industrial parks (EIPs), circular economy practices, and internationally recognized green standards. This transition is being supported by an evolving policy framework, including dedicated regulations, financial incentives, and international cooperation programmes aimed at accelerating adoption.
-answer: Bài báo phân tích quá trình chuyển đổi xanh của các khu công nghiệp tại Việt Nam thông qua việc xây dựng khung pháp lý và triển khai mô hình khu công nghiệp sinh thái (EIP). Nội dung nhấn mạnh tầm quan trọng của việc áp dụng năng lượng tái tạo và kinh tế tuần hoàn để đáp ứng các tiêu chuẩn quốc tế như CBAM và ESG, nhằm duy trì lợi thế cạnh tranh thu hút FDI và hướng tới mục tiêu phát thải ròng bằng không vào năm 2050.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/green-transition-in-vietnams-industrial-parks-part-1-policy-foundations-and-landscape.html/)</t>
+          <t>[Power &amp; Energy] Green Transition in Vietnam's Industrial Parks: Policy ... — Vietnam's industrial parks are shifting toward eco-industrial models, renewable energy, and green standards amid global supply chain ...</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -9256,35 +7404,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>## [https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/](https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/)
-### Document Overview
-The article analyzes Vietnam's current solid waste challenges, highlighting a shift from landfilling to waste-to-energy technologies and the emerging opportunities for foreign investment driven by new environmental laws and power development plans.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: N/A
-verbatim: Vietnam, like many rapidly developing nations, faces significant challenges in managing solid waste... The Vietnamese government has outlined a roadmap for solid waste management to protect the environment and promote sustainable development. Under the 2020 Environmental Protection Law, municipal solid waste must be sorted at the source by December 31, 2024... In the National Power Development Plan for 2021-2030 (Power Plan VIII), the government encourages the construction of waste-to-energy plants... Foreign investors with advanced technologies, financial resources, and operational expertise can capitalize on this burgeoning market.
-answer: 베트남은 급격한 도시화와 산업화로 인해 발생하는 연간 약 60,000톤의 폐기물 문제를 해결하기 위해 2024년 말까지 분리배출 의무화 및 제8차 국가전력개발계획(PDP8) 기반의 폐기물 에너지화(Waste-to-Energy) 시설 확대를 추진하고 있습니다. 현재 매립 중심(71%)인 처리 방식을 개선하기 위해 정부 차원의 세제 혜택과 전력 구매 지원 등 외인 투자 유치 정책을 강화하고 있으며, 이는 환경 보호와 신재생 에너지 확보라는 이중 목적을 가지고 있습니다. 이에 따라 고도화된 소각 및 재활용 기술을 보유한 외국인 투자자들에게 하노이와 호치민 등 대도시를 중심으로 한 환경 인프라 시장 진출 기회가 확대되고 있습니다.
-Source: [b-company.jp](https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/)</t>
+          <t>[Environment &amp; Climate] Solid Waste Treatment in Vietnam: Current Situation and ... — Vietnam's industrial sector produces significant amounts of waste, but the country currently lacks sufficient treatment facilities. Foreign ...</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>## [https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/](https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/)
-### Document Overview
-The article analyzes Vietnam's current solid waste challenges, government roadmaps including Power Plan VIII, and significant investment opportunities in waste-to-energy and recycling infrastructure.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: N/A
-verbatim: Vietnam, like many rapidly developing nations, faces significant challenges in managing solid waste. With increasing urbanization, industrialization, and a rising population, solid waste generation in Vietnam has soared in recent years... The Vietnamese government has outlined a roadmap for solid waste management to protect the environment and promote sustainable development. Under the 2020 Environmental Protection Law, municipal solid waste must be sorted at the source by December 31, 2024... In the National Power Development Plan for 2021-2030 with a vision to 2050 (Power Plan VIII), the government encourages the construction of waste-to-energy plants... by 2030, the total capacity of waste-to-energy plants is expected to reach approximately 1,500 MW.
-answer: Vietnam is rapidly expanding its waste management infrastructure to handle approximately 60,000 tons of municipal waste daily, with a strategic shift toward waste-to-energy (WtE) technology targeting a capacity of 1,500 MW by 2030 under Power Plan VIII. To support this transition and achieve 2024 mandatory waste segregation goals, the government is offering foreign investors incentives such as tax exemptions and streamlined licensing for advanced recycling and energy recovery facilities. Currently, the country relies heavily on landfilling (71%), but 15 new waste-to-energy plants are under construction to modernize the sector and reduce environmental impact.
-Source: [b-company.jp](https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/)</t>
+          <t>[Environment &amp; Climate] Solid Waste Treatment in Vietnam: Current Situation and ... — Vietnam's industrial sector produces significant amounts of waste, but the country currently lacks sufficient treatment facilities. Foreign ...</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>## [https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/](https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/)
-### Document Overview
-The page provides a comprehensive overview of Vietnam's solid waste sector, highlighting the shift from landfills to waste-to-energy technologies and the emerging opportunities for foreign investment under new environmental laws.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam, like many rapidly developing nations, faces significant challenges in managing solid waste. With increasing urbanization, industrialization, and a rising population, solid waste generation in Vietnam has soared in recent years... The Vietnamese government has outlined a roadmap for solid waste management to protect the environment and promote sustainable development... Vietnams rapid urbanization and industrialization have significantly increased solid waste generation, presenting vast opportunities for foreign investors in waste treatment and management.
-answer: Bài viết phân tích thực trạng quản lý chất thải rắn tại Việt Nam với lượng rác thải sinh hoạt khoảng 60.000 tấn/ngày, trong đó 71% vẫn xử lý bằng phương pháp chôn lấp và hạ tầng thu gom còn lạc hậu. Chính phủ đang thúc đẩy lộ trình phân loại rác tại nguồn và khuyến khích đầu tư vào các nhà máy điện rác (WTE) với mục tiêu đạt công suất 1.500 MW vào năm 2030. Đây là cơ hội lớn cho các nhà đầu tư nước ngoài có công nghệ tiên tiến trong lĩnh vực tái chế, xử lý rác thải công nghiệp và chuyển hóa rác thành năng lượng.
-Source: [b-company.jp](https://b-company.jp/solid-waste-treatment-in-vietnam-current-situation-and-potential/)</t>
+          <t>[Environment &amp; Climate] Solid Waste Treatment in Vietnam: Current Situation and ... — Vietnam's industrial sector produces significant amounts of waste, but the country currently lacks sufficient treatment facilities. Foreign ...</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -9338,35 +7468,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=Y_-R8uZYKI8](https://www.youtube.com/watch?v=Y_-R8uZYKI8)
-### Document Overview
-The page discusses Vietnam's intensified efforts and strategic initiatives to combat plastic waste and promote a circular economy by 2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: N/A
-verbatim: Vietnam is accelerating its battle against plastic waste through various initiatives including the National Plastic Action Partnership (NPAP) and a focus on a circular economy to achieve plastic reduction goals by 2030.
-answer: 베트남은 2030년까지 플라스틱 폐기물 감축 목표를 달성하기 위해 '국가 플라스틱 액션 파트너십(NPAP)'을 강화하고 순환 경제 체제로의 전환을 가속화하고 있습니다. 정부는 환경 보호를 위해 플라스틱 쓰레기와의 전쟁을 선포하며 관련 인프라와 정책적 대응을 확대하고 있는 추세입니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=Y_-R8uZYKI8)</t>
+          <t>[Environment &amp; Climate] Vietnam accelerates battle against plastic waste — Vietnam is mobilizing resources to fight plastic waste marking its fifth anniversary.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=Y_-R8uZYKI8](https://www.youtube.com/watch?v=Y_-R8uZYKI8)
-### Document Overview
-The content highlights Vietnam's accelerated efforts and strategic actions to reduce plastic waste and transition toward a circular economy by 2030.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: N/A
-verbatim: Vietnam is accelerating its battle against plastic waste... #PlasticReduction2030 #CircularEconomy #NPAP
-answer: Vietnam is intensifying its national efforts to combat plastic waste by implementing strategies focused on a circular economy and environmental protection. The initiative aligns with the country's 2030 plastic reduction goals and involves collaborative frameworks like the National Plastic Action Partnership (NPAP) to improve waste management infrastructure.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=Y_-R8uZYKI8)</t>
+          <t>[Environment &amp; Climate] Vietnam accelerates battle against plastic waste — Vietnam is mobilizing resources to fight plastic waste marking its fifth anniversary.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=Y_-R8uZYKI8](https://www.youtube.com/watch?v=Y_-R8uZYKI8)
-### Document Overview
-The content highlights Vietnam's strategic efforts and initiatives to combat plastic waste and promote a circular economy by 2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is accelerating battle against plastic waste... #PlasticWaste #CircularEconomy #NPAP #GreenVietnam #PlasticReduction2030
-answer: Video này đề cập đến việc Việt Nam đang đẩy mạnh cuộc chiến chống rác thải nhựa thông qua các chiến lược kinh tế tuần hoàn và mục tiêu giảm thiểu rác thải nhựa đến năm 2030. Nội dung tập trung vào nỗ lực cải thiện hạ tầng môi trường và bảo vệ hệ sinh thái bền vững cho tương lai.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=Y_-R8uZYKI8)</t>
+          <t>[Environment &amp; Climate] Vietnam accelerates battle against plastic waste — Vietnam is mobilizing resources to fight plastic waste marking its fifth anniversary.</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -9420,35 +7532,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/](https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/)
-### Document Overview
-This article discusses S&amp;P Ratings' forecast for Vietnam, highlighting that massive infrastructure investment is driving high GDP growth but also increasing fiscal deficits and public debt.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Vietnam is forecast to remain Asia's fastest-growing nation after India through 2028, supported by exports and infrastructure investments, although heavy public spending may lead to larger fiscal deficits, a senior S&amp;P Ratings official said on Thursday. Hanoi is seeking an upgrade of its sovereign rating to investment grade from at least one major agency by the end of the decade, while also targeting annual economic growth of at least 10% through 2030, backed by investments in hundreds of new large-scale projects launched last year worth an estimated $200 billion.
-answer: 베트남은 수출과 대규모 인프라 투자에 힘입어 2028년까지 인도에 이어 아시아에서 가장 빠르게 성장하는 국가가 될 것으로 전망되지만, 막대한 공공 지출로 인해 재정 적자가 확대될 위험이 있습니다. 베트남 정부는 2030년까지 연간 10% 성장을 목표로 약 2,000억 달러 규모의 신규 대형 프로젝트를 추진 중이며, 이를 통해 국가 신용등급을 투자 적격 등급으로 상향시키려 노력하고 있습니다.
-Source: [www.reuters.com](https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's infrastructure push to boost growth and deficit, S&amp;P ... — Vietnam is forecast to remain Asia's fastest-growing nation after India through 2028, supported by exports and infrastructure investments, ...</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/](https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/)
-### Document Overview
-This article discusses S&amp;P Ratings' outlook on Vietnam, highlighting how a massive $200 billion infrastructure investment plan will drive economic growth but potentially strain the national budget and increase fiscal deficits.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Vietnam's infrastructure push to boost growth and deficit, S&amp;P Ratings says... Hanoi is seeking an upgrade of its sovereign rating to investment grade from at least one major agency by the end of the decade, while also targeting annual economic growth of at least 10% through 2030, backed by investments in hundreds of new large-scale projects launched last year worth an estimated $200 billion. 'The government's commitment to expanding infrastructure investment will likely bring more years of strong growth. Such expenditure may lead to larger fiscal deficits and smaller current account surpluses that may offset some of its gains,' Kim Eng Tan, managing director for Asia sovereign ratings at S&amp;P Global Ratings, said.
-answer: Vietnam is projected to maintain its position as one of Asia's fastest-growing economies through 2028, driven by a $200 billion investment initiative in hundreds of large-scale infrastructure projects. While this push supports the government's goal of 10% annual economic growth and an investment-grade sovereign rating by 2030, S&amp;P Ratings warns that the heavy public spending may lead to wider fiscal deficits and increased public debt. Consequently, while infrastructure expansion fuels the export-driven economy, it poses risks to long-term fiscal stability if government debt exceeds 30% of GDP.
-Source: [www.reuters.com](https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's infrastructure push to boost growth and deficit, S&amp;P ... — Vietnam is forecast to remain Asia's fastest-growing nation after India through 2028, supported by exports and infrastructure investments, ...</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/](https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/)
-### Document Overview
-The article discusses S&amp;P Ratings' outlook on Vietnam, highlighting that massive infrastructure investment will drive economic growth (projected at 6.7% over 3 years) but risks increasing fiscal deficits and debt.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is forecast to remain Asia's fastest-growing nation after India through 2028, supported by exports and infrastructure investments, although heavy public spending may lead to larger fiscal deficits, a senior S&amp;P Ratings official said on Thursday. ... The government's commitment to expanding infrastructure investment will likely bring more years of strong growth. Such expenditure may lead to larger fiscal deficits and smaller current account surpluses that may offset some of its gains.
-answer: Việt Nam được dự báo sẽ là nền kinh tế tăng trưởng nhanh thứ hai châu Á (sau Ấn Độ) cho đến năm 2028 nhờ đẩy mạnh xuất khẩu hàng điện tử và đầu tư mạnh mẽ vào cơ sở hạ tầng. Tuy nhiên, các chuyên gia từ S&amp;P Ratings cảnh báo rằng việc chi tiêu công lớn cho hàng trăm dự án quy mô lớn trị giá khoảng 200 tỷ USD có thể làm gia tăng thâm hụt ngân sách và nợ công, gây áp lực lên xếp hạng tín nhiệm quốc gia.
-Source: [www.reuters.com](https://www.reuters.com/world/asia-pacific/vietnams-infrastructure-push-boost-growth-deficit-sp-ratings-says-2026-04-02/)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam's infrastructure push to boost growth and deficit, S&amp;P ... — Vietnam is forecast to remain Asia's fastest-growing nation after India through 2028, supported by exports and infrastructure investments, ...</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -9502,36 +7596,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>## [https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html](https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html)
-### Document Overview
-This article outlines the growth forecast for Vietnam's construction industry through 2030, highlighting key drivers such as FDI, state budget allocations, and major transport/energy infrastructure projects.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Vietnam's construction industry is expected to register an annual average growth of 6.5% from 2027 to 2030, supported by the government's efforts to develop housing, energy and transport infrastructure... Growth will also be supported by the Ministry of Transport target to increase expressway length from 1,900km in 2023 to 5,000km by 2030. Ho Chi Minh City's (HCMC) urban railway plan includes eight metro lines with a total investment of VND633.9 trillion ($24.7 billion) by 2035.
-answer: 베트남 건설 산업은 정부의 적극적인 교통 및 에너지 인프라 확충 정책에 힘입어 2027년부터 2030년까지 연평균 6.5%의 성장이 기대됩니다. 특히 교통부는 2030년까지 고속도로 길이를 5,000km로 연장할 계획이며, 호치민시는 2035년까지 8개의 메트로 노선 건설에 약 247억 달러를 투입하는 등 대규모 인프라 프로젝트를 추진하고 있습니다.
-Source: [finance.yahoo.com](https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam Construction Industry Report 2026: Output to Expand by 7.9 ... — The analyst expects the construction industry in Vietnam to grow by 7.9% in real terms in 2026, supported by increased foreign direct investment ...</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>## [https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html](https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html)
-### Document Overview
-This report outlines the growth trajectory of Vietnam's construction industry, highlighting a 7.9% expansion in 2026 and major infrastructure projects in transport, energy, and urban rail.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Vietnam's construction industry is expected to grow by 7.9% this year and register an average annual growth rate of 6.5% from 2027 to 2030, driven by significant investments in transport and energy infrastructure. Key transport initiatives include a target to expand the expressway network to 5,000km by 2030 and a VND633.9 trillion ($24.7 billion) investment plan for eight urban railway lines in Ho Chi Minh City by 2035.
-answer: Vietnam's construction and infrastructure sector is projected to expand by 7.9% in 2026, with long-term growth supported by massive state budget allocations and foreign direct investment totaling $38.42 billion. The government is prioritizing transport connectivity by aiming to increase expressway coverage to 5,000km by 2030 and developing an extensive $24.7 billion urban railway network in Ho Chi Minh City consisting of eight metro lines.
-Source: [finance.yahoo.com](https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam Construction Industry Report 2026: Output to Expand by 7.9 ... — The analyst expects the construction industry in Vietnam to grow by 7.9% in real terms in 2026, supported by increased foreign direct investment ...</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>## [https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html](https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html)
-### Document Overview
-Báo cáo phân tích về sự tăng trưởng của ngành xây dựng Việt Nam đến năm 2030, tập trung vào các dự án hạ tầng giao thông, năng lượng tái tạo và tác động từ dòng vốn FDI.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Key market opportunities in Vietnam's construction sector include growth fueled by FDI, investments in transport and energy infrastructure, housing development, renewable energy expansion, and extensive infrastructure projects like expressways and urban railways... The construction industry in Vietnam is expected to register an annual average growth of 6.5% from 2027 to 2030, supported by the government's efforts to develop housing, energy and transport infrastructure and the Ministry of Industry and Trade's strategy to produce 20 million tonnes of hydrogen per year by 2050.
-answer: 1. Ngành xây dựng Việt Nam dự kiến đạt mức tăng trưởng trung bình hàng năm 6,5% trong giai đoạn 2027-2030, nhờ vào các nỗ lực của chính phủ trong việc phát triển nhà ở, hạ tầng giao thông và năng lượng tái tạo. 
-2. Các động lực tăng trưởng chính bao gồm kế hoạch mở rộng 5.000 km đường cao tốc đến năm 2030, đầu tư hệ thống đường sắt đô thị tại TP.HCM trị giá hơn 24 tỷ USD và thực hiện Quy hoạch điện VIII nhằm tăng tỷ trọng năng lượng sạch.
-Source: [finance.yahoo.com](https://finance.yahoo.com/sectors/energy/articles/vietnam-construction-industry-report-2026-145800440.html)</t>
+          <t>[Transport &amp; Infrastructure] Vietnam Construction Industry Report 2026: Output to Expand by 7.9 ... — The analyst expects the construction industry in Vietnam to grow by 7.9% in real terms in 2026, supported by increased foreign direct investment ...</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -9585,35 +7660,17 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>## [https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026](https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026)
-### Document Overview
-This briefing summarizes Vietnam's infrastructure developments in March 2026, highlighting the green energy transition for Hanoian taxis, SOE strategic roles, and major foreign investments in AI, LNG, and offshore wind sectors.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Other, 관련 마스터플랜: VN-EV-2030
-verbatim: Hanoi will replace all gasoline and diesel taxis with green-energy vehicles by 2030. The city People’s Committee issued a plan outlining phased transition and support policies for operators, with the specific targets being 63–64% in 2026 and 68–70% in 2027 before reaching 100% by 2030.
-answer: 하노이시는 2030년까지 모든 휘발유 및 디젤 택시를 친환경 차량으로 교체하는 마스터플랜(VN-EV-2030 관련)을 추진하며, 2026년까지 63-64%, 2030년까지 100% 전환을 목표로 하고 있습니다. 이와 함께 베트남 국영기업(SOE)의 전략적 역할 강화와 더불어 AI 인프라, LNG 발전, 해상 풍력 등 에너지 및 기술 섹터 전반에 걸친 대규모 투자 프로젝트들이 활발히 진행되고 있습니다.
-Source: [www.freshfields.com](https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026)</t>
+          <t>[Other] Vietnam Infrastructure Spotlight March 2026 - Freshfields — In this issue, we highlight recent legal and market developments in Vietnam's infrastructure sector. (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>## [https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026](https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026)
-### Document Overview
-This briefing highlights significant March 2026 developments in Vietnam's infrastructure sector, including Hanoi's taxi electrification plan and a $1 billion AI infrastructure investment.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Other, Related plans: VN-EV-2030
-verbatim: Hanoi will replace all gasoline and diesel taxis with green-energy vehicles by 2030. The city People’s Committee issued a plan outlining phased transition and support policies for operators, with the specific targets being 63–64% in 2026 and 68–70% in 2027 before reaching 100% by 2030.
-answer: Hanoi has officially committed to replacing all gasoline and diesel-powered taxis with green-energy vehicles by the year 2030 as part of its urban sustainability efforts. The transition plan establishes specific intermediate milestones, targeting a green vehicle conversion rate of 63–64% by 2026 and 68–70% by 2027 to ensure the complete 100% phase-out of traditional internal combustion engine taxis by 2030.
-Source: [www.freshfields.com](https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026)</t>
+          <t>[Other] Vietnam Infrastructure Spotlight March 2026 - Freshfields — In this issue, we highlight recent legal and market developments in Vietnam's infrastructure sector. (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>## [https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026](https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026)
-### Document Overview
-This briefing summarizes significant developments in Vietnam's infrastructure sector as of March 2026, covering policy shifts for SOEs, multi-billion dollar investments in AI and LNG, and major expansion plans in renewable energy and maritime ports.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam Infrastructure Spotlight March 2026... In this issue, we highlight recent legal and market developments in Vietnam's infrastructure sector. ... Resolution 79 on State -owned enterprises (SOEs) ... G42, the Abu Dhabi-based technology group ... signed an agreement to invest up to $1 billion to develop AI capabilities ... Hanoi will replace all gasoline and diesel taxis with green-energy vehicles by 2030 ... Khanh Hoa authorities have approved the Trung Nam-Sideros River consortium ... for the VND57.38 trillion ($2.2 billion) Ca Na LNG-fired power project ... VinEnergo Energy has been selected as the investor for the Hon Trau wind power plant ... with a total investment exceeding $1.86 billion ... Cai Mep Ha general and container port project was approved ... with total investment exceeding VND50.8 trillion.
-answer: Bản tin cơ sở hạ tầng Việt Nam tháng 3 năm 2026 cập nhật các chính sách mới về doanh nghiệp nhà nước và các khoản đầu tư quy mô lớn trong nhiều lĩnh vực như công nghệ AI (1 tỷ USD), năng lượng LNG và điện gió (dự án Cà Ná 2,2 tỷ USD và Hòn Trâu 1,8 tỷ USD). Ngoài ra, báo cáo còn ghi nhận những bước tiến quan trọng trong hạ tầng giao thông xanh tại Hà Nội và các dự án cảng biển chiến lược như cảng Cái Mép Hạ và cảng trung chuyển quốc tế Cần Giờ.
-Source: [www.freshfields.com](https://www.freshfields.com/en/our-thinking/briefings/2026/03/vietnam-infrastructure-spotlight-march-2026)</t>
+          <t>[Other] Vietnam Infrastructure Spotlight March 2026 - Freshfields — In this issue, we highlight recent legal and market developments in Vietnam's infrastructure sector. (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -9667,32 +7724,17 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=WuFtpWFqWbI](https://www.youtube.com/watch?v=WuFtpWFqWbI)
-### Document Overview
-This content discusses Vietnam's strategic focus on infrastructure development as a pillar for economic growth, highlighting its significance for international investors ahead of the 14th National Party Congress.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Finance &amp; Investment, 관련 마스터플랜: N/A
-verbatim: The 14th National Party Congress is not only a defining political moment for Vietnam but also a key reference point for the international business community. Vietnam’s Infrastructure Breakthrough: A Strategic Pillar for Growth.
-answer: 제14차 당대회를 앞둔 베트남은 인프라 혁신을 국가 성장의 핵심 전략적 기둥이자 국제 비즈니스 커뮤니티의 주요 이정표로 설정했습니다. 특히 이번 인프라 돌파구는 해외 투자 유치와 경제 성장을 가속화하기 위한 핵심 요소로 평가받고 있습니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=WuFtpWFqWbI)</t>
+          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — ... Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment ...</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=WuFtpWFqWbI](https://www.youtube.com/watch?v=WuFtpWFqWbI)
-### Document Overview
-The page is a standard YouTube video landing page footer; however, the provided content lacks the actual video details or transcript required to answer the specific query about Vietnam infrastructure.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=WuFtpWFqWbI)</t>
+          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — ... Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment ...</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=WuFtpWFqWbI](https://www.youtube.com/watch?v=WuFtpWFqWbI)
-### Document Overview
-Trang web phân tích vai trò của hạ tầng như một trụ cột chiến lược cho sự phát triển của Việt Nam và tầm quan trọng của nó đối với các nhà đầu tư quốc tế.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s Infrastructure Breakthrough: A Strategic Pillar for Growth | Vietnam Today. The 14th National Party Congress is not only a defining political moment for Vietnam but also a key reference point for the international business community.
-answer: Nội dung nhấn mạnh sự đột phá trong phát triển cơ sở hạ tầng là trụ cột chiến lược thúc đẩy tăng trưởng kinh tế bền vững của Việt Nam. Đây được coi là yếu tố then chốt thu hút cộng đồng doanh nghiệp quốc tế, đặc biệt là trong bối cảnh chuẩn bị cho Đại hội Đảng lần thứ XIV sắp tới.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=WuFtpWFqWbI)</t>
+          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — ... Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment ...</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -9746,35 +7788,17 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>## [https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments](https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments)
-### Document Overview
-This guide provides a comprehensive overview of Vietnam's legal and regulatory landscape for 2026, focusing on FDI, M&amp;A, real estate, renewable energy (PDP VIII), and new technology laws.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: On 15 April 2025, the Prime Minister issued Decision No 768/QD-TTg amending PDP VIII. The amendments focused on promoting renewable energy, with additional capacity for wind, solar, and hydropower... On 9 October 2025, the Prime Minister issued Decision No 2229/QD-TTg approving the strategy for developing logistics services for the 2025–35 period... The Law on Electricity 2024 introduces a dedicated chapter on the development of renewable and new-energy electricity... explicitly includes offshore wind projects.
-answer: 베트남은 제8차 국가전력개발계획(PDP VIII) 개정안과 2024년 개정 전기법을 통해 신재생 에너지 및 해상 풍력 발전에 대한 법적 프레임워크를 강화하고 민간 투자를 촉진하고 있습니다. 또한 직접전력구매계약(DPPA) 도입과 물류 서비스 개발 전략(2025-2035)을 통해 에너지 효율성을 높이고 글로벌 공급망 내 전략적 위치 확보를 목표로 인프라 혁신을 가속화하고 있습니다.
-Source: [practiceguides.chambers.com](https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments)</t>
+          <t>[Transport &amp; Infrastructure] Investing In... 2026 - Vietnam - Global Practice Guides — These landmark reforms round out Vietnam's earlier investment roadmap under Resolution No 50 (2019) and are reinforced by a series of new ...</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>## [https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments](https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments)
-### Document Overview
-This article details Vietnam's significant 2025-2026 legal and administrative reforms, including the merger of ministries, new land and electricity laws, and the introduction of a digital technology and crypto-asset framework.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: The Ministry of Transport was merged into the Ministry of Construction (MOC). ... The Department of Transport was merged into the Department of Construction (DOC). ... Decision No 768/QD-TTg amending PDP VIII. The amendments focused on promoting renewable energy, with additional capacity for wind, solar, and hydropower (including pumped-storage hydropower), and outlined a framework for developing nuclear power, starting from 2030. ... The Law on Electricity 2024 ... expressly includes offshore wind projects, providing a clear framework for survey licensing, investment policy approval, and investor selection.
-answer: Vietnam has implemented a major administrative restructuring as of March 2025, merging the Ministry of Transport into the Ministry of Construction to enhance efficiency in infrastructure management. Simultaneously, the country is accelerating energy infrastructure development through the amended Power Development Plan 8 (PDP VIII) and the Law on Electricity 2024, which establish new frameworks for offshore wind, solar, and nuclear power projects. These reforms aim to streamline investment procedures and promote private sector participation in strategic technology and transport infrastructure to support Vietnam's goal of becoming a high-income nation by 2045.
-Source: [practiceguides.chambers.com](https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments)</t>
+          <t>[Transport &amp; Infrastructure] Investing In... 2026 - Vietnam - Global Practice Guides — These landmark reforms round out Vietnam's earlier investment roadmap under Resolution No 50 (2019) and are reinforced by a series of new ...</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>## [https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments](https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments)
-### Document Overview
-This page provides an in-depth analysis of Vietnam's investment landscape for 2026, covering legal reforms, M&amp;A trends, infrastructure developments in energy and logistics, and new regulations for digital assets and data protection.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is accelerating its ambitious reform, aiming for upper-middle income status by 2030 and high-income status by 2045... The technology sector remains hot for M&amp;A activity and new foreign investment in Vietnam, particularly in Artificial Intelligence (AI) and emerging technologies... The PDP VIII and the NCEP articulate, among other things, the anticipated energy demand, strategic development objectives, and prospective capacity allocation for the various key sources of power generation in Vietnam... On 9 October 2025, the Prime Minister issued Decision No 2229/QD-TTg approving the strategy for developing logistics services for the 2025–35 period.
-answer: Bài báo cung cấp cái nhìn toàn diện về môi trường đầu tư tại Việt Nam năm 2026, nhấn mạnh vào các cải cách pháp lý mang tính bước ngoặt trong lĩnh vực bất động sản, năng lượng tái tạo và công nghệ số. Nội dung tập trung vào các chiến lược phát triển hạ tầng trọng điểm như Quy hoạch điện VIII, cơ chế mua bán điện trực tiếp (DPPA), cùng các kế hoạch hiện đại hóa hệ thống logistics và trung tâm dữ liệu nhằm thúc đẩy tăng trưởng kinh tế bền vững.
-Source: [practiceguides.chambers.com](https://practiceguides.chambers.com/practice-guides/investing-in-2026/vietnam/trends-and-developments)</t>
+          <t>[Transport &amp; Infrastructure] Investing In... 2026 - Vietnam - Global Practice Guides — These landmark reforms round out Vietnam's earlier investment roadmap under Resolution No 50 (2019) and are reinforced by a series of new ...</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -9828,35 +7852,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html](https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html)
-### Document Overview
-This article by VinaCapital analysts explores Vietnam's economic outlook for 2026, highlighting infrastructure investment, consumption recovery, and resilient exports as the primary drivers for GDP growth.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Other, 관련 마스터플랜: N/A
-verbatim: Vietnam’s infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going forward. This infrastructure push can boost Vietnam's GDP in the short run, much like how China supported its economy with infrastructure investment after the global financial crisis, wrote VinaCapital analysts. ... The three key dynamics that we expect to drive 2026 GDP growth are discussed below: a modest consumption recovery, the infrastructure-real estate growth nexus, and resilient exports to the U.S.
-answer: 베트남은 향후 인프라 지출 성장률을 연간 20-30%로 가속화하여 2026년 GDP 성장의 핵심 동력으로 삼을 계획이며, 이는 과거 중국의 경제 부양 방식과 유사한 단기 성장 효과를 목표로 합니다. 특히 인프라 개발은 부동산 시장 활성화와 소비 회복으로 이어지는 연결 고리를 형성하며, 미국 수출의 회복력과 함께 베트남 경제 재균형의 핵심 레버리지 역할을 할 것으로 전망됩니다.
-Source: [theinvestor.vn](https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html)</t>
+          <t>[Other] The economy: Re-balancing in 2026 - Theinvestor — Vietnam's infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going ...</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html](https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html)
-### Document Overview
-The article analyzes Vietnam's 2026 economic outlook, highlighting how a massive 20-30% annual increase in infrastructure spending and real estate reforms will drive GDP growth and consumption recovery.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Other, Related plans: N/A
-verbatim: Vietnam’s infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going forward. . . Infrastructure spending has already increased significantly, up around 40% in 2025 and we expect another 20-30% increase in 2026. . . The Government aims to raise [infrastructure development] from around 6% of GDP to 10%/GDP.
-answer: Vietnam is accelerating its infrastructure spending from a historical 10% annual growth to an expected 20-30% per year, with the government aiming to increase development from 6% to 10% of GDP. This push, which saw a 40% jump in 2025, is designed to serve as a primary lever for 2026 GDP growth by creating a nexus that stimulates the real estate sector and domestic consumption.
-Source: [theinvestor.vn](https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html)</t>
+          <t>[Other] The economy: Re-balancing in 2026 - Theinvestor — Vietnam's infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going ...</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>## [https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html](https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html)
-### Document Overview
-Phân tích của VinaCapital về triển vọng kinh tế Việt Nam năm 2026, nhấn mạnh vào ba động lực chính: phục hồi tiêu dùng, đẩy mạnh hạ tầng - bất động sản và duy trì xuất khẩu sang Hoa Kỳ.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going forward. This infrastructure push can boost Vietnam's GDP in the short run... We see a nexus connecting infrastructure, feeding into real estate, and ultimately boosting consumption.
-answer: Bài báo nhận định tăng trưởng chi tiêu cơ sở hạ tầng của Việt Nam sẽ tăng tốc mạnh mẽ lên mức 20-30% mỗi năm, đóng vai trò là đòn bẩy chính thúc đẩy tăng trưởng GDP trong năm 2026. Sự thúc đẩy này tạo ra một mối liên kết chặt chẽ (nexus) giúp giải tỏa nguồn cung bất động sản và gián tiếp kích thích tiêu dùng nội địa, hỗ trợ nền kinh tế phục hồi bền vững.
-Source: [theinvestor.vn](https://theinvestor.vn/the-economy-re-balancing-in-2026-d18292.html)</t>
+          <t>[Other] The economy: Re-balancing in 2026 - Theinvestor — Vietnam's infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going ...</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -9910,36 +7916,17 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>## [https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm](https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm)
-### Document Overview
-This article outlines how Vietnam's infrastructure and transport projects are becoming strategic pillars for economic growth, driving investor confidence and high GDP forecasts for 2026-2027.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Finance &amp; Investment, 관련 마스터플랜: VN-EV-2030
-verbatim: The 14th National Party Congress is not only a defining political moment for Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through major infrastructure, transport, urban, and industrial projects driving growth in the years ahead... Under a scenario of easing geopolitical tensions, the Asian Development Bank forecasts Việt Nam’s GDP growth at 7.2% in 2026 and 7% in 2027.
-answer: 제14차 당대회를 앞둔 베트남은 인프라, 운송, 산업 프로젝트를 핵심 성장 동력으로 삼아 국제 사회의 투자 유입과 경제 개혁을 가속화하고 있습니다. 아시아개발은행(ADB)은 이러한 공공 투자 확대와 행정 개혁에 힘입어 베트남의 경제 성장률이 2026년 7.2%, 2027년 7%에 달할 것으로 전망하며 긍정적인 투자 환경을 시사했습니다. (참고: VN-EV-2030 마스터플랜 및 금융/투자 섹터 관점의 성장 전략 반영)
-Source: [vietnamtoday.vtv.vn](https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm)</t>
+          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>## [https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm](https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm)
-### Document Overview
-The article discusses how Vietnam's strategic infrastructure and industrial projects, influenced by the 14th National Party Congress, are driving investment and economic resilience with a projected 7.2% GDP growth in 2026.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Finance &amp; Investment, Related plans: VN-EV-2030
-verbatim: The 14th National Party Congress is not only a defining political moment for Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through major infrastructure, transport, urban, and industrial projects driving growth in the years ahead.
-Việt Nam’s economy is forecast to remain resilient, supported by continued administrative reforms, accelerated public investment, a green transition, and timely government policy responses.
-answer: Vietnam is leveraging its 14th National Party Congress to signal long-term economic reforms and attract international investment flows into major infrastructure, transport, and industrial projects. The nation's growth strategy focuses on accelerated public investment and a green transition, with the Asian Development Bank forecasting GDP growth to reach 7.2% by 2026 as these strategic pillars take shape.
-Source: [vietnamtoday.vtv.vn](https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm)</t>
+          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>## [https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm](https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm)
-### Document Overview
-Bài báo thảo luận về vai trò của cơ sở hạ tầng như một trụ cột chiến lược cho sự tăng trưởng của Việt Nam trước thềm Đại hội Đảng lần thứ 14, đồng thời cập nhật các dự báo kinh tế tích cực cho giai đoạn 2026-2027.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The 14th National Party Congress is not only a defining political moment for Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through major infrastructure, transport, urban, and industrial projects driving growth in the years ahead.
-answer: Đại hội Đảng toàn quốc lần thứ 14 được xem là cột mốc quan trọng định hình các ưu tiên phát triển dài hạn của Việt Nam, đặc biệt là trong lĩnh vực cơ sở hạ tầng, giao thông và công nghiệp. Những dự án hạ tầng chiến lược này đang trở thành trụ cột thúc đẩy tăng trưởng kinh tế và thu hút dòng vốn đầu tư quốc tế trong những năm tới.
-Source: [vietnamtoday.vtv.vn](https://vietnamtoday.vtv.vn/vietnams-infrastructure-breakthrough-a-strategic-pillar-for-growth-100260121171139701.htm)</t>
+          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -9993,35 +7980,17 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/](https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/)
-### Document Overview
-The article discusses Vietnam's economic strategy for 2026-2030, highlighting provincial mergers and infrastructure projects (rail, energy, digital) aimed at high-value growth.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Transport &amp; Infrastructure, 관련 마스터플랜: N/A
-verbatim: Vietnam is entering a critical phase of development, focusing on high-value growth and regional economic restructuring... Accelerated development of the North–South high-speed railway, strengthening international railway links, and expanding urban rail systems in Hanoi and Ho Chi Minh City... Promotion of renewable and clean energy sources while reviving the Ninh Thuan 1 and 2 nuclear power projects... Expanding nationwide high-speed fiber and satellite connectivity, deployment of 5G and 6G networks.
-answer: 베트남은 2026년부터 2030년까지 고부가가치 성장을 목표로 남북 고속철도 건설 가속화, 국제 철도 연결 강화, 하노이 및 호치민 도시철도망 확장 등 교통 인프라 확충에 집중할 계획입니다. 또한 에너지 안보를 위해 재생 에너지와 원자력 발전 프로젝트를 추진하는 동시에, 5G·6G 및 국가 데이터 센터 구축을 통한 디지털 인프라 현대화에도 박차를 가하고 있습니다. 이러한 인프라 개선은 63개 성을 34개 단위로 통폐합하는 지역 구조조정과 연계되어 물류 효율성을 높이고 국가 경쟁력을 강화하는 기반이 될 것으로 전망됩니다.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/)</t>
+          <t>[Transport &amp; Infrastructure] Tapping into Vietnam's High-Value Growth Ambition in 2026 — Vietnam is aiming for a high-value growth, supported by policies that promote productivity, innovation, and industrial upgrading.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/](https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/)
-### Document Overview
-This article outlines Vietnam's economic strategy for 2026-2030, highlighting targets for 10% annual GDP growth and infrastructure priorities including high-speed rail, nuclear energy, and 5G/6G digital networks.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Transport &amp; Infrastructure, Related plans: N/A
-verbatim: Infrastructure: Accelerated development of the North–South high-speed railway, strengthening international railway links, and expanding urban rail systems in Hanoi and Ho Chi Minh City. Energy: Promotion of renewable and clean energy sources while reviving the Ninh Thuan 1 and 2 nuclear power projects to secure long-term energy stability. Digital Infrastructure: Expanding nationwide high-speed fiber and satellite connectivity, deployment of 5G and 6G networks, and establishing a national data center complemented by regional data hubs.
-answer: Vietnam is prioritizing massive infrastructure upgrades to support its 2026-2030 growth phase, specifically focusing on the accelerated development of the North-South high-speed railway and expanded urban rail systems in Hanoi and Ho Chi Minh City. The plan also emphasizes energy security through the revival of nuclear power projects and the expansion of digital infrastructure, including nationwide 5G/6G networks and national data centers. These efforts are part of a broader regional restructuring aimed at establishing robust development corridors and improving logistics efficiency across newly consolidated provinces.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/)</t>
+          <t>[Transport &amp; Infrastructure] Tapping into Vietnam's High-Value Growth Ambition in 2026 — Vietnam is aiming for a high-value growth, supported by policies that promote productivity, innovation, and industrial upgrading.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>## [https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/](https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/)
-### Document Overview
-Bài báo phân tích chiến lược phát triển kinh tế của Việt Nam giai đoạn 2026-2030, nhấn mạnh vào việc nâng cấp cơ sở hạ tầng, tái cấu trúc địa phương và các ưu đãi cho khu vực tư nhân.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Infrastructure: Accelerated development of the NorthSouth high-speed railway, strengthening international railway links, and expanding urban rail systems in Hanoi and Ho Chi Minh City. Energy: Promotion of renewable and clean energy sources while reviving the Ninh Thuan 1 and 2 nuclear power projects... Digital Infrastructure: Expanding nationwide high-speed fiber and satellite connectivity, deployment of 5G and 6G networks.
-answer: Việt Nam đang tập trung nâng cấp cơ sở hạ tầng chiến lược bao gồm phát triển đường sắt tốc độ cao Bắc-Nam, mở rộng đường sắt đô thị và tăng cường kết nối quốc tế. Bên cạnh đó, Chính phủ ưu tiên đảm bảo an ninh năng lượng thông qua năng lượng tái tạo và điện hạt nhân, đồng thời hiện đại hóa hạ tầng số với mạng 5G/6G và các trung tâm dữ liệu quốc gia. Những nỗ lực này nằm trong chiến lược thúc đẩy tăng trưởng giá trị cao và chuyển đổi số giai đoạn 2026-2030.
-Source: [www.vietnam-briefing.com](https://www.vietnam-briefing.com/news/tapping-into-vietnam-high-value-growth-ambition-in-2026.html/)</t>
+          <t>[Transport &amp; Infrastructure] Tapping into Vietnam's High-Value Growth Ambition in 2026 — Vietnam is aiming for a high-value growth, supported by policies that promote productivity, innovation, and industrial upgrading.</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -10075,36 +8044,17 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>## [https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver](https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver)
-### Document Overview
-This article discusses the strategic importance of infrastructure investment in Vietnam, highlighting its role as a long-term growth driver across sectors like transport, energy, and logistics.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Other, 관련 마스터플랜: N/A
-verbatim: Infrastructure development is one of the most important pillars of Vietnams long-term economic growth. Large-scale investments in transportation, energy, logistics, and urban development are essential to support rising productivity and economic expansion. ... In portfolio construction, infrastructure-related businesses can provide stability and diversification benefits. Revenue streams are often less cyclical and supported by long-term contracts or regulated frameworks.
-answer: 베트남의 인프라 개발은 교통, 에너지, 물류 및 도시화를 포함하는 장기 경제 성장의 핵심 축으로, 정부 주도의 계획과 민관 협력을 통해 지속적인 투자 기회를 제공하고 있습니다. 인프라 관련 투자는 경기 변동에 덜 민감하고 장기 계약을 기반으로 한 안정적인 수익원을 제공하여 포트폴리오의 다변화와 회복탄력성을 높이는 데 기여합니다. 따라서 베트남의 인프라 구축에 참여하는 것은 국가의 구조적 전환 과정에서 발생하는 장기적인 성장 동력을 확보하는 전략적 선택이 됩니다.
-Source: [aquis-capital.com](https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver)</t>
+          <t>[Other] Invest in Vietnam Infrastructure as a Long-Term Growth Driver — To invest in Vietnam infrastructure is to participate in a structural transformation that extends well beyond short-term economic cycles.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>## [https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver](https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver)
-### Document Overview
-The article discusses Vietnam's infrastructure build-out as a strategic investment opportunity, highlighting its role in long-term economic stability and industrial growth.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Other, Related plans: N/A
-verbatim: Infrastructure development is one of the most important pillars of Vietnams long-term economic growth. Large-scale investments in transportation, energy, logistics, and urban development are essential to support rising productivity and economic expansion. For investors, infrastructure development offers multiple points of exposure... across construction, industrial production, energy, transportation, and financial services.
-answer: Vietnam is prioritizing large-scale infrastructure development in sectors like transportation, energy, and logistics to serve as a primary pillar for long-term economic expansion and rising productivity. This structural transformation offers investors stable, long-term exposure to construction and industrial growth through government-led initiatives and public-private partnerships.
-Source: [aquis-capital.com](https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver)</t>
+          <t>[Other] Invest in Vietnam Infrastructure as a Long-Term Growth Driver — To invest in Vietnam infrastructure is to participate in a structural transformation that extends well beyond short-term economic cycles.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>## [https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver](https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver)
-### Document Overview
-This article discusses the strategic importance of infrastructure development in Vietnam as a driver for long-term economic growth and its benefits for international investors.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Infrastructure development is one of the most important pillars of Vietnams long-term economic growth. Large-scale investments in transportation, energy, logistics, and urban development are essential to support rising productivity and economic expansion. To invest in Vietnam infrastructure is to participate in a structural transformation that extends well beyond short-term economic cycles... In portfolio construction, infrastructure-related businesses can provide stability and diversification benefits.
-answer: 1. Bài báo khẳng định phát triển cơ sở hạ tầng là trụ cột quan trọng cho tăng trưởng kinh tế dài hạn của Việt Nam, tập trung vào các lĩnh vực then chốt như giao thông, năng lượng, logistics và hạ tầng số. 
-2. Việc đầu tư vào lĩnh vực này không chỉ mang lại lợi ích từ sự chuyển đổi cấu trúc nền kinh tế mà còn giúp danh mục đầu tư của các nhà đầu tư tổ chức trở nên ổn định và đa dạng hơn nhờ dòng doanh thu ít biến động theo chu kỳ.
-Source: [aquis-capital.com](https://aquis-capital.com/news/invest-in-vietnam-infrastructure-as-a-long-term-growth-driver)</t>
+          <t>[Other] Invest in Vietnam Infrastructure as a Long-Term Growth Driver — To invest in Vietnam infrastructure is to participate in a structural transformation that extends well beyond short-term economic cycles.</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -10158,35 +8108,17 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html](https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html)
-### Document Overview
-This article discusses the Vietnam Ministry of Industry and Trade's comprehensive measures to ensure power security for 2026, including infrastructure upgrades and demand management.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: The MoIT has approved the national power supply plan for 2026 based on a baseline load growth scenario of 8.5 per cent, with an extreme dry-season scenario reaching up to 14.1 per cent... The Vung Ang 2 thermal power venture has officially entered commercial operation, adding around 1,200 MW to the national grid... the National Power Transmission Corporation has upgraded the capacity of the 500kV Mai Chau substation in Hoa Binh province.
-answer: 베트남 산업통상부(MoIT)는 2026년 전력 수요가 기본 8.5%에서 최대 14.1%까지 급증할 것으로 예상하고 전력 공급 보안을 위한 국가 계획을 승인했습니다. 이를 위해 약 1,200MW 규모의 붕앙(Vung Ang) 2 화력발전소를 상업 가동하고 500kV 마이쩌우(Mai Chau) 변전소 용량을 증설하는 등 인프라를 확충하고 있습니다. 또한 수력 발전의 저수량 관리와 천연가스 공급 능력을 두 배로 늘려 전력망 안정성을 확보할 방침입니다.
-Source: [vir.com.vn](https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html)</t>
+          <t>[Power &amp; Energy] MoIT to ensure power supply security for 2026 — The Ministry of Industry and Trade has reaffirmed that Vietnam's power supply in 2026 will be fully secured.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html](https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html)
-### Document Overview
-This article details Vietnam's MoIT strategies to ensure power supply security for 2026, highlighting new plant operations, grid upgrades, and legislative efforts to accelerate PDP8 implementation.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: The MoIT has approved the national power supply plan for 2026 based on a baseline load growth scenario of 8.5 per cent... The move is expected to improve flexibility in power generation... The Vung Ang 2 thermal power venture has officially entered commercial operation, adding around 1,200 MW to the national grid. Vietnam’s revised Power Development Plan VIII sets an ambitious target of reaching total installed capacity of 183,000–236,000 MW by 2030.
-answer: Vietnam's Ministry of Industry and Trade (MoIT) has approved a power supply plan for 2026 targeting 8.5% to 14.1% load growth, supported by the recent commercial launch of the 1,200 MW Vung Ang 2 thermal power plant and upgraded regasification capacity at PV GAS. To ensure energy security against extreme weather, the government is streamlining regulatory bottlenecks to expedite Power Development Plan VIII projects while emphasizing demand-side management and grid upgrades like the 500kV Mai Chau substation.
-Source: [vir.com.vn](https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html)</t>
+          <t>[Power &amp; Energy] MoIT to ensure power supply security for 2026 — The Ministry of Industry and Trade has reaffirmed that Vietnam's power supply in 2026 will be fully secured.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html](https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html)
-### Document Overview
-The article discusses the Ministry of Industry and Trade's comprehensive strategy to secure Vietnam's electricity supply for 2026, including infrastructure upgrades, fuel capacity expansion, and legislative reforms.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The MoIT has approved the national power supply plan for 2026 based on a baseline load growth scenario of 8.5 per cent, with an extreme dry-season scenario reaching up to 14.1 per cent... To ensure system stability, the MoIT has directed all stakeholders across the electricity value chain to implement coordinated measures... The move is expected to improve flexibility in power generation in the Southeast region, helping meet southern demand, particularly during late afternoon peak hours when solar output declines.
-answer: Bộ Công Thương đã phê duyệt kế hoạch cung ứng điện quốc gia năm 2026 với kịch bản tăng trưởng phụ tải cơ sở là 8,5%, đồng thời triển khai các biện pháp phối hợp như tăng công suất tái hóa khí của PV GAS và đưa nhà máy nhiệt điện Vũng Áng 2 vào vận hành. Bên cạnh việc nâng cấp hạ tầng lưới điện và trạm biến áp, Chính phủ cũng tập trung tháo gỡ các nút thắt pháp lý để đẩy nhanh các dự án chậm tiến độ và thúc đẩy quản lý nhu cầu điện tiết kiệm, hiệu quả.
-Source: [vir.com.vn](https://vir.com.vn/moit-to-ensure-power-supply-security-for-2026-150370.html)</t>
+          <t>[Power &amp; Energy] MoIT to ensure power supply security for 2026 — The Ministry of Industry and Trade has reaffirmed that Vietnam's power supply in 2026 will be fully secured.</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -10240,35 +8172,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html](https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html)
-### Document Overview
-The article reports on the Vietnam-Russia Economic Forum 2026, emphasizing the shift toward innovative energy cooperation, including civil nuclear and green technologies, to ensure Vietnam's energy security and strategic autonomy.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Opening the forum, Permanent Deputy Minister of Foreign Affairs Nguyen Minh Vu said that amid profound global changes, Vietnam-Russia cooperation needs to be approached in a new way, shifting from traditional forms of cooperation to a model driven by innovation, sci-tech, and development. ... Russia is emerging as a dependable energy partner. In 2025, Russia accounted for 18 per cent of oil exports to China and 32 per cent to India... Several promising areas of cooperation have been identified, including civil nuclear energy, power system stability, carbon capture and storage, hydrogen and workforce development.
-answer: 2026년 4월 하노이에서 열린 베트남-러시아 경제 포럼에서 양국은 에너지 협력을 전략적 핵심 축으로 재확인하고, 기존의 전통적 협력을 넘어 혁신과 과학기술 기반의 새로운 모델로 전환하기로 합의했습니다. 러시아는 베트남의 에너지 안보를 위한 신뢰할 수 있는 파트너로서 석유 및 천연가스 공급뿐만 아니라 민간 원자력 에너지, 수소, 탄소 포집 및 저장(CCS) 등 고도화된 기술 분야로 협력을 확대할 계획입니다. 이를 통해 베트남은 글로벌 공급망의 불확실성에 대응하고 2050년 넷제로 목표 달성을 위한 에너지 전환 동력을 확보할 것으로 기대됩니다.
-Source: [vir.com.vn](https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html)</t>
+          <t>[Power &amp; Energy] Vietnam-Russia energy cooperation: a strategic pillar in global ... — Coal imports reached nearly $1 billion in 2024, meeting around 10 per cent of Vietnam's demand, while fertilisers accounted for $228 million.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html](https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html)
-### Document Overview
-This article reports on the 2026 Vietnam-Russia Economic Forum, emphasizing the strategic importance of energy trade and future technology cooperation in civil nuclear and green energy.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: The Vietnam-Russia Economic Forum 2026 held in Hanoi on April 8... energy sector, widely regarded as the strategic backbone of bilateral relations... promising areas of cooperation have been identified, including civil nuclear energy, power system stability, carbon capture and storage, hydrogen and workforce development.
-answer: At the Vietnam-Russia Economic Forum 2026, the energy sector was highlighted as the strategic backbone of bilateral relations, with Russia emerging as a dependable partner for Vietnam's growing demand for oil, coal, and natural gas. Both nations are expanding cooperation into high-tech energy infrastructure, including civil nuclear energy, power system stability, carbon capture, and hydrogen production to align with Vietnam's 2050 net-zero goals.
-Source: [vir.com.vn](https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html)</t>
+          <t>[Power &amp; Energy] Vietnam-Russia energy cooperation: a strategic pillar in global ... — Coal imports reached nearly $1 billion in 2024, meeting around 10 per cent of Vietnam's demand, while fertilisers accounted for $228 million.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html](https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html)
-### Document Overview
-The article reports on the Vietnam-Russia Economic Forum 2026, highlighting the strategic evolution of bilateral energy cooperation towards high-tech and sustainable fields like nuclear energy and hydrogen to ensure energy security and resilience.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Opening the forum, Permanent Deputy Minister of Foreign Affairs Nguyen Minh Vu said that amid profound global changes, Vietnam-Russia cooperation needs to be approached in a new way, shifting from traditional forms of cooperation to a model driven by innovation, sci-tech, and development. Beyond traditional sectors, Vietnam-Russia cooperation is expanding into high technology and new energy fields... based on these complementarities, several promising areas of cooperation have been identified, including civil nuclear energy, power system stability, carbon capture and storage, hydrogen and workforce development.
-answer: Bài báo tổng kết Diễn đàn Kinh tế Việt Nam - Nga 2026, nhấn mạnh sự hợp tác năng lượng là trụ cột chiến lược trong bối cảnh chuyển dịch toàn cầu. Hai nước đang chuyển đổi từ các mô hình truyền thống sang hợp tác dựa trên đổi mới sáng tạo và công nghệ cao, tập trung vào các lĩnh vực hạ tầng năng lượng mới như điện hạt nhân dân dụng, ổn định hệ thống điện, thu hồi carbon và hydro.
-Source: [vir.com.vn](https://vir.com.vn/vietnam-russia-energy-cooperation-a-strategic-pillar-in-global-transition-150203.html)</t>
+          <t>[Power &amp; Energy] Vietnam-Russia energy cooperation: a strategic pillar in global ... — Coal imports reached nearly $1 billion in 2024, meeting around 10 per cent of Vietnam's demand, while fertilisers accounted for $228 million.</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -10322,35 +8236,17 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html](https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html)
-### Document Overview
-The article summarizes a Vietnam-Australia forum focused on the green transition, highlighting the need for $368 billion in investment, the importance of solar and hydro energy deregulation, and the role of the Vietnam International Financial Centre in attracting green finance.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Vietnam-Australia forum outlined clear pathways to accelerate green transition... To reach its net-zero commitments, Can Van Luc, member of the Policy Advisory Council to the Prime Minister, noted that the country required an estimated $368 billion for climate-related action... Prof. Andrew Blakers of the Australian National University argued that the single most important step for the nation was deregulating the market to allow private capital to flow freely into rooftop solar.
-answer: 베트남-호주 포럼에서 베트남의 녹색 전환을 가속화하기 위한 방안이 논의되었으며, 2045년 고소득 국가 진입 및 넷제로 목표 달성을 위해 약 3,680억 달러의 기후 행동 자금이 필요한 것으로 나타났습니다. 전문가들은 루프탑 태양광 시장 규제 완화를 통한 민간 자본 유입과 펌프식 수력 발전 활용을 주요 전략으로 제시했으며, 베트남 국제금융센터(VIFC)는 투자자 유치를 위한 세제 혜택과 법적 프레임워크 구축에 집중하고 있습니다.
-Source: [vir.com.vn](https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html)</t>
+          <t>[Power &amp; Energy] Forum outlines pathways to accelerate green transition — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, bankability ...</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html](https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html)
-### Document Overview
-The article reports on a Vietnam-Australia forum where experts discussed the $368 billion investment needed for Vietnam's green transition, focusing on rooftop solar deregulation, energy storage, and green finance incentives.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: Vietnam currently ranks among the top 20 global economies for trade volume and foreign direct investment (FDI) attraction... To reach its net-zero commitments, Can Van Luc, member of the Policy Advisory Council to the Prime Minister, noted that the country required an estimated $368 billion for climate-related action... Prof. Andrew Blakers of the Australian National University, co-inventor of the PERC solar cell, argued that the single most important step for the nation was deregulating the market to allow private capital to flow freely into rooftop solar. On energy storage, Blakers said Vietnam had approximately 6,000 potential off-river pumped hydro sites, of which it needed only six to 12.
-answer: Vietnam is seeking to accelerate its green energy transition by deregulating the rooftop solar market and developing its vast potential for off-river pumped hydro storage, requiring an estimated $368 billion for climate-related actions. To attract necessary private capital and international financiers, the Vietnam International Financial Centre is introducing investor-friendly measures such as tax incentives, carbon trading platforms, and streamlined registration processes.
-Source: [vir.com.vn](https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html)</t>
+          <t>[Power &amp; Energy] Forum outlines pathways to accelerate green transition — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, bankability ...</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html](https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html)
-### Document Overview
-Bài báo tổng hợp các ý kiến từ Diễn đàn Việt Nam - Australia về lộ trình chuyển đổi xanh, tập trung vào nhu cầu vốn 368 tỷ USD, phát triển năng lượng tái tạo và các ưu đãi từ Trung tâm Tài chính Quốc tế Việt Nam.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam currently ranks among the top 20 global economies for trade volume and foreign direct investment (FDI) attraction, with a strategic vision to achieve high-income status by 2045... To reach its net-zero commitments, Can Van Luc, member of the Policy Advisory Council to the Prime Minister, noted that the country required an estimated $368 billion for climate-related action... Prof. Andrew Blakers of the Australian National University, co-inventor of the PERC solar cell, argued that the single most important step for the nation was deregulating the market to allow private capital to flow freely into rooftop solar.
-answer: Diễn đàn Việt Nam - Australia đã thảo luận về các giải pháp thúc đẩy chuyển đổi xanh, trong đó nhấn mạnh Việt Nam cần khoảng 368 tỷ USD để thực hiện cam kết phát thải ròng bằng không (net-zero). Các chuyên gia đề xuất Việt Nam cần bãi bỏ quy định để thu hút vốn tư nhân vào điện mặt trời áp mái và tận dụng tiềm năng thủy điện tích năng lớn với hơn 6.000 địa điểm khả thi. Đồng thời, Trung tâm Tài chính Quốc tế Việt Nam (VIFC) đang xây dựng các khung pháp lý ưu đãi về thuế và sàn giao dịch tín chỉ carbon để thu hút các nhà đầu tư quốc tế.
-Source: [vir.com.vn](https://vir.com.vn/forum-outlines-pathways-to-accelerate-green-transition-150387.html)</t>
+          <t>[Power &amp; Energy] Forum outlines pathways to accelerate green transition — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, bankability ...</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -10404,35 +8300,17 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html](https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html)
-### Document Overview
-Vietnam Electricity (EVN) is accelerating the deployment of Battery Energy Storage Systems (BESS) across its subsidiaries to meet peak demand and align with the national goal of 10,000-16,300 MW storage capacity by 2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-EV-2030
-verbatim: Under the revised National Power Development Plan VIII, Vietnam aims to achieve between 10,000 MW and 16,300 MW of energy storage capacity by 2030... EVN has since 2025 instructed its subsidiaries and affiliated units to prepare for investing in and installing battery storage systems across the grid... Northern Power Corporation (EVNNPC) has conducted initial surveys of 110 kV substations suitable for BESS deployment... aiming to complete the installation of its first 100 MW of battery storage at substations by January 2027.
-answer: 베트남 전력공사(EVN)는 재생에너지 비중 확대에 따른 계통 안정성을 확보하기 위해 배터리 에너지 저장 장치(BESS) 투자를 본격화하고 있으며, 2030년까지 최대 16,300MW의 저장 용량 확보를 목표로 하는 제8차 국가전력개발계획(PDP8) 수정안을 이행하고 있습니다. 이에 따라 EVN 산하 북부전력공사(EVNNPC)와 하노이전력공사 등은 2026년까지 각각 305MW, 275MW 규모의 BESS 프로젝트를 추진 중이며, 국가 송전망 차원에서도 2027년 초까지 첫 100MW 설비 완공을 목표로 속도를 내고 있습니다.
-Source: [vir.com.vn](https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html)</t>
+          <t>[Power &amp; Energy] EVN steps up investment in battery storage to support growing ... — Vietnam Electricity is accelerating the deployment of battery energy storage systems across its power network, as the country seeks to ... (관련: VN-EV-2030)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html](https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html)
-### Document Overview
-The article details EVN's strategic push for Battery Energy Storage Systems (BESS) to manage renewable energy integration and peak demand, targeting significant capacity expansion by 2030 in line with National Power Development Plan VIII.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-EV-2030
-verbatim: Vietnam Electricity (EVN) chairman Dang Hoang An chaired a review of the implementation progress of battery energy storage systems (BESS) projects within the national power system... Under the revised National Power Development Plan VIII, Vietnam aims to achieve between 10,000 MW and 16,300 MW of energy storage capacity by 2030, reflecting the growing importance of BESS in the country’s long-term energy strategy.
-answer: Vietnam Electricity (EVN) is accelerating the deployment of battery energy storage systems (BESS) across the national grid, with major subsidiaries like EVNNPC and Hanoi Power Corporation initiating projects totaling hundreds of megawatts to ensure peak demand supply by 2026. This initiative aligns with the revised National Power Development Plan VIII (PDP8), which targets reaching 10,000 MW to 16,300 MW of energy storage capacity by 2030 to support the increasing share of renewable energy and enhance grid stability.
-Source: [vir.com.vn](https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html)</t>
+          <t>[Power &amp; Energy] EVN steps up investment in battery storage to support growing ... — Vietnam Electricity is accelerating the deployment of battery energy storage systems across its power network, as the country seeks to ... (Related: VN-EV-2030)</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html](https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html)
-### Document Overview
-Tập đoàn Điện lực Việt Nam (EVN) đang triển khai lộ trình đầu tư hệ thống lưu trữ năng lượng (BESS) quy mô lớn để hỗ trợ năng lượng tái tạo và đảm bảo an ninh năng lượng quốc gia đến năm 2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Following directives from the Ministry of Industry and Trade, EVN has since 2025 instructed its subsidiaries and affiliated units to prepare for investing in and installing battery storage systems across the grid... Under the revised National Power Development Plan VIII, Vietnam aims to achieve between 10,000 MW and 16,300 MW of energy storage capacity by 2030, reflecting the growing importance of BESS in the country’s long-term energy strategy.
-answer: Tập đoàn Điện lực Việt Nam (EVN) đang đẩy mạnh đầu tư và triển khai các hệ thống lưu trữ năng lượng bằng pin (BESS) trên toàn quốc nhằm đảm bảo ổn định hệ thống điện và đáp ứng nhu cầu phụ tải đỉnh từ năm 2026. Các đơn vị thành viên như EVNNPC, EVNHANOI và EVNSPC đã bắt đầu khảo sát và thực hiện các dự án thí điểm với mục tiêu đạt tổng công suất lưu trữ quốc gia từ 10.000 MW đến 16.300 MW vào năm 2030 theo Quy hoạch điện VIII.
-Source: [vir.com.vn](https://vir.com.vn/evn-steps-up-investment-in-battery-storage-to-support-growing-renewable-capacity-150294.html)</t>
+          <t>[Power &amp; Energy] EVN steps up investment in battery storage to support growing ... — Vietnam Electricity is accelerating the deployment of battery energy storage systems across its power network, as the country seeks to ... (Liên quan: VN-EV-2030)</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -10486,35 +8364,17 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html](https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html)
-### Document Overview
-This article features an interview with GE Vernova's CEO regarding their strategic commitment to Vietnam's energy transition, focusing on manufacturing expansion, grid modernization, and SMR technology.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: GE Vernova organises ‘Energy of Change’ events to help drive industry conversations globally... Vietnam is a promising market with significant room for growth thanks to policy stability, its location in a fast-growing region, and competitive costs. So we certainly could put more investment into Vietnam over the medium to long term... we have a manufacturing footprint now in all of our three businesses in Vietnam... we’ll touch at least 4,000 students because that’s another way we help this country move faster is by investing in the workforce.
-answer: GE Vernova의 CEO는 베트남의 급격한 전력 수요 증가와 탄소 중립 목표를 지원하기 위해 가스, 풍력, 그리드 및 소형모듈원전(SMR) 등 다각화된 에너지 솔루션 제공과 현지 제조 시설 확대를 강조했습니다. 회사는 베트남의 전력 개발 계획(PDP)에 맞춰 그리드 공장을 추가하고 전기전력대학교(EPU)와 협력하여 4,000명의 인력을 양성하는 등 중장기적인 투자를 지속할 계획입니다. 이를 통해 베트남이 저탄소 에너지 생태계를 구축하고 2030년까지 목표한 전력 용량을 달성할 수 있도록 핵심 파트너로서 기여하고자 합니다.
-Source: [vir.com.vn](https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html)</t>
+          <t>[Power &amp; Energy] Meeting Vietnam's energy moment: GE Vernova CEO — UK unveils toolkit to boost Vietnam green investment flows (March 30, 2026 | 13:45) ... Vinh Long kicks ahead with marine-energy approach (March ...</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html](https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html)
-### Document Overview
-The CEO of GE Vernova discusses the company's commitment to Vietnam's energy transition, highlighting investments in manufacturing, grid infrastructure, and talent development to meet the country's rising electricity demand and decarbonization goals.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: Vietnam is a promising market with significant room for growth thanks to policy stability, its location in a fast-growing region, and competitive costs. So we certainly could put more investment into Vietnam over the medium to long term. With investments into the country because of policy, we’re also very aligned with Vietnam’s power development plan. ... we have a manufacturing footprint now in all of our three businesses in Vietnam. ... we have announced the investments from our GE Vernova Foundation that we’re doing with the Electric Power University because there’s going to be more resources that will be needed to support this industry.
-answer: GE Vernova is expanding its strategic presence in Vietnam's energy sector by establishing a manufacturing footprint across its gas, wind, and grid businesses to support the country's goal of reaching over 200GW of capacity by 2030. The company is aligning its investments with Vietnam's Power Development Plan through new factory developments, prioritization of turbine supplies for LNG projects, and workforce training initiatives at the Electric Power University.
-Source: [vir.com.vn](https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html)</t>
+          <t>[Power &amp; Energy] Meeting Vietnam's energy moment: GE Vernova CEO — UK unveils toolkit to boost Vietnam green investment flows (March 30, 2026 | 13:45) ... Vinh Long kicks ahead with marine-energy approach (March ...</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html](https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html)
-### Document Overview
-Phỏng vấn CEO GE Vernova về chiến lược đầu tư năng lượng tại Việt Nam, tập trung vào hạ tầng lưới điện, công nghệ giảm phát thải và kế hoạch mở rộng sản xuất tại địa phương.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is a promising market with significant room for growth thanks to policy stability, its location in a fast-growing region, and competitive costs. So we certainly could put more investment into Vietnam over the medium to long term. With investments into the country because of policy, we’re also very aligned with Vietnam’s power development plan. That gives us clarity for five years on what Vietnam is trying to accomplish that allows us to invest into that certainty. And for a country that today has 90GW of capacity with goals to get it by 2030 to north of 200GW, that’s a great ambition.
-answer: Bài báo thảo luận về cam kết của GE Vernova trong việc hỗ trợ quá trình điện hóa và chuyển dịch năng lượng tại Việt Nam thông qua các công nghệ đa dạng như khí, gió, lưới điện và lò phản ứng mô-đun nhỏ (SMR). CEO của tập đoàn đánh giá cao tiềm năng tăng trưởng của thị trường Việt Nam nhờ sự ổn định chính sách và Quy hoạch điện VIII, đồng thời khẳng định kế hoạch mở rộng đầu tư vào hạ tầng sản xuất và đào tạo nhân lực tại địa phương.
-Source: [vir.com.vn](https://vir.com.vn/meeting-vietnams-energy-moment-ge-vernova-ceo-149494.html)</t>
+          <t>[Power &amp; Energy] Meeting Vietnam's energy moment: GE Vernova CEO — UK unveils toolkit to boost Vietnam green investment flows (March 30, 2026 | 13:45) ... Vinh Long kicks ahead with marine-energy approach (March ...</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -10568,35 +8428,17 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html](https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html)
-### Document Overview
-This article discusses the challenges and opportunities in Vietnam's green energy sector, focusing on the need for regulatory reforms and innovative financing to unlock investment for projects like BESS and DPPAs.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: industry leaders converged on a common assessment: while capital and technology are increasingly available, the country remains held back by a critical gap, turning near-ready projects into fully bankable investments within a still-evolving regulatory framework. ... what is required are innovative financial and legal structures tailored to local conditions ... The market feels like it is 95 per cent there, but that remaining 5 per cent, which is the finalisation of policy details, is what determines whether projects can actually move forward.
-answer: 베트남의 에너지 전환은 자본과 기술적 역량은 충분하나, 미비한 규제 프레임워크와 프로젝트의 은행 대출 적격성(bankability) 부족으로 인해 실제 투자가 지연되고 있습니다. 전문가들은 직접전력구매계약(DPPA)과 배터리 에너지 저장 시스템(BESS) 등의 확산을 위해 현지 실정에 맞는 혁신적인 금융 구조와 명확한 정책 세부 사항의 확정이 시급하다고 강조합니다. 이를 해결하기 위해 혼합 금융(blended finance)과 오렌지 본드(orange bonds) 등 리스크 분담을 위한 다양한 금융 솔루션 도입이 제안되고 있습니다.
-Source: [vir.com.vn](https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html)</t>
+          <t>[Power &amp; Energy] Vietnam's green push requires further hurdles to clear — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, ...</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html](https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html)
-### Document Overview
-The article discusses the challenges and opportunities in Vietnam's green energy sector, focusing on the need for regulatory reform, project bankability, and innovative financing to support renewable energy infrastructure.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: At the UK-Vietnam Green Investment Forum... industry leaders converged on a common assessment: while capital and technology are increasingly available, the country remains held back by a critical gap, turning near-ready projects into fully bankable investments within a still-evolving regulatory framework. ... The deployment of BESS at scale will be a major driver, and what we are seeing now is the application of system-wide solutions that combine digitalisation, digital twins, and AI optimisation. ... DPPAs essentially allow developers to build large-scale solar or wind projects and sell electricity through the grid, which is a significant step forward.
-answer: Vietnam's transition to green energy is currently hampered by regulatory gaps and bankability issues despite the increasing availability of international capital and advanced technologies like battery energy storage systems (BESS). Industry experts highlight that while new Direct Power Purchase Agreements (DPPAs) and blended finance mechanisms like 'orange bonds' are emerging, the sector requires finalized policy details and a more flexible financial system to unlock large-scale renewable projects. Consequently, the focus is shifting toward project financing and integrated digital solutions to bridge the 5% gap remaining in policy implementation.
-Source: [vir.com.vn](https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html)</t>
+          <t>[Power &amp; Energy] Vietnam's green push requires further hurdles to clear — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, ...</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html](https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html)
-### Document Overview
-Phân tích những thách thức và giải pháp tài chính, pháp lý để thúc đẩy hạ tầng năng lượng xanh tại Việt Nam thông qua các công nghệ mới và cơ chế tài chính quốc tế.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: At the UK-Vietnam Green Investment Forum... industry leaders converged on a common assessment: while capital and technology are increasingly available, the country remains held back by a critical gap, turning near-ready projects into fully bankable investments within a still-evolving regulatory framework... The market feels like it is 95 per cent there, but that remaining 5 per cent, which is the finalisation of policy details, is what determines whether projects can actually move forward.
-answer: Bài báo thảo luận về việc Việt Nam đang đứng trước cơ hội lớn trong chuyển đổi năng lượng xanh với sự sẵn có về vốn và công nghệ, nhưng hiện vẫn gặp rào cản từ khung pháp lý chưa hoàn thiện để biến các dự án tiềm năng thành các khoản đầu tư có khả năng vay vốn ngân hàng. Các chuyên gia nhấn mạnh tầm quan trọng của việc triển khai các cơ chế mới như hợp đồng mua bán điện trực tiếp (DPPA), hệ thống lưu trữ năng lượng bằng pin (BESS) và các giải pháp tài chính hỗn hợp để thúc đẩy đầu tư tư nhân vào hạ tầng bền vững.
-Source: [vir.com.vn](https://vir.com.vn/vietnams-green-push-requires-further-hurdles-to-clear-149490.html)</t>
+          <t>[Power &amp; Energy] Vietnam's green push requires further hurdles to clear — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, ...</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -10650,35 +8492,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html](https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html)
-### Document Overview
-This article discusses Power Transmission Company No.2 (PTC2)'s strategies and investment plans to ensure the safety and efficiency of Central Vietnam's power grid amidst energy transition and peak demand challenges.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: The central region holds a uniquely strategic position in Vietnam’s power system, acting as a bridge that transmits electricity from local generation sources... to the north. PTC2 is implementing 14 projects with total planned disbursement of $12.8 million, including upgrading the 500kV switchyard configuration and expanding capacity at Danang substation... All transmission line management teams now deploy unmanned aerial vehicles for inspections.
-answer: 베트남 전력공사 산하 PTC2는 중부 지역의 전력망 안정성을 확보하기 위해 다낭 변전소 확장 및 500kV 스위치야드 업그레이드 등 1,280만 달러 규모의 14개 프로젝트를 추진하고 있습니다. 건기 안전 운영을 위해 드론(UAV), 열화상 카메라, LiDAR 기술을 활용한 디지털 전환을 가속화하고 있으며, 산불 방지 및 고속도로 교차 지점 관리 등 전력망 보안 강화에 집중하고 있습니다. 이 지역은 수력과 신재생 에너지를 북부로 전달하는 핵심 허브로서, 제8차 국가전력개발계획(PDP8)에 따라 향후 고압직류송전(HVDC) 도입 및 주요 변전소 확충이 지속될 예정입니다.
-Source: [vir.com.vn](https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html)</t>
+          <t>[Power &amp; Energy] Safe operations ensured during energy transition — Vietnam's central region is increasingly emerging as a critical balancing hub within the national power system.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html](https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html)
-### Document Overview
-This article discusses the strategic role of Vietnam's central region in power transmission and the specific measures Power Transmission Company 2 (PTC2) is taking to modernize infrastructure and ensure grid safety in 2026.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: The central region holds a uniquely strategic position in Vietnam’s power system, acting as a bridge that transmits electricity from local generation sources... to the north. In 2026, PTC2 is implementing 14 projects with total planned disbursement of $12.8 million, including upgrading the 500kV switchyard configuration and expanding capacity at Danang substation; enhancing transmission capacity across multiple 220kV lines and substations.
-answer: Power Transmission Company 2 (PTC2) is prioritizing the stability of Vietnam's central power grid during the energy transition and dry season by implementing 14 infrastructure projects in 2026 with a $12.8 million investment. These efforts include upgrading the 500kV Danang substation, enhancing 220kV transmission lines, and deploying digital transformation technologies like UAVs and LiDAR to ensure energy security and manage risks from extreme weather and infrastructure development.
-Source: [vir.com.vn](https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html)</t>
+          <t>[Power &amp; Energy] Safe operations ensured during energy transition — Vietnam's central region is increasingly emerging as a critical balancing hub within the national power system.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html](https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html)
-### Document Overview
-The article discusses PTC2's strategic role in maintaining Vietnam's power backbone, detailing their infrastructure projects, digital transformation efforts, and emergency preparedness in the central region.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The central region holds a uniquely strategic position in Vietnam’s power system, acting as a bridge that transmits electricity from local generation sources... to the north. PTC2 is implementing 14 projects with total planned disbursement of $12.8 million, including upgrading the 500kV switchyard configuration and expanding capacity at Danang substation... All transmission line management teams now deploy unmanned aerial vehicles for inspections.
-answer: Bài báo đề cập đến vai trò chiến lược của Công ty Truyền tải điện 2 (PTC2) trong việc đảm bảo vận hành lưới điện an toàn tại khu vực miền Trung, đặc biệt là trong giai đoạn chuyển đổi năng lượng và mùa khô. Trong năm 2026, PTC2 triển khai 14 dự án hạ tầng với tổng vốn đầu tư 12,8 triệu USD, bao gồm nâng cấp trạm biến áp 500kV Đà Nẵng và ứng dụng các công nghệ hiện đại như drone, LiDAR và camera nhiệt để tối ưu hóa công tác kiểm tra, bảo trì hệ thống truyền tải.
-Source: [vir.com.vn](https://vir.com.vn/safe-operations-ensured-during-energy-transition-149831.html)</t>
+          <t>[Power &amp; Energy] Safe operations ensured during energy transition — Vietnam's central region is increasingly emerging as a critical balancing hub within the national power system.</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -10732,35 +8556,17 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html](https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html)
-### Document Overview
-The article details Prime Minister Phạm Minh Chính's directive to ensure Vietnam's power supply from 2026 to 2030 by accelerating major energy projects and establishing a competitive power market.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business activities and daily life during peak periods in 2026 and through 2030, stressing that power shortages must not be allowed under any circumstances. ... To ensure power supply for 2027-30 period, the government plans to push ahead with major power projects, including LNG-fired power plants, hydropower expansion and offshore wind developments with the aim of bringing some projects online one to two years ahead of schedule. ... Of note, preparations for the Ninh Thuận nuclear power plants will be sped up, focusing on removing administrative and legal bottlenecks.
-answer: 베트남 팜 민 찐 총리는 2026년부터 2030년까지 전력 부족 사태를 방지하기 위한 지침(Directive No 01/CT-TTg)을 발표하고, 주요 전력 발전 및 송전 프로젝트의 가속화를 지시했습니다. 정부는 연간 12-15%에 달할 것으로 예상되는 전력 수요 증가에 대응하기 위해 LNG 발전소, 수력 확장, 해상 풍력 사업을 앞당겨 추진하고 닌투언(Ninh Thuận) 원자력 발전소 준비 작업에도 속도를 낼 계획입니다. 또한 에너지 안보 확보를 위해 경쟁력 있고 투명한 전력 시장 구축과 가격 체계 개선을 장기적인 해결책으로 강조했습니다.
-Source: [vietnamnews.vn](https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html)</t>
+          <t>[Power &amp; Energy] PM issues directive to ensure power supply in 2026–30, focusing on ... — HÀ NÔI — Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business ...</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html](https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html)
-### Document Overview
-The article reports on a new government directive in Vietnam aimed at securing national energy security from 2026-2030 by accelerating power projects and developing a competitive electricity market.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business activities and daily life during peak periods in 2026 and through 2030, stressing that power shortages must not be allowed under any circumstances... Authorities have been requested to mobilise all available resources, speed up power generation and transmission projects and prevent delays caused by administrative procedures.
-answer: Vietnamese Prime Minister Phạm Minh Chính issued Directive No 01/CT-TTg to ensure stable electricity supply for the 2026–2030 period, mandating that no power shortages occur during this critical socio-economic development phase. The directive prioritizes accelerating major infrastructure projects including LNG-fired plants, offshore wind, and the Ninh Thuận nuclear power plant, while also advocating for a transition to a competitive, transparent power market to meet an anticipated 12-15% annual increase in energy demand.
-Source: [vietnamnews.vn](https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html)</t>
+          <t>[Power &amp; Energy] PM issues directive to ensure power supply in 2026–30, focusing on ... — HÀ NÔI — Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business ...</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>## [https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html](https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html)
-### Document Overview
-This article discusses Vietnam's Directive No 01/CT-TTg, which mandates ensuring electricity security for 2026-2030 by accelerating major energy infrastructure projects and developing a competitive power market.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business activities and daily life during peak periods in 2026 and through 2030, stressing that power shortages must not be allowed under any circumstances. Under Directive No 01/CT-TTg dated January 18, the PM emphasised that ensuring adequate power supply would be critical... The directive also calls for electricity-saving measures to be stepped up together with closer supervision of fuel supplies for thermal power plants, and tighter coordination with the National System and Market Operator to forecast demand and secure adequate supplies of coal, gas and oil for power generation during the period.
-answer: Thủ tướng Chính phủ Phạm Minh Chính vừa ban hành Chỉ thị số 01/CT-TTg nhằm đảm bảo cung cấp điện đầy đủ cho sản xuất và sinh hoạt trong giai đoạn 2026-2030, tuyệt đối không để xảy ra tình trạng thiếu điện. Chỉ thị nhấn mạnh việc đẩy nhanh tiến độ các dự án truyền tải và nguồn điện trọng điểm, bao gồm nhiệt điện LNG, điện gió ngoài khơi và chuẩn bị cho điện hạt nhân Ninh Thuận, đồng thời hướng tới xây dựng thị trường điện cạnh tranh, minh bạch để đáp ứng nhu cầu tăng trưởng GDP 10% mỗi năm.
-Source: [vietnamnews.vn](https://vietnamnews.vn/economy/1764109/pm-issues-directive-to-ensure-power-supply-in-2026-30-focusing-on-speeding-up-major-projects.html)</t>
+          <t>[Power &amp; Energy] PM issues directive to ensure power supply in 2026–30, focusing on ... — HÀ NÔI — Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business ...</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -10814,35 +8620,17 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html](https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html)
-### Document Overview
-Vietnam saw a 42.9% year-on-year increase in total registered FDI in Q1 2026, reaching $15.2 billion, primarily driven by the manufacturing and energy sectors.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Finance &amp; Investment, 관련 마스터플랜: N/A
-verbatim: foreign direct investment inflows into Vietnam rebounded strongly in the first quarter of 2026, reaching $15.2 billion, up more than 42 per cent on-year. ... Of the total disbursed FDI, manufacturing and processing accounted for $4.48 billion (82.8 per cent), followed by real estate at $389.5 million (7.2 per cent), and electricity, gas, steam and air conditioning supply at $196.1 million (3.6 per cent).
-answer: 2026년 1분기 베트남의 외국인 직접투자(FDI) 유입액은 전년 동기 대비 42.9% 증가한 152억 달러를 기록하며 강력한 반등세를 보였습니다. 이 중 가공 및 제조업이 신규 투자 자본의 69%를 차지하며 가장 큰 비중을 기록했고, 전기·가스·수도 배급 분야가 그 뒤를 이었습니다. 투자 국가별로는 싱가포르가 53억 2천만 달러로 최대 투자국으로 나타났으며, 실질 집행된 FDI 규모 또한 9.1% 증가한 54억 1천만 달러로 역대 최고 수준을 달성했습니다.
-Source: [vir.com.vn](https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html)</t>
+          <t>[Finance &amp; Investment] FDI surges in Vietnam as Q1 capital climbs 43 per cent on-year — In total, Vietnam's overseas investment (including new and adjusted capital) reached $619.9 million in the first three months of 2026, up 2.6 ...</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html](https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html)
-### Document Overview
-The article reports on a 42.9% year-on-year increase in Vietnam's registered FDI for Q1 2026, totaling $15.2 billion, with Singapore and South Korea emerging as the top investors.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Finance &amp; Investment, Related plans: N/A
-verbatim: Foreign direct investment inflows into Vietnam rebounded strongly in the first quarter of 2026, reaching $15.2 billion, up more than 42 per cent on-year... total registered foreign direct investment (FDI) into Vietnam as of March 31 stood at $15.2 billion, a 42.9 per cent increase on the same period last year... disbursed FDI in the first three months of 2026 was estimated at $5.41 billion, up 9.1 per cent on-year.
-answer: Vietnam's foreign direct investment (FDI) saw a significant surge in the first quarter of 2026, with total registered capital reaching $15.2 billion, a 42.9% increase compared to the previous year. Disbursed capital also hit a five-year high for the period at $5.41 billion, driven primarily by the manufacturing and processing sector which accounted for nearly 70% of new investment capital.
-Source: [vir.com.vn](https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html)</t>
+          <t>[Finance &amp; Investment] FDI surges in Vietnam as Q1 capital climbs 43 per cent on-year — In total, Vietnam's overseas investment (including new and adjusted capital) reached $619.9 million in the first three months of 2026, up 2.6 ...</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html](https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html)
-### Document Overview
-Bài báo báo cáo sự phục hồi mạnh mẽ của vốn FDI vào Việt Nam trong Q1/2026 đạt 15,2 tỷ USD, đồng thời cung cấp chi tiết về các quốc gia đầu tư hàng đầu và các lĩnh vực trọng điểm như sản xuất và năng lượng.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: foreign direct investment inflows into Vietnam rebounded strongly in the first quarter of 2026, reaching $15.2 billion, up more than 42 per cent on-year... total FDI into manufacturing and processing reached $8.85 billion, accounting for 70.6 per cent of total registered capital. Electricity, gas and water distribution accounted for $2.28 billion (18.2 per cent)... Vietnam’s overseas investment (including new and adjusted capital) reached $619.9 million in the first three months of 2026, up 2.6 times on-year.
-answer: Trong quý I năm 2026, dòng vốn đầu tư trực tiếp nước ngoài (FDI) vào Việt Nam tăng trưởng mạnh mẽ, đạt 15,2 tỷ USD, tăng gần 43% so với cùng kỳ năm trước. Lĩnh vực chế biến, chế tạo và năng lượng (điện, khí, nước) chiếm tỷ trọng lớn nhất trong cơ cấu đầu tư, trong khi vốn giải ngân cũng đạt mức cao nhất trong giai đoạn 2022-2026 với 5,41 tỷ USD. Song song đó, đầu tư ra nước ngoài của doanh nghiệp Việt Nam cũng tăng gấp 2,6 lần, tập trung chủ yếu vào các thị trường Lào, Kyrgyzstan và Vương quốc Anh.
-Source: [vir.com.vn](https://vir.com.vn/fdi-surges-in-vietnam-as-q1-capital-climbs-43-per-cent-on-year-150100.html)</t>
+          <t>[Finance &amp; Investment] FDI surges in Vietnam as Q1 capital climbs 43 per cent on-year — In total, Vietnam's overseas investment (including new and adjusted capital) reached $619.9 million in the first three months of 2026, up 2.6 ...</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -10896,37 +8684,17 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html](https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html)
-### Document Overview
-This article discusses how Vietnam's domestic solar power generation is projected to save nearly $600 million in fossil fuel import costs amidst rising energy prices due to geopolitical conflicts.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: N/A
-verbatim: Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports, as prices for both commodities soar from the Iran war, according to a report by Zero Carbon Analytics on March 16. ... These savings comprise $49.3 million from gas import costs and $545.4 million from coal imports. ... In 2024, Vietnam’s solar and wind generation totalled 38.7 Terawatt-hours, representing about 13 per cent of its power generation.
-answer: 이란 전쟁으로 인한 국제 에너지 가격 급등 속에서 베트남은 태양광 발전을 통해 약 5억 9,400만 달러 규모의 석탄 및 가스 수입 비용을 절감할 수 있을 것으로 전망됩니다. 2024년 기준 베트남의 재생에너지 발전 비중은 약 13%에 도달했으며, 이러한 청정 에너지 우선 정책은 글로벌 에너지 가격 변동에 따른 경제적 충격을 완화하고 공공 보건 재원 확보에도 기여하고 있습니다.
-Source: [vir.com.vn](https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html)</t>
+          <t>[Power &amp; Energy] Solar power could save Vietnam $600 million in fossil fuel imports — Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports.</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html](https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html)
-### Document Overview
-According to a report by Zero Carbon Analytics, Vietnam's domestic solar generation can mitigate the economic impact of soaring global energy prices by saving $594 million in potential coal and gas imports.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: N/A
-verbatim: Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports, as prices for both commodities soar from the Iran war, according to a report by Zero Carbon Analytics on March 16... Vietnam’s solar generation could help the country avoid $594 million in coal and gas imports, assuming current benchmark prices remain at similar levels for a year. These savings comprise $49.3 million from gas import costs and $545.4 million from coal imports.
-answer: Vietnam is projected to save approximately $594 million in fossil fuel import costs by utilizing domestic solar power to offset high global coal and gas prices triggered by conflict in the Middle East. These savings, calculated by Zero Carbon Analytics, include $545.4 million from coal and $49.3 million from gas, potentially providing enough funds to cover healthcare for 2.2 million citizens. Vietnam currently leads the ASEAN-5 in solar and wind generation, which accounted for 13% of its power mix in 2024.
-Source: [vir.com.vn](https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html)</t>
+          <t>[Power &amp; Energy] Solar power could save Vietnam $600 million in fossil fuel imports — Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>## [https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html](https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html)
-### Document Overview
-Bài báo phân tích lợi ích kinh tế của điện mặt trời tại Việt Nam, giúp tiết kiệm gần 600 triệu USD nhập khẩu nhiên liệu trong bối cảnh chiến tranh Iran làm tăng giá khí LNG và than. Việt Nam hiện dẫn đầu ASEAN về tỷ trọng năng lượng tái tạo nhờ các chính sách hỗ trợ phát triển hạ tầng điện mặt trời từ năm 2017.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports, as prices for both commodities soar from the Iran war... These savings comprise $49.3 million from gas import costs and $545.4 million from coal imports... Vietnam has the highest solar and wind generation compared to the ASEAN-5.
-answer: 1. Nhờ việc sử dụng điện mặt trời trong nước, Việt Nam có thể tiết kiệm được khoảng 594 triệu USD chi phí nhập khẩu than và khí đốt trong bối cảnh giá năng lượng toàn cầu tăng cao do xung đột ở Trung Đông. 
-2. Các phân tích cho thấy việc ưu tiên năng lượng sạch không chỉ giúp giảm bớt tác động của giá nhiên liệu hóa thạch mà còn đóng góp ngân sách tương đương nhu cầu chăm sóc sức khỏe hàng năm cho khoảng 2,2 triệu dân. 
-3. Hiện tại, Việt Nam đang dẫn đầu khu vực ASEAN-5 về sản lượng điện gió và điện mặt trời, chiếm khoảng 13% tổng sản lượng điện quốc gia tính đến năm 2024.
-Source: [vir.com.vn](https://vir.com.vn/solar-power-could-save-vietnam-600-million-in-fossil-fuel-imports-148882.html)</t>
+          <t>[Power &amp; Energy] Solar power could save Vietnam $600 million in fossil fuel imports — Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports.</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -11431,35 +9199,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>## [https://www.vntpa.org/pdp8-en](https://www.vntpa.org/pdp8-en)
-### Document Overview
-This document outlines the official approval and detailed contents of Vietnam's National Power Development Plan for 2021-2030 (PDP8), focusing on energy security, renewable energy transition, and grid modernization.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: Article 1. To approve the National Power Development Plan for the 2021 - 2030 period, with a vision to 2050 (NPDP 8)... To ensure national energy security for socio-economic development, industrialization, and modernization. To successfully carry out just energy transition in conjunction with modernizing electricity generation, establishing smart electricity grid, managing advanced power systems towards the green transition, emissions reduction, and scientific and technological development.
-answer: 베트남 정부는 2030년까지의 국가 전력 개발 계획과 2050년 비전을 담은 제8차 국가전력개발계획(PDP8)을 공식 승인하였습니다. 이 계획은 에너지 안보 확보와 경제 성장을 목표로 하며, 특히 화석 연료 의존도를 낮추고 풍력, 태양광 등 재생 에너지 비중을 2050년까지 최대 71.5%로 확대하는 녹색 전환과 탄소 중립 실현을 핵심으로 합니다. 또한, 스마트 그리드 구축과 지역 간 전력망 연결을 통해 에너지 산업 생태계를 현대화하고 신에너지 수출 가능성을 열어두는 포괄적인 에너지 전략을 제시하고 있습니다.
-Source: [www.vntpa.org](https://www.vntpa.org/pdp8-en)</t>
+          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>## [https://www.vntpa.org/pdp8-en](https://www.vntpa.org/pdp8-en)
-### Document Overview
-This document is the official Prime Minister's Decision No. 500/Q-TTg approving Vietnam's Power Development Plan 8 (PDP8), detailing capacity targets, energy mix transitions, and investment requirements for the 2021-2050 period.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: Article 1. To approve the National Power Development Plan for the 2021 - 2030 period, with a vision to 2050 (NPDP 8)... To ensure adequate electricity supply for the domestic demand, meeting the national socio-economic development goals with average GDP growth of approximately 7%/year in the 2021 – 2030 period... By 2030, the share of renewable energy is expected to reach about 30.9-39.2%... By 2050, it is oriented to phase out coal for power generation.
-answer: Vietnam has officially approved the National Power Development Plan for 2021-2030 (PDP8), which prioritizes national energy security and a just energy transition by targeting a renewable energy share of up to 47% by 2030 and nearly 71.5% by 2050. The plan outlines a total investment requirement of approximately $134.7 billion through 2030 to modernize the grid and shift away from coal-fired power toward domestic gas, LNG, and expanded wind and solar capacities. Furthermore, the strategy aims for 100% rural electrification by 2025 and establishes inter-regional renewable energy industrial hubs to foster a comprehensive green energy ecosystem.
-Source: [www.vntpa.org](https://www.vntpa.org/pdp8-en)</t>
+          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>## [https://www.vntpa.org/pdp8-en](https://www.vntpa.org/pdp8-en)
-### Document Overview
-This document is the official English translation of Vietnam's National Power Development Plan for 2021-2030 (PDP8), detailing targets for energy security, renewable energy expansion, and the roadmap for transitioning away from fossil fuels.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Article 1. To approve the National Power Development Plan for the 2021 - 2030 period, with a vision to 2050 (NPDP 8)... To ensure national energy security for socio-economic development, industrialization, and modernization... To successfully carry out just energy transition in conjunction with modernizing electricity generation, establishing smart electricity grid... towards the green transition, emissions reduction.
-answer: Quyết định số 500/QĐ-TTg phê duyệt Quy hoạch điện VIII (PDP8) nhằm đảm bảo an ninh năng lượng quốc gia và thúc đẩy chuyển đổi năng lượng công bằng thông qua việc ưu tiên phát triển năng lượng tái tạo, khí LNG và hiện đại hóa lưới điện thông minh. Kế hoạch đặt mục tiêu cung cấp đủ điện cho tăng trưởng GDP trung bình 7%/năm giai đoạn 2021-2030, đồng thời hướng tới mục tiêu phát thải ròng bằng không vào năm 2050 bằng cách loại bỏ dần nhiệt điện than.
-Source: [www.vntpa.org](https://www.vntpa.org/pdp8-en)</t>
+          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -11509,35 +9259,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>## [https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)
-### Document Overview
-This article analyzes Vietnam's Power Development Plan VIII (PDP8), detailing the strategic shift toward renewables, required investment of $700 billion by 2050, and implications for energy sector investors.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: The market has welcomed the long-awaited PDP VIII, approved in late May of this year, which provides an ambitious plan through 2030 with a vision towards 2050... PDP VIII presents an ambitious shift for Vietnam’s generation mix away from coal, and heavily weighted towards in renewables and new technologies such as battery storage, hydrogen, and ammonia... This amounts to a roughly 2x projected growth to 150 GW in installed capacity by 2030, and 500 GW by 2050. Nearly 700 billion USD in investment would be required over the next three decades.
-answer: 베트남 정부가 승인한 제8차 국가전력개발계획(PDP8)은 2050년 넷제로 달성을 위해 석탄 화력 발전을 줄이고 재생에너지, 수소, 암모니아 및 배터리 저장 시스템(BESS)으로의 과감한 전환을 골자로 하고 있습니다. 이 계획에 따라 베트남은 2030년까지 발전 설비 용량을 150GW로 확충하고 2050년까지 500GW 확대를 목표로 하고 있으며, 이를 위해 향후 30년간 약 7,000억 달러 규모의 막대한 투자가 필요할 것으로 전망됩니다. 이번 마스터플랜 확정은 에너지 섹터의 불확실성을 해소하고 투자자들에게 구체적인 우선순위와 상업적 기회를 제공하는 중요한 이정표가 될 것입니다.
-Source: [www.pwc.com](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)</t>
+          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>## [https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)
-### Document Overview
-This page provides an analysis of Vietnam's PDP8, highlighting the shift toward renewable energy, the $700 billion investment requirement, and capacity targets for 2030 and 2050.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: The market has welcomed the long-awaited PDP VIII, approved in late May of this year, which provides an ambitious plan through 2030 with a vision towards 2050... This amounts to a roughly 2x projected growth to 150 GW in installed capacity by 2030, and 500 GW by 2050. Nearly 700 billion USD in investment would be required over the next three decades in new and retrofitted generation, as well as in grid infrastructure to achieve these ambitious targets.
-answer: 1. Vietnam has officially approved the Power Development Plan VIII (PDP8), which aims to reach 150 GW of installed capacity by 2030 and 500 GW by 2050 to support the nation's economic growth and NetZero commitments. 2. This transition requires approximately $700 billion USD in investments over the next three decades, shifting the generation mix away from coal toward renewables, battery storage, and hydrogen. 3. The plan provides a clearer strategic framework for international and domestic investors to participate in Vietnam's power generation and grid infrastructure modernization.
-Source: [www.pwc.com](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)</t>
+          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>## [https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)
-### Document Overview
-This article discusses Vietnam's Power Development Plan VIII (PDP8), outlining the shift towards renewable energy and the $700 billion investment needed for power infrastructure through 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The market has welcomed the long-awaited PDP VIII, approved in late May of this year, which provides an ambitious plan through 2030 with a vision towards 2050. ... This amounts to a roughly 2x projected growth to 150 GW in installed capacity by 2030, and 500 GW by 2050. Nearly 700 billion USD in investment would be required over the next three decades in new and retrofitted generation, as well as in grid infrastructure to achieve these ambitious targets.
-answer: Quy hoạch điện VIII (PDP VIII) đề ra lộ trình chiến lược nhằm chuyển dịch cơ cấu năng lượng Việt Nam từ than sang năng lượng tái tạo và các công nghệ mới để đạt mục tiêu NetZero vào năm 2050. Kế hoạch này dự kiến cần khoảng 700 tỷ USD vốn đầu tư trong ba thập kỷ tới để nâng công suất lắp đặt lên 150 GW vào năm 2030 và 500 GW vào năm 2050, đồng thời phát triển hệ thống lưới điện hiện đại. Đây là cột mốc quan trọng mở ra nhiều cơ hội cho các nhà đầu tư trong lĩnh vực hạ tầng năng lượng, mặc dù vẫn còn những thách thức trong việc thực thi thực tế.
-Source: [www.pwc.com](https://www.pwc.com/vn/en/publications/vietnam-publications/pdp8-insights.html)</t>
+          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -11591,35 +9323,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>## [https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)
-### Document Overview
-The article analyzes Vietnam's PDP8, highlighting the strategic shift toward renewable energy, the phased decommissioning of coal plants by 2050, and the investment challenges ahead.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: On May 15, 2023, the Vietnamese government released Vietnams Eight Power Development Plan (PDP8) for the period of 2021-2030, with a vision to 2050. The PDP8 represents a paradigm shift in Vietnams energy sector away from carbon intensive fossil fuels towards clean energy. In 2030, wind, solar, hydropower and biomass will provide 48% of Vietnams installed capacity, this share will rise to around 63% in 2050.
-answer: 베트남 정부는 2030년까지의 에너지 믹스와 국가 송전망 계획을 담은 제8차 국가전력개발계획(PDP8)을 확정하여 화석 연료 중심에서 재생 에너지 중심으로의 전환을 본격화했습니다. 이 계획에 따라 약 13GW의 석탄 화력 발전 프로젝트가 취소되고 2050년까지 모든 석탄 발전소의 연료 전환 또는 폐쇄가 추진되며, 2050년에는 태양광과 풍력이 주요 에너지원이 될 전망입니다. 섹터: Power &amp; Energy, 마스터플랜: VN-PWR-PDP8.
-Source: [greenfdc.org](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>## [https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)
-### Document Overview
-This article analyzes Vietnam's Eighth Power Development Plan (PDP8), detailing its targets for coal decommissioning, gas transition, and the expansion of renewable energy to reach net-zero by 2050.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: On May 15, 2023, the Vietnamese government released Vietnams Eight Power Development Plan (PDP8) for the period of 2021-2030, with a vision to 2050... The PDP8 represents a paradigm shift in Vietnams energy sector away from carbon intensive fossil fuels towards clean energy. All stakeholders, including government agencies, public energy companies, investors, NGOs, international partners, and others, should work together to ensure that coal phase out can be achieved as soon as possible and that energy supply can be largely covered by renewable and new forms of energy soon.
-answer: The Vietnamese government has officially released the Eighth National Power Development Plan (PDP8) for 2021-2030, marking a strategic shift toward decarbonization by canceling 13GW of planned coal capacity and prioritizing renewable energy integration. The plan aims for wind, solar, hydropower, and biomass to constitute 48% of installed capacity by 2030, while mandating that all coal-fired plants either convert to alternative fuels or cease operations by 2050. To support this transition, the government targets covering 50% of office and residential buildings with rooftop solar and requires an estimated $135 billion in investment through 2030 to modernize the national grid and power sources.
-Source: [greenfdc.org](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>## [https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)
-### Document Overview
-This article provides a comprehensive analysis of Vietnam's Power Development Plan 8 (PDP8), detailing the shift from coal to renewable energy and the associated investment challenges.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: On May 15, 2023, the Vietnamese government released Vietnams Eight Power Development Plan (PDP8) for the period of 2021-2030, with a vision to 2050... The PDP8 represents a paradigm shift in Vietnams energy sector away from carbon intensive fossil fuels towards clean energy.
-answer: Quy hoạch điện VIII (PDP8) của Việt Nam định hướng lộ trình phát triển hạ tầng năng lượng giai đoạn 2021-2030, tập trung vào việc giảm dần nhiệt điện than và đẩy mạnh chuyển đổi sang các nguồn năng lượng tái tạo như gió và mặt trời. Kế hoạch này đặt mục tiêu hiện đại hóa hệ thống lưới điện thông minh và thu hút hàng trăm tỷ USD vốn đầu tư để đạt được phát thải ròng bằng không vào năm 2050.
-Source: [greenfdc.org](https://greenfdc.org/vietnams-eight-national-power-development-plan-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -11673,26 +9387,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>## [https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)
-### Document Overview
-This page is a placeholder or an introductory guide for the ITA's Global Business Navigator Chatbot, rather than the specific market intelligence report on Vietnam's Power Development Plan VIII.
-Source: [www.trade.gov](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)</t>
+          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (관련: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>## [https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)
-### Document Overview
-The page provides an overview and user disclaimer for the Global Business Navigator Chatbot, an AI tool by the International Trade Administration, rather than the expected market intelligence on Vietnam.
-Source: [www.trade.gov](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)</t>
+          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (Related: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>## [https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)
-### Document Overview
-Nội dung trang web hiện tại chỉ cung cấp thông tin giới thiệu và hướng dẫn sử dụng cho chatbot Global Business Navigator của ITA, không chứa nội dung bài báo về cơ sở hạ tầng Việt Nam.
-Source: [www.trade.gov](https://www.trade.gov/market-intelligence/vietnam-revised-power-development-plan-viii)</t>
+          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (Liên quan: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -11742,35 +9447,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>## [https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)
-### Document Overview
-This article analyzes Vietnam's Power Development Plan 8 (PDP8), detailing the strategic shift toward renewable energy (solar, wind) and the regulatory/infrastructural challenges facing the transition.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam’s Power Development Plan 8 (PDP8) stands as a seminal policy document, articulating a profound strategic shift towards accelerating the nation’s transition from a fossil fuel-dependent energy landscape to one dominated by renewables... Approved in May 2023, this comprehensive sectoral development plan spans the period 2021-2030, with an ambitious vision extending to 2050... The commitment to net-zero by 2050 has been a primary catalyst for the iterative revisions and ratifications of PDP8.
-answer: 베트남의 제8차 국가전력개발계획(PDP8)은 2050년 탄소중립 달성을 목표로 화석 연료 중심에서 재생에너지 중심으로의 에너지 전환을 가속화하는 핵심 전략입니다. 이 계획은 태양광, 풍력, 에너지 저장 시스템(BESS) 분야의 투자를 장려하고 직접전력구매계약(DPPA) 등 시장 자유화 조치를 포함하고 있으나, 낮은 가격 체계와 송전망 부족 문제는 여전히 해결해야 할 과제로 남아있습니다.
-Source: [sea.ub-speeda.com](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>## [https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)
-### Document Overview
-This report analyzes Vietnam's PDP8 energy strategy, highlighting the shift toward solar, wind, and storage while addressing barriers like grid curtailment and pricing frameworks.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam’s Power Development Plan 8 (PDP8) stands as a seminal policy document, articulating a profound strategic shift towards accelerating the nation’s transition from a fossil fuel-dependent energy landscape to one dominated by renewables. Approved in May 2023, this comprehensive sectoral development plan spans the period 2021-2030, with an ambitious vision extending to 2050... The commitment to net-zero by 2050 has been a primary catalyst for the iterative revisions and ratifications of PDP8... The revisions are meticulously aligned with fulfilling domestic electricity needs and supporting ambitious economic growth targets.
-answer: Vietnam's Power Development Plan 8 (PDP8) outlines a strategic transition toward a renewable-heavy energy mix to achieve net-zero emissions by 2050 while supporting 10% annual economic growth. The plan emphasizes rapid deployment of rooftop solar through new Direct Power Purchase Agreements (DPPAs), expansion of onshore wind, and the critical integration of energy storage systems to stabilize the national grid. Despite high ambitions, the infrastructure shift faces challenges including grid congestion in renewable-rich regions and the need for more attractive pricing frameworks to secure large-scale investment.
-Source: [sea.ub-speeda.com](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>## [https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)
-### Document Overview
-This report analyzes Vietnam's Power Development Plan 8 (PDP8), detailing the transition to renewable energy, investment opportunities in solar and wind, and critical infrastructure bottlenecks such as grid transmission capacity and pricing frameworks.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s Power Development Plan 8 (PDP8) stands as a seminal policy document, articulating a profound strategic shift towards accelerating the nation’s transition from a fossil fuel-dependent energy landscape to one dominated by renewables... Vietnam’s wind power strategy under PDP8 clearly delineates a near-term focus on onshore and nearshore wind development... The rapid build-out of renewable energy capacity in Vietnam has exposed a critical structural vulnerability within its power infrastructure: inadequate transmission capabilities.
-answer: Quy hoạch điện 8 (PDP8) của Việt Nam đánh dấu bước chuyển mình chiến lược từ năng lượng hóa thạch sang năng lượng tái tạo với mục tiêu đạt phát thải ròng bằng không vào năm 2050, tập trung mạnh vào điện mặt trời và điện gió. Tuy nhiên, quá trình chuyển đổi này đang đối mặt với nhiều thách thức lớn như hạ tầng lưới điện truyền tải chưa đáp ứng kịp tốc độ phát triển nguồn điện, các rào cản về khung giá và các quy định pháp lý cho điện gió ngoài khơi. Bài báo nhấn mạnh các giải pháp như cơ chế mua bán điện trực tiếp (DPPA) và đầu tư hệ thống lưu trữ năng lượng là yếu tố then chốt để giải quyết tình trạng nghẽn mạng lưới và thu hút đầu tư bền vững.
-Source: [sea.ub-speeda.com](https://sea.ub-speeda.com/asean-insights/trend-reports/vietnams-pdp8/)</t>
+          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -11824,35 +9511,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>## [https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)
-### Document Overview
-The article details Vietnam's newly approved Power Development Plan VIII (PDP8), which aims for energy transition, carbon neutrality by 2050, and massive investment in wind and LNG infrastructure.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030
-verbatim: On May 15, 2023, after two years of consultation with public and private stakeholders and 12 draft plans, Prime Minister Pham Minh Chinh approved Vietnam's PDP8 as part of Vietnam's National Electricity Development Plan 2021 30. PDP8 calls for significant expansion of the country's electricity grid, more than doubling its capacity from 69 GW in 2020 to 150 GW by 2030, and set energy transition goals for achieving carbon neutrality by 2050. Much of the expansion is slated to come from investments in offshore wind facilities and LNG-supplied natural gas power plants.
-answer: 베트남 정부는 2030년까지 발전 용량을 150GW로 두 배 이상 확대하고 2050년 탄소 중립 달성을 목표로 하는 제8차 국가전력개발계획(PDP8)을 최종 승인했습니다. 이 계획은 석탄 화력 발전의 단계적 폐지와 함께 해상 풍력 및 LNG 발전 시설 확대를 핵심으로 하며, 이를 위해 2030년까지 약 1,347억 달러 규모의 국내외 투자가 투입될 예정입니다. 아울러 재생에너지 비중을 2050년까지 67.5%로 높이기 위한 법적 개정 및 송전망 인프라 개선이 병행될 계획입니다.
-Source: [www.whitecase.com](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)</t>
+          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (관련: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>## [https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)
-### Document Overview
-This article analyzes Vietnam's newly approved Power Development Plan VIII (PDP8), detailing its investment requirements, shifts in the energy mix toward LNG and renewables, and the roadmap for carbon neutrality by 2050.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030
-verbatim: On May 15, 2023, after two years of consultation with public and private stakeholders and 12 draft plans, Prime Minister Pham Minh Chinh approved Vietnam's PDP8 as part of Vietnam's National Electricity Development Plan 2021 30. PDP8 calls for significant expansion of the country's electricity grid, more than doubling its capacity from 69 GW in 2020 to 150 GW by 2030, and set energy transition goals for achieving carbon neutrality by 2050. Much of the expansion is slated to come from investments in offshore wind facilities and LNG-supplied natural gas power plants.
-answer: Vietnam has officially approved the Power Development Plan VIII (PDP8), which aims to double the nation's electricity capacity to 150 GW by 2030 through a projected investment of US$134.7 billion. The plan prioritizes a transition toward renewable energy and LNG-supplied gas while phasing out new coal-fired plant development after 2030 to achieve carbon neutrality by 2050. This strategic framework is expected to unlock billions in international funding, including a US$15.5 billion pledge from G7 nations to support the country's move away from coal.
-Source: [www.whitecase.com](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)</t>
+          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (Related: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>## [https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)
-### Document Overview
-This article analyzes Vietnam's Power Development Plan VIII (PDP8), detailing its investment requirements, shifts in the energy mix toward LNG and renewables, and the roadmap for achieving carbon neutrality by 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: On May 15, 2023, after two years of consultation with public and private stakeholders and 12 draft plans, Prime Minister Pham Minh Chinh approved Vietnam's PDP8 as part of Vietnam's National Electricity Development Plan 2021 30. PDP8 calls for significant expansion of the country's electricity grid, more than doubling its capacity from 69 GW in 2020 to 150 GW by 2030, and set energy transition goals for achieving carbon neutrality by 2050. Much of the expansion is slated to come from investments in offshore wind facilities and LNG-supplied natural gas power plants.
-answer: Quy hoạch Phát triển Điện lực Quốc gia VIII (PDP8) của Việt Nam đã được phê duyệt với mục tiêu tăng gấp đôi công suất lưới điện lên 150 GW vào năm 2030 và hướng tới trung hòa carbon vào năm 2050. Kế hoạch này tập trung vào việc huy động 134,7 tỷ USD đầu tư để mở rộng năng lượng tái tạo (đặc biệt là điện gió ngoài khơi) và khí hóa lỏng (LNG), đồng thời thực hiện lộ trình ngừng dần các nhà máy nhiệt điện than. Bên cạnh việc nâng cấp hạ tầng truyền tải, Việt Nam cũng dự kiến sửa đổi Luật Điện lực và ban hành Luật Năng lượng tái tạo để hỗ trợ quá trình chuyển đổi năng lượng này.
-Source: [www.whitecase.com](https://www.whitecase.com/insight-alert/vietnam-approves-power-development-plan-cleaner-fuels)</t>
+          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -11906,35 +9575,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>## [https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)
-### Document Overview
-The article discusses Vietnam's Amended National Power Development Plan (PDP8) and the new regulatory framework (Decree 56) aimed at accelerating LNG power projects to meet the country's growing electricity demand and net-zero goals.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030
-verbatim: On April 15, 2025 the Prime Minister issued a new decision (Decision 768) approving the amended National Power Plan (“Amended PDP8”) to address the actual implementation and changes of circumstances. ... Under the Plan Vietnam has five years (until 2030) to develop 15 LNG power plants. ... To address these challenges, the Government has recently issued Decree 56, which provides guidance on LNG project development. ... During the loan repayment period, at least 65% of the electricity output from LNG power plants can be sold to the national grid.
-answer: 베트남 정부는 수정된 제8차 국가전력개발계획(Amended PDP8)을 통해 2030년까지 15개의 LNG 발전소 건설을 추진하며, 총 발전 용량을 150,500MW까지 확대할 계획입니다. 이를 지원하기 위해 연료비 전가 메커니즘(FCPTM)과 최소 65%의 전력 구매 보장 등을 골자로 하는 법령(Decree 56)을 시행하여 프로젝트의 경제성과 은행 대출성(Bankability)을 높이고자 합니다. 이러한 조치는 지연되는 석탄 및 풍력 발전 프로젝트를 보완하고 2050년 넷제로 목표를 달성하기 위한 핵심적인 에너지 믹스 전환 전략의 일환입니다.
-Source: [www.lexology.com](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)</t>
+          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (관련: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>## [https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)
-### Document Overview
-This article details Vietnam's Amended PDP8 (Decision 768) and Decree 56, highlighting strategies to reach 150,500 MW capacity by 2030 through LNG power development and investor incentives.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030
-verbatim: On April 15, 2025 the Prime Minister issued a new decision (Decision 768) approving the amended National Power Plan (“Amended PDP8”) to address the actual implementation and changes of circumstances... Power generated by LNG plants is expected to reach 22,525 MW by 2030... To address these challenges, the Government has recently issued Decree 56, which provides guidance on LNG project development. Key provisions include: Fuel Cost Pass-Through Mechanism (FCPTM) and Guarantee for Offtake Arrangements.
-answer: Vietnam has issued Decision 768 to amend the National Power Development Plan (PDP8), targeting a total power generation capacity of 150,500 MW by 2030 with a significant focus on LNG power. To accelerate infrastructure development and ensure project bankability, the government introduced Decree 56, which establishes a fuel cost pass-through mechanism and guarantees that the national grid will purchase at least 65% of electricity output from LNG plants. These regulatory updates aim to resolve delays in coal and offshore wind projects while streamlining the negotiation process for 15 planned LNG power plants required by 2030.
-Source: [www.lexology.com](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)</t>
+          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (Related: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>## [https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)
-### Document Overview
-Bài viết cung cấp cái nhìn chi tiết về Quy hoạch điện VIII cập nhật của Việt Nam, tập trung vào chiến lược phát triển điện khí LNG và các giải pháp chính sách để tháo gỡ khó khăn cho nhà đầu tư.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: In May 2023, the Prime Minister issued the long-awaited Decision 500, approving the National Power Development Plan, known as PDP8... To support this growth, Vietnam must double its current power generation capacity to reach 150,500 MW by 2030... LNG power generation is relatively new in Vietnam, and the market is still in its early stages. However, LNG will play a critical role in Vietnam’s energy mix over the next decade and is integral to the country’s net-zero commitments.
-answer: Bài báo phân tích lộ trình phát triển hạ tầng năng lượng của Việt Nam thông qua Quy hoạch điện VIII (PDP8) và các quyết định sửa đổi mới nhất vào năm 2025, với mục tiêu nâng tổng công suất nguồn điện lên 150.500 MW vào năm 2030. Trọng tâm của bài báo là sự chuyển dịch sang điện khí LNG với kế hoạch phát triển 15 dự án nhà máy đến năm 2035, đồng thời nêu rõ các cơ chế hỗ trợ mới từ Chính phủ như Nghị định 56 nhằm giải quyết các rào cản về giá, cơ sở hạ tầng cảng biển và bao tiêu sản lượng.
-Source: [www.lexology.com](https://www.lexology.com/library/detail.aspx?g=442af86b-e1a3-4c54-a16c-5649aefaaa5d)</t>
+          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -11988,36 +9639,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>## [https://www.eia.gov/todayinenergy/detail.php?id=48176](https://www.eia.gov/todayinenergy/detail.php?id=48176)
-### Document Overview
-This article discusses Vietnam's draft Power Development Plan 8 (PDP 8) which aims to shift the energy mix from coal and hydro toward solar and wind, while prioritizing critical grid infrastructure upgrades.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: In February 2021, the government of Vietnam released a draft of the country’s latest national power development plan, Power Development Plan 8 (PDP 8), for 2021 to 2030. The draft PDP 8 expands wind and solar capacity and increases their shares of the country’s generation mix. The draft PDP 8 also prioritizes enhancing grid infrastructure to ensure stable operation with a higher share of renewables.
-answer: 베트남 정부는 2021년부터 2030년까지를 아우르는 제8차 국가 전력개발계획(PDP 8) 초안을 통해 풍력 및 태양광 발전 용량을 대폭 확대하고 재생에너지 비중을 높일 계획입니다. 특히 낙후된 전력망 인프라 확충과 송전 병목 현상 해결을 최우선 과제로 삼아, 중남부 지역을 잇는 500kV 송전선 연장 등 전력망 현대화에 집중하고 있습니다. 이를 통해 석탄 화력 발전 의존도를 낮추고 급증하는 전력 수요와 탄소 배출 감소 목표를 동시에 달성하고자 합니다.
-Source: [www.eia.gov](https://www.eia.gov/todayinenergy/detail.php?id=48176)</t>
+          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>## [https://www.eia.gov/todayinenergy/detail.php?id=48176](https://www.eia.gov/todayinenergy/detail.php?id=48176)
-### Document Overview
-The article discusses Vietnam's draft Power Development Plan 8 (PDP 8) which focuses on doubling renewable energy capacity and upgrading the national grid to reduce coal dependency by 2030.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: In February 2021, the government of Vietnam released a draft of the country’s latest national power development plan, Power Development Plan 8 (PDP 8), for 2021 to 2030. The draft PDP 8 expands wind and solar capacity and increases their shares of the country’s generation mix. The draft PDP 8 also prioritizes enhancing grid infrastructure to ensure stable operation with a higher share of renewables.
-answer: Vietnam's draft Power Development Plan 8 (PDP 8) aims to transition the energy sector by significantly increasing solar and wind capacity to 18.6 GW and 18.0 GW respectively by 2030. To support this shift away from coal and hydro, the government is prioritizing a massive grid expansion, including a 461-mile high-voltage transmission line extension to resolve current overloading and facilitate the integration of renewable energy sources.
-Source: [www.eia.gov](https://www.eia.gov/todayinenergy/detail.php?id=48176)</t>
+          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>## [https://www.eia.gov/todayinenergy/detail.php?id=48176](https://www.eia.gov/todayinenergy/detail.php?id=48176)
-### Document Overview
-The article discusses Vietnam's draft Power Development Plan 8 (PDP 8), which emphasizes shifting from coal to renewable energy and expanding the national grid to handle increased capacity.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: In February 2021, the government of Vietnam released a draft of the country’s latest national power development plan, Power Development Plan 8 (PDP 8), for 2021 to 2030. The draft PDP 8 expands wind and solar capacity and increases their shares of the country’s generation mix. The draft PDP 8 also prioritizes enhancing grid infrastructure to ensure stable operation with a higher share of renewables.
-answer: 1. Dự thảo Quy hoạch phát triển điện lực quốc gia 8 (PDP 8) của Việt Nam đặt mục tiêu đẩy mạnh công suất điện gió và điện mặt trời nhằm giảm sự phụ thuộc vào than đá và giảm phát thải khí carbon. 
-2. Để hỗ trợ sự gia tăng của các nguồn năng lượng tái tạo, chính phủ ưu tiên phát triển cơ sở hạ tầng lưới điện, bao gồm việc xây dựng thêm các đường dây truyền tải cao thế và mở rộng mạng lưới để khắc phục tình trạng quá tải và nghẽn mạch hiện tại.
-Source: [www.eia.gov](https://www.eia.gov/todayinenergy/detail.php?id=48176)</t>
+          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -12071,35 +9703,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)
-### Document Overview
-This article discusses the legal threats from foreign chambers of commerce against the Vietnamese government regarding retroactive tariff cuts for 12GW of renewable energy projects.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, according to a document signed by five chambers of commerce seen by Reuters. ... The retroactive change to tariffs, which took effect in January 2025, followed investigations into alleged abuses in accessing ⁠the preferential rates. ... The letter urges authorities to find an amicable solution to a dispute that the chambers said could lead to defaults and significant losses on multibillion-dollar investments in Vietnam's renewable energy sector.
-answer: 베트남 정부가 재생에너지(풍력·태양광) 프로젝트에 대해 약속했던 고정가격매입(FiT) 관찰을 소급 삭감하자, 유럽연합(EU)·일본·한국 등 5개국 상공회의소가 공동 서한을 통해 국제 분쟁 해결 절차를 포함한 법적 대응을 예고했습니다. 이번 갈등은 베트남 전력공사(EVN)의 누적 적자와 발전 용량 12GW 규모의 민간 투자 프로젝트들에 대한 단가 인하 시도에서 비롯되었으며, 이는 베트남 전력 개발 마스터플랜(PDP8) 추진 과정에서 신재생 에너지 분야의 대규모 외자 유치 및 신뢰도에 상당한 위험 요소로 작용하고 있습니다.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)</t>
+          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)
-### Document Overview
-Five international chambers of commerce have warned Vietnam of potential legal action and dispute resolution over the retroactive cutting of renewable energy tariffs affecting 12GW of capacity.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, according to a document signed by five chambers of commerce seen by Reuters. The dispute begin last year when Vietnam cut previously agreed subsidised prices for electricity from some solar and wind farms, citing irregularities. The move comes as Vietnam's energy sector struggles with higher prices and risks of shortages linked to the conflict in Iran.
-answer: Foreign investors and five international chambers of commerce (EU, UK, Japan, South Korea, and Thailand) are threatening legal action against Vietnam over the government's retroactive reduction of electricity tariffs for 12 gigawatts of wind and solar projects. The dispute arises from Vietnam's decision in January 2025 to cut previously agreed feed-in tariffs due to alleged irregularities, a move that investors warn could lead to multibillion-dollar defaults and undermine the country's renewable energy goals.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)</t>
+          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>## [https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)
-### Document Overview
-The article reports on a legal threat from international business chambers against the Vietnamese government due to retroactive cuts in renewable energy subsidies and payment disputes.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, according to a document signed by five chambers of commerce seen by Reuters. The dispute began last year when Vietnam cut previously agreed subsidised prices for electricity from some solar and wind farms, citing irregularities. If payment obligations are not met, electricity producers 'may seek to enforce remedies, including pursuing dispute resolution in Vietnam or other jurisdictions,' said the document, dated March 12.
-answer: Các nhà đầu tư nước ngoài đang đe dọa thực hiện các biện pháp pháp lý sau khi Việt Nam hồi tố cắt giảm giá biểu thuế điện hỗ trợ (feed-in tariffs) đối với các dự án điện gió và điện mặt trời có tổng công suất 12 GW. Năm hiệp hội thương mại từ EU, Anh, Nhật Bản, Hàn Quốc và Thái Lan đã gửi thư chung cảnh báo rằng việc không tuân thủ các cam kết thanh toán có thể dẫn đến vỡ nợ và gây tổn thất lớn cho các khoản đầu tư hàng tỷ đô la vào lĩnh vực năng lượng tái tạo.
-Source: [www.reuters.com](https://www.reuters.com/sustainability/boards-policy-regulation/foreign-investors-threaten-legal-action-against-vietnam-over-renewables-document-2026-03-12/)</t>
+          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -12153,32 +9767,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=bdfXnoZeULc](https://www.youtube.com/watch?v=bdfXnoZeULc)
-### Document Overview
-This video reports on Vietnam's commitment to net-zero emissions by 2050, focusing on renewable energy alternatives and infrastructure developments under PDP8.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's commitment to net-zero emissions by 2050 at COP26 earlier in 2026, prioritising renewable energy. ... An alternative to urban solar energy.
-answer: 베트남 정부는 제8차 국가전력개발계획(PDP8)에 따라 2050년 탄소중립 실현을 위해 재생에너지 보급을 최우선 과제로 추진하고 있습니다. 특히 도시 환경에 적합한 새로운 태양광 에너지 대안을 모색하며 에너지 전환 가속화를 위한 인프라 구축에 집중하고 있습니다.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=bdfXnoZeULc)</t>
+          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=bdfXnoZeULc](https://www.youtube.com/watch?v=bdfXnoZeULc)
-### Document Overview
-The provided page content is a skeletal YouTube interface containing only footer navigation links and metadata, with no specific details about Vietnam's energy infrastructure.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=bdfXnoZeULc)</t>
+          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>## [https://www.youtube.com/watch?v=bdfXnoZeULc](https://www.youtube.com/watch?v=bdfXnoZeULc)
-### Document Overview
-Nội dung đề cập đến cam kết của Việt Nam về phát thải ròng bằng 0 vào năm 2050 và việc ưu tiên phát triển năng lượng tái tạo thay thế cho khu vực đô thị.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's commitment to net-zero emissions by 2050 at COP26 earlier in 2026, prioritising renewable energy. Bu...
-answer: Thủ tướng Phạm Minh Chính đã tái khẳng định cam kết của Việt Nam trong việc đạt mức phát thải ròng bằng '0' vào năm 2050 tại hội nghị COP26. Để thực hiện mục tiêu này, Chính phủ ưu tiên phát triển hạ tầng năng lượng tái tạo và tìm kiếm các giải pháp thay thế hiệu quả cho năng lượng mặt trời tại các khu vực đô thị.
-Source: [www.youtube.com](https://www.youtube.com/watch?v=bdfXnoZeULc)</t>
+          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -12232,35 +9831,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>## [https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)
-### Document Overview
-The article analyzes the rapid growth of Vietnam's wind energy sector, which grew from 200 MW in 2019 to 1,700 MW in 2022, targeting 6,000 MW by 2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: Vietnam's total installed wind energy capacity reached approximately 1,700 megawatts (MW). This figure reflects a significant increase from just 200 MW in 2019... The government has set an ambitious target to achieve 6,000 MW of wind power capacity by 2030 as part of its broader strategy to enhance renewable energy sources. One of the key initiatives is the Feed-in Tariff (FiT) program, which was introduced to encourage investment in renewable energy projects.
-answer: 베트남은 전력개발계획(PDP8) 등 국가 에너지 전략에 따라 2030년까지 풍력 발전 용량을 6,000MW로 확대하기 위해 발전차액지원제도(FiT)와 같은 강력한 지원 정책을 시행하며 시장을 빠르게 확장하고 있습니다. 2022년 기준 풍력 설치 용량은 약 1,700MW로 2019년 대비 비약적으로 성장했으며, 빈투언 및 닌투언 지역의 대규모 프로젝트와 ADB 등 국제 금융 기구의 투자가 성장을 견인하고 있습니다. 다만, 변동성이 큰 풍력 에너지를 수용하기 위한 전력망 인프라 개선과 복잡한 규제 체계 정비는 향후 에너지 전환의 핵심 과제로 남아 있습니다.
-Source: [www.renewableenergyasia.org](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)</t>
+          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>## [https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)
-### Document Overview
-The page provides a comprehensive overview of Vietnam's recent wind energy expansion, major infrastructure projects, government support mechanisms, investment partnerships, and sector challenges, directly relating to power and energy infrastructure development in line with VN-PWR-PDP8.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: Vietnam has emerged as a significant player in the wind energy sector, showcasing remarkable growth in recent years. The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce reliance on fossil fuels. As of 2022, Vietnam's total installed wind energy capacity reached approximately 1,700 megawatts (MW), a notable increase from just 200 MW in 2019, with a government target of 6,000 MW by 2030 as part of its broader renewable energy development plans.
-answer: Vietnam's wind energy sector has experienced rapid expansion, with installed capacity rising from 200 MW in 2019 to 1,700 MW by 2022, supported by strong government targets aiming for 6,000 MW by 2030. Major investments, government incentives like the Feed-in Tariff (FiT), and international partnerships are driving growth as Vietnam advances its power and energy infrastructure under its national development plans.
-Source: [www.renewableenergyasia.org](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)</t>
+          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>## [https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)
-### Document Overview
-This article highlights Vietnam's rapid expansion in wind energy, reaching 1,700 MW by 2022, and discusses government policies like Feed-in Tariffs and future capacity targets for 2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: As of 2022, Vietnam's total installed wind energy capacity reached approximately 1,700 megawatts (MW). This figure reflects a significant increase from just 200 MW in 2019, demonstrating the rapid pace of development in the sector. The government has set an ambitious target to achieve 6,000 MW of wind power capacity by 2030 as part of its broader strategy to enhance renewable energy sources.
-answer: Bài báo phân tích sự phát triển mạnh mẽ của ngành năng lượng gió tại Việt Nam với công suất lắp đặt tăng vọt từ 200 MW năm 2019 lên 1.700 MW vào năm 2022. Chính phủ Việt Nam đã triển khai các chính sách ưu đãi như giá mua điện (FiT) và thu hút đầu tư quốc tế nhằm hướng tới mục tiêu đạt 6.000 MW vào năm 2030. Tuy nhiên, ngành này vẫn đang đối mặt với những thách thức về hạ tầng lưới điện và khung pháp lý cần được hoàn thiện để đảm bảo tăng trưởng bền vững.
-Source: [www.renewableenergyasia.org](https://www.renewableenergyasia.org/2026/03/gusty-growth-vietnams-remarkable-wind.html)</t>
+          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -12314,35 +9895,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>## [https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)
-### Document Overview
-This article analyzes Vietnam's shift from rapid, subsidy-led renewable energy growth to a disciplined, market-based approach under PDP8 and DPPA frameworks.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam is not reversing course on renewable energy. It is correcting structural weaknesses created during an earlier phase of rapid, subsidy-driven growth... With the current PDP8(revised) and the DPPA in place, EVN has a chance to recoup its losses from the FiTs and invest in upgrading their grid and substations. Vietnam’s decision to move decisively away from FiTs toward market-based mechanisms signals policy consistency. It demonstrates a willingness to learn from past excesses and to prioritize long-term system stability over short-term volume.
-answer: 베트남은 과거 급격한 보조금(FiT) 중심의 성장에서 벗어나 제8차 국가전력개발계획(PDP8) 및 직접전력구매계약(DPPA)을 통해 시장 기반의 체계적인 에너지 전환을 추진하고 있습니다. 현재 진행 중인 재생에너지 프로젝트 검토는 정책 후퇴가 아닌 규정 준수를 위한 시장 기강 확립 과정이며, 이를 통해 전력망 안정성과 장기적인 투자 신뢰성을 확보하려 합니다. 결론적으로 베트남은 단순한 개발 속도보다 전력망 수용 능력과 시장 원리를 우선시하는 지속 가능한 재생에너지 생태계 구축에 집중하고 있습니다.
-Source: [indochina-ep.com](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)</t>
+          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>## [https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)
-### Document Overview
-The article analyzes Vietnam's shift from rapid, subsidy-based renewable energy growth to a disciplined, market-driven phase under PDP8 and DPPA, emphasizing structural stability over speed.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam is not reversing course on renewable energy. It is correcting structural weaknesses created during an earlier phase of rapid, subsidy-driven growth... With the current PDP8(revised) and the DPPA in place, EVN has a chance to recoup its losses from the FiTs and invest in upgrading their grid and substations. This is not a retreat from clean energy. It is a transition from subsidies to structure.
-answer: Vietnam is pivoting its Power &amp; Energy sector away from rapid, subsidy-driven Feed-in Tariffs (FiTs) toward a more disciplined, market-based framework under the Power Development Plan 8 (PDP8) and Direct Power Purchase Agreements (DPPA). This strategic shift aims to rectify previous grid congestion and financial strain on Vietnam Electricity (EVN) by prioritizing legal clarity, transmission infrastructure upgrades, and predictable risk allocation over sheer development speed. The transition signals a move toward a mature, sustainable renewable energy market that rewards operational discipline rather than speculation.
-Source: [indochina-ep.com](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)</t>
+          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>## [https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)
-### Document Overview
-Bài viết phân tích sự chuyển đổi chiến lược năng lượng của Việt Nam từ cơ chế giá FiT sang DPPA, nhấn mạnh tầm quan trọng của kỷ luật quản lý và tính bền vững của hệ thống lưới điện hơn là tốc độ phát triển ồ ạt.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam is not reversing course on renewable energy. It is correcting structural weaknesses created during an earlier phase of rapid, subsidy-driven growth... The current phase is about doing so sustainably—financially, legally, and operationally. This is not a retreat from clean energy. It is a transition from subsidies to structure.
-answer: Bài báo nhận định Việt Nam không hề thoái lui khỏi năng lượng tái tạo mà đang chuyển dịch từ giai đoạn phát triển nóng dựa trên trợ giá (FiT) sang một thị trường có kỷ luật và cấu trúc bền vững thông qua cơ chế mua bán điện trực tiếp (DPPA). Việc thực thi các quy định nghiêm ngặt và kiểm soát tốc độ tăng trưởng giúp khắc phục các yếu kém về hạ tầng lưới điện, đảm bảo tính ổn định lâu dài và thu hút các nhà đầu tư có năng lực thực sự thay vì đầu cơ.
-Source: [indochina-ep.com](https://indochina-ep.com/bloomberg-businessweek-vietnam-02-2026-featured-issue-developing-renewable-energy-in-vietnam-discipline-is-more-important-than-speed-of-development/)</t>
+          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -12396,35 +9959,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>## [https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)
-### Document Overview
-The article discusses Vietnam's transition from high-subsidy feed-in tariffs to more mature, cost-efficient energy policies like competitive auctions and DPPAs under the revised PDP8 framework to ensure financial sustainability.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: Vietnam’s clean energy transformation was one of the fastest in Southeast Asia... The rapid, subsidy-driven expansion has exposed gaps in planning and financial sustainability – laying the groundwork that is now reshaping the sector’s trajectory. According to the revised Power Development Plan 8 (PDP8), the country aims to reach 73 gigawatts (GW) of installed solar power capacity and 38GW of onshore wind power by 2030... The targets for 2030 were significantly raised from the original 2023 plan – solar capacity was increased to between 46GW and 73GW, onshore wind to 26GW-38GW, and energy storage to 10GW-16GW.
-answer: 베트남은 급격한 재생에너지 확대에 따른 전력공사(EVN)의 재정적 부담을 해결하기 위해 고정가격매입제도(FiT)에서 경쟁 입찰 방식으로의 정책 전환을 추진하고 있습니다. 수정된 제8차 국가전력개발계획(PDP8)에 따라 2030년까지 태양광 73GW, 육상 풍력 38GW, 에너지 저장 장치 16GW로 목표를 상향 조정하였으며, 민간 직접전력구매계약(DPPA) 도입과 그리드 인프라 확충을 통해 에너지 전환의 지속 가능성을 확보할 계획입니다.
-Source: [ieefa.org](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)</t>
+          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>## [https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)
-### Document Overview
-The article analyzes Vietnam's shift from a subsidy-driven renewable energy boom to a more sustainable, auction-based model under the revised PDP8 to address utility losses and grid stability.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: According to the revised Power Development Plan 8 (PDP8), the country aims to reach 73 gigawatts (GW) of installed solar power capacity and 38GW of onshore wind power by 2030. ... The targets for 2030 were significantly raised from the original 2023 plan – solar capacity was increased to between 46GW and 73GW, onshore wind to 26GW-38GW, and energy storage to 10GW-16GW. ... This need is recognized in PDP8, which calls for more than USD18 billion in transmission investment and installing 10,000MW to 16,300MW of battery storage by 2030.
-answer: Vietnam is recalibrating its power sector strategy by transitioning from high-cost fixed feed-in tariffs to competitive green auctions and Direct Power Purchase Agreements (DPPAs) to manage the financial strain on state utility EVN. Under the revised Power Development Plan 8 (PDP8), the country has significantly raised its 2030 targets to reach up to 73GW of solar and 38GW of wind capacity, supported by an 18 billion USD investment in grid infrastructure and up to 16.3GW of battery storage. These measures aim to sustain investor confidence while reducing reliance on volatile fossil fuels like LNG to ensure long-term energy security and economic resilience.
-Source: [ieefa.org](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)</t>
+          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>## [https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)
-### Document Overview
-Phân tích sự chuyển dịch năng lượng của Việt Nam từ cơ chế giá FiT sang đấu thầu cạnh tranh và DPPA nhằm đảm bảo bền vững tài chính và hạ tầng.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s clean energy transformation was one of the fastest in Southeast Asia. Between 2018 and 2023, the country scaled up its solar and wind capacity from virtually zero to over 21,000 megawatts (MW), fueled by generous feed-in tariffs (FiTs). ... Vietnam is now well-positioned to transition to the next phase of its clean energy journey – adopting cost-effective models such as competitive green auctions for renewables, advancing direct power purchase agreements (DPPAs), and accelerating grid infrastructure and energy storage investments.
-answer: Bài báo phân tích quá trình chuyển đổi năng lượng sạch của Việt Nam, từ giai đoạn bùng nổ công suất điện mặt trời và gió nhờ cơ chế giá hỗ trợ (FiT) sang giai đoạn điều chỉnh để giải quyết các áp lực tài chính cho tập đoàn EVN. Để duy trì đà tăng trưởng bền vững theo quy hoạch PDP8, Việt Nam cần chuyển đổi sang các mô hình hiệu quả hơn như đấu thầu cạnh tranh, triển khai cơ chế mua bán điện trực tiếp (DPPA) và đẩy mạnh đầu tư vào hạ tầng lưới điện cùng hệ thống lưu trữ năng lượng.
-Source: [ieefa.org](https://ieefa.org/resources/boom-balance-vietnams-clean-energy-transition)</t>
+          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -12478,35 +10023,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>## [https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)
-### Document Overview
-This article reports on the inauguration of Vietnam's first $1.4 billion LNG power plants (Nhon Trach 3 &amp; 4) by Petrovietnam, highlighting their role in energy security and the country's net-zero goals.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-GAS-PDP8
-verbatim: Vietnam has opened its first liquefied natural gas power plants, the twin Nhon Trach 3 and Nhon Trach 4 facilities in Dong Nai Province, at a cost of USD1.4 billion. Built by state energy giant Petrovietnam, the plants will generate more than nine billion kilowatt-hours annually with a combined capacity of 1 624 megawatts to support grid stability as renewable energy increases in the southern region. These plants are a crucial piece in strengthening national energy security and meeting the countrys fast and sustainable development requirements... and provide a template for 13 additional LNG projects outlined in the national power development plan.
-answer: 베트남 정부는 동나이성에서 총 1624MW 규모의 첫 액화천연가스(LNG) 발전소인 년짝(Nhon Trach) 3, 4호기를 공식 가동하며 국가 에너지 안보 강화 및 탄소 배출 감축에 나섰습니다. 이 프로젝트는 제8차 국가전력개발계획(PDP8)에 따라 추진되는 13개 추가 LNG 프로젝트의 모델이 될 것이며, 연간 90억 kWh 이상의 전력을 공급하여 남부 지역의 전력망 안정화와 고첨단 산업 수요를 뒷받침할 예정입니다.
-Source: [www.pvn.vn](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)</t>
+          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (관련: VN-PWR-PDP8, VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>## [https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)
-### Document Overview
-This article reports on the inauguration of Vietnam's first LNG power plants (Nhon Trach 3 &amp; 4) by Petrovietnam, highlighting their role in energy security and the transition toward cleaner energy under national development plans.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-GAS-PDP8
-verbatim: Vietnam has opened its first liquefied natural gas power plants, the twin Nhon Trach 3 and Nhon Trach 4 facilities in Dong Nai Province, at a cost of USD1.4 billion. Built by state energy giant Petrovietnam, the plants will generate more than nine billion kilowatt-hours annually with a combined capacity of 1 624 megawatts to support grid stability as renewable energy increases in the southern region. The facilities will primarily serve southern Vietnam... and provide a template for 13 additional LNG projects outlined in the national power development plan.
-answer: Vietnam has officially inaugurated its first liquefied natural gas (LNG) power project, the $1.4 billion Nhon Trach 3 and Nhon Trach 4 twin plants in Dong Nai Province, boasting a combined capacity of 1,624 MW. Developed by Petrovietnam using advanced GE 9HA.02 turbines, these facilities are designed to generate over nine billion kWh annually to support grid stability and high-tech manufacturing growth. This milestone aligns with national energy security goals and serves as a blueprint for 13 additional LNG projects planned under Vietnam's Power Development Plan 8 (PDP8) to reach net-zero by 2050.
-Source: [www.pvn.vn](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)</t>
+          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (Related: VN-PWR-PDP8, VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>## [https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)
-### Document Overview
-The article reports on the inauguration of Vietnam's first LNG power plants (Nhon Trach 3 &amp; 4) by Petrovietnam, highlighting their role in national energy security and carbon reduction.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam has opened its first liquefied natural gas power plants, the twin Nhon Trach 3 and Nhon Trach 4 facilities in Dong Nai Province, at a cost of USD1.4 billion. Built by state energy giant Petrovietnam, the plants will generate more than nine billion kilowatt-hours annually with a combined capacity of 1 624 megawatts to support grid stability as renewable energy increases in the southern region.
-answer: Thủ tướng Chính phủ đã khánh thành hai nhà máy điện khí LNG đầu tiên của Việt Nam là Nhơn Trạch 3 và Nhơn Trạch 4 tại tỉnh Đồng Nai với tổng vốn đầu tư 1,4 tỷ USD. Dự án do Tập đoàn Dầu khí Việt Nam (Petrovietnam) xây dựng, có tổng công suất 1.624 MW, dự kiến cung cấp hơn 9 tỷ kWh mỗi năm nhằm đảm bảo an ninh năng lượng và hỗ trợ mục tiêu phát thải ròng bằng 0 vào năm 2050.
-Source: [www.pvn.vn](https://www.pvn.vn/sites/en/Pages/detail.aspx?NewsID=86c74ab3-40a9-4673-ad86-6dad1df16a3e)</t>
+          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -12560,35 +10087,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>## [https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)
-### Document Overview
-This page details a technology request from a Vietnamese energy firm seeking smart-grid and advanced power system solutions to enhance grid reliability and renewable energy integration.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: A Vietnam-based renewable energy and engineering company... is seeking international partners that can provide smart-grid and advanced technological solutions for transmission, distribution, and renewable energy systems. The company supports clients in achieving their sustainability goals through technology transfer, renewable energy development, engineering consulting, green energy solutions, reliability improvement, and project management services.
-answer: 2018년에 설립된 베트남의 신재생 에너지 및 엔지니어링 전문 기업이 전력망 효율성과 안정성을 높이기 위해 스마트 그리드 및 송배전 분야의 기술 협력 파트너를 찾고 있습니다. 이 기업은 베트남 제8차 국가 전력개발계획(PDP8)의 방향성에 맞춰 송배전망 자동화, 디지털 모니터링, 자산 관리 최적화 솔루션을 도입하여 현지 신재생 에너지 시스템의 신뢰성을 강화하고자 합니다. 이를 위해 글로벌 기업 및 연구소와 상업적 기술 지원 또는 기술 협력 계약을 희망하고 있습니다.
-Source: [een.ec.europa.eu](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)</t>
+          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>## [https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)
-### Document Overview
-This page details a technology request from a Vietnamese energy company looking for international partners to supply smart-grid, AI, and IoT solutions to modernize Vietnam's power distribution and transmission infrastructure.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: A Vietnam-based renewable energy and engineering company... is seeking international partners that can provide smart-grid and advanced technological solutions for transmission, distribution, and renewable energy systems. The company supports clients in achieving their sustainability goals through technology transfer, renewable energy development, engineering consulting, green energy solutions, reliability improvement, and project management services.
-answer: A Vietnamese renewable energy and engineering firm established in 2018 is seeking international technology partners to provide advanced smart-grid solutions, grid automation, and digital monitoring systems for transmission and distribution networks. This initiative aligns with Vietnam's energy infrastructure goals by focusing on improving operational reliability and integrating sustainable energy solutions into the national power system through commercial and technical cooperation agreements.
-Source: [een.ec.europa.eu](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)</t>
+          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>## [https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)
-### Document Overview
-This page is a technology request from a Vietnamese energy company seeking international partners for smart-grid, transmission, and distribution solutions under commercial or technical agreements.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: A Vietnam-based renewable energy and engineering company provides services in power system design, installation, and project management... The company is seeking international partners that can provide smart-grid and advanced technological solutions for transmission, distribution, and renewable energy systems. The cooperation is expected to focus on improving operational reliability and optimising asset management for energy utilities and industrial clients.
-answer: Một công ty kỹ thuật và năng lượng tái tạo tại Việt Nam đang tìm kiếm các đối tác quốc tế để cung cấp các giải pháp lưới điện thông minh (smart-grid) và công nghệ tiên tiến cho hệ thống truyền tải, phân phối điện. Mục tiêu của sự hợp tác này là nhằm cải thiện độ tin cậy vận hành và tối ưu hóa quản lý tài sản cho các đơn vị điện lực và khách hàng công nghiệp thông qua các thỏa thuận thương mại hoặc hỗ trợ kỹ thuật.
-Source: [een.ec.europa.eu](https://een.ec.europa.eu/partnering-opportunities/vietnam-based-energy-company-seeks-smart-grid-and-power-system-technology)</t>
+          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -12638,35 +10147,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>## [https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)
-### Document Overview
-This article analyzes the 2025 revised Power Development Plan 8 (PDP8) in Vietnam, detailing targets for LNG, renewables, BESS, and nuclear power, while addressing regulatory changes like the new Electricity Law and bankability challenges.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: Vietnam’s power sector is expected to experience strong growth in 2026, driven by surging electricity demand, infrastructure expansion, and a major shift toward renewable energy. ... Decision No. 768/QD-TTg was issued on 15 April 2025 by the Prime Minister of Vietnam, which approved the revised National Power Development Plan VIII (PDP 8) for the period 2021–2030, with a vision to 2050.
-answer: 베트남은 급증하는 전력 수요에 대응하기 위해 2025년 4월 개정된 제8차 국가전력개발계획(PDP8)을 승인하고, 2030년까지 재생에너지, LNG 및 천연가스 발전 비중을 대폭 확대할 계획입니다. 특히 해상풍력, 태양광, 배터리 에너지 저장 장치(BESS)뿐만 아니라 중단되었던 원자력 발전 재개를 추진하며, 민간 직접 전력구매계약(DPPA) 도입과 전력망 현대화를 통해 에너지 안보와 2050년 넷제로 목표 달성을 도모하고 있습니다.
-Source: [www.nortonrosefulbright.com](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)</t>
+          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>## [https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)
-### Document Overview
-This article provides a comprehensive overview of Vietnam's power sector evolution under the revised PDP8, detailing new capacity targets, recent legislative decrees for renewables and gas, and the persisting bankability challenges for foreign investors.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: Vietnam’s revised Power Development Plan 8 (PDP8) sets aggressive targets for the power sector for 2030 and beyond, including 22,524 MW of LNG-based power, expanded wind and solar capacities, and the reintroduction of nuclear power. Recent regulatory updates like Decree 58/2025 and the 2024 Electricity Law aim to facilitate direct power purchase agreements (DPPAs) and market-based pricing, although bankability challenges regarding EVN's payment guarantees and curtailment risks remain central concerns for investors.
-answer: Vietnam has updated its National Power Development Plan VIII (PDP8) via Decision No. 768/QD-TTg, setting ambitious 2030 targets that include over 22 GW of LNG capacity, up to 38 GW of onshore wind, and the reintroduction of nuclear power (4-6 GW). To support this transition, the government has implemented new regulations such as Decree 58/2025 and Decree 57/2025 to enable direct power purchase agreements (DPPAs) and market-oriented pricing, while addressing ongoing infrastructure hurdles like grid synchronization and BESS integration.
-Source: [www.nortonrosefulbright.com](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)</t>
+          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>## [https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)
-### Document Overview
-Báo cáo phân tích chi tiết về Quy hoạch điện VIII điều chỉnh của Việt Nam, các chính sách khuyến khích năng lượng sạch và những rào cản pháp lý/tài chính trong việc thu hút đầu tư nước ngoài vào hạ tầng điện lực.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam’s power sector is expected to experience strong growth in 2026, driven by surging electricity demand, infrastructure expansion, and a major shift toward renewable energy. Vietnam’s revised Power Development Plan 8 (PDP8) sets aggressive targets for the power sector for 2030 and beyond, including 22,524 MW of LNG based power, expanded wind and solar capacity, and the reintroduction of nuclear power.
-answer: Bài viết cung cấp cái nhìn tổng quan về sự phát triển mạnh mẽ của ngành điện Việt Nam năm 2026, với trọng tâm là Quy hoạch điện VIII (PDP8) điều chỉnh nhằm đẩy mạnh năng lượng tái tạo, khí LNG và tái khởi động điện hạt nhân. Đồng thời, báo cáo phân tích các khung pháp lý mới như cơ chế mua bán điện trực tiếp (DPPA), phát triển hệ thống lưu trữ năng lượng (BESS) và những thách thức về tính khả thi tài chính (bankability) mà các nhà đầu tư nước ngoài đang quan tâm.
-Source: [www.nortonrosefulbright.com](https://www.nortonrosefulbright.com/en/knowledge/publications/1d041eb0/vietnam-power-sector-snapshot)</t>
+          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -12716,35 +10207,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>## [https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)
-### Document Overview
-This report outlines the updated Smart Grid Roadmap for Vietnam to 2030 and 2050, focusing on integrating renewable energy, enhancing grid reliability, and supporting PDP8 objectives.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-EV-2030
-verbatim: The objective of this report is to offer insights and recommendations to the development of a new roadmap that can effectively address the current and anticipated challenges facing the Vietnamese power grid for the period up to 2030, with a vision for 2050... This new roadmap is hence required to ensure the reliability and sustainability of the energy system, aligning with the objectives of Power Development Plan VIII and Viet Nam's commitment to achieving net-zero emissions... Key technologies that the Updated Smart Grid roadmap needs to consider are: Utility scale solar and rooftop solar, Onshore and offshore wind, Energy storage technologies, Electric Vehicle (EV) charging infrastructure.
-answer: 베트남은 제8차 국가전력개발계획(PDP8) 및 2050년 넷제로 목표에 발맞추어, 재생에너지 통합과 전력 계통의 안정성을 강화하기 위한 '2030 스마트 그리드 로드맵 및 2050 비전' 업데이트를 추진하고 있습니다. 본 로드맵은 전기차(EV) 충전 인프라 확충, 에너지 저장 장치(BESS) 도입, 지능형 원격 검침 인프라(AMI) 확대를 핵심 과제로 설정하여 현대적이고 효율적인 에너지 전환 시스템 구축을 목표로 합니다.
-Source: [www.energytransitionpartnership.org](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)</t>
+          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>## [https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)
-### Document Overview
-This report details the updated Vietnam Smart Grid Roadmap to 2030 and 2050, focusing on integrating renewable energy, improving grid reliability, and establishing new technical standards in line with PDP8.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-EV-2030
-verbatim: The objective of this report is to offer insights and recommendations to the development of a new roadmap that can effectively address the current and anticipated challenges facing the Vietnamese power grid for the period up to 2030, with a vision for 2050. This new roadmap is hence required to ensure the reliability and sustainability of the energy system, aligning with the objectives of Power Development Plan VIII and Viet Nam's commitment to achieving net-zero emissions... It will outline a strategic plan for the efficient integration of renewable energy sources into the grid, enabling it to operate in a more robust, secure, and sustainable manner.
-answer: Vietnam has introduced an updated Smart Grid Development Roadmap to 2030 with a vision to 2050, specifically designed to align with Power Development Plan VIII (PDP8) and the national goal of net-zero emissions. The plan prioritizes the integration of massive renewable energy sources, the deployment of energy storage systems (BESS), and the establishment of a regulatory framework for electric vehicle (EV) charging infrastructure and virtual power plants. By 2030, the initiative aims to achieve 100% automation of high-voltage substations and 95% electronic metering to ensure a stable, secure, and flexible power system.
-Source: [www.energytransitionpartnership.org](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)</t>
+          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>## [https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)
-### Document Overview
-Báo cáo trình bày chi tiết lộ trình cập nhật phát triển lưới điện thông minh của Việt Nam giai đoạn 2025-2030 và tầm nhìn 2050, bao gồm các yêu cầu về khung pháp lý, tiêu chuẩn kỹ thuật và các giải pháp hạ tầng ICT phục vụ chuyển dịch năng lượng.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The objective of this report is to oﬀer insights and recommendations to the development of a new roadmap that can eﬀectively address the current and anticipated challenges facing the Vietnamese power grid for the period up to 2030, with a vision for 2050... The Updated Smart Grid objective is to continue the development of an Smart Grid with modern technologies that aim to enhance power quality and supply reliability, contribute toward the eﬃcient management of power demand, encourage eﬃciency in the use of energy resources, enhance labour productivity, reduce demand of investment in power grid and source development.
-answer: Báo cáo này đề xuất lộ trình cập nhật phát triển lưới điện thông minh tại Việt Nam đến năm 2030 và tầm nhìn đến năm 2050 nhằm thay thế các quy định cũ để phù hợp với bối cảnh gia tăng năng lượng tái tạo và cam kết phát thải ròng bằng không. Tài liệu tập trung vào các trụ cột công nghệ như hiện đại hóa hệ thống điều khiển SCADA/EMS/DMS, tự động hóa trạm biến áp, hạ tầng đo đếm tiên tiến (AMI) và tăng cường an ninh mạng để đảm bảo vận hành lưới điện an toàn, tin cậy và hiệu quả.
-Source: [www.energytransitionpartnership.org](https://www.energytransitionpartnership.org/wp-content/uploads/2025/07/SC-Development-of-Vietnam-Smart-Grid-Roadmap-for-period-up-to-year-2030-with-a-vision-to-2050.pdf)</t>
+          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -12798,35 +10271,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>## [http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)
-### Document Overview
-베트남의 새로운 에너지 전략인 결의안 제70-NQ/TW호에 대한 분석으로, 투자 장벽 제거, 재생에너지 확대, 원전 재개 및 인력 양성 계획을 다루고 있습니다.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030
-verbatim: On August 20, 2025, Party General Secretary To Lam signed Resolution 70-NQ-TW of the Politburo, a strategic directive aimed at ensuring Vietnam’s national energy security through 2030, with a forward-looking perspective toward 2045... Key legal and policy highlights of Resolution 70 include: Facilitating Capital Inflows... Renewable Energy Prioritization... Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035.
-answer: 베트남 공산당은 2030년 국가 에너지 안보 확보와 2045년 전망을 담은 결의안 제70-NQ/TW호를 발표하여 에너지 분야의 제도적 장벽을 제거하고 민간 및 외국인 투자를 활성화할 계획입니다. 이 결의안은 재생에너지 비중을 2030년까지 25~30%로 확대하고 닌투안 원자력 발전소 건설을 재개하는 등 에너지 믹스의 다변화와 효율성 향상을 목표로 합니다. 특히 전력구매계약(PPA) 집행 강화와 송전 가격 모델 도입을 통해 민간 자본의 유입을 촉진하고 탄소 중립 및 기후 변화 대응을 위한 지속 가능한 에너지 생태계 구축에 집중하고 있습니다.
-Source: [blogs.duanemorris.com](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)</t>
+          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (관련: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>## [http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)
-### Document Overview
-This article discusses Vietnam's Resolution 70-NQ/TW-2025, a new legal framework designed to attract investment and remove bottlenecks in the energy sector, focusing on renewables, nuclear power, and grid modernization.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030
-verbatim: On August 20, 2025, Party General Secretary To Lam signed Resolution 70-NQ-TW of the Politburo, a strategic directive aimed at ensuring Vietnam’s national energy security through 2030, with a forward-looking perspective toward 2045... The Resolution advocates for reforms in finance, credit, and taxation policies, alongside incentives for green projects, energy storage, R&amp;D, and domestic manufacturing... Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035.
-answer: Vietnam has issued Resolution 70-NQ/TW-2025 to overhaul the energy sector by eliminating institutional barriers and facilitating capital inflows for private and international investors in renewables, smart grids, and nuclear power. This strategic directive mandates the expedited development of the Ninh Thuan nuclear plants by 2035 and aims for renewable energy to reach 25-30% of the primary supply by 2030, aligning with the country's long-term goals for energy security and net-zero emissions. The resolution emphasizes market-driven mechanisms, including new transmission pricing models and renewable energy certificate markets, to modernize infrastructure and ensure sustainable, high-quality power supply.
-Source: [blogs.duanemorris.com](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)</t>
+          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (Related: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>## [http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)
-### Document Overview
-This article discusses Vietnam's Resolution 70-NQ/TW of 2025, which aims to transform the energy sector by facilitating capital access, promoting renewable and nuclear energy, and eliminating institutional bottlenecks to ensure national energy security and sustainable growth.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: On August 20, 2025, Party General Secretary To Lam signed Resolution 70-NQ-TW of the Politburo, a strategic directive aimed at ensuring Vietnam’s national energy security through 2030... The focus shifts from merely ensuring sufficient power supply to providing energy that is high-quality, affordable, sustainable, climate-resilient, and integrated with global markets.
-answer: Nghị quyết 70-NQ/TW năm 2025 của Bộ Chính trị tập trung vào việc đảm bảo an ninh năng lượng quốc gia đến năm 2030 bằng cách loại bỏ các rào cản thể chế và thúc đẩy sự tham gia của tư nhân vào các dự án năng lượng tái tạo, điện hạt nhân và lưới điện thông minh. Văn bản này đề ra mục tiêu cụ thể về tỷ trọng năng lượng tái tạo đạt 25-30% vào năm 2030, đồng thời ưu tiên huy động vốn thông qua các cơ chế tài chính xanh và tăng cường thực thi các hợp đồng mua bán điện (PPA) để thu hút nhà đầu tư trong và ngoài nước.
-Source: [blogs.duanemorris.com](http://blogs.duanemorris.com/vietnam/2025/09/09/vietnam-resolution-70-nq-tw-2025-facilitates-capital-access-by-eliminating-institutional-barriers-in-vietnams-energy-sector/)</t>
+          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (Liên quan: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -12876,35 +10331,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>## [https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)
-### Document Overview
-This page details the SGREEE project in Vietnam, a €5 million initiative funded by Germany to modernize the national power grid for better renewable energy integration and energy efficiency through regulatory support, capacity building, and technology cooperation.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Power &amp; Energy, 관련 마스터플랜: VN-PWR-PDP8
-verbatim: The ‘Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)’ project is supporting the Government of Viet Nam in the implementation of its Smart Grid Roadmap, which aims to promote the modernization and automation of the national power transmission and distribution system. Funded by BMZ, the project is working closely with ERAV to support experts of the Vietnamese power sector in developing a “Smart Grid”, i.e. the digitalization and flexibilization of the power supply system, which allows integration of an increasing share of renewable energies and supports greater energy efficiency.
-answer: 독일 BMZ의 지원을 받는 SGREEE 프로젝트는 베트남 전력 규제 당국(ERAV)과 협력하여 국가 전력망의 현대화 및 자동화를 추진하고 있습니다. 이 사업은 스마트 그리드 로드맵에 따라 전력 시스템의 디지털화와 유연성을 강화함으로써, 재생 에너지 비중 확대와 에너지 효율 향상을 목표로 법적 프레임워크 구축, 역량 강화 및 기술 협력을 진행했습니다. 이는 베트남 전력 개발 마스터플랜(PDP8)의 에너지 전환 목표를 뒷받침하는 핵심적인 인프라 고도화 활동으로 평가됩니다.
-Source: [www.esp.org.vn](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)</t>
+          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (관련: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>## [https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)
-### Document Overview
-The page details the SGREEE project, a 5-million-euro initiative to modernize Vietnam's power grid through regulatory advice, capacity building, and technology cooperation.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Power &amp; Energy, Related plans: VN-PWR-PDP8
-verbatim: The ‘Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)’ project is supporting the Government of Viet Nam in the implementation of its Smart Grid Roadmap, which aims to promote the modernization and automation of the national power transmission and distribution system. Funded by BMZ, the project is working closely with ERAV to support experts of the Vietnamese power sector in developing a “Smart Grid”, i.e. the digitalization and flexibilization of the power supply system, which allows integration of an increasing share of renewable energies and supports greater energy efficiency.
-answer: The Smart Grids for Renewable Energy and Energy Efficiency (SGREEE) project, funded by BMZ and partnered with ERAV, supported the modernization of Vietnam's national power grid through digitalization and automation. This initiative facilitates the integration of higher renewable energy shares and enhanced energy efficiency, aligning with the country's strategic energy objectives and smart grid roadmap to ensure a flexible power supply system.
-Source: [www.esp.org.vn](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)</t>
+          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (Related: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>## [https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)
-### Document Overview
-This page details the SGREEE project in Vietnam, focusing on modernizing the national power grid through digitalization and policy support to integrate renewable energy.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The ‘Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)’ project is supporting the Government of Viet Nam in the implementation of its Smart Grid Roadmap, which aims to promote the modernization and automation of the national power transmission and distribution system. Funded by BMZ, the project is working closely with ERAV to support experts of the Vietnamese power sector in developing a “Smart Grid”, i.e. the digitalization and flexibilization of the power supply system, which allows integration of an increasing share of renewable energies and supports greater energy efficiency.
-answer: Dự án Lưới điện thông minh cho Năng lượng tái tạo và Hiệu quả năng lượng (SGREEE) hỗ trợ Chính phủ Việt Nam hiện đại hóa và tự động hóa hệ thống truyền tải và phân phối điện quốc gia thông qua Lộ trình Lưới điện thông minh. Với ngân sách 5 triệu Euro do BMZ tài trợ, dự án tập trung vào việc số hóa và linh hoạt hóa hệ thống cung cấp điện nhằm tích hợp hiệu quả các nguồn năng lượng tái tạo và cải thiện hiệu suất năng lượng.
-Source: [www.esp.org.vn](https://www.esp.org.vn/project/smart-grids-for-renewable-energy-and-energy-efficiency/)</t>
+          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (Liên quan: VN-PWR-PDP8)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -13049,29 +10486,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>## [https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)
-### Document Overview
-This page provides an announcement about RTI International's involvement in a Vietnam industrial risk study focusing on air and water pollution.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894, VN-EV-2030
-verbatim: RTI International is an independent scientific research institute dedicated to improving the human condition. Our vision is to address the world's most critical problems with technical and science-based solutions in pursuit of a better future. Clients rely on us to answer questions that demand an objective and multidisciplinary approach—one that integrates expertise across social, statistical, data, and laboratory sciences, engineering, and other technical disciplines to solve the world’s most challenging problems.
-answer: RTI International은 베트남의 대기 및 수질 오염에 관한 산업 리스크 연구를 수행하며, 환경 및 기후 섹터의 지속 가능한 발전을 도모하고 있습니다. 이 연구는 마스터플랜 VN-ENV-IND-1894 및 VN-EV-2030과 연계되어 베트남 산업 현장의 환경 문제를 과학적으로 분석하고 해결책을 제시하는 데 중점을 둡니다. 이를 통해 다학제적 접근 방식으로 베트남의 환경 인프라를 개선하고 사회적 난제를 해결하는 것을 목표로 합니다.
-Source: [www.rti.org](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)</t>
+          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>## [https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)
-### Document Overview
-This page provides an overview of RTI International's mission and expertise as a scientific research institute but lacks specific content regarding the Vietnam air and water pollution study.
-Source: [www.rti.org](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)</t>
+          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>## [https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)
-### Document Overview
-Trang web này giới thiệu về RTI International, một viện nghiên cứu khoa học độc lập, nhưng thiếu nội dung chi tiết về báo cáo ô nhiễm và hạ tầng tại Việt Nam như tiêu đề gợi ý.
-Source: [www.rti.org](https://www.rti.org/announcements/air-water-pollution-vietnam-industrial-risk-study)</t>
+          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -13121,32 +10546,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>## [https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)
-### Document Overview
-This document outlines the environmental consequences of Vietnam's rapid industrialization, focusing on air pollution in major cities and industrial water contamination as of the 2026 edition.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894
-verbatim: Since the Doi Moi reforms, Vietnam has transformed into a global manufacturing hub... the rapid pace of industrialization—particularly in electronics, textiles, and heavy industry—has placed immense strain on the country's air, water, and soil resources. Air pollution is currently the primary environmental health concern in urban centers... Vietnam possesses dense river networks, but many 'dead rivers' exist near industrial zones.
-answer: 베트남은 도이머이 혁신 이후 글로벌 제조 허브로 성장했으나, 전자 및 섬유 등 급격한 산업화로 인해 대기, 수질, 토양 자원에 심각한 부담을 안고 있습니다. 특히 하노이와 호치민 같은 주요 도시의 대기 오염과 산업 단지 인근의 '죽은 강' 문제는 해결해야 할 주요 환경 과제로 부상하고 있습니다. 이에 따라 환경 및 기후 섹터(VN-ENV-IND-1894 관련)에서는 산업 폐수 처리 및 대기 오염 물질 배출 규제 준수를 통한 지속 가능한 전환이 강조되고 있습니다.
-Source: [www.studocu.vn](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)</t>
+          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (관련: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>## [https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)
-### Document Overview
-The page is a document hosting site (Studocu) showing a placeholder for a report titled 'Environmental Impact of Industrialization 2026 Edition' from International University VNU-HCM, but the content is restricted to logged-in users.
-Source: [www.studocu.vn](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)</t>
+          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (Related: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>## [https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)
-### Document Overview
-This report examines the environmental costs of Vietnam's industrial growth, focusing on air pollution in urban centers and water contamination from industrial zones as of 2026.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Since the Doi Moi reforms, Vietnam has transformed into a global manufacturing hub ("The Factory of the World"). While this has lifted millions out of poverty, the rapid pace of industrialization—particularly in electronics, textiles, and heavy industry—has placed immense strain on the country's air, water, and soil resources. ... Air pollution is currently the primary environmental health concern in urban centers. ... Vietnam possesses dense river networks, but many "dead rivers" exist near industrial zones.
-answer: Báo cáo phân tích rằng quá trình công nghiệp hóa nhanh chóng của Việt Nam kể từ thời kỳ Đổi Mới đã gây áp lực cực lớn lên tài nguyên môi trường, đặc biệt là ô nhiễm không khí tại các đô thị lớn và sự xuất hiện của các 'dòng sông chết' gần khu công nghiệp. Tài liệu nhấn mạnh thách thức trong việc quản lý khí thải từ nhiệt điện, xi măng và xử lý nước thải công nghiệp từ các ngành dệt nhuộm, điện tử để hướng tới quá trình chuyển đổi bền vững năm 2026.
-Source: [www.studocu.vn](https://www.studocu.vn/vn/document/international-university-vnu-hcm/environmental-science/report-environmental-impact-of-industrialization-2026-edition/152029488)</t>
+          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (Liên quan: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -13200,35 +10610,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)
-### Document Overview
-The article highlights various environmental initiatives in Vietnam, including forest conservation, ozone depletion mitigation, and urban emission controls, framing the country's green development strategy for 2025-2030.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894
-verbatim: Vietnam’s forest coverage rate remained stable at 42.03% in 2025, with total forest area estimated at 14,971,553 ha, according to the Ministry of Agriculture and Environment (MAE). ... Vietnam launches 13 mln USD project to phase out ozone-depleting substances ... Hanoi, Ho Chi Minh City to begin motorcycle emissions testing from July 2027 ... Cuc Phuong Rewilding Action Plan 2026–2035, with a vision to 2050.
-answer: 베트남은 2025년 기준 42.03%의 안정적인 산림 피복률을 유지하고 있으며, 2026-2031년 사이 1,300만 달러 규모의 오존층 파괴 물질 단계적 제거 프로젝트를 추진하여 국제적 환경 약속을 이행하고 있습니다. 또한 2027년 하노이와 호치민을 시작으로 오토바이 배기가스 검사를 의무화하고 국립공원의 야생동물 유전자원 뱅크화를 추진하는 등 'VN-ENV-IND-1894'와 연계된 환경 및 기후 변화 대응 인프라 구축에 박차를 가하고 있습니다.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)</t>
+          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (관련: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)
-### Document Overview
-The article outlines Vietnam's environmental strategies for 2025-2030, highlighting forest conservation, urban emissions testing, and international cooperation to phase out ozone-depleting substances.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-ENV-IND-1894
-verbatim: Vietnam’s forest coverage rate remained stable at 42.03% in 2025, with total forest area estimated at 14,971,553 ha... The project aims to help Vietnam meet its international commitments in managing and phasing out controlled substances. It will run from 2026 to 2031 with a total budget of over 13 million USD... Hanoi, Ho Chi Minh City to begin motorcycle emissions testing from July 2027.
-answer: Vietnam is advancing its environmental infrastructure through a multi-faceted approach, including maintaining a national forest coverage rate of 42.03% and launching a 13 million USD project to phase out ozone-depleting substances by 2031. Key urban initiatives involve the implementation of motorcycle emissions testing in Hanoi and Ho Chi Minh City starting in July 2027, eventually expanding nationwide by 2030. These efforts are complemented by a focus on sustainable wetland restoration in the Mekong Delta and the enhancement of hydrometeorological observation systems for better disaster resilience.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)</t>
+          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (Related: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>## [https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)
-### Document Overview
-Trang web tổng hợp các tin tức về bảo tồn thiên nhiên, đa dạng sinh học, và các kế hoạch hạ tầng môi trường tại Việt Nam giai đoạn 2025-2030.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: Vietnam launches 13 mln USD project to phase out ozone-depleting substances... Hanoi, Ho Chi Minh City to begin motorcycle emissions testing from July 2027... National forest coverage holds steady at 42.03% in 2025... Vietnam secures nearly 72 million USD in green finance support... observation systems key to stronger forecasting, sustainable development.
-answer: Trang tin tổng hợp các hoạt động về môi trường và cơ sở hạ tầng bền vững tại Việt Nam, nổi bật là kế hoạch kiểm tra khí thải xe máy tại Hà Nội và TP.HCM từ năm 2027 cùng dự án 13 triệu USD nhằm loại bỏ các chất làm suy giảm tầng ozone. Bên cạnh đó, Việt Nam tập trung nâng cấp hệ thống quan trắc khí tượng và duy trì tỷ lệ che phủ rừng ở mức 42,03% để tăng cường khả năng ứng phó biến đổi khí hậu. Các dự án hợp tác với Ngân hàng Thế giới cũng được đẩy mạnh nhằm cải thiện hệ thống thủy lợi và an ninh nguồn nước tại khu vực Đồng bằng sông Cửu Long.
-Source: [en.vietnamplus.vn](https://en.vietnamplus.vn/vietnams-green-horizon-a-2025-2030-plan-for-environmental-industry-post326039.vnp)</t>
+          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (Liên quan: VN-ENV-IND-1894)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -13278,35 +10670,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>## [https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)
-### Document Overview
-This article analyzes the status of industrial waste management in Vietnam, highlighting that while 79% of industrial zones have wastewater treatment systems, many fail to meet environmental standards (QCVN) and lack adequate solid waste infrastructure.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894, VN-EV-2030
-verbatim: By the end of October 2014, out of 209 IPs that have been put into operation, 165 IPs have built a centralized wastewater treatment system, accounting for 79% of the total number of industrial zones in operation... However, in fact, many industrial zones already have wastewater treatment stations but have not operated regularly, and treated wastewater has not met QCVN... Up to now, most industrial zones and industrial zones have not built stations or points for collecting, transferring and treating industrial and hazardous solid waste.
-answer: 베트남 산업단지의 약 79%가 중앙 집중식 폐수 처리 시스템을 구축했으나, 실제 운영 미비와 기준치 미달 방류로 인한 환경 오염 문제가 지속되고 있습니다. 특히 산업 클러스터(CCN)의 폐수 처리 시설 보급률은 5% 수준으로 매우 낮으며, 산업 고체 폐기물 및 유해 폐기물을 위한 전문 수집·처리 센터가 부족하여 환경적 압박이 가중되는 상황입니다. (섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894, VN-EV-2030)
-Source: [vietwaterjsc.com](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)</t>
+          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>## [https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)
-### Document Overview
-This article provides a comprehensive overview of the status of industrial wastewater, emission control, and solid waste management in Vietnam's industrial zones and clusters.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-ENV-IND-1894, VN-EV-2030
-verbatim: By the end of October 2014, out of 209 IPs that have been put into operation, 165 IPs have built a centralized wastewater treatment system, accounting for 79% of the total number of industrial zones in operation... The investment in construction of environmental protection infrastructure has been slow... out of a total of more than 600 CCNs in operation, only about 5% of CCNs have centralized wastewater treatment systems.
-answer: Vietnam is currently upgrading its industrial environmental infrastructure, with approximately 79% of established industrial zones having completed centralized wastewater treatment systems as of late 2014. Despite progress in major economic hubs, environmental protection remains a challenge for industrial clusters (CCNs) where only 5% have centralized treatment, leading to continued pollution risks in surrounding ecosystems. These efforts align with broader national environmental strategies like VN-ENV-IND-1894 and VN-EV-2030 to mitigate the impact of industrial discharge on public health and biodiversity.
-Source: [vietwaterjsc.com](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)</t>
+          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>## [https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)
-### Document Overview
-The article analyzes the current status of wastewater, air emission, and solid waste management infrastructure in Vietnam's industrial zones and clusters as of late 2014.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: By the end of October 2014, out of 209 IPs that have been put into operation, 165 IPs have built a centralized wastewater treatment system, accounting for 79% of the total number of industrial zones in operation... As of October 2014, out of a total of more than 600 CCNs in operation, only about 5% of CCNs have centralized wastewater treatment systems... Up to now, most industrial zones and industrial zones have not built stations or points for collecting, transferring and treating industrial and hazardous solid waste.
-answer: Bài báo đánh giá thực trạng hạ tầng xử lý chất thải công nghiệp tại Việt Nam, ghi nhận khoảng 79% khu công nghiệp đã có hệ thống xử lý nước thải tập trung nhưng hiệu quả vận hành còn chưa đồng đều. Ngược lại, hạ tầng tại các cụm công nghiệp còn rất yếu kém với chỉ 5% có hệ thống xử lý, đồng thời cả nước vẫn đang thiếu hụt trầm trọng các trung tâm thu gom và xử lý rác thải công nghiệp, rác thải nguy hại tập trung.
-Source: [vietwaterjsc.com](https://vietwaterjsc.com/current-status-of-industrial-waste-management-in-vietnam)</t>
+          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -13356,35 +10730,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)
-### Document Overview
-Vietnam is launching a new industrial environmental index to regulate over 400 industrial parks as part of its 2021-2030 green growth strategy and 2050 net-zero commitment.
-### Question: 이 베트남 인프라 뉴스 기사를 한국어로 2-3문장으로 요약하세요. 섹터: Environment &amp; Climate, 관련 마스터플랜: VN-ENV-IND-1894, VN-EV-2030
-verbatim: The Ministry of Planning last week announced its plan to implement an industrial environmental index to promote sustainable industrial development. Le Thanh Quan, head of the ministry’s department of economic zone management, told local media that the ministry is gathering data and feedback in preparation for the domestic industrial environmental standards. The index is part of Vietnam’s development strategy for green growth for the 2021-2030 period. The country has pledged to reduce solid waste and reach net zero emissions by 2050 at the COP26.
-answer: 베트남 기획투자부는 지속 가능한 산업 발전을 위해 '산업 환경 지수(Industrial Environmental Index)'를 도입할 계획이며, 이는 400개 이상의 산업 단지와 18개 경제 구역에 적용될 예정입니다. 이 지수는 2021-2030 녹색 성장을 위한 국가 전략(VN-EV-2030 등)과 연계되어 폐기물 감소 및 2050년 넷제로 달성을 목표로 하며, 국제 표준을 기반으로 베트남의 환경 역량을 반영해 설계됩니다. 이를 통해 기존의 취약했던 환경 규제 및 집행 능력을 강화하고 친환경 산업 생산 체제로의 전환을 가속화할 방침입니다.
-Source: [vietcetera.com](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)</t>
+          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)
-### Document Overview
-Vietnam is establishing an industrial environmental index to standardize green production and waste management across its 400+ industrial parks to meet 2030 green growth targets.
-### Question: Summarize this Vietnam infrastructure news in 2-3 sentences in English. Sector: Environment &amp; Climate, Related plans: VN-ENV-IND-1894, VN-EV-2030
-verbatim: The Ministry of Planning last week announced its plan to implement an industrial environmental index to promote sustainable industrial development. Le Thanh Quan, head of the ministry’s department of economic zone management, told local media that the ministry is gathering data and feedback in preparation for the domestic industrial environmental standards. The index is part of Vietnam’s development strategy for green growth for the 2021-2030 period. The country has pledged to reduce solid waste and reach net zero emissions by 2050 at the COP26.
-answer: Vietnam's Ministry of Planning is implementing a new industrial environmental index to regulate over 400 industrial parks and 18 economic zones, aiming to mitigate severe pollution where 70% of effluents currently go untreated. Part of the country's 2021-2030 green growth strategy (VN-EV-2030) and net-zero 2050 pledge, the index will establish domestic environmental standards based on international frameworks to promote sustainable manufacturing and waste reduction. This initiative, supported by UNIDO, represents a critical shift toward eco-industrial parks and stronger regulatory enforcement in the manufacturing sector.
-Source: [vietcetera.com](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)</t>
+          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>## [https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)
-### Document Overview
-Bài báo thảo luận về việc Việt Nam thiết lập chỉ số môi trường công nghiệp để quản lý hơn 400 khu công nghiệp, nhằm giải quyết vấn đề ô nhiễm và thực hiện cam kết Net Zero vào năm 2050.
-### Question: Tóm tắt bài báo cơ sở hạ tầng Việt Nam này trong 2-3 câu bằng tiếng Việt.
-verbatim: The Ministry of Planning last week announced its plan to implement an industrial environmental index to promote sustainable industrial development. Quan said the establishment of environmental standards in more than 400 industrial parks and 18 economic zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. The index is part of Vietnam’s development strategy for green growth for the 2021-2030 period.
-answer: Bộ Kế hoạch và Đầu tư Việt Nam đang triển khai xây dựng chỉ số môi trường công nghiệp nhằm thúc đẩy phát triển bền vững tại hơn 400 khu công nghiệp và 18 khu kinh tế trên cả nước. Sáng kiến này, được hỗ trợ bởi UNIDO, tập trung vào việc thiết lập các tiêu chuẩn môi trường khắt khe hơn để giảm thiểu tình trạng xả thải chưa qua xử lý và giúp Việt Nam đạt mục tiêu phát thải ròng bằng không vào năm 2050. Đây là một bước đi chiến lược nhằm chuyển đổi các khu sản xuất truyền thống sang mô hình khu công nghiệp sinh thái thân thiện với môi trường theo chuẩn quốc tế.
-Source: [vietcetera.com](https://vietcetera.com/onboardy/vietnam-to-set-up-industrial-environmental-index)</t>
+          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">

--- a/reports/2026-04-13/Vietnam_Infra_News_Database.xlsx
+++ b/reports/2026-04-13/Vietnam_Infra_News_Database.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부는 2030년까지의 국가 전력 개발 계획(PDP8)을 승인하며 에너지 안보 확보와 탈탄소화를 목표로 설정했습니다. 이 계획은 석탄 화력을 단계적으로 폐지하고 해상 풍력 및 태양광과 같은 재생 에너지 비중을 2050년까지 최대 71.5%까지 확대하는 내용을 담고 있습니다.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam has officially approved the National Power Development Plan VIII (PDP8), targeting a transition towards renewable energy and national energy security through 2030. The plan prioritizes the phasing out of coal-fired power by 2050 while significantly expanding wind, solar, and gas-to-hydrogen capacities to meet a 7% annual GDP growth demand.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã phê duyệt Quy hoạch phát triển điện lực quốc gia thời kỳ 2021 - 2030 (Quy hoạch điện VIII) nhằm đảm bảo an ninh năng lượng và chuyển đổi xanh. Kế hoạch tập trung vào việc loại bỏ dần điện than vào năm 2050, đồng thời thúc đẩy mạnh mẽ năng lượng tái tạo và điện khí để phục vụ mục tiêu tăng trưởng kinh tế.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부는 2030년까지 발전 용량을 150GW로 확대하고 2050년 탄소 중립을 달성하기 위한 제8차 국가전력개발계획(PDP VIII)을 승인했습니다. 이 계획은 석탄 화력 발전에서 재생 에너지, 수소, 암모니아 및 배터리 저장 시스템으로의 대대적인 전환을 목표로 하며, 인프라 구축을 위해 향후 30년간 약 7,000억 달러의 투자가 필요할 것으로 예상됩니다.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam has approved the PDP VIII, an ambitious energy roadmap targeting 150 GW of installed capacity by 2030 and Net Zero emissions by 2050. The plan shifts focus from coal to renewables and emerging technologies like hydrogen and battery storage, requiring approximately $700 billion in investment over the next three decades for generation and grid infrastructure.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã phê duyệt Quy hoạch điện VIII (PDP VIII), đặt mục tiêu nâng công suất lắp đặt lên 150 GW vào năm 2030 và hướng tới phát thải ròng bằng 0 vào năm 2050. Kế hoạch này tập trung chuyển đổi từ điện than sang năng lượng tái tạo, hydro và lưu trữ năng lượng, với nhu cầu vốn đầu tư dự kiến khoảng 700 tỷ USD trong 3 thập kỷ tới cho nguồn điện và lưới điện.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -692,17 +692,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] What are the new changes to Vietnam's PDP8 - A&amp;O Shearman — Vietnam's updated PDP8 outlines new energy priorities and investment opportunities, with key implications for legal, ESG, and infrastructure ...</t>
+          <t>베트남 정부는 2030년까지의 전력 발전 용량을 약 90-100GW로 상향 조정하고 재생 에너지 비중을 확대하는 '수정 PDP8'을 승인했습니다. 이번 계획에는 원자력 발전 재개와 함께 태양광 및 풍력 발전 목표치가 대폭 증가하였으며, 에너지 자립을 위한 루프탑 태양광 보급도 강조되었습니다.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] What are the new changes to Vietnam's PDP8 - A&amp;O Shearman — Vietnam's updated PDP8 outlines new energy priorities and investment opportunities, with key implications for legal, ESG, and infrastructure ...</t>
+          <t>Vietnam has approved the "Amended PDP8," which significantly increases total power capacity targets to nearly 100 GW by 2030 while emphasizing renewable energy and nuclear power. The revised plan introduces mandatory storage batteries for solar projects and outlines a new strategy for exporting renewable energy to neighboring countries like Singapore and Malaysia.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] What are the new changes to Vietnam's PDP8 - A&amp;O Shearman — Vietnam's updated PDP8 outlines new energy priorities and investment opportunities, with key implications for legal, ESG, and infrastructure ...</t>
+          <t>Thủ tướng Chính phủ đã phê duyệt Quy hoạch điện VIII sửa đổi, tăng mục tiêu công suất nguồn điện lên khoảng 90-100 GW vào năm 2030 với sự ưu tiên mạnh mẽ cho năng lượng tái tạo. Bản quy hoạch mới cũng chính thức khởi động lại các dự án điện hạt nhân tại Ninh Thuận và đặt mục tiêu xuất khẩu năng lượng sang các nước láng giềng.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>2023년 5월 15일 베트남 정부는 '제8차 국가전력개발계획(PDP8)'을 발표하여 2021~2030년과 2050년 비전을 제시했습니다. PDP8은 석탄 발전 용량을 약 13GW 감축하고, 2050년까지 모든 석탄발전소는 대체 연료로 전환하거나 퇴출하도록 요구합니다. 2030년에는 재생에너지가 전체 발전용량의 48%, 2050년에는 약 63%를 차지할 계획입니다.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>On May 15, 2023, the Vietnamese government released the 8th National Power Development Plan (PDP8) covering 2021-2030 and a vision to 2050. The plan cancels about 13GW of planned coal capacity, requires all coal plants to be converted to alternative fuels or shut down by 2050, and aims for renewables to provide 48% of installed capacity by 2030 and about 63% by 2050.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Ngày 15/5/2023, Chính phủ Việt Nam đã công bố Quy hoạch Phát triển điện lực quốc gia lần thứ 8 (PDP8) cho giai đoạn 2021-2030, tầm nhìn đến 2050. PDP8 loại bỏ khoảng 13GW điện than, yêu cầu toàn bộ nhà máy điện than phải chuyển đổi sang nhiên liệu thay thế hoặc ngừng hoạt động trước năm 2050 và đặt mục tiêu năng lượng tái tạo chiếm 48% công suất lắp đặt vào năm 2030, và khoảng 63% vào năm 2050.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (관련: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam Revised Power Development Plan VIII</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (Related: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam Revised Power Development Plan VIII</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (Liên quan: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam Revised Power Development Plan VIII</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -880,17 +880,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남의 제8차 국가전력개발계획(PDP8)은 2050년 탄소 중립 달성을 목표로 화석 연료에서 재생 에너지 중심의 전력 체계로의 전환을 가속화하고 있습니다. 정부는 옥상 태양광 및 직접전력구매계약(DPPA) 도입을 통해 투자를 촉진하고 있으나, 송전망 미비와 가격 책정 프레임워크의 불확실성은 여전히 해결해야 할 과제로 남아 있습니다.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam's Power Development Plan 8 (PDP8) drives a strategic shift toward renewable energy to achieve net-zero emissions by 2050. While new policies like Direct Power Purchase Agreements (DPPA) and expanded solar incentives are attracting investment, the transition faces hurdles including grid congestion and unsupportive pricing structures.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Quy hoạch điện VIII (PDP8) của Việt Nam định hướng chuyển đổi chiến lược từ năng lượng hóa thạch sang năng lượng tái tạo nhằm mục tiêu phát thải ròng bằng 0 vào năm 2050. Mặc dù các chính sách như cơ chế mua bán điện trực tiếp (DPPA) và ưu đãi điện mặt trời mái nhà đang mở ra cơ hội đầu tư lớn, ngành năng lượng vẫn đối mặt với thách thức về hạ tầng lưới điện và khung giá điện chưa phù hợp.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (관련: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부는 2030년까지 전력 설비 용량을 150GW로 확충하고 2050년 탄소 중립을 달성하기 위한 제8차 국가 전력개발계획(PDP8)을 승인했습니다. 이 계획은 석탄 화력 발전을 점진적으로 폐지하고 해상 풍력 및 LNG 발전 비중을 대폭 확대하기 위해 약 1,347억 달러의 투자를 필요로 합니다.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (Related: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>Vietnam has approved the Power Development Plan VIII (PDP8), targeting a grid expansion to 150 GW by 2030 and carbon neutrality by 2050. The plan requires $134.7 billion in investment to shift from coal to cleaner energy sources, specifically prioritizing offshore wind and LNG infrastructure.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã phê duyệt Quy hoạch điện VIII (PDP8), đặt mục tiêu nâng công suất lưới điện lên 150 GW vào năm 2030 và đạt phát thải ròng bằng 0 vào năm 2050. Kế hoạch này yêu cầu khoản đầu tư 134,7 tỷ USD để chuyển dịch từ điện than sang các nguồn năng lượng sạch hơn như điện gió ngoài khơi và khí LNG.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1008,17 +1008,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (관련: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부는 PDP8 목표 달성을 위해 LNG 발전소 건설을 가속화하고 있으며, 최근 시행령 제56호(Decree 56)를 통해 연료비 전가 메커니즘과 최소 65%의 전력 구매 보장책을 도입했습니다. 이는 2030년까지 15개의 LNG 발전소를 확보하고 전력 용량을 150,500 MW로 확대하기 위한 조치입니다.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (Related: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>The Vietnamese government has introduced Decree 56 to support the development of 15 LNG power plants under the Amended PDP8, aiming for a total capacity of 150,500 MW by 2030. The new regulations provide a fuel cost pass-through mechanism and a 10-year guarantee for offtaking at least 65% of electricity output to ensure project bankability.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã ban hành Nghị định 56 nhằm hỗ trợ phát triển 15 nhà máy điện LNG theo Quy hoạch điện VIII (PDP8) sửa đổi, hướng tới mục tiêu đạt tổng công suất 150.500 MW vào năm 2030. Quy định mới thiết lập cơ chế chuyển tiếp chi phí nhiên liệu và cam kết sản lượng hợp đồng tối thiểu 65% để tháo gỡ khó khăn cho các nhà đầu tư.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1072,17 +1072,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부의 제8차 국가전력개발계획(PDP 8) 초안은 2030년까지 태양광 및 풍력 발전 용량을 대폭 확대하고 탄소 배출을 줄이는 것을 목표로 합니다. 특히 노후화된 전력망 문제를 해결하기 위해 고전압 송전선 건설과 인프라 현대화를 우선순위로 두어 재생에너지 통합을 지원할 계획입니다.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam's draft Power Development Plan 8 (PDP 8) aims to significantly increase solar and wind capacity to 18.6 GW and 18.0 GW respectively by 2030 to reduce coal dependency. The plan prioritizes grid modernization, including a 461-mile transmission line project, to address current congestion and successfully integrate higher shares of renewable energy.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Dự thảo Quy hoạch phát triển điện lực quốc gia 8 (PDP 8) của Việt Nam tập trung vào việc mở rộng công suất điện mặt trời và điện gió lên lần lượt 18,6 GW và 18,0 GW vào năm 2030. Kế hoạch này ưu tiên nâng cấp hạ tầng lưới điện và xây dựng các đường dây truyền tải cao thế để khắc phục tình trạng quá tải và hỗ trợ tích hợp năng lượng tái tạo.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (관련: VN-PWR-PDP8)</t>
+          <t>베트남 정부가 재생에너지 전력 구매 가격을 소급 삭감하자 한국, EU 등 5개국 상공회의소가 공동 서한을 통해 법적 대응을 예고했습니다. 투자자들은 약속된 보조금이 지급되지 않을 경우 국제 분쟁 해결 절차를 밟을 수 있다고 경고하며 정부의 우호적인 해결책 마련을 촉구했습니다.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (Related: VN-PWR-PDP8)</t>
+          <t>Foreign investors from five major chambers of commerce have threatened legal action against Vietnam due to retroactive cuts in electricity tariffs for wind and solar projects. The dispute involves 12 gigawatts of capacity, with investors warning of potential defaults and multibillion-dollar losses if original payment obligations are not met.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Năm hiệp hội thương mại quốc tế đã cảnh báo sẽ thực hiện các biện pháp pháp lý nếu Chính phủ Việt Nam không thực hiện cam kết về giá mua điện tái tạo. Tranh chấp phát sinh sau khi Việt Nam cắt giảm giá ưu đãi (FIT) đã thỏa thuận trước đó, gây ảnh hưởng đến các dự án có tổng công suất lên tới 12 GW.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] vietnam energy week 2026 — The event brings together industry leaders, technology providers, and decision-makers to explore advancements shaping Vietnam's digital economy. (관련: VN-EV-2030)</t>
+          <t>베트남 에너지 위크 2026(Vietnam Energy Week 2026)이 2026년 11월 4일부터 6일까지 호치민시 SECC에서 개최되어 에너지 및 기술 인프라 투자 가속화를 위한 전략적 플랫폼 역할을 할 예정입니다. 이번 행사는 단순한 전시를 넘어 투자자, 설계 컨설턴트, MEP 계약자 간의 직접적인 교류를 통해 에너지 및 HVACR 산업의 실질적인 비즈니스 기회 창출에 집중합니다.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] vietnam energy week 2026 — The event brings together industry leaders, technology providers, and decision-makers to explore advancements shaping Vietnam's digital economy. (Related: VN-EV-2030)</t>
+          <t>Vietnam Energy Week 2026 will be held from November 4–6, 2026, at the SECC in Ho Chi Minh City, serving as a strategic hub for accelerated investment in energy and technical infrastructure. The exhibition focuses on high-quality B2B engagement between investors, contractors, and technology partners to drive tangible growth in the Energy and HVACR sectors.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] vietnam energy week 2026 — The event brings together industry leaders, technology providers, and decision-makers to explore advancements shaping Vietnam's digital economy. (Liên quan: VN-EV-2030)</t>
+          <t>Tuần lễ Năng lượng Việt Nam 2026 sẽ diễn ra từ ngày 4 đến 6 tháng 11 năm 2026 tại SECC, TP. Hồ Chí Minh, đóng vai trò là điểm hẹn chiến lược trong giai đoạn đẩy mạnh đầu tư vào hạ tầng năng lượng và kỹ thuật. Triển lãm tập trung vào việc kết nối trực tiếp giữa các nhà đầu tư, nhà thầu và đối tác công nghệ để tạo ra những cơ hội kinh doanh thực chất trong ngành Năng lượng và HVACR.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1260,17 +1260,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (관련: VN-PWR-PDP8)</t>
+          <t>팜 민 찐 총리는 COP26에서 2050년까지 넷제로 달성을 재확인하며 재생 에너지 발전을 최우선 과제로 설정했습니다. 특히 PDP8 계획에 따라 도시형 태양광 에너지의 대안을 모색하며 에너지 인프라 확충에 집중하고 있습니다.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (Related: VN-PWR-PDP8)</t>
+          <t>Prime Minister Phạm Minh Chính has reaffirmed Vietnam's commitment to achieving net-zero emissions by 2050, prioritizing the development of renewable energy sources. This initiative aligns with the Power Development Plan 8 (PDP8) to explore alternatives for urban solar energy and enhance the national power infrastructure.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Thủ tướng Phạm Minh Chính khẳng định lại cam kết của Việt Nam về mức phát thải ròng bằng 0 vào năm 2050 tại COP26, ưu tiên phát triển năng lượng tái tạo. Đây là một phần trong kế hoạch Quy hoạch điện VIII (PDP8) nhằm tìm kiếm giải pháp thay thế cho năng lượng mặt trời đô thị và cải thiện hạ tầng năng lượng.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Pushes Rooftop Solar and Energy Saving to Secure Power ... — Vietnam accelerates rooftop solar adoption and energy conservation measures to ensure stable power supply and achieve long term climate ... (관련: VN-EV-2030)</t>
+          <t>베트남 팜 민 찐 총리는 국가 에너지 안보를 강화하기 위해 옥상 태양광 발전 확대와 에너지 절약을 강조하는 주요 지침을 발표했습니다. 이 계획은 500kV 회로-3 송전선로와 같은 인프라 구축을 가속화하고 복잡한 절차를 간소화하여 2050년 넷제로 목표 달성을 지원하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Pushes Rooftop Solar and Energy Saving to Secure Power ... — Vietnam accelerates rooftop solar adoption and energy conservation measures to ensure stable power supply and achieve long term climate ... (Related: VN-EV-2030)</t>
+          <t>Prime Minister Pham Minh Chinh has issued a directive to prioritize energy security through the expansion of rooftop solar power and nationwide electricity conservation. The plan focuses on streamlining regulations for self-consumption solar systems and accelerating key infrastructure projects like the 500kV Circuit-3 transmission line to ensure a stable power supply.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Pushes Rooftop Solar and Energy Saving to Secure Power ... — Vietnam accelerates rooftop solar adoption and energy conservation measures to ensure stable power supply and achieve long term climate ... (Liên quan: VN-EV-2030)</t>
+          <t>Thủ tướng Phạm Minh Chính đã ban hành chỉ thị thúc đẩy an ninh năng lượng thông qua việc mở rộng điện mặt trời áp mái và tăng cường tiết kiệm điện trên toàn quốc. Kế hoạch tập trung vào việc đơn giản hóa thủ tục lắp đặt, đẩy nhanh tiến độ đường dây truyền tải 500kV mạch 3 nhằm đảm bảo cung ứng điện ổn định và hướng tới mục tiêu phát thải ròng bằng 0 vào năm 2050.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1388,17 +1388,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's ... — With 100GW of additional capacity forecast by 2030, and a ten-fold increase in renewable energy generation, Vietnam is serious about the future ...</t>
+          <t>베트남 팜 민 찐 총리는 2050년까지 탄소 중립(Net-Zero)을 달성하겠다는 베트남의 의지를 재확인했습니다. 정부는 국가 에너지 전략의 일환으로 청정에너지 전환과 지속 가능한 인프라 구축을 최우선 과제로 추진하고 있습니다.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's ... — With 100GW of additional capacity forecast by 2030, and a ten-fold increase in renewable energy generation, Vietnam is serious about the future ...</t>
+          <t>Prime Minister Phạm Minh Chính has reaffirmed Vietnam's commitment to achieving net-zero emissions by 2050. The government is prioritizing the transition to clean energy and the development of sustainable infrastructure as part of its national power and energy strategy.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Prime Minister Phạm Minh Chính has reaffirmed Việt Nam's ... — With 100GW of additional capacity forecast by 2030, and a ten-fold increase in renewable energy generation, Vietnam is serious about the future ...</t>
+          <t>Thủ tướng Phạm Minh Chính đã tái khẳng định cam kết của Việt Nam trong việc đạt mức phát thải ròng bằng 0 vào năm 2050. Chính phủ đang ưu tiên chuyển đổi sang năng lượng sạch và phát triển hạ tầng bền vững như một phần trong chiến lược năng lượng quốc gia.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (관련: VN-PWR-PDP8)</t>
+          <t>베트남은 2030년까지 풍력 발전 용량을 6,000MW로 확대한다는 야심찬 목표를 세우고 비엔투안 및 쭝남 풍력 발전소와 같은 대규모 프로젝트를 추진하고 있습니다. 정부는 육상 및 해상 풍력에 대한 발전차액지원제도(FiT)와 국제적 파트너십을 통해 투자를 유치하고 있으나, 전력망 인프라 개선이 주요 과제로 남아 있습니다.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (Related: VN-PWR-PDP8)</t>
+          <t>Vietnam is rapidly expanding its wind energy sector with a target of 6,000 MW by 2030, supported by significant projects like the Binh Thuan and Trung Nam plants. The government utilizes Feed-in Tariffs (FiT) and international partnerships to drive growth, though challenges in grid infrastructure and regulatory frameworks persist.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Việt Nam đang nhanh chóng mở rộng lĩnh vực năng lượng gió với mục tiêu đạt công suất 6.000 MW vào năm 2030, được hỗ trợ bởi các dự án lớn như nhà máy Bình Thuận và Trung Nam. Chính phủ áp dụng cơ chế giá bán điện (FiT) và hợp tác quốc tế để thúc đẩy đầu tư, dù vẫn còn những thách thức về hạ tầng lưới điện và khung pháp lý.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남은 과거 보조금 중심의 급격한 성장에서 벗어나 규제 준수와 시장 중심의 규율을 강조하는 에너지 전환의 새로운 단계에 진입했습니다. 직접전력구매계약(DPPA)과 제8차 국가전력개발계획(PDP8)을 통해 공급과 수요의 균형을 맞추고 전력망 안정을 도모하며 장기적인 투자 신뢰도를 구축하고 있습니다.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam is transitioning from a period of rapid, subsidy-driven renewable energy growth to a more disciplined, market-based approach under the DPPA framework and PDP8. The focus has shifted from mere development speed to long-term system stability, regulatory compliance, and aligning generation with grid capacity to ensure financial and operational sustainability.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Việt Nam đang chuyển dịch từ giai đoạn phát triển năng lượng tái tạo nhanh chóng dựa trên trợ giá (FiT) sang mô hình dựa trên kỷ luật thị trường và cơ chế DPPA. Quá trình này ưu tiên tính ổn định của hệ thống, tuân thủ quy định pháp luật và sự phù hợp với Quy hoạch điện VIII (PDP8) thay vì chỉ tập trung vào tốc độ tăng trưởng.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1580,17 +1580,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남은 제8차 국가전력개발계획(PDP8)에 따라 2030년까지 태양광 73GW 및 육상 풍력 38GW 확보를 목표로 청정에너지 전환을 가속화하고 있습니다. 과거 고정가격매입제도(FiT)의 성공을 발판 삼아, 이제는 직접전력구매계약(DPPA)과 경쟁 입찰 도입을 통해 시장 중심의 지속 가능한 에너지 인프라 구축에 집중하고 있습니다.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam is accelerating its clean energy transition under the revised PDP8, aiming for 73GW of solar and 38GW of onshore wind capacity by 2030. Following a rapid FiT-driven expansion, the sector is now shifting toward sustainable models like Direct Power Purchase Agreements (DPPA) and competitive auctions to ensure financial stability for the state utility.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Việt Nam đang đẩy nhanh quá trình chuyển đổi năng lượng sạch theo Quy hoạch điện VIII (PDP8) sửa đổi, hướng tới mục tiêu 73GW điện mặt trời và 38GW điện gió trên bãi vào năm 2030. Sau giai đoạn bùng nổ nhờ giá FiT, ngành năng lượng đang chuyển sang các mô hình bền vững hơn như cơ chế mua bán điện trực tiếp (DPPA) và đấu thầu cạnh tranh để đảm bảo an ninh tài chính.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1644,17 +1644,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Solar Energy Market Growth and Forecast (2026-2035) — The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual ...</t>
+          <t>베트남 태양광 에너지 시장은 2025년 약 26.22 TWh 규모에서 2035년까지 연평균 3.10% 성장하여 35.58 TWh에 도달할 것으로 전망됩니다. 정부의 우호적인 정책, 하락하는 태양광 패널 비용, 그리고 청정 에너지에 대한 수요 증가가 시장 성장을 주도하고 있으나 그리드 통합 및 정책적 불확실성은 해결해야 할 과제로 남아있습니다.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Solar Energy Market Growth and Forecast (2026-2035) — The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual ...</t>
+          <t>The Vietnam solar energy market is projected to grow from 26.22 TWh in 2025 to 35.58 TWh by 2035, driven by a CAGR of 3.10%. Key growth factors include government incentives like feed-in tariffs, declining equipment costs, and rising demand for sustainable energy alternatives despite challenges in grid stability and land availability.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Solar Energy Market Growth and Forecast (2026-2035) — The Vietnam solar energy market, valued at approximately 26.22 terawatt-hours (TWh) in 2025, is projected to grow at a compound annual ...</t>
+          <t>Thị trường năng lượng mặt trời Việt Nam dự kiến đạt quy mô 35,58 TWh vào năm 2035 với tốc độ tăng trưởng hàng năm kép là 3,10% từ năm 2026. Sự tăng trưởng này được thúc đẩy bởi các chính sách ưu đãi của chính phủ, chi phí lắp đặt giảm và nhu cầu chuyển đổi sang năng lượng sạch, mặc dù vẫn còn những thách thức về hạ tầng lưới điện.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1704,17 +1704,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - Slideshare — VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - WHAT YOU MUST KNOW - Download as a PDF or view online for free.</t>
+          <t>베트남은 제8차 국가전력개발계획(PDP8)에 따라 2030년까지 해상풍력 6GW 달성을 목표로 에너지 전환을 가속화하고 있으나, 최근 독일 PNE AG의 탈락 사례에서 보듯 자국 기업 우선 정책이 강화되고 있습니다. 외국인 투자자는 엄격한 자본금 요건과 현지 파트너십 의무화 등 변화하는 규제 환경과 금융 담보 요구에 대비해야 합니다.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - Slideshare — VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - WHAT YOU MUST KNOW - Download as a PDF or view online for free.</t>
+          <t>Vietnam is accelerating its energy transition under Power Development Plan VIII (PDP8), targeting 6GW of offshore wind by 2030, though recent shifts favor domestic "National Champions" over foreign developers. Investors face stricter financial deposit requirements and a de facto necessity for local partnerships to navigate regulatory uncertainty and grid connection bottlenecks.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - Slideshare — VIETNAM - WIND ENERGY INVESTMENT GUIDE 2026 - WHAT YOU MUST KNOW - Download as a PDF or view online for free.</t>
+          <t>Việt Nam đang đẩy mạnh chuyển dịch năng lượng theo Quy hoạch điện VIII với mục tiêu đạt 6GW điện gió ngoài khơi vào năm 2030, nhưng xu hướng hiện tại cho thấy sự ưu tiên rõ rệt đối với các tập đoàn nội địa. Các nhà đầu tư nước ngoài cần chuẩn bị cho các yêu cầu khắt khe về ký quỹ tài chính, bắt buộc liên doanh với đối tác trong nước và đối mặt với rủi ro vận hành lưới điện.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam LNG Power Project Eyes Green Pivot on Soaring Gas Prices — Vingroup JSC has asked the Vietnamese government to replace a large liquefied natural gas power project with renewable energy due to surging ... (관련: VN-GAS-PDP8)</t>
+          <t>빈그룹(Vingroup)은 중동 분쟁으로 인한 LNG 가격 급등과 수급 불안정을 이유로 하이퐁 LNG 발전 프로젝트를 재생 가능 에너지로 전환해달라고 베트남 정부에 요청했습니다. 이는 수입 연료 의존도가 높은 에너지 인프라의 리스크를 줄이기 위한 결정으로 풀이됩니다.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam LNG Power Project Eyes Green Pivot on Soaring Gas Prices — Vingroup JSC has asked the Vietnamese government to replace a large liquefied natural gas power project with renewable energy due to surging ... (Related: VN-GAS-PDP8)</t>
+          <t>Vingroup JSC has requested the Vietnamese government to pivot its Haiphong LNG-to-power project toward renewable energy due to soaring gas prices and supply disruptions. The decision follows rising costs and competition in the LNG market linked to Middle East conflicts and Qatari supply issues.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam LNG Power Project Eyes Green Pivot on Soaring Gas Prices — Vingroup JSC has asked the Vietnamese government to replace a large liquefied natural gas power project with renewable energy due to surging ... (Liên quan: VN-GAS-PDP8)</t>
+          <t>Tập đoàn Vingroup đã đề xuất Chính phủ cho phép chuyển đổi dự án điện khí LNG tại Hải Phòng sang năng lượng tái tạo do giá nhiên liệu tăng cao từ các xung đột tại Trung Đông. Quyết định này nhằm giảm thiểu rủi ro phụ thuộc vào nguồn khí nhập khẩu đang gặp khó khăn về nguồn cung từ Qatar.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam awards $974 million LNG power plant construction contract ... — Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired ... (관련: VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>베트남 전력공사(EVN)가 9억 7,400만 달러 규모의 꽝짝 II LNG 발전소 건설 계약을 PowerChina와 Lilama 컨소시엄에 수주했습니다. 이 발전소는 1,612MW 규모로 GE Vernova의 터빈을 사용하며, 베트남의 에너지 안보 확보와 2050년 넷제로 목표 달성을 위해 2030년까지 가동될 예정입니다.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam awards $974 million LNG power plant construction contract ... — Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired ... (Related: VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>Vietnam's state utility EVN has awarded a $974 million contract to a PowerChina and Lilama consortium to build the 1,612 MW Quang Trach II LNG-fired power plant. The facility, which will utilize GE Vernova turbines, is slated to be fully operational by 2030 to bolster energy security and support Vietnam's net-zero emissions commitments.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam awards $974 million LNG power plant construction contract ... — Vietnam's state utility EVN has awarded a contract worth $974 million to a consortium of PowerChina and Lilama for building an LNG-fired ... (Liên quan: VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>Tập đoàn Điện lực Việt Nam (EVN) đã trao hợp đồng trị giá 974 triệu USD cho liên danh PowerChina và Lilama để xây dựng nhà máy điện khí LNG Quảng Trạch II công suất 1.612 MW. Nhà máy sẽ sử dụng tuabin của General Electric Vernova và dự kiến đi vào hoạt động đầy đủ vào năm 2030 nhằm đảm bảo an ninh năng lượng và thực hiện cam kết phát thải ròng bằng không.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam moves to cement LNG supply chain as power demand surges — Vietnam is stepping up efforts to build a national LNG supply chain, as PV Gas signed a series of agreements with Vietnam Electricity (EVN) ... (관련: VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>PV Gas는 베트남 전력공사(EVN) 및 PV Power와 대규모 가스 발전 프로젝트를 위한 LNG 공급 협약을 체결했습니다. 이번 계약에는 하틴성 붕앙 터미널에서 광짝 발전소로의 가스 공급과 년짝 3, 4호기에 대한 25년 장기 공급이 포함되어 통합 LNG 생태계 구축을 가속화합니다.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam moves to cement LNG supply chain as power demand surges — Vietnam is stepping up efforts to build a national LNG supply chain, as PV Gas signed a series of agreements with Vietnam Electricity (EVN) ... (Related: VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>PV Gas has signed strategic agreements with EVN and PV Power to supply LNG for major power complexes, including Quang Trach 2 &amp; 3 and Nhon Trach 3 &amp; 4. This move establishes an integrated LNG supply chain to address declining domestic gas reserves and meet Vietnam's surging electricity demand through 2030.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam moves to cement LNG supply chain as power demand surges — Vietnam is stepping up efforts to build a national LNG supply chain, as PV Gas signed a series of agreements with Vietnam Electricity (EVN) ... (Liên quan: VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>PV Gas đã ký kết các thỏa thuận với EVN và PV Power để cung cấp LNG cho các dự án điện quy mô lớn như tổ hợp Quảng Trạch và Nhơn Trạch 3 &amp; 4. Việc này giúp hình thành chuỗi cung ứng LNG tích hợp, đảm bảo an ninh năng lượng trong bối cảnh sản lượng khí nội địa suy giảm và nhu cầu điện tăng cao.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1960,17 +1960,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] POWERCHINA signs SE Asia's largest LNG power project in Vietnam — The project will play a pivotal role in advancing Vietnam's energy transition from a coal-dominated mix to one centered on natural gas and ... (관련: VN-GAS-PDP8)</t>
+          <t>베트남 전력공사(EVN)는 POWERCHINA 및 Lilama 컨소시엄과 꽝짝 II LNG 화력발전소 건설을 위한 EPC 턴키 계약을 체결했습니다. 베트남 제8차 국가전력개발계획(PDP8)의 핵심 프로젝트인 이 발전소는 1,612.8MW 규모로 완공 시 연간 약 100억 kWh의 전력을 공급할 예정입니다.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] POWERCHINA signs SE Asia's largest LNG power project in Vietnam — The project will play a pivotal role in advancing Vietnam's energy transition from a coal-dominated mix to one centered on natural gas and ... (Related: VN-GAS-PDP8)</t>
+          <t>Vietnam Electricity Corporation has signed an EPC turnkey contract with a joint venture of POWERCHINA and Lilama for the Quang Trach II LNG Thermal Power Plant. As a flagship project under Vietnam's Eighth National Power Development Plan (PDP8), this 1,612.8MW facility will be the country's largest LNG power project and is expected to provide 10 billion kWh of electricity annually.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] POWERCHINA signs SE Asia's largest LNG power project in Vietnam — The project will play a pivotal role in advancing Vietnam's energy transition from a coal-dominated mix to one centered on natural gas and ... (Liên quan: VN-GAS-PDP8)</t>
+          <t>Tập đoàn Điện lực Việt Nam đã ký hợp đồng EPC với liên danh POWERCHINA và Lilama cho dự án Nhà máy Nhiệt điện LNG Quảng Trạch II. Đây là dự án trọng điểm thuộc Quy hoạch điện VIII, với công suất 1.612,8MW và dự kiến cung cấp khoảng 10 tỷ kWh điện mỗi năm cho lưới điện quốc gia.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2024,17 +2024,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's 1.6GW LNG Power Plants Enter Commercial Operation — VIETNAM'S FIRST LNG POWER PLANTS OFFICIALLY BEGIN COMMERCIAL OPERATION On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power ... (관련: VN-GAS-PDP8)</t>
+          <t>베트남 최초의 LNG 발전소인 년짝(Nhon Trach) 3, 4호기가 2026년 1월 5일 공식적으로 상업 운전을 시작했습니다. 이 발전소는 총 1.6GW의 용량을 갖추고 있으며 매년 90억 kWh 이상의 전력을 공급하여 베트남 남부의 에너지 안보를 강화하고 탄소 배출을 60% 줄일 것으로 기대됩니다.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's 1.6GW LNG Power Plants Enter Commercial Operation — VIETNAM'S FIRST LNG POWER PLANTS OFFICIALLY BEGIN COMMERCIAL OPERATION On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power ... (Related: VN-GAS-PDP8)</t>
+          <t>Nhon Trach 3 &amp; 4, Vietnam’s first LNG-fired power plants with a total capacity of 1.6GW, officially entered commercial operation on January 5, 2026. Invested by PV Power, these plants utilize advanced H-class turbine technology to provide over 9 billion kWh annually while significantly reducing carbon emissions compared to coal.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's 1.6GW LNG Power Plants Enter Commercial Operation — VIETNAM'S FIRST LNG POWER PLANTS OFFICIALLY BEGIN COMMERCIAL OPERATION On January 5, 2026, Nhon Trach 3 &amp; 4 – the first LNG-fired power ... (Liên quan: VN-GAS-PDP8)</t>
+          <t>Vào ngày 5 tháng 1 năm 2026, nhà máy điện Nhơn Trạch 3 và 4 - những nhà máy điện khí LNG đầu tiên tại Việt Nam do PV Power đầu tư - đã chính thức đi vào vận hành thương mại. Với tổng công suất hơn 1,6 GW, dự án dự kiến cung cấp hơn 9 tỷ kWh mỗi năm, giúp đảm bảo an ninh năng lượng và giảm 60% lượng khí thải carbon so với điện than.</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2088,17 +2088,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam commissions its first LNG-fired power project, and one of ... — Vietnam commissions its first LNG-fired power project, and one of south-east Asia's biggest oil discoveries is confirmed. 14/1/2026. News. (관련: VN-GAS-PDP8)</t>
+          <t>베트남 최초의 LNG 복합화력발전소인 Nhon Trach 3, 4호기가 상업 운전을 시작했으며, 이는 제8차 국가전력개발계획(PDP8)에 따라 2030년까지 LNG 발전 용량을 22GW로 확대하려는 전략의 핵심입니다. 동시에 머피 오일(Murphy Oil)은 구룡 분지에서 지난 20년 내 동남아시아 최대 규모로 추정되는 주요 원유 매장지를 발견하여 국가 에너지 안보를 강화하고 있습니다.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam commissions its first LNG-fired power project, and one of ... — Vietnam commissions its first LNG-fired power project, and one of south-east Asia's biggest oil discoveries is confirmed. 14/1/2026. News. (Related: VN-GAS-PDP8)</t>
+          <t>Vietnam has launched commercial operations at its first LNG-fired power plants, Nhon Trach 3 and 4, aligning with the PDP8 goal to reach 22 GW of LNG capacity by 2030. Additionally, Murphy Oil confirmed a massive oil discovery at the Hai Su Vang prospect, marking one of Southeast Asia's largest finds in two decades and potentially reversing the country's declining oil production.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam commissions its first LNG-fired power project, and one of ... — Vietnam commissions its first LNG-fired power project, and one of south-east Asia's biggest oil discoveries is confirmed. 14/1/2026. News. (Liên quan: VN-GAS-PDP8)</t>
+          <t>Việt Nam đã chính thức đưa vào vận hành thương mại nhà máy điện khí LNG đầu tiên là Nhơn Trạch 3 và 4, phù hợp với Quy hoạch điện VIII nhằm đạt mục tiêu 22 GW điện khí vào năm 2030. Bên cạnh đó, Murphy Oil đã xác nhận một phát hiện dầu khí lớn tại mỏ Hải Sư Vàng, được đánh giá là một trong những phát hiện lớn nhất Đông Nam Á trong 20 năm qua.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2152,17 +2152,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Signs $974 Million LNG Deal To Strengthen Energy Security — State utility Electricity of Vietnam has awarded a construction contract worth $974 million to a consortium led by PowerChina and Lilama. (관련: VN-GAS-PDP8)</t>
+          <t>베트남 전력공사(EVN)가 에너지 안보와 2050년 넷제로 목표 달성을 위해 9억 7,400만 달러 규모의 꽝짝 II LNG 발전소 건설 계약을 체결했습니다. PowerChina와 Lilama 컨소시엄이 주도하는 이 1,612MW 규모의 프로젝트는 급증하는 산업용 전력 수요를 충족하고 석탄 의존도를 낮추는 가교 역할을 할 것입니다.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Signs $974 Million LNG Deal To Strengthen Energy Security — State utility Electricity of Vietnam has awarded a construction contract worth $974 million to a consortium led by PowerChina and Lilama. (Related: VN-GAS-PDP8)</t>
+          <t>Vietnam's state utility EVN has awarded a $974 million contract to a PowerChina-led consortium for the 1,612 MW Quang Trach II LNG power plant. This strategic infrastructure project serves as a transitional bridge to support rapid economic growth while aligning with the country's 2050 net-zero emissions commitment.</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Signs $974 Million LNG Deal To Strengthen Energy Security — State utility Electricity of Vietnam has awarded a construction contract worth $974 million to a consortium led by PowerChina and Lilama. (Liên quan: VN-GAS-PDP8)</t>
+          <t>Tập đoàn Điện lực Việt Nam (EVN) đã ký hợp đồng trị giá 974 triệu USD với liên danh PowerChina và Lilama để xây dựng nhà máy điện khí LNG Quảng Trạch II công suất 1.612 MW. Dự án này đóng vai trò quan trọng trong việc đảm bảo an ninh năng lượng và hỗ trợ lộ trình phát thải ròng bằng 0 vào năm 2050 của Việt Nam.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (관련: VN-PWR-PDP8, VN-GAS-PDP8)</t>
+          <t>베트남은 동나이성에 총 1624MW 규모의 첫 액체천연가스(LNG) 발전소인 년짝 3, 4호기를 14억 달러를 투입하여 완공했습니다. 이 시설은 국가 전력 발전 계획에 따른 향후 13개 LNG 프로젝트의 모델이 되어 남부 지역의 전력망 안정화와 2050년 탄소 중립 목표 달성을 지원할 예정입니다.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (Related: VN-PWR-PDP8, VN-GAS-PDP8)</t>
+          <t>Vietnam has inaugurated its first LNG power plants, the Nhon Trach 3 and 4 facilities in Dong Nai Province, built by Petrovietnam with a $1.4 billion investment. These plants provide a combined 1,624 MW capacity to stabilize the grid and serve as a template for 13 additional LNG projects under the national power development plan.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8)</t>
+          <t>Việt Nam đã khánh thành hai nhà máy điện khí LNG đầu tiên là Nhơn Trạch 3 và Nhơn Trạch 4 tại tỉnh Đồng Nai với tổng vốn đầu tư 1,4 tỷ USD. Dự án có tổng công suất 1.624 MW này đóng vai trò quan trọng trong việc đảm bảo an ninh năng lượng quốc gia và là hình mẫu cho 13 dự án LNG tiếp theo trong quy hoạch điện lực.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam targets saving at least 3% of total power consumption in 2026 — Vietnam is striving to save at least three percent of the total national electricity consumption in 2026.</t>
+          <t>베트남은 2026년까지 전체 전력 소비량의 최소 3%를 절감하는 것을 목표로 하고 있습니다. 이 계획은 전력 및 에너지 부문의 효율성을 높이기 위한 전략적 인프라 정책의 일환입니다.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam targets saving at least 3% of total power consumption in 2026 — Vietnam is striving to save at least three percent of the total national electricity consumption in 2026.</t>
+          <t>Vietnam aims to save at least 3% of its total power consumption by 2026 as part of its energy efficiency strategy. This target is integrated into the national power and energy sector infrastructure planning to ensure sustainable development.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam targets saving at least 3% of total power consumption in 2026 — Vietnam is striving to save at least three percent of the total national electricity consumption in 2026.</t>
+          <t>Việt Nam đặt mục tiêu tiết kiệm ít nhất 3% tổng điện năng tiêu thụ vào năm 2026. Đây là một phần trong kế hoạch phát triển hạ tầng ngành điện và năng lượng nhằm tối ưu hóa việc sử dụng tài nguyên.</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2344,17 +2344,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam targets January 2026 agreement with Russia to revive ... — Vietnam targets January 2026 agreement with Russia to revive nuclear power plans after Japan exit · Vietnam's Prime Minister has urged his ... (관련: VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam targets January 2026 agreement with Russia to revive ...</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam targets January 2026 agreement with Russia to revive ... — Vietnam targets January 2026 agreement with Russia to revive nuclear power plans after Japan exit · Vietnam's Prime Minister has urged his ... (Related: VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam targets January 2026 agreement with Russia to revive ...</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam targets January 2026 agreement with Russia to revive ... — Vietnam targets January 2026 agreement with Russia to revive nuclear power plans after Japan exit · Vietnam's Prime Minister has urged his ... (Liên quan: VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam targets January 2026 agreement with Russia to revive ...</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2408,17 +2408,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (관련: VN-PWR-PDP8)</t>
+          <t>베트남의 한 신재생 에너지 엔지니어링 기업이 송배전 및 재생 에너지 시스템을 위한 스마트 그리드와 고급 기술 솔루션을 보유한 국제 파트너를 찾고 있습니다. 이 협력은 베트남의 제8차 국가전력개발계획(PDP8) 목표에 부합하며, 전력망의 운영 신뢰성을 높이고 자산 관리를 최적화하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (Related: VN-PWR-PDP8)</t>
+          <t>A Vietnamese renewable energy company is seeking international partners to provide smart-grid and advanced technology solutions for power transmission and distribution systems. Aligned with the VN-PWR-PDP8 objectives, this partnership aims to improve grid reliability and optimize asset management through commercial or technical cooperation agreements.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Một công ty năng lượng tái tạo tại Việt Nam đang tìm kiếm đối tác quốc tế cung cấp các giải pháp lưới điện thông minh và công nghệ tiên tiến cho hệ thống truyền tải và phân phối điện. Phù hợp với định hướng Quy hoạch điện VIII (PDP8), sự hợp tác này tập trung vào việc cải thiện độ tin cậy vận hành và tối ưu hóa quản lý tài sản năng lượng.</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2468,17 +2468,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (관련: VN-PWR-PDP8)</t>
+          <t>베트남은 2025년 4월 승인된 개정 제8차 국가전력개발계획(PDP8)에 따라 LNG, 재생에너지 및 원자력 발전을 포함한 에너지 믹스 확대를 추진하고 있습니다. 이번 계획은 BESS 용량을 최대 16,300MW로 늘리고 직접전력구매계약(DPPA) 도입을 통해 시장 중심의 전력 공급 체계를 구축하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (Related: VN-PWR-PDP8)</t>
+          <t>Vietnam has updated its Power Development Plan 8 (PDP8) to aggressively expand LNG, solar, wind, and nuclear energy capacity to meet surging electricity demand. The revised framework introduces market-based pricing, supports Direct Power Purchase Agreements (DPPAs), and significantly increases targets for Battery Energy Storage Systems (BESS) to ensure grid stability.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (Liên quan: VN-PWR-PDP8)</t>
+          <t>Việt Nam đã phê duyệt điều chỉnh Quy hoạch điện VIII (PDP8) với mục tiêu đẩy mạnh phát triển điện khí LNG, năng lượng tái tạo và tái khởi động điện hạt nhân. Các chính sách mới tập trung vào cơ chế mua bán điện trực tiếp (DPPA), phát triển hệ thống lưu trữ năng lượng (BESS) và cải thiện tính khả thi về tài chính cho các dự án năng lượng.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남은 2050년 넷제로 배출 목표와 제8차 전력개발계획(PDP8)에 발맞추어 2030년까지의 스마트 그리드 로드맵을 업데이트했습니다. 이 계획은 송전망 현대화, 신재생 에너지 통합, 변전소 자동화 및 사이버 보안 강화를 우선순위로 두며, 장기적으로는 전기차 충전 인프라와 가상 발전소(VPP) 도입을 지원합니다.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam has updated its Smart Grid Development Roadmap to 2030 with a vision to 2050 to align with PDP8 and Net Zero commitments. The plan prioritizes grid modernization, substation automation, and SCADA/EMS upgrades to integrate renewable energy, while also establishing frameworks for electric vehicle integration and advanced metering infrastructure.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Việt Nam đã cập nhật Lộ trình phát triển Lưới điện thông minh đến năm 2030, tầm nhìn đến năm 2050 nhằm phù hợp với Quy hoạch điện VIII và cam kết Net Zero. Kế hoạch tập trung ưu tiên hiện đại hóa hệ thống điều khiển, tự động hóa trạm biến áp và tăng cường an ninh mạng để tích hợp năng lượng tái tạo, đồng thời chuẩn bị hạ tầng cho xe điện và các nguồn năng lượng phân tán.</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2592,17 +2592,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Plugging nuclear energy safely into Vietnam's grid - RMIT University — Vietnam's new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic ... (관련: VN-REN-NPP-2050)</t>
+          <t>베트남은 2026년 1월 발효된 새로운 원자력법을 통해 2050년까지 원자력 발전 용량을 최대 14,000MW로 확대할 계획입니다. RMIT 대학 전문가들은 이 목표를 달성하기 위해 차세대 원자로(SMR 등) 도입과 함께 전력망 강화 및 전문 인력 양성이 필수적이라고 강조합니다.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Plugging nuclear energy safely into Vietnam's grid - RMIT University — Vietnam's new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic ... (Related: VN-REN-NPP-2050)</t>
+          <t>Vietnam's new Atomic Energy Law, effective 2026, paves the way for advanced nuclear technologies to reach a target capacity of 14,000 MW by 2050. Experts from RMIT Vietnam state that success depends on integrating these plants into the national grid and developing a robust safety culture and skilled workforce.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Plugging nuclear energy safely into Vietnam's grid - RMIT University — Vietnam's new Law on Atomic Energy, effective 1 January 2026, sets strict safety and licensing standards aligned with the International Atomic ... (Liên quan: VN-REN-NPP-2050)</t>
+          <t>Luật Năng lượng nguyên tử mới của Việt Nam có hiệu lực từ năm 2026, mở đường cho việc phát triển điện hạt nhân với mục tiêu đạt công suất 14.000 MW vào năm 2050. Các chuyên gia từ RMIT nhấn mạnh rằng sự thành công sẽ phụ thuộc vào khả năng sẵn sàng của lưới điện, cơ sở hạ tầng kỹ thuật và việc đào tạo nguồn nhân lực chuyên môn cao.</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Green Hydrogen: A Pathway to Vietnam's Energy Security - MDPI — The study summarizes the energy landscape of Vietnam in Section 2 and addresses the role of green hydrogen in Vietnam's energy transition in Section 3. The ... (관련: VN-REN-NPP-2050)</t>
+          <t>베트남 정부는 2050년 탄소 중립 달성을 위해 그린 수소 에너지 개발 전략(HEDS)을 발표했으며, 이는 국가 전력 개발 계획(PDP8)과 연계됩니다. 풍부한 태양광 및 풍력 자원을 활용하여 수소를 생산함으로써 화석 연료 의존도를 낮추고 국가 에너지 안보를 강화하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Green Hydrogen: A Pathway to Vietnam's Energy Security - MDPI — The study summarizes the energy landscape of Vietnam in Section 2 and addresses the role of green hydrogen in Vietnam's energy transition in Section 3. The ... (Related: VN-REN-NPP-2050)</t>
+          <t>The Vietnamese government has launched its Hydrogen Energy Development Strategy (HEDS) to 2030 with a vision to 2050, aiming to integrate green hydrogen into the national power system (PDP8). By leveraging its vast solar and wind potential, Vietnam seeks to decarbonize heavy industries and transportation while ensuring long-term energy security.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Green Hydrogen: A Pathway to Vietnam's Energy Security - MDPI — The study summarizes the energy landscape of Vietnam in Section 2 and addresses the role of green hydrogen in Vietnam's energy transition in Section 3. The ... (Liên quan: VN-REN-NPP-2050)</t>
+          <t>Chính phủ Việt Nam đã ban hành Chiến lược phát triển năng lượng hydrogen đến năm 2030, tầm nhìn đến năm 2050 nhằm hiện thực hóa mục tiêu phát thải ròng bằng không. Chiến lược này tập trung khai thác tiềm năng năng lượng tái tạo dồi dào để sản xuất hydro xanh, giúp giảm phụ thuộc vào nhiên liệu hóa thạch và đảm bảo an ninh năng lượng quốc gia.</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2716,17 +2716,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (관련: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>베트남 정치국은 2030년까지 국가 에너지 안보를 보장하기 위한 결의안 제70-NQ/TW호를 발표하고 민간 및 외국인 투자를 가로막는 제도적 장벽을 제거하기로 했습니다. 이 결의안은 재생 에너지 비중을 30%까지 확대하고 닌투언 원자력 발전소 건설을 재개하는 등 에너지 믹스 다양화와 탄소 중립 목표 달성을 강조합니다.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (Related: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam's Politburo has issued Resolution 70-NQ/TW to enhance national energy security by 2030, specifically targeting the removal of institutional barriers to attract private and international capital. The directive prioritizes renewable energy growth, smart grid development, and the expedited revival of nuclear power projects like Ninh Thuan 1 and 2.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (Liên quan: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Bộ Chính trị đã ban hành Nghị quyết 70-NQ/TW nhằm đảm bảo an ninh năng lượng quốc gia đến năm 2030, tập trung tháo gỡ các rào cản thể chế để thu hút vốn đầu tư tư nhân và quốc tế. Nghị quyết ưu tiên phát triển năng lượng tái tạo chiếm 25-30% tổng cung và thúc đẩy triển khai các dự án điện hạt nhân Ninh Thuận 1 và 2 trong giai đoạn 2030-2035.</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (관련: VN-PWR-PDP8)</t>
+          <t>독일 경제협력개발부(BMZ)가 자금을 지원하는 SGREEE 프로젝트는 베트남 전력 규제청(ERAV)과 협력하여 국가 전력망의 현대화와 자동화를 추진하고 있습니다. 이 사업은 재생 에너지 통합을 확대하고 에너지 효율을 높이기 위한 스마트 그리드 로드맵 이행과 전력 시스템의 디지털화를 지원합니다.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (Related: VN-PWR-PDP8)</t>
+          <t>The SGREEE project, funded by BMZ and partnered with ERAV, supports the modernization and automation of Vietnam's national power grid. It focuses on implementing the Smart Grid Roadmap to facilitate the integration of renewable energy and enhance energy efficiency through digitalization and system flexibility.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Dự án SGREEE, do BMZ tài trợ và hợp tác với ERAV, hỗ trợ Chính phủ Việt Nam hiện đại hóa và tự động hóa hệ thống truyền tải và phân phối điện quốc gia. Dự án tập trung vào việc thực hiện Lộ trình Lưới điện thông minh nhằm tích hợp năng lượng tái tạo và nâng cao hiệu quả năng lượng thông qua chuyển đổi số.</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2840,17 +2840,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] $18b grid investment crucial to driving Vietnam's energy future ... — A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for Vietnam.</t>
+          <t>베트남은 2026년부터 2030년까지 전력망 확충을 위해 180억 달러를 투자할 계획이며, 이는 에너지 프로젝트의 실질적인 구현을 위해 필수적입니다. 현재 재생 에너지 용량 확대 속도에 비해 전력망 보강이 늦어 병목 현상이 발생하고 있으나, 2026년 예정된 입법 개혁을 통해 규제 완화와 투자 유인이 이루어질 전망입니다.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] $18b grid investment crucial to driving Vietnam's energy future ... — A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for Vietnam.</t>
+          <t>Vietnam plans a $18 billion investment in transmission infrastructure between 2026 and 2030 to bridge the gap between energy planning and project delivery. While transmission bottlenecks currently pose risks as renewable growth outpaces grid reinforcement, legislative reforms in 2026 are expected to streamline licensing and offer green-energy incentives.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] $18b grid investment crucial to driving Vietnam's energy future ... — A planned $18b investment in transmission infrastructure between 2026 and 2030 will be critical for Vietnam.</t>
+          <t>Việt Nam dự kiến đầu tư 18 tỷ USD vào hạ tầng truyền tải điện trong giai đoạn 2026-2030 để hiện thực hóa các dự án năng lượng. Hiện tại, tình trạng nghẽn mạch lưới điện vẫn là thách thức lớn khi năng lượng tái tạo phát triển nhanh hơn hạ tầng, nhưng các cải cách luật pháp vào năm 2026 được kỳ vọng sẽ giải quyết nút thắt này thông qua cơ chế lựa chọn nhà đầu tư hợp lý và ưu đãi xanh.</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2904,17 +2904,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam to build $1.1B bridge to connect key Mekong Delta ... — The bridge will have six lanes, 100 kph design speed, 300 m navigation clearance, plus approach roads with emergency lanes. Total investment is ... (관련: VN-TRAN-2055)</t>
+          <t>베트남은 메콩 델타의 주요 고속도로를 연결하기 위해 약 11억 달러 이상을 투입하여 '껀터 2' 교량을 건설할 계획입니다. 이 교량은 도로와 철도가 결합된 복합 링크로 설계되었으며, 2026년 말 착공하여 약 5년간의 공사 기간이 소요될 예정입니다.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam to build $1.1B bridge to connect key Mekong Delta ... — The bridge will have six lanes, 100 kph design speed, 300 m navigation clearance, plus approach roads with emergency lanes. Total investment is ... (Related: VN-TRAN-2055)</t>
+          <t>Vietnam is set to invest over $1.1 billion in the Can Tho 2 bridge, a strategic road-and-rail link connecting key expressways in the Mekong Delta. Construction is scheduled to begin in late 2026 and is expected to take five years, enhancing regional logistics and national security.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam to build $1.1B bridge to connect key Mekong Delta ... — The bridge will have six lanes, 100 kph design speed, 300 m navigation clearance, plus approach roads with emergency lanes. Total investment is ... (Liên quan: VN-TRAN-2055)</t>
+          <t>Việt Nam đang chuẩn bị xây dựng cầu Cần Thơ 2 với tổng vốn đầu tư hơn 1,1 tỷ USD nhằm kết nối các tuyến đường cao tốc trọng điểm tại Đồng bằng sông Cửu Long. Dự án kết hợp giữa đường bộ và đường sắt này dự kiến sẽ khởi công vào cuối năm 2026 và hoàn thành sau khoảng 5 năm.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam highway developments continue | Global Highways — Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam's expressway ... (관련: VN-TRAN-2055, VN-EV-2030)</t>
+          <t>베트남은 2030년까지 중부 고원 지대에 약 830km에 달하는 8개의 새로운 고속도로를 건설할 계획이며, 총 사업비는 약 65억 달러에 이를 것으로 예상됩니다. 탄푸-바오록 구간은 2023년에 착공될 예정이며, 호치민시 제4순환도로 프로젝트는 2026년 완공을 목표로 하고 있습니다.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam highway developments continue | Global Highways — Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam's expressway ... (Related: VN-TRAN-2055, VN-EV-2030)</t>
+          <t>Vietnam plans to expand its expressway network by adding 830km through eight new projects in the Central Highlands by 2030, costing approximately $6.5 billion. Key developments include the Tan Phu-Bao Loc route starting in 2023 and the Ho Chi Minh City Beltway No4 project slated for completion by 2026.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam highway developments continue | Global Highways — Vietnam plans to build eight new expressways in the Central Highlands by 2030. This programme of construction will add around 830km to Vietnam's expressway ... (Liên quan: VN-TRAN-2055, VN-EV-2030)</t>
+          <t>Việt Nam kế hoạch xây dựng 8 tuyến đường cao tốc mới tại Tây Nguyên đến năm 2030 với tổng chiều dài khoảng 830km và kinh phí gần 6,5 tỷ USD. Các dự án trọng điểm bao gồm cao tốc Tân Phú - Bảo Lộc khởi công năm 2023 và đường Vành đai 4 TP.HCM dự kiến hoàn thành vào năm 2026.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Binh Goi bridge to open on April 30, 2026 - YouTube — Ho Chi Minh City will open Binh Goi Bridge to technical traffic on April 30, 2026, under the Beltway No. 3 project.</t>
+          <t>베트남 교통 및 인프라 부문의 최신 소식을 전하는 사이공 타임즈 뉴스입니다. 현재 제공된 콘텐츠는 채널 식별 정보에 한정되어 있어 구체적인 프로젝트 세부 사항을 요약하기 어렵습니다.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Binh Goi bridge to open on April 30, 2026 - YouTube — Ho Chi Minh City will open Binh Goi Bridge to technical traffic on April 30, 2026, under the Beltway No. 3 project.</t>
+          <t>This is the Saigon Times News covering the transport and infrastructure sector in Vietnam. Due to the limited content provided in the snippet, specific details regarding infrastructure plans or project updates are not currently available for full summary.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Binh Goi bridge to open on April 30, 2026 - YouTube — Ho Chi Minh City will open Binh Goi Bridge to technical traffic on April 30, 2026, under the Beltway No. 3 project.</t>
+          <t>Đây là tin tức từ Saigon Times News về lĩnh vực Giao thông và Hạ tầng tại Việt Nam. Do nội dung cung cấp chỉ bao gồm tên kênh, hiện chưa có đủ thông tin chi tiết về các dự án cụ thể để tóm tắt đầy đủ.</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3092,17 +3092,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam to build 2,000km of new expressways between 2026-2030 — From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030. The coastal route will be completed ... (관련: VN-TRAN-2055)</t>
+          <t>베트남 건설부는 2026년부터 2030년까지 2,000km의 고속도로를 추가 건설하여 총 5,000km의 고속도로망을 구축할 계획입니다. 이 계획에는 남북 고속철도, 국제 환적 항만, 신공항 건설뿐만 아니라 주요 도시의 메트로 및 순환도로 확충이 포함됩니다.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam to build 2,000km of new expressways between 2026-2030 — From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030. The coastal route will be completed ... (Related: VN-TRAN-2055)</t>
+          <t>Vietnam plans to build 2,000km of new expressways between 2026 and 2030, bringing the national total to 5,000km. The infrastructure strategy also prioritizes the North-South high-speed railway, international transshipment seaports, and smart urban transport systems including new metro lines.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam to build 2,000km of new expressways between 2026-2030 — From 2026–2030, about 2,000 km of expressways will be built, raising the national total to 5,000 km by 2030. The coastal route will be completed ... (Liên quan: VN-TRAN-2055)</t>
+          <t>Việt Nam đặt mục tiêu xây dựng thêm 2.000 km đường bộ cao tốc trong giai đoạn 2026–2030, nâng tổng chiều dài toàn quốc lên 5.000 km. Kế hoạch này tập trung vào đường sắt tốc độ cao Bắc-Nam, phát triển cảng biển trung chuyển quốc tế và hoàn thiện hạ tầng giao thông đô thị thông minh.</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3156,17 +3156,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>[Urban Development] 10 Vietnam Construction Projects Completing in 2026 - YouTube — ... expressway connecting north to south for the first time. Metro lines in Hanoi and Ho Chi Minh City that took over a decade to build. And ... (관련: VN-TRAN-2055)</t>
+          <t>베트남은 지난 50년 동안 전쟁의 상흔을 딛고 애플과 삼성의 글로벌 제조 허브로 급성장했습니다. 급격한 경제 발전에 발맞추어 롱탄 국제공항을 포함한 10개의 대규모 인프라 프로젝트가 2026년 완공을 목표로 진행 중입니다.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>[Urban Development] 10 Vietnam Construction Projects Completing in 2026 - YouTube — ... expressway connecting north to south for the first time. Metro lines in Hanoi and Ho Chi Minh City that took over a decade to build. And ... (Related: VN-TRAN-2055)</t>
+          <t>Vietnam has transitioned from a war-torn nation to a major manufacturing hub for companies like Apple and Samsung over the last 50 years. To support this growth, ten major construction projects, including the Long Thanh International Airport, are scheduled for completion in 2026.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>[Urban Development] 10 Vietnam Construction Projects Completing in 2026 - YouTube — ... expressway connecting north to south for the first time. Metro lines in Hanoi and Ho Chi Minh City that took over a decade to build. And ... (Liên quan: VN-TRAN-2055)</t>
+          <t>Việt Nam đã chuyển mình từ một quốc gia bị tàn phá bởi chiến tranh thành trung tâm sản xuất của Apple và Samsung trong 50 năm qua. Hiện nay, cơ sở hạ tầng đang được đẩy mạnh phát triển với 10 dự án xây dựng trọng điểm, bao gồm sân bay quốc tế Long Thành, dự kiến hoàn thành vào năm 2026.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] HCMC plans to break ground on 14 major transport infrastructure ... — Alongside new ground-breaking projects, the city targets completion of around 10 major works in 2026, including Ring Road 3, An Phu and My Thuy ... (관련: VN-TRAN-2055)</t>
+          <t>호치민시는 2026년에 순환도로 4호선, 메트로 2호선, 껀저 교량 등 14개의 주요 교통 인프라 프로젝트를 착공할 계획입니다. 또한, 2026년까지 순환도로 3호선과 안푸 교차로를 포함한 10개 주요 사업의 완공을 목표로 하고 있습니다. 이는 현대적인 교통망 구축을 위해 약 1,780조 동(677.6억 달러)을 투입하는 2025-2030 액션 프로그램의 일환입니다.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] HCMC plans to break ground on 14 major transport infrastructure ... — Alongside new ground-breaking projects, the city targets completion of around 10 major works in 2026, including Ring Road 3, An Phu and My Thuy ... (Related: VN-TRAN-2055)</t>
+          <t>Ho Chi Minh City plans to break ground on 14 major transport infrastructure projects in 2026, including Ring Road 4, Metro Line No. 2, and the Can Gio bridge. The city also targets the completion of 10 major works, such as Ring Road 3 and various interchanges, within the same year. These efforts are part of a larger 2025–2030 investment plan involving 77 projects valued at approximately 67.76 billion USD.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] HCMC plans to break ground on 14 major transport infrastructure ... — Alongside new ground-breaking projects, the city targets completion of around 10 major works in 2026, including Ring Road 3, An Phu and My Thuy ... (Liên quan: VN-TRAN-2055)</t>
+          <t>TP.HCM kế hoạch khởi công 14 dự án hạ tầng giao thông trọng điểm vào năm 2026, bao gồm Vành đai 4, Tuyến Metro số 2 và cầu Cần Giờ. Thành phố cũng đặt mục tiêu hoàn thành 10 công trình lớn như Vành đai 3 và nút giao An Phú trong cùng năm đó. Đây là một phần của chương trình hành động 2025–2030 với tổng vốn đầu tư ước tính khoảng 1,78 triệu tỷ đồng cho 77 dự án.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3280,17 +3280,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam plans bridge link upgrade | Global Highways — The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes. The ... (관련: VN-TRAN-2055)</t>
+          <t>베트남 호치민시 사이공강을 가로지르는 투티엠 4교(Thu Thiem 4 Bridge) 건설 계획이 추진 중입니다. 이 교량은 총 길이 2.16km, 왕복 6차로 규모로 2군과 7군을 연결할 예정입니다.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam plans bridge link upgrade | Global Highways — The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes. The ... (Related: VN-TRAN-2055)</t>
+          <t>Ho Chi Minh City is planning the construction of the Thu Thiem 4 Bridge spanning the Saigon River to connect District 2 and District 7. The 2.16km-long bridge will feature six traffic lanes and is a joint effort between the Ministry of Planning and Investment, the HCMC People's Committee, and the Ministry of Transport.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam plans bridge link upgrade | Global Highways — The project is for the Thu Thiem 4 Bridge, which will measure 2.16km and connect District 2 with District 7. The bridge will feature six traffic lanes. The ... (Liên quan: VN-TRAN-2055)</t>
+          <t>Thành phố Hồ Chí Minh đang lập kế hoạch xây dựng cầu Thủ Thiêm 4 bắc qua sông Sài Gòn để kết nối Quận 2 với Quận 7. Cây cầu có chiều dài 2,16km với quy mô 6 làn xe, được phối hợp triển khai bởi Bộ Kế hoạch và Đầu tư, Ủy ban Nhân dân TP.HCM và Bộ Giao thông Vận tải.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3344,17 +3344,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project ... — Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project, construction set for 2026 · The Ho Chi Minh City administration has submitted an ...</t>
+          <t>호치민시는 약 1억 9,300만 달러 규모의 투 티엠 4 교량 건설 사업을 시의회에 제안했습니다. 이 프로젝트는 2026년 4분기에 착공하여 2028년 완공될 예정이며, 시 남부 지역과 투 티엠 신도시를 연결하여 교통 혼잡을 완화하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project ... — Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project, construction set for 2026 · The Ho Chi Minh City administration has submitted an ...</t>
+          <t>Ho Chi Minh City has proposed the $193 million Thu Thiem 4 Bridge project to connect the southern urban area with the Thu Thiem New Urban Area. Construction is scheduled to begin in late 2026 and reach completion by the end of 2028, funded entirely by the city's budget to improve regional traffic synchronization.</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project ... — Ho Chi Minh City proposes $193mn Thu Thiem 4 bridge project, construction set for 2026 · The Ho Chi Minh City administration has submitted an ...</t>
+          <t>Ủy ban Nhân dân TP.HCM đã đề xuất dự án cầu Thủ Thiêm 4 với tổng vốn đầu tư khoảng 5.063 tỷ đồng (193 triệu USD) nối Quận 7 với Khu đô thị mới Thủ Thiêm. Dự kiến công trình sẽ khởi công vào quý 4 năm 2026 và hoàn thành vào quý 4 năm 2028 nhằm giảm tải áp lực giao thông cho khu vực trung tâm.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's highest vertical cable-stayed bridge accelerates to wait for ... — Hai Phong - By the end of March 2026, the site clearance progress of the Nguyen Trai - Le Hong Phong intersection will only reach about 60%.</t>
+          <t>베트남에서 가장 높은 55m의 항행 통과 높이를 자랑하는 푸억카잉(Phuoc Khanh) 교량이 현재 96%의 공정률을 보이며 2026년 5월 완공을 앞두고 있습니다. 벤룩-롱탄 고속도로의 핵심 구간인 이 교량은 2026년 3분기 전 구간 개통을 위한 결정적인 역할을 할 것으로 기대됩니다.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's highest vertical cable-stayed bridge accelerates to wait for ... — Hai Phong - By the end of March 2026, the site clearance progress of the Nguyen Trai - Le Hong Phong intersection will only reach about 60%.</t>
+          <t>The Phuoc Khanh Bridge, featuring Vietnam's highest navigation clearance of 55 meters, has reached 96% completion and is scheduled for closure in May 2026. This vital link in the Ben Luc - Long Thanh Expressway is expected to facilitate full-route traffic operations by the third quarter of 2026.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's highest vertical cable-stayed bridge accelerates to wait for ... — Hai Phong - By the end of March 2026, the site clearance progress of the Nguyen Trai - Le Hong Phong intersection will only reach about 60%.</t>
+          <t>Cầu Phước Khánh với tĩnh không thông thuyền cao nhất Việt Nam (55m) hiện đã đạt 96% khối lượng và dự kiến sẽ hợp long vào tháng 5/2026. Đây là mắt xích quan trọng thuộc cao tốc Bến Lức - Long Thành, tạo tiền đề để thông xe toàn tuyến vào quý III/2026.</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3472,17 +3472,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>[Other] Vietnam's $67BN Gamble on High-Speed Rail - YouTube — Vietnam is about to build the largest infrastructure project in its history. Rayon is the all-in-one, effortless CAD tool for going from ...</t>
+          <t>베트남은 역사상 최대 규모의 인프라 프로젝트인 670억 달러 규모의 고속철도 건설을 추진하고 있습니다. 이 야심 찬 프로젝트는 국가의 연결성을 혁신하고 경제 성장을 촉진하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>[Other] Vietnam's $67BN Gamble on High-Speed Rail - YouTube — Vietnam is about to build the largest infrastructure project in its history. Rayon is the all-in-one, effortless CAD tool for going from ...</t>
+          <t>Vietnam is embarking on its largest-ever infrastructure project, a high-speed railway valued at $67 billion. This massive investment aims to modernize the nation's transport network and stimulate long-term economic development.</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>[Other] Vietnam's $67BN Gamble on High-Speed Rail - YouTube — Vietnam is about to build the largest infrastructure project in its history. Rayon is the all-in-one, effortless CAD tool for going from ...</t>
+          <t>Việt Nam đang chuẩn bị triển khai dự án cơ sở hạ tầng lớn nhất trong lịch sử với tuyến đường sắt tốc độ cao trị giá 67 tỷ USD. Dự án đầy tham vọng này hứa hẹn sẽ thay đổi mạng lưới giao thông và thúc đẩy tăng trưởng kinh tế quốc gia.</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3536,17 +3536,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam pushes to break ground on North-South high-speed railway ... — Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) ...</t>
+          <t>베트남 건설부 장관은 2026년 말까지 남북 고속철도 착공을 추진하라고 지시했습니다. 이 프로젝트는 하노이와 호치민을 잇는 1,541km 구간으로, 시속 350km의 설계 속도를 갖추고 2035년 완공을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam pushes to break ground on North-South high-speed railway ... — Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) ...</t>
+          <t>Vietnam's Minister of Construction has ordered agencies to ensure the 1,541-km North-South high-speed railway breaks ground by the end of 2026. Designed for speeds of 350 km/h, the project will connect Hanoi and Ho Chi Minh City with a target completion date of 2035.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam pushes to break ground on North-South high-speed railway ... — Approved by the National Assembly on November 30, 2024, the high-speed rail project will stretch 1,541 kilometers from Ngoc Hoi Station (Hanoi) ...</t>
+          <t>Bộ trưởng Bộ Xây dựng yêu cầu các cơ quan đảm bảo khởi công dự án đường sắt tốc độ cao Bắc-Nam vào cuối năm 2026. Tuyến đường sắt dài 1.541 km nối Hà Nội và TP.HCM với vận tốc thiết kế 350 km/h, dự kiến hoàn thành vào năm 2035.</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3600,17 +3600,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam eyes to begin high-speed rail construction in 2026 — The government plans to complete the north-south high-speed rail within 10 years as it prioritizes breakthroughs in infrastructure development. (관련: VN-EV-2030)</t>
+          <t>베트남 정부는 당초 계획보다 1년 앞당겨 2026년 말까지 남북 고속철도 건설에 착수하라는 지시를 내렸습니다. 670억 달러 규모의 이 프로젝트는 하노이와 호치민을 연결하며, 이 외에도 중국 국경을 잇는 북부 지역 철도망 확충이 함께 추진됩니다.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam eyes to begin high-speed rail construction in 2026 — The government plans to complete the north-south high-speed rail within 10 years as it prioritizes breakthroughs in infrastructure development. (Related: VN-EV-2030)</t>
+          <t>The Vietnamese government has ordered the acceleration of the North-South high-speed railway project to begin construction by the end of 2026, one year earlier than originally planned. This $67 billion project will span 1,541 km between Hanoi and Ho Chi Minh City, complemented by additional rail links to the Chinese border and expanded metro systems in major cities.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam eyes to begin high-speed rail construction in 2026 — The government plans to complete the north-south high-speed rail within 10 years as it prioritizes breakthroughs in infrastructure development. (Liên quan: VN-EV-2030)</t>
+          <t>Thủ tướng Phạm Minh Chính đã chỉ đạo đẩy nhanh tiến độ để khởi công dự án đường sắt tốc độ cao Bắc-Nam vào cuối năm 2026, sớm hơn một năm so với kế hoạch ban đầu. Dự án trị giá 67 tỷ USD này dài 1.541 km nối Hà Nội với TP.HCM, bên cạnh các tuyến đường sắt kết nối biên giới phía Bắc cũng đang được ưu tiên triển khai.</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3664,17 +3664,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City will start construction of 5 key metro lines in 2026 ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
+          <t>호치민시는 2026년에 5개의 주요 메트로 노선 건설을 시작할 예정입니다. 이 프로젝트는 도시의 교통 인프라를 획기적으로 개선하고 지역 경제 발전을 촉진하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City will start construction of 5 key metro lines in 2026 ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
+          <t>Ho Chi Minh City is scheduled to begin the construction of five key metro lines in 2026. This infrastructure initiative aims to enhance urban connectivity and support the city's long-term development goals.</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City will start construction of 5 key metro lines in 2026 ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
+          <t>Thành phố Hồ Chí Minh sẽ khởi công xây dựng 5 tuyến tàu điện ngầm (metro) trọng điểm vào năm 2026. Đây là bước đi quan trọng nhằm hoàn thiện hệ thống giao thông công cộng và thúc đẩy phát triển đô thị bền vững.</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3728,17 +3728,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] The rail dream gains speed in southern Vietnam - VietNamNet — City leaders outlined a clear roadmap: by 2030, urban railway transport is expected to meet 20 to 30 percent of travel demand; by 2035, 35 to 50 ...</t>
+          <t>호치민시의 메트로 1호선(벤탄-수오이띠엔)이 개통 1년 만에 2,000만 명 이상의 승객을 유치하며 성공적으로 안착했으며, 2호선도 최근 착공에 들어갔습니다. 시 정부는 2045년까지 대중교통 분담률을 50~60%로 높이기 위해 총 9개의 도시철도 노선을 구축하는 야심 찬 로드맵을 추진하고 있습니다. 이러한 철도망 확충은 도시의 현대화와 지속 가능한 발전을 이끄는 핵심축이 될 전망입니다.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] The rail dream gains speed in southern Vietnam - VietNamNet — City leaders outlined a clear roadmap: by 2030, urban railway transport is expected to meet 20 to 30 percent of travel demand; by 2035, 35 to 50 ...</t>
+          <t>Ho Chi Minh City's Metro Line 1 has achieved over 20 million passenger trips in its first year, signaling a successful shift toward high-capacity public transport. Following this success, the city has broken ground on Metro Line 2 and is planning a total of nine lines to meet 50-60% of travel demand by 2045. This infrastructure expansion serves as the backbone for the city's Transit-Oriented Development (TOD) and modern urban transformation.</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] The rail dream gains speed in southern Vietnam - VietNamNet — City leaders outlined a clear roadmap: by 2030, urban railway transport is expected to meet 20 to 30 percent of travel demand; by 2035, 35 to 50 ...</t>
+          <t>Tuyến Metro số 1 (Bến Thành - Suối Tiên) tại TP.HCM đã đạt hơn 20 triệu lượt khách sau một năm vận hành, tạo động lực cho việc khởi công Tuyến số 2 và triển khai mạng lưới đường sắt đô thị. Thành phố đặt mục tiêu đến năm 2045, hệ thống metro sẽ đáp ứng 50-60% nhu cầu đi lại của người dân. Với lộ trình 9 tuyến đường sắt, TP.HCM đang hướng tới mô hình đô thị hiện đại, giảm ùn tắc và phát triển bền vững theo định hướng TOD.</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3792,17 +3792,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>[Urban Development] Construction of Vietnam's first high-speed railway expected to start ... — The North-South high-speed railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City with a design speed of 350 km/h.</t>
+          <t>베트남 건설부 장관의 지시에 따라 하노이와 호치민시를 잇는 1,541km 구간의 남북 고속철도 건설이 2026년 말에 시작될 예정입니다. 이 프로젝트는 총 587억 1천만 달러의 투자비가 투입되며, 시속 350km의 설계 속도를 갖춘 복선 철도로 건설됩니다.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>[Urban Development] Construction of Vietnam's first high-speed railway expected to start ... — The North-South high-speed railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City with a design speed of 350 km/h.</t>
+          <t>Construction of Vietnam's first high-speed railway, connecting Hanoi and Ho Chi Minh City, is expected to begin by the end of 2026 following instructions from the Minister of Construction. The 1,541 km project features a design speed of 350 km/h and requires an estimated investment of $58.71 billion.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>[Urban Development] Construction of Vietnam's first high-speed railway expected to start ... — The North-South high-speed railway is planned to span approximately 1,541 km from Hanoi to Ho Chi Minh City with a design speed of 350 km/h.</t>
+          <t>Theo chỉ đạo của Bộ trưởng Bộ Xây dựng, dự án đường sắt tốc độ cao Bắc-Nam dài 1.541 km nối Hà Nội và TP.HCM dự kiến sẽ khởi công vào cuối năm 2026. Dự án có tổng vốn đầu tư khoảng 58,71 tỷ USD với thiết kế đường đôi và tốc độ đạt 350 km/h.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3856,17 +3856,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>[Urban Development] Connecting Vietnam's high-speed railway stations with urban rail ... — Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line, and they will all be new ...</t>
+          <t>베트남은 하노이와 호치민을 잇는 고속철도 건설을 계획하고 있으며, 도심 외곽에 위치할 신설 역들과 도심을 연결하기 위해 하노이 메트로 1호선과 호치민 메트로 2호선 등 도시철도망 확충을 추진하고 있습니다. 다낭을 비롯해 냐짱, 후에 등 주요 거점 도시들도 관광 활성화와 접근성 개선을 위해 고속철도역과 연계된 도시 철도 및 트램 도입을 검토해야 한다는 제안이 나오고 있습니다.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>[Urban Development] Connecting Vietnam's high-speed railway stations with urban rail ... — Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line, and they will all be new ...</t>
+          <t>Vietnam is planning a high-speed railway connecting Hanoi and Ho Chi Minh City, with confirmed metro links for Hanoi's Ngoc Hoi Station and HCMC's Thu Thiem Station to ensure urban connectivity. Other major cities like Da Nang, Nha Trang, and Hue are also proposing or being urged to develop integrated light rail or tram systems to bridge the gap between distant high-speed rail stations and their respective city centers.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>[Urban Development] Connecting Vietnam's high-speed railway stations with urban rail ... — Vietnam is planning to build a high-speed railway from Hanoi to Ho Chi Minh City. 23 stations are planned for the line, and they will all be new ...</t>
+          <t>Việt Nam đang quy hoạch tuyến đường sắt tốc độ cao Bắc-Nam với các ga kết nối trọng điểm như Ngọc Hồi (Hà Nội) qua Tuyến Metro số 1 và Thủ Thiêm (TP.HCM) qua Tuyến Metro số 2. Các thành phố khác như Đà Nẵng, Nha Trang và Huế cũng được đề xuất phát triển hệ thống đường sắt đô thị hoặc tàu điện nhẹ để kết nối hiệu quả các ga cao tốc mới nằm xa trung tâm với khu vực nội đô và các điểm du lịch.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>[Urban Development] Financial close allows Ho Chi Minh City Line 2 civil works to start — The Ho Chi Minh City Party Committee decided in November 2025 to use the municipal and national budget to complete Line 2. Completion is ...</t>
+          <t>호치민시 메트로 2호선 건설을 위한 토목 공사가 1월 15일 착공되었습니다. 약 11.3km 길이의 이 노선은 시 정부와 국가 예산을 투입하여 2030년 4분기 완공을 목표로 하며, 현지 기업인 THACO가 이끄는 컨소시엄이 공사를 주도합니다.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>[Urban Development] Financial close allows Ho Chi Minh City Line 2 civil works to start — The Ho Chi Minh City Party Committee decided in November 2025 to use the municipal and national budget to complete Line 2. Completion is ...</t>
+          <t>Civil works for the 11.3 km Ho Chi Minh City Metro Line 2 have officially commenced following a groundbreaking ceremony on January 15. The project, now funded by domestic municipal and national budgets after international funding plans were scrapped, is slated for completion in the fourth quarter of 2030.</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>[Urban Development] Financial close allows Ho Chi Minh City Line 2 civil works to start — The Ho Chi Minh City Party Committee decided in November 2025 to use the municipal and national budget to complete Line 2. Completion is ...</t>
+          <t>Công trình dân dụng cho tuyến tàu điện ngầm số 2 tại TP.HCM dài 11,3 km đã chính thức được khởi công vào ngày 15 tháng 1. Dự án sử dụng ngân sách thành phố và quốc gia để triển khai sau khi thay đổi phương án vốn, dự kiến sẽ hoàn thành vào quý IV năm 2030.</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -3984,17 +3984,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City's metro vision: Big plans, slow progress Ho Chi ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
+          <t>호치민시는 교통 체증을 완화하기 위해 야심 찬 메트로 노선망을 계획하고 있으나, 현재 프로젝트 진행이 상당히 지연되고 있습니다. 도시 마스터 플랜에는 도심 교통을 현대화하고 주요 지역을 연결하기 위한 여러 노선이 포함되어 있습니다.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City's metro vision: Big plans, slow progress Ho Chi ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
+          <t>Ho Chi Minh City is planning an ambitious metro network to alleviate traffic congestion, though projects have experienced significant delays. The city's master plan features multiple routes aimed at modernizing urban transport and connecting key districts.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City's metro vision: Big plans, slow progress Ho Chi ... — Construction is scheduled to begin at the end of 2026. The railway will span 1,541 kilometers with a total investment of approximately US$67 ...</t>
+          <t>Thành phố Hồ Chí Minh đang lập kế hoạch cho mạng lưới tàu điện ngầm đầy tham vọng nhằm giảm bớt tình trạng tắc nghẽn giao thông, mặc dù các dự án đang đối mặt với sự chậm trễ đáng kể. Quy hoạch tổng thể của thành phố bao gồm nhiều tuyến đường được thiết kế để hiện đại hóa giao thông đô thị và kết nối các quận trọng điểm.</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4048,17 +4048,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City Metro Ride: An Phu Station to Saigon Centre — ... 2026 Support Me PayPal: https://paypal.me/actionkidyt?locale.x=en_US Cash App: $ ... Bullet Train | Shanghai - Beijing. Solo Solo Travel.</t>
+          <t>이 영상은 타오디엔의 안푸역에서 1군 중심부인 사이공 센터까지 이어지는 호치민 지하철 여정을 담고 있습니다. 도시 개발의 핵심인 메트로 라인을 통해 베트남의 현대화된 대중교통 인프라를 직접 확인할 수 있습니다.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City Metro Ride: An Phu Station to Saigon Centre — ... 2026 Support Me PayPal: https://paypal.me/actionkidyt?locale.x=en_US Cash App: $ ... Bullet Train | Shanghai - Beijing. Solo Solo Travel.</t>
+          <t>This video showcases the journey on the Ho Chi Minh City Metro from An Phu Station in Thao Dien to the Saigon Centre in District 1. It highlights the progress of urban transportation infrastructure connecting vibrant residential areas to the city's commercial heart.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City Metro Ride: An Phu Station to Saigon Centre — ... 2026 Support Me PayPal: https://paypal.me/actionkidyt?locale.x=en_US Cash App: $ ... Bullet Train | Shanghai - Beijing. Solo Solo Travel.</t>
+          <t>Video này ghi lại hành trình đi tàu điện Metro từ ga An Phú tại Thảo Điền đến Saigon Centre tại Quận 1. Đây là minh chứng cho sự phát triển của hạ tầng giao thông đô thị, kết nối các khu dân cư sầm uất với trung tâm kinh tế của thành phố.</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4112,17 +4112,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's infrastructure: Six forces shaping investment in 2026 ... — According to the Ministry of Finance, disbursed foreign direct investment in Vietnam was estimated at US$27.6 billion, up 9 per cent from a year ...</t>
+          <t>베트남은 2030년까지 약 1,500억~2,000억 달러의 인프라 투자 격차를 해소하기 위해 민간 및 외국 자본 유치를 필수 과제로 삼고 있습니다. 2025년 단행된 법적 개혁과 새로운 지도부의 정책은 국영기업(SOE) 및 민간 대기업과의 파트너십을 장려하여 해상 풍력, LNG, 교통망 등 주요 프로젝트의 투자 환경을 강화하고 있습니다.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's infrastructure: Six forces shaping investment in 2026 ... — According to the Ministry of Finance, disbursed foreign direct investment in Vietnam was estimated at US$27.6 billion, up 9 per cent from a year ...</t>
+          <t>Vietnam is prioritizing foreign and private investment to bridge an estimated $150–200 billion infrastructure funding gap through 2030. Driven by new leadership and legislative reforms in 2025, the country is fostering partnerships between international investors, state-owned enterprises, and domestic conglomerates in sectors like renewable energy and logistics.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's infrastructure: Six forces shaping investment in 2026 ... — According to the Ministry of Finance, disbursed foreign direct investment in Vietnam was estimated at US$27.6 billion, up 9 per cent from a year ...</t>
+          <t>Việt Nam đang nỗ lực thu hút vốn đầu tư nước ngoài và tư nhân để lấp đầy khoảng trống tài chính cơ sở hạ tầng ước tính khoảng 150–200 tỷ USD đến năm 2030. Với các cải cách luật pháp năm 2025 và định hướng của ban lãnh đạo mới, Chính phủ khuyến khích hợp tác giữa nhà đầu tư quốc tế với các doanh nghiệp nhà nước và tập đoàn tư nhân trong các lĩnh vực trọng điểm như năng lượng tái tạo và giao thông.</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4176,17 +4176,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's $16B Airport Why Construction Just STOPPED - YouTube — Vietnam's $16 Billion Long Thanh International Airport was supposed to be the "Jewel of Southeast Asia" and a rival to Singapore's Changi.</t>
+          <t>베트남의 160억 달러 규모 롱탄 국제공항 건설 프로젝트가 중단 위기에 처하며 동남아시아의 허브가 되려던 계획에 차질이 생겼습니다. 싱가포르 창이 공항에 도전하려던 이 대규모 인프라 사업은 최근 여러 문제로 인해 난항을 겪고 있습니다.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's $16B Airport Why Construction Just STOPPED - YouTube — Vietnam's $16 Billion Long Thanh International Airport was supposed to be the "Jewel of Southeast Asia" and a rival to Singapore's Changi.</t>
+          <t>Vietnam's $16 billion Long Thanh International Airport project, intended to rival Singapore's Changi Airport, has faced significant construction delays and reported stoppages. This ambitious infrastructure development is struggling to meet its goal of becoming the premier transport hub of Southeast Asia.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's $16B Airport Why Construction Just STOPPED - YouTube — Vietnam's $16 Billion Long Thanh International Airport was supposed to be the "Jewel of Southeast Asia" and a rival to Singapore's Changi.</t>
+          <t>Dự án sân bay quốc tế Long Thành trị giá 16 tỷ USD của Việt Nam đang đối mặt với việc tạm dừng thi công, đe dọa mục tiêu cạnh tranh với sân bay Changi của Singapore. Đây là công trình hạ tầng trọng điểm được kỳ vọng sẽ trở thành trung tâm trung chuyển mới của khu vực Đông Nam Á.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4240,17 +4240,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Transport infrastructure in process of synchronisation — By the end of 2025, Vietnam had 3,345km of main expressways and 458km of interchanges and access roads in operation; it had fully completed and ... (관련: VN-TRAN-2055)</t>
+          <t>베트남 정부는 정체된 인프라 프로젝트를 해결하기 위해 강력한 지침을 내렸으며, 올해 벤룩-롱탄 고속도로와 호치민 제3순환도로 등 주요 도로망이 완공될 예정입니다. 롱탄 국제공항의 상업 운항 시작과 더불어 673억 달러 규모의 남북 고속철도 착공이 계획되어 국가 운송 인프라의 동기화가 가속화되고 있습니다.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Transport infrastructure in process of synchronisation — By the end of 2025, Vietnam had 3,345km of main expressways and 458km of interchanges and access roads in operation; it had fully completed and ... (Related: VN-TRAN-2055)</t>
+          <t>The Vietnamese government is accelerating key infrastructure projects, with the Ben Luc-Long Thanh Expressway and HCMC Ring Road 3 nearing completion this year. Significant milestones include the commencement of operations at Long Thanh International Airport and the groundbreaking of the $67.3 billion North-South high-speed railway.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Transport infrastructure in process of synchronisation — By the end of 2025, Vietnam had 3,345km of main expressways and 458km of interchanges and access roads in operation; it had fully completed and ... (Liên quan: VN-TRAN-2055)</t>
+          <t>Chính phủ Việt Nam đang đẩy nhanh tiến độ các dự án hạ tầng trọng điểm, trong đó cao tốc Bến Lức - Long Thành và Vành đai 3 TP.HCM dự kiến sẽ hoàn thành trong năm nay. Những cột mốc quan trọng bao gồm việc đưa Cảng hàng không quốc tế Long Thành vào khai thác thương mại và khởi công dự án đường sắt tốc độ cao Bắc - Nam trị giá hơn 67,3 tỷ USD.</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4304,17 +4304,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's aviation lifts off with major airport breakthroughs — Landmark infrastructure shaping a new development axis · Fleet expansion and robust market recovery · Toward double-digit growth in 2026. (관련: VN-EV-2030)</t>
+          <t>베트남은 롱타인 국제공항의 기술적 개항과 자빈 국제공항의 물류 허브 개발을 포함한 대규모 항공 인프라 확장을 가속화하고 있습니다. 2025년 역대 최고인 8,350만 명의 승객을 기록했으며, 2026년에는 경제 성장과 규제 완화에 힘입어 이용객이 9,500만 명에 이를 것으로 전망됩니다.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's aviation lifts off with major airport breakthroughs — Landmark infrastructure shaping a new development axis · Fleet expansion and robust market recovery · Toward double-digit growth in 2026. (Related: VN-EV-2030)</t>
+          <t>Vietnam is accelerating its aviation infrastructure with flagship projects like Long Thanh International Airport and the new Gia Binh dual-use airport. The sector achieved a record 83.5 million passengers in 2025 and is projected to grow to 95 million in 2026, supported by fleet expansions and upgraded terminals like Tan Son Nhat T3.</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's aviation lifts off with major airport breakthroughs — Landmark infrastructure shaping a new development axis · Fleet expansion and robust market recovery · Toward double-digit growth in 2026. (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang đẩy mạnh hạ tầng hàng không với các dự án trọng điểm như sân bay quốc tế Long Thành và sân bay Gia Bình, nhằm thúc đẩy kết nối vùng và logistics. Năm 2025, ngành hàng không đạt kỷ lục 83,5 triệu lượt khách và dự kiến sẽ tăng trưởng lên 95 triệu lượt vào năm 2026 nhờ việc mở rộng đội bay và nâng cấp các nhà ga.</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4368,17 +4368,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's largest airport is about to be put into operation - Seetao — The first phase of Vietnam Longcheng International Airport project will be completed and put into operation in the first half of 2026.</t>
+          <t>베트남 동나이성에 위치한 롱타인 국제공항이 2026년 상반기 1단계 개항을 앞두고 있습니다. 한국 희림종합건축사사무소가 설계한 이 공항은 연꽃을 형상화한 디자인과 세계 최대 규모의 대나무 구조물을 특징으로 하며, 최종 완공 시 연간 1억 명의 승객을 수용하는 4F급 허브가 될 전망입니다.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's largest airport is about to be put into operation - Seetao — The first phase of Vietnam Longcheng International Airport project will be completed and put into operation in the first half of 2026.</t>
+          <t>Vietnam's Long Thanh International Airport is nearing the completion of its first phase, scheduled for operation in the first half of 2026. Designed with a lotus-inspired aesthetic and utilizing sustainable bamboo structures, the 4F-level hub aims to handle 100 million passengers annually upon its full completion by 2040.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's largest airport is about to be put into operation - Seetao — The first phase of Vietnam Longcheng International Airport project will be completed and put into operation in the first half of 2026.</t>
+          <t>Sân bay Quốc tế Long Thành tại tỉnh Đồng Nai đang hoàn thiện giai đoạn 1 để dự kiến đi vào hoạt động trong nửa đầu năm 2026. Với thiết kế lấy cảm hứng từ hoa sen và cấu trúc tre bền vững, dự án cấp 4F này đặt mục tiêu phục vụ 100 triệu hành khách mỗi năm khi hoàn thành toàn bộ vào năm 2040.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4432,17 +4432,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's Long Thanh Airport to Launch by 2026 with $16B ... — Vietnam's Long Thanh Airport to Launch by 2026 with $16B Investment ... terminal, VIP terminal, and aviation infrastructure. • Capacity ...</t>
+          <t>베트남 정부는 총 사업비 약 160억 달러 규모의 롱탄 국제공항 건설을 가속화하기 위해 30일 이내에 핵심 계약 체결을 완료하라는 지침을 내렸습니다. 이 프로젝트는 2026년 말 상업 운영 시작을 목표로 하며, 연간 1억 명의 승객을 수용하는 지역 주요 항공 허브로 거듭날 전망입니다.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's Long Thanh Airport to Launch by 2026 with $16B ... — Vietnam's Long Thanh Airport to Launch by 2026 with $16B Investment ... terminal, VIP terminal, and aviation infrastructure. • Capacity ...</t>
+          <t>The Vietnamese government has mandated a 30-day deadline to finalize key contracts for the Long Thanh International Airport, a $16 billion project aimed at starting operations by late 2026. The development is set to transform the region into a major aviation hub with an eventual capacity of 100 million passengers per year.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's Long Thanh Airport to Launch by 2026 with $16B ... — Vietnam's Long Thanh Airport to Launch by 2026 with $16B Investment ... terminal, VIP terminal, and aviation infrastructure. • Capacity ...</t>
+          <t>Chính phủ Việt Nam đã chốt thời hạn 30 ngày để hoàn tất ký kết các hợp đồng then chốt cho dự án sân bay quốc tế Long Thành với tổng vốn đầu tư khoảng 16 tỷ USD. Dự án đặt mục tiêu bắt đầu vận hành khai thác vào cuối năm 2026 và hướng tới công suất 100 triệu hành khách mỗi năm.</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam PM presses for Long Thanh airport phase 1 completion by ... — Long Thanh International Airport is a national key project spanning about 5,000 hectares, with a total estimated investment of more than VND336.</t>
+          <t>베트남 팜 민 찐 총리는 롱탄 국제공항 1단계 사업을 2026년 상반기까지 완료할 것을 지시했습니다. 약 42억 달러가 투입된 이 프로젝트는 연간 2,500만 명의 승객을 수용하는 것을 목표로 하며, 스마트 및 친환경 기술이 도입될 예정입니다.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam PM presses for Long Thanh airport phase 1 completion by ... — Long Thanh International Airport is a national key project spanning about 5,000 hectares, with a total estimated investment of more than VND336.</t>
+          <t>Vietnam's Prime Minister Pham Minh Chinh has directed that Phase 1 of the Long Thanh International Airport be completed by the first half of 2026. This $4.2 billion phase aims to handle 25 million passengers annually and will feature advanced biometric systems and smart infrastructure.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam PM presses for Long Thanh airport phase 1 completion by ... — Long Thanh International Airport is a national key project spanning about 5,000 hectares, with a total estimated investment of more than VND336.</t>
+          <t>Thủ tướng Phạm Minh Chính đã chỉ đạo hoàn thành giai đoạn 1 của dự án Cảng hàng không quốc tế Long Thành trong nửa đầu năm 2026. Với tổng vốn đầu tư giai đoạn này khoảng 109 nghìn tỷ đồng, sân bay được kỳ vọng sẽ phục vụ 25 triệu lượt khách mỗi năm và trở thành trung tâm hàng không hiện đại của khu vực.</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's $16B AIRPORT MEGA PROJECT Could Change Asia ... — ... infrastructure move yet—and why the rest of Asia is watching ... HUGE Vietnam Visa Update 2026 NOBODY Expected (WHY?!) Duong Global ...</t>
+          <t>베트남은 아시아 항공 지형을 바꿀 수 있는 160억 달러 규모의 초대형 신공항 프로젝트를 추진하고 있습니다. 이 메가 프로젝트는 글로벌 항공 시장에 막대한 영향을 미칠 것으로 예상됩니다.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's $16B AIRPORT MEGA PROJECT Could Change Asia ... — ... infrastructure move yet—and why the rest of Asia is watching ... HUGE Vietnam Visa Update 2026 NOBODY Expected (WHY?!) Duong Global ...</t>
+          <t>Vietnam is moving forward with a massive $16 billion mega airport project aimed at reshaping Asia's aviation landscape. This infrastructure development is expected to have a significant global impact and potentially change regional travel forever.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's $16B AIRPORT MEGA PROJECT Could Change Asia ... — ... infrastructure move yet—and why the rest of Asia is watching ... HUGE Vietnam Visa Update 2026 NOBODY Expected (WHY?!) Duong Global ...</t>
+          <t>Việt Nam đang đẩy mạnh dự án siêu sân bay trị giá 16 tỷ USD có khả năng thay đổi vĩnh viễn bản đồ hàng không châu Á. Dự án hạ tầng khổng lồ này được dự báo sẽ tạo ra tác động lớn trên phạm vi toàn cầu.</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Viet Nam approves investment policy for Gia Binh International Airport — The airport will be completed by the end of 2026, with trial operations beginning in February 2027. Covering nearly 1,960 hectares, the airport ...</t>
+          <t>베트남 박닌성에 위치한 가빈(Gia Binh) 국제공항 건설 사업이 투자 승인을 받아 본격화되었습니다. 이 공항은 2026년 말 완공되어 2027년 2월 시운전을 시작할 예정이며, 연간 3,000만 명의 승객과 160만 톤의 화물을 처리하는 북부 지역의 주요 항공 허브가 될 것으로 기대됩니다.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Viet Nam approves investment policy for Gia Binh International Airport — The airport will be completed by the end of 2026, with trial operations beginning in February 2027. Covering nearly 1,960 hectares, the airport ...</t>
+          <t>Vietnam has approved the investment policy for Gia Binh International Airport in Bac Ninh province, aiming for completion by the end of 2026. This dual-use facility is designed to handle 30 million passengers and 1.6 million tons of cargo annually by 2030, serving as a strategic logistics and transport hub near Hanoi.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Viet Nam approves investment policy for Gia Binh International Airport — The airport will be completed by the end of 2026, with trial operations beginning in February 2027. Covering nearly 1,960 hectares, the airport ...</t>
+          <t>Việt Nam đã phê duyệt chính sách đầu tư cho dự án Cảng hàng không quốc tế Gia Bình tại tỉnh Bắc Ninh, dự kiến hoàn thành vào cuối năm 2026. Sân bay lưỡng dụng này có công suất thiết kế đạt 30 triệu hành khách và 1,6 triệu tấn hàng hóa mỗi năm vào giai đoạn 2021-2030, tạo động lực phát triển cho vùng kinh tế phía Bắc.</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -4684,17 +4684,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Planning &amp; Bidding Vietnam Aviation Infrastructure — Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025.</t>
+          <t>2025년 기준 베트남의 주요 공항 건설 프로젝트, 입찰 프로세스 및 신규 전략 제안에 대한 통합 데이터입니다. 미래에셋증권 베트남 법인이 교통부와 국가 공항망 마스터플랜을 분석하여 정리한 자료입니다.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Planning &amp; Bidding Vietnam Aviation Infrastructure — Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025.</t>
+          <t>This report provides consolidated data on key airport projects under construction, bidding activities, and strategic proposals in Vietnam as of 2025. It is based on Mirae Asset Securities Vietnam's analysis of Ministry of Transport data and the National Airport Network Master Plan.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Planning &amp; Bidding Vietnam Aviation Infrastructure — Consolidated data on key airport projects under construction, active bidding processes, and new strategic proposals as of 2025.</t>
+          <t>Báo cáo tổng hợp dữ liệu về các dự án sân bay trọng điểm đang xây dựng, quá trình đấu thầu và các đề xuất chiến lược mới tại Việt Nam tính đến năm 2025. Thông tin được Mirae Asset Securities Vietnam phân tích và tổng hợp từ Bộ Giao thông Vận tải cùng Quy hoạch tổng thể hệ thống cảng hàng không toàn quốc.</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -4748,17 +4748,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Decree 29/2026: Vietnam Operationalizes Its First Carbon Trading ... — At COP26, the country pledged to reach net-zero emissions by 2050 and reduce methane emissions by 30 percent by 2030 compared to 2020 levels. (관련: VN-EV-2030)</t>
+          <t>베트남은 시행령 제29/2026/ND-CP호를 통해 국가 최초의 탄소 배출권 거래소 운영 프레임워크를 구축하고 환경 인프라를 본격화했습니다. 2025-2026년 시범 기간 동안 화력 발전소, 철강 및 시멘트 공장을 대상으로 온실가스 배출 할당량을 부여하여 2050년 넷제로 목표 달성을 추진합니다.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Decree 29/2026: Vietnam Operationalizes Its First Carbon Trading ... — At COP26, the country pledged to reach net-zero emissions by 2050 and reduce methane emissions by 30 percent by 2030 compared to 2020 levels. (Related: VN-EV-2030)</t>
+          <t>Vietnam has operationalized its first domestic carbon trading exchange under Decree 29/2026/ND-CP, integrating emission quotas into its securities market infrastructure. The 2025-2026 pilot phase targets high-emission sectors like power, steel, and cement to support the country's VN-EV-2030 and net-zero climate commitments.</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Decree 29/2026: Vietnam Operationalizes Its First Carbon Trading ... — At COP26, the country pledged to reach net-zero emissions by 2050 and reduce methane emissions by 30 percent by 2030 compared to 2020 levels. (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đã chính thức vận hành sàn giao dịch tín chỉ carbon đầu tiên thông qua Nghị định 29/2026/NĐ-CP, tích hợp hạn ngạch phát thải vào hạ tầng thị trường chứng khoán. Trong giai đoạn thí điểm 2025-2026, chính phủ phân bổ hạn ngạch cho các nhà máy nhiệt điện, thép và xi măng nhằm hiện thực hóa mục tiêu giảm phát thải khí nhà kính và Net Zero vào năm 2050.</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -4812,17 +4812,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Fulfilling climate commitments at COP26: Vietnam's comprehensive ... — At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050 - a historic milestone underscoring its ... (관련: VN-EV-2030)</t>
+          <t>베트남은 COP26에서 약속한 2050년 넷제로 목표를 달성하기 위해 에너지, 농업, 산림 등 전 분야에 걸친 포괄적인 실행 계획을 추진하고 있습니다. 제8차 전력개발계획(PDP8)을 통해 재생 에너지를 확대하고 석탄 의존도를 낮추는 인프라 전환과 더불어 저탄소 농업 및 폐기물 에너지화 기술을 적극 도입하고 있습니다.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Fulfilling climate commitments at COP26: Vietnam's comprehensive ... — At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050 - a historic milestone underscoring its ... (Related: VN-EV-2030)</t>
+          <t>Vietnam is implementing a comprehensive cross-sector strategy to fulfill its COP26 commitment of reaching net-zero emissions by 2050. Key infrastructure initiatives include transitioning to renewable energy under Power Development Plan VIII, scaling up low-emission rice cultivation in the Mekong Delta, and adopting waste-to-energy technologies.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Fulfilling climate commitments at COP26: Vietnam's comprehensive ... — At COP26, Vietnam raised its ambition with the landmark pledge to achieve net-zero emissions by 2050 - a historic milestone underscoring its ... (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang tích cực triển khai các cam kết tại COP26 thông qua chiến lược toàn diện nhằm đạt phát thải ròng bằng "0" vào năm 2050. Các hành động cụ thể bao gồm chuyển đổi năng lượng tái tạo theo Quy hoạch điện VIII, phát triển một triệu héc-ta lúa chất lượng cao phát thải thấp và thúc đẩy các mô hình kinh tế tuần hoàn trên toàn quốc.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -4876,17 +4876,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Achieving net-zero emissions by 2050 is a political mission of Vietnam — Bringing Vietnam to net-zero emissions by 2050 is not merely a promise but a commitment to action - a political mission of the nation and a ... (관련: VN-EV-2030)</t>
+          <t>베트남 팜 민 찐 총리는 2050년 탄소 중립 달성이 국가적 정치 임무임을 강조하며, 이를 위한 제도적 개선과 탄소 시장 구축을 촉구했습니다. 특히 탄소 배출권 할당 시범 운영과 함께 전기차 및 친환경 에너지 기반의 대중교통 시스템 구축 등 녹색 교통 인프라 확대를 지시했습니다.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Achieving net-zero emissions by 2050 is a political mission of Vietnam — Bringing Vietnam to net-zero emissions by 2050 is not merely a promise but a commitment to action - a political mission of the nation and a ... (Related: VN-EV-2030)</t>
+          <t>Prime Minister Pham Minh Chinh reaffirmed Vietnam's commitment to achieving Net Zero by 2050, labeling it a core political mission that drives sustainable development and international integration. The government is accelerating the development of a domestic carbon market and prioritizing green infrastructure, specifically the electrification of public transport and the transition to clean energy vehicles (VN-EV-2030).</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Achieving net-zero emissions by 2050 is a political mission of Vietnam — Bringing Vietnam to net-zero emissions by 2050 is not merely a promise but a commitment to action - a political mission of the nation and a ... (Liên quan: VN-EV-2030)</t>
+          <t>Thủ tướng Phạm Minh Chính khẳng định đạt phát thải ròng bằng 0 vào năm 2050 là nhiệm vụ chính trị trọng tâm nhằm phát triển đất nước bền vững và tự chủ. Chính phủ sẽ đẩy mạnh thị trường carbon nội bộ và yêu cầu các địa phương tiên phong phát triển hệ thống giao thông công cộng chạy bằng điện và năng lượng xanh.</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -4936,17 +4936,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Viet Nam - Policies &amp; action | Climate Action Tracker — Viet Nam's emissions under current policies will reach around 686–722 MtCO2e in 2030 (excl. LULUCF) whereas a 1.5˚C fair share pathway is 344 MtCO2e in 2030. (관련: VN-CARBON-2050)</t>
+          <t>베트남은 2050년 넷제로 목표를 달성하기 위해 제8차 전력개발계획(PDP8) 및 국가 기후변화 전략을 수립하고 에너지 인프라를 대대적으로 개편하고 있습니다. 석탄 화력 발전소를 2050년까지 단계적으로 폐쇄하는 동시에 태양광, 해상 풍력 등 재생 에너지 비중을 대폭 확대하고 전력망 현대화에 집중하고 있습니다.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Viet Nam - Policies &amp; action | Climate Action Tracker — Viet Nam's emissions under current policies will reach around 686–722 MtCO2e in 2030 (excl. LULUCF) whereas a 1.5˚C fair share pathway is 344 MtCO2e in 2030. (Related: VN-CARBON-2050)</t>
+          <t>Vietnam is overhaulng its energy infrastructure through the Power Development Plan 8 (PDP8) to achieve net-zero emissions by 2050. The strategy involves phasing out coal power by 2050 while rapidly scaling up solar and offshore wind capacity alongside critical grid upgrades supported by the Just Energy Transition Partnership (JETP).</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Viet Nam - Policies &amp; action | Climate Action Tracker — Viet Nam's emissions under current policies will reach around 686–722 MtCO2e in 2030 (excl. LULUCF) whereas a 1.5˚C fair share pathway is 344 MtCO2e in 2030. (Liên quan: VN-CARBON-2050)</t>
+          <t>Việt Nam đang triển khai Quy hoạch điện VIII (PDP8) và Chiến lược quốc gia về biến đổi khí hậu để hướng tới mục tiêu phát thải ròng bằng 0 vào năm 2050. Các kế hoạch tập trung vào việc loại bỏ dần điện than vào năm 2050, đẩy mạnh phát triển năng lượng tái tạo như điện gió ngoài khơi và hiện đại hóa hệ thống lưới điện truyền tải.</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5000,17 +5000,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Roadmap for Vietnam's carbon exchange | NetZero.VN — To realize its net-zero by 2050 target, Vietnam is currently promoting a wide range of emission reduction projects across industrial production, ...</t>
+          <t>베트남 정부는 2050년 넷제로 목표 달성을 위해 국내 탄소 거래소 설립에 관한 시행령 제29/2026/ND-CP호를 공표했습니다. 이 거래소는 2026년 말 공식 운영을 시작할 예정이며, 기업들의 저탄소 기술 투자 유도와 국제 탄소 시장 연결을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Roadmap for Vietnam's carbon exchange | NetZero.VN — To realize its net-zero by 2050 target, Vietnam is currently promoting a wide range of emission reduction projects across industrial production, ...</t>
+          <t>The Vietnamese government issued Decree No. 29/2026/ND-CP to establish a domestic carbon exchange, supporting the country's goal of achieving net-zero emissions by 2050. The exchange is expected to begin official operations by the end of 2026, providing a transparent platform for trading emission allowances and carbon credits.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Roadmap for Vietnam's carbon exchange | NetZero.VN — To realize its net-zero by 2050 target, Vietnam is currently promoting a wide range of emission reduction projects across industrial production, ...</t>
+          <t>Chính phủ Việt Nam đã ban hành Nghị định số 29/2026/NĐ-CP về sàn giao dịch tín chỉ carbon trong nước nhằm hiện thực hóa mục tiêu phát thải ròng bằng 0 vào năm 2050. Sàn giao dịch dự kiến sẽ chính thức đi vào vận hành từ cuối năm 2026, tạo nền tảng minh bạch để các doanh nghiệp trao đổi hạn ngạch phát thải và tín chỉ carbon.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5060,17 +5060,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Reporting on Vietnam's Pathways to Net Zero — The government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. (관련: VN-CARBON-2050)</t>
+          <t>베트남 정부는 2050년까지 탄소 중립을 달성하기 위한 '국가 기후 변화 전략'을 수립하고 재생 에너지 비중을 확대하고 있습니다. 이에 따라 Internews의 지구 저널리즘 네트워크(EJN)는 현지 언론인의 에너지 전환 보도 역량을 강화하기 위한 교육 및 지원 프로젝트를 운영하고 있습니다.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Reporting on Vietnam's Pathways to Net Zero — The government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. (Related: VN-CARBON-2050)</t>
+          <t>The Vietnamese government has launched a National Climate Change Strategy to reach net-zero emissions by 2050, focusing on increasing renewable energy and cutting land-use emissions. Internews’ Earth Journalism Network (EJN) is supporting this transition by providing training, grants, and mentorship to local journalists to improve the quality of reporting on Vietnam's energy pathways.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Reporting on Vietnam's Pathways to Net Zero — The government of Vietnam approved a National Climate Change Strategy on 26 July 2022 to meet its pledge to become a net-zero carbon emissions country by 2050. (Liên quan: VN-CARBON-2050)</t>
+          <t>Chính phủ Việt Nam đã phê duyệt Chiến lược quốc gia về biến đổi khí hậu nhằm đạt mục tiêu phát thải ròng bằng 0 vào năm 2050 thông qua chuyển đổi năng lượng và bảo vệ rừng. Dự án của Mạng lưới Báo chí Trái đất (EJN) đang hỗ trợ các phóng viên trong nước nâng cao kỹ năng truyền thông và kiến thức chuyên môn để phản ánh lộ trình tiến tới Net Zero của quốc gia.</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5124,17 +5124,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's 2050 Net-Zero Target Represents a $2.4 Trillion Opportunity — In this net-zero pathway, three drivers account for 78% of Vietnam's emissions abatement through to mid-century: clean power, carbon capture and ...</t>
+          <t>블룸버그NEF 보고서에 따르면 베트남이 2050년 넷제로 목표를 달성하기 위해서는 2.4조 달러 규모의 투자가 필요하며, 이는 재생 에너지와 탄소 포집 기술의 급격한 확대를 동반해야 합니다. 특히 태양광 및 풍력 발전은 2026년까지 전력 부문의 탄소 배출 정점을 달성하는 데 핵심적인 역할을 할 것으로 전망됩니다.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's 2050 Net-Zero Target Represents a $2.4 Trillion Opportunity — In this net-zero pathway, three drivers account for 78% of Vietnam's emissions abatement through to mid-century: clean power, carbon capture and ...</t>
+          <t>According to a BloombergNEF report, Vietnam requires $2.4 trillion in investment to reach its 2050 net-zero target, necessitating a rapid scale-up of renewable energy and carbon capture technologies. The transition focuses on peaking power sector emissions by 2026 through massive solar and wind deployment while electrifying the transport sector by 2029.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's 2050 Net-Zero Target Represents a $2.4 Trillion Opportunity — In this net-zero pathway, three drivers account for 78% of Vietnam's emissions abatement through to mid-century: clean power, carbon capture and ...</t>
+          <t>Báo cáo của BloombergNEF cho thấy Việt Nam cần huy động 2,4 nghìn tỷ USD đầu tư để đạt mục tiêu phát thải ròng bằng không vào năm 2050 thông qua việc đẩy mạnh năng lượng tái tạo và xe điện. Lộ trình này dự kiến giúp phát thải ngành điện đạt đỉnh vào năm 2026 và thúc đẩy tiềm năng trở thành trung tâm sản xuất xanh cho các tập đoàn đa quốc gia.</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5188,17 +5188,17 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam's shift to green growth | Vietnam Today - YouTube — Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic ... (관련: VN-EV-2030)</t>
+          <t>베트남은 COP26에서 2050년까지 탄소 중립을 달성하겠다고 선언하며 경제 구조를 녹색 성장으로 전환하고 있습니다. 이러한 변화는 환경 및 기후 분야의 인프라 구축과 지속 가능한 발전을 촉진하는 중요한 계기가 되었습니다.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam's shift to green growth | Vietnam Today - YouTube — Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic ... (Related: VN-EV-2030)</t>
+          <t>Vietnam is fundamentally shifting its economic trajectory toward green growth following its COP26 commitment to reach net-zero emissions by 2050. This transition highlights a strategic focus on climate-resilient infrastructure and sustainable development within the Environment and Climate sector.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam's shift to green growth | Vietnam Today - YouTube — Việt Nam's commitment to achieving net-zero emissions by 2050, announced at COP26, has triggered a fundamental shift in its economic ... (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang chuyển đổi mạnh mẽ lộ trình kinh tế sang hướng tăng trưởng xanh sau cam kết đạt phát thải ròng bằng 0 vào năm 2050 tại COP26. Sự thay đổi này thúc đẩy phát triển hạ tầng bền vững và các giải pháp thích ứng với biến đổi khí hậu theo định hướng kế hoạch VN-EV-2030.</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5252,17 +5252,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Net-zero emissions by 2050: Vietnam's action-driven commitment — The ministry is also preparing Vietnam's updated Nationally Determined Contribution for 2026-2035, known as NDC 3.0, with flexible emissions ...</t>
+          <t>베트남은 2050년까지 탄소 중립(Net-Zero) 달성을 단순한 외교적 약속이 아닌 국가적 정치 과제로 설정하고, 전기차 보급 확대 및 녹색 금융 활성화를 추진하고 있습니다. 팜 민 찐 총리는 이를 위해 제도 개선, 녹색 금융 동원, 기술 이전 가속화 등 5대 우선순위를 발표하며 지속 가능한 발전을 강조했습니다.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Net-zero emissions by 2050: Vietnam's action-driven commitment — The ministry is also preparing Vietnam's updated Nationally Determined Contribution for 2026-2035, known as NDC 3.0, with flexible emissions ...</t>
+          <t>Vietnam has reaffirmed its commitment to achieving net-zero emissions by 2050 as a core political mission, focusing on green growth and energy transition across sectors like transport and agriculture. Prime Minister Pham Minh Chinh outlined key priorities including institutional improvements, mobilizing green finance, and accelerating technology transfer to drive sustainable development.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Net-zero emissions by 2050: Vietnam's action-driven commitment — The ministry is also preparing Vietnam's updated Nationally Determined Contribution for 2026-2035, known as NDC 3.0, with flexible emissions ...</t>
+          <t>Việt Nam khẳng định mục tiêu đạt phát thải ròng bằng 0 vào năm 2050 không chỉ là lời hứa ngoại giao mà là một nhiệm vụ chính trị gắn liền với phát triển xanh và bền vững. Thủ tướng Phạm Minh Chính đã nêu rõ 5 ưu tiên chính gồm hoàn thiện thể chế, huy động tài chính xanh, chuyển giao công nghệ, quản trị thông minh và phát triển nguồn nhân lực.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>[Water Resources] ℹ The Mekong Flood and Drought Forecast ... — #Laos is currently experiencing significant flooding due to rising water levels in the #MekongRiver and its tributaries, exacerbated by ... (관련: VN-WAT-2050, VN-EV-2030)</t>
+          <t>ℹ The Mekong Flood and Drought Forecast ...</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>[Water Resources] ℹ The Mekong Flood and Drought Forecast ... — #Laos is currently experiencing significant flooding due to rising water levels in the #MekongRiver and its tributaries, exacerbated by ... (Related: VN-WAT-2050, VN-EV-2030)</t>
+          <t>ℹ The Mekong Flood and Drought Forecast ...</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>[Water Resources] ℹ The Mekong Flood and Drought Forecast ... — #Laos is currently experiencing significant flooding due to rising water levels in the #MekongRiver and its tributaries, exacerbated by ... (Liên quan: VN-WAT-2050, VN-EV-2030)</t>
+          <t>ℹ The Mekong Flood and Drought Forecast ...</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5380,17 +5380,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Floods in Vietnam: Will rising waters tame the Rising Dragon? — Vietnam faces mounting flood risk as climate change, land subsidence, and hydropower infrastructure combine with record typhoon activity.</t>
+          <t>베트남의 급격한 경제 성장과 수력 발전소 네트워크는 퇴적물 차단과 유량 변화를 유발하여 홍수 위험을 심화시키고 있습니다. 특히 호아빈 댐과 같은 전력 인프라는 하류 지역의 토양 보충을 방해하고 비상 방류 시 홍수 피해를 가중시키는 주요 요인으로 지목되었습니다.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Floods in Vietnam: Will rising waters tame the Rising Dragon? — Vietnam faces mounting flood risk as climate change, land subsidence, and hydropower infrastructure combine with record typhoon activity.</t>
+          <t>Vietnam's rapid economic development and dense hydropower network are increasing flood risks through sediment trapping and altered water flows. Key energy infrastructure, such as the Hoa Binh Dam, contributes to downstream vulnerability by blocking essential sediment delivery and exacerbating floods during emergency water releases.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Floods in Vietnam: Will rising waters tame the Rising Dragon? — Vietnam faces mounting flood risk as climate change, land subsidence, and hydropower infrastructure combine with record typhoon activity.</t>
+          <t>Sự phát triển kinh tế nhanh chóng và mạng lưới thủy điện dày đặc tại Việt Nam đang làm tăng nguy cơ lũ lụt thông qua việc bẫy trầm tích và thay đổi dòng chảy. Các cơ sở hạ tầng năng lượng như đập Hòa Bình đã góp phần làm trầm trọng thêm tình trạng ngập lụt ở hạ lưu do ngăn chặn bồi đắp phù sa và xả lũ khẩn cấp trong các đợt thiên tai.</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>[Water Resources] [PDF] Cumulative impact dams and climate change on the hydrology of the ... — More than 1,000 hydropower and irrigation reservoirs/ponds have been built in the. Mekong basin, and another 350 hydropower and irrigation dams are proposed. (관련: VN-WAT-2050)</t>
+          <t>[PDF] Cumulative impact dams and climate change on the hydrology of the ...</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>[Water Resources] [PDF] Cumulative impact dams and climate change on the hydrology of the ... — More than 1,000 hydropower and irrigation reservoirs/ponds have been built in the. Mekong basin, and another 350 hydropower and irrigation dams are proposed. (Related: VN-WAT-2050)</t>
+          <t>[PDF] Cumulative impact dams and climate change on the hydrology of the ...</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>[Water Resources] [PDF] Cumulative impact dams and climate change on the hydrology of the ... — More than 1,000 hydropower and irrigation reservoirs/ponds have been built in the. Mekong basin, and another 350 hydropower and irrigation dams are proposed. (Liên quan: VN-WAT-2050)</t>
+          <t>[PDF] Cumulative impact dams and climate change on the hydrology of the ...</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>[Water Resources] Drought and salinity expected near average levels this dry season — Drought and water shortages during the 2025-2026 dry season are expected to occur mainly in localized areas, while saltwater intrusion in ... (관련: VN-EV-2030)</t>
+          <t>Drought and salinity expected near average levels this dry season</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>[Water Resources] Drought and salinity expected near average levels this dry season — Drought and water shortages during the 2025-2026 dry season are expected to occur mainly in localized areas, while saltwater intrusion in ... (Related: VN-EV-2030)</t>
+          <t>Drought and salinity expected near average levels this dry season</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>[Water Resources] Drought and salinity expected near average levels this dry season — Drought and water shortages during the 2025-2026 dry season are expected to occur mainly in localized areas, while saltwater intrusion in ... (Liên quan: VN-EV-2030)</t>
+          <t>Drought and salinity expected near average levels this dry season</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>[Water Resources] Mekong Flood and Drought Forecast Channel on 13 January 2026 — ... Vietnamese) ☀️Drought forecast: Mild drought ... Water levels updates: ⬆️Water levels from Chiang ... (관련: VN-WAT-2050, VN-EV-2030)</t>
+          <t>메콩강 위원회(MRC)는 2026년 1월 13일자 메콩강 홍수 및 가뭄 예측 보고서를 발표했습니다. 이 보고서는 베트남의 수자원 인프라 관리 및 VN-WAT-2050 계획에 필수적인 하류 지역의 수위 변화와 기상 정보를 제공합니다.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>[Water Resources] Mekong Flood and Drought Forecast Channel on 13 January 2026 — ... Vietnamese) ☀️Drought forecast: Mild drought ... Water levels updates: ⬆️Water levels from Chiang ... (Related: VN-WAT-2050, VN-EV-2030)</t>
+          <t>The Mekong River Commission released its flood and drought forecast for January 13, 2026, focusing on water levels across the Mekong basin. This data supports Vietnam's water resource management and infrastructure planning under frameworks like VN-WAT-2050 and VN-EV-2030.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>[Water Resources] Mekong Flood and Drought Forecast Channel on 13 January 2026 — ... Vietnamese) ☀️Drought forecast: Mild drought ... Water levels updates: ⬆️Water levels from Chiang ... (Liên quan: VN-WAT-2050, VN-EV-2030)</t>
+          <t>Ủy ban Sông Mê Công đã công bố bản tin dự báo lũ và hạn hán ngày 13 tháng 1 năm 2026 cho khu vực hạ lưu sông. Thông tin này đóng vai trò quan trọng trong việc vận hành cơ sở hạ tầng tài nguyên nước của Việt Nam theo các quy hoạch VN-WAT-2050 và VN-EV-2030.</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -5632,17 +5632,17 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>[Water Resources] Mekong Delta races to respond to peak flood levels — Water levels on the Mekong River are rising rapidly and expected to peak in the coming days, according to meteorological agencies. (관련: VN-EV-2030)</t>
+          <t>메콩강의 수위가 빠르게 상승하고 있으며 앞으로 며칠 내에 정점에 도달할 것으로 예보되었습니다. 남부 지역 당국은 시장, 도로, 주거 지역 침수와 같은 피해를 줄이기 위해 경고 발령과 재해 방지 조치를 신속하게 시행하고 있습니다.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>[Water Resources] Mekong Delta races to respond to peak flood levels — Water levels on the Mekong River are rising rapidly and expected to peak in the coming days, according to meteorological agencies. (Related: VN-EV-2030)</t>
+          <t>Water levels on the Mekong River are rising rapidly and are forecast to peak between October 8 and 10, causing severe flooding in Can Tho City and other parts of the Mekong Delta. Local authorities are issuing flood warnings and implementing emergency measures to protect vulnerable infrastructure and residents.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>[Water Resources] Mekong Delta races to respond to peak flood levels — Water levels on the Mekong River are rising rapidly and expected to peak in the coming days, according to meteorological agencies. (Liên quan: VN-EV-2030)</t>
+          <t>Mực nước sông Mê Kông đang tăng nhanh và dự báo sẽ đạt đỉnh từ ngày 8 đến 10 tháng 10, gây ngập lụt nghiêm trọng tại thành phố Cần Thơ và các khu vực khác ở đồng bằng sông Cửu Long. Chính quyền địa phương đang triển khai nhiều biện pháp cảnh báo ngập lụt và bảo vệ cơ sở hạ tầng, cư dân khu vực dễ bị ảnh hưởng.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -5696,17 +5696,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City Charts A New Path For Urban ... — The city is piloting a new approach: integrating digital transformation, green growth, and modern finance to restructure urban space, ...</t>
+          <t>호치민시는 디지털 전환과 녹색 성장을 통합한 '이중 전환' 전략을 통해 2050년까지 저탄소 메가시티로의 도약을 목표로 하고 있습니다. 도시는 인공지능(AI), 반도체 등 하이테크 산업 육성과 국제금융센터(IFC) 구축을 포함한 5대 핵심 발전축을 기반으로 다극 성장 모델을 추진하고 있습니다.</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City Charts A New Path For Urban ... — The city is piloting a new approach: integrating digital transformation, green growth, and modern finance to restructure urban space, ...</t>
+          <t>Ho Chi Minh City is implementing a dual transformation strategy that integrates digital and green growth to become a low-carbon mega-city by 2050. The development focuses on five strategic pillars, including high-tech industries like AI and semiconductors, and the establishment of an International Financial Center to enhance global competitiveness.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City Charts A New Path For Urban ... — The city is piloting a new approach: integrating digital transformation, green growth, and modern finance to restructure urban space, ...</t>
+          <t>Thành phố Hồ Chí Minh đang triển khai chiến lược chuyển đổi kép, kết hợp giữa chuyển đổi số và tăng trưởng xanh để trở thành siêu đô thị phát thải thấp vào năm 2050. Thành phố tập trung vào mô hình tăng trưởng đa cực với 5 trụ cột chiến lược, bao gồm phát triển công nghệ cao, trung tâm tài chính quốc tế và hiện đại hóa quản trị đô thị.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -5760,17 +5760,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Ho Chi Minh City outlines roadmap of new urban development — To reach double-digit growth, Ho Chi Minh City is adding three new pillars, including VIFC-HCM, urban railways and a Free Trade Zone. (관련: VN-EV-2030)</t>
+          <t>호치민시는 메트로 2호선 건설과 국제금융센터(VIFC-HCM) 및 자유무역지대 조성을 포함한 새로운 도시 개발 로드맵을 발표했습니다. 이 계획은 행정 구역 통합과 교통 인프라 확충을 통해 2050년까지 인구 2,000만 명 규모의 글로벌 메가시티로 도약하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Ho Chi Minh City outlines roadmap of new urban development — To reach double-digit growth, Ho Chi Minh City is adding three new pillars, including VIFC-HCM, urban railways and a Free Trade Zone. (Related: VN-EV-2030)</t>
+          <t>Ho Chi Minh City has unveiled a strategic roadmap focusing on three new pillars: a financial center, urban railways including Metro Line No. 2, and a Free Trade Zone. The plan aims to transform the city into a regional megacity by 2050, leveraging integrated transport networks and administrative consolidation to drive double-digit economic growth.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Ho Chi Minh City outlines roadmap of new urban development — To reach double-digit growth, Ho Chi Minh City is adding three new pillars, including VIFC-HCM, urban railways and a Free Trade Zone. (Liên quan: VN-EV-2030)</t>
+          <t>Thành phố Hồ Chí Minh đã công bố lộ trình phát triển đô thị mới với ba trụ cột chiến lược gồm Trung tâm Tài chính Quốc tế, đường sắt đô thị (tuyến Metro số 2) và Khu thương mại tự do. Kế hoạch này hướng tới mục tiêu đưa thành phố trở thành siêu đô thị khu vực vào năm 2050 thông qua việc kết nối hạ tầng giao thông đồng bộ và cải cách quản trị.</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -5824,17 +5824,17 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>[Urban Development] Satellite cities to be centres of real estate development for ... — The urbanisation rate is projected at 50 per cent, equivalent to 51 million urban residents, while the middle class could expand to 75 per cent ... (관련: VN-EV-2030)</t>
+          <t>베트남은 490억 달러 규모의 인프라 투자를 통해 남북 고속도로와 롱타 Thành 국제공항 등을 건설하며 도시 지형을 재편하고 있습니다. 새빌스 베트남은 급격한 도시화와 위성 도시의 성장이 향후 10년간 부동산 개발의 핵심이 될 것으로 전망했습니다.</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>[Urban Development] Satellite cities to be centres of real estate development for ... — The urbanisation rate is projected at 50 per cent, equivalent to 51 million urban residents, while the middle class could expand to 75 per cent ... (Related: VN-EV-2030)</t>
+          <t>Vietnam is investing US$49 billion in nationwide infrastructure, including major expressways and airports, to redefine its urban landscape and connect emerging growth hubs. Savills Vietnam predicts that satellite cities and rapid urbanization will drive the real estate market over the next decade, supported by a growing middle class and high-tech industrial shifts.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>[Urban Development] Satellite cities to be centres of real estate development for ... — The urbanisation rate is projected at 50 per cent, equivalent to 51 million urban residents, while the middle class could expand to 75 per cent ... (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang triển khai 49 tỷ USD vào hạ tầng chiến lược như cao tốc Bắc-Nam và sân bay Long Thành để kết nối các hành lang phát triển kinh tế. Savills dự báo các đô thị vệ tinh sẽ trở thành trọng tâm phát triển bất động sản trong thập kỷ tới nhờ tốc độ đô thị hóa nhanh và sự gia tăng của tầng lớp trung lưu.</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -5888,17 +5888,17 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City moves to real smart urban governance in ... — Ho Chi Minh City is building a governance model where real-time data, AI and digital twins guide decisions and reshape daily urban life.</t>
+          <t>호치민시는 2026년까지 데이터 표준화와 AI 기술을 활용하여 진정한 스마트 도시 거버넌스로 전환할 계획입니다. 시민 앱과 스마트 도시 운영 센터를 통해 교통 체증 및 홍수 예측 등 실시간 데이터 기반의 공공 서비스를 제공하고자 합니다.</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City moves to real smart urban governance in ... — Ho Chi Minh City is building a governance model where real-time data, AI and digital twins guide decisions and reshape daily urban life.</t>
+          <t>By 2026, Ho Chi Minh City aims to transition to a smart urban governance model by standardizing data and integrating AI and Digital Twin technology. The initiative focuses on enhancing public services through the Citizen App and a centralized Operations Center to manage traffic, flooding, and administrative procedures in real-time.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City moves to real smart urban governance in ... — Ho Chi Minh City is building a governance model where real-time data, AI and digital twins guide decisions and reshape daily urban life.</t>
+          <t>Đến năm 2026, TP.HCM sẽ tập trung chuẩn hóa dữ liệu và ứng dụng AI để vận hành hệ thống quản trị đô thị thông minh thực thụ. Thành phố hướng tới việc chuyển đổi dịch vụ công từ "xử lý hồ sơ" sang "phục vụ nhu cầu" thông qua Ứng dụng Công dân và Trung tâm Điều hành Đô thị Thông minh.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -5952,17 +5952,17 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam's Ho Chi Minh City adopts multi-center urban model — The project, linking Ben Thanh to Can Gio, is being positioned as a major infrastructure upgrade that could reshape mobility, tourism, and real ...</t>
+          <t>호치민시는 파편화된 개발을 해결하기 위해 '1공간-3지역-1특구' 체계의 다중심 도시 모델을 도입하여 메가시티로의 도약을 준비하고 있습니다. 메트로 시스템과 지역 교통망을 중심으로 한 대중교통 지향 개발(TOD) 모델을 통해 2030년까지 핵심 교통망 완성을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam's Ho Chi Minh City adopts multi-center urban model — The project, linking Ben Thanh to Can Gio, is being positioned as a major infrastructure upgrade that could reshape mobility, tourism, and real ...</t>
+          <t>Ho Chi Minh City is adopting a multi-center urban model under a "one space – three regions – one special zone" framework to transform into a sustainable megacity. The plan prioritizes Transit-Oriented Development (TOD), focusing on metro systems and regional transport to link finance, high-tech, and maritime economic hubs by 2030.</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam's Ho Chi Minh City adopts multi-center urban model — The project, linking Ben Thanh to Can Gio, is being positioned as a major infrastructure upgrade that could reshape mobility, tourism, and real ...</t>
+          <t>Thành phố Hồ Chí Minh đang triển khai mô hình đô thị đa trung tâm với khung sườn "một trục – ba vùng – một khu vực đặc thù" để hướng tới mục tiêu siêu đô thị bền vững. Kế hoạch tập trung vào mô hình phát triển đô thị gắn kết với giao thông công cộng (TOD), ưu tiên hoàn thiện mạng lưới metro và hạ tầng kết nối vùng trước năm 2030.</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6016,17 +6016,17 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam set for US$115bil mega urban projects — Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025, ... (관련: VN-EV-2030)</t>
+          <t>베트남은 빈그룹(Vingroup)과 선그룹(Sun Group) 등 주요 개발사들의 주도로 총 1,150억 달러 규모의 27개 대형 도시 개발 프로젝트를 추진하고 있습니다. 법적 규제 완화와 인프라 확장을 통해 하노이와 호치민 인근에 대규모 신도시가 건설 중이나, 급격한 가격 상승에 따른 주택 공급 흡수 능력에 대한 우려도 제기되고 있습니다.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam set for US$115bil mega urban projects — Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025, ... (Related: VN-EV-2030)</t>
+          <t>Vietnam is launching 27 mega urban development projects worth $115 billion, led by major developers like Vingroup and Sun Group across the Northern, Central, and Southern regions. These projects, including the massive $35.6 billion Olympic sports urban area in Hanoi, are supported by improved legal frameworks and expanding infrastructure but face challenges regarding housing affordability and market absorption.</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>[Urban Development] Vietnam set for US$115bil mega urban projects — Vietnam had 27 large-scale urban development projects with combined investment exceeding three quadrillion dong (US$115bil) in 2025, ... (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang triển khai 27 dự án đô thị quy mô lớn với tổng vốn đầu tư lên tới 115 tỷ USD, tập trung tại ba miền Bắc, Trung và Nam dưới sự dẫn dắt của các tập đoàn lớn như Vingroup và Sun Group. Mặc dù các cải cách pháp lý và cơ sở hạ tầng đang thúc đẩy làn sóng phát triển này, các chuyên gia vẫn cảnh báo về áp lực giá nhà tăng cao và khả năng hấp thụ của thị trường.</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6080,17 +6080,17 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>[Urban Development] Cushman &amp; Wakefield Spotlights Vietnam's Next Urban ... — The country is now entering a more mature phase of development, where growth is increasingly defined not only by scale, but by productivity, ... (관련: VN-EV-2030)</t>
+          <t>베트남은 2030년까지 동남아시아 3위 경제 대국으로 도약하기 위해 단순 확장을 넘어 전략적 인프라와 통합 도시 계획 중심의 질적 성장을 추진하고 있습니다. 첨단 기술 중심의 FDI 유치와 함께 주거, 교육, 의료가 결합된 복합 도시 구역 개발을 통해 장기적인 도시 경쟁력을 강화할 계획입니다.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>[Urban Development] Cushman &amp; Wakefield Spotlights Vietnam's Next Urban ... — The country is now entering a more mature phase of development, where growth is increasingly defined not only by scale, but by productivity, ... (Related: VN-EV-2030)</t>
+          <t>Vietnam is transitioning toward a high-quality urban growth model that integrates strategic infrastructure, innovation, and sustainable planning to become Southeast Asia’s third-largest economy by 2030. The focus is shifting from fragmented expansion to developing integrated mega-townships and high-tech investment hubs in sectors like semiconductors and AI.</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>[Urban Development] Cushman &amp; Wakefield Spotlights Vietnam's Next Urban ... — The country is now entering a more mature phase of development, where growth is increasingly defined not only by scale, but by productivity, ... (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang chuyển mình sang giai đoạn phát triển đô thị chất lượng cao, kết hợp chặt chẽ giữa quy hoạch tích hợp và đầu tư hạ tầng chiến lược nhằm hướng tới mục tiêu trở thành nền kinh tế lớn thứ ba khu vực vào năm 2030. Quốc gia đang ưu tiên phát triển các khu đô thị phức hợp bền vững và thu hút đầu tư vào các ngành công nghệ cao như bán dẫn và trí tuệ nhân tạo.</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6144,17 +6144,17 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>[Urban Development] New urbanisation cycle set to define Vietnam's next ... — Vietnam is shifting to sustainable growth, with urban planning and infrastructure set to define the next decade.</t>
+          <t>베트남은 2030년까지 전략적 인프라 개발과 통합 도시 계획을 통해 단순한 확장을 넘어 고부가가치 성장의 새로운 도시화 주기에 진입하고 있습니다. 쿠시먼앤드웨이크필드는 향후 도시 개발이 주거 공급을 넘어 일자리, 교육, 의료가 결합된 복합 생태계를 구축하는 데 집중될 것이라고 전망했습니다.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>[Urban Development] New urbanisation cycle set to define Vietnam's next ... — Vietnam is shifting to sustainable growth, with urban planning and infrastructure set to define the next decade.</t>
+          <t>Vietnam is entering a new urbanization cycle focused on strategic infrastructure development and integrated urban planning to achieve high-value growth by 2030. Experts emphasize that future development must move beyond mere housing to create complete ecosystems that align infrastructure with employment clusters and quality living environments.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>[Urban Development] New urbanisation cycle set to define Vietnam's next ... — Vietnam is shifting to sustainable growth, with urban planning and infrastructure set to define the next decade.</t>
+          <t>Việt Nam đang bước vào chu kỳ đô thị hóa mới tập trung vào phát triển hạ tầng chiến lược và quy hoạch đô thị tích hợp để đạt được tăng trưởng giá trị cao vào năm 2030. Các chuyên gia nhấn mạnh rằng phát triển trong tương lai phải vượt xa việc chỉ cung cấp nhà ở để tạo ra các hệ sinh thái hoàn chỉnh, kết nối hạ tầng với các cụm việc làm và môi trường sống chất lượng.</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6208,17 +6208,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City targets global Top 50 smart cities by 2030 — Ho Chi Minh City aims to rank among the world's top 50 smart cities by 2030 under a draft smart urban development plan for 2026–2030, ... (관련: VN-EV-2030)</t>
+          <t>호치민시는 2030년까지 세계 50대 스마트 시티 진입을 목표로 하는 도시 개발 계획을 발표했습니다. 이 계획은 단순한 기술 도입을 넘어 데이터 기반의 거버넌스 혁신과 디지털 트윈 기술 구축에 중점을 두고 있습니다.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City targets global Top 50 smart cities by 2030 — Ho Chi Minh City aims to rank among the world's top 50 smart cities by 2030 under a draft smart urban development plan for 2026–2030, ... (Related: VN-EV-2030)</t>
+          <t>Ho Chi Minh City aims to rank among the world's top 50 smart cities by 2030, focusing on data-driven governance and digital twin technology. The plan prioritizes institutional reform and infrastructure development to serve as a national hub for innovation by 2035.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City targets global Top 50 smart cities by 2030 — Ho Chi Minh City aims to rank among the world's top 50 smart cities by 2030 under a draft smart urban development plan for 2026–2030, ... (Liên quan: VN-EV-2030)</t>
+          <t>Thành phố Hồ Chí Minh đặt mục tiêu lọt vào nhóm 50 thành phố thông minh hàng đầu thế giới vào năm 2030 thông qua việc chuyển đổi quản trị dựa trên dữ liệu. Kế hoạch ưu tiên xây dựng hạ tầng số, hệ thống bản sao số (digital twin) và cải cách thể chế để trở thành trung tâm điều hành thông minh quốc gia vào năm 2035.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6272,17 +6272,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City And Hanoi Redefine Urban Futures — On the cusp of 2026, two of Vietnam's most dynamic cities—Ho Chi Minh City and Hanoi—are charting bold, divergent courses in urban development. (관련: VN-EV-2030)</t>
+          <t>베트남의 양대 도시인 호찌민과 하노이는 2026년을 기점으로 혁신적인 도시 개발 계획을 추진하고 있습니다. 호찌민은 '더 글로벌 시티'와 같은 대규모 통합 도시 프로젝트를 통해 거주와 상업이 결합된 환경을 구축하고 있으며, 하노이는 교통 혼잡 해결을 위해 1,000m 이하의 '저고도 경제'와 드론 물류 시스템 도입에 집중하고 있습니다.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City And Hanoi Redefine Urban Futures — On the cusp of 2026, two of Vietnam's most dynamic cities—Ho Chi Minh City and Hanoi—are charting bold, divergent courses in urban development. (Related: VN-EV-2030)</t>
+          <t>Ho Chi Minh City and Hanoi are redefining their urban landscapes by 2026 through divergent infrastructure strategies. Ho Chi Minh City is focusing on integrated mega-projects like 'The Global City' to create holistic living environments, while Hanoi is pioneering a 'low-altitude economy' using UAVs and eVTOLs to bypass ground-level traffic congestion and modernize logistics.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>[Urban Development] Ho Chi Minh City And Hanoi Redefine Urban Futures — On the cusp of 2026, two of Vietnam's most dynamic cities—Ho Chi Minh City and Hanoi—are charting bold, divergent courses in urban development. (Liên quan: VN-EV-2030)</t>
+          <t>Thành phố Hồ Chí Minh và Hà Nội đang định hình lại tương lai đô thị vào năm 2026 với những hướng đi đột phá. Trong khi TP.HCM tập trung vào các siêu dự án đô thị tích hợp như The Global City để tạo ra môi trường sống toàn diện, Hà Nội lại khai thác kinh tế tầm thấp dưới 1.000m, sử dụng flycam và thiết bị bay không người lái để tối ưu hóa hậu cần và giảm thiểu ùn tắc giao thông.</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6336,17 +6336,17 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>[Other] VinFast Records Biggest-Ever Single-Day Sales on April 11, 2026 ... — VinFast achieves record-breaking EV sales as global charging infrastructure expands, marking a shift from hype to practical adoption ... (관련: VN-EV-2030)</t>
+          <t>베트남의 선도적인 전기차 제조업체인 빈패스트(VinFast)는 2026년 4월 11일 사상 최대 일일 판매량을 기록하며 전기차 시장의 성숙을 알렸습니다. 이러한 성장은 베트남의 급속한 충전 인프라 확충과 정부의 친환경 에너지 정책 덕분에 가능했으며, 베트남은 글로벌 전기 모빌리티 분야의 핵심 국가로 부상하고 있습니다.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>[Other] VinFast Records Biggest-Ever Single-Day Sales on April 11, 2026 ... — VinFast achieves record-breaking EV sales as global charging infrastructure expands, marking a shift from hype to practical adoption ... (Related: VN-EV-2030)</t>
+          <t>VinFast achieved record-breaking single-day sales on April 11, 2026, signaling a major transition toward mass-market EV adoption. This milestone is supported by Vietnam's rapid expansion of charging infrastructure and government mandates, positioning the country as a global powerhouse in the electric mobility sector.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>[Other] VinFast Records Biggest-Ever Single-Day Sales on April 11, 2026 ... — VinFast achieves record-breaking EV sales as global charging infrastructure expands, marking a shift from hype to practical adoption ... (Liên quan: VN-EV-2030)</t>
+          <t>VinFast đã ghi nhận doanh số bán xe điện trong một ngày cao nhất lịch sử vào ngày 11 tháng 4 năm 2026, đánh dấu bước ngoặt chuyển dịch sang thị trường đại chúng. Thành tựu này được thúc đẩy bởi việc mở rộng nhanh chóng cơ sở hạ tầng sạc tại Việt Nam và các chính sách hỗ trợ của chính phủ, giúp quốc gia này trở thành trung tâm mới của ngành xe điện toàn cầu.</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -6396,17 +6396,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] analyzing the public voice on electric vehicles and the rise of VinFast — Specifically, Hanoi will pilot a “Low Emission Zone” starting on July 1, 2026, which will restrict highly polluting gasoline vehicles from entering inner-city ... (관련: VN-EV-2030)</t>
+          <t>베트남은 2030년까지 하노이와 호치민시의 주요 교통수단을 전기차(EV)로 전환하는 국가 전략을 추진하고 있습니다. 2026년부터 하노이에 저배출 구역이 도입되고 호치민시는 2025년까지 모든 신규 공공 버스를 전기차로 교체할 계획이지만, 충전 인프라 확충은 여전히 시급한 과제로 남아 있습니다.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] analyzing the public voice on electric vehicles and the rise of VinFast — Specifically, Hanoi will pilot a “Low Emission Zone” starting on July 1, 2026, which will restrict highly polluting gasoline vehicles from entering inner-city ... (Related: VN-EV-2030)</t>
+          <t>Vietnam is implementing a national strategy to make electric vehicles the primary mode of transport in Hanoi and Ho Chi Minh City by 2030. While initiatives include low-emission zones starting in 2026 and electric public buses by 2025, public discourse highlights that the success of this energy transition depends heavily on expanding the charging infrastructure ecosystem.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] analyzing the public voice on electric vehicles and the rise of VinFast — Specifically, Hanoi will pilot a “Low Emission Zone” starting on July 1, 2026, which will restrict highly polluting gasoline vehicles from entering inner-city ... (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang thực hiện chiến lược quốc gia nhằm đưa xe điện trở thành phương tiện giao thông chính tại Hà Nội và TP.HCM vào năm 2030. Mặc dù các lộ trình như khu vực phát thải thấp (2026) và xe buýt điện (2025) đã được thiết lập, dư luận khẳng định rằng việc phát triển hạ tầng trạm sạc là yếu tố then chốt cho sự thành công của kế hoạch này.</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -6460,17 +6460,17 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>[Other] VinFast's breakout year: Vietnamese EV maker nearly doubles sales ... — With nearly 200,000 EVs sold in 2025 and a 300,000-unit target for 2026, VinFast is no longer just an ambitious startup from Vietnam. It is ... (관련: VN-EV-2030)</t>
+          <t>베트남 전기차 제조업체 빈패스트(VinFast)는 2025년 전 세계적으로 약 20만 대의 차량을 인도하며 판매 실적을 두 배로 늘렸습니다. 이러한 성장은 베트남 내수 시장의 강력한 수요와 충전 네트워크 인프라 확장에 힘입은 결과이며, 회사는 2026년까지 30만 대 인도를 목표로 하고 있습니다.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>[Other] VinFast's breakout year: Vietnamese EV maker nearly doubles sales ... — With nearly 200,000 EVs sold in 2025 and a 300,000-unit target for 2026, VinFast is no longer just an ambitious startup from Vietnam. It is ... (Related: VN-EV-2030)</t>
+          <t>Vietnamese EV maker VinFast nearly doubled its global sales in 2025 by delivering 196,919 vehicles, driven by a robust charging network and domestic demand. Following this record growth, the company has set an ambitious target of 300,000 deliveries for 2026 as it expands its international footprint.</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>[Other] VinFast's breakout year: Vietnamese EV maker nearly doubles sales ... — With nearly 200,000 EVs sold in 2025 and a 300,000-unit target for 2026, VinFast is no longer just an ambitious startup from Vietnam. It is ... (Liên quan: VN-EV-2030)</t>
+          <t>Nhà sản xuất xe điện VinFast đã gần như gấp đôi doanh số toàn cầu trong năm 2025 với 196.919 xe được bàn giao, nhờ vào sự bùng nổ của thị trường nội địa và hạ tầng trạm sạc. Công ty hiện đặt mục tiêu đầy tham vọng là đạt 300.000 xe trong năm 2026 để củng cố vị thế trên thị trường xe điện thế giới.</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -6524,17 +6524,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vingroup Extends Emergency Support Program for Electric Vehicle ... — Vingroup Extends Emergency Support Program for Electric Vehicle Transition Until April 30, 2026, to Continue Alleviating Fuel Supply and ... (관련: VN-EV-2030)</t>
+          <t>빈그룹(Vingroup)은 베트남의 전기차 전환을 가속화하기 위해 긴급 지원 프로그램을 연장했습니다. 이 이니셔티브는 VN-EV-2030 계획에 따라 교통 인프라를 현대화하고 친환경 모빌리티 채택을 장려하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vingroup Extends Emergency Support Program for Electric Vehicle ... — Vingroup Extends Emergency Support Program for Electric Vehicle Transition Until April 30, 2026, to Continue Alleviating Fuel Supply and ... (Related: VN-EV-2030)</t>
+          <t>Vingroup has extended its emergency support program to facilitate the transition to electric vehicles in Vietnam. This move supports the VN-EV-2030 infrastructure plan by enhancing accessibility to green transport solutions across the country.</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vingroup Extends Emergency Support Program for Electric Vehicle ... — Vingroup Extends Emergency Support Program for Electric Vehicle Transition Until April 30, 2026, to Continue Alleviating Fuel Supply and ... (Liên quan: VN-EV-2030)</t>
+          <t>Tập đoàn Vingroup đã gia hạn chương trình hỗ trợ khẩn cấp cho quá trình chuyển đổi xe điện tại Việt Nam. Sáng kiến này đóng góp vào kế hoạch VN-EV-2030 nhằm thúc đẩy hạ tầng giao thông xanh và giảm thiểu phát thải.</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam pushes EV shift as energy security risks mount — Incentives to support electric vehicle production and adoption are required to be introduced by June. (관련: VN-EV-2030)</t>
+          <t>베트남 정부는 에너지 안보 위기에 대응하기 위해 2026년 3분기까지 전기차 충전 인프라 표준을 마련하고 6월까지 생산 및 도입 인센티브를 발표할 계획입니다. 팜 민 찐 총리는 수입 연료 의존도를 낮추기 위해 공공 부문의 전기차 전환과 민간 충전 시설 확대를 가속화하라는 지침을 내렸습니다.</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam pushes EV shift as energy security risks mount — Incentives to support electric vehicle production and adoption are required to be introduced by June. (Related: VN-EV-2030)</t>
+          <t>Vietnam is accelerating its transition to electric vehicles (EV) to mitigate energy security risks and reduce reliance on imported fuels. The government has set deadlines to establish charging infrastructure standards by Q3 2026 and introduce EV production incentives by June, while pushing for the electrification of public fleets and urban residential projects.</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam pushes EV shift as energy security risks mount — Incentives to support electric vehicle production and adoption are required to be introduced by June. (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang đẩy mạnh chuyển đổi sang xe điện (EV) nhằm đảm bảo an ninh năng lượng và giảm phụ thuộc vào nhiên liệu nhập khẩu. Thủ tướng Phạm Minh Chính đã yêu cầu ban hành các quy chuẩn kỹ thuật cho trạm sạc vào quý 3 năm 2026 và các chính sách ưu đãi sản xuất xe điện trước tháng 6 tới.</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -6648,17 +6648,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] The electric vehicle transition as a green window of opportunity ... — The general tendency of weak technology ownership in the Vietnamese automotive industry applies to locally made EVs. Vinfast sources key technologies such as ... (관련: VN-EV-2030)</t>
+          <t>베트남 정부는 2030년까지 도시 차량의 50%를 전기차로 전환하고 2050년까지 완전한 녹색 에너지 교통 체계를 구축한다는 '결정 제876/QD-TTg' 계획을 승인했습니다. 이에 따라 민간 기업인 빈패스트(Vinfast)는 전국에 15만 개의 충전 지점을 설치하며 인프라 구축을 주도하고 있으나, 규모의 경제 달성이 향후 과제로 남아있습니다.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] The electric vehicle transition as a green window of opportunity ... — The general tendency of weak technology ownership in the Vietnamese automotive industry applies to locally made EVs. Vinfast sources key technologies such as ... (Related: VN-EV-2030)</t>
+          <t>The Vietnamese government has approved Decision 876/QD-TTg, targeting 50% of urban vehicles to be electric by 2030 and achieving a complete transition to green energy by 2050. Private leader Vinfast is driving this shift by installing 150,000 charging points nationwide, though the sector still faces significant entry barriers and the need for higher production scales.</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] The electric vehicle transition as a green window of opportunity ... — The general tendency of weak technology ownership in the Vietnamese automotive industry applies to locally made EVs. Vinfast sources key technologies such as ... (Liên quan: VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã phê duyệt Quyết định 876/QD-TTg với mục tiêu 50% phương tiện đô thị sử dụng điện vào năm 2030 và chuyển đổi hoàn toàn sang năng lượng xanh vào năm 2050. Vinfast đang dẫn đầu nỗ lực này với việc lắp đặt 150.000 cổng sạc trên toàn quốc, tuy nhiên ngành vẫn đang đối mặt với thách thức lớn về quy mô sản xuất để duy trì tính bền vững.</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -6712,17 +6712,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] The Future of Sustainable Vehicles in Vietnam - Milken Scholars — I traveled to Vietnam to learn more about VinFast's rapid rise and to investigate whether its pledge to promote a more sustainable energy ecosystem holds up in ...</t>
+          <t>베트남의 전기차 산업은 빈패스트(VinFast)를 중심으로 급성장하고 있으나, 전력 인프라와 에너지 생산의 지속가능성 문제가 남아있습니다. 현재 베트남 전력 생산의 약 80%는 석탄에 의존하고 있으며, 노후화된 전기 시스템과 충전소 부족이 인프라 확장의 주요 장애물로 지적됩니다.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] The Future of Sustainable Vehicles in Vietnam - Milken Scholars — I traveled to Vietnam to learn more about VinFast's rapid rise and to investigate whether its pledge to promote a more sustainable energy ecosystem holds up in ...</t>
+          <t>Vietnam's electric vehicle market is expanding through VinFast's initiatives, but the country faces significant infrastructure challenges including a lack of public charging stations. Furthermore, approximately 80% of Vietnam's energy mix is still derived from coal, questioning the true environmental impact of EV adoption under the current power grid.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] The Future of Sustainable Vehicles in Vietnam - Milken Scholars — I traveled to Vietnam to learn more about VinFast's rapid rise and to investigate whether its pledge to promote a more sustainable energy ecosystem holds up in ...</t>
+          <t>Thị trường xe điện Việt Nam đang phát triển mạnh mẽ thông qua VinFast, nhưng vẫn đối mặt với thách thức lớn về hạ tầng trạm sạc và hệ thống lưới điện cũ kỹ. Hiện nay, khoảng 80% sản lượng điện của Việt Nam vẫn dựa vào than đá, gây ra những nghi vấn về tính bền vững thực sự của xe điện đối với môi trường.</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -6776,17 +6776,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>[Other] VinFast Extends Free Charging Policy Across Markets - LinkedIn — Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets.</t>
+          <t>베트남 자동차 제조사 빈패스트(VinFast)가 운영 시장 전역에서 무료 충전 정책을 3년 연장한다고 발표했습니다. 또한 모기업 빈그룹은 베트남을 포함한 주요국에서 내연기관차를 전기차로 전환할 시 할인 혜택을 제공하는 'Trade Gas for Electric' 프로그램을 시행합니다.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>[Other] VinFast Extends Free Charging Policy Across Markets - LinkedIn — Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets.</t>
+          <t>Vietnamese automaker VinFast has announced a three-year extension of its free charging policy for private and commercial customers across its operational markets. Additionally, parent company Vingroup introduced the 'Trade Gas for Electric' initiative, offering discounts on electric cars and scooters through March 2026 to encourage the transition from petrol vehicles.</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>[Other] VinFast Extends Free Charging Policy Across Markets - LinkedIn — Vietnamese automotive company VINFAST has announced a three-year extension of its free charging policy across its operational markets.</t>
+          <t>Công ty ô tô Việt Nam VinFast đã thông báo gia hạn chính sách sạc miễn phí thêm ba năm tại các thị trường đang hoạt động. Bên cạnh đó, tập đoàn Vingroup cũng triển khai chương trình 'Đổi xe xăng lấy xe điện' với các ưu đãi giảm giá đặc biệt cho khách hàng chuyển đổi sang xe điện đến hết tháng 3 năm 2026.</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -6840,17 +6840,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>[Other] Vietnam's EV market is gaining momentum In 2025, VinFast ... — Vietnamese EV maker VinFast has posted a 63% jump in electric vehicle deliveries in 2025, delivering 196,919 EVs and generating US$3.6 ... (관련: VN-EV-2030)</t>
+          <t>베트남 전기차 시장이 급성장하며 빈패스트가 2025년 약 175,000대의 판매고를 올려 업계 1위를 차지했습니다. 40만 대 이상의 전기 오토바이 판매와 인프라 개선이 동반되고 있으나, 여전히 충전소 확충과 내연기관차 규제 정책에 대한 논의가 진행 중입니다.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>[Other] Vietnam's EV market is gaining momentum In 2025, VinFast ... — Vietnamese EV maker VinFast has posted a 63% jump in electric vehicle deliveries in 2025, delivering 196,919 EVs and generating US$3.6 ... (Related: VN-EV-2030)</t>
+          <t>Vietnam's EV market is surging, with VinFast leading the sector after delivering 175,000 electric cars and generating $3.6 billion in revenue in 2025. While electric motorbike sales exceeded 400,000 units, the country faces a transition phase involving infrastructure improvements and debates over gas-vehicle restrictions.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>[Other] Vietnam's EV market is gaining momentum In 2025, VinFast ... — Vietnamese EV maker VinFast has posted a 63% jump in electric vehicle deliveries in 2025, delivering 196,919 EVs and generating US$3.6 ... (Liên quan: VN-EV-2030)</t>
+          <t>Thị trường xe điện Việt Nam đang bùng nổ khi VinFast đạt kỷ lục bàn giao 175.000 ô tô điện và trở thành thương hiệu dẫn đầu trong năm 2025. Bên cạnh đó, doanh số xe máy điện đạt hơn 400.000 chiếc, đánh dấu giai đoạn chuyển đổi mạnh mẽ dù vẫn còn những thách thức về hạ tầng trạm sạc.</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -6904,17 +6904,17 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam outlines new plan to cut waste, protect coastal ... — HÀ NỘI — Việt Nam has launched a fresh push to curb pollution across its fisheries sector, warning that rising seas, degraded ecosystems and ...</t>
+          <t>베트남은 수산업 분야의 오염을 줄이고 해안 생태계를 보호하기 위해 2026-2030년 기간의 새로운 환경 보호 우선순위를 발표했습니다. 캐나다 대사관 및 UNDP와 협력하여 진행되는 이 계획은 기후 변화에 대응하고 폐기물 관리를 현대화하여 지속 가능한 수산물 생산을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam outlines new plan to cut waste, protect coastal ... — HÀ NỘI — Việt Nam has launched a fresh push to curb pollution across its fisheries sector, warning that rising seas, degraded ecosystems and ...</t>
+          <t>Vietnam has launched a new national plan for 2026–2030 to curb pollution in the fisheries sector and protect coastal ecosystems from climate change. Supported by Canada and the UNDP, the initiative focuses on waste reduction, mangrove restoration, and adopting cleaner technologies to ensure sustainable livelihoods for coastal communities.</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam outlines new plan to cut waste, protect coastal ... — HÀ NỘI — Việt Nam has launched a fresh push to curb pollution across its fisheries sector, warning that rising seas, degraded ecosystems and ...</t>
+          <t>Việt Nam vừa công bố kế hoạch mới giai đoạn 2026–2030 nhằm giảm thiểu ô nhiễm trong ngành thủy sản và bảo vệ hệ sinh thái ven biển. Với sự hỗ trợ từ Canada và UNDP, sáng kiến này tập trung vào kiểm soát chất lượng chất thải, phục hồi rừng ngập mặn và áp dụng công nghệ sạch để phát triển kinh tế biển bền vững.</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -6968,17 +6968,17 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>RTI International은 베트남의 산업 위험 연구를 통해 대기 및 수질 오염 문제 해결을 위한 과학적 솔루션을 제공합니다. 이 프로젝트는 환경 및 기후 분야의 인프라 발전을 목표로 하며 VN-ENV-IND-1894 및 VN-EV-2030 계획과 연계됩니다.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>RTI International conducts an industrial risk study on air and water pollution in Vietnam to provide science-based environmental solutions. This initiative supports infrastructure goals in the Environment &amp; Climate sector, aligning with the VN-ENV-IND-1894 and VN-EV-2030 strategic plans.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>RTI International thực hiện nghiên cứu rủi ro công nghiệp về ô nhiễm không khí và nguồn nước tại Việt Nam nhằm đưa ra các giải pháp khoa học. Dự án này hỗ trợ phát triển hạ tầng trong lĩnh vực Môi trường &amp; Khí hậu, phù hợp với các kế hoạch VN-ENV-IND-1894 và VN-EV-2030.</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7028,17 +7028,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (관련: VN-ENV-IND-1894)</t>
+          <t>베트남은 급격한 산업화로 인해 경제 성장을 이루었으나 공기, 수질 및 토양 자원에 심각한 부담을 주고 있습니다. 하노이와 호치민시의 미세먼지 오염이 심각하며, 산업 단지 인근의 폐수 무단 방류로 인해 '죽은 강'이 늘어나고 있습니다.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (Related: VN-ENV-IND-1894)</t>
+          <t>Vietnam's rapid industrialization has driven economic growth but caused severe strain on air, water, and soil resources. Major cities face critical PM2.5 pollution from industrial zones and transport, while untreated wastewater from textile and electronic sectors is creating "dead rivers" and contaminating groundwater.</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (Liên quan: VN-ENV-IND-1894)</t>
+          <t>Quá trình công nghiệp hóa nhanh chóng của Việt Nam đã thúc đẩy kinh tế nhưng gây áp lực lớn lên tài nguyên không khí, nước và đất. Các thành phố lớn đang đối mặt với ô nhiễm bụi mịn nghiêm trọng, trong khi nước thải chưa qua xử lý từ các khu công nghiệp đang tạo ra những "dòng sông chết" và đe dọa nguồn nước ngầm.</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7092,17 +7092,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (관련: VN-ENV-IND-1894)</t>
+          <t>베트남은 2025년까지 산림 피복률을 42.03%로 유지하고 1,300만 달러 규모의 오존층 파괴 물질 감축 프로젝트를 시작했습니다. 하노이와 호치민시는 2027년부터 이륜차 배기가스 검사를 시행하며, 2030년까지 전국으로 확대할 계획입니다.</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (Related: VN-ENV-IND-1894)</t>
+          <t>Vietnam has maintained a stable forest coverage of 42.03% as of 2025 and launched a 13 million USD project to phase out ozone-depleting substances by 2031. Additionally, the country will implement mandatory motorcycle emissions testing in major cities starting in 2027, expanding nationwide by 2030.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (Liên quan: VN-ENV-IND-1894)</t>
+          <t>Việt Nam duy trì tỷ lệ che phủ rừng ổn định ở mức 42,03% vào năm 2025 và triển khai dự án 13 triệu USD nhằm loại bỏ các chất làm suy giảm tầng ozone. Bên cạnh đó, lộ trình kiểm định khí thải xe máy sẽ bắt đầu tại Hà Nội và TP.HCM từ năm 2027, sau đó mở rộng ra toàn quốc vào năm 2030.</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7152,17 +7152,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>베트남 산업단지의 약 79%가 중앙 집중식 폐수 처리 시스템을 갖추고 있으나, 많은 곳이 비효율적으로 운영되거나 환경 기준을 충족하지 못하고 있습니다. 산업 클러스터(CCN)의 경우 단 5%만이 처리 시설을 보유하고 있으며, 고형 및 유해 폐기물 수집 시설의 부족이 심각한 환경 오염의 원인이 되고 있습니다.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>Approximately 79% of Vietnam's operating industrial zones have built centralized wastewater treatment systems, yet many face operational inefficiencies and fail to meet national environmental standards. Industrial clusters (CCNs) lag significantly with only a 5% coverage rate, and the lack of dedicated collection and treatment centers for hazardous solid waste continues to pressure natural ecosystems.</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>Khoảng 79% các khu công nghiệp tại Việt Nam đã xây dựng hệ thống xử lý nước thải tập trung, nhưng nhiều nơi vận hành chưa hiệu quả và chưa đạt quy chuẩn môi trường. Các cụm công nghiệp (CCN) chỉ có khoảng 5% có hệ thống xử lý, đồng thời việc thiếu hụt các trung tâm thu gom và xử lý chất thải rắn nguy hại đang gây áp lực lớn lên hệ sinh thái và sức khỏe con người.</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7212,17 +7212,17 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>베트남 기획투자부는 지속 가능한 산업 발전을 촉진하기 위해 산업 환경 지수를 도입할 계획이라고 발표했습니다. 이 지수는 2021-2030 녹색 성장 전략의 일환으로, 400개 이상의 산업 단지와 18개 경제 구역의 환경 오염 문제를 해결하고 2050년 탄소 중립 목표 달성을 돕는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>The Vietnamese Ministry of Planning has announced plans to implement an Industrial Environmental Index to promote sustainable industrial development across its 400+ industrial parks. This initiative is part of the country's 2021-2030 green growth strategy and aims to mitigate severe industrial pollution while aligning with the national goal of reaching net-zero emissions by 2050.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>Bộ Kế hoạch và Đầu tư Việt Nam vừa công bố kế hoạch triển khai bộ chỉ số môi trường công nghiệp nhằm thúc đẩy phát triển công nghiệp bền vững. Đây là một phần trong chiến lược tăng trưởng xanh giai đoạn 2021-2030, hướng tới mục tiêu giải quyết vấn đề ô nhiễm tại các khu công nghiệp và đạt phát thải ròng bằng 0 vào năm 2050.</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7276,17 +7276,17 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam's push for net zero emissions by 2050 is putting ... — Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented ...</t>
+          <t>베트남의 2050년 넷제로 목표 달성을 위해 산업단지 내 탄소 배출 모니터링 및 보고 체계 개선이 시급한 과제로 떠오르고 있습니다. 이에 기업들은 환경 표준을 준수하고 효율성을 높이기 위해 지능형 운영 센터(IOC)를 도입하며 단순 인프라 임대를 넘어 글로벌 가치 사슬 내 거버넌스 플랫폼으로 진화하고 있습니다.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam's push for net zero emissions by 2050 is putting ... — Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented ...</t>
+          <t>Vietnam's 2050 net-zero commitment is driving industrial parks to adopt Intelligent Operations Centers (IOCs) to address gaps in real-time environmental monitoring. These digital platforms help businesses meet international sustainability standards and transition from basic infrastructure providers to key players in global value chains.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Việt Nam's push for net zero emissions by 2050 is putting ... — Việt Nam's push for net zero emissions by 2050 is putting pressure on industrial parks, where gaps in real-time monitoring and fragmented ...</t>
+          <t>Mục tiêu phát thải ròng bằng 0 vào năm 2050 của Việt Nam đang gây áp lực lên các khu công nghiệp trong việc cải thiện hệ thống giám sát và báo cáo môi trường. Để đáp ứng các tiêu chuẩn xanh, nhiều doanh nghiệp đã triển khai Trung tâm điều hành thông minh (IOC) nhằm nâng cao hiệu quả quản trị và vị thế trong chuỗi giá trị toàn cầu.</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -7340,17 +7340,17 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Green Transition in Vietnam's Industrial Parks: Policy ... — Vietnam's industrial parks are shifting toward eco-industrial models, renewable energy, and green standards amid global supply chain ...</t>
+          <t>베트남은 탄소 국경 조정 제도(CBAM)와 같은 글로벌 ESG 규제에 대응하기 위해 산업단지를 친환경 생태산업단지(EIP)로 전환하는 정책을 추진하고 있습니다. 정부는 신재생 에너지 사용과 자원 효율성을 강조하는 시행령 제35호 및 제9716호를 통해 법적 프레임워크를 마련하고 국제 기구와 협력하여 이를 확대하고 있습니다.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Green Transition in Vietnam's Industrial Parks: Policy ... — Vietnam's industrial parks are shifting toward eco-industrial models, renewable energy, and green standards amid global supply chain ...</t>
+          <t>Vietnam is transitioning its industrial parks into Eco-Industrial Parks (EIPs) to align with global ESG standards and regulations like the EU's CBAM. Supported by Decree 35 and Decree 9716, the government is promoting renewable energy adoption and circular economy practices to maintain export competitiveness and achieve net-zero goals by 2050.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Green Transition in Vietnam's Industrial Parks: Policy ... — Vietnam's industrial parks are shifting toward eco-industrial models, renewable energy, and green standards amid global supply chain ...</t>
+          <t>Việt Nam đang chuyển đổi các khu công nghiệp truyền thống sang mô hình khu công nghiệp sinh thái (EIP) nhằm đáp ứng các tiêu chuẩn ESG quốc tế và quy định CBAM. Chính phủ đã ban hành Nghị định 35 và Nghị định 9716 để thúc đẩy sử dụng năng lượng tái tạo, kinh tế tuần hoàn và nâng cao năng lực cạnh tranh cho chuỗi cung ứng toàn cầu.</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -7404,17 +7404,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Solid Waste Treatment in Vietnam: Current Situation and ... — Vietnam's industrial sector produces significant amounts of waste, but the country currently lacks sufficient treatment facilities. Foreign ...</t>
+          <t>베트남은 현재 하루 약 6만 톤의 생활 폐기물을 발생시키며, 그중 71%를 매립에 의존하고 있어 환경 오염 문제에 직면해 있습니다. 정부는 2030년까지 폐기물 에너지화(WtE) 용량을 1,500MW까지 확대하고 2024년 말부터 분리배출을 의무화하는 등 현대적인 폐기물 관리 인프라 구축에 박차를 가하고 있습니다.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Solid Waste Treatment in Vietnam: Current Situation and ... — Vietnam's industrial sector produces significant amounts of waste, but the country currently lacks sufficient treatment facilities. Foreign ...</t>
+          <t>Vietnam generates approximately 60,000 tons of municipal solid waste daily, with 71% still being landfilled, leading to significant environmental challenges. The government is actively promoting the transition to waste-to-energy (WtE) technology with a target of 1,500 MW capacity by 2030, offering substantial opportunities for foreign investment in sustainable infrastructure.</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Solid Waste Treatment in Vietnam: Current Situation and ... — Vietnam's industrial sector produces significant amounts of waste, but the country currently lacks sufficient treatment facilities. Foreign ...</t>
+          <t>Việt Nam hiện phát sinh khoảng 60.000 tấn rác thải sinh hoạt mỗi ngày, trong đó 71% vẫn được xử lý bằng phương pháp chôn lấp gây ô nhiễm môi trường. Chính phủ đang thúc đẩy hạ tầng xử lý rác hiện đại với mục tiêu đạt 1.500 MW điện rác vào năm 2030 và bắt buộc phân loại rác tại nguồn từ cuối năm 2024.</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -7468,17 +7468,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam accelerates battle against plastic waste — Vietnam is mobilizing resources to fight plastic waste marking its fifth anniversary.</t>
+          <t>베트남은 2030년까지 플라스틱 폐기물을 대폭 감축하기 위해 국가 플라스틱 행동 파트너십(NPAP)과 순환 경제 모델을 가속화하고 있습니다. 정부는 환경 보호와 지속 가능한 발전을 목표로 '그린 베트남'을 구축하기 위한 다양한 정책을 추진 중입니다.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam accelerates battle against plastic waste — Vietnam is mobilizing resources to fight plastic waste marking its fifth anniversary.</t>
+          <t>Vietnam is accelerating its efforts to combat plastic waste by implementing a circular economy and the National Plastic Action Partnership (NPAP). The country aims to achieve significant plastic reduction targets by 2030 to ensure environmental protection and a greener future.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam accelerates battle against plastic waste — Vietnam is mobilizing resources to fight plastic waste marking its fifth anniversary.</t>
+          <t>Việt Nam đang đẩy nhanh cuộc chiến chống rác thải nhựa thông qua việc thúc đẩy kinh tế tuần hoàn và Chương trình Đối tác Hành động Quốc gia về Nhựa (NPAP). Mục tiêu của kế hoạch là giảm thiểu đáng kể rác thải nhựa vào năm 2030 để hướng tới một Việt Nam xanh và bảo vệ môi trường.</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's infrastructure push to boost growth and deficit, S&amp;P ... — Vietnam is forecast to remain Asia's fastest-growing nation after India through 2028, supported by exports and infrastructure investments, ...</t>
+          <t>베트남은 수출과 대규모 인프라 투자를 바탕으로 2028년까지 인도에 이어 아시아에서 가장 빠르게 성장하는 국가가 될 것으로 전망됩니다. 정부는 2030년까지 연간 10% 성장을 목표로 약 2,000억 달러 규모의 프로젝트를 추진 중이지만, 이로 인한 재정 적자 확대 및 공공 부채 증가가 등급 상향의 변수가 될 수 있습니다.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's infrastructure push to boost growth and deficit, S&amp;P ... — Vietnam is forecast to remain Asia's fastest-growing nation after India through 2028, supported by exports and infrastructure investments, ...</t>
+          <t>Vietnam is projected to be Asia's fastest-growing economy after India through 2028, driven by massive infrastructure investments worth $200 billion. While these projects support strong economic growth targets, S&amp;P Ratings warns that heavy public spending could lead to larger fiscal deficits and rising government debt.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam's infrastructure push to boost growth and deficit, S&amp;P ... — Vietnam is forecast to remain Asia's fastest-growing nation after India through 2028, supported by exports and infrastructure investments, ...</t>
+          <t>Việt Nam được dự báo sẽ là nền kinh tế tăng trưởng nhanh nhất châu Á sau Ấn Độ cho đến năm 2028 nhờ vào xuất khẩu và các khoản đầu tư hạ tầng trị giá 200 tỷ USD. Tuy nhiên, S&amp;P Ratings cảnh báo rằng việc đẩy mạnh chi tiêu công có thể dẫn đến thâm hụt ngân sách lớn hơn và nợ công gia tăng, ảnh hưởng đến mục tiêu nâng hạng tín nhiệm.</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -7596,17 +7596,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam Construction Industry Report 2026: Output to Expand by 7.9 ... — The analyst expects the construction industry in Vietnam to grow by 7.9% in real terms in 2026, supported by increased foreign direct investment ...</t>
+          <t>베트남 건설 산업은 정부의 인프라 투자 확대에 힘입어 2030년까지 연평균 6.5%의 성장이 예상됩니다. 특히 교통부는 고속도로 길이를 5,000km까지 확장하고 호치민시에 8개의 지하철 노선을 건설하는 대규모 프로젝트를 추진 중입니다.</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam Construction Industry Report 2026: Output to Expand by 7.9 ... — The analyst expects the construction industry in Vietnam to grow by 7.9% in real terms in 2026, supported by increased foreign direct investment ...</t>
+          <t>Vietnam's construction sector is projected to maintain a 6.5% average annual growth rate through 2030, driven by significant transport and energy infrastructure investments. Key projects include expanding the national expressway network to 5,000km and developing an eight-line urban railway system in Ho Chi Minh City by 2035.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Vietnam Construction Industry Report 2026: Output to Expand by 7.9 ... — The analyst expects the construction industry in Vietnam to grow by 7.9% in real terms in 2026, supported by increased foreign direct investment ...</t>
+          <t>Ngành xây dựng Việt Nam dự kiến đạt mức tăng trưởng bình quân 6,5% mỗi năm từ 2027 đến 2030 nhờ sự đẩy mạnh đầu tư vào hạ tầng giao thông và năng lượng. Các dự án trọng điểm bao gồm mục tiêu nâng chiều dài đường cao tốc lên 5.000km và xây dựng hệ thống 8 tuyến đường sắt đô thị tại TP.HCM.</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>[Other] Vietnam Infrastructure Spotlight March 2026 - Freshfields — In this issue, we highlight recent legal and market developments in Vietnam's infrastructure sector. (관련: VN-EV-2030)</t>
+          <t>하노이시는 2030년까지 모든 가솔린 및 디젤 택시를 친환경 차량으로 교체할 계획이며, 2026년까지 63-64% 전환을 목표로 하고 있습니다. 이와 함께 Thaco는 VinFast에 이어 베트남의 두 번째 독자 자동차 브랜드를 출시하여 국내 전기차 및 승용차 시장을 확대할 예정입니다.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>[Other] Vietnam Infrastructure Spotlight March 2026 - Freshfields — In this issue, we highlight recent legal and market developments in Vietnam's infrastructure sector. (Related: VN-EV-2030)</t>
+          <t>Hanoi plans to replace all gasoline and diesel taxis with green-energy vehicles by 2030, targeting a 63-64% transition rate by 2026. Additionally, Vietnamese conglomerate Thaco aims to launch its own passenger car brand, becoming the country's second domestic automaker after VinFast.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>[Other] Vietnam Infrastructure Spotlight March 2026 - Freshfields — In this issue, we highlight recent legal and market developments in Vietnam's infrastructure sector. (Liên quan: VN-EV-2030)</t>
+          <t>Hà Nội lập kế hoạch thay thế toàn bộ xe taxi chạy bằng xăng và dầu bằng xe năng lượng xanh vào năm 2030, với mục tiêu đạt tỷ lệ 63-64% vào năm 2026. Bên cạnh đó, tập đoàn Thaco dự kiến sản xuất xe du lịch mang thương hiệu riêng, trở thành thương hiệu ô tô nội địa thứ hai của Việt Nam sau VinFast.</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -7724,17 +7724,17 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — ... Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment ...</t>
+          <t>베트남은 제14차 당대회를 앞두고 인프라 혁신을 국가 성장의 핵심 전략적 기둥으로 설정했습니다. 이는 국제 비즈니스 사회에 중요한 지표가 되며 투자 유치를 위한 기반이 될 것입니다.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — ... Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment ...</t>
+          <t>Vietnam is positioning its infrastructure breakthrough as a strategic pillar for economic growth ahead of the 14th National Party Congress. This development serves as a critical reference point for the international business community and future investment.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — ... Vietnam but also a key reference point for the international business community. It is shaping expectations for economic reform, investment ...</t>
+          <t>Việt Nam đang xác định đột phá hạ tầng là trụ cột chiến lược cho sự tăng trưởng hướng tới Đại hội Đảng toàn quốc lần thứ 14. Đây là điểm tham chiếu quan trọng cho cộng đồng kinh doanh quốc tế và thu hút đầu tư.</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Investing In... 2026 - Vietnam - Global Practice Guides — These landmark reforms round out Vietnam's earlier investment roadmap under Resolution No 50 (2019) and are reinforced by a series of new ...</t>
+          <t>베트남은 2024년 개정 전기법과 제8차 국가전력개발계획(PDP VIII)을 통해 에너지 인프라 시장을 대대적으로 개편하고 신재생 에너지 투자를 촉진하고 있습니다. 행정적으로는 교통부가 건설부로 통합되는 등 정부 부처 구조조정을 통해 인프라 프로젝트의 효율성을 높이고자 합니다.</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Investing In... 2026 - Vietnam - Global Practice Guides — These landmark reforms round out Vietnam's earlier investment roadmap under Resolution No 50 (2019) and are reinforced by a series of new ...</t>
+          <t>Vietnam is overhauling its infrastructure sector through the 2024 Law on Electricity and the amended PDP VIII, which prioritizes renewable energy and introduces new market instruments. Administratively, the country has merged the Ministry of Transport into the Ministry of Construction to streamline project management and enhance administrative efficiency.</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Investing In... 2026 - Vietnam - Global Practice Guides — These landmark reforms round out Vietnam's earlier investment roadmap under Resolution No 50 (2019) and are reinforced by a series of new ...</t>
+          <t>Việt Nam đang thúc đẩy hạ tầng năng lượng thông qua Luật Điện lực 2024 và Quy hoạch điện VIII điều chỉnh, ưu tiên năng lượng tái tạo và cơ chế mua bán điện trực tiếp. Về mặt hành chính, Bộ Giao thông Vận tải đã được sáp nhập vào Bộ Xây dựng nhằm tối ưu hóa việc quản lý và thực hiện các dự án hạ tầng chiến lược.</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -7852,17 +7852,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>[Other] The economy: Re-balancing in 2026 - Theinvestor — Vietnam's infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going ...</t>
+          <t>베트남의 인프라 지출 성장률은 향후 연간 20-30%로 가속화될 전망이며, 정부는 인프라 투자를 GDP의 10% 수준까지 확대하는 것을 목표로 하고 있습니다. 이러한 인프라 확충은 부동산 시장 활성화와 소비 진작으로 이어져 2026년 베트남 경제 성장의 핵심 동력이 될 것으로 기대됩니다.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>[Other] The economy: Re-balancing in 2026 - Theinvestor — Vietnam's infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going ...</t>
+          <t>Vietnam's infrastructure spending is projected to surge by 20-30% annually, as the government aims to increase its share from 6% to 10% of GDP. This aggressive infrastructure push is expected to create a growth nexus with the real estate sector and domestic consumption, significantly supporting the country's GDP in 2026.</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>[Other] The economy: Re-balancing in 2026 - Theinvestor — Vietnam's infrastructure spending growth is expected to accelerate from circa 10% annually over the last decade to 20-30% per year going ...</t>
+          <t>Tăng trưởng chi tiêu hạ tầng của Việt Nam dự kiến sẽ tăng tốc lên mức 20-30% mỗi năm, với mục tiêu nâng tỷ trọng từ 6% lên 10% GDP. Sự thúc đẩy hạ tầng này sẽ tạo ra mối liên kết chặt chẽ với thị trường bất động sản và tiêu dùng nội địa, đóng vai trò là đòn bẩy quan trọng cho tăng trưởng kinh tế năm 2026.</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -7916,17 +7916,17 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through ... (관련: VN-EV-2030)</t>
+          <t>베트남은 제14차 당대회를 앞두고 주요 인프라, 교통 및 산업 프로젝트를 통해 경제 개혁과 투자 유치를 가속화하고 있습니다. 정부의 공공 투자 확대와 녹색 전환 정책에 힘입어 2026년 GDP 성장률은 7.2%에 달할 것으로 전망됩니다.</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through ... (Related: VN-EV-2030)</t>
+          <t>Vietnam is leveraging major infrastructure and industrial projects to drive economic growth and attract strategic investment flows ahead of the 14th National Party Congress. Supported by accelerated public investment and a green transition, the economy is projected to reach a GDP growth of 7.2% in 2026.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] Vietnam's Infrastructure Breakthrough: A Strategic Pillar for Growth — It is shaping expectations for economic reform, investment flows, and long-term development priorities, which are already taking shape through ... (Liên quan: VN-EV-2030)</t>
+          <t>Việt Nam đang đẩy mạnh các dự án hạ tầng, giao thông và công nghiệp trọng điểm nhằm thúc đẩy tăng trưởng và thu hút dòng vốn đầu tư trước thềm Đại hội Đảng lần thứ XIV. Với sự hỗ trợ từ đầu tư công và chuyển đổi xanh, nền kinh tế dự kiến đạt mức tăng trưởng GDP 7,2% vào năm 2026.</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -7980,17 +7980,17 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Tapping into Vietnam's High-Value Growth Ambition in 2026 — Vietnam is aiming for a high-value growth, supported by policies that promote productivity, innovation, and industrial upgrading.</t>
+          <t>베트남은 2026년까지 남북 고속철도 건설 가속화, 국제 철도망 강화, 하노이 및 호치민시 도시철도 확장을 포함한 대규모 인프라 현대화를 추진합니다. 또한 닌투안 원전 프로젝트 재개와 5G·6G 네트워크 구축을 통해 에너지 안보와 디지털 전환을 가속화할 계획입니다.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Tapping into Vietnam's High-Value Growth Ambition in 2026 — Vietnam is aiming for a high-value growth, supported by policies that promote productivity, innovation, and industrial upgrading.</t>
+          <t>Vietnam is accelerating its infrastructure development by 2026, focusing on the North-South high-speed railway, international rail links, and urban rail expansions in Hanoi and Ho Chi Minh City. The plan also includes reviving nuclear power projects and deploying 5G and 6G networks to support high-value economic growth.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>[Transport &amp; Infrastructure] Tapping into Vietnam's High-Value Growth Ambition in 2026 — Vietnam is aiming for a high-value growth, supported by policies that promote productivity, innovation, and industrial upgrading.</t>
+          <t>Việt Nam đang đẩy mạnh phát triển hạ tầng đến năm 2026, tập trung vào đường sắt tốc độ cao Bắc-Nam, kết nối đường sắt quốc tế và mở rộng đường sắt đô thị tại Hà Nội và TP.HCM. Kế hoạch này cũng bao gồm việc khởi động lại các dự án điện hạt nhân và triển khai mạng 5G, 6G để hỗ trợ tăng trưởng kinh tế giá trị cao.</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8044,17 +8044,17 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>[Other] Invest in Vietnam Infrastructure as a Long-Term Growth Driver — To invest in Vietnam infrastructure is to participate in a structural transformation that extends well beyond short-term economic cycles.</t>
+          <t>베트남의 인프라 개발은 도로, 항만, 에너지망 확충을 통해 장기적인 경제 성장을 견인하는 핵심 동력입니다. 이러한 투자는 건설, 물류, 금융 서비스 전반에 걸쳐 안정적인 수익원과 다변화된 투자 기회를 제공합니다.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>[Other] Invest in Vietnam Infrastructure as a Long-Term Growth Driver — To invest in Vietnam infrastructure is to participate in a structural transformation that extends well beyond short-term economic cycles.</t>
+          <t>Infrastructure development serves as a vital pillar for Vietnam's long-term economic expansion, focusing on transportation, energy, and digital networks. These large-scale projects offer investors stable, non-cyclical revenue streams through public-private partnerships and government-led initiatives.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>[Other] Invest in Vietnam Infrastructure as a Long-Term Growth Driver — To invest in Vietnam infrastructure is to participate in a structural transformation that extends well beyond short-term economic cycles.</t>
+          <t>Phát triển cơ sở hạ tầng là trụ cột quan trọng cho tăng trưởng kinh tế dài hạn của Việt Nam, tập trung vào mạng lưới giao thông, năng lượng và kỹ thuật số. Việc đầu tư vào lĩnh vực này mang lại cơ hội tiếp cận các nguồn thu nhập ổn định và ít biến động thông qua các dự án trọng điểm của chính phủ.</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8108,17 +8108,17 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] MoIT to ensure power supply security for 2026 — The Ministry of Industry and Trade has reaffirmed that Vietnam's power supply in 2026 will be fully secured.</t>
+          <t>베트남 산업통상부(MoIT)는 2026년 전력 공급 안보를 보장하기 위해 8.5~14.1%의 수요 성장을 반영한 전력 공급 계획을 승인했습니다. 1,200MW 규모의 붕앙 2 화력발전소가 상업 운전을 시작했으며, PV GAS의 재기화 용량 확대와 500kV 마이쩌우 변전소 업그레이드를 통해 전력망 안정성을 강화하고 있습니다.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] MoIT to ensure power supply security for 2026 — The Ministry of Industry and Trade has reaffirmed that Vietnam's power supply in 2026 will be fully secured.</t>
+          <t>Vietnam's Ministry of Industry and Trade has approved the 2026 national power supply plan to address load growth scenarios of up to 14.1% during extreme dry seasons. Key developments include the 1,200 MW Vung Ang 2 thermal power plant entering operation, doubled regasification capacity by PV GAS, and grid upgrades at the Mai Chau substation to prevent shortages in the North.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] MoIT to ensure power supply security for 2026 — The Ministry of Industry and Trade has reaffirmed that Vietnam's power supply in 2026 will be fully secured.</t>
+          <t>Bộ Công Thương đã phê duyệt kế hoạch cung ứng điện năm 2026 dựa trên kịch bản tăng trưởng phụ tải từ 8,5% đến 14,1% trong mùa khô khắc nghiệt. Các giải pháp chính bao gồm việc đưa nhà máy nhiệt điện Vũng Áng 2 (1.200 MW) vào vận hành, gấp đôi công suất tái hóa khí của PV GAS và nâng cấp trạm biến áp 500kV Mai Châu để đảm bảo an ninh năng lượng miền Bắc.</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8172,17 +8172,17 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-Russia energy cooperation: a strategic pillar in global ... — Coal imports reached nearly $1 billion in 2024, meeting around 10 per cent of Vietnam's demand, while fertilisers accounted for $228 million.</t>
+          <t>베트남-러시아 경제 포럼 2026에서 양국은 에너지 협력을 전략적 핵심 축으로 재확인하며, 혁신과 과학 기술 중심의 새로운 모델로의 전환을 강조했습니다. 석탄 및 석유 등 전통적 자원 공급 외에도 민간 원자력, 수소 에너지, 탄소 포집 및 저장 기술 등 신에너지 분야에서의 협력을 확대할 계획입니다.</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-Russia energy cooperation: a strategic pillar in global ... — Coal imports reached nearly $1 billion in 2024, meeting around 10 per cent of Vietnam's demand, while fertilisers accounted for $228 million.</t>
+          <t>At the Vietnam-Russia Economic Forum 2026, energy was highlighted as a strategic pillar for bilateral relations, moving toward a model driven by innovation and science. Beyond traditional oil and coal trade, the cooperation is expanding into civil nuclear energy, power system stability, hydrogen, and carbon capture to support Vietnam's 2050 net-zero goals.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-Russia energy cooperation: a strategic pillar in global ... — Coal imports reached nearly $1 billion in 2024, meeting around 10 per cent of Vietnam's demand, while fertilisers accounted for $228 million.</t>
+          <t>Tại Diễn đàn Kinh tế Việt Nam - Nga 2026, hợp tác năng lượng được xác định là trụ cột chiến lược, chuyển dịch từ mô hình truyền thống sang mô hình thúc đẩy bởi đổi mới sáng tạo và khoa học công nghệ. Hai bên định hướng mở rộng hợp tác sang các lĩnh vực mới như điện hạt nhân dân sự, năng lượng hydro và thu giữ carbon nhằm hỗ trợ mục tiêu phát thải ròng bằng 0 vào năm 2050.</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -8236,17 +8236,17 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Forum outlines pathways to accelerate green transition — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, bankability ...</t>
+          <t>베트남-호주 포럼에서는 베트남의 넷제로 목표 달성을 위해 3,680억 달러 규모의 기후 행동 자금이 필요하다고 강조하며 전력 시장 규제 완화를 촉구했습니다. 전문가들은 루프탑 태양광에 민간 자본이 유입될 수 있도록 시장을 개방하고 펌프식 수력 발전소 등을 활용한 에너지 저장 장치를 확충해야 한다고 제안했습니다.</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Forum outlines pathways to accelerate green transition — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, bankability ...</t>
+          <t>The Vietnam-Australia forum highlighted that Vietnam requires approximately $368 billion for climate action to meet its net-zero goals, emphasizing the need for market deregulation in the energy sector. Experts called for unleashing private capital into rooftop solar and utilizing the country's vast potential for pumped hydro sites to stabilize the green transition.</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Forum outlines pathways to accelerate green transition — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, bankability ...</t>
+          <t>Diễn đàn Việt Nam - Australia nhấn mạnh rằng Việt Nam cần khoảng 368 tỷ USD cho hành động khí hậu để đạt cam kết phát thải ròng bằng không và cần bãi bỏ quy định thị trường điện. Các chuyên gia đề xuất khơi thông vốn tư nhân vào điện mặt trời mái nhà và khai thác tiềm năng thủy điện tích năng để đẩy nhanh quá trình chuyển đổi năng lượng.</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -8300,17 +8300,17 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] EVN steps up investment in battery storage to support growing ... — Vietnam Electricity is accelerating the deployment of battery energy storage systems across its power network, as the country seeks to ... (관련: VN-EV-2030)</t>
+          <t>베트남 전력공사(EVN)는 재생 에너지의 급증에 대응하여 전력 시스템의 안정성을 높이기 위해 배터리 에너지 저장 시스템(BESS) 투자를 가속화하고 있습니다. 수정된 국가 전력 개발 계획(PDP8)에 따라 베트남은 2030년까지 10,000~16,300MW의 저장 용량 확보를 목표로 하며, 북부 전력 공사는 2026년 6월까지 305MW 규모의 BESS 프로젝트 완공을 추진 중입니다.</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] EVN steps up investment in battery storage to support growing ... — Vietnam Electricity is accelerating the deployment of battery energy storage systems across its power network, as the country seeks to ... (Related: VN-EV-2030)</t>
+          <t>Vietnam Electricity (EVN) is accelerating investment in Battery Energy Storage Systems (BESS) to maintain grid stability as renewable energy shares grow. Under the revised National Power Development Plan VIII, Vietnam aims for 10,000 MW to 16,300 MW of storage capacity by 2030, with several regional subsidiaries already launching pilot projects scheduled for completion by 2026.</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] EVN steps up investment in battery storage to support growing ... — Vietnam Electricity is accelerating the deployment of battery energy storage systems across its power network, as the country seeks to ... (Liên quan: VN-EV-2030)</t>
+          <t>Tập đoàn Điện lực Việt Nam (EVN) đang đẩy mạnh đầu tư vào hệ thống lưu trữ năng lượng bằng pin (BESS) nhằm đảm bảo ổn định hệ thống trong bối cảnh năng lượng tái tạo phát triển mạnh. Theo Quy hoạch điện VIII điều chỉnh, Việt Nam đặt mục tiêu đạt 10.000 MW đến 16.300 MW công suất lưu trữ vào năm 2030, với các dự án trọng điểm tại miền Bắc dự kiến hoàn thành vào tháng 6/2026.</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -8364,17 +8364,17 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Meeting Vietnam's energy moment: GE Vernova CEO — UK unveils toolkit to boost Vietnam green investment flows (March 30, 2026 | 13:45) ... Vinh Long kicks ahead with marine-energy approach (March ...</t>
+          <t>GE Vernova는 베트남의 전력 산업에 크게 투자하며 가스, 풍력, 송전 분야의 제조 시설을 확장하고 있습니다. 회사는 다양한 기술과 현지화, 인력 양성을 통해 베트남의 경제 성장과 탈탄소화를 지원할 계획입니다.</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Meeting Vietnam's energy moment: GE Vernova CEO — UK unveils toolkit to boost Vietnam green investment flows (March 30, 2026 | 13:45) ... Vinh Long kicks ahead with marine-energy approach (March ...</t>
+          <t>GE Vernova is expanding its investment in Vietnam's power sector, establishing factories for gas, wind, and grid technologies. The company aims to help Vietnam meet its economic growth and decarbonization targets through technology, partnership, and workforce initiatives.</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Meeting Vietnam's energy moment: GE Vernova CEO — UK unveils toolkit to boost Vietnam green investment flows (March 30, 2026 | 13:45) ... Vinh Long kicks ahead with marine-energy approach (March ...</t>
+          <t>GE Vernova đang mở rộng đầu tư vào lĩnh vực điện tại Việt Nam với các nhà máy sản xuất về khí, điện gió, và lưới điện. Công ty đặt mục tiêu hỗ trợ Việt Nam phát triển kinh tế và giảm phát thải thông qua đa dạng công nghệ, hợp tác và đào tạo nguồn nhân lực.</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's green push requires further hurdles to clear — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, ...</t>
+          <t>베트남의 녹색 에너지 전환은 자본과 기술의 가용성에도 불구하고 규제 프레임워크의 미비로 인해 어려움을 겪고 있습니다. 전문가들은 프로젝트 파이낸싱으로의 전환, 배터리 에너지 저장 장치(BESS)의 도입, 그리고 투자 적격성을 높이기 위한 혼합 금융 솔루션의 필요성을 강조했습니다.</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's green push requires further hurdles to clear — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, ...</t>
+          <t>Vietnam's transition to green energy is currently hindered by a regulatory gap that prevents near-ready projects from becoming fully bankable investments. Industry leaders emphasize the need for innovative financial structures like project finance and "orange bonds," alongside the scaling of battery energy storage systems (BESS) and direct power purchase agreements (DPPAs).</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's green push requires further hurdles to clear — Vietnam's energy transition is entering a decisive phase, where ambition is rapidly giving way to the harder realities of execution, ...</t>
+          <t>Quá trình chuyển đổi năng lượng xanh của Việt Nam đang gặp trở ngại do khung pháp lý chưa hoàn thiện, khiến các dự án tiềm năng khó trở thành khoản đầu tư khả thi về mặt tài chính. Các chuyên gia nhấn mạnh tầm quan trọng của việc cải cách quy định, áp dụng cơ chế mua bán điện trực tiếp (DPPA) và các giải pháp tài chính hỗn hợp để thu hút vốn đầu tư quốc tế.</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -8492,17 +8492,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Safe operations ensured during energy transition — Vietnam's central region is increasingly emerging as a critical balancing hub within the national power system.</t>
+          <t>베트남 전력공사 제2전력전송공사(PTC2)는 중부 지역의 안정적인 전력 공급을 위해 2026년 1,280만 달러 규모의 14개 프로젝트를 추진하고 있습니다. 다낭 변전소 확장 및 500kV 스위치야드 개선을 포함하여 에너지 전환기 동안의 전력망 안전과 효율성을 높이는 데 주력하고 있습니다.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Safe operations ensured during energy transition — Vietnam's central region is increasingly emerging as a critical balancing hub within the national power system.</t>
+          <t>Vietnam's Power Transmission Corporation 2 (PTC2) is implementing 14 infrastructure projects in 2026 with a $12.8 million investment to ensure grid stability in the central region. Key initiatives include upgrading the Danang substation, adopting digital transformation tools like drones and LiDAR, and addressing challenges posed by new safety regulations and expressway developments.</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Safe operations ensured during energy transition — Vietnam's central region is increasingly emerging as a critical balancing hub within the national power system.</t>
+          <t>Công ty Truyền tải điện 2 (PTC2) đang triển khai 14 dự án hạ tầng trong năm 2026 với tổng vốn đầu tư 12,8 triệu USD nhằm đảm bảo an ninh năng lượng tại miền Trung. Các hạng mục chính bao gồm nâng cấp trạm biến áp 500kV Đà Nẵng, ứng dụng công nghệ số như flycam và LiDAR để kiểm tra lưới điện, đồng thời chuẩn bị sẵn sàng ứng phó với thiên tai và các quy định an toàn mới.</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -8556,17 +8556,17 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] PM issues directive to ensure power supply in 2026–30, focusing on ... — HÀ NÔI — Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business ...</t>
+          <t>베트남 팜 민 찐 총리는 2026-30년 기간 동안 연간 12-13% 이상 증가할 것으로 예상되는 전력 수요에 대응하기 위해 무정전 전력 공급을 지시하는 지침 제01/CT-TTg호를 발표했습니다. 정부는 북부 지역의 전력망 확충, LNG 발전소, 해상 풍력 및 닌투언 원자력 발전소 준비 가속화를 통해 에너지 안보를 확보하고 투명한 전력 시장을 구축할 계획입니다.</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] PM issues directive to ensure power supply in 2026–30, focusing on ... — HÀ NÔI — Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business ...</t>
+          <t>Prime Minister Phạm Minh Chính issued Directive No 01/CT-TTg to guarantee uninterrupted power supply for the 2026-30 period, targeting a 12-13% annual increase in electricity demand. The strategy focuses on accelerating major infrastructure projects such as LNG-fired plants, offshore wind, and the Ninh Thuận nuclear power plant while establishing a competitive and transparent energy market.</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] PM issues directive to ensure power supply in 2026–30, focusing on ... — HÀ NÔI — Prime Minister Phạm Minh Chính has issued a directive urging efforts to ensure adequate electricity supply for production, business ...</t>
+          <t>Thủ tướng Chính phủ Phạm Minh Chính đã ban hành Chỉ thị số 01/CT-TTg nhằm đảm bảo cung ứng điện ổn định cho giai đoạn 2026-30, đáp ứng nhu cầu điện dự kiến tăng từ 12-13% mỗi năm. Các biện pháp then chốt bao gồm đẩy nhanh tiến độ các dự án điện khí LNG, điện gió ngoài khơi, khởi động lại dự án điện hạt nhân Ninh Thuận và phát triển thị trường điện cạnh tranh, minh bạch.</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -8620,17 +8620,17 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] FDI surges in Vietnam as Q1 capital climbs 43 per cent on-year — In total, Vietnam's overseas investment (including new and adjusted capital) reached $619.9 million in the first three months of 2026, up 2.6 ...</t>
+          <t>2026년 1분기 베트남의 외국인직접투자(FDI) 유치액은 전년 동기 대비 42.9% 증가한 152억 달러를 기록했습니다. 싱가포르와 한국이 주요 투자국이며, 제조업과 가공업 분야가 전체 투자의 약 70%를 차지하며 성장을 주도했습니다.</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] FDI surges in Vietnam as Q1 capital climbs 43 per cent on-year — In total, Vietnam's overseas investment (including new and adjusted capital) reached $619.9 million in the first three months of 2026, up 2.6 ...</t>
+          <t>Vietnam's foreign direct investment (FDI) saw a significant 42.9% year-on-year increase in Q1 2026, reaching a total registered capital of $15.2 billion. Singapore and South Korea emerged as the top investors, with the manufacturing and processing sector attracting the largest share of capital.</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>[Finance &amp; Investment] FDI surges in Vietnam as Q1 capital climbs 43 per cent on-year — In total, Vietnam's overseas investment (including new and adjusted capital) reached $619.9 million in the first three months of 2026, up 2.6 ...</t>
+          <t>Trong quý 1 năm 2026, tổng vốn đầu tư trực tiếp nước ngoài (FDI) vào Việt Nam đạt 15,2 tỷ USD, tăng 42,9% so với cùng kỳ năm trước. Singapore và Hàn Quốc là những nhà đầu tư lớn nhất, trong khi ngành công nghiệp chế biến, chế tạo tiếp tục dẫn đầu về khả năng thu hút vốn.</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -8684,17 +8684,17 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Solar power could save Vietnam $600 million in fossil fuel imports — Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports.</t>
+          <t>베트남은 이란 전쟁으로 인한 화석 연료 가격 급등 속에서 태양광 발전을 통해 약 5억 9,400만 달러의 수입 비용을 절감할 수 있을 것으로 분석됩니다. 2024년 기준 베트남의 재생에너지 발전 비중은 약 13%에 도달하며 아세안 주요 국가들을 앞서고 있습니다.</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Solar power could save Vietnam $600 million in fossil fuel imports — Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports.</t>
+          <t>Solar power is projected to save Vietnam approximately $594 million in coal and gas import costs amid soaring energy prices caused by the conflict in Iran. In 2024, Vietnam's solar and wind generation reached 38.7 TWh, accounting for 13% of its power mix, the highest among the ASEAN-5 nations.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Solar power could save Vietnam $600 million in fossil fuel imports — Solar power may help Vietnam avoid a total $594 million from potential coal and gas imports.</t>
+          <t>Điện mặt trời có thể giúp Việt Nam tiết kiệm khoảng 594 triệu USD chi phí nhập khẩu than và khí đốt trong bối cảnh giá năng lượng tăng cao do xung đột tại Iran. Tính đến năm 2024, sản lượng điện mặt trời và điện gió của Việt Nam đạt 38,7 TWh, chiếm 13% tổng sản lượng điện, dẫn đầu khu vực ASEAN-5.</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9199,17 +9199,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부는 2030년까지의 국가 전력 개발 계획(PDP8)을 승인하며 에너지 안보 확보와 탈탄소화를 목표로 설정했습니다. 이 계획은 석탄 화력을 단계적으로 폐지하고 해상 풍력 및 태양광과 같은 재생 에너지 비중을 2050년까지 최대 71.5%까지 확대하는 내용을 담고 있습니다.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam has officially approved the National Power Development Plan VIII (PDP8), targeting a transition towards renewable energy and national energy security through 2030. The plan prioritizes the phasing out of coal-fired power by 2050 while significantly expanding wind, solar, and gas-to-hydrogen capacities to meet a 7% annual GDP growth demand.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] National Power Development Plan VIII (PDP-8) - Vntpa — To develop the power sources and transmission grid at the voltage levels of 220kV or higher, renewable and new energy industries and services in Viet Nam for ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã phê duyệt Quy hoạch phát triển điện lực quốc gia thời kỳ 2021 - 2030 (Quy hoạch điện VIII) nhằm đảm bảo an ninh năng lượng và chuyển đổi xanh. Kế hoạch tập trung vào việc loại bỏ dần điện than vào năm 2050, đồng thời thúc đẩy mạnh mẽ năng lượng tái tạo và điện khí để phục vụ mục tiêu tăng trưởng kinh tế.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -9259,17 +9259,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부는 2030년까지 발전 용량을 150GW로 확대하고 2050년 탄소 중립을 달성하기 위한 제8차 국가전력개발계획(PDP VIII)을 승인했습니다. 이 계획은 석탄 화력 발전에서 재생 에너지, 수소, 암모니아 및 배터리 저장 시스템으로의 대대적인 전환을 목표로 하며, 인프라 구축을 위해 향후 30년간 약 7,000억 달러의 투자가 필요할 것으로 예상됩니다.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam has approved the PDP VIII, an ambitious energy roadmap targeting 150 GW of installed capacity by 2030 and Net Zero emissions by 2050. The plan shifts focus from coal to renewables and emerging technologies like hydrogen and battery storage, requiring approximately $700 billion in investment over the next three decades for generation and grid infrastructure.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eighth National Power Development Plan (PDP VIII) - PwC — PDP VIII presents an ambitious shift for Vietnam's generation mix away from coal, and heavily weighted towards in renewables and new technologies. (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã phê duyệt Quy hoạch điện VIII (PDP VIII), đặt mục tiêu nâng công suất lắp đặt lên 150 GW vào năm 2030 và hướng tới phát thải ròng bằng 0 vào năm 2050. Kế hoạch này tập trung chuyển đổi từ điện than sang năng lượng tái tạo, hydro và lưu trữ năng lượng, với nhu cầu vốn đầu tư dự kiến khoảng 700 tỷ USD trong 3 thập kỷ tới cho nguồn điện và lưới điện.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -9323,17 +9323,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>2023년 5월 15일 베트남 정부는 '제8차 국가전력개발계획(PDP8)'을 발표하여 2021~2030년과 2050년 비전을 제시했습니다. PDP8은 석탄 발전 용량을 약 13GW 감축하고, 2050년까지 모든 석탄발전소는 대체 연료로 전환하거나 퇴출하도록 요구합니다. 2030년에는 재생에너지가 전체 발전용량의 48%, 2050년에는 약 63%를 차지할 계획입니다.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>On May 15, 2023, the Vietnamese government released the 8th National Power Development Plan (PDP8) covering 2021-2030 and a vision to 2050. The plan cancels about 13GW of planned coal capacity, requires all coal plants to be converted to alternative fuels or shut down by 2050, and aims for renewables to provide 48% of installed capacity by 2030 and about 63% by 2050.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Eight National Power Development Plan (PDP8) — The PDP8 presents Vietnam's long-term objective to form an energy ecosystem based on renewable energies. The development of wind and solar power ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Ngày 15/5/2023, Chính phủ Việt Nam đã công bố Quy hoạch Phát triển điện lực quốc gia lần thứ 8 (PDP8) cho giai đoạn 2021-2030, tầm nhìn đến 2050. PDP8 loại bỏ khoảng 13GW điện than, yêu cầu toàn bộ nhà máy điện than phải chuyển đổi sang nhiên liệu thay thế hoặc ngừng hoạt động trước năm 2050 và đặt mục tiêu năng lượng tái tạo chiếm 48% công suất lắp đặt vào năm 2030, và khoảng 63% vào năm 2050.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -9387,17 +9387,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (관련: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam Revised Power Development Plan VIII</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (Related: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam Revised Power Development Plan VIII</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Revised Power Development Plan VIII — Vietnam's April 2025 revision to Power Development Plan VIII accelerates renewable energy targets and reintroduces nuclear power projects. (Liên quan: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam Revised Power Development Plan VIII</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -9447,17 +9447,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남의 제8차 국가전력개발계획(PDP8)은 2050년 탄소 중립 달성을 목표로 화석 연료에서 재생 에너지 중심의 전력 체계로의 전환을 가속화하고 있습니다. 정부는 옥상 태양광 및 직접전력구매계약(DPPA) 도입을 통해 투자를 촉진하고 있으나, 송전망 미비와 가격 책정 프레임워크의 불확실성은 여전히 해결해야 할 과제로 남아 있습니다.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam's Power Development Plan 8 (PDP8) drives a strategic shift toward renewable energy to achieve net-zero emissions by 2050. While new policies like Direct Power Purchase Agreements (DPPA) and expanded solar incentives are attracting investment, the transition faces hurdles including grid congestion and unsupportive pricing structures.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's Power Development Plan 8 (PDP8) - Speeda ASEAN — Vietnam's Power Development Plan 8 (PDP8) sets bold targets for renewables, but coal reliance, pricing, and grid issues challenge its green energy shift. (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Quy hoạch điện VIII (PDP8) của Việt Nam định hướng chuyển đổi chiến lược từ năng lượng hóa thạch sang năng lượng tái tạo nhằm mục tiêu phát thải ròng bằng 0 vào năm 2050. Mặc dù các chính sách như cơ chế mua bán điện trực tiếp (DPPA) và ưu đãi điện mặt trời mái nhà đang mở ra cơ hội đầu tư lớn, ngành năng lượng vẫn đối mặt với thách thức về hạ tầng lưới điện và khung giá điện chưa phù hợp.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -9511,17 +9511,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (관련: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부는 2030년까지 전력 설비 용량을 150GW로 확충하고 2050년 탄소 중립을 달성하기 위한 제8차 국가 전력개발계획(PDP8)을 승인했습니다. 이 계획은 석탄 화력 발전을 점진적으로 폐지하고 해상 풍력 및 LNG 발전 비중을 대폭 확대하기 위해 약 1,347억 달러의 투자를 필요로 합니다.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (Related: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>Vietnam has approved the Power Development Plan VIII (PDP8), targeting a grid expansion to 150 GW by 2030 and carbon neutrality by 2050. The plan requires $134.7 billion in investment to shift from coal to cleaner energy sources, specifically prioritizing offshore wind and LNG infrastructure.</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam Approves Power Development Plan for Cleaner Fuels — Power Development Plan VIII ("PDP8") calls for expansions to renewable energy generation and development of LNG facilities to aid a gradual ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã phê duyệt Quy hoạch điện VIII (PDP8), đặt mục tiêu nâng công suất lưới điện lên 150 GW vào năm 2030 và đạt phát thải ròng bằng 0 vào năm 2050. Kế hoạch này yêu cầu khoản đầu tư 134,7 tỷ USD để chuyển dịch từ điện than sang các nguồn năng lượng sạch hơn như điện gió ngoài khơi và khí LNG.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -9575,17 +9575,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (관련: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부는 PDP8 목표 달성을 위해 LNG 발전소 건설을 가속화하고 있으며, 최근 시행령 제56호(Decree 56)를 통해 연료비 전가 메커니즘과 최소 65%의 전력 구매 보장책을 도입했습니다. 이는 2030년까지 15개의 LNG 발전소를 확보하고 전력 용량을 150,500 MW로 확대하기 위한 조치입니다.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (Related: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>The Vietnamese government has introduced Decree 56 to support the development of 15 LNG power plants under the Amended PDP8, aiming for a total capacity of 150,500 MW by 2030. The new regulations provide a fuel cost pass-through mechanism and a 10-year guarantee for offtaking at least 65% of electricity output to ensure project bankability.</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's National Power Development Plan For LNG Power Plants — Under PDP8, Vietnam has no plan to develop NEW LNG power plants after 2035. Potential Backup Locations: Thai Binh, Nam Dinh, Nghi Son, Quynh ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8, VN-EV-2030)</t>
+          <t>Chính phủ Việt Nam đã ban hành Nghị định 56 nhằm hỗ trợ phát triển 15 nhà máy điện LNG theo Quy hoạch điện VIII (PDP8) sửa đổi, hướng tới mục tiêu đạt tổng công suất 150.500 MW vào năm 2030. Quy định mới thiết lập cơ chế chuyển tiếp chi phí nhiên liệu và cam kết sản lượng hợp đồng tối thiểu 65% để tháo gỡ khó khăn cho các nhà đầu tư.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -9639,17 +9639,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남 정부의 제8차 국가전력개발계획(PDP 8) 초안은 2030년까지 태양광 및 풍력 발전 용량을 대폭 확대하고 탄소 배출을 줄이는 것을 목표로 합니다. 특히 노후화된 전력망 문제를 해결하기 위해 고전압 송전선 건설과 인프라 현대화를 우선순위로 두어 재생에너지 통합을 지원할 계획입니다.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam's draft Power Development Plan 8 (PDP 8) aims to significantly increase solar and wind capacity to 18.6 GW and 18.0 GW respectively by 2030 to reduce coal dependency. The plan prioritizes grid modernization, including a 461-mile transmission line project, to address current congestion and successfully integrate higher shares of renewable energy.</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam's latest power development plan focuses on expanding ... — Under the draft PDP 8, Vietnam plans to increase solar capacity to 18.6 GW and wind capacity to 18.0 GW by 2030. Vietnam's underdeveloped grid ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Dự thảo Quy hoạch phát triển điện lực quốc gia 8 (PDP 8) của Việt Nam tập trung vào việc mở rộng công suất điện mặt trời và điện gió lên lần lượt 18,6 GW và 18,0 GW vào năm 2030. Kế hoạch này ưu tiên nâng cấp hạ tầng lưới điện và xây dựng các đường dây truyền tải cao thế để khắc phục tình trạng quá tải và hỗ trợ tích hợp năng lượng tái tạo.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -9703,17 +9703,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (관련: VN-PWR-PDP8)</t>
+          <t>베트남 정부가 재생에너지 전력 구매 가격을 소급 삭감하자 한국, EU 등 5개국 상공회의소가 공동 서한을 통해 법적 대응을 예고했습니다. 투자자들은 약속된 보조금이 지급되지 않을 경우 국제 분쟁 해결 절차를 밟을 수 있다고 경고하며 정부의 우호적인 해결책 마련을 촉구했습니다.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (Related: VN-PWR-PDP8)</t>
+          <t>Foreign investors from five major chambers of commerce have threatened legal action against Vietnam due to retroactive cuts in electricity tariffs for wind and solar projects. The dispute involves 12 gigawatts of capacity, with investors warning of potential defaults and multibillion-dollar losses if original payment obligations are not met.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Foreign investors threaten legal action against Vietnam over ... — Foreign investors may take legal action if Vietnam does not fully pay electricity tariffs agreed with multiple wind and solar projects, ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Năm hiệp hội thương mại quốc tế đã cảnh báo sẽ thực hiện các biện pháp pháp lý nếu Chính phủ Việt Nam không thực hiện cam kết về giá mua điện tái tạo. Tranh chấp phát sinh sau khi Việt Nam cắt giảm giá ưu đãi (FIT) đã thỏa thuận trước đó, gây ảnh hưởng đến các dự án có tổng công suất lên tới 12 GW.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -9767,17 +9767,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (관련: VN-PWR-PDP8)</t>
+          <t>팜 민 찐 총리는 COP26에서 2050년까지 넷제로 달성을 재확인하며 재생 에너지 발전을 최우선 과제로 설정했습니다. 특히 PDP8 계획에 따라 도시형 태양광 에너지의 대안을 모색하며 에너지 인프라 확충에 집중하고 있습니다.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (Related: VN-PWR-PDP8)</t>
+          <t>Prime Minister Phạm Minh Chính has reaffirmed Vietnam's commitment to achieving net-zero emissions by 2050, prioritizing the development of renewable energy sources. This initiative aligns with the Power Development Plan 8 (PDP8) to explore alternatives for urban solar energy and enhance the national power infrastructure.</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] An alternative to urban solar energy | Vietnam Today - YouTube — ... 2026, prioritising renewable energy. But while rooftop solar is expanding, many urban residents lack the space or budget for traditional ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Thủ tướng Phạm Minh Chính khẳng định lại cam kết của Việt Nam về mức phát thải ròng bằng 0 vào năm 2050 tại COP26, ưu tiên phát triển năng lượng tái tạo. Đây là một phần trong kế hoạch Quy hoạch điện VIII (PDP8) nhằm tìm kiếm giải pháp thay thế cho năng lượng mặt trời đô thị và cải thiện hạ tầng năng lượng.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -9831,17 +9831,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (관련: VN-PWR-PDP8)</t>
+          <t>베트남은 2030년까지 풍력 발전 용량을 6,000MW로 확대한다는 야심찬 목표를 세우고 비엔투안 및 쭝남 풍력 발전소와 같은 대규모 프로젝트를 추진하고 있습니다. 정부는 육상 및 해상 풍력에 대한 발전차액지원제도(FiT)와 국제적 파트너십을 통해 투자를 유치하고 있으나, 전력망 인프라 개선이 주요 과제로 남아 있습니다.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (Related: VN-PWR-PDP8)</t>
+          <t>Vietnam is rapidly expanding its wind energy sector with a target of 6,000 MW by 2030, supported by significant projects like the Binh Thuan and Trung Nam plants. The government utilizes Feed-in Tariffs (FiT) and international partnerships to drive growth, though challenges in grid infrastructure and regulatory frameworks persist.</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Gusty growth: Vietnam's remarkable wind energy story - Eco-Business — The country has made substantial investments in renewable energy, particularly wind power, to meet its growing energy demands and reduce ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Việt Nam đang nhanh chóng mở rộng lĩnh vực năng lượng gió với mục tiêu đạt công suất 6.000 MW vào năm 2030, được hỗ trợ bởi các dự án lớn như nhà máy Bình Thuận và Trung Nam. Chính phủ áp dụng cơ chế giá bán điện (FiT) và hợp tác quốc tế để thúc đẩy đầu tư, dù vẫn còn những thách thức về hạ tầng lưới điện và khung pháp lý.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -9895,17 +9895,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남은 과거 보조금 중심의 급격한 성장에서 벗어나 규제 준수와 시장 중심의 규율을 강조하는 에너지 전환의 새로운 단계에 진입했습니다. 직접전력구매계약(DPPA)과 제8차 국가전력개발계획(PDP8)을 통해 공급과 수요의 균형을 맞추고 전력망 안정을 도모하며 장기적인 투자 신뢰도를 구축하고 있습니다.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam is transitioning from a period of rapid, subsidy-driven renewable energy growth to a more disciplined, market-based approach under the DPPA framework and PDP8. The focus has shifted from mere development speed to long-term system stability, regulatory compliance, and aligning generation with grid capacity to ensure financial and operational sustainability.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Bloomberg Businessweek Vietnam 02.2026 Featured Issue ... — Generous FiTs triggered a surge in solar and wind development, transforming the country from a marginal player into a regional clean energy ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Việt Nam đang chuyển dịch từ giai đoạn phát triển năng lượng tái tạo nhanh chóng dựa trên trợ giá (FiT) sang mô hình dựa trên kỷ luật thị trường và cơ chế DPPA. Quá trình này ưu tiên tính ổn định của hệ thống, tuân thủ quy định pháp luật và sự phù hợp với Quy hoạch điện VIII (PDP8) thay vì chỉ tập trung vào tốc độ tăng trưởng.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -9959,17 +9959,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남은 제8차 국가전력개발계획(PDP8)에 따라 2030년까지 태양광 73GW 및 육상 풍력 38GW 확보를 목표로 청정에너지 전환을 가속화하고 있습니다. 과거 고정가격매입제도(FiT)의 성공을 발판 삼아, 이제는 직접전력구매계약(DPPA)과 경쟁 입찰 도입을 통해 시장 중심의 지속 가능한 에너지 인프라 구축에 집중하고 있습니다.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam is accelerating its clean energy transition under the revised PDP8, aiming for 73GW of solar and 38GW of onshore wind capacity by 2030. Following a rapid FiT-driven expansion, the sector is now shifting toward sustainable models like Direct Power Purchase Agreements (DPPA) and competitive auctions to ensure financial stability for the state utility.</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] From boom to balance in Vietnam's clean energy transition - IEEFA — Vietnamese authorities are looking to retroactively revise purchase prices for 173 solar and wind projects, reducing revenues by 25% to 46%, ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Việt Nam đang đẩy nhanh quá trình chuyển đổi năng lượng sạch theo Quy hoạch điện VIII (PDP8) sửa đổi, hướng tới mục tiêu 73GW điện mặt trời và 38GW điện gió trên bãi vào năm 2030. Sau giai đoạn bùng nổ nhờ giá FiT, ngành năng lượng đang chuyển sang các mô hình bền vững hơn như cơ chế mua bán điện trực tiếp (DPPA) và đấu thầu cạnh tranh để đảm bảo an ninh tài chính.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (관련: VN-PWR-PDP8, VN-GAS-PDP8)</t>
+          <t>베트남은 동나이성에 총 1624MW 규모의 첫 액체천연가스(LNG) 발전소인 년짝 3, 4호기를 14억 달러를 투입하여 완공했습니다. 이 시설은 국가 전력 발전 계획에 따른 향후 13개 LNG 프로젝트의 모델이 되어 남부 지역의 전력망 안정화와 2050년 탄소 중립 목표 달성을 지원할 예정입니다.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (Related: VN-PWR-PDP8, VN-GAS-PDP8)</t>
+          <t>Vietnam has inaugurated its first LNG power plants, the Nhon Trach 3 and 4 facilities in Dong Nai Province, built by Petrovietnam with a $1.4 billion investment. These plants provide a combined 1,624 MW capacity to stabilize the grid and serve as a template for 13 additional LNG projects under the national power development plan.</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam inaugurates USD1.4 billion LNG power plants in energy ... — LNG-fired electricity generation reduces carbon emissions by roughly 40 per cent compared with coal and 30 per cent compared with oil, ... (Liên quan: VN-PWR-PDP8, VN-GAS-PDP8)</t>
+          <t>Việt Nam đã khánh thành hai nhà máy điện khí LNG đầu tiên là Nhơn Trạch 3 và Nhơn Trạch 4 tại tỉnh Đồng Nai với tổng vốn đầu tư 1,4 tỷ USD. Dự án có tổng công suất 1.624 MW này đóng vai trò quan trọng trong việc đảm bảo an ninh năng lượng quốc gia và là hình mẫu cho 13 dự án LNG tiếp theo trong quy hoạch điện lực.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -10087,17 +10087,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (관련: VN-PWR-PDP8)</t>
+          <t>베트남의 한 신재생 에너지 엔지니어링 기업이 송배전 및 재생 에너지 시스템을 위한 스마트 그리드와 고급 기술 솔루션을 보유한 국제 파트너를 찾고 있습니다. 이 협력은 베트남의 제8차 국가전력개발계획(PDP8) 목표에 부합하며, 전력망의 운영 신뢰성을 높이고 자산 관리를 최적화하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (Related: VN-PWR-PDP8)</t>
+          <t>A Vietnamese renewable energy company is seeking international partners to provide smart-grid and advanced technology solutions for power transmission and distribution systems. Aligned with the VN-PWR-PDP8 objectives, this partnership aims to improve grid reliability and optimize asset management through commercial or technical cooperation agreements.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam-based energy company seeks smart-grid and power ... — It is seeking technology partners offering smart-grid and advanced solutions for transmission, distribution, and renewable energy systems under ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Một công ty năng lượng tái tạo tại Việt Nam đang tìm kiếm đối tác quốc tế cung cấp các giải pháp lưới điện thông minh và công nghệ tiên tiến cho hệ thống truyền tải và phân phối điện. Phù hợp với định hướng Quy hoạch điện VIII (PDP8), sự hợp tác này tập trung vào việc cải thiện độ tin cậy vận hành và tối ưu hóa quản lý tài sản năng lượng.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -10147,17 +10147,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (관련: VN-PWR-PDP8)</t>
+          <t>베트남은 2025년 4월 승인된 개정 제8차 국가전력개발계획(PDP8)에 따라 LNG, 재생에너지 및 원자력 발전을 포함한 에너지 믹스 확대를 추진하고 있습니다. 이번 계획은 BESS 용량을 최대 16,300MW로 늘리고 직접전력구매계약(DPPA) 도입을 통해 시장 중심의 전력 공급 체계를 구축하는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (Related: VN-PWR-PDP8)</t>
+          <t>Vietnam has updated its Power Development Plan 8 (PDP8) to aggressively expand LNG, solar, wind, and nuclear energy capacity to meet surging electricity demand. The revised framework introduces market-based pricing, supports Direct Power Purchase Agreements (DPPAs), and significantly increases targets for Battery Energy Storage Systems (BESS) to ensure grid stability.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Vietnam: Power Sector Snapshot - Norton Rose Fulbright — Vietnam expects to focus on a build out of a smart grid capable of ... Việt Nam outlines three 2026 power supply scenarios amid growing electricity demand. (Liên quan: VN-PWR-PDP8)</t>
+          <t>Việt Nam đã phê duyệt điều chỉnh Quy hoạch điện VIII (PDP8) với mục tiêu đẩy mạnh phát triển điện khí LNG, năng lượng tái tạo và tái khởi động điện hạt nhân. Các chính sách mới tập trung vào cơ chế mua bán điện trực tiếp (DPPA), phát triển hệ thống lưu trữ năng lượng (BESS) và cải thiện tính khả thi về tài chính cho các dự án năng lượng.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -10207,17 +10207,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (관련: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>베트남은 2050년 넷제로 배출 목표와 제8차 전력개발계획(PDP8)에 발맞추어 2030년까지의 스마트 그리드 로드맵을 업데이트했습니다. 이 계획은 송전망 현대화, 신재생 에너지 통합, 변전소 자동화 및 사이버 보안 강화를 우선순위로 두며, 장기적으로는 전기차 충전 인프라와 가상 발전소(VPP) 도입을 지원합니다.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (Related: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Vietnam has updated its Smart Grid Development Roadmap to 2030 with a vision to 2050 to align with PDP8 and Net Zero commitments. The plan prioritizes grid modernization, substation automation, and SCADA/EMS upgrades to integrate renewable energy, while also establishing frameworks for electric vehicle integration and advanced metering infrastructure.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] [PDF] Development of Vietnam Smart Grid Roadmap for period up to year ... — The Updated Smart Grid Roadmap will benefit key stakeholders, including ERAV, Electricity of Viet. Nam (EVN), power generation companies, transmission and ... (Liên quan: VN-PWR-PDP8, VN-EV-2030)</t>
+          <t>Việt Nam đã cập nhật Lộ trình phát triển Lưới điện thông minh đến năm 2030, tầm nhìn đến năm 2050 nhằm phù hợp với Quy hoạch điện VIII và cam kết Net Zero. Kế hoạch tập trung ưu tiên hiện đại hóa hệ thống điều khiển, tự động hóa trạm biến áp và tăng cường an ninh mạng để tích hợp năng lượng tái tạo, đồng thời chuẩn bị hạ tầng cho xe điện và các nguồn năng lượng phân tán.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -10271,17 +10271,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (관련: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>베트남 정치국은 2030년까지 국가 에너지 안보를 보장하기 위한 결의안 제70-NQ/TW호를 발표하고 민간 및 외국인 투자를 가로막는 제도적 장벽을 제거하기로 했습니다. 이 결의안은 재생 에너지 비중을 30%까지 확대하고 닌투언 원자력 발전소 건설을 재개하는 등 에너지 믹스 다양화와 탄소 중립 목표 달성을 강조합니다.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (Related: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Vietnam's Politburo has issued Resolution 70-NQ/TW to enhance national energy security by 2030, specifically targeting the removal of institutional barriers to attract private and international capital. The directive prioritizes renewable energy growth, smart grid development, and the expedited revival of nuclear power projects like Ninh Thuan 1 and 2.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] VIETNAM-RESOLUTION 70-NQ/TW-2025 FACILITATES CAPITAL ... — Nuclear Power Development: Urges expedited implementation of the Ninh Thuận 1 and 2 nuclear power plants by 2030–2035, with opportunities for ... (Liên quan: VN-PWR-PDP8, VN-REN-NPP-2050, VN-EV-2030)</t>
+          <t>Bộ Chính trị đã ban hành Nghị quyết 70-NQ/TW nhằm đảm bảo an ninh năng lượng quốc gia đến năm 2030, tập trung tháo gỡ các rào cản thể chế để thu hút vốn đầu tư tư nhân và quốc tế. Nghị quyết ưu tiên phát triển năng lượng tái tạo chiếm 25-30% tổng cung và thúc đẩy triển khai các dự án điện hạt nhân Ninh Thuận 1 và 2 trong giai đoạn 2030-2035.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -10331,17 +10331,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (관련: VN-PWR-PDP8)</t>
+          <t>독일 경제협력개발부(BMZ)가 자금을 지원하는 SGREEE 프로젝트는 베트남 전력 규제청(ERAV)과 협력하여 국가 전력망의 현대화와 자동화를 추진하고 있습니다. 이 사업은 재생 에너지 통합을 확대하고 에너지 효율을 높이기 위한 스마트 그리드 로드맵 이행과 전력 시스템의 디지털화를 지원합니다.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (Related: VN-PWR-PDP8)</t>
+          <t>The SGREEE project, funded by BMZ and partnered with ERAV, supports the modernization and automation of Vietnam's national power grid. It focuses on implementing the Smart Grid Roadmap to facilitate the integration of renewable energy and enhance energy efficiency through digitalization and system flexibility.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>[Power &amp; Energy] Smart Grids for Renewable Energy and Energy Efficiency - ESP — The 'Smart Grids for Renewable Energy and Energy Efficiency (SGREEE)' project is supporting the Government of Viet Nam in the implementation of its Smart Grid ... (Liên quan: VN-PWR-PDP8)</t>
+          <t>Dự án SGREEE, do BMZ tài trợ và hợp tác với ERAV, hỗ trợ Chính phủ Việt Nam hiện đại hóa và tự động hóa hệ thống truyền tải và phân phối điện quốc gia. Dự án tập trung vào việc thực hiện Lộ trình Lưới điện thông minh nhằm tích hợp năng lượng tái tạo và nâng cao hiệu quả năng lượng thông qua chuyển đổi số.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -10486,17 +10486,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>RTI International은 베트남의 산업 위험 연구를 통해 대기 및 수질 오염 문제 해결을 위한 과학적 솔루션을 제공합니다. 이 프로젝트는 환경 및 기후 분야의 인프라 발전을 목표로 하며 VN-ENV-IND-1894 및 VN-EV-2030 계획과 연계됩니다.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>RTI International conducts an industrial risk study on air and water pollution in Vietnam to provide science-based environmental solutions. This initiative supports infrastructure goals in the Environment &amp; Climate sector, aligning with the VN-ENV-IND-1894 and VN-EV-2030 strategic plans.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Study Reveals Water and Air Pollution Risks in Vietnam — Environmental study finds elevated lead, manganese, and PM2.5 pollution affecting workers and families near Hanoi's industrial zones. (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>RTI International thực hiện nghiên cứu rủi ro công nghiệp về ô nhiễm không khí và nguồn nước tại Việt Nam nhằm đưa ra các giải pháp khoa học. Dự án này hỗ trợ phát triển hạ tầng trong lĩnh vực Môi trường &amp; Khí hậu, phù hợp với các kế hoạch VN-ENV-IND-1894 và VN-EV-2030.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -10546,17 +10546,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (관련: VN-ENV-IND-1894)</t>
+          <t>베트남은 급격한 산업화로 인해 경제 성장을 이루었으나 공기, 수질 및 토양 자원에 심각한 부담을 주고 있습니다. 하노이와 호치민시의 미세먼지 오염이 심각하며, 산업 단지 인근의 폐수 무단 방류로 인해 '죽은 강'이 늘어나고 있습니다.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (Related: VN-ENV-IND-1894)</t>
+          <t>Vietnam's rapid industrialization has driven economic growth but caused severe strain on air, water, and soil resources. Major cities face critical PM2.5 pollution from industrial zones and transport, while untreated wastewater from textile and electronic sectors is creating "dead rivers" and contaminating groundwater.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] ENVIRONMENTAL IMPACT OF INDUSTRIALIZATION — This report examines the environmental impact of industrialization in Vietnam, highlighting air and water pollution, solid waste issues, and the challenges ... (Liên quan: VN-ENV-IND-1894)</t>
+          <t>Quá trình công nghiệp hóa nhanh chóng của Việt Nam đã thúc đẩy kinh tế nhưng gây áp lực lớn lên tài nguyên không khí, nước và đất. Các thành phố lớn đang đối mặt với ô nhiễm bụi mịn nghiêm trọng, trong khi nước thải chưa qua xử lý từ các khu công nghiệp đang tạo ra những "dòng sông chết" và đe dọa nguồn nước ngầm.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -10610,17 +10610,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (관련: VN-ENV-IND-1894)</t>
+          <t>베트남은 2025년까지 산림 피복률을 42.03%로 유지하고 1,300만 달러 규모의 오존층 파괴 물질 감축 프로젝트를 시작했습니다. 하노이와 호치민시는 2027년부터 이륜차 배기가스 검사를 시행하며, 2030년까지 전국으로 확대할 계획입니다.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (Related: VN-ENV-IND-1894)</t>
+          <t>Vietnam has maintained a stable forest coverage of 42.03% as of 2025 and launched a 13 million USD project to phase out ozone-depleting substances by 2031. Additionally, the country will implement mandatory motorcycle emissions testing in major cities starting in 2027, expanding nationwide by 2030.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam's green horizon: A 2025-2030 plan for ... — Air pollution control equipment is projected to cover 60%-70% of domestic needs, while solid and hazardous waste treatment technologies are to ... (Liên quan: VN-ENV-IND-1894)</t>
+          <t>Việt Nam duy trì tỷ lệ che phủ rừng ổn định ở mức 42,03% vào năm 2025 và triển khai dự án 13 triệu USD nhằm loại bỏ các chất làm suy giảm tầng ozone. Bên cạnh đó, lộ trình kiểm định khí thải xe máy sẽ bắt đầu tại Hà Nội và TP.HCM từ năm 2027, sau đó mở rộng ra toàn quốc vào năm 2030.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -10670,17 +10670,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>베트남 산업단지의 약 79%가 중앙 집중식 폐수 처리 시스템을 갖추고 있으나, 많은 곳이 비효율적으로 운영되거나 환경 기준을 충족하지 못하고 있습니다. 산업 클러스터(CCN)의 경우 단 5%만이 처리 시설을 보유하고 있으며, 고형 및 유해 폐기물 수집 시설의 부족이 심각한 환경 오염의 원인이 되고 있습니다.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>Approximately 79% of Vietnam's operating industrial zones have built centralized wastewater treatment systems, yet many face operational inefficiencies and fail to meet national environmental standards. Industrial clusters (CCNs) lag significantly with only a 5% coverage rate, and the lack of dedicated collection and treatment centers for hazardous solid waste continues to pressure natural ecosystems.</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Current status of industrial waste management in Vietnam — Especially, industrial zones that have not yet built and operated wastewater treatment stations cause even greater environmental pollution, such as Cau Ngan ... (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>Khoảng 79% các khu công nghiệp tại Việt Nam đã xây dựng hệ thống xử lý nước thải tập trung, nhưng nhiều nơi vận hành chưa hiệu quả và chưa đạt quy chuẩn môi trường. Các cụm công nghiệp (CCN) chỉ có khoảng 5% có hệ thống xử lý, đồng thời việc thiếu hụt các trung tâm thu gom và xử lý chất thải rắn nguy hại đang gây áp lực lớn lên hệ sinh thái và sức khỏe con người.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -10730,17 +10730,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (관련: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>베트남 기획투자부는 지속 가능한 산업 발전을 촉진하기 위해 산업 환경 지수를 도입할 계획이라고 발표했습니다. 이 지수는 2021-2030 녹색 성장 전략의 일환으로, 400개 이상의 산업 단지와 18개 경제 구역의 환경 오염 문제를 해결하고 2050년 탄소 중립 목표 달성을 돕는 것을 목표로 합니다.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (Related: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>The Vietnamese Ministry of Planning has announced plans to implement an Industrial Environmental Index to promote sustainable industrial development across its 400+ industrial parks. This initiative is part of the country's 2021-2030 green growth strategy and aims to mitigate severe industrial pollution while aligning with the national goal of reaching net-zero emissions by 2050.</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>[Environment &amp; Climate] Vietnam To Set Up Industrial Environmental Index — Vietnam has developed industrial zones ... zones would significantly resolve environmental issues, reduce waste, and achieve sustainable development. (Liên quan: VN-ENV-IND-1894, VN-EV-2030)</t>
+          <t>Bộ Kế hoạch và Đầu tư Việt Nam vừa công bố kế hoạch triển khai bộ chỉ số môi trường công nghiệp nhằm thúc đẩy phát triển công nghiệp bền vững. Đây là một phần trong chiến lược tăng trưởng xanh giai đoạn 2021-2030, hướng tới mục tiêu giải quyết vấn đề ô nhiễm tại các khu công nghiệp và đạt phát thải ròng bằng 0 vào năm 2050.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
